--- a/DecompositionLU/docs/statistics.xlsx
+++ b/DecompositionLU/docs/statistics.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maxim\source\repos\practice\SECOND_COURSE\FOR_ITLAB\ITLAB_LU_decomposition\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maxim\source\repos\practice\SECOND_COURSE\FOR_ITLAB\ArchBenchs\DecompositionLU\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CF8FF89-6E67-47AD-AB2F-9EB25CAEC3C0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41A68739-CF7C-43FF-A221-C9063AB72525}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-114" yWindow="-114" windowWidth="27602" windowHeight="15027" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="78">
   <si>
     <t>Я не уверен, будет ли это использоваться в готовой презентации и так ли это надо делать, если да, так что пока считаем, что файл для личного пользования.</t>
   </si>
@@ -248,9 +248,6 @@
     <t>а тут логично…</t>
   </si>
   <si>
-    <t xml:space="preserve"> ( сек)</t>
-  </si>
-  <si>
     <t>~1162</t>
   </si>
   <si>
@@ -312,6 +309,24 @@
   </si>
   <si>
     <t>Версия 2.0 (распараллеленная версия 1.1)</t>
+  </si>
+  <si>
+    <t>~154</t>
+  </si>
+  <si>
+    <t>~7321 (7,3 сек)</t>
+  </si>
+  <si>
+    <t>~7475 (7,5 сек)</t>
+  </si>
+  <si>
+    <t>~21</t>
+  </si>
+  <si>
+    <t>~61</t>
+  </si>
+  <si>
+    <t>~82</t>
   </si>
 </sst>
 </file>
@@ -404,7 +419,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -464,11 +479,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -516,6 +540,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1400,7 +1427,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B31" s="13"/>
       <c r="C31" s="13"/>
@@ -1449,16 +1476,16 @@
         <v>7</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -1466,19 +1493,19 @@
         <v>8</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -1486,16 +1513,16 @@
         <v>9</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1511,52 +1538,64 @@
       <c r="A39" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B39" s="9"/>
-      <c r="C39" s="10"/>
+      <c r="B39" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>72</v>
+      </c>
       <c r="D39" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B40" s="9"/>
+      <c r="B40" s="9" t="s">
+        <v>76</v>
+      </c>
       <c r="C40" s="10" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B41" s="9"/>
+      <c r="B41" s="9" t="s">
+        <v>77</v>
+      </c>
       <c r="C41" s="10" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E41" s="10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B42" s="20" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E42" s="1" t="s">
-        <v>68</v>
-      </c>
+      <c r="C42" s="20"/>
+      <c r="D42" s="20"/>
+      <c r="E42" s="20"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
+    <mergeCell ref="B42:E42"/>
     <mergeCell ref="A31:E31"/>
     <mergeCell ref="B32:E32"/>
     <mergeCell ref="A34:E34"/>

--- a/DecompositionLU/docs/statistics.xlsx
+++ b/DecompositionLU/docs/statistics.xlsx
@@ -8,24 +8,31 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maxim\source\repos\practice\SECOND_COURSE\FOR_ITLAB\ArchBenchs\DecompositionLU\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41A68739-CF7C-43FF-A221-C9063AB72525}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BF38F48-B947-4425-AE12-16D6FDB9CE80}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-114" yWindow="-114" windowWidth="27602" windowHeight="15027" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet name="Таблица" sheetId="1" r:id="rId1"/>
+    <sheet name="Графики" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="82">
   <si>
     <t>Я не уверен, будет ли это использоваться в готовой презентации и так ли это надо делать, если да, так что пока считаем, что файл для личного пользования.</t>
   </si>
@@ -251,9 +258,6 @@
     <t>~1162</t>
   </si>
   <si>
-    <t>чет очень скромное ускорение</t>
-  </si>
-  <si>
     <t>~673</t>
   </si>
   <si>
@@ -327,13 +331,28 @@
   </si>
   <si>
     <t>~82</t>
+  </si>
+  <si>
+    <t>Кол-во потоков</t>
+  </si>
+  <si>
+    <t>Время вычисления</t>
+  </si>
+  <si>
+    <t>n = 5000</t>
+  </si>
+  <si>
+    <t>n = 3000</t>
+  </si>
+  <si>
+    <t>Я искренне не понимаю этих результатов</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -398,6 +417,43 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="GOST Common"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="GOST Common"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="14"/>
+      <color rgb="FF0070C0"/>
+      <name val="GOST Common"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="14"/>
+      <name val="GOST Common"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="GOST Common"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -419,7 +475,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -488,11 +544,48 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -520,6 +613,16 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -528,9 +631,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -541,8 +641,60 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -559,6 +711,1704 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="104"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="4"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>n = 5000</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Графики!$C$4:$C$19</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>40525</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>40933</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>35748</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>34657</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>36335</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>38071</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>36151</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>37594</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>36727</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>36931</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>38323</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>40896</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>38132</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>38962</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>38825</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>39364</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-DFDA-4FBA-8E35-21ED64A1AC56}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="2034815519"/>
+        <c:axId val="1972086687"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="2034815519"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1972086687"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1972086687"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="34000"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2034815519"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="108"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="8"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>n = 3000</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Графики!$D$4:$D$19</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="0">
+                  <c:v>8737</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8116</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8005</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7387</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6863</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7472</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6861</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7389</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>7908</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>8155</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>7985</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>8411</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>8314</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>8287</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>8452</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>7844</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8747-4A5E-85F4-772AAE4EC689}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="52875439"/>
+        <c:axId val="1972084607"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="52875439"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1972084607"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1972084607"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="6500"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="52875439"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="15">
+  <a:schemeClr val="accent2"/>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="19">
+  <a:schemeClr val="accent6"/>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -728,6 +2578,83 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>9052</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>13579</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>525100</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>40739</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Диаграмма 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9C1BB01-F75F-4D40-BA20-D7288523072B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>9052</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>13579</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>525100</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>176542</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Диаграмма 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63E3D050-E508-4926-853F-B56EA689B234}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -994,15 +2921,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T42"/>
+  <dimension ref="A1:W42"/>
   <sheetFormatPr defaultRowHeight="17.850000000000001" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="71.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="65.7109375" style="1" customWidth="1"/>
     <col min="2" max="5" width="26.7109375" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="6" max="6" width="9.140625" style="1"/>
+    <col min="7" max="7" width="23.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="24.85546875" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -1026,7 +2956,7 @@
       <c r="S1" s="2"/>
       <c r="T1" s="2"/>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1050,7 +2980,7 @@
       <c r="S2" s="2"/>
       <c r="T2" s="2"/>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
@@ -1068,39 +2998,43 @@
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
     </row>
-    <row r="5" spans="1:20" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
+    <row r="5" spans="1:23" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="G5" s="16" t="s">
+      <c r="B5" s="38"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="39"/>
+      <c r="G5" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
-      <c r="J5" s="16"/>
-      <c r="K5" s="16"/>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="H5" s="15"/>
+      <c r="S5" s="5"/>
+      <c r="T5" s="14"/>
+      <c r="U5" s="14"/>
+      <c r="V5" s="14"/>
+      <c r="W5" s="14"/>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="16"/>
-      <c r="K6" s="16"/>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="S6" s="14"/>
+      <c r="T6" s="14"/>
+      <c r="U6" s="14"/>
+      <c r="V6" s="14"/>
+      <c r="W6" s="14"/>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
@@ -1116,27 +3050,31 @@
       <c r="E7" s="8">
         <v>10000</v>
       </c>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="16"/>
-      <c r="J7" s="16"/>
-      <c r="K7" s="16"/>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
+      <c r="G7" s="15"/>
+      <c r="H7" s="15"/>
+      <c r="S7" s="14"/>
+      <c r="T7" s="14"/>
+      <c r="U7" s="14"/>
+      <c r="V7" s="14"/>
+      <c r="W7" s="14"/>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A8" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="S8" s="14"/>
+      <c r="T8" s="14"/>
+      <c r="U8" s="14"/>
+      <c r="V8" s="14"/>
+      <c r="W8" s="14"/>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
@@ -1152,13 +3090,13 @@
       <c r="E9" s="10">
         <v>1746</v>
       </c>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
-      <c r="K9" s="16"/>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="S9" s="14"/>
+      <c r="T9" s="14"/>
+      <c r="U9" s="14"/>
+      <c r="V9" s="14"/>
+      <c r="W9" s="14"/>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>8</v>
       </c>
@@ -1174,8 +3112,13 @@
       <c r="E10" s="10" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="S10" s="5"/>
+      <c r="T10" s="5"/>
+      <c r="U10" s="5"/>
+      <c r="V10" s="5"/>
+      <c r="W10" s="5"/>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>9</v>
       </c>
@@ -1193,19 +3136,23 @@
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A12" s="15" t="s">
+      <c r="S11" s="5"/>
+      <c r="T11" s="5"/>
+      <c r="U11" s="5"/>
+      <c r="V11" s="5"/>
+      <c r="W11" s="5"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A12" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
       <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>7</v>
       </c>
@@ -1215,16 +3162,15 @@
       <c r="C13" s="10">
         <v>232</v>
       </c>
-      <c r="D13" s="17" t="s">
+      <c r="D13" s="20" t="s">
         <v>21</v>
       </c>
       <c r="E13" s="10">
         <v>1811</v>
       </c>
       <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1234,7 +3180,7 @@
       <c r="C14" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="18"/>
+      <c r="D14" s="21"/>
       <c r="E14" s="10" t="s">
         <v>10</v>
       </c>
@@ -1242,7 +3188,7 @@
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>9</v>
       </c>
@@ -1252,32 +3198,32 @@
       <c r="C15" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="19"/>
+      <c r="D15" s="22"/>
       <c r="E15" s="10" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="13" t="s">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B19" s="14" t="s">
+      <c r="B19" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>6</v>
       </c>
@@ -1294,16 +3240,16 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="15" t="s">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B21" s="15"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>7</v>
       </c>
@@ -1320,7 +3266,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>8</v>
       </c>
@@ -1337,7 +3283,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>9</v>
       </c>
@@ -1353,17 +3299,23 @@
       <c r="E24" s="10" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="15" t="s">
+      <c r="G24" s="29"/>
+      <c r="H24" s="30"/>
+      <c r="I24" s="30"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="B25" s="15"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="G25" s="31"/>
+      <c r="H25" s="26"/>
+      <c r="I25" s="26"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>7</v>
       </c>
@@ -1379,8 +3331,11 @@
       <c r="E26" s="10" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G26" s="32"/>
+      <c r="H26" s="33"/>
+      <c r="I26" s="34"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>8</v>
       </c>
@@ -1396,8 +3351,11 @@
       <c r="E27" s="10" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G27" s="32"/>
+      <c r="H27" s="33"/>
+      <c r="I27" s="29"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>9</v>
       </c>
@@ -1413,8 +3371,11 @@
       <c r="E28" s="10" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G28" s="35"/>
+      <c r="H28" s="29"/>
+      <c r="I28" s="29"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C29" s="1" t="s">
         <v>40</v>
       </c>
@@ -1424,28 +3385,42 @@
       <c r="E29" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="B31" s="13"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G29" s="32"/>
+      <c r="H29" s="33"/>
+      <c r="I29" s="29"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G30" s="35"/>
+      <c r="H30" s="29"/>
+      <c r="I30" s="29"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="B31" s="17"/>
+      <c r="C31" s="17"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="G31" s="32"/>
+      <c r="H31" s="33"/>
+      <c r="I31" s="29"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B32" s="14" t="s">
+      <c r="B32" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="G32" s="35"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="29"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>6</v>
       </c>
@@ -1461,146 +3436,171 @@
       <c r="E33" s="8">
         <v>10000</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="15" t="s">
+      <c r="G33" s="32"/>
+      <c r="H33" s="33"/>
+      <c r="I33" s="29"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B34" s="15"/>
-      <c r="C34" s="15"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="G34" s="35"/>
+      <c r="H34" s="29"/>
+      <c r="I34" s="29"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G35" s="35"/>
+      <c r="H35" s="29"/>
+      <c r="I35" s="29"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+      <c r="G36" s="35"/>
+      <c r="H36" s="29"/>
+      <c r="I36" s="29"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="G37" s="32"/>
+      <c r="H37" s="33"/>
+      <c r="I37" s="29"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="B38" s="15"/>
-      <c r="C38" s="15"/>
-      <c r="D38" s="15"/>
-      <c r="E38" s="15"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B38" s="19"/>
+      <c r="C38" s="19"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="19"/>
+      <c r="G38" s="35"/>
+      <c r="H38" s="29"/>
+      <c r="I38" s="29"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+      <c r="G39" s="35"/>
+      <c r="H39" s="29"/>
+      <c r="I39" s="29"/>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+      <c r="G40" s="35"/>
+      <c r="H40" s="29"/>
+      <c r="I40" s="29"/>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E41" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="G41" s="32"/>
+      <c r="H41" s="33"/>
+      <c r="I41" s="29"/>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B42" s="16" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B42" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="C42" s="20"/>
-      <c r="D42" s="20"/>
-      <c r="E42" s="20"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="16"/>
+      <c r="E42" s="16"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="16">
+    <mergeCell ref="H24:I24"/>
+    <mergeCell ref="G5:H8"/>
     <mergeCell ref="B42:E42"/>
     <mergeCell ref="A31:E31"/>
     <mergeCell ref="B32:E32"/>
     <mergeCell ref="A34:E34"/>
     <mergeCell ref="A38:E38"/>
-    <mergeCell ref="G5:K9"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="A12:E12"/>
     <mergeCell ref="A8:E8"/>
@@ -1616,4 +3616,232 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09C7CB48-3C9F-48A0-8672-FA001DBD72EC}">
+  <dimension ref="B2:E24"/>
+  <sheetFormatPr defaultRowHeight="13.55" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="42"/>
+    <col min="2" max="2" width="23.140625" style="42" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="21.28515625" style="42" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="42"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" ht="17.850000000000001" x14ac:dyDescent="0.25">
+      <c r="B2" s="25"/>
+      <c r="C2" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="D2" s="27"/>
+    </row>
+    <row r="3" spans="2:5" ht="17.850000000000001" x14ac:dyDescent="0.25">
+      <c r="B3" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C3" s="41" t="s">
+        <v>79</v>
+      </c>
+      <c r="D3" s="41" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" ht="17.850000000000001" x14ac:dyDescent="0.25">
+      <c r="B4" s="23">
+        <v>1</v>
+      </c>
+      <c r="C4" s="36">
+        <v>40525</v>
+      </c>
+      <c r="D4" s="28">
+        <v>8737</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" ht="17.850000000000001" x14ac:dyDescent="0.25">
+      <c r="B5" s="23">
+        <v>2</v>
+      </c>
+      <c r="C5" s="36">
+        <v>40933</v>
+      </c>
+      <c r="D5" s="28">
+        <v>8116</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" ht="17.850000000000001" x14ac:dyDescent="0.25">
+      <c r="B6" s="24">
+        <v>3</v>
+      </c>
+      <c r="C6" s="24">
+        <v>35748</v>
+      </c>
+      <c r="D6" s="24">
+        <v>8005</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" ht="17.850000000000001" x14ac:dyDescent="0.25">
+      <c r="B7" s="23">
+        <v>4</v>
+      </c>
+      <c r="C7" s="36">
+        <v>34657</v>
+      </c>
+      <c r="D7" s="28">
+        <v>7387</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" ht="17.850000000000001" x14ac:dyDescent="0.25">
+      <c r="B8" s="24">
+        <v>5</v>
+      </c>
+      <c r="C8" s="24">
+        <v>36335</v>
+      </c>
+      <c r="D8" s="24">
+        <v>6863</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" ht="17.850000000000001" x14ac:dyDescent="0.25">
+      <c r="B9" s="23">
+        <v>6</v>
+      </c>
+      <c r="C9" s="36">
+        <v>38071</v>
+      </c>
+      <c r="D9" s="28">
+        <v>7472</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" ht="17.850000000000001" x14ac:dyDescent="0.25">
+      <c r="B10" s="24">
+        <v>7</v>
+      </c>
+      <c r="C10" s="24">
+        <v>36151</v>
+      </c>
+      <c r="D10" s="24">
+        <v>6861</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" ht="17.850000000000001" x14ac:dyDescent="0.25">
+      <c r="B11" s="23">
+        <v>8</v>
+      </c>
+      <c r="C11" s="36">
+        <v>37594</v>
+      </c>
+      <c r="D11" s="28">
+        <v>7389</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" ht="17.850000000000001" x14ac:dyDescent="0.25">
+      <c r="B12" s="24">
+        <v>9</v>
+      </c>
+      <c r="C12" s="24">
+        <v>36727</v>
+      </c>
+      <c r="D12" s="24">
+        <v>7908</v>
+      </c>
+      <c r="E12" s="43"/>
+    </row>
+    <row r="13" spans="2:5" ht="17.850000000000001" x14ac:dyDescent="0.25">
+      <c r="B13" s="24">
+        <v>10</v>
+      </c>
+      <c r="C13" s="24">
+        <v>36931</v>
+      </c>
+      <c r="D13" s="24">
+        <v>8155</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" ht="17.850000000000001" x14ac:dyDescent="0.25">
+      <c r="B14" s="24">
+        <v>11</v>
+      </c>
+      <c r="C14" s="24">
+        <v>38323</v>
+      </c>
+      <c r="D14" s="24">
+        <v>7985</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" ht="17.850000000000001" x14ac:dyDescent="0.25">
+      <c r="B15" s="23">
+        <v>12</v>
+      </c>
+      <c r="C15" s="36">
+        <v>40896</v>
+      </c>
+      <c r="D15" s="28">
+        <v>8411</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" ht="17.850000000000001" x14ac:dyDescent="0.25">
+      <c r="B16" s="24">
+        <v>13</v>
+      </c>
+      <c r="C16" s="24">
+        <v>38132</v>
+      </c>
+      <c r="D16" s="24">
+        <v>8314</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" ht="17.850000000000001" x14ac:dyDescent="0.25">
+      <c r="B17" s="24">
+        <v>14</v>
+      </c>
+      <c r="C17" s="24">
+        <v>38962</v>
+      </c>
+      <c r="D17" s="24">
+        <v>8287</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" ht="17.850000000000001" x14ac:dyDescent="0.25">
+      <c r="B18" s="24">
+        <v>15</v>
+      </c>
+      <c r="C18" s="24">
+        <v>38825</v>
+      </c>
+      <c r="D18" s="24">
+        <v>8452</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" ht="17.850000000000001" x14ac:dyDescent="0.25">
+      <c r="B19" s="23">
+        <v>16</v>
+      </c>
+      <c r="C19" s="36">
+        <v>39364</v>
+      </c>
+      <c r="D19" s="28">
+        <v>7844</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" ht="17.850000000000001" x14ac:dyDescent="0.2">
+      <c r="C20" s="40">
+        <v>4</v>
+      </c>
+      <c r="D20" s="40">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" ht="17.850000000000001" x14ac:dyDescent="0.25">
+      <c r="B24" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/DecompositionLU/docs/statistics.xlsx
+++ b/DecompositionLU/docs/statistics.xlsx
@@ -1,24 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4505"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maxim\source\repos\practice\SECOND_COURSE\FOR_ITLAB\ArchBenchs\DecompositionLU\docs\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BF38F48-B947-4425-AE12-16D6FDB9CE80}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-114" yWindow="-114" windowWidth="27602" windowHeight="15027" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="27600" windowHeight="15030" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Таблица" sheetId="1" r:id="rId1"/>
     <sheet name="Графики" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <calcPr calcId="124519"/>
+  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -32,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="82">
   <si>
     <t>Я не уверен, будет ли это использоваться в готовой презентации и так ли это надо делать, если да, так что пока считаем, что файл для личного пользования.</t>
   </si>
@@ -351,8 +345,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -617,30 +611,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -651,16 +621,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -678,15 +642,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -695,6 +650,45 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -714,18 +708,9 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="ru-RU"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="104"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="4"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
+  <c:style val="4"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -753,7 +738,7 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:overlay val="0"/>
+      <c:layout/>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -761,33 +746,11 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="ru-RU"/>
-        </a:p>
-      </c:txPr>
     </c:title>
-    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
         <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -872,35 +835,24 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-DFDA-4FBA-8E35-21ED64A1AC56}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
+        <c:dLbls/>
         <c:marker val="1"/>
-        <c:smooth val="0"/>
-        <c:axId val="2034815519"/>
-        <c:axId val="1972086687"/>
+        <c:axId val="153173376"/>
+        <c:axId val="153175168"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="2034815519"/>
+        <c:axId val="153173376"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
@@ -935,20 +887,18 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1972086687"/>
+        <c:crossAx val="153175168"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1972086687"/>
+        <c:axId val="153175168"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="34000"/>
         </c:scaling>
-        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines>
           <c:spPr>
@@ -966,7 +916,6 @@
         </c:majorGridlines>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
@@ -995,7 +944,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2034815519"/>
+        <c:crossAx val="153173376"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1009,14 +958,13 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:extLst>
+    <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
           <c16r3:dispNaAsBlank val="1"/>
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1047,25 +995,16 @@
   </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageMargins b="0.75000000000000011" l="0.70000000000000007" r="0.70000000000000007" t="0.75000000000000011" header="0.30000000000000004" footer="0.30000000000000004"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:lang val="ru-RU"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="108"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="8"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
+  <c:style val="8"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -1093,7 +1032,7 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:overlay val="0"/>
+      <c:layout/>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -1101,33 +1040,11 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="ru-RU"/>
-        </a:p>
-      </c:txPr>
     </c:title>
-    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
         <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -1212,35 +1129,24 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-8747-4A5E-85F4-772AAE4EC689}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
+        <c:dLbls/>
         <c:marker val="1"/>
-        <c:smooth val="0"/>
-        <c:axId val="52875439"/>
-        <c:axId val="1972084607"/>
+        <c:axId val="153621248"/>
+        <c:axId val="153622784"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="52875439"/>
+        <c:axId val="153621248"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
@@ -1275,20 +1181,18 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1972084607"/>
+        <c:crossAx val="153622784"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1972084607"/>
+        <c:axId val="153622784"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="6500"/>
         </c:scaling>
-        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines>
           <c:spPr>
@@ -1306,7 +1210,6 @@
         </c:majorGridlines>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
@@ -1335,7 +1238,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="52875439"/>
+        <c:crossAx val="153621248"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1349,14 +1252,13 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:extLst>
+    <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
           <c16r3:dispNaAsBlank val="1"/>
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1387,1028 +1289,118 @@
   </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageMargins b="0.75000000000000011" l="0.70000000000000007" r="0.70000000000000007" t="0.75000000000000011" header="0.30000000000000004" footer="0.30000000000000004"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="15">
-  <a:schemeClr val="accent2"/>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="19">
-  <a:schemeClr val="accent6"/>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="ru-RU"/>
+  <c:chart>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Графики!$O$4:$O$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Графики!$Q$4:$Q$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>4557</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3948</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4020</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3448</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3996</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+        </c:ser>
+        <c:axId val="54167424"/>
+        <c:axId val="54165888"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="54167424"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="54165888"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="54165888"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="54167424"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2426,7 +1418,7 @@
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{77301E52-0432-4D04-B3B3-00D890F3A041}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{77301E52-0432-4D04-B3B3-00D890F3A041}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2481,7 +1473,7 @@
         <xdr:cNvPr id="3" name="TextBox 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A60DEF0B-7AC5-4BE9-B97A-367940A351A6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A60DEF0B-7AC5-4BE9-B97A-367940A351A6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2536,7 +1528,7 @@
         <xdr:cNvPr id="4" name="TextBox 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35C2101E-3BC3-486A-87D7-AB0DA6ED7DA8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{35C2101E-3BC3-486A-87D7-AB0DA6ED7DA8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2601,7 +1593,7 @@
         <xdr:cNvPr id="5" name="Диаграмма 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9C1BB01-F75F-4D40-BA20-D7288523072B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{D9C1BB01-F75F-4D40-BA20-D7288523072B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2637,7 +1629,7 @@
         <xdr:cNvPr id="7" name="Диаграмма 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63E3D050-E508-4926-853F-B56EA689B234}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{63E3D050-E508-4926-853F-B56EA689B234}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2650,6 +1642,36 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>561975</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Диаграмма 7"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2701,7 +1723,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
@@ -2736,7 +1758,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
@@ -2913,16 +1935,16 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:W42"/>
-  <sheetFormatPr defaultRowHeight="17.850000000000001" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="65.7109375" style="1" customWidth="1"/>
     <col min="2" max="5" width="26.7109375" style="1" customWidth="1"/>
@@ -2932,7 +1954,7 @@
     <col min="10" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -2956,7 +1978,7 @@
       <c r="S1" s="2"/>
       <c r="T1" s="2"/>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -2980,7 +2002,7 @@
       <c r="S2" s="2"/>
       <c r="T2" s="2"/>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23">
       <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
@@ -2998,7 +2020,7 @@
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
     </row>
-    <row r="5" spans="1:23" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" ht="17.850000000000001" customHeight="1">
       <c r="A5" s="37" t="s">
         <v>22</v>
       </c>
@@ -3006,35 +2028,35 @@
       <c r="C5" s="38"/>
       <c r="D5" s="38"/>
       <c r="E5" s="39"/>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="H5" s="15"/>
+      <c r="H5" s="32"/>
       <c r="S5" s="5"/>
       <c r="T5" s="14"/>
       <c r="U5" s="14"/>
       <c r="V5" s="14"/>
       <c r="W5" s="14"/>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" ht="18.75">
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="35"/>
+      <c r="G6" s="32"/>
+      <c r="H6" s="32"/>
       <c r="S6" s="14"/>
       <c r="T6" s="14"/>
       <c r="U6" s="14"/>
       <c r="V6" s="14"/>
       <c r="W6" s="14"/>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" ht="18.75">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
@@ -3050,31 +2072,31 @@
       <c r="E7" s="8">
         <v>10000</v>
       </c>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
+      <c r="G7" s="32"/>
+      <c r="H7" s="32"/>
       <c r="S7" s="14"/>
       <c r="T7" s="14"/>
       <c r="U7" s="14"/>
       <c r="V7" s="14"/>
       <c r="W7" s="14"/>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
+    <row r="8" spans="1:23" ht="18.75">
+      <c r="A8" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
+      <c r="B8" s="36"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="32"/>
       <c r="S8" s="14"/>
       <c r="T8" s="14"/>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
       <c r="W8" s="14"/>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" ht="18.75">
       <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
@@ -3096,7 +2118,7 @@
       <c r="V9" s="14"/>
       <c r="W9" s="14"/>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23">
       <c r="A10" s="3" t="s">
         <v>8</v>
       </c>
@@ -3118,7 +2140,7 @@
       <c r="V10" s="5"/>
       <c r="W10" s="5"/>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23">
       <c r="A11" s="3" t="s">
         <v>9</v>
       </c>
@@ -3142,17 +2164,17 @@
       <c r="V11" s="5"/>
       <c r="W11" s="5"/>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
+    <row r="12" spans="1:23">
+      <c r="A12" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
+      <c r="B12" s="36"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
       <c r="F12" s="5"/>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23">
       <c r="A13" s="3" t="s">
         <v>7</v>
       </c>
@@ -3162,7 +2184,7 @@
       <c r="C13" s="10">
         <v>232</v>
       </c>
-      <c r="D13" s="20" t="s">
+      <c r="D13" s="40" t="s">
         <v>21</v>
       </c>
       <c r="E13" s="10">
@@ -3170,7 +2192,7 @@
       </c>
       <c r="F13" s="5"/>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23">
       <c r="A14" s="3" t="s">
         <v>8</v>
       </c>
@@ -3180,7 +2202,7 @@
       <c r="C14" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="21"/>
+      <c r="D14" s="41"/>
       <c r="E14" s="10" t="s">
         <v>10</v>
       </c>
@@ -3188,7 +2210,7 @@
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23">
       <c r="A15" s="3" t="s">
         <v>9</v>
       </c>
@@ -3198,32 +2220,32 @@
       <c r="C15" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="22"/>
+      <c r="D15" s="42"/>
       <c r="E15" s="10" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="17" t="s">
+    <row r="18" spans="1:9">
+      <c r="A18" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B18" s="34"/>
+      <c r="C18" s="34"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="34"/>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B19" s="18" t="s">
+      <c r="B19" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C19" s="35"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="35"/>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="3" t="s">
         <v>6</v>
       </c>
@@ -3240,16 +2262,16 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="19" t="s">
+    <row r="21" spans="1:9">
+      <c r="A21" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B21" s="36"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" s="3" t="s">
         <v>7</v>
       </c>
@@ -3266,7 +2288,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9">
       <c r="A23" s="3" t="s">
         <v>8</v>
       </c>
@@ -3283,7 +2305,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9">
       <c r="A24" s="3" t="s">
         <v>9</v>
       </c>
@@ -3299,23 +2321,23 @@
       <c r="E24" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="G24" s="29"/>
-      <c r="H24" s="30"/>
-      <c r="I24" s="30"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="19" t="s">
+      <c r="G24" s="20"/>
+      <c r="H24" s="31"/>
+      <c r="I24" s="31"/>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="G25" s="31"/>
-      <c r="H25" s="26"/>
-      <c r="I25" s="26"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B25" s="36"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="36"/>
+      <c r="E25" s="36"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="18"/>
+    </row>
+    <row r="26" spans="1:9" ht="18.75">
       <c r="A26" s="3" t="s">
         <v>7</v>
       </c>
@@ -3331,11 +2353,11 @@
       <c r="E26" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="G26" s="32"/>
-      <c r="H26" s="33"/>
-      <c r="I26" s="34"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G26" s="22"/>
+      <c r="H26" s="23"/>
+      <c r="I26" s="24"/>
+    </row>
+    <row r="27" spans="1:9" ht="18.75">
       <c r="A27" s="3" t="s">
         <v>8</v>
       </c>
@@ -3351,11 +2373,11 @@
       <c r="E27" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="G27" s="32"/>
-      <c r="H27" s="33"/>
-      <c r="I27" s="29"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G27" s="22"/>
+      <c r="H27" s="23"/>
+      <c r="I27" s="20"/>
+    </row>
+    <row r="28" spans="1:9" ht="18.75">
       <c r="A28" s="3" t="s">
         <v>9</v>
       </c>
@@ -3371,11 +2393,11 @@
       <c r="E28" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="G28" s="35"/>
-      <c r="H28" s="29"/>
-      <c r="I28" s="29"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G28" s="25"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="20"/>
+    </row>
+    <row r="29" spans="1:9" ht="18.75">
       <c r="C29" s="1" t="s">
         <v>40</v>
       </c>
@@ -3385,42 +2407,42 @@
       <c r="E29" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G29" s="32"/>
-      <c r="H29" s="33"/>
-      <c r="I29" s="29"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G30" s="35"/>
-      <c r="H30" s="29"/>
-      <c r="I30" s="29"/>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="17" t="s">
+      <c r="G29" s="22"/>
+      <c r="H29" s="23"/>
+      <c r="I29" s="20"/>
+    </row>
+    <row r="30" spans="1:9" ht="18.75">
+      <c r="G30" s="25"/>
+      <c r="H30" s="20"/>
+      <c r="I30" s="20"/>
+    </row>
+    <row r="31" spans="1:9" ht="18.75">
+      <c r="A31" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="G31" s="32"/>
-      <c r="H31" s="33"/>
-      <c r="I31" s="29"/>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B31" s="34"/>
+      <c r="C31" s="34"/>
+      <c r="D31" s="34"/>
+      <c r="E31" s="34"/>
+      <c r="G31" s="22"/>
+      <c r="H31" s="23"/>
+      <c r="I31" s="20"/>
+    </row>
+    <row r="32" spans="1:9" ht="18.75">
       <c r="A32" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B32" s="18" t="s">
+      <c r="B32" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="G32" s="35"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="29"/>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C32" s="35"/>
+      <c r="D32" s="35"/>
+      <c r="E32" s="35"/>
+      <c r="G32" s="25"/>
+      <c r="H32" s="20"/>
+      <c r="I32" s="20"/>
+    </row>
+    <row r="33" spans="1:9" ht="18.75">
       <c r="A33" s="3" t="s">
         <v>6</v>
       </c>
@@ -3436,23 +2458,23 @@
       <c r="E33" s="8">
         <v>10000</v>
       </c>
-      <c r="G33" s="32"/>
-      <c r="H33" s="33"/>
-      <c r="I33" s="29"/>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="19" t="s">
+      <c r="G33" s="22"/>
+      <c r="H33" s="23"/>
+      <c r="I33" s="20"/>
+    </row>
+    <row r="34" spans="1:9" ht="18.75">
+      <c r="A34" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="B34" s="19"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="G34" s="35"/>
-      <c r="H34" s="29"/>
-      <c r="I34" s="29"/>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B34" s="36"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="20"/>
+      <c r="I34" s="20"/>
+    </row>
+    <row r="35" spans="1:9" ht="18.75">
       <c r="A35" s="3" t="s">
         <v>7</v>
       </c>
@@ -3468,11 +2490,11 @@
       <c r="E35" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="G35" s="35"/>
-      <c r="H35" s="29"/>
-      <c r="I35" s="29"/>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G35" s="25"/>
+      <c r="H35" s="20"/>
+      <c r="I35" s="20"/>
+    </row>
+    <row r="36" spans="1:9" ht="18.75">
       <c r="A36" s="3" t="s">
         <v>8</v>
       </c>
@@ -3488,11 +2510,11 @@
       <c r="E36" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="G36" s="35"/>
-      <c r="H36" s="29"/>
-      <c r="I36" s="29"/>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G36" s="25"/>
+      <c r="H36" s="20"/>
+      <c r="I36" s="20"/>
+    </row>
+    <row r="37" spans="1:9" ht="18.75">
       <c r="A37" s="3" t="s">
         <v>9</v>
       </c>
@@ -3508,23 +2530,23 @@
       <c r="E37" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="G37" s="32"/>
-      <c r="H37" s="33"/>
-      <c r="I37" s="29"/>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="19" t="s">
+      <c r="G37" s="22"/>
+      <c r="H37" s="23"/>
+      <c r="I37" s="20"/>
+    </row>
+    <row r="38" spans="1:9" ht="18.75">
+      <c r="A38" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="B38" s="19"/>
-      <c r="C38" s="19"/>
-      <c r="D38" s="19"/>
-      <c r="E38" s="19"/>
-      <c r="G38" s="35"/>
-      <c r="H38" s="29"/>
-      <c r="I38" s="29"/>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B38" s="36"/>
+      <c r="C38" s="36"/>
+      <c r="D38" s="36"/>
+      <c r="E38" s="36"/>
+      <c r="G38" s="25"/>
+      <c r="H38" s="20"/>
+      <c r="I38" s="20"/>
+    </row>
+    <row r="39" spans="1:9" ht="18.75">
       <c r="A39" s="3" t="s">
         <v>7</v>
       </c>
@@ -3540,11 +2562,11 @@
       <c r="E39" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="G39" s="35"/>
-      <c r="H39" s="29"/>
-      <c r="I39" s="29"/>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G39" s="25"/>
+      <c r="H39" s="20"/>
+      <c r="I39" s="20"/>
+    </row>
+    <row r="40" spans="1:9" ht="18.75">
       <c r="A40" s="3" t="s">
         <v>8</v>
       </c>
@@ -3560,11 +2582,11 @@
       <c r="E40" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="G40" s="35"/>
-      <c r="H40" s="29"/>
-      <c r="I40" s="29"/>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G40" s="25"/>
+      <c r="H40" s="20"/>
+      <c r="I40" s="20"/>
+    </row>
+    <row r="41" spans="1:9" ht="18.75">
       <c r="A41" s="3" t="s">
         <v>9</v>
       </c>
@@ -3580,17 +2602,17 @@
       <c r="E41" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="G41" s="32"/>
-      <c r="H41" s="33"/>
-      <c r="I41" s="29"/>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B42" s="16" t="s">
+      <c r="G41" s="22"/>
+      <c r="H41" s="23"/>
+      <c r="I41" s="20"/>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="B42" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="C42" s="16"/>
-      <c r="D42" s="16"/>
-      <c r="E42" s="16"/>
+      <c r="C42" s="33"/>
+      <c r="D42" s="33"/>
+      <c r="E42" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -3619,227 +2641,330 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09C7CB48-3C9F-48A0-8672-FA001DBD72EC}">
-  <dimension ref="B2:E24"/>
-  <sheetFormatPr defaultRowHeight="13.55" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="B2:Q24"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="42"/>
-    <col min="2" max="2" width="23.140625" style="42" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="21.28515625" style="42" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="42"/>
+    <col min="1" max="1" width="9.140625" style="29"/>
+    <col min="2" max="2" width="23.140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="21.28515625" style="29" customWidth="1"/>
+    <col min="5" max="14" width="9.140625" style="29"/>
+    <col min="15" max="15" width="23" style="29" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="15.28515625" style="29" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="29"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" ht="17.850000000000001" x14ac:dyDescent="0.25">
-      <c r="B2" s="25"/>
-      <c r="C2" s="27" t="s">
+    <row r="2" spans="2:17" ht="18">
+      <c r="B2" s="17"/>
+      <c r="C2" s="43" t="s">
         <v>78</v>
       </c>
-      <c r="D2" s="27"/>
-    </row>
-    <row r="3" spans="2:5" ht="17.850000000000001" x14ac:dyDescent="0.25">
+      <c r="D2" s="43"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="43" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q2" s="43"/>
+    </row>
+    <row r="3" spans="2:17" ht="18">
       <c r="B3" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C3" s="41" t="s">
+      <c r="C3" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="D3" s="41" t="s">
+      <c r="D3" s="28" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="4" spans="2:5" ht="17.850000000000001" x14ac:dyDescent="0.25">
-      <c r="B4" s="23">
+      <c r="O3" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="P3" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q3" s="28" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="2:17" ht="18.75">
+      <c r="B4" s="15">
         <v>1</v>
       </c>
-      <c r="C4" s="36">
+      <c r="C4" s="26">
         <v>40525</v>
       </c>
-      <c r="D4" s="28">
+      <c r="D4" s="19">
         <v>8737</v>
       </c>
-    </row>
-    <row r="5" spans="2:5" ht="17.850000000000001" x14ac:dyDescent="0.25">
-      <c r="B5" s="23">
+      <c r="O4" s="15">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="19">
+        <v>4557</v>
+      </c>
+    </row>
+    <row r="5" spans="2:17" ht="18.75">
+      <c r="B5" s="15">
         <v>2</v>
       </c>
-      <c r="C5" s="36">
+      <c r="C5" s="26">
         <v>40933</v>
       </c>
-      <c r="D5" s="28">
+      <c r="D5" s="19">
         <v>8116</v>
       </c>
-    </row>
-    <row r="6" spans="2:5" ht="17.850000000000001" x14ac:dyDescent="0.25">
-      <c r="B6" s="24">
+      <c r="O5" s="15">
+        <v>2</v>
+      </c>
+      <c r="Q5" s="19">
+        <v>3948</v>
+      </c>
+    </row>
+    <row r="6" spans="2:17" ht="18.75">
+      <c r="B6" s="16">
         <v>3</v>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="16">
         <v>35748</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="16">
         <v>8005</v>
       </c>
-    </row>
-    <row r="7" spans="2:5" ht="17.850000000000001" x14ac:dyDescent="0.25">
-      <c r="B7" s="23">
+      <c r="O6" s="16">
+        <v>3</v>
+      </c>
+      <c r="Q6" s="16">
+        <v>4020</v>
+      </c>
+    </row>
+    <row r="7" spans="2:17" ht="18.75">
+      <c r="B7" s="15">
         <v>4</v>
       </c>
-      <c r="C7" s="36">
+      <c r="C7" s="26">
         <v>34657</v>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="19">
         <v>7387</v>
       </c>
-    </row>
-    <row r="8" spans="2:5" ht="17.850000000000001" x14ac:dyDescent="0.25">
-      <c r="B8" s="24">
+      <c r="O7" s="15">
+        <v>4</v>
+      </c>
+      <c r="Q7" s="19">
+        <v>3448</v>
+      </c>
+    </row>
+    <row r="8" spans="2:17" ht="18.75">
+      <c r="B8" s="16">
         <v>5</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="16">
         <v>36335</v>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="16">
         <v>6863</v>
       </c>
-    </row>
-    <row r="9" spans="2:5" ht="17.850000000000001" x14ac:dyDescent="0.25">
-      <c r="B9" s="23">
+      <c r="O8" s="16">
+        <v>5</v>
+      </c>
+      <c r="Q8" s="16">
+        <v>3996</v>
+      </c>
+    </row>
+    <row r="9" spans="2:17" ht="18.75">
+      <c r="B9" s="15">
         <v>6</v>
       </c>
-      <c r="C9" s="36">
+      <c r="C9" s="26">
         <v>38071</v>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="19">
         <v>7472</v>
       </c>
-    </row>
-    <row r="10" spans="2:5" ht="17.850000000000001" x14ac:dyDescent="0.25">
-      <c r="B10" s="24">
+      <c r="O9" s="15">
+        <v>6</v>
+      </c>
+      <c r="P9" s="26"/>
+      <c r="Q9" s="19"/>
+    </row>
+    <row r="10" spans="2:17" ht="18.75">
+      <c r="B10" s="16">
         <v>7</v>
       </c>
-      <c r="C10" s="24">
+      <c r="C10" s="16">
         <v>36151</v>
       </c>
-      <c r="D10" s="24">
+      <c r="D10" s="16">
         <v>6861</v>
       </c>
-    </row>
-    <row r="11" spans="2:5" ht="17.850000000000001" x14ac:dyDescent="0.25">
-      <c r="B11" s="23">
+      <c r="O10" s="16">
+        <v>7</v>
+      </c>
+      <c r="P10" s="16"/>
+      <c r="Q10" s="16"/>
+    </row>
+    <row r="11" spans="2:17" ht="18.75">
+      <c r="B11" s="15">
         <v>8</v>
       </c>
-      <c r="C11" s="36">
+      <c r="C11" s="26">
         <v>37594</v>
       </c>
-      <c r="D11" s="28">
+      <c r="D11" s="19">
         <v>7389</v>
       </c>
-    </row>
-    <row r="12" spans="2:5" ht="17.850000000000001" x14ac:dyDescent="0.25">
-      <c r="B12" s="24">
+      <c r="O11" s="15">
+        <v>8</v>
+      </c>
+      <c r="P11" s="26"/>
+      <c r="Q11" s="19"/>
+    </row>
+    <row r="12" spans="2:17" ht="18.75">
+      <c r="B12" s="16">
         <v>9</v>
       </c>
-      <c r="C12" s="24">
+      <c r="C12" s="16">
         <v>36727</v>
       </c>
-      <c r="D12" s="24">
+      <c r="D12" s="16">
         <v>7908</v>
       </c>
-      <c r="E12" s="43"/>
-    </row>
-    <row r="13" spans="2:5" ht="17.850000000000001" x14ac:dyDescent="0.25">
-      <c r="B13" s="24">
+      <c r="E12" s="30"/>
+      <c r="O12" s="16">
+        <v>9</v>
+      </c>
+      <c r="P12" s="16"/>
+      <c r="Q12" s="16"/>
+    </row>
+    <row r="13" spans="2:17" ht="18.75">
+      <c r="B13" s="16">
         <v>10</v>
       </c>
-      <c r="C13" s="24">
+      <c r="C13" s="16">
         <v>36931</v>
       </c>
-      <c r="D13" s="24">
+      <c r="D13" s="16">
         <v>8155</v>
       </c>
-    </row>
-    <row r="14" spans="2:5" ht="17.850000000000001" x14ac:dyDescent="0.25">
-      <c r="B14" s="24">
+      <c r="O13" s="16">
+        <v>10</v>
+      </c>
+      <c r="P13" s="16"/>
+      <c r="Q13" s="16"/>
+    </row>
+    <row r="14" spans="2:17" ht="18.75">
+      <c r="B14" s="16">
         <v>11</v>
       </c>
-      <c r="C14" s="24">
+      <c r="C14" s="16">
         <v>38323</v>
       </c>
-      <c r="D14" s="24">
+      <c r="D14" s="16">
         <v>7985</v>
       </c>
-    </row>
-    <row r="15" spans="2:5" ht="17.850000000000001" x14ac:dyDescent="0.25">
-      <c r="B15" s="23">
+      <c r="O14" s="16">
+        <v>11</v>
+      </c>
+      <c r="P14" s="16"/>
+      <c r="Q14" s="16"/>
+    </row>
+    <row r="15" spans="2:17" ht="18.75">
+      <c r="B15" s="15">
         <v>12</v>
       </c>
-      <c r="C15" s="36">
+      <c r="C15" s="26">
         <v>40896</v>
       </c>
-      <c r="D15" s="28">
+      <c r="D15" s="19">
         <v>8411</v>
       </c>
-    </row>
-    <row r="16" spans="2:5" ht="17.850000000000001" x14ac:dyDescent="0.25">
-      <c r="B16" s="24">
+      <c r="O15" s="15">
+        <v>12</v>
+      </c>
+      <c r="P15" s="26"/>
+      <c r="Q15" s="19"/>
+    </row>
+    <row r="16" spans="2:17" ht="18.75">
+      <c r="B16" s="16">
         <v>13</v>
       </c>
-      <c r="C16" s="24">
+      <c r="C16" s="16">
         <v>38132</v>
       </c>
-      <c r="D16" s="24">
+      <c r="D16" s="16">
         <v>8314</v>
       </c>
-    </row>
-    <row r="17" spans="2:4" ht="17.850000000000001" x14ac:dyDescent="0.25">
-      <c r="B17" s="24">
+      <c r="O16" s="16">
+        <v>13</v>
+      </c>
+      <c r="P16" s="16"/>
+      <c r="Q16" s="16"/>
+    </row>
+    <row r="17" spans="2:17" ht="18.75">
+      <c r="B17" s="16">
         <v>14</v>
       </c>
-      <c r="C17" s="24">
+      <c r="C17" s="16">
         <v>38962</v>
       </c>
-      <c r="D17" s="24">
+      <c r="D17" s="16">
         <v>8287</v>
       </c>
-    </row>
-    <row r="18" spans="2:4" ht="17.850000000000001" x14ac:dyDescent="0.25">
-      <c r="B18" s="24">
+      <c r="O17" s="16">
+        <v>14</v>
+      </c>
+      <c r="P17" s="16"/>
+      <c r="Q17" s="16"/>
+    </row>
+    <row r="18" spans="2:17" ht="18.75">
+      <c r="B18" s="16">
         <v>15</v>
       </c>
-      <c r="C18" s="24">
+      <c r="C18" s="16">
         <v>38825</v>
       </c>
-      <c r="D18" s="24">
+      <c r="D18" s="16">
         <v>8452</v>
       </c>
-    </row>
-    <row r="19" spans="2:4" ht="17.850000000000001" x14ac:dyDescent="0.25">
-      <c r="B19" s="23">
+      <c r="O18" s="16">
+        <v>15</v>
+      </c>
+      <c r="P18" s="16"/>
+      <c r="Q18" s="16"/>
+    </row>
+    <row r="19" spans="2:17" ht="18.75">
+      <c r="B19" s="15">
         <v>16</v>
       </c>
-      <c r="C19" s="36">
+      <c r="C19" s="26">
         <v>39364</v>
       </c>
-      <c r="D19" s="28">
+      <c r="D19" s="19">
         <v>7844</v>
       </c>
-    </row>
-    <row r="20" spans="2:4" ht="17.850000000000001" x14ac:dyDescent="0.2">
-      <c r="C20" s="40">
+      <c r="O19" s="15">
+        <v>16</v>
+      </c>
+      <c r="P19" s="26"/>
+      <c r="Q19" s="19"/>
+    </row>
+    <row r="20" spans="2:17" ht="18">
+      <c r="C20" s="27">
         <v>4</v>
       </c>
-      <c r="D20" s="40">
+      <c r="D20" s="27">
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="2:4" ht="17.850000000000001" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:17" ht="18">
       <c r="B24" s="1" t="s">
         <v>81</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="C2:D2"/>
+    <mergeCell ref="P2:Q2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/DecompositionLU/docs/statistics.xlsx
+++ b/DecompositionLU/docs/statistics.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="84">
   <si>
     <t>Я не уверен, будет ли это использоваться в готовой презентации и так ли это надо делать, если да, так что пока считаем, что файл для личного пользования.</t>
   </si>
@@ -340,6 +340,12 @@
   </si>
   <si>
     <t>Я искренне не понимаю этих результатов</t>
+  </si>
+  <si>
+    <t>Тесты были на машине с числом физ ядер - 6 и лог ядер - 12</t>
+  </si>
+  <si>
+    <t>какой-то бред</t>
   </si>
 </sst>
 </file>
@@ -579,7 +585,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -690,6 +696,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -841,13 +848,12 @@
             </c:ext>
           </c:extLst>
         </c:ser>
-        <c:dLbls/>
         <c:marker val="1"/>
-        <c:axId val="153173376"/>
-        <c:axId val="153175168"/>
+        <c:axId val="141630848"/>
+        <c:axId val="141640832"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="153173376"/>
+        <c:axId val="141630848"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -887,14 +893,14 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="153175168"/>
+        <c:crossAx val="141640832"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="153175168"/>
+        <c:axId val="141640832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="34000"/>
@@ -944,7 +950,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="153173376"/>
+        <c:crossAx val="141630848"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -995,7 +1001,7 @@
   </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000011" l="0.70000000000000007" r="0.70000000000000007" t="0.75000000000000011" header="0.30000000000000004" footer="0.30000000000000004"/>
+    <c:pageMargins b="0.75000000000000022" l="0.70000000000000018" r="0.70000000000000018" t="0.75000000000000022" header="0.3000000000000001" footer="0.3000000000000001"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
@@ -1135,13 +1141,12 @@
             </c:ext>
           </c:extLst>
         </c:ser>
-        <c:dLbls/>
         <c:marker val="1"/>
-        <c:axId val="153621248"/>
-        <c:axId val="153622784"/>
+        <c:axId val="141685504"/>
+        <c:axId val="141687040"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="153621248"/>
+        <c:axId val="141685504"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1181,14 +1186,14 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="153622784"/>
+        <c:crossAx val="141687040"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="153622784"/>
+        <c:axId val="141687040"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="6500"/>
@@ -1238,7 +1243,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="153621248"/>
+        <c:crossAx val="141685504"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1289,7 +1294,7 @@
   </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000011" l="0.70000000000000007" r="0.70000000000000007" t="0.75000000000000011" header="0.30000000000000004" footer="0.30000000000000004"/>
+    <c:pageMargins b="0.75000000000000022" l="0.70000000000000018" r="0.70000000000000018" t="0.75000000000000022" header="0.3000000000000001" footer="0.3000000000000001"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
@@ -1301,22 +1306,36 @@
   <c:chart>
     <c:plotArea>
       <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:spPr>
-            <a:ln w="19050">
-              <a:noFill/>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
             </a:ln>
           </c:spPr>
-          <c:xVal>
+          <c:marker>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
             <c:numRef>
-              <c:f>Графики!$O$4:$O$8</c:f>
+              <c:f>Графики!$O$4:$O$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -1324,23 +1343,29 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5</c:v>
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>12</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:xVal>
-          <c:yVal>
+          </c:cat>
+          <c:val>
             <c:numRef>
-              <c:f>Графики!$Q$4:$Q$8</c:f>
+              <c:f>Графики!$Q$4:$Q$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>4557</c:v>
                 </c:pt>
@@ -1348,35 +1373,44 @@
                   <c:v>3948</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4020</c:v>
+                  <c:v>3448</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3448</c:v>
+                  <c:v>3554</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3996</c:v>
+                  <c:v>3538</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3696</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4272</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:yVal>
+          </c:val>
         </c:ser>
-        <c:axId val="54167424"/>
-        <c:axId val="54165888"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="54167424"/>
+        <c:marker val="1"/>
+        <c:axId val="128556416"/>
+        <c:axId val="142235520"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="128556416"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:axPos val="b"/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="54165888"/>
+        <c:crossAx val="142235520"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
       <c:valAx>
-        <c:axId val="54165888"/>
+        <c:axId val="142235520"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1384,20 +1418,149 @@
         <c:majorGridlines/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="54167424"/>
+        <c:crossAx val="128556416"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
+        <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:layout/>
-    </c:legend>
     <c:plotVisOnly val="1"/>
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageMargins b="0.75000000000000011" l="0.70000000000000007" r="0.70000000000000007" t="0.75000000000000011" header="0.30000000000000004" footer="0.30000000000000004"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="ru-RU"/>
+  <c:chart>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Графики!$O$4:$O$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>12</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Графики!$P$4:$P$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>21978</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>18990</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18915</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19263</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19123</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>19536</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>20535</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:marker val="1"/>
+        <c:axId val="130061824"/>
+        <c:axId val="130781568"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="130061824"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="130781568"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="130781568"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="130061824"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000033" l="0.70000000000000029" r="0.70000000000000029" t="0.75000000000000033" header="0.30000000000000016" footer="0.30000000000000016"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
@@ -1418,7 +1581,7 @@
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{77301E52-0432-4D04-B3B3-00D890F3A041}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{77301E52-0432-4D04-B3B3-00D890F3A041}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1473,7 +1636,7 @@
         <xdr:cNvPr id="3" name="TextBox 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A60DEF0B-7AC5-4BE9-B97A-367940A351A6}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A60DEF0B-7AC5-4BE9-B97A-367940A351A6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1528,7 +1691,7 @@
         <xdr:cNvPr id="4" name="TextBox 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{35C2101E-3BC3-486A-87D7-AB0DA6ED7DA8}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35C2101E-3BC3-486A-87D7-AB0DA6ED7DA8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1593,7 +1756,7 @@
         <xdr:cNvPr id="5" name="Диаграмма 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{D9C1BB01-F75F-4D40-BA20-D7288523072B}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9C1BB01-F75F-4D40-BA20-D7288523072B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1629,7 +1792,7 @@
         <xdr:cNvPr id="7" name="Диаграмма 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{63E3D050-E508-4926-853F-B56EA689B234}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63E3D050-E508-4926-853F-B56EA689B234}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1649,16 +1812,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>257175</xdr:colOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>561975</xdr:colOff>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>552450</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1672,6 +1835,36 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Диаграмма 5"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1935,7 +2128,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2642,7 +2835,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B2:Q24"/>
+  <dimension ref="B2:T24"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="29"/>
@@ -2654,7 +2847,7 @@
     <col min="18" max="16384" width="9.140625" style="29"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:17" ht="18">
+    <row r="2" spans="2:19" ht="18">
       <c r="B2" s="17"/>
       <c r="C2" s="43" t="s">
         <v>78</v>
@@ -2665,8 +2858,11 @@
         <v>78</v>
       </c>
       <c r="Q2" s="43"/>
-    </row>
-    <row r="3" spans="2:17" ht="18">
+      <c r="S2" s="29" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="2:19" ht="18">
       <c r="B3" s="13" t="s">
         <v>77</v>
       </c>
@@ -2686,7 +2882,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="2:17" ht="18.75">
+    <row r="4" spans="2:19" ht="18.75">
       <c r="B4" s="15">
         <v>1</v>
       </c>
@@ -2699,11 +2895,14 @@
       <c r="O4" s="15">
         <v>1</v>
       </c>
+      <c r="P4" s="19">
+        <v>21978</v>
+      </c>
       <c r="Q4" s="19">
         <v>4557</v>
       </c>
     </row>
-    <row r="5" spans="2:17" ht="18.75">
+    <row r="5" spans="2:19" ht="18.75">
       <c r="B5" s="15">
         <v>2</v>
       </c>
@@ -2716,11 +2915,14 @@
       <c r="O5" s="15">
         <v>2</v>
       </c>
+      <c r="P5" s="19">
+        <v>18990</v>
+      </c>
       <c r="Q5" s="19">
         <v>3948</v>
       </c>
     </row>
-    <row r="6" spans="2:17" ht="18.75">
+    <row r="6" spans="2:19" ht="18.75">
       <c r="B6" s="16">
         <v>3</v>
       </c>
@@ -2730,14 +2932,17 @@
       <c r="D6" s="16">
         <v>8005</v>
       </c>
-      <c r="O6" s="16">
-        <v>3</v>
-      </c>
-      <c r="Q6" s="16">
-        <v>4020</v>
-      </c>
-    </row>
-    <row r="7" spans="2:17" ht="18.75">
+      <c r="O6" s="15">
+        <v>4</v>
+      </c>
+      <c r="P6" s="19">
+        <v>18915</v>
+      </c>
+      <c r="Q6" s="19">
+        <v>3448</v>
+      </c>
+    </row>
+    <row r="7" spans="2:19" ht="18.75">
       <c r="B7" s="15">
         <v>4</v>
       </c>
@@ -2748,13 +2953,16 @@
         <v>7387</v>
       </c>
       <c r="O7" s="15">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="P7" s="19">
+        <v>19263</v>
       </c>
       <c r="Q7" s="19">
-        <v>3448</v>
-      </c>
-    </row>
-    <row r="8" spans="2:17" ht="18.75">
+        <v>3554</v>
+      </c>
+    </row>
+    <row r="8" spans="2:19" ht="18.75">
       <c r="B8" s="16">
         <v>5</v>
       </c>
@@ -2764,14 +2972,17 @@
       <c r="D8" s="16">
         <v>6863</v>
       </c>
-      <c r="O8" s="16">
-        <v>5</v>
-      </c>
-      <c r="Q8" s="16">
-        <v>3996</v>
-      </c>
-    </row>
-    <row r="9" spans="2:17" ht="18.75">
+      <c r="O8" s="15">
+        <v>8</v>
+      </c>
+      <c r="P8" s="26">
+        <v>19123</v>
+      </c>
+      <c r="Q8" s="19">
+        <v>3538</v>
+      </c>
+    </row>
+    <row r="9" spans="2:19" ht="18.75">
       <c r="B9" s="15">
         <v>6</v>
       </c>
@@ -2782,12 +2993,16 @@
         <v>7472</v>
       </c>
       <c r="O9" s="15">
-        <v>6</v>
-      </c>
-      <c r="P9" s="26"/>
-      <c r="Q9" s="19"/>
-    </row>
-    <row r="10" spans="2:17" ht="18.75">
+        <v>10</v>
+      </c>
+      <c r="P9" s="26">
+        <v>19536</v>
+      </c>
+      <c r="Q9" s="19">
+        <v>3696</v>
+      </c>
+    </row>
+    <row r="10" spans="2:19" ht="18.75">
       <c r="B10" s="16">
         <v>7</v>
       </c>
@@ -2797,13 +3012,17 @@
       <c r="D10" s="16">
         <v>6861</v>
       </c>
-      <c r="O10" s="16">
-        <v>7</v>
-      </c>
-      <c r="P10" s="16"/>
-      <c r="Q10" s="16"/>
-    </row>
-    <row r="11" spans="2:17" ht="18.75">
+      <c r="O10" s="15">
+        <v>12</v>
+      </c>
+      <c r="P10" s="26">
+        <v>20535</v>
+      </c>
+      <c r="Q10" s="19">
+        <v>4272</v>
+      </c>
+    </row>
+    <row r="11" spans="2:19" ht="18.75">
       <c r="B11" s="15">
         <v>8</v>
       </c>
@@ -2813,13 +3032,11 @@
       <c r="D11" s="19">
         <v>7389</v>
       </c>
-      <c r="O11" s="15">
-        <v>8</v>
-      </c>
-      <c r="P11" s="26"/>
-      <c r="Q11" s="19"/>
-    </row>
-    <row r="12" spans="2:17" ht="18.75">
+      <c r="O11" s="44"/>
+      <c r="P11" s="44"/>
+      <c r="Q11" s="44"/>
+    </row>
+    <row r="12" spans="2:19" ht="18.75">
       <c r="B12" s="16">
         <v>9</v>
       </c>
@@ -2830,13 +3047,11 @@
         <v>7908</v>
       </c>
       <c r="E12" s="30"/>
-      <c r="O12" s="16">
-        <v>9</v>
-      </c>
-      <c r="P12" s="16"/>
-      <c r="Q12" s="16"/>
-    </row>
-    <row r="13" spans="2:17" ht="18.75">
+      <c r="O12" s="25"/>
+      <c r="P12" s="25"/>
+      <c r="Q12" s="25"/>
+    </row>
+    <row r="13" spans="2:19" ht="18.75">
       <c r="B13" s="16">
         <v>10</v>
       </c>
@@ -2846,13 +3061,11 @@
       <c r="D13" s="16">
         <v>8155</v>
       </c>
-      <c r="O13" s="16">
-        <v>10</v>
-      </c>
-      <c r="P13" s="16"/>
-      <c r="Q13" s="16"/>
-    </row>
-    <row r="14" spans="2:17" ht="18.75">
+      <c r="O13" s="25"/>
+      <c r="P13" s="25"/>
+      <c r="Q13" s="25"/>
+    </row>
+    <row r="14" spans="2:19" ht="18.75">
       <c r="B14" s="16">
         <v>11</v>
       </c>
@@ -2862,13 +3075,11 @@
       <c r="D14" s="16">
         <v>7985</v>
       </c>
-      <c r="O14" s="16">
-        <v>11</v>
-      </c>
-      <c r="P14" s="16"/>
-      <c r="Q14" s="16"/>
-    </row>
-    <row r="15" spans="2:17" ht="18.75">
+      <c r="O14" s="25"/>
+      <c r="P14" s="25"/>
+      <c r="Q14" s="25"/>
+    </row>
+    <row r="15" spans="2:19" ht="18.75">
       <c r="B15" s="15">
         <v>12</v>
       </c>
@@ -2878,13 +3089,11 @@
       <c r="D15" s="19">
         <v>8411</v>
       </c>
-      <c r="O15" s="15">
-        <v>12</v>
-      </c>
-      <c r="P15" s="26"/>
-      <c r="Q15" s="19"/>
-    </row>
-    <row r="16" spans="2:17" ht="18.75">
+      <c r="O15" s="44"/>
+      <c r="P15" s="44"/>
+      <c r="Q15" s="44"/>
+    </row>
+    <row r="16" spans="2:19" ht="18.75">
       <c r="B16" s="16">
         <v>13</v>
       </c>
@@ -2894,13 +3103,11 @@
       <c r="D16" s="16">
         <v>8314</v>
       </c>
-      <c r="O16" s="16">
-        <v>13</v>
-      </c>
-      <c r="P16" s="16"/>
-      <c r="Q16" s="16"/>
-    </row>
-    <row r="17" spans="2:17" ht="18.75">
+      <c r="O16" s="25"/>
+      <c r="P16" s="25"/>
+      <c r="Q16" s="25"/>
+    </row>
+    <row r="17" spans="2:20" ht="18.75">
       <c r="B17" s="16">
         <v>14</v>
       </c>
@@ -2910,13 +3117,14 @@
       <c r="D17" s="16">
         <v>8287</v>
       </c>
-      <c r="O17" s="16">
-        <v>14</v>
-      </c>
-      <c r="P17" s="16"/>
-      <c r="Q17" s="16"/>
-    </row>
-    <row r="18" spans="2:17" ht="18.75">
+      <c r="O17" s="25"/>
+      <c r="P17" s="25"/>
+      <c r="Q17" s="25"/>
+      <c r="T17" s="29" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="2:20" ht="18.75">
       <c r="B18" s="16">
         <v>15</v>
       </c>
@@ -2926,13 +3134,11 @@
       <c r="D18" s="16">
         <v>8452</v>
       </c>
-      <c r="O18" s="16">
-        <v>15</v>
-      </c>
-      <c r="P18" s="16"/>
-      <c r="Q18" s="16"/>
-    </row>
-    <row r="19" spans="2:17" ht="18.75">
+      <c r="O18" s="25"/>
+      <c r="P18" s="25"/>
+      <c r="Q18" s="25"/>
+    </row>
+    <row r="19" spans="2:20" ht="18.75">
       <c r="B19" s="15">
         <v>16</v>
       </c>
@@ -2942,13 +3148,8 @@
       <c r="D19" s="19">
         <v>7844</v>
       </c>
-      <c r="O19" s="15">
-        <v>16</v>
-      </c>
-      <c r="P19" s="26"/>
-      <c r="Q19" s="19"/>
-    </row>
-    <row r="20" spans="2:17" ht="18">
+    </row>
+    <row r="20" spans="2:20" ht="18">
       <c r="C20" s="27">
         <v>4</v>
       </c>
@@ -2956,7 +3157,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="2:17" ht="18">
+    <row r="24" spans="2:20" ht="18">
       <c r="B24" s="1" t="s">
         <v>81</v>
       </c>
@@ -2967,6 +3168,7 @@
     <mergeCell ref="P2:Q2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/DecompositionLU/docs/statistics.xlsx
+++ b/DecompositionLU/docs/statistics.xlsx
@@ -1,32 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maxim\source\repos\practice\SECOND_COURSE\FOR_ITLAB\ArchBenchs\DecompositionLU\docs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{363B386D-8DCD-4796-907B-32AA2501C8E2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="27600" windowHeight="15030" activeTab="1"/>
+    <workbookView xWindow="-114" yWindow="-114" windowWidth="27602" windowHeight="15027" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Таблица" sheetId="1" r:id="rId1"/>
     <sheet name="Графики" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519"/>
-  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="83">
   <si>
     <t>Я не уверен, будет ли это использоваться в готовой презентации и так ли это надо делать, если да, так что пока считаем, что файл для личного пользования.</t>
   </si>
@@ -344,15 +344,12 @@
   <si>
     <t>Тесты были на машине с числом физ ядер - 6 и лог ядер - 12</t>
   </si>
-  <si>
-    <t>какой-то бред</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="14">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -657,6 +654,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -696,7 +694,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -715,9 +712,18 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
-  <c:style val="4"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="104"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="4"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
@@ -745,7 +751,7 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
+      <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -754,10 +760,12 @@
         <a:effectLst/>
       </c:spPr>
     </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
         <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -842,13 +850,23 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:smooth val="0"/>
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-DFDA-4FBA-8E35-21ED64A1AC56}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:marker val="1"/>
+        <c:smooth val="0"/>
         <c:axId val="141630848"/>
         <c:axId val="141640832"/>
       </c:lineChart>
@@ -857,8 +875,10 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
@@ -898,6 +918,7 @@
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="141640832"/>
@@ -905,6 +926,7 @@
           <c:orientation val="minMax"/>
           <c:min val="34000"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines>
           <c:spPr>
@@ -922,6 +944,7 @@
         </c:majorGridlines>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
@@ -964,13 +987,14 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+    <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
           <c16r3:dispNaAsBlank val="1"/>
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1008,9 +1032,18 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
-  <c:style val="8"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="108"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="8"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
@@ -1038,7 +1071,7 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
+      <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -1047,10 +1080,12 @@
         <a:effectLst/>
       </c:spPr>
     </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
         <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -1135,13 +1170,23 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+          <c:smooth val="0"/>
+          <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-8747-4A5E-85F4-772AAE4EC689}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:marker val="1"/>
+        <c:smooth val="0"/>
         <c:axId val="141685504"/>
         <c:axId val="141687040"/>
       </c:lineChart>
@@ -1150,8 +1195,10 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
@@ -1191,6 +1238,7 @@
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="141687040"/>
@@ -1198,6 +1246,7 @@
           <c:orientation val="minMax"/>
           <c:min val="6500"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines>
           <c:spPr>
@@ -1215,6 +1264,7 @@
         </c:majorGridlines>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
@@ -1257,13 +1307,14 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+    <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
           <c16r3:dispNaAsBlank val="1"/>
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1301,13 +1352,25 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
         <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -1390,8 +1453,23 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6F6D-4B42-88DB-CFE117E40602}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:marker val="1"/>
+        <c:smooth val="0"/>
         <c:axId val="128556416"/>
         <c:axId val="142235520"/>
       </c:lineChart>
@@ -1400,23 +1478,30 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="142235520"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="142235520"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="128556416"/>
         <c:crosses val="autoZero"/>
@@ -1424,6 +1509,8 @@
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
@@ -1434,13 +1521,25 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
         <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -1523,8 +1622,23 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-052C-4765-B247-6AC6F5FF1439}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:marker val="1"/>
+        <c:smooth val="0"/>
         <c:axId val="130061824"/>
         <c:axId val="130781568"/>
       </c:lineChart>
@@ -1533,23 +1647,30 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="130781568"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="130781568"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="130061824"/>
         <c:crosses val="autoZero"/>
@@ -1557,6 +1678,8 @@
       </c:valAx>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
@@ -1581,7 +1704,7 @@
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{77301E52-0432-4D04-B3B3-00D890F3A041}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1636,7 +1759,7 @@
         <xdr:cNvPr id="3" name="TextBox 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A60DEF0B-7AC5-4BE9-B97A-367940A351A6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1691,7 +1814,7 @@
         <xdr:cNvPr id="4" name="TextBox 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35C2101E-3BC3-486A-87D7-AB0DA6ED7DA8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1756,7 +1879,7 @@
         <xdr:cNvPr id="5" name="Диаграмма 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9C1BB01-F75F-4D40-BA20-D7288523072B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000005000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1792,7 +1915,7 @@
         <xdr:cNvPr id="7" name="Диаграмма 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63E3D050-E508-4926-853F-B56EA689B234}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000007000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1825,7 +1948,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="8" name="Диаграмма 7"/>
+        <xdr:cNvPr id="8" name="Диаграмма 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -1855,7 +1984,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="6" name="Диаграмма 5"/>
+        <xdr:cNvPr id="6" name="Диаграмма 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -2128,16 +2263,16 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:W42"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="17.850000000000001" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="65.7109375" style="1" customWidth="1"/>
     <col min="2" max="5" width="26.7109375" style="1" customWidth="1"/>
@@ -2147,7 +2282,7 @@
     <col min="10" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -2171,7 +2306,7 @@
       <c r="S1" s="2"/>
       <c r="T1" s="2"/>
     </row>
-    <row r="2" spans="1:23">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -2195,7 +2330,7 @@
       <c r="S2" s="2"/>
       <c r="T2" s="2"/>
     </row>
-    <row r="3" spans="1:23">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
@@ -2213,43 +2348,43 @@
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
     </row>
-    <row r="5" spans="1:23" ht="17.850000000000001" customHeight="1">
-      <c r="A5" s="37" t="s">
+    <row r="5" spans="1:23" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="38"/>
-      <c r="C5" s="38"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="39"/>
-      <c r="G5" s="32" t="s">
+      <c r="B5" s="39"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="40"/>
+      <c r="G5" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="H5" s="32"/>
+      <c r="H5" s="33"/>
       <c r="S5" s="5"/>
       <c r="T5" s="14"/>
       <c r="U5" s="14"/>
       <c r="V5" s="14"/>
       <c r="W5" s="14"/>
     </row>
-    <row r="6" spans="1:23" ht="18.75">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="35" t="s">
+      <c r="B6" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="35"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="35"/>
-      <c r="G6" s="32"/>
-      <c r="H6" s="32"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="36"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
       <c r="S6" s="14"/>
       <c r="T6" s="14"/>
       <c r="U6" s="14"/>
       <c r="V6" s="14"/>
       <c r="W6" s="14"/>
     </row>
-    <row r="7" spans="1:23" ht="18.75">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
@@ -2265,31 +2400,31 @@
       <c r="E7" s="8">
         <v>10000</v>
       </c>
-      <c r="G7" s="32"/>
-      <c r="H7" s="32"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="33"/>
       <c r="S7" s="14"/>
       <c r="T7" s="14"/>
       <c r="U7" s="14"/>
       <c r="V7" s="14"/>
       <c r="W7" s="14"/>
     </row>
-    <row r="8" spans="1:23" ht="18.75">
-      <c r="A8" s="36" t="s">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A8" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="36"/>
-      <c r="C8" s="36"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
+      <c r="B8" s="37"/>
+      <c r="C8" s="37"/>
+      <c r="D8" s="37"/>
+      <c r="E8" s="37"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
       <c r="S8" s="14"/>
       <c r="T8" s="14"/>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
       <c r="W8" s="14"/>
     </row>
-    <row r="9" spans="1:23" ht="18.75">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
@@ -2311,7 +2446,7 @@
       <c r="V9" s="14"/>
       <c r="W9" s="14"/>
     </row>
-    <row r="10" spans="1:23">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>8</v>
       </c>
@@ -2333,7 +2468,7 @@
       <c r="V10" s="5"/>
       <c r="W10" s="5"/>
     </row>
-    <row r="11" spans="1:23">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>9</v>
       </c>
@@ -2357,17 +2492,17 @@
       <c r="V11" s="5"/>
       <c r="W11" s="5"/>
     </row>
-    <row r="12" spans="1:23">
-      <c r="A12" s="36" t="s">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A12" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="36"/>
-      <c r="C12" s="36"/>
-      <c r="D12" s="36"/>
-      <c r="E12" s="36"/>
+      <c r="B12" s="37"/>
+      <c r="C12" s="37"/>
+      <c r="D12" s="37"/>
+      <c r="E12" s="37"/>
       <c r="F12" s="5"/>
     </row>
-    <row r="13" spans="1:23">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>7</v>
       </c>
@@ -2377,7 +2512,7 @@
       <c r="C13" s="10">
         <v>232</v>
       </c>
-      <c r="D13" s="40" t="s">
+      <c r="D13" s="41" t="s">
         <v>21</v>
       </c>
       <c r="E13" s="10">
@@ -2385,7 +2520,7 @@
       </c>
       <c r="F13" s="5"/>
     </row>
-    <row r="14" spans="1:23">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>8</v>
       </c>
@@ -2395,7 +2530,7 @@
       <c r="C14" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="41"/>
+      <c r="D14" s="42"/>
       <c r="E14" s="10" t="s">
         <v>10</v>
       </c>
@@ -2403,7 +2538,7 @@
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
     </row>
-    <row r="15" spans="1:23">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>9</v>
       </c>
@@ -2413,32 +2548,32 @@
       <c r="C15" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="42"/>
+      <c r="D15" s="43"/>
       <c r="E15" s="10" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
-      <c r="A18" s="34" t="s">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="34"/>
-      <c r="C18" s="34"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="34"/>
-    </row>
-    <row r="19" spans="1:9">
+      <c r="B18" s="35"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="35"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B19" s="35" t="s">
+      <c r="B19" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="C19" s="35"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="35"/>
-    </row>
-    <row r="20" spans="1:9">
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>6</v>
       </c>
@@ -2455,16 +2590,16 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
-      <c r="A21" s="36" t="s">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="B21" s="36"/>
-      <c r="C21" s="36"/>
-      <c r="D21" s="36"/>
-      <c r="E21" s="36"/>
-    </row>
-    <row r="22" spans="1:9">
+      <c r="B21" s="37"/>
+      <c r="C21" s="37"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="37"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>7</v>
       </c>
@@ -2481,7 +2616,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>8</v>
       </c>
@@ -2498,7 +2633,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>9</v>
       </c>
@@ -2515,22 +2650,22 @@
         <v>35</v>
       </c>
       <c r="G24" s="20"/>
-      <c r="H24" s="31"/>
-      <c r="I24" s="31"/>
-    </row>
-    <row r="25" spans="1:9">
-      <c r="A25" s="36" t="s">
+      <c r="H24" s="32"/>
+      <c r="I24" s="32"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="B25" s="36"/>
-      <c r="C25" s="36"/>
-      <c r="D25" s="36"/>
-      <c r="E25" s="36"/>
+      <c r="B25" s="37"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="37"/>
       <c r="G25" s="21"/>
       <c r="H25" s="18"/>
       <c r="I25" s="18"/>
     </row>
-    <row r="26" spans="1:9" ht="18.75">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>7</v>
       </c>
@@ -2550,7 +2685,7 @@
       <c r="H26" s="23"/>
       <c r="I26" s="24"/>
     </row>
-    <row r="27" spans="1:9" ht="18.75">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>8</v>
       </c>
@@ -2570,7 +2705,7 @@
       <c r="H27" s="23"/>
       <c r="I27" s="20"/>
     </row>
-    <row r="28" spans="1:9" ht="18.75">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>9</v>
       </c>
@@ -2590,7 +2725,7 @@
       <c r="H28" s="20"/>
       <c r="I28" s="20"/>
     </row>
-    <row r="29" spans="1:9" ht="18.75">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C29" s="1" t="s">
         <v>40</v>
       </c>
@@ -2604,38 +2739,38 @@
       <c r="H29" s="23"/>
       <c r="I29" s="20"/>
     </row>
-    <row r="30" spans="1:9" ht="18.75">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="G30" s="25"/>
       <c r="H30" s="20"/>
       <c r="I30" s="20"/>
     </row>
-    <row r="31" spans="1:9" ht="18.75">
-      <c r="A31" s="34" t="s">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="35" t="s">
         <v>70</v>
       </c>
-      <c r="B31" s="34"/>
-      <c r="C31" s="34"/>
-      <c r="D31" s="34"/>
-      <c r="E31" s="34"/>
+      <c r="B31" s="35"/>
+      <c r="C31" s="35"/>
+      <c r="D31" s="35"/>
+      <c r="E31" s="35"/>
       <c r="G31" s="22"/>
       <c r="H31" s="23"/>
       <c r="I31" s="20"/>
     </row>
-    <row r="32" spans="1:9" ht="18.75">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B32" s="35" t="s">
+      <c r="B32" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="35"/>
-      <c r="D32" s="35"/>
-      <c r="E32" s="35"/>
+      <c r="C32" s="36"/>
+      <c r="D32" s="36"/>
+      <c r="E32" s="36"/>
       <c r="G32" s="25"/>
       <c r="H32" s="20"/>
       <c r="I32" s="20"/>
     </row>
-    <row r="33" spans="1:9" ht="18.75">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>6</v>
       </c>
@@ -2655,19 +2790,19 @@
       <c r="H33" s="23"/>
       <c r="I33" s="20"/>
     </row>
-    <row r="34" spans="1:9" ht="18.75">
-      <c r="A34" s="36" t="s">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="B34" s="36"/>
-      <c r="C34" s="36"/>
-      <c r="D34" s="36"/>
-      <c r="E34" s="36"/>
+      <c r="B34" s="37"/>
+      <c r="C34" s="37"/>
+      <c r="D34" s="37"/>
+      <c r="E34" s="37"/>
       <c r="G34" s="25"/>
       <c r="H34" s="20"/>
       <c r="I34" s="20"/>
     </row>
-    <row r="35" spans="1:9" ht="18.75">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>7</v>
       </c>
@@ -2687,7 +2822,7 @@
       <c r="H35" s="20"/>
       <c r="I35" s="20"/>
     </row>
-    <row r="36" spans="1:9" ht="18.75">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>8</v>
       </c>
@@ -2707,7 +2842,7 @@
       <c r="H36" s="20"/>
       <c r="I36" s="20"/>
     </row>
-    <row r="37" spans="1:9" ht="18.75">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>9</v>
       </c>
@@ -2727,19 +2862,19 @@
       <c r="H37" s="23"/>
       <c r="I37" s="20"/>
     </row>
-    <row r="38" spans="1:9" ht="18.75">
-      <c r="A38" s="36" t="s">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="B38" s="36"/>
-      <c r="C38" s="36"/>
-      <c r="D38" s="36"/>
-      <c r="E38" s="36"/>
+      <c r="B38" s="37"/>
+      <c r="C38" s="37"/>
+      <c r="D38" s="37"/>
+      <c r="E38" s="37"/>
       <c r="G38" s="25"/>
       <c r="H38" s="20"/>
       <c r="I38" s="20"/>
     </row>
-    <row r="39" spans="1:9" ht="18.75">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>7</v>
       </c>
@@ -2759,7 +2894,7 @@
       <c r="H39" s="20"/>
       <c r="I39" s="20"/>
     </row>
-    <row r="40" spans="1:9" ht="18.75">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>8</v>
       </c>
@@ -2779,7 +2914,7 @@
       <c r="H40" s="20"/>
       <c r="I40" s="20"/>
     </row>
-    <row r="41" spans="1:9" ht="18.75">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>9</v>
       </c>
@@ -2799,13 +2934,13 @@
       <c r="H41" s="23"/>
       <c r="I41" s="20"/>
     </row>
-    <row r="42" spans="1:9">
-      <c r="B42" s="33" t="s">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B42" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="C42" s="33"/>
-      <c r="D42" s="33"/>
-      <c r="E42" s="33"/>
+      <c r="C42" s="34"/>
+      <c r="D42" s="34"/>
+      <c r="E42" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -2834,9 +2969,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B2:T24"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="B2:S24"/>
+  <sheetFormatPr defaultRowHeight="13.55" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="29"/>
     <col min="2" max="2" width="23.140625" style="29" bestFit="1" customWidth="1"/>
@@ -2847,22 +2982,22 @@
     <col min="18" max="16384" width="9.140625" style="29"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:19" ht="18">
+    <row r="2" spans="2:19" ht="17.850000000000001" x14ac:dyDescent="0.25">
       <c r="B2" s="17"/>
-      <c r="C2" s="43" t="s">
+      <c r="C2" s="44" t="s">
         <v>78</v>
       </c>
-      <c r="D2" s="43"/>
+      <c r="D2" s="44"/>
       <c r="O2" s="17"/>
-      <c r="P2" s="43" t="s">
+      <c r="P2" s="44" t="s">
         <v>78</v>
       </c>
-      <c r="Q2" s="43"/>
+      <c r="Q2" s="44"/>
       <c r="S2" s="29" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="2:19" ht="18">
+    <row r="3" spans="2:19" ht="17.850000000000001" x14ac:dyDescent="0.25">
       <c r="B3" s="13" t="s">
         <v>77</v>
       </c>
@@ -2882,7 +3017,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="2:19" ht="18.75">
+    <row r="4" spans="2:19" ht="17.850000000000001" x14ac:dyDescent="0.25">
       <c r="B4" s="15">
         <v>1</v>
       </c>
@@ -2902,7 +3037,7 @@
         <v>4557</v>
       </c>
     </row>
-    <row r="5" spans="2:19" ht="18.75">
+    <row r="5" spans="2:19" ht="17.850000000000001" x14ac:dyDescent="0.25">
       <c r="B5" s="15">
         <v>2</v>
       </c>
@@ -2922,7 +3057,7 @@
         <v>3948</v>
       </c>
     </row>
-    <row r="6" spans="2:19" ht="18.75">
+    <row r="6" spans="2:19" ht="17.850000000000001" x14ac:dyDescent="0.25">
       <c r="B6" s="16">
         <v>3</v>
       </c>
@@ -2942,7 +3077,7 @@
         <v>3448</v>
       </c>
     </row>
-    <row r="7" spans="2:19" ht="18.75">
+    <row r="7" spans="2:19" ht="17.850000000000001" x14ac:dyDescent="0.25">
       <c r="B7" s="15">
         <v>4</v>
       </c>
@@ -2962,7 +3097,7 @@
         <v>3554</v>
       </c>
     </row>
-    <row r="8" spans="2:19" ht="18.75">
+    <row r="8" spans="2:19" ht="17.850000000000001" x14ac:dyDescent="0.25">
       <c r="B8" s="16">
         <v>5</v>
       </c>
@@ -2982,7 +3117,7 @@
         <v>3538</v>
       </c>
     </row>
-    <row r="9" spans="2:19" ht="18.75">
+    <row r="9" spans="2:19" ht="17.850000000000001" x14ac:dyDescent="0.25">
       <c r="B9" s="15">
         <v>6</v>
       </c>
@@ -3002,7 +3137,7 @@
         <v>3696</v>
       </c>
     </row>
-    <row r="10" spans="2:19" ht="18.75">
+    <row r="10" spans="2:19" ht="17.850000000000001" x14ac:dyDescent="0.25">
       <c r="B10" s="16">
         <v>7</v>
       </c>
@@ -3022,7 +3157,7 @@
         <v>4272</v>
       </c>
     </row>
-    <row r="11" spans="2:19" ht="18.75">
+    <row r="11" spans="2:19" ht="17.850000000000001" x14ac:dyDescent="0.25">
       <c r="B11" s="15">
         <v>8</v>
       </c>
@@ -3032,11 +3167,11 @@
       <c r="D11" s="19">
         <v>7389</v>
       </c>
-      <c r="O11" s="44"/>
-      <c r="P11" s="44"/>
-      <c r="Q11" s="44"/>
-    </row>
-    <row r="12" spans="2:19" ht="18.75">
+      <c r="O11" s="31"/>
+      <c r="P11" s="31"/>
+      <c r="Q11" s="31"/>
+    </row>
+    <row r="12" spans="2:19" ht="17.850000000000001" x14ac:dyDescent="0.25">
       <c r="B12" s="16">
         <v>9</v>
       </c>
@@ -3051,7 +3186,7 @@
       <c r="P12" s="25"/>
       <c r="Q12" s="25"/>
     </row>
-    <row r="13" spans="2:19" ht="18.75">
+    <row r="13" spans="2:19" ht="17.850000000000001" x14ac:dyDescent="0.25">
       <c r="B13" s="16">
         <v>10</v>
       </c>
@@ -3065,7 +3200,7 @@
       <c r="P13" s="25"/>
       <c r="Q13" s="25"/>
     </row>
-    <row r="14" spans="2:19" ht="18.75">
+    <row r="14" spans="2:19" ht="17.850000000000001" x14ac:dyDescent="0.25">
       <c r="B14" s="16">
         <v>11</v>
       </c>
@@ -3079,7 +3214,7 @@
       <c r="P14" s="25"/>
       <c r="Q14" s="25"/>
     </row>
-    <row r="15" spans="2:19" ht="18.75">
+    <row r="15" spans="2:19" ht="17.850000000000001" x14ac:dyDescent="0.25">
       <c r="B15" s="15">
         <v>12</v>
       </c>
@@ -3089,11 +3224,11 @@
       <c r="D15" s="19">
         <v>8411</v>
       </c>
-      <c r="O15" s="44"/>
-      <c r="P15" s="44"/>
-      <c r="Q15" s="44"/>
-    </row>
-    <row r="16" spans="2:19" ht="18.75">
+      <c r="O15" s="31"/>
+      <c r="P15" s="31"/>
+      <c r="Q15" s="31"/>
+    </row>
+    <row r="16" spans="2:19" ht="17.850000000000001" x14ac:dyDescent="0.25">
       <c r="B16" s="16">
         <v>13</v>
       </c>
@@ -3107,7 +3242,7 @@
       <c r="P16" s="25"/>
       <c r="Q16" s="25"/>
     </row>
-    <row r="17" spans="2:20" ht="18.75">
+    <row r="17" spans="2:17" ht="17.850000000000001" x14ac:dyDescent="0.25">
       <c r="B17" s="16">
         <v>14</v>
       </c>
@@ -3120,11 +3255,8 @@
       <c r="O17" s="25"/>
       <c r="P17" s="25"/>
       <c r="Q17" s="25"/>
-      <c r="T17" s="29" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="18" spans="2:20" ht="18.75">
+    </row>
+    <row r="18" spans="2:17" ht="17.850000000000001" x14ac:dyDescent="0.25">
       <c r="B18" s="16">
         <v>15</v>
       </c>
@@ -3138,7 +3270,7 @@
       <c r="P18" s="25"/>
       <c r="Q18" s="25"/>
     </row>
-    <row r="19" spans="2:20" ht="18.75">
+    <row r="19" spans="2:17" ht="17.850000000000001" x14ac:dyDescent="0.25">
       <c r="B19" s="15">
         <v>16</v>
       </c>
@@ -3149,7 +3281,7 @@
         <v>7844</v>
       </c>
     </row>
-    <row r="20" spans="2:20" ht="18">
+    <row r="20" spans="2:17" ht="17.850000000000001" x14ac:dyDescent="0.2">
       <c r="C20" s="27">
         <v>4</v>
       </c>
@@ -3157,7 +3289,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="2:20" ht="18">
+    <row r="24" spans="2:17" ht="17.850000000000001" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
         <v>81</v>
       </c>

--- a/DecompositionLU/docs/statistics.xlsx
+++ b/DecompositionLU/docs/statistics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maxim\source\repos\practice\SECOND_COURSE\FOR_ITLAB\ArchBenchs\DecompositionLU\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{363B386D-8DCD-4796-907B-32AA2501C8E2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F28F07AA-7477-46AC-9E9D-97388D1E91EE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-114" yWindow="-114" windowWidth="27602" windowHeight="15027" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-114" yWindow="-114" windowWidth="27602" windowHeight="15027" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Таблица" sheetId="1" r:id="rId1"/>
@@ -1856,6 +1856,94 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>474897</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>66375</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Рисунок 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BCB4897C-D529-49E0-9F69-9210738BDAF8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11516008" y="2037030"/>
+          <a:ext cx="6251008" cy="1424395"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>446456</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>182892</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Рисунок 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BC18F56D-86EB-4BFF-98EC-5332254432C5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11516008" y="3621386"/>
+          <a:ext cx="5643145" cy="5162298"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 

--- a/DecompositionLU/docs/statistics.xlsx
+++ b/DecompositionLU/docs/statistics.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maxim\source\repos\practice\SECOND_COURSE\FOR_ITLAB\ArchBenchs\DecompositionLU\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F28F07AA-7477-46AC-9E9D-97388D1E91EE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F99DBD33-6294-41FD-B06B-01AC3F0208A9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-114" yWindow="-114" windowWidth="27602" windowHeight="15027" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-114" yWindow="-114" windowWidth="27602" windowHeight="15027" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Таблица" sheetId="1" r:id="rId1"/>
     <sheet name="Графики" sheetId="2" r:id="rId2"/>
+    <sheet name="Про процессор" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="94">
   <si>
     <t>Я не уверен, будет ли это использоваться в готовой презентации и так ли это надо делать, если да, так что пока считаем, что файл для личного пользования.</t>
   </si>
@@ -342,14 +343,47 @@
     <t>Я искренне не понимаю этих результатов</t>
   </si>
   <si>
-    <t>Тесты были на машине с числом физ ядер - 6 и лог ядер - 12</t>
+    <t>Версия 3.0 (блочная версия алгоритма)</t>
+  </si>
+  <si>
+    <t>Хотя бы здесь логично</t>
+  </si>
+  <si>
+    <t>Замеры версии 2.0</t>
+  </si>
+  <si>
+    <t>Замеры на ноутбуке, данные процессора на вкладке "про процессор"</t>
+  </si>
+  <si>
+    <t>Комментарии:</t>
+  </si>
+  <si>
+    <t>Замеры на учебном компьютере, число физ ядер - 6 и лог ядер - 12</t>
+  </si>
+  <si>
+    <t>Функция плохо распараллеливается больше чем на 4 потока</t>
+  </si>
+  <si>
+    <t>Замеры версии 3.0</t>
+  </si>
+  <si>
+    <t>Соотв. таблица</t>
+  </si>
+  <si>
+    <t>Соотв. графики</t>
+  </si>
+  <si>
+    <t>Соотв. Графики</t>
+  </si>
+  <si>
+    <t>Мне нравится</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -451,8 +485,16 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <i/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="GOST Common"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -471,8 +513,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -578,11 +632,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -617,14 +680,8 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
@@ -644,17 +701,17 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -692,6 +749,44 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -793,12 +888,45 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Графики!$B$4:$B$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>16</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Графики!$C$4:$C$19</c:f>
+              <c:f>Графики!$C$4:$C$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>40525</c:v>
                 </c:pt>
@@ -806,45 +934,21 @@
                   <c:v>40933</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>35748</c:v>
+                  <c:v>34657</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>34657</c:v>
+                  <c:v>38071</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>36335</c:v>
+                  <c:v>37594</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>38071</c:v>
+                  <c:v>36931</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>36151</c:v>
+                  <c:v>40896</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>37594</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>36727</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>36931</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>38323</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>40896</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>38132</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>38962</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>38825</c:v>
-                </c:pt>
-                <c:pt idx="15">
                   <c:v>39364</c:v>
                 </c:pt>
               </c:numCache>
@@ -853,7 +957,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-DFDA-4FBA-8E35-21ED64A1AC56}"/>
+              <c16:uniqueId val="{00000000-2BAF-4570-BC3E-1CD3E98D98FB}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -877,6 +981,7 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1038,6 +1143,407 @@
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0"/>
+              <a:t>n = 3000</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Графики!$B$15:$B$21</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>12</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Графики!$D$15:$D$21</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>4557</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3948</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3448</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3554</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3538</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3696</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4272</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-BEB4-4AD3-9B18-79E032C5B9F9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="128556416"/>
+        <c:axId val="142235520"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="128556416"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="142235520"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="142235520"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="3250"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="128556416"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="250"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000011" l="0.70000000000000007" r="0.70000000000000007" t="0.75000000000000011" header="0.30000000000000004" footer="0.30000000000000004"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0"/>
+              <a:t>n = 5000</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Графики!$B$15:$B$21</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>12</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Графики!$C$15:$C$21</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>21978</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>18990</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18915</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19263</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19123</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>19536</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>20535</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E356-49E0-978B-AE57A6813BB1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="130061824"/>
+        <c:axId val="130781568"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="130061824"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="130781568"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="130781568"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="18500"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="130061824"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000033" l="0.70000000000000029" r="0.70000000000000029" t="0.75000000000000033" header="0.30000000000000016" footer="0.30000000000000016"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
       <c14:style val="108"/>
     </mc:Choice>
     <mc:Fallback>
@@ -1113,12 +1619,45 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Графики!$B$4:$B$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>16</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Графики!$D$4:$D$19</c:f>
+              <c:f>Графики!$D$4:$D$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>8737</c:v>
                 </c:pt>
@@ -1126,45 +1665,21 @@
                   <c:v>8116</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8005</c:v>
+                  <c:v>7387</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7387</c:v>
+                  <c:v>7472</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6863</c:v>
+                  <c:v>7389</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>7472</c:v>
+                  <c:v>8155</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>6861</c:v>
+                  <c:v>8411</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>7389</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>7908</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>8155</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>7985</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>8411</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>8314</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>8287</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>8452</c:v>
-                </c:pt>
-                <c:pt idx="15">
                   <c:v>7844</c:v>
                 </c:pt>
               </c:numCache>
@@ -1173,7 +1688,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-8747-4A5E-85F4-772AAE4EC689}"/>
+              <c16:uniqueId val="{00000000-6156-4052-AC80-4496F909B3BD}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1197,6 +1712,7 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1244,7 +1760,648 @@
         <c:axId val="141687040"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:min val="6500"/>
+          <c:min val="7250"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="141685504"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="250"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000022" l="0.70000000000000018" r="0.70000000000000018" t="0.75000000000000022" header="0.3000000000000001" footer="0.3000000000000001"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="104"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="4"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>n = 5000</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Графики!$B$4:$B$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>16</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Графики!$C$27:$C$34</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>84305</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>42965</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>23077</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>18001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>14258</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>12636</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>11424</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9939</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-DA14-44C0-8EE4-78CA089A0DB1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="141630848"/>
+        <c:axId val="141640832"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="141630848"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="141640832"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="141640832"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="141630848"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000022" l="0.70000000000000018" r="0.70000000000000018" t="0.75000000000000022" header="0.3000000000000001" footer="0.3000000000000001"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="108"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="8"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>n = 3000</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Графики!$B$4:$B$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>16</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Графики!$D$27:$D$34</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>17805</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9403</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4920</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4044</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3317</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2987</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2738</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2487</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4C4E-49A3-9476-E67D282226BE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="141685504"/>
+        <c:axId val="141687040"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="141685504"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="141687040"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="141687040"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -1346,344 +2503,6 @@
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75000000000000022" l="0.70000000000000018" r="0.70000000000000018" t="0.75000000000000022" header="0.3000000000000001" footer="0.3000000000000001"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="ru-RU"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:spPr>
-            <a:ln>
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:ln>
-                <a:solidFill>
-                  <a:srgbClr val="FF0000"/>
-                </a:solidFill>
-              </a:ln>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>Графики!$O$4:$O$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>12</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Графики!$Q$4:$Q$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>4557</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>3948</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3448</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>3554</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>3538</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>3696</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>4272</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-6F6D-4B42-88DB-CFE117E40602}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:marker val="1"/>
-        <c:smooth val="0"/>
-        <c:axId val="128556416"/>
-        <c:axId val="142235520"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="128556416"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="142235520"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="142235520"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="128556416"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000011" l="0.70000000000000007" r="0.70000000000000007" t="0.75000000000000011" header="0.30000000000000004" footer="0.30000000000000004"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="ru-RU"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:spPr>
-            <a:ln>
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:ln>
-                <a:solidFill>
-                  <a:srgbClr val="FF0000"/>
-                </a:solidFill>
-              </a:ln>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>Графики!$O$4:$O$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>12</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Графики!$P$4:$P$10</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>21978</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>18990</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>18915</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>19263</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>19123</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>19536</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>20535</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-052C-4765-B247-6AC6F5FF1439}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:marker val="1"/>
-        <c:smooth val="0"/>
-        <c:axId val="130061824"/>
-        <c:axId val="130781568"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="130061824"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="130781568"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="130781568"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="130061824"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000033" l="0.70000000000000029" r="0.70000000000000029" t="0.75000000000000033" header="0.30000000000000016" footer="0.30000000000000016"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
@@ -1856,25 +2675,318 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>9054</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>113168</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="65" cy="172227"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="TextBox 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{99E00BDC-B281-41DE-A145-891E1532423F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9252642" y="8713960"/>
+          <a:ext cx="65" cy="172227"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="ru-RU" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>474897</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>66375</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>887241</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>253497</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="11" name="Диаграмма 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E443F810-5600-4C30-9DCC-5AD5631F4F58}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>869133</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="12" name="Диаграмма 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CF924618-0EBE-45C7-9FEC-B38948D0143F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>860080</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>235390</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="14" name="Диаграмма 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C244D70C-7C69-4FEE-AC69-87AAB93ABCB6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>887239</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>244519</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="15" name="Диаграмма 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{62D131ED-68EE-4A0F-9CBC-7D599203312A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>887241</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>253497</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="16" name="Диаграмма 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9834E67B-593D-4CC3-84B5-CB678D7E053C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>887239</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>244519</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="17" name="Диаграмма 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B83444C0-C37D-421E-91A4-54A85174FBA9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>9053</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>465843</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>156910</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Рисунок 4">
+        <xdr:cNvPr id="2" name="Рисунок 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BCB4897C-D529-49E0-9F69-9210738BDAF8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{77F3D0DE-7688-4F41-B6B2-A8862A31AAEF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1890,7 +3002,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11516008" y="2037030"/>
+          <a:off x="9053" y="0"/>
           <a:ext cx="6251008" cy="1424395"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1902,23 +3014,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>36214</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>446456</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>182892</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>428349</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>128571</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Рисунок 5">
+        <xdr:cNvPr id="3" name="Рисунок 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BC18F56D-86EB-4BFF-98EC-5332254432C5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8AF8B7F6-D74A-4CDC-B0AF-980BCBE244CF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1934,7 +3046,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11516008" y="3621386"/>
+          <a:off x="0" y="1484768"/>
           <a:ext cx="5643145" cy="5162298"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1942,155 +3054,6 @@
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>9052</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>13579</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>525100</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>40739</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name="Диаграмма 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000005000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>9052</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>13579</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>525100</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>176542</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="7" name="Диаграмма 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000007000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>247650</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>552450</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="8" name="Диаграмма 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000008000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>257175</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="6" name="Диаграмма 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000006000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -2359,7 +3322,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W42"/>
+  <dimension ref="A1:W55"/>
   <sheetFormatPr defaultRowHeight="17.850000000000001" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="65.7109375" style="1" customWidth="1"/>
@@ -2437,17 +3400,17 @@
       <c r="N3" s="6"/>
     </row>
     <row r="5" spans="1:23" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="39"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="40"/>
-      <c r="G5" s="33" t="s">
+      <c r="B5" s="37"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="38"/>
+      <c r="G5" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="H5" s="33"/>
+      <c r="H5" s="31"/>
       <c r="S5" s="5"/>
       <c r="T5" s="14"/>
       <c r="U5" s="14"/>
@@ -2458,14 +3421,14 @@
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="36" t="s">
+      <c r="B6" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="34"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="31"/>
       <c r="S6" s="14"/>
       <c r="T6" s="14"/>
       <c r="U6" s="14"/>
@@ -2488,8 +3451,8 @@
       <c r="E7" s="8">
         <v>10000</v>
       </c>
-      <c r="G7" s="33"/>
-      <c r="H7" s="33"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="31"/>
       <c r="S7" s="14"/>
       <c r="T7" s="14"/>
       <c r="U7" s="14"/>
@@ -2497,15 +3460,15 @@
       <c r="W7" s="14"/>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A8" s="37" t="s">
+      <c r="A8" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="37"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
+      <c r="B8" s="35"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="35"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
       <c r="S8" s="14"/>
       <c r="T8" s="14"/>
       <c r="U8" s="14"/>
@@ -2581,13 +3544,13 @@
       <c r="W11" s="5"/>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A12" s="37" t="s">
+      <c r="A12" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="37"/>
-      <c r="C12" s="37"/>
-      <c r="D12" s="37"/>
-      <c r="E12" s="37"/>
+      <c r="B12" s="35"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
       <c r="F12" s="5"/>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.25">
@@ -2600,7 +3563,7 @@
       <c r="C13" s="10">
         <v>232</v>
       </c>
-      <c r="D13" s="41" t="s">
+      <c r="D13" s="39" t="s">
         <v>21</v>
       </c>
       <c r="E13" s="10">
@@ -2618,7 +3581,7 @@
       <c r="C14" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="42"/>
+      <c r="D14" s="40"/>
       <c r="E14" s="10" t="s">
         <v>10</v>
       </c>
@@ -2636,30 +3599,30 @@
       <c r="C15" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="43"/>
+      <c r="D15" s="41"/>
       <c r="E15" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="35" t="s">
+      <c r="A18" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="35"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="35"/>
+      <c r="B18" s="33"/>
+      <c r="C18" s="33"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="33"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B19" s="36" t="s">
+      <c r="B19" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="C19" s="36"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="36"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="34"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
@@ -2679,13 +3642,13 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="37" t="s">
+      <c r="A21" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="B21" s="37"/>
-      <c r="C21" s="37"/>
-      <c r="D21" s="37"/>
-      <c r="E21" s="37"/>
+      <c r="B21" s="35"/>
+      <c r="C21" s="35"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="35"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
@@ -2737,21 +3700,21 @@
       <c r="E24" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="G24" s="20"/>
-      <c r="H24" s="32"/>
-      <c r="I24" s="32"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="30"/>
+      <c r="I24" s="30"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="37" t="s">
+      <c r="A25" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="B25" s="37"/>
-      <c r="C25" s="37"/>
-      <c r="D25" s="37"/>
-      <c r="E25" s="37"/>
-      <c r="G25" s="21"/>
-      <c r="H25" s="18"/>
-      <c r="I25" s="18"/>
+      <c r="B25" s="35"/>
+      <c r="C25" s="35"/>
+      <c r="D25" s="35"/>
+      <c r="E25" s="35"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="17"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
@@ -2769,9 +3732,9 @@
       <c r="E26" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="G26" s="22"/>
-      <c r="H26" s="23"/>
-      <c r="I26" s="24"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="22"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
@@ -2789,9 +3752,9 @@
       <c r="E27" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="G27" s="22"/>
-      <c r="H27" s="23"/>
-      <c r="I27" s="20"/>
+      <c r="G27" s="20"/>
+      <c r="H27" s="21"/>
+      <c r="I27" s="18"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
@@ -2809,9 +3772,9 @@
       <c r="E28" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="G28" s="25"/>
-      <c r="H28" s="20"/>
-      <c r="I28" s="20"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="18"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C29" s="1" t="s">
@@ -2823,40 +3786,44 @@
       <c r="E29" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G29" s="22"/>
-      <c r="H29" s="23"/>
-      <c r="I29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="21"/>
+      <c r="I29" s="18"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G30" s="25"/>
-      <c r="H30" s="20"/>
-      <c r="I30" s="20"/>
+      <c r="G30" s="23"/>
+      <c r="H30" s="18"/>
+      <c r="I30" s="18"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="35" t="s">
+      <c r="A31" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="B31" s="35"/>
-      <c r="C31" s="35"/>
-      <c r="D31" s="35"/>
-      <c r="E31" s="35"/>
-      <c r="G31" s="22"/>
-      <c r="H31" s="23"/>
-      <c r="I31" s="20"/>
+      <c r="B31" s="37"/>
+      <c r="C31" s="38"/>
+      <c r="D31" s="59" t="s">
+        <v>91</v>
+      </c>
+      <c r="E31" s="59" t="s">
+        <v>91</v>
+      </c>
+      <c r="G31" s="20"/>
+      <c r="H31" s="21"/>
+      <c r="I31" s="18"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B32" s="36" t="s">
+      <c r="B32" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="36"/>
-      <c r="D32" s="36"/>
-      <c r="E32" s="36"/>
-      <c r="G32" s="25"/>
-      <c r="H32" s="20"/>
-      <c r="I32" s="20"/>
+      <c r="C32" s="34"/>
+      <c r="D32" s="34"/>
+      <c r="E32" s="34"/>
+      <c r="G32" s="23"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="18"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
@@ -2874,21 +3841,21 @@
       <c r="E33" s="8">
         <v>10000</v>
       </c>
-      <c r="G33" s="22"/>
-      <c r="H33" s="23"/>
-      <c r="I33" s="20"/>
+      <c r="G33" s="20"/>
+      <c r="H33" s="21"/>
+      <c r="I33" s="18"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="37" t="s">
+      <c r="A34" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="B34" s="37"/>
-      <c r="C34" s="37"/>
-      <c r="D34" s="37"/>
-      <c r="E34" s="37"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="20"/>
-      <c r="I34" s="20"/>
+      <c r="B34" s="35"/>
+      <c r="C34" s="35"/>
+      <c r="D34" s="35"/>
+      <c r="E34" s="35"/>
+      <c r="G34" s="23"/>
+      <c r="H34" s="18"/>
+      <c r="I34" s="18"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
@@ -2906,9 +3873,9 @@
       <c r="E35" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="G35" s="25"/>
-      <c r="H35" s="20"/>
-      <c r="I35" s="20"/>
+      <c r="G35" s="23"/>
+      <c r="H35" s="18"/>
+      <c r="I35" s="18"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
@@ -2926,9 +3893,9 @@
       <c r="E36" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="G36" s="25"/>
-      <c r="H36" s="20"/>
-      <c r="I36" s="20"/>
+      <c r="G36" s="23"/>
+      <c r="H36" s="18"/>
+      <c r="I36" s="18"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
@@ -2946,21 +3913,21 @@
       <c r="E37" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="G37" s="22"/>
-      <c r="H37" s="23"/>
-      <c r="I37" s="20"/>
+      <c r="G37" s="20"/>
+      <c r="H37" s="21"/>
+      <c r="I37" s="18"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="37" t="s">
+      <c r="A38" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="B38" s="37"/>
-      <c r="C38" s="37"/>
-      <c r="D38" s="37"/>
-      <c r="E38" s="37"/>
-      <c r="G38" s="25"/>
-      <c r="H38" s="20"/>
-      <c r="I38" s="20"/>
+      <c r="B38" s="35"/>
+      <c r="C38" s="35"/>
+      <c r="D38" s="35"/>
+      <c r="E38" s="35"/>
+      <c r="G38" s="23"/>
+      <c r="H38" s="18"/>
+      <c r="I38" s="18"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
@@ -2978,9 +3945,9 @@
       <c r="E39" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="G39" s="25"/>
-      <c r="H39" s="20"/>
-      <c r="I39" s="20"/>
+      <c r="G39" s="23"/>
+      <c r="H39" s="18"/>
+      <c r="I39" s="18"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
@@ -2998,9 +3965,9 @@
       <c r="E40" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="G40" s="25"/>
-      <c r="H40" s="20"/>
-      <c r="I40" s="20"/>
+      <c r="G40" s="23"/>
+      <c r="H40" s="18"/>
+      <c r="I40" s="18"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
@@ -3018,24 +3985,196 @@
       <c r="E41" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="G41" s="22"/>
-      <c r="H41" s="23"/>
-      <c r="I41" s="20"/>
+      <c r="G41" s="20"/>
+      <c r="H41" s="21"/>
+      <c r="I41" s="18"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B42" s="34" t="s">
+      <c r="B42" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="C42" s="34"/>
-      <c r="D42" s="34"/>
-      <c r="E42" s="34"/>
+      <c r="C42" s="32"/>
+      <c r="D42" s="32"/>
+      <c r="E42" s="32"/>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" s="36" t="s">
+        <v>82</v>
+      </c>
+      <c r="B44" s="37"/>
+      <c r="C44" s="38"/>
+      <c r="D44" s="59" t="s">
+        <v>92</v>
+      </c>
+      <c r="E44" s="59" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B45" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="C45" s="34"/>
+      <c r="D45" s="34"/>
+      <c r="E45" s="34"/>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B46" s="28">
+        <v>1000</v>
+      </c>
+      <c r="C46" s="28">
+        <v>3000</v>
+      </c>
+      <c r="D46" s="8">
+        <v>7000</v>
+      </c>
+      <c r="E46" s="8">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="B47" s="35"/>
+      <c r="C47" s="35"/>
+      <c r="D47" s="35"/>
+      <c r="E47" s="35"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B48" s="9">
+        <v>16</v>
+      </c>
+      <c r="C48" s="10">
+        <v>123</v>
+      </c>
+      <c r="D48" s="10">
+        <v>378</v>
+      </c>
+      <c r="E48" s="10">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B49" s="9">
+        <v>122</v>
+      </c>
+      <c r="C49" s="10">
+        <v>2103</v>
+      </c>
+      <c r="D49" s="10">
+        <v>26833</v>
+      </c>
+      <c r="E49" s="10">
+        <v>73485</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B50" s="9">
+        <v>139</v>
+      </c>
+      <c r="C50" s="10">
+        <v>2226</v>
+      </c>
+      <c r="D50" s="10">
+        <v>27211</v>
+      </c>
+      <c r="E50" s="10">
+        <v>74635</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="B51" s="35"/>
+      <c r="C51" s="35"/>
+      <c r="D51" s="35"/>
+      <c r="E51" s="35"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B52" s="9">
+        <v>8</v>
+      </c>
+      <c r="C52" s="10">
+        <v>114</v>
+      </c>
+      <c r="D52" s="10">
+        <v>627</v>
+      </c>
+      <c r="E52" s="10">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B53" s="9">
+        <v>145</v>
+      </c>
+      <c r="C53" s="10">
+        <v>6258</v>
+      </c>
+      <c r="D53" s="10">
+        <v>77559</v>
+      </c>
+      <c r="E53" s="10">
+        <v>224458</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B54" s="9">
+        <v>155</v>
+      </c>
+      <c r="C54" s="10">
+        <v>6373</v>
+      </c>
+      <c r="D54" s="10">
+        <v>78186</v>
+      </c>
+      <c r="E54" s="10">
+        <v>225744</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C55" s="1" t="s">
+        <v>83</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="22">
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A31:C31"/>
     <mergeCell ref="H24:I24"/>
     <mergeCell ref="G5:H8"/>
     <mergeCell ref="B42:E42"/>
-    <mergeCell ref="A31:E31"/>
     <mergeCell ref="B32:E32"/>
     <mergeCell ref="A34:E34"/>
     <mergeCell ref="A38:E38"/>
@@ -3050,6 +4189,10 @@
     <mergeCell ref="A25:E25"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="E31" location="Графики!A1" display="Соотв. графики" xr:uid="{B555E463-05C4-4E05-8D89-54A4D9AA7A6E}"/>
+    <hyperlink ref="E44" location="Графики!A24" display="Соотв. графики" xr:uid="{E92A20FD-A4FF-4EDF-8463-75004668F010}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -3058,337 +4201,920 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B2:S24"/>
+  <dimension ref="A1:Z50"/>
   <sheetFormatPr defaultRowHeight="13.55" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="29"/>
-    <col min="2" max="2" width="23.140625" style="29" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="21.28515625" style="29" customWidth="1"/>
-    <col min="5" max="14" width="9.140625" style="29"/>
-    <col min="15" max="15" width="23" style="29" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="15.28515625" style="29" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" width="15.28515625" style="26" customWidth="1"/>
+    <col min="2" max="2" width="28" style="26" customWidth="1"/>
+    <col min="3" max="3" width="23.5703125" style="26" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" style="26" customWidth="1"/>
+    <col min="5" max="17" width="14.28515625" style="26" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="26"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:19" ht="17.850000000000001" x14ac:dyDescent="0.25">
-      <c r="B2" s="17"/>
-      <c r="C2" s="44" t="s">
+    <row r="1" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="59" t="s">
+        <v>90</v>
+      </c>
+      <c r="N1" s="59"/>
+      <c r="O1" s="55"/>
+      <c r="P1" s="52"/>
+      <c r="Q1" s="52"/>
+      <c r="R1" s="52"/>
+      <c r="S1" s="52"/>
+      <c r="T1" s="52"/>
+      <c r="U1" s="52"/>
+      <c r="V1" s="52"/>
+      <c r="W1" s="52"/>
+      <c r="X1" s="52"/>
+      <c r="Y1" s="52"/>
+      <c r="Z1" s="52"/>
+    </row>
+    <row r="2" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="46" t="s">
+        <v>85</v>
+      </c>
+      <c r="B2" s="16"/>
+      <c r="C2" s="42" t="s">
         <v>78</v>
       </c>
-      <c r="D2" s="44"/>
-      <c r="O2" s="17"/>
-      <c r="P2" s="44" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q2" s="44"/>
-      <c r="S2" s="29" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="3" spans="2:19" ht="17.850000000000001" x14ac:dyDescent="0.25">
-      <c r="B3" s="13" t="s">
+      <c r="D2" s="42"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="44"/>
+      <c r="M2" s="44"/>
+      <c r="N2" s="51"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="43"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
+      <c r="T2" s="43"/>
+      <c r="U2" s="43"/>
+      <c r="V2" s="43"/>
+      <c r="W2" s="43"/>
+      <c r="X2" s="43"/>
+      <c r="Y2" s="43"/>
+      <c r="Z2" s="43"/>
+    </row>
+    <row r="3" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="46"/>
+      <c r="B3" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="C3" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="D3" s="28" t="s">
+      <c r="D3" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="O3" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="P3" s="28" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q3" s="28" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="4" spans="2:19" ht="17.850000000000001" x14ac:dyDescent="0.25">
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="44"/>
+      <c r="J3" s="44"/>
+      <c r="K3" s="44"/>
+      <c r="L3" s="44"/>
+      <c r="M3" s="44"/>
+      <c r="N3" s="51"/>
+      <c r="O3" s="56"/>
+      <c r="P3" s="43"/>
+      <c r="Q3" s="43"/>
+      <c r="R3" s="43"/>
+      <c r="S3" s="43"/>
+      <c r="T3" s="43"/>
+      <c r="U3" s="43"/>
+      <c r="V3" s="43"/>
+      <c r="W3" s="43"/>
+      <c r="X3" s="43"/>
+      <c r="Y3" s="43"/>
+      <c r="Z3" s="43"/>
+    </row>
+    <row r="4" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="46"/>
       <c r="B4" s="15">
         <v>1</v>
       </c>
-      <c r="C4" s="26">
+      <c r="C4" s="24">
         <v>40525</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="60">
         <v>8737</v>
       </c>
-      <c r="O4" s="15">
-        <v>1</v>
-      </c>
-      <c r="P4" s="19">
-        <v>21978</v>
-      </c>
-      <c r="Q4" s="19">
-        <v>4557</v>
-      </c>
-    </row>
-    <row r="5" spans="2:19" ht="17.850000000000001" x14ac:dyDescent="0.25">
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="44"/>
+      <c r="J4" s="44"/>
+      <c r="K4" s="44"/>
+      <c r="L4" s="44"/>
+      <c r="M4" s="44"/>
+      <c r="N4" s="51"/>
+      <c r="O4" s="56"/>
+      <c r="P4" s="43"/>
+      <c r="Q4" s="43"/>
+      <c r="R4" s="43"/>
+      <c r="S4" s="43"/>
+      <c r="T4" s="43"/>
+      <c r="U4" s="43"/>
+      <c r="V4" s="43"/>
+      <c r="W4" s="43"/>
+      <c r="X4" s="43"/>
+      <c r="Y4" s="43"/>
+      <c r="Z4" s="43"/>
+    </row>
+    <row r="5" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="46"/>
       <c r="B5" s="15">
         <v>2</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="24">
         <v>40933</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="60">
         <v>8116</v>
       </c>
-      <c r="O5" s="15">
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="44"/>
+      <c r="I5" s="44"/>
+      <c r="J5" s="44"/>
+      <c r="K5" s="44"/>
+      <c r="L5" s="44"/>
+      <c r="M5" s="44"/>
+      <c r="N5" s="51"/>
+      <c r="O5" s="56"/>
+      <c r="P5" s="43"/>
+      <c r="Q5" s="43"/>
+      <c r="R5" s="43"/>
+      <c r="S5" s="43"/>
+      <c r="T5" s="43"/>
+      <c r="U5" s="43"/>
+      <c r="V5" s="43"/>
+      <c r="W5" s="43"/>
+      <c r="X5" s="43"/>
+      <c r="Y5" s="43"/>
+      <c r="Z5" s="43"/>
+    </row>
+    <row r="6" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="46"/>
+      <c r="B6" s="15">
+        <v>4</v>
+      </c>
+      <c r="C6" s="24">
+        <v>34657</v>
+      </c>
+      <c r="D6" s="60">
+        <v>7387</v>
+      </c>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="44"/>
+      <c r="J6" s="44"/>
+      <c r="K6" s="44"/>
+      <c r="L6" s="44"/>
+      <c r="M6" s="44"/>
+      <c r="N6" s="51"/>
+      <c r="O6" s="57"/>
+    </row>
+    <row r="7" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="46"/>
+      <c r="B7" s="15">
+        <v>6</v>
+      </c>
+      <c r="C7" s="24">
+        <v>38071</v>
+      </c>
+      <c r="D7" s="60">
+        <v>7472</v>
+      </c>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="44"/>
+      <c r="I7" s="44"/>
+      <c r="J7" s="44"/>
+      <c r="K7" s="44"/>
+      <c r="L7" s="44"/>
+      <c r="M7" s="44"/>
+      <c r="N7" s="51"/>
+      <c r="O7" s="57"/>
+    </row>
+    <row r="8" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="46"/>
+      <c r="B8" s="15">
+        <v>8</v>
+      </c>
+      <c r="C8" s="24">
+        <v>37594</v>
+      </c>
+      <c r="D8" s="60">
+        <v>7389</v>
+      </c>
+      <c r="E8" s="44"/>
+      <c r="F8" s="44"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="44"/>
+      <c r="J8" s="44"/>
+      <c r="K8" s="44"/>
+      <c r="L8" s="44"/>
+      <c r="M8" s="44"/>
+      <c r="N8" s="51"/>
+      <c r="O8" s="57"/>
+    </row>
+    <row r="9" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="46"/>
+      <c r="B9" s="15">
+        <v>10</v>
+      </c>
+      <c r="C9" s="24">
+        <v>36931</v>
+      </c>
+      <c r="D9" s="60">
+        <v>8155</v>
+      </c>
+      <c r="E9" s="44"/>
+      <c r="F9" s="44"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="44"/>
+      <c r="I9" s="44"/>
+      <c r="J9" s="44"/>
+      <c r="K9" s="44"/>
+      <c r="L9" s="44"/>
+      <c r="M9" s="44"/>
+      <c r="N9" s="51"/>
+      <c r="O9" s="57"/>
+    </row>
+    <row r="10" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="46"/>
+      <c r="B10" s="15">
+        <v>12</v>
+      </c>
+      <c r="C10" s="24">
+        <v>40896</v>
+      </c>
+      <c r="D10" s="60">
+        <v>8411</v>
+      </c>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="44"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="44"/>
+      <c r="M10" s="44"/>
+      <c r="N10" s="51"/>
+      <c r="O10" s="57"/>
+    </row>
+    <row r="11" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="46"/>
+      <c r="B11" s="15">
+        <v>16</v>
+      </c>
+      <c r="C11" s="24">
+        <v>39364</v>
+      </c>
+      <c r="D11" s="60">
+        <v>7844</v>
+      </c>
+      <c r="E11" s="44"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="44"/>
+      <c r="I11" s="44"/>
+      <c r="J11" s="44"/>
+      <c r="K11" s="44"/>
+      <c r="L11" s="44"/>
+      <c r="M11" s="44"/>
+      <c r="N11" s="51"/>
+      <c r="O11" s="57"/>
+      <c r="P11" s="27"/>
+      <c r="Q11" s="27"/>
+    </row>
+    <row r="12" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="46"/>
+      <c r="B12" s="47" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="D12" s="48"/>
+      <c r="E12" s="48"/>
+      <c r="F12" s="48"/>
+      <c r="G12" s="48"/>
+      <c r="H12" s="48"/>
+      <c r="I12" s="48"/>
+      <c r="J12" s="48"/>
+      <c r="K12" s="48"/>
+      <c r="L12" s="48"/>
+      <c r="M12" s="48"/>
+      <c r="N12" s="53"/>
+      <c r="O12" s="58"/>
+      <c r="P12" s="23"/>
+      <c r="Q12" s="23"/>
+    </row>
+    <row r="13" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="46" t="s">
+        <v>87</v>
+      </c>
+      <c r="B13" s="16"/>
+      <c r="C13" s="42" t="s">
+        <v>78</v>
+      </c>
+      <c r="D13" s="42"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="44"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="44"/>
+      <c r="I13" s="44"/>
+      <c r="J13" s="44"/>
+      <c r="K13" s="44"/>
+      <c r="L13" s="44"/>
+      <c r="M13" s="44"/>
+      <c r="N13" s="51"/>
+      <c r="O13" s="58"/>
+      <c r="P13" s="23"/>
+      <c r="Q13" s="23"/>
+    </row>
+    <row r="14" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="46"/>
+      <c r="B14" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="D14" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="E14" s="45"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="44"/>
+      <c r="J14" s="44"/>
+      <c r="K14" s="44"/>
+      <c r="L14" s="44"/>
+      <c r="M14" s="44"/>
+      <c r="N14" s="51"/>
+      <c r="O14" s="58"/>
+      <c r="P14" s="23"/>
+      <c r="Q14" s="23"/>
+    </row>
+    <row r="15" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="46"/>
+      <c r="B15" s="15">
+        <v>1</v>
+      </c>
+      <c r="C15" s="60">
+        <v>21978</v>
+      </c>
+      <c r="D15" s="60">
+        <v>4557</v>
+      </c>
+      <c r="E15" s="44"/>
+      <c r="F15" s="44"/>
+      <c r="G15" s="44"/>
+      <c r="H15" s="44"/>
+      <c r="I15" s="44"/>
+      <c r="J15" s="44"/>
+      <c r="K15" s="44"/>
+      <c r="L15" s="44"/>
+      <c r="M15" s="44"/>
+      <c r="N15" s="51"/>
+      <c r="O15" s="57"/>
+      <c r="P15" s="27"/>
+      <c r="Q15" s="27"/>
+    </row>
+    <row r="16" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="46"/>
+      <c r="B16" s="15">
         <v>2</v>
       </c>
-      <c r="P5" s="19">
+      <c r="C16" s="60">
         <v>18990</v>
       </c>
-      <c r="Q5" s="19">
+      <c r="D16" s="60">
         <v>3948</v>
       </c>
-    </row>
-    <row r="6" spans="2:19" ht="17.850000000000001" x14ac:dyDescent="0.25">
-      <c r="B6" s="16">
-        <v>3</v>
-      </c>
-      <c r="C6" s="16">
-        <v>35748</v>
-      </c>
-      <c r="D6" s="16">
-        <v>8005</v>
-      </c>
-      <c r="O6" s="15">
+      <c r="E16" s="44"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="44"/>
+      <c r="I16" s="44"/>
+      <c r="J16" s="44"/>
+      <c r="K16" s="44"/>
+      <c r="L16" s="44"/>
+      <c r="M16" s="44"/>
+      <c r="N16" s="51"/>
+      <c r="O16" s="58"/>
+      <c r="P16" s="23"/>
+      <c r="Q16" s="23"/>
+    </row>
+    <row r="17" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="46"/>
+      <c r="B17" s="15">
         <v>4</v>
       </c>
-      <c r="P6" s="19">
+      <c r="C17" s="60">
         <v>18915</v>
       </c>
-      <c r="Q6" s="19">
+      <c r="D17" s="60">
         <v>3448</v>
       </c>
-    </row>
-    <row r="7" spans="2:19" ht="17.850000000000001" x14ac:dyDescent="0.25">
-      <c r="B7" s="15">
+      <c r="E17" s="44"/>
+      <c r="F17" s="44"/>
+      <c r="G17" s="44"/>
+      <c r="H17" s="44"/>
+      <c r="I17" s="44"/>
+      <c r="J17" s="44"/>
+      <c r="K17" s="44"/>
+      <c r="L17" s="44"/>
+      <c r="M17" s="44"/>
+      <c r="N17" s="51"/>
+      <c r="O17" s="58"/>
+      <c r="P17" s="23"/>
+      <c r="Q17" s="23"/>
+    </row>
+    <row r="18" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="46"/>
+      <c r="B18" s="15">
+        <v>6</v>
+      </c>
+      <c r="C18" s="60">
+        <v>19263</v>
+      </c>
+      <c r="D18" s="60">
+        <v>3554</v>
+      </c>
+      <c r="E18" s="44"/>
+      <c r="F18" s="44"/>
+      <c r="G18" s="44"/>
+      <c r="H18" s="44"/>
+      <c r="I18" s="44"/>
+      <c r="J18" s="44"/>
+      <c r="K18" s="44"/>
+      <c r="L18" s="44"/>
+      <c r="M18" s="44"/>
+      <c r="N18" s="51"/>
+      <c r="O18" s="58"/>
+      <c r="P18" s="23"/>
+      <c r="Q18" s="23"/>
+    </row>
+    <row r="19" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="46"/>
+      <c r="B19" s="15">
+        <v>8</v>
+      </c>
+      <c r="C19" s="24">
+        <v>19123</v>
+      </c>
+      <c r="D19" s="60">
+        <v>3538</v>
+      </c>
+      <c r="E19" s="44"/>
+      <c r="F19" s="44"/>
+      <c r="G19" s="44"/>
+      <c r="H19" s="44"/>
+      <c r="I19" s="44"/>
+      <c r="J19" s="44"/>
+      <c r="K19" s="44"/>
+      <c r="L19" s="44"/>
+      <c r="M19" s="44"/>
+      <c r="N19" s="51"/>
+      <c r="O19" s="57"/>
+    </row>
+    <row r="20" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="46"/>
+      <c r="B20" s="15">
+        <v>10</v>
+      </c>
+      <c r="C20" s="24">
+        <v>19536</v>
+      </c>
+      <c r="D20" s="60">
+        <v>3696</v>
+      </c>
+      <c r="E20" s="44"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="44"/>
+      <c r="I20" s="44"/>
+      <c r="J20" s="44"/>
+      <c r="K20" s="44"/>
+      <c r="L20" s="44"/>
+      <c r="M20" s="44"/>
+      <c r="N20" s="51"/>
+      <c r="O20" s="57"/>
+    </row>
+    <row r="21" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="46"/>
+      <c r="B21" s="15">
+        <v>12</v>
+      </c>
+      <c r="C21" s="24">
+        <v>20535</v>
+      </c>
+      <c r="D21" s="60">
+        <v>4272</v>
+      </c>
+      <c r="E21" s="44"/>
+      <c r="F21" s="44"/>
+      <c r="G21" s="44"/>
+      <c r="H21" s="44"/>
+      <c r="I21" s="44"/>
+      <c r="J21" s="44"/>
+      <c r="K21" s="44"/>
+      <c r="L21" s="44"/>
+      <c r="M21" s="44"/>
+      <c r="N21" s="51"/>
+      <c r="O21" s="57"/>
+    </row>
+    <row r="22" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="46"/>
+      <c r="B22" s="49" t="s">
+        <v>86</v>
+      </c>
+      <c r="C22" s="50" t="s">
+        <v>88</v>
+      </c>
+      <c r="D22" s="50"/>
+      <c r="E22" s="50"/>
+      <c r="F22" s="50"/>
+      <c r="G22" s="50"/>
+      <c r="H22" s="50"/>
+      <c r="I22" s="50"/>
+      <c r="J22" s="50"/>
+      <c r="K22" s="50"/>
+      <c r="L22" s="50"/>
+      <c r="M22" s="50"/>
+      <c r="N22" s="54"/>
+      <c r="O22" s="57"/>
+    </row>
+    <row r="23" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="46"/>
+      <c r="B23" s="49"/>
+      <c r="C23" s="50"/>
+      <c r="D23" s="50"/>
+      <c r="E23" s="50"/>
+      <c r="F23" s="50"/>
+      <c r="G23" s="50"/>
+      <c r="H23" s="50"/>
+      <c r="I23" s="50"/>
+      <c r="J23" s="50"/>
+      <c r="K23" s="50"/>
+      <c r="L23" s="50"/>
+      <c r="M23" s="50"/>
+      <c r="N23" s="54"/>
+      <c r="O23" s="57"/>
+    </row>
+    <row r="24" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="33" t="s">
+        <v>89</v>
+      </c>
+      <c r="B24" s="33"/>
+      <c r="C24" s="33"/>
+      <c r="D24" s="33"/>
+      <c r="E24" s="33"/>
+      <c r="F24" s="33"/>
+      <c r="G24" s="33"/>
+      <c r="H24" s="33"/>
+      <c r="I24" s="33"/>
+      <c r="J24" s="33"/>
+      <c r="K24" s="33"/>
+      <c r="L24" s="33"/>
+      <c r="M24" s="59" t="s">
+        <v>90</v>
+      </c>
+      <c r="N24" s="59"/>
+      <c r="O24" s="57"/>
+    </row>
+    <row r="25" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="46" t="s">
+        <v>85</v>
+      </c>
+      <c r="B25" s="16"/>
+      <c r="C25" s="42" t="s">
+        <v>78</v>
+      </c>
+      <c r="D25" s="42"/>
+      <c r="E25" s="44"/>
+      <c r="F25" s="44"/>
+      <c r="G25" s="44"/>
+      <c r="H25" s="44"/>
+      <c r="I25" s="44"/>
+      <c r="J25" s="44"/>
+      <c r="K25" s="44"/>
+      <c r="L25" s="44"/>
+      <c r="M25" s="44"/>
+      <c r="N25" s="51"/>
+      <c r="O25" s="57"/>
+    </row>
+    <row r="26" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="46"/>
+      <c r="B26" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="C26" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="D26" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="E26" s="44"/>
+      <c r="F26" s="44"/>
+      <c r="G26" s="44"/>
+      <c r="H26" s="44"/>
+      <c r="I26" s="44"/>
+      <c r="J26" s="44"/>
+      <c r="K26" s="44"/>
+      <c r="L26" s="44"/>
+      <c r="M26" s="44"/>
+      <c r="N26" s="51"/>
+      <c r="O26" s="57"/>
+    </row>
+    <row r="27" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="46"/>
+      <c r="B27" s="15">
+        <v>1</v>
+      </c>
+      <c r="C27" s="24">
+        <v>84305</v>
+      </c>
+      <c r="D27" s="60">
+        <v>17805</v>
+      </c>
+      <c r="E27" s="44"/>
+      <c r="F27" s="44"/>
+      <c r="G27" s="44"/>
+      <c r="H27" s="44"/>
+      <c r="I27" s="44"/>
+      <c r="J27" s="44"/>
+      <c r="K27" s="44"/>
+      <c r="L27" s="44"/>
+      <c r="M27" s="44"/>
+      <c r="N27" s="51"/>
+      <c r="O27" s="57"/>
+    </row>
+    <row r="28" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="46"/>
+      <c r="B28" s="15">
+        <v>2</v>
+      </c>
+      <c r="C28" s="24">
+        <v>42965</v>
+      </c>
+      <c r="D28" s="60">
+        <v>9403</v>
+      </c>
+      <c r="E28" s="44"/>
+      <c r="F28" s="44"/>
+      <c r="G28" s="44"/>
+      <c r="H28" s="44"/>
+      <c r="I28" s="44"/>
+      <c r="J28" s="44"/>
+      <c r="K28" s="44"/>
+      <c r="L28" s="44"/>
+      <c r="M28" s="44"/>
+      <c r="N28" s="51"/>
+      <c r="O28" s="57"/>
+    </row>
+    <row r="29" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="46"/>
+      <c r="B29" s="15">
         <v>4</v>
       </c>
-      <c r="C7" s="26">
-        <v>34657</v>
-      </c>
-      <c r="D7" s="19">
-        <v>7387</v>
-      </c>
-      <c r="O7" s="15">
+      <c r="C29" s="24">
+        <v>23077</v>
+      </c>
+      <c r="D29" s="60">
+        <v>4920</v>
+      </c>
+      <c r="E29" s="44"/>
+      <c r="F29" s="44"/>
+      <c r="G29" s="44"/>
+      <c r="H29" s="44"/>
+      <c r="I29" s="44"/>
+      <c r="J29" s="44"/>
+      <c r="K29" s="44"/>
+      <c r="L29" s="44"/>
+      <c r="M29" s="44"/>
+      <c r="N29" s="51"/>
+      <c r="O29" s="57"/>
+    </row>
+    <row r="30" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="46"/>
+      <c r="B30" s="15">
         <v>6</v>
       </c>
-      <c r="P7" s="19">
-        <v>19263</v>
-      </c>
-      <c r="Q7" s="19">
-        <v>3554</v>
-      </c>
-    </row>
-    <row r="8" spans="2:19" ht="17.850000000000001" x14ac:dyDescent="0.25">
-      <c r="B8" s="16">
-        <v>5</v>
-      </c>
-      <c r="C8" s="16">
-        <v>36335</v>
-      </c>
-      <c r="D8" s="16">
-        <v>6863</v>
-      </c>
-      <c r="O8" s="15">
+      <c r="C30" s="24">
+        <v>18001</v>
+      </c>
+      <c r="D30" s="60">
+        <v>4044</v>
+      </c>
+      <c r="E30" s="44"/>
+      <c r="F30" s="44"/>
+      <c r="G30" s="44"/>
+      <c r="H30" s="44"/>
+      <c r="I30" s="44"/>
+      <c r="J30" s="44"/>
+      <c r="K30" s="44"/>
+      <c r="L30" s="44"/>
+      <c r="M30" s="44"/>
+      <c r="N30" s="51"/>
+      <c r="O30" s="57"/>
+    </row>
+    <row r="31" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="46"/>
+      <c r="B31" s="15">
         <v>8</v>
       </c>
-      <c r="P8" s="26">
-        <v>19123</v>
-      </c>
-      <c r="Q8" s="19">
-        <v>3538</v>
-      </c>
-    </row>
-    <row r="9" spans="2:19" ht="17.850000000000001" x14ac:dyDescent="0.25">
-      <c r="B9" s="15">
-        <v>6</v>
-      </c>
-      <c r="C9" s="26">
-        <v>38071</v>
-      </c>
-      <c r="D9" s="19">
-        <v>7472</v>
-      </c>
-      <c r="O9" s="15">
+      <c r="C31" s="24">
+        <v>14258</v>
+      </c>
+      <c r="D31" s="60">
+        <v>3317</v>
+      </c>
+      <c r="E31" s="44"/>
+      <c r="F31" s="44"/>
+      <c r="G31" s="44"/>
+      <c r="H31" s="44"/>
+      <c r="I31" s="44"/>
+      <c r="J31" s="44"/>
+      <c r="K31" s="44"/>
+      <c r="L31" s="44"/>
+      <c r="M31" s="44"/>
+      <c r="N31" s="51"/>
+      <c r="O31" s="57"/>
+    </row>
+    <row r="32" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="46"/>
+      <c r="B32" s="15">
         <v>10</v>
       </c>
-      <c r="P9" s="26">
-        <v>19536</v>
-      </c>
-      <c r="Q9" s="19">
-        <v>3696</v>
-      </c>
-    </row>
-    <row r="10" spans="2:19" ht="17.850000000000001" x14ac:dyDescent="0.25">
-      <c r="B10" s="16">
-        <v>7</v>
-      </c>
-      <c r="C10" s="16">
-        <v>36151</v>
-      </c>
-      <c r="D10" s="16">
-        <v>6861</v>
-      </c>
-      <c r="O10" s="15">
+      <c r="C32" s="24">
+        <v>12636</v>
+      </c>
+      <c r="D32" s="60">
+        <v>2987</v>
+      </c>
+      <c r="E32" s="44"/>
+      <c r="F32" s="44"/>
+      <c r="G32" s="44"/>
+      <c r="H32" s="44"/>
+      <c r="I32" s="44"/>
+      <c r="J32" s="44"/>
+      <c r="K32" s="44"/>
+      <c r="L32" s="44"/>
+      <c r="M32" s="44"/>
+      <c r="N32" s="51"/>
+      <c r="O32" s="57"/>
+    </row>
+    <row r="33" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="46"/>
+      <c r="B33" s="15">
         <v>12</v>
       </c>
-      <c r="P10" s="26">
-        <v>20535</v>
-      </c>
-      <c r="Q10" s="19">
-        <v>4272</v>
-      </c>
-    </row>
-    <row r="11" spans="2:19" ht="17.850000000000001" x14ac:dyDescent="0.25">
-      <c r="B11" s="15">
-        <v>8</v>
-      </c>
-      <c r="C11" s="26">
-        <v>37594</v>
-      </c>
-      <c r="D11" s="19">
-        <v>7389</v>
-      </c>
-      <c r="O11" s="31"/>
-      <c r="P11" s="31"/>
-      <c r="Q11" s="31"/>
-    </row>
-    <row r="12" spans="2:19" ht="17.850000000000001" x14ac:dyDescent="0.25">
-      <c r="B12" s="16">
-        <v>9</v>
-      </c>
-      <c r="C12" s="16">
-        <v>36727</v>
-      </c>
-      <c r="D12" s="16">
-        <v>7908</v>
-      </c>
-      <c r="E12" s="30"/>
-      <c r="O12" s="25"/>
-      <c r="P12" s="25"/>
-      <c r="Q12" s="25"/>
-    </row>
-    <row r="13" spans="2:19" ht="17.850000000000001" x14ac:dyDescent="0.25">
-      <c r="B13" s="16">
-        <v>10</v>
-      </c>
-      <c r="C13" s="16">
-        <v>36931</v>
-      </c>
-      <c r="D13" s="16">
-        <v>8155</v>
-      </c>
-      <c r="O13" s="25"/>
-      <c r="P13" s="25"/>
-      <c r="Q13" s="25"/>
-    </row>
-    <row r="14" spans="2:19" ht="17.850000000000001" x14ac:dyDescent="0.25">
-      <c r="B14" s="16">
-        <v>11</v>
-      </c>
-      <c r="C14" s="16">
-        <v>38323</v>
-      </c>
-      <c r="D14" s="16">
-        <v>7985</v>
-      </c>
-      <c r="O14" s="25"/>
-      <c r="P14" s="25"/>
-      <c r="Q14" s="25"/>
-    </row>
-    <row r="15" spans="2:19" ht="17.850000000000001" x14ac:dyDescent="0.25">
-      <c r="B15" s="15">
-        <v>12</v>
-      </c>
-      <c r="C15" s="26">
-        <v>40896</v>
-      </c>
-      <c r="D15" s="19">
-        <v>8411</v>
-      </c>
-      <c r="O15" s="31"/>
-      <c r="P15" s="31"/>
-      <c r="Q15" s="31"/>
-    </row>
-    <row r="16" spans="2:19" ht="17.850000000000001" x14ac:dyDescent="0.25">
-      <c r="B16" s="16">
-        <v>13</v>
-      </c>
-      <c r="C16" s="16">
-        <v>38132</v>
-      </c>
-      <c r="D16" s="16">
-        <v>8314</v>
-      </c>
-      <c r="O16" s="25"/>
-      <c r="P16" s="25"/>
-      <c r="Q16" s="25"/>
-    </row>
-    <row r="17" spans="2:17" ht="17.850000000000001" x14ac:dyDescent="0.25">
-      <c r="B17" s="16">
-        <v>14</v>
-      </c>
-      <c r="C17" s="16">
-        <v>38962</v>
-      </c>
-      <c r="D17" s="16">
-        <v>8287</v>
-      </c>
-      <c r="O17" s="25"/>
-      <c r="P17" s="25"/>
-      <c r="Q17" s="25"/>
-    </row>
-    <row r="18" spans="2:17" ht="17.850000000000001" x14ac:dyDescent="0.25">
-      <c r="B18" s="16">
-        <v>15</v>
-      </c>
-      <c r="C18" s="16">
-        <v>38825</v>
-      </c>
-      <c r="D18" s="16">
-        <v>8452</v>
-      </c>
-      <c r="O18" s="25"/>
-      <c r="P18" s="25"/>
-      <c r="Q18" s="25"/>
-    </row>
-    <row r="19" spans="2:17" ht="17.850000000000001" x14ac:dyDescent="0.25">
-      <c r="B19" s="15">
+      <c r="C33" s="24">
+        <v>11424</v>
+      </c>
+      <c r="D33" s="60">
+        <v>2738</v>
+      </c>
+      <c r="E33" s="44"/>
+      <c r="F33" s="44"/>
+      <c r="G33" s="44"/>
+      <c r="H33" s="44"/>
+      <c r="I33" s="44"/>
+      <c r="J33" s="44"/>
+      <c r="K33" s="44"/>
+      <c r="L33" s="44"/>
+      <c r="M33" s="44"/>
+      <c r="N33" s="51"/>
+      <c r="O33" s="57"/>
+    </row>
+    <row r="34" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="46"/>
+      <c r="B34" s="15">
         <v>16</v>
       </c>
-      <c r="C19" s="26">
-        <v>39364</v>
-      </c>
-      <c r="D19" s="19">
-        <v>7844</v>
-      </c>
-    </row>
-    <row r="20" spans="2:17" ht="17.850000000000001" x14ac:dyDescent="0.2">
-      <c r="C20" s="27">
-        <v>4</v>
-      </c>
-      <c r="D20" s="27">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" spans="2:17" ht="17.850000000000001" x14ac:dyDescent="0.25">
-      <c r="B24" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
+      <c r="C34" s="24">
+        <v>9939</v>
+      </c>
+      <c r="D34" s="60">
+        <v>2487</v>
+      </c>
+      <c r="E34" s="44"/>
+      <c r="F34" s="44"/>
+      <c r="G34" s="44"/>
+      <c r="H34" s="44"/>
+      <c r="I34" s="44"/>
+      <c r="J34" s="44"/>
+      <c r="K34" s="44"/>
+      <c r="L34" s="44"/>
+      <c r="M34" s="44"/>
+      <c r="N34" s="51"/>
+      <c r="O34" s="57"/>
+    </row>
+    <row r="35" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="46"/>
+      <c r="B35" s="47" t="s">
+        <v>86</v>
+      </c>
+      <c r="C35" s="48" t="s">
+        <v>93</v>
+      </c>
+      <c r="D35" s="48"/>
+      <c r="E35" s="48"/>
+      <c r="F35" s="48"/>
+      <c r="G35" s="48"/>
+      <c r="H35" s="48"/>
+      <c r="I35" s="48"/>
+      <c r="J35" s="48"/>
+      <c r="K35" s="48"/>
+      <c r="L35" s="48"/>
+      <c r="M35" s="48"/>
+      <c r="N35" s="53"/>
+      <c r="O35" s="57"/>
+    </row>
+    <row r="36" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="37" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="38" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="39" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="40" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="41" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="42" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="43" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="44" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="45" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="46" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="47" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="48" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="49" ht="21.6" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="50" ht="21.6" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="14">
+    <mergeCell ref="C22:N23"/>
+    <mergeCell ref="A25:A35"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C35:N35"/>
+    <mergeCell ref="A24:L24"/>
+    <mergeCell ref="M24:N24"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="C13:D13"/>
     <mergeCell ref="C2:D2"/>
-    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="C12:N12"/>
+    <mergeCell ref="A2:A12"/>
+    <mergeCell ref="A13:A23"/>
+    <mergeCell ref="B22:B23"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="M1" location="Таблица!A44" display="Соотв. таблица" xr:uid="{4CD65288-3286-4AD3-A58F-54F99559607B}"/>
+    <hyperlink ref="M24" location="Таблица!A44" display="Соотв. таблица" xr:uid="{9D7BFC76-831B-45ED-A711-BD69FCBDF5EA}"/>
+    <hyperlink ref="M1:N1" location="Таблица!A31" display="Соотв. таблица" xr:uid="{A11C2496-942C-485E-9C90-BC6832A5FEFB}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4269BDC4-CFAE-4A4A-95F0-395DE59C8746}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/DecompositionLU/docs/statistics.xlsx
+++ b/DecompositionLU/docs/statistics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maxim\source\repos\practice\SECOND_COURSE\FOR_ITLAB\ArchBenchs\DecompositionLU\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F99DBD33-6294-41FD-B06B-01AC3F0208A9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D008614A-3AA6-44F3-9329-9BDFFF850BE6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-114" yWindow="-114" windowWidth="27602" windowHeight="15027" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,17 +17,23 @@
     <sheet name="Графики" sheetId="2" r:id="rId2"/>
     <sheet name="Про процессор" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="99">
   <si>
     <t>Я не уверен, будет ли это использоваться в готовой презентации и так ли это надо делать, если да, так что пока считаем, что файл для личного пользования.</t>
   </si>
@@ -376,14 +382,29 @@
     <t>Соотв. Графики</t>
   </si>
   <si>
-    <t>Мне нравится</t>
+    <t>Intel Core i5-1240P 12th Gen</t>
+  </si>
+  <si>
+    <t>LU</t>
+  </si>
+  <si>
+    <t>блок</t>
+  </si>
+  <si>
+    <t>Ускорение S</t>
+  </si>
+  <si>
+    <t>Эффективность</t>
+  </si>
+  <si>
+    <t>Мне нравится, но ускорение могло быть лучше</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -493,8 +514,15 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="GOST Common"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -522,6 +550,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -645,7 +679,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -712,22 +746,41 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -739,6 +792,15 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -748,20 +810,29 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -769,25 +840,8 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -957,7 +1011,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-2BAF-4570-BC3E-1CD3E98D98FB}"/>
+              <c16:uniqueId val="{00000000-D8EE-49E8-A7D9-F83A800C75F4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1136,37 +1190,54 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
+      <c14:style val="108"/>
     </mc:Choice>
     <mc:Fallback>
-      <c:style val="2"/>
+      <c:style val="8"/>
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr/>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0"/>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1400" b="0"/>
+              <a:rPr lang="en-US"/>
               <a:t>n = 3000</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
       <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -1177,31 +1248,27 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
-          <c:spPr>
-            <a:ln>
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
           <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="FF0000"/>
+                <a:schemeClr val="accent6"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln w="9525">
                 <a:solidFill>
-                  <a:srgbClr val="FF0000"/>
+                  <a:schemeClr val="accent6"/>
                 </a:solidFill>
               </a:ln>
+              <a:effectLst/>
             </c:spPr>
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Графики!$B$15:$B$21</c:f>
+              <c:f>Графики!$B$4:$B$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -1222,36 +1289,42 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>16</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Графики!$D$15:$D$21</c:f>
+              <c:f>Графики!$D$47:$D$54</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>4557</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3948</c:v>
+                  <c:v>0.94677230671062429</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3448</c:v>
+                  <c:v>0.90472560975609762</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3554</c:v>
+                  <c:v>0.73380316518298716</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3538</c:v>
+                  <c:v>0.67097527886644559</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3696</c:v>
+                  <c:v>0.59608302644794109</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4272</c:v>
+                  <c:v>0.54191015339663984</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.44745174909529556</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1259,7 +1332,74 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-BEB4-4AD3-9B18-79E032C5B9F9}"/>
+              <c16:uniqueId val="{00000000-3A12-4B35-9283-17F7FE171DB8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="65000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:prstDash val="sysDash"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="65000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:schemeClr val="bg1">
+                    <a:lumMod val="65000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:prstDash val="sysDash"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:val>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="8"/>
+              <c:pt idx="0">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="5">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="6">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="7">
+                <c:v>1</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-3A12-4B35-9283-17F7FE171DB8}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1273,21 +1413,54 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="128556416"/>
-        <c:axId val="142235520"/>
+        <c:axId val="141685504"/>
+        <c:axId val="141687040"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="128556416"/>
+        <c:axId val="141685504"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
+        <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="142235520"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="141687040"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1295,28 +1468,95 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="142235520"/>
+        <c:axId val="141687040"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:min val="3250"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:majorGridlines/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
+        <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="128556416"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="141685504"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
-        <c:majorUnit val="250"/>
       </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
     <c:showDLblsOverMax val="0"/>
   </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
   <c:txPr>
     <a:bodyPr/>
     <a:lstStyle/>
@@ -1331,43 +1571,60 @@
   </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000011" l="0.70000000000000007" r="0.70000000000000007" t="0.75000000000000011" header="0.30000000000000004" footer="0.30000000000000004"/>
+    <c:pageMargins b="0.75000000000000022" l="0.70000000000000018" r="0.70000000000000018" t="0.75000000000000022" header="0.3000000000000001" footer="0.3000000000000001"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
+      <c14:style val="104"/>
     </mc:Choice>
     <mc:Fallback>
-      <c:style val="2"/>
+      <c:style val="4"/>
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr/>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0"/>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1400" b="0"/>
+              <a:rPr lang="en-US"/>
               <a:t>n = 5000</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
       <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -1378,31 +1635,27 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
-          <c:spPr>
-            <a:ln>
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
           <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="FF0000"/>
+                <a:schemeClr val="accent2"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln w="9525">
                 <a:solidFill>
-                  <a:srgbClr val="FF0000"/>
+                  <a:schemeClr val="accent2"/>
                 </a:solidFill>
               </a:ln>
+              <a:effectLst/>
             </c:spPr>
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Графики!$B$15:$B$21</c:f>
+              <c:f>Графики!$B$4:$B$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -1423,44 +1676,26 @@
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>16</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Графики!$C$15:$C$21</c:f>
+              <c:f>Графики!$C$58:$C$65</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>21978</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>18990</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>18915</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>19263</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>19123</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>19536</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>20535</c:v>
-                </c:pt>
+                <c:ptCount val="8"/>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-E356-49E0-978B-AE57A6813BB1}"/>
+              <c16:uniqueId val="{00000000-2B12-40B9-8B93-CCDD969CFAFF}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1474,21 +1709,54 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="130061824"/>
-        <c:axId val="130781568"/>
+        <c:axId val="141630848"/>
+        <c:axId val="141640832"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="130061824"/>
+        <c:axId val="141630848"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
+        <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="130781568"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="141640832"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1496,27 +1764,95 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="130781568"/>
+        <c:axId val="141640832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:min val="18500"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:majorGridlines/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
+        <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="130061824"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="141630848"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
     <c:showDLblsOverMax val="0"/>
   </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
   <c:txPr>
     <a:bodyPr/>
     <a:lstStyle/>
@@ -1531,13 +1867,1693 @@
   </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.75000000000000033" l="0.70000000000000029" r="0.70000000000000029" t="0.75000000000000033" header="0.30000000000000016" footer="0.30000000000000016"/>
+    <c:pageMargins b="0.75000000000000022" l="0.70000000000000018" r="0.70000000000000018" t="0.75000000000000022" header="0.3000000000000001" footer="0.3000000000000001"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="108"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="8"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>n = 3000</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Графики!$D$58:$D$65</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-ACBC-4E97-9F7F-8144F7B32341}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="141685504"/>
+        <c:axId val="141687040"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="141685504"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="141687040"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="141687040"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="141685504"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000022" l="0.70000000000000018" r="0.70000000000000018" t="0.75000000000000022" header="0.3000000000000001" footer="0.3000000000000001"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="104"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="4"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>n = 5000</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="65000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:prstDash val="sysDash"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="65000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:schemeClr val="bg1">
+                    <a:lumMod val="65000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:prstDash val="sysDash"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Графики!$B$37:$B$44</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>16</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-8D33-4C9F-9A87-3B52A026294D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="1"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Графики!$C$68:$C$75</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-8D33-4C9F-9A87-3B52A026294D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="141630848"/>
+        <c:axId val="141640832"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="141630848"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="141640832"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="141640832"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="141630848"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000022" l="0.70000000000000018" r="0.70000000000000018" t="0.75000000000000022" header="0.3000000000000001" footer="0.3000000000000001"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="108"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="8"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>n = 3000</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="65000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:prstDash val="sysDash"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="65000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:schemeClr val="bg1">
+                    <a:lumMod val="65000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:prstDash val="sysDash"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Графики!$B$37:$B$44</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>16</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-0436-4CED-9765-F0D3BD8F27DE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Графики!$D$68:$D$75</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>#DIV/0!</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>#DIV/0!</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>#DIV/0!</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>#DIV/0!</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>#DIV/0!</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>#DIV/0!</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>#DIV/0!</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>#DIV/0!</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:val>
+            <c:numRef>
+              <c:f>Графики!$D$68:$D$75</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-0436-4CED-9765-F0D3BD8F27DE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="141685504"/>
+        <c:axId val="141687040"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="141685504"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="141687040"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="141687040"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="141685504"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000022" l="0.70000000000000018" r="0.70000000000000018" t="0.75000000000000022" header="0.3000000000000001" footer="0.3000000000000001"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="104"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="4"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>n = 5000</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="65000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:prstDash val="sysDash"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="65000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="bg1">
+                    <a:lumMod val="65000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:prstDash val="sysDash"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:val>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="8"/>
+              <c:pt idx="0">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="5">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="6">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="7">
+                <c:v>1</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-F169-486D-B4FD-AEBEAEF395C6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Графики!$C$78:$C$85</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>#DIV/0!</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>#DIV/0!</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>#DIV/0!</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>#DIV/0!</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>#DIV/0!</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>#DIV/0!</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>#DIV/0!</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>#DIV/0!</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:val>
+            <c:numRef>
+              <c:f>Графики!$C$78:$C$85</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-F169-486D-B4FD-AEBEAEF395C6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="141630848"/>
+        <c:axId val="141640832"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="141630848"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="141640832"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="141640832"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="141630848"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000022" l="0.70000000000000018" r="0.70000000000000018" t="0.75000000000000022" header="0.3000000000000001" footer="0.3000000000000001"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart16.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="108"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="8"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>n = 3000</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="65000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:prstDash val="sysDash"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="65000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="bg1">
+                    <a:lumMod val="65000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:prstDash val="sysDash"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:val>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="8"/>
+              <c:pt idx="0">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="5">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="6">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="7">
+                <c:v>1</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-4785-4288-96E0-4870A518189D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="1"/>
+          <c:val>
+            <c:numRef>
+              <c:f>Графики!$D$78:$D$85</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-4785-4288-96E0-4870A518189D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="141685504"/>
+        <c:axId val="141687040"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="141685504"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="141687040"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="141687040"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="141685504"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000022" l="0.70000000000000018" r="0.70000000000000018" t="0.75000000000000022" header="0.3000000000000001" footer="0.3000000000000001"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
@@ -1688,7 +3704,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-6156-4052-AC80-4496F909B3BD}"/>
+              <c16:uniqueId val="{00000000-661F-4E7F-9011-07057B53A2AE}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1868,6 +3884,407 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0"/>
+              <a:t>n = 5000</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Графики!$B$15:$B$21</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>12</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Графики!$C$15:$C$21</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>21978</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>18990</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18915</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19263</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19123</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>19536</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>20535</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-986B-42BF-B001-B92726F26922}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="130061824"/>
+        <c:axId val="130781568"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="130061824"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="130781568"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="130781568"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="18500"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="130061824"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000033" l="0.70000000000000029" r="0.70000000000000029" t="0.75000000000000033" header="0.30000000000000016" footer="0.30000000000000016"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0"/>
+              <a:t>n = 3000</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Графики!$B$15:$B$21</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>12</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Графики!$D$15:$D$21</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>4557</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3948</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3448</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3554</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3538</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3696</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4272</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-86B7-409F-BFC7-51EFCBAB1DD9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="128556416"/>
+        <c:axId val="142235520"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="128556416"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="142235520"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="142235520"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="3250"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="128556416"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="250"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000011" l="0.70000000000000007" r="0.70000000000000007" t="0.75000000000000011" header="0.30000000000000004" footer="0.30000000000000004"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
@@ -2010,7 +4427,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-DA14-44C0-8EE4-78CA089A0DB1}"/>
+              <c16:uniqueId val="{00000000-B9CB-47A3-B77F-907269E8EE8E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2330,7 +4747,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-4C4E-49A3-9476-E67D282226BE}"/>
+              <c16:uniqueId val="{00000000-4CCF-409A-9720-58AF68EBF15A}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2451,6 +4868,1173 @@
           </a:p>
         </c:txPr>
         <c:crossAx val="141685504"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000022" l="0.70000000000000018" r="0.70000000000000018" t="0.75000000000000022" header="0.3000000000000001" footer="0.3000000000000001"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="104"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="4"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>n = 5000</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Графики!$B$4:$B$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>16</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Графики!$C$37:$C$44</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.9621785173978821</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.6532044893183691</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.6833509249486136</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.9128208724926354</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6.6718106995884776</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7.379639355742297</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8.4822416742126983</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A403-4510-B0A7-C71642708FAE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="65000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:prstDash val="sysDash"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="65000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:schemeClr val="bg1">
+                    <a:lumMod val="65000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:prstDash val="sysDash"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Графики!$B$37:$B$44</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>16</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-A403-4510-B0A7-C71642708FAE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="141630848"/>
+        <c:axId val="141640832"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="141630848"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="141640832"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="141640832"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="141630848"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000022" l="0.70000000000000018" r="0.70000000000000018" t="0.75000000000000022" header="0.3000000000000001" footer="0.3000000000000001"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="108"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="8"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>n = 3000</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Графики!$B$4:$B$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>16</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Графики!$D$37:$D$44</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.8935446134212486</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.6189024390243905</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.4028189910979227</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.3678022309315647</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.9608302644794104</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6.5029218407596785</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7.1592279855247289</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-08F3-4284-80ED-8FB8F563121A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="65000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:prstDash val="sysDash"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="65000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:schemeClr val="bg1">
+                    <a:lumMod val="65000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:prstDash val="sysDash"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Графики!$B$37:$B$44</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>16</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-08F3-4284-80ED-8FB8F563121A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="141685504"/>
+        <c:axId val="141687040"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="141685504"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="141687040"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="141687040"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="141685504"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75000000000000022" l="0.70000000000000018" r="0.70000000000000018" t="0.75000000000000022" header="0.3000000000000001" footer="0.3000000000000001"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="104"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="4"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>n = 5000</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Графики!$B$4:$B$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>16</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Графики!$C$47:$C$54</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.98108925869894104</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.91330112232959226</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.78055848749143564</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.73910260906157943</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.66718106995884774</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.61496994631185808</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.53014010463829364</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D878-4984-9A05-F053C0AA2720}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="65000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:prstDash val="sysDash"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="65000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:schemeClr val="bg1">
+                    <a:lumMod val="65000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:prstDash val="sysDash"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:val>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="8"/>
+              <c:pt idx="0">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="5">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="6">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="7">
+                <c:v>1</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-D878-4984-9A05-F053C0AA2720}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="141630848"/>
+        <c:axId val="141640832"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="141630848"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="141640832"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="141640832"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="141630848"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2737,23 +6321,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>887241</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>887240</xdr:colOff>
       <xdr:row>10</xdr:row>
       <xdr:rowOff>253497</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="11" name="Диаграмма 10">
+        <xdr:cNvPr id="21" name="Диаграмма 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E443F810-5600-4C30-9DCC-5AD5631F4F58}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46EFB198-613C-41EB-92C2-302FD7019664}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2775,23 +6359,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>869133</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>887239</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>244519</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="12" name="Диаграмма 11">
+        <xdr:cNvPr id="22" name="Диаграмма 21">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CF924618-0EBE-45C7-9FEC-B38948D0143F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B0B393B-00E7-4859-B5CE-3D4C90F4A0CB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2813,23 +6397,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>860080</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>887240</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>235390</xdr:rowOff>
+      <xdr:rowOff>262550</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="14" name="Диаграмма 13">
+        <xdr:cNvPr id="23" name="Диаграмма 22">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C244D70C-7C69-4FEE-AC69-87AAB93ABCB6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EC7763B0-D6A2-40FC-AABC-A0C2C7C862A0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2851,23 +6435,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>887239</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>244519</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>896347</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>253225</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="15" name="Диаграмма 14">
+        <xdr:cNvPr id="24" name="Диаграмма 23">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{62D131ED-68EE-4A0F-9CBC-7D599203312A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2B63319-8D26-419E-BF23-B2F93296BA93}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2889,23 +6473,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>24</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>887241</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>887240</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>253497</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="16" name="Диаграмма 15">
+        <xdr:cNvPr id="25" name="Диаграмма 24">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9834E67B-593D-4CC3-84B5-CB678D7E053C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40F3455D-E49B-4CC5-A190-A113C13FF81D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2927,23 +6511,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>24</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
+      <xdr:col>13</xdr:col>
       <xdr:colOff>887239</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>244519</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="17" name="Диаграмма 16">
+        <xdr:cNvPr id="26" name="Диаграмма 25">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B83444C0-C37D-421E-91A4-54A85174FBA9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{075FFBB8-9FF2-4DFD-9C58-79595C6527A6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2958,6 +6542,386 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>271603</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>887240</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>271603</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="27" name="Диаграмма 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7506755D-6642-405C-8511-40183F8F0CB9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>271603</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>887239</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>271603</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="28" name="Диаграмма 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ACFE8604-BEA0-4179-A03E-EDEFECE39493}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>271603</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>887240</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>9052</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="31" name="Диаграмма 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7E4DC270-CB1E-4BCA-8B3D-2DBE7BA07785}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>271603</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>887239</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>9052</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="32" name="Диаграмма 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E53FD53-7618-4CC6-B715-29C993CEFFC4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>887240</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>253497</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="33" name="Диаграмма 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{96BE8D23-9B39-4BCE-A90E-A3EDA7391C7D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>887239</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>244519</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="34" name="Диаграмма 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9DF28C9-EEC0-42E6-8D12-29F330DDED3A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId12"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>271603</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>887240</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>271603</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="35" name="Диаграмма 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4FB83698-57D9-4E1F-81B1-F7D536C736C2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId13"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>271603</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>887239</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>271603</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="36" name="Диаграмма 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E666B4E9-8FAF-4AAD-BAA0-2770B11A2FA5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId14"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>271603</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>887240</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>9052</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="37" name="Диаграмма 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F243027-DDE4-4DF5-9C0E-6E65A9006C54}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>271603</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>887239</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>9052</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="38" name="Диаграмма 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92330F2E-1163-4F29-A1BA-33525AB5819C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId16"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2978,8 +6942,8 @@
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>465843</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>156910</xdr:rowOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>21108</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3015,15 +6979,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>36214</xdr:rowOff>
+      <xdr:colOff>63374</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>81481</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>428349</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>128571</xdr:rowOff>
+      <xdr:colOff>491723</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>191945</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3046,8 +7010,52 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="1484768"/>
+          <a:off x="63374" y="1484768"/>
           <a:ext cx="5643145" cy="5162298"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>574735</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>275139</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Рисунок 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{221F9B8A-2F8A-4250-B9AE-2A1DBD282628}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6373640" y="280657"/>
+          <a:ext cx="6368952" cy="1678427"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3400,17 +7408,17 @@
       <c r="N3" s="6"/>
     </row>
     <row r="5" spans="1:23" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="36" t="s">
+      <c r="A5" s="49" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="38"/>
-      <c r="G5" s="31" t="s">
+      <c r="B5" s="50"/>
+      <c r="C5" s="50"/>
+      <c r="D5" s="50"/>
+      <c r="E5" s="51"/>
+      <c r="G5" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="H5" s="31"/>
+      <c r="H5" s="53"/>
       <c r="S5" s="5"/>
       <c r="T5" s="14"/>
       <c r="U5" s="14"/>
@@ -3421,14 +7429,14 @@
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="34" t="s">
+      <c r="B6" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
-      <c r="G6" s="31"/>
-      <c r="H6" s="31"/>
+      <c r="C6" s="46"/>
+      <c r="D6" s="46"/>
+      <c r="E6" s="46"/>
+      <c r="G6" s="53"/>
+      <c r="H6" s="53"/>
       <c r="S6" s="14"/>
       <c r="T6" s="14"/>
       <c r="U6" s="14"/>
@@ -3451,8 +7459,8 @@
       <c r="E7" s="8">
         <v>10000</v>
       </c>
-      <c r="G7" s="31"/>
-      <c r="H7" s="31"/>
+      <c r="G7" s="53"/>
+      <c r="H7" s="53"/>
       <c r="S7" s="14"/>
       <c r="T7" s="14"/>
       <c r="U7" s="14"/>
@@ -3460,15 +7468,15 @@
       <c r="W7" s="14"/>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A8" s="35" t="s">
+      <c r="A8" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="35"/>
-      <c r="C8" s="35"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="35"/>
-      <c r="G8" s="31"/>
-      <c r="H8" s="31"/>
+      <c r="B8" s="47"/>
+      <c r="C8" s="47"/>
+      <c r="D8" s="47"/>
+      <c r="E8" s="47"/>
+      <c r="G8" s="53"/>
+      <c r="H8" s="53"/>
       <c r="S8" s="14"/>
       <c r="T8" s="14"/>
       <c r="U8" s="14"/>
@@ -3544,13 +7552,13 @@
       <c r="W11" s="5"/>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A12" s="35" t="s">
+      <c r="A12" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="35"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="35"/>
+      <c r="B12" s="47"/>
+      <c r="C12" s="47"/>
+      <c r="D12" s="47"/>
+      <c r="E12" s="47"/>
       <c r="F12" s="5"/>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.25">
@@ -3563,7 +7571,7 @@
       <c r="C13" s="10">
         <v>232</v>
       </c>
-      <c r="D13" s="39" t="s">
+      <c r="D13" s="55" t="s">
         <v>21</v>
       </c>
       <c r="E13" s="10">
@@ -3581,7 +7589,7 @@
       <c r="C14" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="40"/>
+      <c r="D14" s="56"/>
       <c r="E14" s="10" t="s">
         <v>10</v>
       </c>
@@ -3599,30 +7607,30 @@
       <c r="C15" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="41"/>
+      <c r="D15" s="57"/>
       <c r="E15" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="33" t="s">
+      <c r="A18" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="33"/>
-      <c r="C18" s="33"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="33"/>
+      <c r="B18" s="58"/>
+      <c r="C18" s="58"/>
+      <c r="D18" s="58"/>
+      <c r="E18" s="58"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B19" s="34" t="s">
+      <c r="B19" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="C19" s="34"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="34"/>
+      <c r="C19" s="46"/>
+      <c r="D19" s="46"/>
+      <c r="E19" s="46"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
@@ -3642,13 +7650,13 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="35" t="s">
+      <c r="A21" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="B21" s="35"/>
-      <c r="C21" s="35"/>
-      <c r="D21" s="35"/>
-      <c r="E21" s="35"/>
+      <c r="B21" s="47"/>
+      <c r="C21" s="47"/>
+      <c r="D21" s="47"/>
+      <c r="E21" s="47"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
@@ -3701,17 +7709,17 @@
         <v>35</v>
       </c>
       <c r="G24" s="18"/>
-      <c r="H24" s="30"/>
-      <c r="I24" s="30"/>
+      <c r="H24" s="52"/>
+      <c r="I24" s="52"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="35" t="s">
+      <c r="A25" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="B25" s="35"/>
-      <c r="C25" s="35"/>
-      <c r="D25" s="35"/>
-      <c r="E25" s="35"/>
+      <c r="B25" s="47"/>
+      <c r="C25" s="47"/>
+      <c r="D25" s="47"/>
+      <c r="E25" s="47"/>
       <c r="G25" s="19"/>
       <c r="H25" s="17"/>
       <c r="I25" s="17"/>
@@ -3796,15 +7804,15 @@
       <c r="I30" s="18"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="36" t="s">
+      <c r="A31" s="49" t="s">
         <v>70</v>
       </c>
-      <c r="B31" s="37"/>
-      <c r="C31" s="38"/>
-      <c r="D31" s="59" t="s">
+      <c r="B31" s="50"/>
+      <c r="C31" s="51"/>
+      <c r="D31" s="48" t="s">
         <v>91</v>
       </c>
-      <c r="E31" s="59" t="s">
+      <c r="E31" s="48" t="s">
         <v>91</v>
       </c>
       <c r="G31" s="20"/>
@@ -3815,12 +7823,12 @@
       <c r="A32" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B32" s="34" t="s">
+      <c r="B32" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="34"/>
-      <c r="D32" s="34"/>
-      <c r="E32" s="34"/>
+      <c r="C32" s="46"/>
+      <c r="D32" s="46"/>
+      <c r="E32" s="46"/>
       <c r="G32" s="23"/>
       <c r="H32" s="18"/>
       <c r="I32" s="18"/>
@@ -3846,13 +7854,13 @@
       <c r="I33" s="18"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="35" t="s">
+      <c r="A34" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="B34" s="35"/>
-      <c r="C34" s="35"/>
-      <c r="D34" s="35"/>
-      <c r="E34" s="35"/>
+      <c r="B34" s="47"/>
+      <c r="C34" s="47"/>
+      <c r="D34" s="47"/>
+      <c r="E34" s="47"/>
       <c r="G34" s="23"/>
       <c r="H34" s="18"/>
       <c r="I34" s="18"/>
@@ -3918,13 +7926,13 @@
       <c r="I37" s="18"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="35" t="s">
+      <c r="A38" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="B38" s="35"/>
-      <c r="C38" s="35"/>
-      <c r="D38" s="35"/>
-      <c r="E38" s="35"/>
+      <c r="B38" s="47"/>
+      <c r="C38" s="47"/>
+      <c r="D38" s="47"/>
+      <c r="E38" s="47"/>
       <c r="G38" s="23"/>
       <c r="H38" s="18"/>
       <c r="I38" s="18"/>
@@ -3990,23 +7998,23 @@
       <c r="I41" s="18"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B42" s="32" t="s">
+      <c r="B42" s="54" t="s">
         <v>66</v>
       </c>
-      <c r="C42" s="32"/>
-      <c r="D42" s="32"/>
-      <c r="E42" s="32"/>
+      <c r="C42" s="54"/>
+      <c r="D42" s="54"/>
+      <c r="E42" s="54"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="36" t="s">
+      <c r="A44" s="49" t="s">
         <v>82</v>
       </c>
-      <c r="B44" s="37"/>
-      <c r="C44" s="38"/>
-      <c r="D44" s="59" t="s">
+      <c r="B44" s="50"/>
+      <c r="C44" s="51"/>
+      <c r="D44" s="48" t="s">
         <v>92</v>
       </c>
-      <c r="E44" s="59" t="s">
+      <c r="E44" s="48" t="s">
         <v>91</v>
       </c>
     </row>
@@ -4014,12 +8022,12 @@
       <c r="A45" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B45" s="34" t="s">
+      <c r="B45" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="C45" s="34"/>
-      <c r="D45" s="34"/>
-      <c r="E45" s="34"/>
+      <c r="C45" s="46"/>
+      <c r="D45" s="46"/>
+      <c r="E45" s="46"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
@@ -4039,13 +8047,19 @@
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="35" t="s">
+      <c r="A47" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="B47" s="35"/>
-      <c r="C47" s="35"/>
-      <c r="D47" s="35"/>
-      <c r="E47" s="35"/>
+      <c r="B47" s="47"/>
+      <c r="C47" s="47"/>
+      <c r="D47" s="47"/>
+      <c r="E47" s="47"/>
+      <c r="G47" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
@@ -4063,8 +8077,14 @@
       <c r="E48" s="10">
         <v>1131</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G48" s="1">
+        <v>32</v>
+      </c>
+      <c r="H48" s="1">
+        <v>73835</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>8</v>
       </c>
@@ -4080,8 +8100,14 @@
       <c r="E49" s="10">
         <v>73485</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G49" s="1">
+        <v>128</v>
+      </c>
+      <c r="H49" s="1">
+        <v>74361</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>9</v>
       </c>
@@ -4097,17 +8123,23 @@
       <c r="E50" s="10">
         <v>74635</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="35" t="s">
+      <c r="G50" s="1">
+        <v>256</v>
+      </c>
+      <c r="H50" s="1">
+        <v>83998</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="B51" s="35"/>
-      <c r="C51" s="35"/>
-      <c r="D51" s="35"/>
-      <c r="E51" s="35"/>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B51" s="47"/>
+      <c r="C51" s="47"/>
+      <c r="D51" s="47"/>
+      <c r="E51" s="47"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>7</v>
       </c>
@@ -4124,7 +8156,7 @@
         <v>1285</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>8</v>
       </c>
@@ -4141,7 +8173,7 @@
         <v>224458</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>9</v>
       </c>
@@ -4158,20 +8190,13 @@
         <v>225744</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="C55" s="1" t="s">
         <v>83</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="B45:E45"/>
-    <mergeCell ref="A47:E47"/>
-    <mergeCell ref="A51:E51"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A31:C31"/>
     <mergeCell ref="H24:I24"/>
     <mergeCell ref="G5:H8"/>
     <mergeCell ref="B42:E42"/>
@@ -4187,6 +8212,13 @@
     <mergeCell ref="B19:E19"/>
     <mergeCell ref="A21:E21"/>
     <mergeCell ref="A25:E25"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A31:C31"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <hyperlinks>
@@ -4201,7 +8233,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Z50"/>
+  <dimension ref="A1:Z86"/>
   <sheetFormatPr defaultRowHeight="13.55" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.28515625" style="26" customWidth="1"/>
@@ -4213,71 +8245,71 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="58" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="59" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="58"/>
+      <c r="J1" s="58"/>
+      <c r="K1" s="58"/>
+      <c r="L1" s="58"/>
+      <c r="M1" s="48" t="s">
         <v>90</v>
       </c>
-      <c r="N1" s="59"/>
-      <c r="O1" s="55"/>
-      <c r="P1" s="52"/>
-      <c r="Q1" s="52"/>
-      <c r="R1" s="52"/>
-      <c r="S1" s="52"/>
-      <c r="T1" s="52"/>
-      <c r="U1" s="52"/>
-      <c r="V1" s="52"/>
-      <c r="W1" s="52"/>
-      <c r="X1" s="52"/>
-      <c r="Y1" s="52"/>
-      <c r="Z1" s="52"/>
+      <c r="N1" s="48"/>
+      <c r="O1" s="36"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="35"/>
+      <c r="R1" s="35"/>
+      <c r="S1" s="35"/>
+      <c r="T1" s="35"/>
+      <c r="U1" s="35"/>
+      <c r="V1" s="35"/>
+      <c r="W1" s="35"/>
+      <c r="X1" s="35"/>
+      <c r="Y1" s="35"/>
+      <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="65" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="42" t="s">
+      <c r="B2" s="44"/>
+      <c r="C2" s="59" t="s">
         <v>78</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
-      <c r="K2" s="44"/>
-      <c r="L2" s="44"/>
-      <c r="M2" s="44"/>
-      <c r="N2" s="51"/>
-      <c r="O2" s="56"/>
-      <c r="P2" s="43"/>
-      <c r="Q2" s="43"/>
-      <c r="R2" s="43"/>
-      <c r="S2" s="43"/>
-      <c r="T2" s="43"/>
-      <c r="U2" s="43"/>
-      <c r="V2" s="43"/>
-      <c r="W2" s="43"/>
-      <c r="X2" s="43"/>
-      <c r="Y2" s="43"/>
-      <c r="Z2" s="43"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="34"/>
+      <c r="O2" s="37"/>
+      <c r="P2" s="30"/>
+      <c r="Q2" s="30"/>
+      <c r="R2" s="30"/>
+      <c r="S2" s="30"/>
+      <c r="T2" s="30"/>
+      <c r="U2" s="30"/>
+      <c r="V2" s="30"/>
+      <c r="W2" s="30"/>
+      <c r="X2" s="30"/>
+      <c r="Y2" s="30"/>
+      <c r="Z2" s="30"/>
     </row>
     <row r="3" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="46"/>
+      <c r="A3" s="65"/>
       <c r="B3" s="29" t="s">
         <v>77</v>
       </c>
@@ -4287,285 +8319,285 @@
       <c r="D3" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
-      <c r="K3" s="44"/>
-      <c r="L3" s="44"/>
-      <c r="M3" s="44"/>
-      <c r="N3" s="51"/>
-      <c r="O3" s="56"/>
-      <c r="P3" s="43"/>
-      <c r="Q3" s="43"/>
-      <c r="R3" s="43"/>
-      <c r="S3" s="43"/>
-      <c r="T3" s="43"/>
-      <c r="U3" s="43"/>
-      <c r="V3" s="43"/>
-      <c r="W3" s="43"/>
-      <c r="X3" s="43"/>
-      <c r="Y3" s="43"/>
-      <c r="Z3" s="43"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="31"/>
+      <c r="L3" s="31"/>
+      <c r="M3" s="31"/>
+      <c r="N3" s="34"/>
+      <c r="O3" s="37"/>
+      <c r="P3" s="30"/>
+      <c r="Q3" s="30"/>
+      <c r="R3" s="30"/>
+      <c r="S3" s="30"/>
+      <c r="T3" s="30"/>
+      <c r="U3" s="30"/>
+      <c r="V3" s="30"/>
+      <c r="W3" s="30"/>
+      <c r="X3" s="30"/>
+      <c r="Y3" s="30"/>
+      <c r="Z3" s="30"/>
     </row>
     <row r="4" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="46"/>
+      <c r="A4" s="65"/>
       <c r="B4" s="15">
         <v>1</v>
       </c>
       <c r="C4" s="24">
         <v>40525</v>
       </c>
-      <c r="D4" s="60">
+      <c r="D4" s="40">
         <v>8737</v>
       </c>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="44"/>
-      <c r="H4" s="44"/>
-      <c r="I4" s="44"/>
-      <c r="J4" s="44"/>
-      <c r="K4" s="44"/>
-      <c r="L4" s="44"/>
-      <c r="M4" s="44"/>
-      <c r="N4" s="51"/>
-      <c r="O4" s="56"/>
-      <c r="P4" s="43"/>
-      <c r="Q4" s="43"/>
-      <c r="R4" s="43"/>
-      <c r="S4" s="43"/>
-      <c r="T4" s="43"/>
-      <c r="U4" s="43"/>
-      <c r="V4" s="43"/>
-      <c r="W4" s="43"/>
-      <c r="X4" s="43"/>
-      <c r="Y4" s="43"/>
-      <c r="Z4" s="43"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="34"/>
+      <c r="O4" s="37"/>
+      <c r="P4" s="30"/>
+      <c r="Q4" s="30"/>
+      <c r="R4" s="30"/>
+      <c r="S4" s="30"/>
+      <c r="T4" s="30"/>
+      <c r="U4" s="30"/>
+      <c r="V4" s="30"/>
+      <c r="W4" s="30"/>
+      <c r="X4" s="30"/>
+      <c r="Y4" s="30"/>
+      <c r="Z4" s="30"/>
     </row>
     <row r="5" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="46"/>
+      <c r="A5" s="65"/>
       <c r="B5" s="15">
         <v>2</v>
       </c>
       <c r="C5" s="24">
         <v>40933</v>
       </c>
-      <c r="D5" s="60">
+      <c r="D5" s="40">
         <v>8116</v>
       </c>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="44"/>
-      <c r="J5" s="44"/>
-      <c r="K5" s="44"/>
-      <c r="L5" s="44"/>
-      <c r="M5" s="44"/>
-      <c r="N5" s="51"/>
-      <c r="O5" s="56"/>
-      <c r="P5" s="43"/>
-      <c r="Q5" s="43"/>
-      <c r="R5" s="43"/>
-      <c r="S5" s="43"/>
-      <c r="T5" s="43"/>
-      <c r="U5" s="43"/>
-      <c r="V5" s="43"/>
-      <c r="W5" s="43"/>
-      <c r="X5" s="43"/>
-      <c r="Y5" s="43"/>
-      <c r="Z5" s="43"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="31"/>
+      <c r="K5" s="31"/>
+      <c r="L5" s="31"/>
+      <c r="M5" s="31"/>
+      <c r="N5" s="34"/>
+      <c r="O5" s="37"/>
+      <c r="P5" s="30"/>
+      <c r="Q5" s="30"/>
+      <c r="R5" s="30"/>
+      <c r="S5" s="30"/>
+      <c r="T5" s="30"/>
+      <c r="U5" s="30"/>
+      <c r="V5" s="30"/>
+      <c r="W5" s="30"/>
+      <c r="X5" s="30"/>
+      <c r="Y5" s="30"/>
+      <c r="Z5" s="30"/>
     </row>
     <row r="6" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="46"/>
+      <c r="A6" s="65"/>
       <c r="B6" s="15">
         <v>4</v>
       </c>
       <c r="C6" s="24">
         <v>34657</v>
       </c>
-      <c r="D6" s="60">
+      <c r="D6" s="40">
         <v>7387</v>
       </c>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="44"/>
-      <c r="L6" s="44"/>
-      <c r="M6" s="44"/>
-      <c r="N6" s="51"/>
-      <c r="O6" s="57"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="31"/>
+      <c r="M6" s="31"/>
+      <c r="N6" s="34"/>
+      <c r="O6" s="38"/>
     </row>
     <row r="7" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="46"/>
+      <c r="A7" s="65"/>
       <c r="B7" s="15">
         <v>6</v>
       </c>
       <c r="C7" s="24">
         <v>38071</v>
       </c>
-      <c r="D7" s="60">
+      <c r="D7" s="40">
         <v>7472</v>
       </c>
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="44"/>
-      <c r="I7" s="44"/>
-      <c r="J7" s="44"/>
-      <c r="K7" s="44"/>
-      <c r="L7" s="44"/>
-      <c r="M7" s="44"/>
-      <c r="N7" s="51"/>
-      <c r="O7" s="57"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="31"/>
+      <c r="L7" s="31"/>
+      <c r="M7" s="31"/>
+      <c r="N7" s="34"/>
+      <c r="O7" s="38"/>
     </row>
     <row r="8" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="46"/>
+      <c r="A8" s="65"/>
       <c r="B8" s="15">
         <v>8</v>
       </c>
       <c r="C8" s="24">
         <v>37594</v>
       </c>
-      <c r="D8" s="60">
+      <c r="D8" s="40">
         <v>7389</v>
       </c>
-      <c r="E8" s="44"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="44"/>
-      <c r="H8" s="44"/>
-      <c r="I8" s="44"/>
-      <c r="J8" s="44"/>
-      <c r="K8" s="44"/>
-      <c r="L8" s="44"/>
-      <c r="M8" s="44"/>
-      <c r="N8" s="51"/>
-      <c r="O8" s="57"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="31"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="31"/>
+      <c r="M8" s="31"/>
+      <c r="N8" s="34"/>
+      <c r="O8" s="38"/>
     </row>
     <row r="9" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="46"/>
+      <c r="A9" s="65"/>
       <c r="B9" s="15">
         <v>10</v>
       </c>
       <c r="C9" s="24">
         <v>36931</v>
       </c>
-      <c r="D9" s="60">
+      <c r="D9" s="40">
         <v>8155</v>
       </c>
-      <c r="E9" s="44"/>
-      <c r="F9" s="44"/>
-      <c r="G9" s="44"/>
-      <c r="H9" s="44"/>
-      <c r="I9" s="44"/>
-      <c r="J9" s="44"/>
-      <c r="K9" s="44"/>
-      <c r="L9" s="44"/>
-      <c r="M9" s="44"/>
-      <c r="N9" s="51"/>
-      <c r="O9" s="57"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="31"/>
+      <c r="K9" s="31"/>
+      <c r="L9" s="31"/>
+      <c r="M9" s="31"/>
+      <c r="N9" s="34"/>
+      <c r="O9" s="38"/>
     </row>
     <row r="10" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="46"/>
+      <c r="A10" s="65"/>
       <c r="B10" s="15">
         <v>12</v>
       </c>
       <c r="C10" s="24">
         <v>40896</v>
       </c>
-      <c r="D10" s="60">
+      <c r="D10" s="40">
         <v>8411</v>
       </c>
-      <c r="E10" s="44"/>
-      <c r="F10" s="44"/>
-      <c r="G10" s="44"/>
-      <c r="H10" s="44"/>
-      <c r="I10" s="44"/>
-      <c r="J10" s="44"/>
-      <c r="K10" s="44"/>
-      <c r="L10" s="44"/>
-      <c r="M10" s="44"/>
-      <c r="N10" s="51"/>
-      <c r="O10" s="57"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="31"/>
+      <c r="M10" s="31"/>
+      <c r="N10" s="34"/>
+      <c r="O10" s="38"/>
     </row>
     <row r="11" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="46"/>
+      <c r="A11" s="65"/>
       <c r="B11" s="15">
         <v>16</v>
       </c>
       <c r="C11" s="24">
         <v>39364</v>
       </c>
-      <c r="D11" s="60">
+      <c r="D11" s="40">
         <v>7844</v>
       </c>
-      <c r="E11" s="44"/>
-      <c r="F11" s="44"/>
-      <c r="G11" s="44"/>
-      <c r="H11" s="44"/>
-      <c r="I11" s="44"/>
-      <c r="J11" s="44"/>
-      <c r="K11" s="44"/>
-      <c r="L11" s="44"/>
-      <c r="M11" s="44"/>
-      <c r="N11" s="51"/>
-      <c r="O11" s="57"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="31"/>
+      <c r="K11" s="31"/>
+      <c r="L11" s="31"/>
+      <c r="M11" s="31"/>
+      <c r="N11" s="34"/>
+      <c r="O11" s="38"/>
       <c r="P11" s="27"/>
       <c r="Q11" s="27"/>
     </row>
     <row r="12" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="46"/>
-      <c r="B12" s="47" t="s">
+      <c r="A12" s="65"/>
+      <c r="B12" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="C12" s="48" t="s">
+      <c r="C12" s="63" t="s">
         <v>81</v>
       </c>
-      <c r="D12" s="48"/>
-      <c r="E12" s="48"/>
-      <c r="F12" s="48"/>
-      <c r="G12" s="48"/>
-      <c r="H12" s="48"/>
-      <c r="I12" s="48"/>
-      <c r="J12" s="48"/>
-      <c r="K12" s="48"/>
-      <c r="L12" s="48"/>
-      <c r="M12" s="48"/>
-      <c r="N12" s="53"/>
-      <c r="O12" s="58"/>
+      <c r="D12" s="63"/>
+      <c r="E12" s="63"/>
+      <c r="F12" s="63"/>
+      <c r="G12" s="63"/>
+      <c r="H12" s="63"/>
+      <c r="I12" s="63"/>
+      <c r="J12" s="63"/>
+      <c r="K12" s="63"/>
+      <c r="L12" s="63"/>
+      <c r="M12" s="63"/>
+      <c r="N12" s="64"/>
+      <c r="O12" s="39"/>
       <c r="P12" s="23"/>
       <c r="Q12" s="23"/>
     </row>
     <row r="13" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="46" t="s">
+      <c r="A13" s="65" t="s">
         <v>87</v>
       </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="42" t="s">
+      <c r="B13" s="44"/>
+      <c r="C13" s="59" t="s">
         <v>78</v>
       </c>
-      <c r="D13" s="42"/>
-      <c r="E13" s="45"/>
-      <c r="F13" s="44"/>
-      <c r="G13" s="44"/>
-      <c r="H13" s="44"/>
-      <c r="I13" s="44"/>
-      <c r="J13" s="44"/>
-      <c r="K13" s="44"/>
-      <c r="L13" s="44"/>
-      <c r="M13" s="44"/>
-      <c r="N13" s="51"/>
-      <c r="O13" s="58"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="31"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="31"/>
+      <c r="K13" s="31"/>
+      <c r="L13" s="31"/>
+      <c r="M13" s="31"/>
+      <c r="N13" s="34"/>
+      <c r="O13" s="39"/>
       <c r="P13" s="23"/>
       <c r="Q13" s="23"/>
     </row>
     <row r="14" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="46"/>
+      <c r="A14" s="65"/>
       <c r="B14" s="13" t="s">
         <v>77</v>
       </c>
@@ -4575,272 +8607,272 @@
       <c r="D14" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="E14" s="45"/>
-      <c r="F14" s="44"/>
-      <c r="G14" s="44"/>
-      <c r="H14" s="44"/>
-      <c r="I14" s="44"/>
-      <c r="J14" s="44"/>
-      <c r="K14" s="44"/>
-      <c r="L14" s="44"/>
-      <c r="M14" s="44"/>
-      <c r="N14" s="51"/>
-      <c r="O14" s="58"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="31"/>
+      <c r="H14" s="31"/>
+      <c r="I14" s="31"/>
+      <c r="J14" s="31"/>
+      <c r="K14" s="31"/>
+      <c r="L14" s="31"/>
+      <c r="M14" s="31"/>
+      <c r="N14" s="34"/>
+      <c r="O14" s="39"/>
       <c r="P14" s="23"/>
       <c r="Q14" s="23"/>
     </row>
     <row r="15" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="46"/>
+      <c r="A15" s="65"/>
       <c r="B15" s="15">
         <v>1</v>
       </c>
-      <c r="C15" s="60">
+      <c r="C15" s="40">
         <v>21978</v>
       </c>
-      <c r="D15" s="60">
+      <c r="D15" s="40">
         <v>4557</v>
       </c>
-      <c r="E15" s="44"/>
-      <c r="F15" s="44"/>
-      <c r="G15" s="44"/>
-      <c r="H15" s="44"/>
-      <c r="I15" s="44"/>
-      <c r="J15" s="44"/>
-      <c r="K15" s="44"/>
-      <c r="L15" s="44"/>
-      <c r="M15" s="44"/>
-      <c r="N15" s="51"/>
-      <c r="O15" s="57"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="31"/>
+      <c r="K15" s="31"/>
+      <c r="L15" s="31"/>
+      <c r="M15" s="31"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="38"/>
       <c r="P15" s="27"/>
       <c r="Q15" s="27"/>
     </row>
     <row r="16" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="46"/>
+      <c r="A16" s="65"/>
       <c r="B16" s="15">
         <v>2</v>
       </c>
-      <c r="C16" s="60">
+      <c r="C16" s="40">
         <v>18990</v>
       </c>
-      <c r="D16" s="60">
+      <c r="D16" s="40">
         <v>3948</v>
       </c>
-      <c r="E16" s="44"/>
-      <c r="F16" s="44"/>
-      <c r="G16" s="44"/>
-      <c r="H16" s="44"/>
-      <c r="I16" s="44"/>
-      <c r="J16" s="44"/>
-      <c r="K16" s="44"/>
-      <c r="L16" s="44"/>
-      <c r="M16" s="44"/>
-      <c r="N16" s="51"/>
-      <c r="O16" s="58"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="31"/>
+      <c r="G16" s="31"/>
+      <c r="H16" s="31"/>
+      <c r="I16" s="31"/>
+      <c r="J16" s="31"/>
+      <c r="K16" s="31"/>
+      <c r="L16" s="31"/>
+      <c r="M16" s="31"/>
+      <c r="N16" s="34"/>
+      <c r="O16" s="39"/>
       <c r="P16" s="23"/>
       <c r="Q16" s="23"/>
     </row>
     <row r="17" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="46"/>
+      <c r="A17" s="65"/>
       <c r="B17" s="15">
         <v>4</v>
       </c>
-      <c r="C17" s="60">
+      <c r="C17" s="40">
         <v>18915</v>
       </c>
-      <c r="D17" s="60">
+      <c r="D17" s="40">
         <v>3448</v>
       </c>
-      <c r="E17" s="44"/>
-      <c r="F17" s="44"/>
-      <c r="G17" s="44"/>
-      <c r="H17" s="44"/>
-      <c r="I17" s="44"/>
-      <c r="J17" s="44"/>
-      <c r="K17" s="44"/>
-      <c r="L17" s="44"/>
-      <c r="M17" s="44"/>
-      <c r="N17" s="51"/>
-      <c r="O17" s="58"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="31"/>
+      <c r="K17" s="31"/>
+      <c r="L17" s="31"/>
+      <c r="M17" s="31"/>
+      <c r="N17" s="34"/>
+      <c r="O17" s="39"/>
       <c r="P17" s="23"/>
       <c r="Q17" s="23"/>
     </row>
     <row r="18" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="46"/>
+      <c r="A18" s="65"/>
       <c r="B18" s="15">
         <v>6</v>
       </c>
-      <c r="C18" s="60">
+      <c r="C18" s="40">
         <v>19263</v>
       </c>
-      <c r="D18" s="60">
+      <c r="D18" s="40">
         <v>3554</v>
       </c>
-      <c r="E18" s="44"/>
-      <c r="F18" s="44"/>
-      <c r="G18" s="44"/>
-      <c r="H18" s="44"/>
-      <c r="I18" s="44"/>
-      <c r="J18" s="44"/>
-      <c r="K18" s="44"/>
-      <c r="L18" s="44"/>
-      <c r="M18" s="44"/>
-      <c r="N18" s="51"/>
-      <c r="O18" s="58"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="31"/>
+      <c r="G18" s="31"/>
+      <c r="H18" s="31"/>
+      <c r="I18" s="31"/>
+      <c r="J18" s="31"/>
+      <c r="K18" s="31"/>
+      <c r="L18" s="31"/>
+      <c r="M18" s="31"/>
+      <c r="N18" s="34"/>
+      <c r="O18" s="39"/>
       <c r="P18" s="23"/>
       <c r="Q18" s="23"/>
     </row>
     <row r="19" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="46"/>
+      <c r="A19" s="65"/>
       <c r="B19" s="15">
         <v>8</v>
       </c>
       <c r="C19" s="24">
         <v>19123</v>
       </c>
-      <c r="D19" s="60">
+      <c r="D19" s="40">
         <v>3538</v>
       </c>
-      <c r="E19" s="44"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="44"/>
-      <c r="H19" s="44"/>
-      <c r="I19" s="44"/>
-      <c r="J19" s="44"/>
-      <c r="K19" s="44"/>
-      <c r="L19" s="44"/>
-      <c r="M19" s="44"/>
-      <c r="N19" s="51"/>
-      <c r="O19" s="57"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="31"/>
+      <c r="G19" s="31"/>
+      <c r="H19" s="31"/>
+      <c r="I19" s="31"/>
+      <c r="J19" s="31"/>
+      <c r="K19" s="31"/>
+      <c r="L19" s="31"/>
+      <c r="M19" s="31"/>
+      <c r="N19" s="34"/>
+      <c r="O19" s="38"/>
     </row>
     <row r="20" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="46"/>
+      <c r="A20" s="65"/>
       <c r="B20" s="15">
         <v>10</v>
       </c>
       <c r="C20" s="24">
         <v>19536</v>
       </c>
-      <c r="D20" s="60">
+      <c r="D20" s="40">
         <v>3696</v>
       </c>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="44"/>
-      <c r="H20" s="44"/>
-      <c r="I20" s="44"/>
-      <c r="J20" s="44"/>
-      <c r="K20" s="44"/>
-      <c r="L20" s="44"/>
-      <c r="M20" s="44"/>
-      <c r="N20" s="51"/>
-      <c r="O20" s="57"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="31"/>
+      <c r="G20" s="31"/>
+      <c r="H20" s="31"/>
+      <c r="I20" s="31"/>
+      <c r="J20" s="31"/>
+      <c r="K20" s="31"/>
+      <c r="L20" s="31"/>
+      <c r="M20" s="31"/>
+      <c r="N20" s="34"/>
+      <c r="O20" s="38"/>
     </row>
     <row r="21" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="46"/>
+      <c r="A21" s="65"/>
       <c r="B21" s="15">
         <v>12</v>
       </c>
       <c r="C21" s="24">
         <v>20535</v>
       </c>
-      <c r="D21" s="60">
+      <c r="D21" s="40">
         <v>4272</v>
       </c>
-      <c r="E21" s="44"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="44"/>
-      <c r="H21" s="44"/>
-      <c r="I21" s="44"/>
-      <c r="J21" s="44"/>
-      <c r="K21" s="44"/>
-      <c r="L21" s="44"/>
-      <c r="M21" s="44"/>
-      <c r="N21" s="51"/>
-      <c r="O21" s="57"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="31"/>
+      <c r="L21" s="31"/>
+      <c r="M21" s="31"/>
+      <c r="N21" s="34"/>
+      <c r="O21" s="38"/>
     </row>
     <row r="22" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="46"/>
-      <c r="B22" s="49" t="s">
+      <c r="A22" s="65"/>
+      <c r="B22" s="66" t="s">
         <v>86</v>
       </c>
-      <c r="C22" s="50" t="s">
+      <c r="C22" s="67" t="s">
         <v>88</v>
       </c>
-      <c r="D22" s="50"/>
-      <c r="E22" s="50"/>
-      <c r="F22" s="50"/>
-      <c r="G22" s="50"/>
-      <c r="H22" s="50"/>
-      <c r="I22" s="50"/>
-      <c r="J22" s="50"/>
-      <c r="K22" s="50"/>
-      <c r="L22" s="50"/>
-      <c r="M22" s="50"/>
-      <c r="N22" s="54"/>
-      <c r="O22" s="57"/>
+      <c r="D22" s="67"/>
+      <c r="E22" s="67"/>
+      <c r="F22" s="67"/>
+      <c r="G22" s="67"/>
+      <c r="H22" s="67"/>
+      <c r="I22" s="67"/>
+      <c r="J22" s="67"/>
+      <c r="K22" s="67"/>
+      <c r="L22" s="67"/>
+      <c r="M22" s="67"/>
+      <c r="N22" s="68"/>
+      <c r="O22" s="38"/>
     </row>
     <row r="23" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="46"/>
-      <c r="B23" s="49"/>
-      <c r="C23" s="50"/>
-      <c r="D23" s="50"/>
-      <c r="E23" s="50"/>
-      <c r="F23" s="50"/>
-      <c r="G23" s="50"/>
-      <c r="H23" s="50"/>
-      <c r="I23" s="50"/>
-      <c r="J23" s="50"/>
-      <c r="K23" s="50"/>
-      <c r="L23" s="50"/>
-      <c r="M23" s="50"/>
-      <c r="N23" s="54"/>
-      <c r="O23" s="57"/>
+      <c r="A23" s="65"/>
+      <c r="B23" s="66"/>
+      <c r="C23" s="67"/>
+      <c r="D23" s="67"/>
+      <c r="E23" s="67"/>
+      <c r="F23" s="67"/>
+      <c r="G23" s="67"/>
+      <c r="H23" s="67"/>
+      <c r="I23" s="67"/>
+      <c r="J23" s="67"/>
+      <c r="K23" s="67"/>
+      <c r="L23" s="67"/>
+      <c r="M23" s="67"/>
+      <c r="N23" s="68"/>
+      <c r="O23" s="38"/>
     </row>
     <row r="24" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="33" t="s">
+      <c r="A24" s="58" t="s">
         <v>89</v>
       </c>
-      <c r="B24" s="33"/>
-      <c r="C24" s="33"/>
-      <c r="D24" s="33"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="33"/>
-      <c r="G24" s="33"/>
-      <c r="H24" s="33"/>
-      <c r="I24" s="33"/>
-      <c r="J24" s="33"/>
-      <c r="K24" s="33"/>
-      <c r="L24" s="33"/>
-      <c r="M24" s="59" t="s">
+      <c r="B24" s="58"/>
+      <c r="C24" s="58"/>
+      <c r="D24" s="58"/>
+      <c r="E24" s="58"/>
+      <c r="F24" s="58"/>
+      <c r="G24" s="58"/>
+      <c r="H24" s="58"/>
+      <c r="I24" s="58"/>
+      <c r="J24" s="58"/>
+      <c r="K24" s="58"/>
+      <c r="L24" s="58"/>
+      <c r="M24" s="48" t="s">
         <v>90</v>
       </c>
-      <c r="N24" s="59"/>
-      <c r="O24" s="57"/>
+      <c r="N24" s="48"/>
+      <c r="O24" s="38"/>
     </row>
     <row r="25" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="46" t="s">
+      <c r="A25" s="60" t="s">
         <v>85</v>
       </c>
-      <c r="B25" s="16"/>
-      <c r="C25" s="42" t="s">
+      <c r="B25" s="44"/>
+      <c r="C25" s="59" t="s">
         <v>78</v>
       </c>
-      <c r="D25" s="42"/>
-      <c r="E25" s="44"/>
-      <c r="F25" s="44"/>
-      <c r="G25" s="44"/>
-      <c r="H25" s="44"/>
-      <c r="I25" s="44"/>
-      <c r="J25" s="44"/>
-      <c r="K25" s="44"/>
-      <c r="L25" s="44"/>
-      <c r="M25" s="44"/>
-      <c r="N25" s="51"/>
-      <c r="O25" s="57"/>
+      <c r="D25" s="59"/>
+      <c r="E25" s="31"/>
+      <c r="F25" s="31"/>
+      <c r="G25" s="31"/>
+      <c r="H25" s="31"/>
+      <c r="I25" s="31"/>
+      <c r="J25" s="31"/>
+      <c r="K25" s="31"/>
+      <c r="L25" s="31"/>
+      <c r="M25" s="31"/>
+      <c r="N25" s="31"/>
+      <c r="O25" s="27"/>
     </row>
     <row r="26" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="46"/>
-      <c r="B26" s="29" t="s">
+      <c r="A26" s="61"/>
+      <c r="B26" s="42" t="s">
         <v>77</v>
       </c>
       <c r="C26" s="25" t="s">
@@ -4849,244 +8881,1396 @@
       <c r="D26" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="E26" s="44"/>
-      <c r="F26" s="44"/>
-      <c r="G26" s="44"/>
-      <c r="H26" s="44"/>
-      <c r="I26" s="44"/>
-      <c r="J26" s="44"/>
-      <c r="K26" s="44"/>
-      <c r="L26" s="44"/>
-      <c r="M26" s="44"/>
-      <c r="N26" s="51"/>
-      <c r="O26" s="57"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="31"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="31"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+      <c r="K26" s="31"/>
+      <c r="L26" s="31"/>
+      <c r="M26" s="31"/>
+      <c r="N26" s="31"/>
+      <c r="O26" s="27"/>
     </row>
     <row r="27" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="46"/>
+      <c r="A27" s="61"/>
       <c r="B27" s="15">
         <v>1</v>
       </c>
       <c r="C27" s="24">
         <v>84305</v>
       </c>
-      <c r="D27" s="60">
+      <c r="D27" s="40">
         <v>17805</v>
       </c>
-      <c r="E27" s="44"/>
-      <c r="F27" s="44"/>
-      <c r="G27" s="44"/>
-      <c r="H27" s="44"/>
-      <c r="I27" s="44"/>
-      <c r="J27" s="44"/>
-      <c r="K27" s="44"/>
-      <c r="L27" s="44"/>
-      <c r="M27" s="44"/>
-      <c r="N27" s="51"/>
-      <c r="O27" s="57"/>
+      <c r="E27" s="31"/>
+      <c r="F27" s="31"/>
+      <c r="G27" s="31"/>
+      <c r="H27" s="31"/>
+      <c r="I27" s="31"/>
+      <c r="J27" s="31"/>
+      <c r="K27" s="31"/>
+      <c r="L27" s="31"/>
+      <c r="M27" s="31"/>
+      <c r="N27" s="31"/>
+      <c r="O27" s="27"/>
     </row>
     <row r="28" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="46"/>
+      <c r="A28" s="61"/>
       <c r="B28" s="15">
         <v>2</v>
       </c>
       <c r="C28" s="24">
         <v>42965</v>
       </c>
-      <c r="D28" s="60">
+      <c r="D28" s="40">
         <v>9403</v>
       </c>
-      <c r="E28" s="44"/>
-      <c r="F28" s="44"/>
-      <c r="G28" s="44"/>
-      <c r="H28" s="44"/>
-      <c r="I28" s="44"/>
-      <c r="J28" s="44"/>
-      <c r="K28" s="44"/>
-      <c r="L28" s="44"/>
-      <c r="M28" s="44"/>
-      <c r="N28" s="51"/>
-      <c r="O28" s="57"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="H28" s="31"/>
+      <c r="I28" s="31"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="31"/>
+      <c r="N28" s="31"/>
+      <c r="O28" s="27"/>
     </row>
     <row r="29" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="46"/>
+      <c r="A29" s="61"/>
       <c r="B29" s="15">
         <v>4</v>
       </c>
       <c r="C29" s="24">
         <v>23077</v>
       </c>
-      <c r="D29" s="60">
+      <c r="D29" s="40">
         <v>4920</v>
       </c>
-      <c r="E29" s="44"/>
-      <c r="F29" s="44"/>
-      <c r="G29" s="44"/>
-      <c r="H29" s="44"/>
-      <c r="I29" s="44"/>
-      <c r="J29" s="44"/>
-      <c r="K29" s="44"/>
-      <c r="L29" s="44"/>
-      <c r="M29" s="44"/>
-      <c r="N29" s="51"/>
-      <c r="O29" s="57"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="31"/>
+      <c r="G29" s="31"/>
+      <c r="H29" s="31"/>
+      <c r="I29" s="31"/>
+      <c r="J29" s="31"/>
+      <c r="K29" s="31"/>
+      <c r="L29" s="31"/>
+      <c r="M29" s="31"/>
+      <c r="N29" s="31"/>
+      <c r="O29" s="27"/>
     </row>
     <row r="30" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="46"/>
+      <c r="A30" s="61"/>
       <c r="B30" s="15">
         <v>6</v>
       </c>
       <c r="C30" s="24">
         <v>18001</v>
       </c>
-      <c r="D30" s="60">
+      <c r="D30" s="40">
         <v>4044</v>
       </c>
-      <c r="E30" s="44"/>
-      <c r="F30" s="44"/>
-      <c r="G30" s="44"/>
-      <c r="H30" s="44"/>
-      <c r="I30" s="44"/>
-      <c r="J30" s="44"/>
-      <c r="K30" s="44"/>
-      <c r="L30" s="44"/>
-      <c r="M30" s="44"/>
-      <c r="N30" s="51"/>
-      <c r="O30" s="57"/>
+      <c r="E30" s="31"/>
+      <c r="F30" s="31"/>
+      <c r="G30" s="31"/>
+      <c r="H30" s="31"/>
+      <c r="I30" s="31"/>
+      <c r="J30" s="31"/>
+      <c r="K30" s="31"/>
+      <c r="L30" s="31"/>
+      <c r="M30" s="31"/>
+      <c r="N30" s="31"/>
+      <c r="O30" s="27"/>
     </row>
     <row r="31" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="46"/>
+      <c r="A31" s="61"/>
       <c r="B31" s="15">
         <v>8</v>
       </c>
       <c r="C31" s="24">
         <v>14258</v>
       </c>
-      <c r="D31" s="60">
+      <c r="D31" s="40">
         <v>3317</v>
       </c>
-      <c r="E31" s="44"/>
-      <c r="F31" s="44"/>
-      <c r="G31" s="44"/>
-      <c r="H31" s="44"/>
-      <c r="I31" s="44"/>
-      <c r="J31" s="44"/>
-      <c r="K31" s="44"/>
-      <c r="L31" s="44"/>
-      <c r="M31" s="44"/>
-      <c r="N31" s="51"/>
-      <c r="O31" s="57"/>
+      <c r="E31" s="31"/>
+      <c r="F31" s="31"/>
+      <c r="G31" s="31"/>
+      <c r="H31" s="31"/>
+      <c r="I31" s="31"/>
+      <c r="J31" s="31"/>
+      <c r="K31" s="31"/>
+      <c r="L31" s="31"/>
+      <c r="M31" s="31"/>
+      <c r="N31" s="31"/>
+      <c r="O31" s="27"/>
     </row>
     <row r="32" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="46"/>
+      <c r="A32" s="61"/>
       <c r="B32" s="15">
         <v>10</v>
       </c>
       <c r="C32" s="24">
         <v>12636</v>
       </c>
-      <c r="D32" s="60">
+      <c r="D32" s="40">
         <v>2987</v>
       </c>
-      <c r="E32" s="44"/>
-      <c r="F32" s="44"/>
-      <c r="G32" s="44"/>
-      <c r="H32" s="44"/>
-      <c r="I32" s="44"/>
-      <c r="J32" s="44"/>
-      <c r="K32" s="44"/>
-      <c r="L32" s="44"/>
-      <c r="M32" s="44"/>
-      <c r="N32" s="51"/>
-      <c r="O32" s="57"/>
-    </row>
-    <row r="33" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="46"/>
+      <c r="E32" s="31"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="31"/>
+      <c r="I32" s="31"/>
+      <c r="J32" s="31"/>
+      <c r="K32" s="31"/>
+      <c r="L32" s="31"/>
+      <c r="M32" s="31"/>
+      <c r="N32" s="31"/>
+      <c r="O32" s="27"/>
+    </row>
+    <row r="33" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="61"/>
       <c r="B33" s="15">
         <v>12</v>
       </c>
       <c r="C33" s="24">
         <v>11424</v>
       </c>
-      <c r="D33" s="60">
+      <c r="D33" s="40">
         <v>2738</v>
       </c>
-      <c r="E33" s="44"/>
-      <c r="F33" s="44"/>
-      <c r="G33" s="44"/>
-      <c r="H33" s="44"/>
-      <c r="I33" s="44"/>
-      <c r="J33" s="44"/>
-      <c r="K33" s="44"/>
-      <c r="L33" s="44"/>
-      <c r="M33" s="44"/>
-      <c r="N33" s="51"/>
-      <c r="O33" s="57"/>
-    </row>
-    <row r="34" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="46"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="31"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="31"/>
+      <c r="I33" s="31"/>
+      <c r="J33" s="31"/>
+      <c r="K33" s="31"/>
+      <c r="L33" s="31"/>
+      <c r="M33" s="31"/>
+      <c r="N33" s="31"/>
+      <c r="O33" s="27"/>
+    </row>
+    <row r="34" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="61"/>
       <c r="B34" s="15">
         <v>16</v>
       </c>
       <c r="C34" s="24">
         <v>9939</v>
       </c>
-      <c r="D34" s="60">
+      <c r="D34" s="40">
         <v>2487</v>
       </c>
-      <c r="E34" s="44"/>
-      <c r="F34" s="44"/>
-      <c r="G34" s="44"/>
-      <c r="H34" s="44"/>
-      <c r="I34" s="44"/>
-      <c r="J34" s="44"/>
-      <c r="K34" s="44"/>
-      <c r="L34" s="44"/>
-      <c r="M34" s="44"/>
-      <c r="N34" s="51"/>
-      <c r="O34" s="57"/>
-    </row>
-    <row r="35" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="46"/>
-      <c r="B35" s="47" t="s">
+      <c r="E34" s="31"/>
+      <c r="F34" s="31"/>
+      <c r="G34" s="31"/>
+      <c r="H34" s="31"/>
+      <c r="I34" s="31"/>
+      <c r="J34" s="31"/>
+      <c r="K34" s="31"/>
+      <c r="L34" s="31"/>
+      <c r="M34" s="31"/>
+      <c r="N34" s="31"/>
+      <c r="O34" s="27"/>
+    </row>
+    <row r="35" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="61"/>
+      <c r="B35" s="45"/>
+      <c r="C35" s="59" t="s">
+        <v>96</v>
+      </c>
+      <c r="D35" s="59"/>
+      <c r="E35" s="31"/>
+      <c r="F35" s="31"/>
+      <c r="G35" s="31"/>
+      <c r="H35" s="31"/>
+      <c r="I35" s="31"/>
+      <c r="J35" s="31"/>
+      <c r="K35" s="31"/>
+      <c r="L35" s="31"/>
+      <c r="M35" s="31"/>
+      <c r="N35" s="31"/>
+      <c r="O35" s="27"/>
+    </row>
+    <row r="36" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="61"/>
+      <c r="B36" s="42" t="s">
+        <v>77</v>
+      </c>
+      <c r="C36" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="D36" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="E36" s="43"/>
+      <c r="F36" s="43"/>
+      <c r="G36" s="43"/>
+      <c r="H36" s="16"/>
+      <c r="I36" s="16"/>
+      <c r="J36" s="16"/>
+      <c r="K36" s="16"/>
+      <c r="L36" s="16"/>
+      <c r="M36" s="16"/>
+      <c r="N36" s="16"/>
+      <c r="O36" s="1"/>
+      <c r="P36" s="1"/>
+    </row>
+    <row r="37" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="61"/>
+      <c r="B37" s="42">
+        <v>1</v>
+      </c>
+      <c r="C37" s="43">
+        <f>C27/C27</f>
+        <v>1</v>
+      </c>
+      <c r="D37" s="43">
+        <f>D27/D27</f>
+        <v>1</v>
+      </c>
+      <c r="E37" s="43"/>
+      <c r="F37" s="43"/>
+      <c r="G37" s="43"/>
+      <c r="H37" s="16"/>
+      <c r="I37" s="16"/>
+      <c r="J37" s="16"/>
+      <c r="K37" s="16"/>
+      <c r="L37" s="16"/>
+      <c r="M37" s="16"/>
+      <c r="N37" s="16"/>
+      <c r="O37" s="1"/>
+      <c r="P37" s="1"/>
+    </row>
+    <row r="38" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="61"/>
+      <c r="B38" s="42">
+        <v>2</v>
+      </c>
+      <c r="C38" s="43">
+        <f>C27/C28</f>
+        <v>1.9621785173978821</v>
+      </c>
+      <c r="D38" s="43">
+        <f>D27/D28</f>
+        <v>1.8935446134212486</v>
+      </c>
+      <c r="E38" s="43"/>
+      <c r="F38" s="43"/>
+      <c r="G38" s="43"/>
+      <c r="H38" s="16"/>
+      <c r="I38" s="16"/>
+      <c r="J38" s="16"/>
+      <c r="K38" s="16"/>
+      <c r="L38" s="16"/>
+      <c r="M38" s="16"/>
+      <c r="N38" s="16"/>
+      <c r="O38" s="1"/>
+      <c r="P38" s="1"/>
+    </row>
+    <row r="39" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="61"/>
+      <c r="B39" s="42">
+        <v>4</v>
+      </c>
+      <c r="C39" s="43">
+        <f>C27/C29</f>
+        <v>3.6532044893183691</v>
+      </c>
+      <c r="D39" s="43">
+        <f>D27/D29</f>
+        <v>3.6189024390243905</v>
+      </c>
+      <c r="E39" s="43"/>
+      <c r="F39" s="43"/>
+      <c r="G39" s="43"/>
+      <c r="H39" s="16"/>
+      <c r="I39" s="16"/>
+      <c r="J39" s="16"/>
+      <c r="K39" s="16"/>
+      <c r="L39" s="16"/>
+      <c r="M39" s="16"/>
+      <c r="N39" s="16"/>
+      <c r="O39" s="1"/>
+      <c r="P39" s="1"/>
+    </row>
+    <row r="40" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="61"/>
+      <c r="B40" s="42">
+        <v>6</v>
+      </c>
+      <c r="C40" s="43">
+        <f>C27/C30</f>
+        <v>4.6833509249486136</v>
+      </c>
+      <c r="D40" s="43">
+        <f>D27/D30</f>
+        <v>4.4028189910979227</v>
+      </c>
+      <c r="E40" s="43"/>
+      <c r="F40" s="43"/>
+      <c r="G40" s="43"/>
+      <c r="H40" s="16"/>
+      <c r="I40" s="16"/>
+      <c r="J40" s="16"/>
+      <c r="K40" s="16"/>
+      <c r="L40" s="16"/>
+      <c r="M40" s="16"/>
+      <c r="N40" s="16"/>
+      <c r="O40" s="1"/>
+      <c r="P40" s="1"/>
+    </row>
+    <row r="41" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="61"/>
+      <c r="B41" s="42">
+        <v>8</v>
+      </c>
+      <c r="C41" s="43">
+        <f>C27/C31</f>
+        <v>5.9128208724926354</v>
+      </c>
+      <c r="D41" s="43">
+        <f>D27/D31</f>
+        <v>5.3678022309315647</v>
+      </c>
+      <c r="E41" s="43"/>
+      <c r="F41" s="43"/>
+      <c r="G41" s="43"/>
+      <c r="H41" s="16"/>
+      <c r="I41" s="16"/>
+      <c r="J41" s="16"/>
+      <c r="K41" s="16"/>
+      <c r="L41" s="16"/>
+      <c r="M41" s="16"/>
+      <c r="N41" s="16"/>
+      <c r="O41" s="1"/>
+      <c r="P41" s="1"/>
+    </row>
+    <row r="42" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="61"/>
+      <c r="B42" s="42">
+        <v>10</v>
+      </c>
+      <c r="C42" s="43">
+        <f>C27/C32</f>
+        <v>6.6718106995884776</v>
+      </c>
+      <c r="D42" s="43">
+        <f>D27/D32</f>
+        <v>5.9608302644794104</v>
+      </c>
+      <c r="E42" s="43"/>
+      <c r="F42" s="43"/>
+      <c r="G42" s="43"/>
+      <c r="H42" s="16"/>
+      <c r="I42" s="16"/>
+      <c r="J42" s="16"/>
+      <c r="K42" s="16"/>
+      <c r="L42" s="16"/>
+      <c r="M42" s="16"/>
+      <c r="N42" s="16"/>
+      <c r="O42" s="1"/>
+      <c r="P42" s="1"/>
+    </row>
+    <row r="43" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="61"/>
+      <c r="B43" s="42">
+        <v>12</v>
+      </c>
+      <c r="C43" s="43">
+        <f>C27/C33</f>
+        <v>7.379639355742297</v>
+      </c>
+      <c r="D43" s="43">
+        <f>D27/D33</f>
+        <v>6.5029218407596785</v>
+      </c>
+      <c r="E43" s="43"/>
+      <c r="F43" s="43"/>
+      <c r="G43" s="43"/>
+      <c r="H43" s="16"/>
+      <c r="I43" s="16"/>
+      <c r="J43" s="16"/>
+      <c r="K43" s="16"/>
+      <c r="L43" s="16"/>
+      <c r="M43" s="16"/>
+      <c r="N43" s="16"/>
+      <c r="O43" s="1"/>
+      <c r="P43" s="1"/>
+    </row>
+    <row r="44" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="61"/>
+      <c r="B44" s="42">
+        <v>16</v>
+      </c>
+      <c r="C44" s="43">
+        <f>C27/C34</f>
+        <v>8.4822416742126983</v>
+      </c>
+      <c r="D44" s="43">
+        <f>D27/D34</f>
+        <v>7.1592279855247289</v>
+      </c>
+      <c r="E44" s="43"/>
+      <c r="F44" s="43"/>
+      <c r="G44" s="43"/>
+      <c r="H44" s="16"/>
+      <c r="I44" s="16"/>
+      <c r="J44" s="16"/>
+      <c r="K44" s="16"/>
+      <c r="L44" s="16"/>
+      <c r="M44" s="16"/>
+      <c r="N44" s="16"/>
+      <c r="O44" s="1"/>
+      <c r="P44" s="1"/>
+    </row>
+    <row r="45" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="61"/>
+      <c r="B45" s="45"/>
+      <c r="C45" s="59" t="s">
+        <v>97</v>
+      </c>
+      <c r="D45" s="59"/>
+      <c r="E45" s="43"/>
+      <c r="F45" s="43"/>
+      <c r="G45" s="43"/>
+      <c r="H45" s="16"/>
+      <c r="I45" s="16"/>
+      <c r="J45" s="16"/>
+      <c r="K45" s="16"/>
+      <c r="L45" s="16"/>
+      <c r="M45" s="16"/>
+      <c r="N45" s="16"/>
+      <c r="O45" s="1"/>
+      <c r="P45" s="1"/>
+    </row>
+    <row r="46" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="61"/>
+      <c r="B46" s="42" t="s">
+        <v>77</v>
+      </c>
+      <c r="C46" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="D46" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="E46" s="43"/>
+      <c r="F46" s="43"/>
+      <c r="G46" s="43"/>
+      <c r="H46" s="16"/>
+      <c r="I46" s="16"/>
+      <c r="J46" s="16"/>
+      <c r="K46" s="16"/>
+      <c r="L46" s="16"/>
+      <c r="M46" s="16"/>
+      <c r="N46" s="16"/>
+      <c r="O46" s="1"/>
+      <c r="P46" s="1"/>
+    </row>
+    <row r="47" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="61"/>
+      <c r="B47" s="42">
+        <v>1</v>
+      </c>
+      <c r="C47" s="43">
+        <f>C37/B37</f>
+        <v>1</v>
+      </c>
+      <c r="D47" s="43">
+        <f>D37/B37</f>
+        <v>1</v>
+      </c>
+      <c r="E47" s="43"/>
+      <c r="F47" s="43"/>
+      <c r="G47" s="43"/>
+      <c r="H47" s="16"/>
+      <c r="I47" s="16"/>
+      <c r="J47" s="16"/>
+      <c r="K47" s="16"/>
+      <c r="L47" s="16"/>
+      <c r="M47" s="16"/>
+      <c r="N47" s="16"/>
+      <c r="O47" s="1"/>
+      <c r="P47" s="1"/>
+    </row>
+    <row r="48" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="61"/>
+      <c r="B48" s="42">
+        <v>2</v>
+      </c>
+      <c r="C48" s="43">
+        <f>C38/B38</f>
+        <v>0.98108925869894104</v>
+      </c>
+      <c r="D48" s="43">
+        <f>D38/B38</f>
+        <v>0.94677230671062429</v>
+      </c>
+      <c r="E48" s="43"/>
+      <c r="F48" s="43"/>
+      <c r="G48" s="43"/>
+      <c r="H48" s="16"/>
+      <c r="I48" s="16"/>
+      <c r="J48" s="16"/>
+      <c r="K48" s="16"/>
+      <c r="L48" s="16"/>
+      <c r="M48" s="16"/>
+      <c r="N48" s="16"/>
+      <c r="O48" s="1"/>
+      <c r="P48" s="1"/>
+    </row>
+    <row r="49" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="61"/>
+      <c r="B49" s="42">
+        <v>4</v>
+      </c>
+      <c r="C49" s="43">
+        <f>C39/B39</f>
+        <v>0.91330112232959226</v>
+      </c>
+      <c r="D49" s="43">
+        <f>D39/B39</f>
+        <v>0.90472560975609762</v>
+      </c>
+      <c r="E49" s="43"/>
+      <c r="F49" s="43"/>
+      <c r="G49" s="43"/>
+      <c r="H49" s="16"/>
+      <c r="I49" s="16"/>
+      <c r="J49" s="16"/>
+      <c r="K49" s="16"/>
+      <c r="L49" s="16"/>
+      <c r="M49" s="16"/>
+      <c r="N49" s="16"/>
+      <c r="O49" s="1"/>
+      <c r="P49" s="1"/>
+    </row>
+    <row r="50" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="61"/>
+      <c r="B50" s="42">
+        <v>6</v>
+      </c>
+      <c r="C50" s="43">
+        <f>C40/B40</f>
+        <v>0.78055848749143564</v>
+      </c>
+      <c r="D50" s="43">
+        <f>D40/B40</f>
+        <v>0.73380316518298716</v>
+      </c>
+      <c r="E50" s="43"/>
+      <c r="F50" s="43"/>
+      <c r="G50" s="43"/>
+      <c r="H50" s="16"/>
+      <c r="I50" s="16"/>
+      <c r="J50" s="16"/>
+      <c r="K50" s="16"/>
+      <c r="L50" s="16"/>
+      <c r="M50" s="16"/>
+      <c r="N50" s="16"/>
+      <c r="O50" s="1"/>
+      <c r="P50" s="1"/>
+    </row>
+    <row r="51" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="61"/>
+      <c r="B51" s="42">
+        <v>8</v>
+      </c>
+      <c r="C51" s="43">
+        <f>C41/B41</f>
+        <v>0.73910260906157943</v>
+      </c>
+      <c r="D51" s="43">
+        <f>D41/B41</f>
+        <v>0.67097527886644559</v>
+      </c>
+      <c r="E51" s="43"/>
+      <c r="F51" s="43"/>
+      <c r="G51" s="43"/>
+      <c r="H51" s="16"/>
+      <c r="I51" s="16"/>
+      <c r="J51" s="16"/>
+      <c r="K51" s="16"/>
+      <c r="L51" s="16"/>
+      <c r="M51" s="16"/>
+      <c r="N51" s="16"/>
+      <c r="O51" s="1"/>
+    </row>
+    <row r="52" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="61"/>
+      <c r="B52" s="42">
+        <v>10</v>
+      </c>
+      <c r="C52" s="43">
+        <f>C42/B42</f>
+        <v>0.66718106995884774</v>
+      </c>
+      <c r="D52" s="43">
+        <f>D42/B42</f>
+        <v>0.59608302644794109</v>
+      </c>
+      <c r="E52" s="43"/>
+      <c r="F52" s="43"/>
+      <c r="G52" s="43"/>
+      <c r="H52" s="16"/>
+      <c r="I52" s="16"/>
+      <c r="J52" s="16"/>
+      <c r="K52" s="16"/>
+      <c r="L52" s="16"/>
+      <c r="M52" s="16"/>
+      <c r="N52" s="16"/>
+      <c r="O52" s="1"/>
+    </row>
+    <row r="53" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="61"/>
+      <c r="B53" s="42">
+        <v>12</v>
+      </c>
+      <c r="C53" s="43">
+        <f>C43/B43</f>
+        <v>0.61496994631185808</v>
+      </c>
+      <c r="D53" s="43">
+        <f>D43/B43</f>
+        <v>0.54191015339663984</v>
+      </c>
+      <c r="E53" s="31"/>
+      <c r="F53" s="31"/>
+      <c r="G53" s="31"/>
+      <c r="H53" s="31"/>
+      <c r="I53" s="31"/>
+      <c r="J53" s="31"/>
+      <c r="K53" s="31"/>
+      <c r="L53" s="31"/>
+      <c r="M53" s="31"/>
+      <c r="N53" s="31"/>
+      <c r="O53" s="1"/>
+    </row>
+    <row r="54" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="61"/>
+      <c r="B54" s="42">
+        <v>16</v>
+      </c>
+      <c r="C54" s="43">
+        <f>C44/B44</f>
+        <v>0.53014010463829364</v>
+      </c>
+      <c r="D54" s="43">
+        <f>D44/B44</f>
+        <v>0.44745174909529556</v>
+      </c>
+      <c r="E54" s="31"/>
+      <c r="F54" s="31"/>
+      <c r="G54" s="31"/>
+      <c r="H54" s="31"/>
+      <c r="I54" s="31"/>
+      <c r="J54" s="31"/>
+      <c r="K54" s="31"/>
+      <c r="L54" s="31"/>
+      <c r="M54" s="31"/>
+      <c r="N54" s="31"/>
+      <c r="O54" s="1"/>
+    </row>
+    <row r="55" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="62"/>
+      <c r="B55" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="C35" s="48" t="s">
-        <v>93</v>
-      </c>
-      <c r="D35" s="48"/>
-      <c r="E35" s="48"/>
-      <c r="F35" s="48"/>
-      <c r="G35" s="48"/>
-      <c r="H35" s="48"/>
-      <c r="I35" s="48"/>
-      <c r="J35" s="48"/>
-      <c r="K35" s="48"/>
-      <c r="L35" s="48"/>
-      <c r="M35" s="48"/>
-      <c r="N35" s="53"/>
-      <c r="O35" s="57"/>
-    </row>
-    <row r="36" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="37" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="38" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="39" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="41" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="42" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="43" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="45" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="46" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="47" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="48" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="49" ht="21.6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" ht="21.6" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="C55" s="63" t="s">
+        <v>98</v>
+      </c>
+      <c r="D55" s="63"/>
+      <c r="E55" s="63"/>
+      <c r="F55" s="63"/>
+      <c r="G55" s="63"/>
+      <c r="H55" s="63"/>
+      <c r="I55" s="63"/>
+      <c r="J55" s="63"/>
+      <c r="K55" s="63"/>
+      <c r="L55" s="63"/>
+      <c r="M55" s="63"/>
+      <c r="N55" s="63"/>
+    </row>
+    <row r="56" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="60" t="s">
+        <v>87</v>
+      </c>
+      <c r="B56" s="44"/>
+      <c r="C56" s="59" t="s">
+        <v>78</v>
+      </c>
+      <c r="D56" s="59"/>
+      <c r="E56" s="31"/>
+      <c r="F56" s="31"/>
+      <c r="G56" s="31"/>
+      <c r="H56" s="31"/>
+      <c r="I56" s="31"/>
+      <c r="J56" s="31"/>
+      <c r="K56" s="31"/>
+      <c r="L56" s="31"/>
+      <c r="M56" s="31"/>
+      <c r="N56" s="31"/>
+    </row>
+    <row r="57" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="61"/>
+      <c r="B57" s="42" t="s">
+        <v>77</v>
+      </c>
+      <c r="C57" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="D57" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="E57" s="31"/>
+      <c r="F57" s="31"/>
+      <c r="G57" s="31"/>
+      <c r="H57" s="31"/>
+      <c r="I57" s="31"/>
+      <c r="J57" s="31"/>
+      <c r="K57" s="31"/>
+      <c r="L57" s="31"/>
+      <c r="M57" s="31"/>
+      <c r="N57" s="31"/>
+    </row>
+    <row r="58" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="61"/>
+      <c r="B58" s="15">
+        <v>1</v>
+      </c>
+      <c r="C58" s="24"/>
+      <c r="D58" s="40"/>
+      <c r="E58" s="31"/>
+      <c r="F58" s="31"/>
+      <c r="G58" s="31"/>
+      <c r="H58" s="31"/>
+      <c r="I58" s="31"/>
+      <c r="J58" s="31"/>
+      <c r="K58" s="31"/>
+      <c r="L58" s="31"/>
+      <c r="M58" s="31"/>
+      <c r="N58" s="31"/>
+    </row>
+    <row r="59" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="61"/>
+      <c r="B59" s="15">
+        <v>2</v>
+      </c>
+      <c r="C59" s="24"/>
+      <c r="D59" s="40"/>
+      <c r="E59" s="31"/>
+      <c r="F59" s="31"/>
+      <c r="G59" s="31"/>
+      <c r="H59" s="31"/>
+      <c r="I59" s="31"/>
+      <c r="J59" s="31"/>
+      <c r="K59" s="31"/>
+      <c r="L59" s="31"/>
+      <c r="M59" s="31"/>
+      <c r="N59" s="31"/>
+    </row>
+    <row r="60" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="61"/>
+      <c r="B60" s="15">
+        <v>4</v>
+      </c>
+      <c r="C60" s="24"/>
+      <c r="D60" s="40"/>
+      <c r="E60" s="31"/>
+      <c r="F60" s="31"/>
+      <c r="G60" s="31"/>
+      <c r="H60" s="31"/>
+      <c r="I60" s="31"/>
+      <c r="J60" s="31"/>
+      <c r="K60" s="31"/>
+      <c r="L60" s="31"/>
+      <c r="M60" s="31"/>
+      <c r="N60" s="31"/>
+    </row>
+    <row r="61" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="61"/>
+      <c r="B61" s="15">
+        <v>6</v>
+      </c>
+      <c r="C61" s="24"/>
+      <c r="D61" s="40"/>
+      <c r="E61" s="31"/>
+      <c r="F61" s="31"/>
+      <c r="G61" s="31"/>
+      <c r="H61" s="31"/>
+      <c r="I61" s="31"/>
+      <c r="J61" s="31"/>
+      <c r="K61" s="31"/>
+      <c r="L61" s="31"/>
+      <c r="M61" s="31"/>
+      <c r="N61" s="31"/>
+    </row>
+    <row r="62" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="61"/>
+      <c r="B62" s="15">
+        <v>8</v>
+      </c>
+      <c r="C62" s="24"/>
+      <c r="D62" s="40"/>
+      <c r="E62" s="31"/>
+      <c r="F62" s="31"/>
+      <c r="G62" s="31"/>
+      <c r="H62" s="31"/>
+      <c r="I62" s="31"/>
+      <c r="J62" s="31"/>
+      <c r="K62" s="31"/>
+      <c r="L62" s="31"/>
+      <c r="M62" s="31"/>
+      <c r="N62" s="31"/>
+    </row>
+    <row r="63" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="61"/>
+      <c r="B63" s="15">
+        <v>10</v>
+      </c>
+      <c r="C63" s="24"/>
+      <c r="D63" s="40"/>
+      <c r="E63" s="31"/>
+      <c r="F63" s="31"/>
+      <c r="G63" s="31"/>
+      <c r="H63" s="31"/>
+      <c r="I63" s="31"/>
+      <c r="J63" s="31"/>
+      <c r="K63" s="31"/>
+      <c r="L63" s="31"/>
+      <c r="M63" s="31"/>
+      <c r="N63" s="31"/>
+    </row>
+    <row r="64" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="61"/>
+      <c r="B64" s="15">
+        <v>12</v>
+      </c>
+      <c r="C64" s="24"/>
+      <c r="D64" s="40"/>
+      <c r="E64" s="31"/>
+      <c r="F64" s="31"/>
+      <c r="G64" s="31"/>
+      <c r="H64" s="31"/>
+      <c r="I64" s="31"/>
+      <c r="J64" s="31"/>
+      <c r="K64" s="31"/>
+      <c r="L64" s="31"/>
+      <c r="M64" s="31"/>
+      <c r="N64" s="31"/>
+    </row>
+    <row r="65" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="61"/>
+      <c r="B65" s="15">
+        <v>16</v>
+      </c>
+      <c r="C65" s="24"/>
+      <c r="D65" s="40"/>
+      <c r="E65" s="31"/>
+      <c r="F65" s="31"/>
+      <c r="G65" s="31"/>
+      <c r="H65" s="31"/>
+      <c r="I65" s="31"/>
+      <c r="J65" s="31"/>
+      <c r="K65" s="31"/>
+      <c r="L65" s="31"/>
+      <c r="M65" s="31"/>
+      <c r="N65" s="31"/>
+    </row>
+    <row r="66" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="61"/>
+      <c r="B66" s="45"/>
+      <c r="C66" s="59" t="s">
+        <v>96</v>
+      </c>
+      <c r="D66" s="59"/>
+      <c r="E66" s="31"/>
+      <c r="F66" s="31"/>
+      <c r="G66" s="31"/>
+      <c r="H66" s="31"/>
+      <c r="I66" s="31"/>
+      <c r="J66" s="31"/>
+      <c r="K66" s="31"/>
+      <c r="L66" s="31"/>
+      <c r="M66" s="31"/>
+      <c r="N66" s="31"/>
+    </row>
+    <row r="67" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="61"/>
+      <c r="B67" s="42" t="s">
+        <v>77</v>
+      </c>
+      <c r="C67" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="D67" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="E67" s="43"/>
+      <c r="F67" s="43"/>
+      <c r="G67" s="43"/>
+      <c r="H67" s="16"/>
+      <c r="I67" s="16"/>
+      <c r="J67" s="16"/>
+      <c r="K67" s="16"/>
+      <c r="L67" s="16"/>
+      <c r="M67" s="16"/>
+      <c r="N67" s="16"/>
+    </row>
+    <row r="68" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="61"/>
+      <c r="B68" s="42">
+        <v>1</v>
+      </c>
+      <c r="C68" s="43" t="e">
+        <f>C58/C58</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D68" s="43" t="e">
+        <f>D58/D58</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E68" s="43"/>
+      <c r="F68" s="43"/>
+      <c r="G68" s="43"/>
+      <c r="H68" s="16"/>
+      <c r="I68" s="16"/>
+      <c r="J68" s="16"/>
+      <c r="K68" s="16"/>
+      <c r="L68" s="16"/>
+      <c r="M68" s="16"/>
+      <c r="N68" s="16"/>
+    </row>
+    <row r="69" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="61"/>
+      <c r="B69" s="42">
+        <v>2</v>
+      </c>
+      <c r="C69" s="43" t="e">
+        <f>C58/C59</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D69" s="43" t="e">
+        <f>D58/D59</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E69" s="43"/>
+      <c r="F69" s="43"/>
+      <c r="G69" s="43"/>
+      <c r="H69" s="16"/>
+      <c r="I69" s="16"/>
+      <c r="J69" s="16"/>
+      <c r="K69" s="16"/>
+      <c r="L69" s="16"/>
+      <c r="M69" s="16"/>
+      <c r="N69" s="16"/>
+    </row>
+    <row r="70" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="61"/>
+      <c r="B70" s="42">
+        <v>4</v>
+      </c>
+      <c r="C70" s="43" t="e">
+        <f>C58/C60</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D70" s="43" t="e">
+        <f>D58/D60</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E70" s="43"/>
+      <c r="F70" s="43"/>
+      <c r="G70" s="43"/>
+      <c r="H70" s="16"/>
+      <c r="I70" s="16"/>
+      <c r="J70" s="16"/>
+      <c r="K70" s="16"/>
+      <c r="L70" s="16"/>
+      <c r="M70" s="16"/>
+      <c r="N70" s="16"/>
+    </row>
+    <row r="71" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="61"/>
+      <c r="B71" s="42">
+        <v>6</v>
+      </c>
+      <c r="C71" s="43" t="e">
+        <f>C58/C61</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D71" s="43" t="e">
+        <f>D58/D61</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E71" s="43"/>
+      <c r="F71" s="43"/>
+      <c r="G71" s="43"/>
+      <c r="H71" s="16"/>
+      <c r="I71" s="16"/>
+      <c r="J71" s="16"/>
+      <c r="K71" s="16"/>
+      <c r="L71" s="16"/>
+      <c r="M71" s="16"/>
+      <c r="N71" s="16"/>
+    </row>
+    <row r="72" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="61"/>
+      <c r="B72" s="42">
+        <v>8</v>
+      </c>
+      <c r="C72" s="43" t="e">
+        <f>C58/C62</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D72" s="43" t="e">
+        <f>D58/D62</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E72" s="43"/>
+      <c r="F72" s="43"/>
+      <c r="G72" s="43"/>
+      <c r="H72" s="16"/>
+      <c r="I72" s="16"/>
+      <c r="J72" s="16"/>
+      <c r="K72" s="16"/>
+      <c r="L72" s="16"/>
+      <c r="M72" s="16"/>
+      <c r="N72" s="16"/>
+    </row>
+    <row r="73" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="61"/>
+      <c r="B73" s="42">
+        <v>10</v>
+      </c>
+      <c r="C73" s="43" t="e">
+        <f>C58/C63</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D73" s="43" t="e">
+        <f>D58/D63</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E73" s="43"/>
+      <c r="F73" s="43"/>
+      <c r="G73" s="43"/>
+      <c r="H73" s="16"/>
+      <c r="I73" s="16"/>
+      <c r="J73" s="16"/>
+      <c r="K73" s="16"/>
+      <c r="L73" s="16"/>
+      <c r="M73" s="16"/>
+      <c r="N73" s="16"/>
+    </row>
+    <row r="74" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="61"/>
+      <c r="B74" s="42">
+        <v>12</v>
+      </c>
+      <c r="C74" s="43" t="e">
+        <f>C58/C64</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D74" s="43" t="e">
+        <f>D58/D64</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E74" s="43"/>
+      <c r="F74" s="43"/>
+      <c r="G74" s="43"/>
+      <c r="H74" s="16"/>
+      <c r="I74" s="16"/>
+      <c r="J74" s="16"/>
+      <c r="K74" s="16"/>
+      <c r="L74" s="16"/>
+      <c r="M74" s="16"/>
+      <c r="N74" s="16"/>
+    </row>
+    <row r="75" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="61"/>
+      <c r="B75" s="42">
+        <v>16</v>
+      </c>
+      <c r="C75" s="43" t="e">
+        <f>C58/C65</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D75" s="43" t="e">
+        <f>D58/D65</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E75" s="43"/>
+      <c r="F75" s="43"/>
+      <c r="G75" s="43"/>
+      <c r="H75" s="16"/>
+      <c r="I75" s="16"/>
+      <c r="J75" s="16"/>
+      <c r="K75" s="16"/>
+      <c r="L75" s="16"/>
+      <c r="M75" s="16"/>
+      <c r="N75" s="16"/>
+    </row>
+    <row r="76" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="61"/>
+      <c r="B76" s="45"/>
+      <c r="C76" s="59" t="s">
+        <v>97</v>
+      </c>
+      <c r="D76" s="59"/>
+      <c r="E76" s="43"/>
+      <c r="F76" s="43"/>
+      <c r="G76" s="43"/>
+      <c r="H76" s="16"/>
+      <c r="I76" s="16"/>
+      <c r="J76" s="16"/>
+      <c r="K76" s="16"/>
+      <c r="L76" s="16"/>
+      <c r="M76" s="16"/>
+      <c r="N76" s="16"/>
+    </row>
+    <row r="77" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="61"/>
+      <c r="B77" s="42" t="s">
+        <v>77</v>
+      </c>
+      <c r="C77" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="D77" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="E77" s="43"/>
+      <c r="F77" s="43"/>
+      <c r="G77" s="43"/>
+      <c r="H77" s="16"/>
+      <c r="I77" s="16"/>
+      <c r="J77" s="16"/>
+      <c r="K77" s="16"/>
+      <c r="L77" s="16"/>
+      <c r="M77" s="16"/>
+      <c r="N77" s="16"/>
+    </row>
+    <row r="78" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="61"/>
+      <c r="B78" s="42">
+        <v>1</v>
+      </c>
+      <c r="C78" s="43" t="e">
+        <f>C68/B68</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D78" s="43" t="e">
+        <f>D68/B68</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E78" s="43"/>
+      <c r="F78" s="43"/>
+      <c r="G78" s="43"/>
+      <c r="H78" s="16"/>
+      <c r="I78" s="16"/>
+      <c r="J78" s="16"/>
+      <c r="K78" s="16"/>
+      <c r="L78" s="16"/>
+      <c r="M78" s="16"/>
+      <c r="N78" s="16"/>
+    </row>
+    <row r="79" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="61"/>
+      <c r="B79" s="42">
+        <v>2</v>
+      </c>
+      <c r="C79" s="43" t="e">
+        <f>C69/B69</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D79" s="43" t="e">
+        <f t="shared" ref="D79:D85" si="0">D69/B69</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E79" s="43"/>
+      <c r="F79" s="43"/>
+      <c r="G79" s="43"/>
+      <c r="H79" s="16"/>
+      <c r="I79" s="16"/>
+      <c r="J79" s="16"/>
+      <c r="K79" s="16"/>
+      <c r="L79" s="16"/>
+      <c r="M79" s="16"/>
+      <c r="N79" s="16"/>
+    </row>
+    <row r="80" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="61"/>
+      <c r="B80" s="42">
+        <v>4</v>
+      </c>
+      <c r="C80" s="43" t="e">
+        <f t="shared" ref="C80:C85" si="1">C70/B70</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D80" s="43" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E80" s="43"/>
+      <c r="F80" s="43"/>
+      <c r="G80" s="43"/>
+      <c r="H80" s="16"/>
+      <c r="I80" s="16"/>
+      <c r="J80" s="16"/>
+      <c r="K80" s="16"/>
+      <c r="L80" s="16"/>
+      <c r="M80" s="16"/>
+      <c r="N80" s="16"/>
+    </row>
+    <row r="81" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="61"/>
+      <c r="B81" s="42">
+        <v>6</v>
+      </c>
+      <c r="C81" s="43" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D81" s="43" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E81" s="43"/>
+      <c r="F81" s="43"/>
+      <c r="G81" s="43"/>
+      <c r="H81" s="16"/>
+      <c r="I81" s="16"/>
+      <c r="J81" s="16"/>
+      <c r="K81" s="16"/>
+      <c r="L81" s="16"/>
+      <c r="M81" s="16"/>
+      <c r="N81" s="16"/>
+    </row>
+    <row r="82" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="61"/>
+      <c r="B82" s="42">
+        <v>8</v>
+      </c>
+      <c r="C82" s="43" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D82" s="43" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E82" s="43"/>
+      <c r="F82" s="43"/>
+      <c r="G82" s="43"/>
+      <c r="H82" s="16"/>
+      <c r="I82" s="16"/>
+      <c r="J82" s="16"/>
+      <c r="K82" s="16"/>
+      <c r="L82" s="16"/>
+      <c r="M82" s="16"/>
+      <c r="N82" s="16"/>
+    </row>
+    <row r="83" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="61"/>
+      <c r="B83" s="42">
+        <v>10</v>
+      </c>
+      <c r="C83" s="43" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D83" s="43" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E83" s="43"/>
+      <c r="F83" s="43"/>
+      <c r="G83" s="43"/>
+      <c r="H83" s="16"/>
+      <c r="I83" s="16"/>
+      <c r="J83" s="16"/>
+      <c r="K83" s="16"/>
+      <c r="L83" s="16"/>
+      <c r="M83" s="16"/>
+      <c r="N83" s="16"/>
+    </row>
+    <row r="84" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="61"/>
+      <c r="B84" s="42">
+        <v>12</v>
+      </c>
+      <c r="C84" s="43" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D84" s="43" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E84" s="31"/>
+      <c r="F84" s="31"/>
+      <c r="G84" s="31"/>
+      <c r="H84" s="31"/>
+      <c r="I84" s="31"/>
+      <c r="J84" s="31"/>
+      <c r="K84" s="31"/>
+      <c r="L84" s="31"/>
+      <c r="M84" s="31"/>
+      <c r="N84" s="31"/>
+    </row>
+    <row r="85" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="61"/>
+      <c r="B85" s="42">
+        <v>16</v>
+      </c>
+      <c r="C85" s="43" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D85" s="43" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E85" s="31"/>
+      <c r="F85" s="31"/>
+      <c r="G85" s="31"/>
+      <c r="H85" s="31"/>
+      <c r="I85" s="31"/>
+      <c r="J85" s="31"/>
+      <c r="K85" s="31"/>
+      <c r="L85" s="31"/>
+      <c r="M85" s="31"/>
+      <c r="N85" s="31"/>
+    </row>
+    <row r="86" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="62"/>
+      <c r="B86" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="C86" s="63"/>
+      <c r="D86" s="63"/>
+      <c r="E86" s="63"/>
+      <c r="F86" s="63"/>
+      <c r="G86" s="63"/>
+      <c r="H86" s="63"/>
+      <c r="I86" s="63"/>
+      <c r="J86" s="63"/>
+      <c r="K86" s="63"/>
+      <c r="L86" s="63"/>
+      <c r="M86" s="63"/>
+      <c r="N86" s="63"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="C22:N23"/>
-    <mergeCell ref="A25:A35"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C35:N35"/>
+  <mergeCells count="21">
+    <mergeCell ref="A56:A86"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="C86:N86"/>
     <mergeCell ref="A24:L24"/>
     <mergeCell ref="M24:N24"/>
     <mergeCell ref="M1:N1"/>
@@ -5097,6 +10281,12 @@
     <mergeCell ref="A2:A12"/>
     <mergeCell ref="A13:A23"/>
     <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:N23"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C55:N55"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="A25:A55"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="M1" location="Таблица!A44" display="Соотв. таблица" xr:uid="{4CD65288-3286-4AD3-A58F-54F99559607B}"/>
@@ -5111,10 +10301,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4269BDC4-CFAE-4A4A-95F0-395DE59C8746}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <dimension ref="M10"/>
+  <sheetFormatPr defaultRowHeight="22.1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="16384" width="9.140625" style="41"/>
+  </cols>
+  <sheetData>
+    <row r="10" spans="13:13" x14ac:dyDescent="0.3">
+      <c r="M10" s="41" t="s">
+        <v>93</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/DecompositionLU/docs/statistics.xlsx
+++ b/DecompositionLU/docs/statistics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maxim\source\repos\practice\SECOND_COURSE\FOR_ITLAB\ArchBenchs\DecompositionLU\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D008614A-3AA6-44F3-9329-9BDFFF850BE6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53BC1C17-75AD-4989-A155-43BF22094778}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-114" yWindow="-114" windowWidth="27602" windowHeight="15027" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-114" yWindow="-114" windowWidth="27602" windowHeight="15027" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Таблица" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="103">
   <si>
     <t>Я не уверен, будет ли это использоваться в готовой презентации и так ли это надо делать, если да, так что пока считаем, что файл для личного пользования.</t>
   </si>
@@ -397,14 +397,26 @@
     <t>Эффективность</t>
   </si>
   <si>
-    <t>Мне нравится, но ускорение могло быть лучше</t>
+    <t>Мне нравится, но ускорение могло быть лучше. Возможно, это связано с энергосберегающими ядрами процессора</t>
+  </si>
+  <si>
+    <t>4 производительных, 8 энергосберегающих ядер</t>
+  </si>
+  <si>
+    <t>Производительные: ~1.7-2.1 GHz, ~4.4 Ghz, hyperthreading</t>
+  </si>
+  <si>
+    <t>Энергосберегающие: ~1.2-1.5 GHz, ~3.3 GHz</t>
+  </si>
+  <si>
+    <t>12 Мб кэша третьего уровня, 10 Мб - второго</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -515,6 +527,14 @@
       <charset val="204"/>
     </font>
     <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="GOST Common"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
       <sz val="18"/>
       <color theme="1"/>
       <name val="GOST Common"/>
@@ -679,7 +699,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -774,6 +794,7 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -816,6 +837,9 @@
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
@@ -824,9 +848,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2597,28 +2618,28 @@
               <c:strCache>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>#DIV/0!</c:v>
+                  <c:v>#ДЕЛ/0!</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>#DIV/0!</c:v>
+                  <c:v>#ДЕЛ/0!</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>#DIV/0!</c:v>
+                  <c:v>#ДЕЛ/0!</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>#DIV/0!</c:v>
+                  <c:v>#ДЕЛ/0!</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>#DIV/0!</c:v>
+                  <c:v>#ДЕЛ/0!</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>#DIV/0!</c:v>
+                  <c:v>#ДЕЛ/0!</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>#DIV/0!</c:v>
+                  <c:v>#ДЕЛ/0!</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>#DIV/0!</c:v>
+                  <c:v>#ДЕЛ/0!</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2971,28 +2992,28 @@
               <c:strCache>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>#DIV/0!</c:v>
+                  <c:v>#ДЕЛ/0!</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>#DIV/0!</c:v>
+                  <c:v>#ДЕЛ/0!</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>#DIV/0!</c:v>
+                  <c:v>#ДЕЛ/0!</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>#DIV/0!</c:v>
+                  <c:v>#ДЕЛ/0!</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>#DIV/0!</c:v>
+                  <c:v>#ДЕЛ/0!</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>#DIV/0!</c:v>
+                  <c:v>#ДЕЛ/0!</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>#DIV/0!</c:v>
+                  <c:v>#ДЕЛ/0!</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>#DIV/0!</c:v>
+                  <c:v>#ДЕЛ/0!</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6935,22 +6956,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>9053</xdr:colOff>
+      <xdr:colOff>208229</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>162962</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>465843</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>21108</xdr:rowOff>
+      <xdr:colOff>57156</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>273426</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Рисунок 1">
+        <xdr:cNvPr id="3" name="Рисунок 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{77F3D0DE-7688-4F41-B6B2-A8862A31AAEF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8AF8B7F6-D74A-4CDC-B0AF-980BCBE244CF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6966,8 +6987,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9053" y="0"/>
-          <a:ext cx="6251008" cy="1424395"/>
+          <a:off x="208229" y="162962"/>
+          <a:ext cx="5643145" cy="5162298"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6978,23 +6999,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>63374</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>81481</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>181069</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>262550</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>491723</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>191945</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>176382</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>257032</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Рисунок 2">
+        <xdr:cNvPr id="4" name="Рисунок 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8AF8B7F6-D74A-4CDC-B0AF-980BCBE244CF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{221F9B8A-2F8A-4250-B9AE-2A1DBD282628}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7010,51 +7031,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="63374" y="1484768"/>
-          <a:ext cx="5643145" cy="5162298"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>574735</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>275139</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Рисунок 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{221F9B8A-2F8A-4250-B9AE-2A1DBD282628}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6373640" y="280657"/>
+          <a:off x="5975287" y="262550"/>
           <a:ext cx="6368952" cy="1678427"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -7408,17 +7385,17 @@
       <c r="N3" s="6"/>
     </row>
     <row r="5" spans="1:23" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="49" t="s">
+      <c r="A5" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="50"/>
-      <c r="C5" s="50"/>
-      <c r="D5" s="50"/>
-      <c r="E5" s="51"/>
-      <c r="G5" s="53" t="s">
+      <c r="B5" s="51"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="52"/>
+      <c r="G5" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="H5" s="53"/>
+      <c r="H5" s="54"/>
       <c r="S5" s="5"/>
       <c r="T5" s="14"/>
       <c r="U5" s="14"/>
@@ -7429,14 +7406,14 @@
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="46" t="s">
+      <c r="B6" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="46"/>
-      <c r="D6" s="46"/>
-      <c r="E6" s="46"/>
-      <c r="G6" s="53"/>
-      <c r="H6" s="53"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="47"/>
+      <c r="E6" s="47"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
       <c r="S6" s="14"/>
       <c r="T6" s="14"/>
       <c r="U6" s="14"/>
@@ -7459,8 +7436,8 @@
       <c r="E7" s="8">
         <v>10000</v>
       </c>
-      <c r="G7" s="53"/>
-      <c r="H7" s="53"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="54"/>
       <c r="S7" s="14"/>
       <c r="T7" s="14"/>
       <c r="U7" s="14"/>
@@ -7468,15 +7445,15 @@
       <c r="W7" s="14"/>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A8" s="47" t="s">
+      <c r="A8" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="47"/>
-      <c r="C8" s="47"/>
-      <c r="D8" s="47"/>
-      <c r="E8" s="47"/>
-      <c r="G8" s="53"/>
-      <c r="H8" s="53"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="48"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="54"/>
       <c r="S8" s="14"/>
       <c r="T8" s="14"/>
       <c r="U8" s="14"/>
@@ -7552,13 +7529,13 @@
       <c r="W11" s="5"/>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A12" s="47" t="s">
+      <c r="A12" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="47"/>
-      <c r="C12" s="47"/>
-      <c r="D12" s="47"/>
-      <c r="E12" s="47"/>
+      <c r="B12" s="48"/>
+      <c r="C12" s="48"/>
+      <c r="D12" s="48"/>
+      <c r="E12" s="48"/>
       <c r="F12" s="5"/>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.25">
@@ -7571,7 +7548,7 @@
       <c r="C13" s="10">
         <v>232</v>
       </c>
-      <c r="D13" s="55" t="s">
+      <c r="D13" s="56" t="s">
         <v>21</v>
       </c>
       <c r="E13" s="10">
@@ -7589,7 +7566,7 @@
       <c r="C14" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="56"/>
+      <c r="D14" s="57"/>
       <c r="E14" s="10" t="s">
         <v>10</v>
       </c>
@@ -7607,30 +7584,30 @@
       <c r="C15" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="57"/>
+      <c r="D15" s="58"/>
       <c r="E15" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="58" t="s">
+      <c r="A18" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="58"/>
-      <c r="C18" s="58"/>
-      <c r="D18" s="58"/>
-      <c r="E18" s="58"/>
+      <c r="B18" s="59"/>
+      <c r="C18" s="59"/>
+      <c r="D18" s="59"/>
+      <c r="E18" s="59"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B19" s="46" t="s">
+      <c r="B19" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="C19" s="46"/>
-      <c r="D19" s="46"/>
-      <c r="E19" s="46"/>
+      <c r="C19" s="47"/>
+      <c r="D19" s="47"/>
+      <c r="E19" s="47"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
@@ -7650,13 +7627,13 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="47" t="s">
+      <c r="A21" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="B21" s="47"/>
-      <c r="C21" s="47"/>
-      <c r="D21" s="47"/>
-      <c r="E21" s="47"/>
+      <c r="B21" s="48"/>
+      <c r="C21" s="48"/>
+      <c r="D21" s="48"/>
+      <c r="E21" s="48"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
@@ -7709,17 +7686,17 @@
         <v>35</v>
       </c>
       <c r="G24" s="18"/>
-      <c r="H24" s="52"/>
-      <c r="I24" s="52"/>
+      <c r="H24" s="53"/>
+      <c r="I24" s="53"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="47" t="s">
+      <c r="A25" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="B25" s="47"/>
-      <c r="C25" s="47"/>
-      <c r="D25" s="47"/>
-      <c r="E25" s="47"/>
+      <c r="B25" s="48"/>
+      <c r="C25" s="48"/>
+      <c r="D25" s="48"/>
+      <c r="E25" s="48"/>
       <c r="G25" s="19"/>
       <c r="H25" s="17"/>
       <c r="I25" s="17"/>
@@ -7804,15 +7781,15 @@
       <c r="I30" s="18"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="49" t="s">
+      <c r="A31" s="50" t="s">
         <v>70</v>
       </c>
-      <c r="B31" s="50"/>
-      <c r="C31" s="51"/>
-      <c r="D31" s="48" t="s">
+      <c r="B31" s="51"/>
+      <c r="C31" s="52"/>
+      <c r="D31" s="49" t="s">
         <v>91</v>
       </c>
-      <c r="E31" s="48" t="s">
+      <c r="E31" s="49" t="s">
         <v>91</v>
       </c>
       <c r="G31" s="20"/>
@@ -7823,12 +7800,12 @@
       <c r="A32" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B32" s="46" t="s">
+      <c r="B32" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="46"/>
-      <c r="D32" s="46"/>
-      <c r="E32" s="46"/>
+      <c r="C32" s="47"/>
+      <c r="D32" s="47"/>
+      <c r="E32" s="47"/>
       <c r="G32" s="23"/>
       <c r="H32" s="18"/>
       <c r="I32" s="18"/>
@@ -7854,13 +7831,13 @@
       <c r="I33" s="18"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="47" t="s">
+      <c r="A34" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="B34" s="47"/>
-      <c r="C34" s="47"/>
-      <c r="D34" s="47"/>
-      <c r="E34" s="47"/>
+      <c r="B34" s="48"/>
+      <c r="C34" s="48"/>
+      <c r="D34" s="48"/>
+      <c r="E34" s="48"/>
       <c r="G34" s="23"/>
       <c r="H34" s="18"/>
       <c r="I34" s="18"/>
@@ -7926,13 +7903,13 @@
       <c r="I37" s="18"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="47" t="s">
+      <c r="A38" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="B38" s="47"/>
-      <c r="C38" s="47"/>
-      <c r="D38" s="47"/>
-      <c r="E38" s="47"/>
+      <c r="B38" s="48"/>
+      <c r="C38" s="48"/>
+      <c r="D38" s="48"/>
+      <c r="E38" s="48"/>
       <c r="G38" s="23"/>
       <c r="H38" s="18"/>
       <c r="I38" s="18"/>
@@ -7998,23 +7975,23 @@
       <c r="I41" s="18"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B42" s="54" t="s">
+      <c r="B42" s="55" t="s">
         <v>66</v>
       </c>
-      <c r="C42" s="54"/>
-      <c r="D42" s="54"/>
-      <c r="E42" s="54"/>
+      <c r="C42" s="55"/>
+      <c r="D42" s="55"/>
+      <c r="E42" s="55"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="49" t="s">
+      <c r="A44" s="50" t="s">
         <v>82</v>
       </c>
-      <c r="B44" s="50"/>
-      <c r="C44" s="51"/>
-      <c r="D44" s="48" t="s">
+      <c r="B44" s="51"/>
+      <c r="C44" s="52"/>
+      <c r="D44" s="49" t="s">
         <v>92</v>
       </c>
-      <c r="E44" s="48" t="s">
+      <c r="E44" s="49" t="s">
         <v>91</v>
       </c>
     </row>
@@ -8022,12 +7999,12 @@
       <c r="A45" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B45" s="46" t="s">
+      <c r="B45" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="C45" s="46"/>
-      <c r="D45" s="46"/>
-      <c r="E45" s="46"/>
+      <c r="C45" s="47"/>
+      <c r="D45" s="47"/>
+      <c r="E45" s="47"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
@@ -8047,13 +8024,13 @@
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="47" t="s">
+      <c r="A47" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="B47" s="47"/>
-      <c r="C47" s="47"/>
-      <c r="D47" s="47"/>
-      <c r="E47" s="47"/>
+      <c r="B47" s="48"/>
+      <c r="C47" s="48"/>
+      <c r="D47" s="48"/>
+      <c r="E47" s="48"/>
       <c r="G47" s="1" t="s">
         <v>95</v>
       </c>
@@ -8066,16 +8043,16 @@
         <v>7</v>
       </c>
       <c r="B48" s="9">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C48" s="10">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c r="D48" s="10">
-        <v>378</v>
+        <v>486</v>
       </c>
       <c r="E48" s="10">
-        <v>1131</v>
+        <v>1184</v>
       </c>
       <c r="G48" s="1">
         <v>32</v>
@@ -8089,16 +8066,16 @@
         <v>8</v>
       </c>
       <c r="B49" s="9">
-        <v>122</v>
+        <v>77</v>
       </c>
       <c r="C49" s="10">
-        <v>2103</v>
+        <v>994</v>
       </c>
       <c r="D49" s="10">
-        <v>26833</v>
+        <v>9972</v>
       </c>
       <c r="E49" s="10">
-        <v>73485</v>
+        <v>28809</v>
       </c>
       <c r="G49" s="1">
         <v>128</v>
@@ -8112,16 +8089,16 @@
         <v>9</v>
       </c>
       <c r="B50" s="9">
-        <v>139</v>
+        <v>99</v>
       </c>
       <c r="C50" s="10">
-        <v>2226</v>
+        <v>1149</v>
       </c>
       <c r="D50" s="10">
-        <v>27211</v>
+        <v>10459</v>
       </c>
       <c r="E50" s="10">
-        <v>74635</v>
+        <v>30062</v>
       </c>
       <c r="G50" s="1">
         <v>256</v>
@@ -8131,13 +8108,13 @@
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="47" t="s">
+      <c r="A51" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="B51" s="47"/>
-      <c r="C51" s="47"/>
-      <c r="D51" s="47"/>
-      <c r="E51" s="47"/>
+      <c r="B51" s="48"/>
+      <c r="C51" s="48"/>
+      <c r="D51" s="48"/>
+      <c r="E51" s="48"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
@@ -8245,24 +8222,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="59" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
-      <c r="I1" s="58"/>
-      <c r="J1" s="58"/>
-      <c r="K1" s="58"/>
-      <c r="L1" s="58"/>
-      <c r="M1" s="48" t="s">
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="59"/>
+      <c r="K1" s="59"/>
+      <c r="L1" s="59"/>
+      <c r="M1" s="49" t="s">
         <v>90</v>
       </c>
-      <c r="N1" s="48"/>
+      <c r="N1" s="49"/>
       <c r="O1" s="36"/>
       <c r="P1" s="35"/>
       <c r="Q1" s="35"/>
@@ -8277,14 +8254,14 @@
       <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="65" t="s">
+      <c r="A2" s="66" t="s">
         <v>85</v>
       </c>
       <c r="B2" s="44"/>
-      <c r="C2" s="59" t="s">
+      <c r="C2" s="60" t="s">
         <v>78</v>
       </c>
-      <c r="D2" s="59"/>
+      <c r="D2" s="60"/>
       <c r="E2" s="31"/>
       <c r="F2" s="31"/>
       <c r="G2" s="31"/>
@@ -8309,7 +8286,7 @@
       <c r="Z2" s="30"/>
     </row>
     <row r="3" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="65"/>
+      <c r="A3" s="66"/>
       <c r="B3" s="29" t="s">
         <v>77</v>
       </c>
@@ -8343,7 +8320,7 @@
       <c r="Z3" s="30"/>
     </row>
     <row r="4" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="65"/>
+      <c r="A4" s="66"/>
       <c r="B4" s="15">
         <v>1</v>
       </c>
@@ -8377,7 +8354,7 @@
       <c r="Z4" s="30"/>
     </row>
     <row r="5" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="65"/>
+      <c r="A5" s="66"/>
       <c r="B5" s="15">
         <v>2</v>
       </c>
@@ -8411,7 +8388,7 @@
       <c r="Z5" s="30"/>
     </row>
     <row r="6" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="65"/>
+      <c r="A6" s="66"/>
       <c r="B6" s="15">
         <v>4</v>
       </c>
@@ -8434,7 +8411,7 @@
       <c r="O6" s="38"/>
     </row>
     <row r="7" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="65"/>
+      <c r="A7" s="66"/>
       <c r="B7" s="15">
         <v>6</v>
       </c>
@@ -8457,7 +8434,7 @@
       <c r="O7" s="38"/>
     </row>
     <row r="8" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="65"/>
+      <c r="A8" s="66"/>
       <c r="B8" s="15">
         <v>8</v>
       </c>
@@ -8480,7 +8457,7 @@
       <c r="O8" s="38"/>
     </row>
     <row r="9" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="65"/>
+      <c r="A9" s="66"/>
       <c r="B9" s="15">
         <v>10</v>
       </c>
@@ -8503,7 +8480,7 @@
       <c r="O9" s="38"/>
     </row>
     <row r="10" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="65"/>
+      <c r="A10" s="66"/>
       <c r="B10" s="15">
         <v>12</v>
       </c>
@@ -8526,7 +8503,7 @@
       <c r="O10" s="38"/>
     </row>
     <row r="11" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="65"/>
+      <c r="A11" s="66"/>
       <c r="B11" s="15">
         <v>16</v>
       </c>
@@ -8551,37 +8528,37 @@
       <c r="Q11" s="27"/>
     </row>
     <row r="12" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="65"/>
+      <c r="A12" s="66"/>
       <c r="B12" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="C12" s="63" t="s">
+      <c r="C12" s="61" t="s">
         <v>81</v>
       </c>
-      <c r="D12" s="63"/>
-      <c r="E12" s="63"/>
-      <c r="F12" s="63"/>
-      <c r="G12" s="63"/>
-      <c r="H12" s="63"/>
-      <c r="I12" s="63"/>
-      <c r="J12" s="63"/>
-      <c r="K12" s="63"/>
-      <c r="L12" s="63"/>
-      <c r="M12" s="63"/>
-      <c r="N12" s="64"/>
+      <c r="D12" s="61"/>
+      <c r="E12" s="61"/>
+      <c r="F12" s="61"/>
+      <c r="G12" s="61"/>
+      <c r="H12" s="61"/>
+      <c r="I12" s="61"/>
+      <c r="J12" s="61"/>
+      <c r="K12" s="61"/>
+      <c r="L12" s="61"/>
+      <c r="M12" s="61"/>
+      <c r="N12" s="65"/>
       <c r="O12" s="39"/>
       <c r="P12" s="23"/>
       <c r="Q12" s="23"/>
     </row>
     <row r="13" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="65" t="s">
+      <c r="A13" s="66" t="s">
         <v>87</v>
       </c>
       <c r="B13" s="44"/>
-      <c r="C13" s="59" t="s">
+      <c r="C13" s="60" t="s">
         <v>78</v>
       </c>
-      <c r="D13" s="59"/>
+      <c r="D13" s="60"/>
       <c r="E13" s="32"/>
       <c r="F13" s="31"/>
       <c r="G13" s="31"/>
@@ -8597,7 +8574,7 @@
       <c r="Q13" s="23"/>
     </row>
     <row r="14" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="65"/>
+      <c r="A14" s="66"/>
       <c r="B14" s="13" t="s">
         <v>77</v>
       </c>
@@ -8622,7 +8599,7 @@
       <c r="Q14" s="23"/>
     </row>
     <row r="15" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="65"/>
+      <c r="A15" s="66"/>
       <c r="B15" s="15">
         <v>1</v>
       </c>
@@ -8647,7 +8624,7 @@
       <c r="Q15" s="27"/>
     </row>
     <row r="16" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="65"/>
+      <c r="A16" s="66"/>
       <c r="B16" s="15">
         <v>2</v>
       </c>
@@ -8672,7 +8649,7 @@
       <c r="Q16" s="23"/>
     </row>
     <row r="17" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="65"/>
+      <c r="A17" s="66"/>
       <c r="B17" s="15">
         <v>4</v>
       </c>
@@ -8697,7 +8674,7 @@
       <c r="Q17" s="23"/>
     </row>
     <row r="18" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="65"/>
+      <c r="A18" s="66"/>
       <c r="B18" s="15">
         <v>6</v>
       </c>
@@ -8722,7 +8699,7 @@
       <c r="Q18" s="23"/>
     </row>
     <row r="19" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="65"/>
+      <c r="A19" s="66"/>
       <c r="B19" s="15">
         <v>8</v>
       </c>
@@ -8745,7 +8722,7 @@
       <c r="O19" s="38"/>
     </row>
     <row r="20" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="65"/>
+      <c r="A20" s="66"/>
       <c r="B20" s="15">
         <v>10</v>
       </c>
@@ -8768,7 +8745,7 @@
       <c r="O20" s="38"/>
     </row>
     <row r="21" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="65"/>
+      <c r="A21" s="66"/>
       <c r="B21" s="15">
         <v>12</v>
       </c>
@@ -8791,73 +8768,73 @@
       <c r="O21" s="38"/>
     </row>
     <row r="22" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="65"/>
-      <c r="B22" s="66" t="s">
+      <c r="A22" s="66"/>
+      <c r="B22" s="67" t="s">
         <v>86</v>
       </c>
-      <c r="C22" s="67" t="s">
+      <c r="C22" s="68" t="s">
         <v>88</v>
       </c>
-      <c r="D22" s="67"/>
-      <c r="E22" s="67"/>
-      <c r="F22" s="67"/>
-      <c r="G22" s="67"/>
-      <c r="H22" s="67"/>
-      <c r="I22" s="67"/>
-      <c r="J22" s="67"/>
-      <c r="K22" s="67"/>
-      <c r="L22" s="67"/>
-      <c r="M22" s="67"/>
-      <c r="N22" s="68"/>
+      <c r="D22" s="68"/>
+      <c r="E22" s="68"/>
+      <c r="F22" s="68"/>
+      <c r="G22" s="68"/>
+      <c r="H22" s="68"/>
+      <c r="I22" s="68"/>
+      <c r="J22" s="68"/>
+      <c r="K22" s="68"/>
+      <c r="L22" s="68"/>
+      <c r="M22" s="68"/>
+      <c r="N22" s="69"/>
       <c r="O22" s="38"/>
     </row>
     <row r="23" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="65"/>
-      <c r="B23" s="66"/>
-      <c r="C23" s="67"/>
-      <c r="D23" s="67"/>
-      <c r="E23" s="67"/>
-      <c r="F23" s="67"/>
-      <c r="G23" s="67"/>
-      <c r="H23" s="67"/>
-      <c r="I23" s="67"/>
-      <c r="J23" s="67"/>
-      <c r="K23" s="67"/>
-      <c r="L23" s="67"/>
-      <c r="M23" s="67"/>
-      <c r="N23" s="68"/>
+      <c r="A23" s="66"/>
+      <c r="B23" s="67"/>
+      <c r="C23" s="68"/>
+      <c r="D23" s="68"/>
+      <c r="E23" s="68"/>
+      <c r="F23" s="68"/>
+      <c r="G23" s="68"/>
+      <c r="H23" s="68"/>
+      <c r="I23" s="68"/>
+      <c r="J23" s="68"/>
+      <c r="K23" s="68"/>
+      <c r="L23" s="68"/>
+      <c r="M23" s="68"/>
+      <c r="N23" s="69"/>
       <c r="O23" s="38"/>
     </row>
     <row r="24" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="58" t="s">
+      <c r="A24" s="59" t="s">
         <v>89</v>
       </c>
-      <c r="B24" s="58"/>
-      <c r="C24" s="58"/>
-      <c r="D24" s="58"/>
-      <c r="E24" s="58"/>
-      <c r="F24" s="58"/>
-      <c r="G24" s="58"/>
-      <c r="H24" s="58"/>
-      <c r="I24" s="58"/>
-      <c r="J24" s="58"/>
-      <c r="K24" s="58"/>
-      <c r="L24" s="58"/>
-      <c r="M24" s="48" t="s">
+      <c r="B24" s="59"/>
+      <c r="C24" s="59"/>
+      <c r="D24" s="59"/>
+      <c r="E24" s="59"/>
+      <c r="F24" s="59"/>
+      <c r="G24" s="59"/>
+      <c r="H24" s="59"/>
+      <c r="I24" s="59"/>
+      <c r="J24" s="59"/>
+      <c r="K24" s="59"/>
+      <c r="L24" s="59"/>
+      <c r="M24" s="49" t="s">
         <v>90</v>
       </c>
-      <c r="N24" s="48"/>
+      <c r="N24" s="49"/>
       <c r="O24" s="38"/>
     </row>
     <row r="25" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="60" t="s">
+      <c r="A25" s="62" t="s">
         <v>85</v>
       </c>
       <c r="B25" s="44"/>
-      <c r="C25" s="59" t="s">
+      <c r="C25" s="60" t="s">
         <v>78</v>
       </c>
-      <c r="D25" s="59"/>
+      <c r="D25" s="60"/>
       <c r="E25" s="31"/>
       <c r="F25" s="31"/>
       <c r="G25" s="31"/>
@@ -8871,7 +8848,7 @@
       <c r="O25" s="27"/>
     </row>
     <row r="26" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="61"/>
+      <c r="A26" s="63"/>
       <c r="B26" s="42" t="s">
         <v>77</v>
       </c>
@@ -8894,7 +8871,7 @@
       <c r="O26" s="27"/>
     </row>
     <row r="27" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="61"/>
+      <c r="A27" s="63"/>
       <c r="B27" s="15">
         <v>1</v>
       </c>
@@ -8917,7 +8894,7 @@
       <c r="O27" s="27"/>
     </row>
     <row r="28" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="61"/>
+      <c r="A28" s="63"/>
       <c r="B28" s="15">
         <v>2</v>
       </c>
@@ -8940,7 +8917,7 @@
       <c r="O28" s="27"/>
     </row>
     <row r="29" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="61"/>
+      <c r="A29" s="63"/>
       <c r="B29" s="15">
         <v>4</v>
       </c>
@@ -8963,7 +8940,7 @@
       <c r="O29" s="27"/>
     </row>
     <row r="30" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="61"/>
+      <c r="A30" s="63"/>
       <c r="B30" s="15">
         <v>6</v>
       </c>
@@ -8986,7 +8963,7 @@
       <c r="O30" s="27"/>
     </row>
     <row r="31" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="61"/>
+      <c r="A31" s="63"/>
       <c r="B31" s="15">
         <v>8</v>
       </c>
@@ -9009,7 +8986,7 @@
       <c r="O31" s="27"/>
     </row>
     <row r="32" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="61"/>
+      <c r="A32" s="63"/>
       <c r="B32" s="15">
         <v>10</v>
       </c>
@@ -9032,7 +9009,7 @@
       <c r="O32" s="27"/>
     </row>
     <row r="33" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="61"/>
+      <c r="A33" s="63"/>
       <c r="B33" s="15">
         <v>12</v>
       </c>
@@ -9055,7 +9032,7 @@
       <c r="O33" s="27"/>
     </row>
     <row r="34" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="61"/>
+      <c r="A34" s="63"/>
       <c r="B34" s="15">
         <v>16</v>
       </c>
@@ -9078,12 +9055,12 @@
       <c r="O34" s="27"/>
     </row>
     <row r="35" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="61"/>
+      <c r="A35" s="63"/>
       <c r="B35" s="45"/>
-      <c r="C35" s="59" t="s">
+      <c r="C35" s="60" t="s">
         <v>96</v>
       </c>
-      <c r="D35" s="59"/>
+      <c r="D35" s="60"/>
       <c r="E35" s="31"/>
       <c r="F35" s="31"/>
       <c r="G35" s="31"/>
@@ -9097,7 +9074,7 @@
       <c r="O35" s="27"/>
     </row>
     <row r="36" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="61"/>
+      <c r="A36" s="63"/>
       <c r="B36" s="42" t="s">
         <v>77</v>
       </c>
@@ -9121,7 +9098,7 @@
       <c r="P36" s="1"/>
     </row>
     <row r="37" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="61"/>
+      <c r="A37" s="63"/>
       <c r="B37" s="42">
         <v>1</v>
       </c>
@@ -9147,7 +9124,7 @@
       <c r="P37" s="1"/>
     </row>
     <row r="38" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="61"/>
+      <c r="A38" s="63"/>
       <c r="B38" s="42">
         <v>2</v>
       </c>
@@ -9173,7 +9150,7 @@
       <c r="P38" s="1"/>
     </row>
     <row r="39" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="61"/>
+      <c r="A39" s="63"/>
       <c r="B39" s="42">
         <v>4</v>
       </c>
@@ -9199,7 +9176,7 @@
       <c r="P39" s="1"/>
     </row>
     <row r="40" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="61"/>
+      <c r="A40" s="63"/>
       <c r="B40" s="42">
         <v>6</v>
       </c>
@@ -9225,7 +9202,7 @@
       <c r="P40" s="1"/>
     </row>
     <row r="41" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="61"/>
+      <c r="A41" s="63"/>
       <c r="B41" s="42">
         <v>8</v>
       </c>
@@ -9251,7 +9228,7 @@
       <c r="P41" s="1"/>
     </row>
     <row r="42" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="61"/>
+      <c r="A42" s="63"/>
       <c r="B42" s="42">
         <v>10</v>
       </c>
@@ -9277,7 +9254,7 @@
       <c r="P42" s="1"/>
     </row>
     <row r="43" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="61"/>
+      <c r="A43" s="63"/>
       <c r="B43" s="42">
         <v>12</v>
       </c>
@@ -9303,7 +9280,7 @@
       <c r="P43" s="1"/>
     </row>
     <row r="44" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="61"/>
+      <c r="A44" s="63"/>
       <c r="B44" s="42">
         <v>16</v>
       </c>
@@ -9329,12 +9306,12 @@
       <c r="P44" s="1"/>
     </row>
     <row r="45" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="61"/>
+      <c r="A45" s="63"/>
       <c r="B45" s="45"/>
-      <c r="C45" s="59" t="s">
+      <c r="C45" s="60" t="s">
         <v>97</v>
       </c>
-      <c r="D45" s="59"/>
+      <c r="D45" s="60"/>
       <c r="E45" s="43"/>
       <c r="F45" s="43"/>
       <c r="G45" s="43"/>
@@ -9349,7 +9326,7 @@
       <c r="P45" s="1"/>
     </row>
     <row r="46" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="61"/>
+      <c r="A46" s="63"/>
       <c r="B46" s="42" t="s">
         <v>77</v>
       </c>
@@ -9373,16 +9350,16 @@
       <c r="P46" s="1"/>
     </row>
     <row r="47" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="61"/>
+      <c r="A47" s="63"/>
       <c r="B47" s="42">
         <v>1</v>
       </c>
       <c r="C47" s="43">
-        <f>C37/B37</f>
+        <f t="shared" ref="C47:C54" si="0">C37/B37</f>
         <v>1</v>
       </c>
       <c r="D47" s="43">
-        <f>D37/B37</f>
+        <f t="shared" ref="D47:D54" si="1">D37/B37</f>
         <v>1</v>
       </c>
       <c r="E47" s="43"/>
@@ -9399,16 +9376,16 @@
       <c r="P47" s="1"/>
     </row>
     <row r="48" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="61"/>
+      <c r="A48" s="63"/>
       <c r="B48" s="42">
         <v>2</v>
       </c>
       <c r="C48" s="43">
-        <f>C38/B38</f>
+        <f t="shared" si="0"/>
         <v>0.98108925869894104</v>
       </c>
       <c r="D48" s="43">
-        <f>D38/B38</f>
+        <f t="shared" si="1"/>
         <v>0.94677230671062429</v>
       </c>
       <c r="E48" s="43"/>
@@ -9425,16 +9402,16 @@
       <c r="P48" s="1"/>
     </row>
     <row r="49" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="61"/>
+      <c r="A49" s="63"/>
       <c r="B49" s="42">
         <v>4</v>
       </c>
       <c r="C49" s="43">
-        <f>C39/B39</f>
+        <f t="shared" si="0"/>
         <v>0.91330112232959226</v>
       </c>
       <c r="D49" s="43">
-        <f>D39/B39</f>
+        <f t="shared" si="1"/>
         <v>0.90472560975609762</v>
       </c>
       <c r="E49" s="43"/>
@@ -9451,16 +9428,16 @@
       <c r="P49" s="1"/>
     </row>
     <row r="50" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="61"/>
+      <c r="A50" s="63"/>
       <c r="B50" s="42">
         <v>6</v>
       </c>
       <c r="C50" s="43">
-        <f>C40/B40</f>
+        <f t="shared" si="0"/>
         <v>0.78055848749143564</v>
       </c>
       <c r="D50" s="43">
-        <f>D40/B40</f>
+        <f t="shared" si="1"/>
         <v>0.73380316518298716</v>
       </c>
       <c r="E50" s="43"/>
@@ -9477,16 +9454,16 @@
       <c r="P50" s="1"/>
     </row>
     <row r="51" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="61"/>
+      <c r="A51" s="63"/>
       <c r="B51" s="42">
         <v>8</v>
       </c>
       <c r="C51" s="43">
-        <f>C41/B41</f>
+        <f t="shared" si="0"/>
         <v>0.73910260906157943</v>
       </c>
       <c r="D51" s="43">
-        <f>D41/B41</f>
+        <f t="shared" si="1"/>
         <v>0.67097527886644559</v>
       </c>
       <c r="E51" s="43"/>
@@ -9502,16 +9479,16 @@
       <c r="O51" s="1"/>
     </row>
     <row r="52" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="61"/>
+      <c r="A52" s="63"/>
       <c r="B52" s="42">
         <v>10</v>
       </c>
       <c r="C52" s="43">
-        <f>C42/B42</f>
+        <f t="shared" si="0"/>
         <v>0.66718106995884774</v>
       </c>
       <c r="D52" s="43">
-        <f>D42/B42</f>
+        <f t="shared" si="1"/>
         <v>0.59608302644794109</v>
       </c>
       <c r="E52" s="43"/>
@@ -9527,16 +9504,16 @@
       <c r="O52" s="1"/>
     </row>
     <row r="53" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="61"/>
+      <c r="A53" s="63"/>
       <c r="B53" s="42">
         <v>12</v>
       </c>
       <c r="C53" s="43">
-        <f>C43/B43</f>
+        <f t="shared" si="0"/>
         <v>0.61496994631185808</v>
       </c>
       <c r="D53" s="43">
-        <f>D43/B43</f>
+        <f t="shared" si="1"/>
         <v>0.54191015339663984</v>
       </c>
       <c r="E53" s="31"/>
@@ -9552,16 +9529,16 @@
       <c r="O53" s="1"/>
     </row>
     <row r="54" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="61"/>
+      <c r="A54" s="63"/>
       <c r="B54" s="42">
         <v>16</v>
       </c>
       <c r="C54" s="43">
-        <f>C44/B44</f>
+        <f t="shared" si="0"/>
         <v>0.53014010463829364</v>
       </c>
       <c r="D54" s="43">
-        <f>D44/B44</f>
+        <f t="shared" si="1"/>
         <v>0.44745174909529556</v>
       </c>
       <c r="E54" s="31"/>
@@ -9577,34 +9554,34 @@
       <c r="O54" s="1"/>
     </row>
     <row r="55" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="62"/>
+      <c r="A55" s="64"/>
       <c r="B55" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="C55" s="63" t="s">
+      <c r="C55" s="61" t="s">
         <v>98</v>
       </c>
-      <c r="D55" s="63"/>
-      <c r="E55" s="63"/>
-      <c r="F55" s="63"/>
-      <c r="G55" s="63"/>
-      <c r="H55" s="63"/>
-      <c r="I55" s="63"/>
-      <c r="J55" s="63"/>
-      <c r="K55" s="63"/>
-      <c r="L55" s="63"/>
-      <c r="M55" s="63"/>
-      <c r="N55" s="63"/>
+      <c r="D55" s="61"/>
+      <c r="E55" s="61"/>
+      <c r="F55" s="61"/>
+      <c r="G55" s="61"/>
+      <c r="H55" s="61"/>
+      <c r="I55" s="61"/>
+      <c r="J55" s="61"/>
+      <c r="K55" s="61"/>
+      <c r="L55" s="61"/>
+      <c r="M55" s="61"/>
+      <c r="N55" s="61"/>
     </row>
     <row r="56" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="60" t="s">
+      <c r="A56" s="62" t="s">
         <v>87</v>
       </c>
       <c r="B56" s="44"/>
-      <c r="C56" s="59" t="s">
+      <c r="C56" s="60" t="s">
         <v>78</v>
       </c>
-      <c r="D56" s="59"/>
+      <c r="D56" s="60"/>
       <c r="E56" s="31"/>
       <c r="F56" s="31"/>
       <c r="G56" s="31"/>
@@ -9617,7 +9594,7 @@
       <c r="N56" s="31"/>
     </row>
     <row r="57" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="61"/>
+      <c r="A57" s="63"/>
       <c r="B57" s="42" t="s">
         <v>77</v>
       </c>
@@ -9639,7 +9616,7 @@
       <c r="N57" s="31"/>
     </row>
     <row r="58" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="61"/>
+      <c r="A58" s="63"/>
       <c r="B58" s="15">
         <v>1</v>
       </c>
@@ -9657,7 +9634,7 @@
       <c r="N58" s="31"/>
     </row>
     <row r="59" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="61"/>
+      <c r="A59" s="63"/>
       <c r="B59" s="15">
         <v>2</v>
       </c>
@@ -9675,7 +9652,7 @@
       <c r="N59" s="31"/>
     </row>
     <row r="60" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="61"/>
+      <c r="A60" s="63"/>
       <c r="B60" s="15">
         <v>4</v>
       </c>
@@ -9693,7 +9670,7 @@
       <c r="N60" s="31"/>
     </row>
     <row r="61" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="61"/>
+      <c r="A61" s="63"/>
       <c r="B61" s="15">
         <v>6</v>
       </c>
@@ -9711,7 +9688,7 @@
       <c r="N61" s="31"/>
     </row>
     <row r="62" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="61"/>
+      <c r="A62" s="63"/>
       <c r="B62" s="15">
         <v>8</v>
       </c>
@@ -9729,7 +9706,7 @@
       <c r="N62" s="31"/>
     </row>
     <row r="63" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="61"/>
+      <c r="A63" s="63"/>
       <c r="B63" s="15">
         <v>10</v>
       </c>
@@ -9747,7 +9724,7 @@
       <c r="N63" s="31"/>
     </row>
     <row r="64" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="61"/>
+      <c r="A64" s="63"/>
       <c r="B64" s="15">
         <v>12</v>
       </c>
@@ -9765,7 +9742,7 @@
       <c r="N64" s="31"/>
     </row>
     <row r="65" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="61"/>
+      <c r="A65" s="63"/>
       <c r="B65" s="15">
         <v>16</v>
       </c>
@@ -9783,12 +9760,12 @@
       <c r="N65" s="31"/>
     </row>
     <row r="66" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="61"/>
+      <c r="A66" s="63"/>
       <c r="B66" s="45"/>
-      <c r="C66" s="59" t="s">
+      <c r="C66" s="60" t="s">
         <v>96</v>
       </c>
-      <c r="D66" s="59"/>
+      <c r="D66" s="60"/>
       <c r="E66" s="31"/>
       <c r="F66" s="31"/>
       <c r="G66" s="31"/>
@@ -9801,7 +9778,7 @@
       <c r="N66" s="31"/>
     </row>
     <row r="67" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="61"/>
+      <c r="A67" s="63"/>
       <c r="B67" s="42" t="s">
         <v>77</v>
       </c>
@@ -9823,7 +9800,7 @@
       <c r="N67" s="16"/>
     </row>
     <row r="68" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="61"/>
+      <c r="A68" s="63"/>
       <c r="B68" s="42">
         <v>1</v>
       </c>
@@ -9847,7 +9824,7 @@
       <c r="N68" s="16"/>
     </row>
     <row r="69" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="61"/>
+      <c r="A69" s="63"/>
       <c r="B69" s="42">
         <v>2</v>
       </c>
@@ -9871,7 +9848,7 @@
       <c r="N69" s="16"/>
     </row>
     <row r="70" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="61"/>
+      <c r="A70" s="63"/>
       <c r="B70" s="42">
         <v>4</v>
       </c>
@@ -9895,7 +9872,7 @@
       <c r="N70" s="16"/>
     </row>
     <row r="71" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="61"/>
+      <c r="A71" s="63"/>
       <c r="B71" s="42">
         <v>6</v>
       </c>
@@ -9919,7 +9896,7 @@
       <c r="N71" s="16"/>
     </row>
     <row r="72" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="61"/>
+      <c r="A72" s="63"/>
       <c r="B72" s="42">
         <v>8</v>
       </c>
@@ -9943,7 +9920,7 @@
       <c r="N72" s="16"/>
     </row>
     <row r="73" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="61"/>
+      <c r="A73" s="63"/>
       <c r="B73" s="42">
         <v>10</v>
       </c>
@@ -9967,7 +9944,7 @@
       <c r="N73" s="16"/>
     </row>
     <row r="74" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="61"/>
+      <c r="A74" s="63"/>
       <c r="B74" s="42">
         <v>12</v>
       </c>
@@ -9991,7 +9968,7 @@
       <c r="N74" s="16"/>
     </row>
     <row r="75" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="61"/>
+      <c r="A75" s="63"/>
       <c r="B75" s="42">
         <v>16</v>
       </c>
@@ -10015,12 +9992,12 @@
       <c r="N75" s="16"/>
     </row>
     <row r="76" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="61"/>
+      <c r="A76" s="63"/>
       <c r="B76" s="45"/>
-      <c r="C76" s="59" t="s">
+      <c r="C76" s="60" t="s">
         <v>97</v>
       </c>
-      <c r="D76" s="59"/>
+      <c r="D76" s="60"/>
       <c r="E76" s="43"/>
       <c r="F76" s="43"/>
       <c r="G76" s="43"/>
@@ -10033,7 +10010,7 @@
       <c r="N76" s="16"/>
     </row>
     <row r="77" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="61"/>
+      <c r="A77" s="63"/>
       <c r="B77" s="42" t="s">
         <v>77</v>
       </c>
@@ -10055,7 +10032,7 @@
       <c r="N77" s="16"/>
     </row>
     <row r="78" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="61"/>
+      <c r="A78" s="63"/>
       <c r="B78" s="42">
         <v>1</v>
       </c>
@@ -10079,7 +10056,7 @@
       <c r="N78" s="16"/>
     </row>
     <row r="79" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="61"/>
+      <c r="A79" s="63"/>
       <c r="B79" s="42">
         <v>2</v>
       </c>
@@ -10088,7 +10065,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="D79" s="43" t="e">
-        <f t="shared" ref="D79:D85" si="0">D69/B69</f>
+        <f t="shared" ref="D79:D85" si="2">D69/B69</f>
         <v>#DIV/0!</v>
       </c>
       <c r="E79" s="43"/>
@@ -10103,16 +10080,16 @@
       <c r="N79" s="16"/>
     </row>
     <row r="80" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="61"/>
+      <c r="A80" s="63"/>
       <c r="B80" s="42">
         <v>4</v>
       </c>
       <c r="C80" s="43" t="e">
-        <f t="shared" ref="C80:C85" si="1">C70/B70</f>
+        <f t="shared" ref="C80:C85" si="3">C70/B70</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D80" s="43" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E80" s="43"/>
@@ -10127,16 +10104,16 @@
       <c r="N80" s="16"/>
     </row>
     <row r="81" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="61"/>
+      <c r="A81" s="63"/>
       <c r="B81" s="42">
         <v>6</v>
       </c>
       <c r="C81" s="43" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="D81" s="43" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E81" s="43"/>
@@ -10151,16 +10128,16 @@
       <c r="N81" s="16"/>
     </row>
     <row r="82" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="61"/>
+      <c r="A82" s="63"/>
       <c r="B82" s="42">
         <v>8</v>
       </c>
       <c r="C82" s="43" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="D82" s="43" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E82" s="43"/>
@@ -10175,16 +10152,16 @@
       <c r="N82" s="16"/>
     </row>
     <row r="83" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="61"/>
+      <c r="A83" s="63"/>
       <c r="B83" s="42">
         <v>10</v>
       </c>
       <c r="C83" s="43" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="D83" s="43" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E83" s="43"/>
@@ -10199,16 +10176,16 @@
       <c r="N83" s="16"/>
     </row>
     <row r="84" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="61"/>
+      <c r="A84" s="63"/>
       <c r="B84" s="42">
         <v>12</v>
       </c>
       <c r="C84" s="43" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="D84" s="43" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E84" s="31"/>
@@ -10223,16 +10200,16 @@
       <c r="N84" s="31"/>
     </row>
     <row r="85" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="61"/>
+      <c r="A85" s="63"/>
       <c r="B85" s="42">
         <v>16</v>
       </c>
       <c r="C85" s="43" t="e">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
       <c r="D85" s="43" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E85" s="31"/>
@@ -10247,22 +10224,22 @@
       <c r="N85" s="31"/>
     </row>
     <row r="86" spans="1:14" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="62"/>
+      <c r="A86" s="64"/>
       <c r="B86" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="C86" s="63"/>
-      <c r="D86" s="63"/>
-      <c r="E86" s="63"/>
-      <c r="F86" s="63"/>
-      <c r="G86" s="63"/>
-      <c r="H86" s="63"/>
-      <c r="I86" s="63"/>
-      <c r="J86" s="63"/>
-      <c r="K86" s="63"/>
-      <c r="L86" s="63"/>
-      <c r="M86" s="63"/>
-      <c r="N86" s="63"/>
+      <c r="C86" s="61"/>
+      <c r="D86" s="61"/>
+      <c r="E86" s="61"/>
+      <c r="F86" s="61"/>
+      <c r="G86" s="61"/>
+      <c r="H86" s="61"/>
+      <c r="I86" s="61"/>
+      <c r="J86" s="61"/>
+      <c r="K86" s="61"/>
+      <c r="L86" s="61"/>
+      <c r="M86" s="61"/>
+      <c r="N86" s="61"/>
     </row>
   </sheetData>
   <mergeCells count="21">
@@ -10301,15 +10278,35 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4269BDC4-CFAE-4A4A-95F0-395DE59C8746}">
-  <dimension ref="M10"/>
+  <dimension ref="M10:M14"/>
   <sheetFormatPr defaultRowHeight="22.1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="16384" width="9.140625" style="41"/>
   </cols>
   <sheetData>
     <row r="10" spans="13:13" x14ac:dyDescent="0.3">
-      <c r="M10" s="41" t="s">
+      <c r="M10" s="46" t="s">
         <v>93</v>
+      </c>
+    </row>
+    <row r="11" spans="13:13" x14ac:dyDescent="0.3">
+      <c r="M11" s="41" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="12" spans="13:13" x14ac:dyDescent="0.3">
+      <c r="M12" s="41" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="13:13" x14ac:dyDescent="0.3">
+      <c r="M13" s="41" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="14" spans="13:13" x14ac:dyDescent="0.3">
+      <c r="M14" s="41" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/DecompositionLU/docs/statistics.xlsx
+++ b/DecompositionLU/docs/statistics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maxim\source\repos\practice\SECOND_COURSE\FOR_ITLAB\ArchBenchs\DecompositionLU\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41C1BB95-E955-4778-A974-4BFE16B50F67}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{889A587D-CBA0-45E5-847D-B55C9EF9927A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-114" yWindow="-114" windowWidth="27602" windowHeight="15027" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -975,13 +975,40 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -992,24 +1019,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1029,31 +1038,22 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -35204,16 +35204,16 @@
         <v>6</v>
       </c>
       <c r="B78" s="48">
+        <v>3000</v>
+      </c>
+      <c r="C78" s="8">
         <v>5000</v>
       </c>
-      <c r="C78" s="8">
+      <c r="D78" s="8">
+        <v>7000</v>
+      </c>
+      <c r="E78" s="8">
         <v>10000</v>
-      </c>
-      <c r="D78" s="8">
-        <v>15000</v>
-      </c>
-      <c r="E78" s="8">
-        <v>20000</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -35245,18 +35245,11 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="A57:C57"/>
-    <mergeCell ref="D57:E57"/>
-    <mergeCell ref="B58:E58"/>
-    <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A64:E64"/>
-    <mergeCell ref="B45:E45"/>
-    <mergeCell ref="A47:E47"/>
-    <mergeCell ref="A51:E51"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A70:C70"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="B71:E71"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A77:E77"/>
     <mergeCell ref="H24:I24"/>
     <mergeCell ref="G5:H8"/>
     <mergeCell ref="B42:E42"/>
@@ -35272,11 +35265,18 @@
     <mergeCell ref="B19:E19"/>
     <mergeCell ref="A21:E21"/>
     <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A70:C70"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="B71:E71"/>
-    <mergeCell ref="A72:E72"/>
-    <mergeCell ref="A77:E77"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="D57:E57"/>
+    <mergeCell ref="B58:E58"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A64:E64"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <hyperlinks>
@@ -35339,14 +35339,14 @@
       <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="76" t="s">
+      <c r="A2" s="79" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="65" t="s">
+      <c r="B2" s="74" t="s">
         <v>78</v>
       </c>
-      <c r="C2" s="66"/>
-      <c r="D2" s="67"/>
+      <c r="C2" s="75"/>
+      <c r="D2" s="76"/>
       <c r="E2" s="31"/>
       <c r="F2" s="31"/>
       <c r="G2" s="31"/>
@@ -35371,7 +35371,7 @@
       <c r="Z2" s="30"/>
     </row>
     <row r="3" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="76"/>
+      <c r="A3" s="79"/>
       <c r="B3" s="29" t="s">
         <v>77</v>
       </c>
@@ -35405,7 +35405,7 @@
       <c r="Z3" s="30"/>
     </row>
     <row r="4" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="76"/>
+      <c r="A4" s="79"/>
       <c r="B4" s="15">
         <v>1</v>
       </c>
@@ -35439,7 +35439,7 @@
       <c r="Z4" s="30"/>
     </row>
     <row r="5" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="76"/>
+      <c r="A5" s="79"/>
       <c r="B5" s="15">
         <v>2</v>
       </c>
@@ -35473,7 +35473,7 @@
       <c r="Z5" s="30"/>
     </row>
     <row r="6" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="76"/>
+      <c r="A6" s="79"/>
       <c r="B6" s="15">
         <v>4</v>
       </c>
@@ -35496,7 +35496,7 @@
       <c r="O6" s="38"/>
     </row>
     <row r="7" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="76"/>
+      <c r="A7" s="79"/>
       <c r="B7" s="15">
         <v>6</v>
       </c>
@@ -35519,7 +35519,7 @@
       <c r="O7" s="38"/>
     </row>
     <row r="8" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="76"/>
+      <c r="A8" s="79"/>
       <c r="B8" s="15">
         <v>8</v>
       </c>
@@ -35542,7 +35542,7 @@
       <c r="O8" s="38"/>
     </row>
     <row r="9" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="76"/>
+      <c r="A9" s="79"/>
       <c r="B9" s="15">
         <v>10</v>
       </c>
@@ -35565,7 +35565,7 @@
       <c r="O9" s="38"/>
     </row>
     <row r="10" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="76"/>
+      <c r="A10" s="79"/>
       <c r="B10" s="15">
         <v>12</v>
       </c>
@@ -35588,7 +35588,7 @@
       <c r="O10" s="38"/>
     </row>
     <row r="11" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="76"/>
+      <c r="A11" s="79"/>
       <c r="B11" s="15">
         <v>16</v>
       </c>
@@ -35613,37 +35613,37 @@
       <c r="Q11" s="27"/>
     </row>
     <row r="12" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="76"/>
+      <c r="A12" s="79"/>
       <c r="B12" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="C12" s="74" t="s">
+      <c r="C12" s="77" t="s">
         <v>81</v>
       </c>
-      <c r="D12" s="74"/>
-      <c r="E12" s="74"/>
-      <c r="F12" s="74"/>
-      <c r="G12" s="74"/>
-      <c r="H12" s="74"/>
-      <c r="I12" s="74"/>
-      <c r="J12" s="74"/>
-      <c r="K12" s="74"/>
-      <c r="L12" s="74"/>
-      <c r="M12" s="74"/>
-      <c r="N12" s="75"/>
+      <c r="D12" s="77"/>
+      <c r="E12" s="77"/>
+      <c r="F12" s="77"/>
+      <c r="G12" s="77"/>
+      <c r="H12" s="77"/>
+      <c r="I12" s="77"/>
+      <c r="J12" s="77"/>
+      <c r="K12" s="77"/>
+      <c r="L12" s="77"/>
+      <c r="M12" s="77"/>
+      <c r="N12" s="78"/>
       <c r="O12" s="39"/>
       <c r="P12" s="23"/>
       <c r="Q12" s="23"/>
     </row>
     <row r="13" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="76" t="s">
+      <c r="A13" s="79" t="s">
         <v>87</v>
       </c>
-      <c r="B13" s="65" t="s">
+      <c r="B13" s="74" t="s">
         <v>78</v>
       </c>
-      <c r="C13" s="66"/>
-      <c r="D13" s="67"/>
+      <c r="C13" s="75"/>
+      <c r="D13" s="76"/>
       <c r="E13" s="32"/>
       <c r="F13" s="31"/>
       <c r="G13" s="31"/>
@@ -35659,7 +35659,7 @@
       <c r="Q13" s="23"/>
     </row>
     <row r="14" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="76"/>
+      <c r="A14" s="79"/>
       <c r="B14" s="13" t="s">
         <v>77</v>
       </c>
@@ -35684,7 +35684,7 @@
       <c r="Q14" s="23"/>
     </row>
     <row r="15" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="76"/>
+      <c r="A15" s="79"/>
       <c r="B15" s="15">
         <v>1</v>
       </c>
@@ -35709,7 +35709,7 @@
       <c r="Q15" s="27"/>
     </row>
     <row r="16" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="76"/>
+      <c r="A16" s="79"/>
       <c r="B16" s="15">
         <v>2</v>
       </c>
@@ -35734,7 +35734,7 @@
       <c r="Q16" s="23"/>
     </row>
     <row r="17" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="76"/>
+      <c r="A17" s="79"/>
       <c r="B17" s="15">
         <v>4</v>
       </c>
@@ -35759,7 +35759,7 @@
       <c r="Q17" s="23"/>
     </row>
     <row r="18" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="76"/>
+      <c r="A18" s="79"/>
       <c r="B18" s="15">
         <v>6</v>
       </c>
@@ -35784,7 +35784,7 @@
       <c r="Q18" s="23"/>
     </row>
     <row r="19" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="76"/>
+      <c r="A19" s="79"/>
       <c r="B19" s="15">
         <v>8</v>
       </c>
@@ -35807,7 +35807,7 @@
       <c r="O19" s="38"/>
     </row>
     <row r="20" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="76"/>
+      <c r="A20" s="79"/>
       <c r="B20" s="15">
         <v>10</v>
       </c>
@@ -35830,7 +35830,7 @@
       <c r="O20" s="38"/>
     </row>
     <row r="21" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="76"/>
+      <c r="A21" s="79"/>
       <c r="B21" s="15">
         <v>12</v>
       </c>
@@ -35853,41 +35853,41 @@
       <c r="O21" s="38"/>
     </row>
     <row r="22" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="76"/>
-      <c r="B22" s="77" t="s">
+      <c r="A22" s="79"/>
+      <c r="B22" s="80" t="s">
         <v>86</v>
       </c>
-      <c r="C22" s="78" t="s">
+      <c r="C22" s="81" t="s">
         <v>88</v>
       </c>
-      <c r="D22" s="78"/>
-      <c r="E22" s="78"/>
-      <c r="F22" s="78"/>
-      <c r="G22" s="78"/>
-      <c r="H22" s="78"/>
-      <c r="I22" s="78"/>
-      <c r="J22" s="78"/>
-      <c r="K22" s="78"/>
-      <c r="L22" s="78"/>
-      <c r="M22" s="78"/>
-      <c r="N22" s="79"/>
+      <c r="D22" s="81"/>
+      <c r="E22" s="81"/>
+      <c r="F22" s="81"/>
+      <c r="G22" s="81"/>
+      <c r="H22" s="81"/>
+      <c r="I22" s="81"/>
+      <c r="J22" s="81"/>
+      <c r="K22" s="81"/>
+      <c r="L22" s="81"/>
+      <c r="M22" s="81"/>
+      <c r="N22" s="82"/>
       <c r="O22" s="38"/>
     </row>
     <row r="23" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="76"/>
-      <c r="B23" s="77"/>
-      <c r="C23" s="78"/>
-      <c r="D23" s="78"/>
-      <c r="E23" s="78"/>
-      <c r="F23" s="78"/>
-      <c r="G23" s="78"/>
-      <c r="H23" s="78"/>
-      <c r="I23" s="78"/>
-      <c r="J23" s="78"/>
-      <c r="K23" s="78"/>
-      <c r="L23" s="78"/>
-      <c r="M23" s="78"/>
-      <c r="N23" s="79"/>
+      <c r="A23" s="79"/>
+      <c r="B23" s="80"/>
+      <c r="C23" s="81"/>
+      <c r="D23" s="81"/>
+      <c r="E23" s="81"/>
+      <c r="F23" s="81"/>
+      <c r="G23" s="81"/>
+      <c r="H23" s="81"/>
+      <c r="I23" s="81"/>
+      <c r="J23" s="81"/>
+      <c r="K23" s="81"/>
+      <c r="L23" s="81"/>
+      <c r="M23" s="81"/>
+      <c r="N23" s="82"/>
       <c r="O23" s="38"/>
     </row>
     <row r="24" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -35912,14 +35912,14 @@
       <c r="O24" s="38"/>
     </row>
     <row r="25" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="71" t="s">
+      <c r="A25" s="65" t="s">
         <v>85</v>
       </c>
-      <c r="B25" s="65" t="s">
+      <c r="B25" s="74" t="s">
         <v>78</v>
       </c>
-      <c r="C25" s="66"/>
-      <c r="D25" s="67"/>
+      <c r="C25" s="75"/>
+      <c r="D25" s="76"/>
       <c r="E25" s="31"/>
       <c r="F25" s="31"/>
       <c r="G25" s="31"/>
@@ -35933,7 +35933,7 @@
       <c r="O25" s="27"/>
     </row>
     <row r="26" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="72"/>
+      <c r="A26" s="66"/>
       <c r="B26" s="42" t="s">
         <v>77</v>
       </c>
@@ -35956,7 +35956,7 @@
       <c r="O26" s="27"/>
     </row>
     <row r="27" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="72"/>
+      <c r="A27" s="66"/>
       <c r="B27" s="15">
         <v>1</v>
       </c>
@@ -35979,7 +35979,7 @@
       <c r="O27" s="27"/>
     </row>
     <row r="28" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="72"/>
+      <c r="A28" s="66"/>
       <c r="B28" s="15">
         <v>2</v>
       </c>
@@ -36002,7 +36002,7 @@
       <c r="O28" s="27"/>
     </row>
     <row r="29" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="72"/>
+      <c r="A29" s="66"/>
       <c r="B29" s="15">
         <v>4</v>
       </c>
@@ -36025,7 +36025,7 @@
       <c r="O29" s="27"/>
     </row>
     <row r="30" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="72"/>
+      <c r="A30" s="66"/>
       <c r="B30" s="15">
         <v>6</v>
       </c>
@@ -36048,7 +36048,7 @@
       <c r="O30" s="27"/>
     </row>
     <row r="31" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="72"/>
+      <c r="A31" s="66"/>
       <c r="B31" s="15">
         <v>8</v>
       </c>
@@ -36071,7 +36071,7 @@
       <c r="O31" s="27"/>
     </row>
     <row r="32" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="72"/>
+      <c r="A32" s="66"/>
       <c r="B32" s="15">
         <v>10</v>
       </c>
@@ -36094,7 +36094,7 @@
       <c r="O32" s="27"/>
     </row>
     <row r="33" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="72"/>
+      <c r="A33" s="66"/>
       <c r="B33" s="15">
         <v>12</v>
       </c>
@@ -36117,7 +36117,7 @@
       <c r="O33" s="27"/>
     </row>
     <row r="34" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="72"/>
+      <c r="A34" s="66"/>
       <c r="B34" s="15">
         <v>16</v>
       </c>
@@ -36140,12 +36140,12 @@
       <c r="O34" s="27"/>
     </row>
     <row r="35" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="72"/>
-      <c r="B35" s="65" t="s">
+      <c r="A35" s="66"/>
+      <c r="B35" s="74" t="s">
         <v>96</v>
       </c>
-      <c r="C35" s="66"/>
-      <c r="D35" s="67"/>
+      <c r="C35" s="75"/>
+      <c r="D35" s="76"/>
       <c r="E35" s="31"/>
       <c r="F35" s="31"/>
       <c r="G35" s="31"/>
@@ -36159,7 +36159,7 @@
       <c r="O35" s="27"/>
     </row>
     <row r="36" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="72"/>
+      <c r="A36" s="66"/>
       <c r="B36" s="42" t="s">
         <v>77</v>
       </c>
@@ -36183,7 +36183,7 @@
       <c r="P36" s="1"/>
     </row>
     <row r="37" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="72"/>
+      <c r="A37" s="66"/>
       <c r="B37" s="42">
         <v>1</v>
       </c>
@@ -36209,7 +36209,7 @@
       <c r="P37" s="1"/>
     </row>
     <row r="38" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="72"/>
+      <c r="A38" s="66"/>
       <c r="B38" s="42">
         <v>2</v>
       </c>
@@ -36235,7 +36235,7 @@
       <c r="P38" s="1"/>
     </row>
     <row r="39" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="72"/>
+      <c r="A39" s="66"/>
       <c r="B39" s="42">
         <v>4</v>
       </c>
@@ -36261,7 +36261,7 @@
       <c r="P39" s="1"/>
     </row>
     <row r="40" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="72"/>
+      <c r="A40" s="66"/>
       <c r="B40" s="42">
         <v>6</v>
       </c>
@@ -36287,7 +36287,7 @@
       <c r="P40" s="1"/>
     </row>
     <row r="41" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="72"/>
+      <c r="A41" s="66"/>
       <c r="B41" s="42">
         <v>8</v>
       </c>
@@ -36313,7 +36313,7 @@
       <c r="P41" s="1"/>
     </row>
     <row r="42" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="72"/>
+      <c r="A42" s="66"/>
       <c r="B42" s="42">
         <v>10</v>
       </c>
@@ -36339,7 +36339,7 @@
       <c r="P42" s="1"/>
     </row>
     <row r="43" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="72"/>
+      <c r="A43" s="66"/>
       <c r="B43" s="42">
         <v>12</v>
       </c>
@@ -36365,7 +36365,7 @@
       <c r="P43" s="1"/>
     </row>
     <row r="44" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="72"/>
+      <c r="A44" s="66"/>
       <c r="B44" s="42">
         <v>16</v>
       </c>
@@ -36391,12 +36391,12 @@
       <c r="P44" s="1"/>
     </row>
     <row r="45" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="72"/>
-      <c r="B45" s="65" t="s">
+      <c r="A45" s="66"/>
+      <c r="B45" s="74" t="s">
         <v>97</v>
       </c>
-      <c r="C45" s="66"/>
-      <c r="D45" s="67"/>
+      <c r="C45" s="75"/>
+      <c r="D45" s="76"/>
       <c r="E45" s="43"/>
       <c r="F45" s="43"/>
       <c r="G45" s="43"/>
@@ -36411,7 +36411,7 @@
       <c r="P45" s="1"/>
     </row>
     <row r="46" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="72"/>
+      <c r="A46" s="66"/>
       <c r="B46" s="42" t="s">
         <v>77</v>
       </c>
@@ -36435,7 +36435,7 @@
       <c r="P46" s="1"/>
     </row>
     <row r="47" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="72"/>
+      <c r="A47" s="66"/>
       <c r="B47" s="42">
         <v>1</v>
       </c>
@@ -36461,7 +36461,7 @@
       <c r="P47" s="1"/>
     </row>
     <row r="48" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="72"/>
+      <c r="A48" s="66"/>
       <c r="B48" s="42">
         <v>2</v>
       </c>
@@ -36487,7 +36487,7 @@
       <c r="P48" s="1"/>
     </row>
     <row r="49" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="72"/>
+      <c r="A49" s="66"/>
       <c r="B49" s="42">
         <v>4</v>
       </c>
@@ -36513,7 +36513,7 @@
       <c r="P49" s="1"/>
     </row>
     <row r="50" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="72"/>
+      <c r="A50" s="66"/>
       <c r="B50" s="42">
         <v>6</v>
       </c>
@@ -36539,7 +36539,7 @@
       <c r="P50" s="1"/>
     </row>
     <row r="51" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="72"/>
+      <c r="A51" s="66"/>
       <c r="B51" s="42">
         <v>8</v>
       </c>
@@ -36564,7 +36564,7 @@
       <c r="O51" s="1"/>
     </row>
     <row r="52" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="72"/>
+      <c r="A52" s="66"/>
       <c r="B52" s="42">
         <v>10</v>
       </c>
@@ -36589,7 +36589,7 @@
       <c r="O52" s="1"/>
     </row>
     <row r="53" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="72"/>
+      <c r="A53" s="66"/>
       <c r="B53" s="42">
         <v>12</v>
       </c>
@@ -36614,7 +36614,7 @@
       <c r="O53" s="1"/>
     </row>
     <row r="54" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="72"/>
+      <c r="A54" s="66"/>
       <c r="B54" s="42">
         <v>16</v>
       </c>
@@ -36639,40 +36639,40 @@
       <c r="O54" s="1"/>
     </row>
     <row r="55" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="72"/>
+      <c r="A55" s="66"/>
       <c r="B55" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="C55" s="82" t="s">
+      <c r="C55" s="70" t="s">
         <v>102</v>
       </c>
-      <c r="D55" s="82"/>
-      <c r="E55" s="82"/>
-      <c r="F55" s="82"/>
-      <c r="G55" s="82"/>
-      <c r="H55" s="82"/>
-      <c r="I55" s="82"/>
-      <c r="J55" s="82"/>
-      <c r="K55" s="82"/>
-      <c r="L55" s="82"/>
-      <c r="M55" s="82"/>
-      <c r="N55" s="82"/>
+      <c r="D55" s="70"/>
+      <c r="E55" s="70"/>
+      <c r="F55" s="70"/>
+      <c r="G55" s="70"/>
+      <c r="H55" s="70"/>
+      <c r="I55" s="70"/>
+      <c r="J55" s="70"/>
+      <c r="K55" s="70"/>
+      <c r="L55" s="70"/>
+      <c r="M55" s="70"/>
+      <c r="N55" s="70"/>
     </row>
     <row r="56" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="68" t="s">
+      <c r="A56" s="71" t="s">
         <v>103</v>
       </c>
-      <c r="B56" s="69"/>
-      <c r="C56" s="69"/>
-      <c r="D56" s="69"/>
-      <c r="E56" s="69"/>
-      <c r="F56" s="69"/>
-      <c r="G56" s="69"/>
-      <c r="H56" s="69"/>
-      <c r="I56" s="69"/>
-      <c r="J56" s="69"/>
-      <c r="K56" s="69"/>
-      <c r="L56" s="70"/>
+      <c r="B56" s="72"/>
+      <c r="C56" s="72"/>
+      <c r="D56" s="72"/>
+      <c r="E56" s="72"/>
+      <c r="F56" s="72"/>
+      <c r="G56" s="72"/>
+      <c r="H56" s="72"/>
+      <c r="I56" s="72"/>
+      <c r="J56" s="72"/>
+      <c r="K56" s="72"/>
+      <c r="L56" s="73"/>
       <c r="M56" s="52" t="s">
         <v>90</v>
       </c>
@@ -36680,14 +36680,14 @@
       <c r="O56" s="30"/>
     </row>
     <row r="57" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="71" t="s">
+      <c r="A57" s="65" t="s">
         <v>85</v>
       </c>
-      <c r="B57" s="65" t="s">
+      <c r="B57" s="74" t="s">
         <v>78</v>
       </c>
-      <c r="C57" s="66"/>
-      <c r="D57" s="67"/>
+      <c r="C57" s="75"/>
+      <c r="D57" s="76"/>
       <c r="E57" s="31"/>
       <c r="F57" s="31"/>
       <c r="G57" s="31"/>
@@ -36701,7 +36701,7 @@
       <c r="O57" s="30"/>
     </row>
     <row r="58" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="72"/>
+      <c r="A58" s="66"/>
       <c r="B58" s="42" t="s">
         <v>77</v>
       </c>
@@ -36724,7 +36724,7 @@
       <c r="O58" s="30"/>
     </row>
     <row r="59" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="72"/>
+      <c r="A59" s="66"/>
       <c r="B59" s="15">
         <v>1</v>
       </c>
@@ -36747,7 +36747,7 @@
       <c r="O59" s="30"/>
     </row>
     <row r="60" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="72"/>
+      <c r="A60" s="66"/>
       <c r="B60" s="15">
         <v>2</v>
       </c>
@@ -36770,7 +36770,7 @@
       <c r="O60" s="30"/>
     </row>
     <row r="61" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="72"/>
+      <c r="A61" s="66"/>
       <c r="B61" s="15">
         <v>4</v>
       </c>
@@ -36793,7 +36793,7 @@
       <c r="O61" s="30"/>
     </row>
     <row r="62" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="72"/>
+      <c r="A62" s="66"/>
       <c r="B62" s="15">
         <v>6</v>
       </c>
@@ -36816,7 +36816,7 @@
       <c r="O62" s="30"/>
     </row>
     <row r="63" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="72"/>
+      <c r="A63" s="66"/>
       <c r="B63" s="15">
         <v>8</v>
       </c>
@@ -36839,7 +36839,7 @@
       <c r="O63" s="30"/>
     </row>
     <row r="64" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="72"/>
+      <c r="A64" s="66"/>
       <c r="B64" s="15">
         <v>10</v>
       </c>
@@ -36862,7 +36862,7 @@
       <c r="O64" s="30"/>
     </row>
     <row r="65" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="72"/>
+      <c r="A65" s="66"/>
       <c r="B65" s="15">
         <v>12</v>
       </c>
@@ -36885,7 +36885,7 @@
       <c r="O65" s="30"/>
     </row>
     <row r="66" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="72"/>
+      <c r="A66" s="66"/>
       <c r="B66" s="15">
         <v>16</v>
       </c>
@@ -36908,12 +36908,12 @@
       <c r="O66" s="30"/>
     </row>
     <row r="67" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="72"/>
-      <c r="B67" s="65" t="s">
+      <c r="A67" s="66"/>
+      <c r="B67" s="74" t="s">
         <v>96</v>
       </c>
-      <c r="C67" s="66"/>
-      <c r="D67" s="67"/>
+      <c r="C67" s="75"/>
+      <c r="D67" s="76"/>
       <c r="E67" s="31"/>
       <c r="F67" s="31"/>
       <c r="G67" s="31"/>
@@ -36927,7 +36927,7 @@
       <c r="O67" s="30"/>
     </row>
     <row r="68" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="72"/>
+      <c r="A68" s="66"/>
       <c r="B68" s="42" t="s">
         <v>77</v>
       </c>
@@ -36950,7 +36950,7 @@
       <c r="O68" s="30"/>
     </row>
     <row r="69" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="72"/>
+      <c r="A69" s="66"/>
       <c r="B69" s="42">
         <v>1</v>
       </c>
@@ -36975,7 +36975,7 @@
       <c r="O69" s="30"/>
     </row>
     <row r="70" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="72"/>
+      <c r="A70" s="66"/>
       <c r="B70" s="42">
         <v>2</v>
       </c>
@@ -37000,7 +37000,7 @@
       <c r="O70" s="30"/>
     </row>
     <row r="71" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="72"/>
+      <c r="A71" s="66"/>
       <c r="B71" s="42">
         <v>4</v>
       </c>
@@ -37025,7 +37025,7 @@
       <c r="O71" s="30"/>
     </row>
     <row r="72" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="72"/>
+      <c r="A72" s="66"/>
       <c r="B72" s="42">
         <v>6</v>
       </c>
@@ -37050,7 +37050,7 @@
       <c r="O72" s="30"/>
     </row>
     <row r="73" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="72"/>
+      <c r="A73" s="66"/>
       <c r="B73" s="42">
         <v>8</v>
       </c>
@@ -37075,7 +37075,7 @@
       <c r="O73" s="30"/>
     </row>
     <row r="74" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="72"/>
+      <c r="A74" s="66"/>
       <c r="B74" s="42">
         <v>10</v>
       </c>
@@ -37100,7 +37100,7 @@
       <c r="O74" s="30"/>
     </row>
     <row r="75" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="72"/>
+      <c r="A75" s="66"/>
       <c r="B75" s="42">
         <v>12</v>
       </c>
@@ -37125,7 +37125,7 @@
       <c r="O75" s="30"/>
     </row>
     <row r="76" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="72"/>
+      <c r="A76" s="66"/>
       <c r="B76" s="42">
         <v>16</v>
       </c>
@@ -37150,12 +37150,12 @@
       <c r="O76" s="30"/>
     </row>
     <row r="77" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="72"/>
-      <c r="B77" s="65" t="s">
+      <c r="A77" s="66"/>
+      <c r="B77" s="74" t="s">
         <v>97</v>
       </c>
-      <c r="C77" s="66"/>
-      <c r="D77" s="67"/>
+      <c r="C77" s="75"/>
+      <c r="D77" s="76"/>
       <c r="E77" s="43"/>
       <c r="F77" s="43"/>
       <c r="G77" s="43"/>
@@ -37169,7 +37169,7 @@
       <c r="O77" s="30"/>
     </row>
     <row r="78" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="72"/>
+      <c r="A78" s="66"/>
       <c r="B78" s="42" t="s">
         <v>77</v>
       </c>
@@ -37192,7 +37192,7 @@
       <c r="O78" s="30"/>
     </row>
     <row r="79" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="72"/>
+      <c r="A79" s="66"/>
       <c r="B79" s="42">
         <v>1</v>
       </c>
@@ -37217,7 +37217,7 @@
       <c r="O79" s="30"/>
     </row>
     <row r="80" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="72"/>
+      <c r="A80" s="66"/>
       <c r="B80" s="42">
         <v>2</v>
       </c>
@@ -37242,7 +37242,7 @@
       <c r="O80" s="30"/>
     </row>
     <row r="81" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="72"/>
+      <c r="A81" s="66"/>
       <c r="B81" s="42">
         <v>4</v>
       </c>
@@ -37267,7 +37267,7 @@
       <c r="O81" s="30"/>
     </row>
     <row r="82" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="72"/>
+      <c r="A82" s="66"/>
       <c r="B82" s="42">
         <v>6</v>
       </c>
@@ -37292,7 +37292,7 @@
       <c r="O82" s="30"/>
     </row>
     <row r="83" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="72"/>
+      <c r="A83" s="66"/>
       <c r="B83" s="42">
         <v>8</v>
       </c>
@@ -37317,7 +37317,7 @@
       <c r="O83" s="30"/>
     </row>
     <row r="84" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="72"/>
+      <c r="A84" s="66"/>
       <c r="B84" s="42">
         <v>10</v>
       </c>
@@ -37342,7 +37342,7 @@
       <c r="O84" s="30"/>
     </row>
     <row r="85" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="72"/>
+      <c r="A85" s="66"/>
       <c r="B85" s="42">
         <v>12</v>
       </c>
@@ -37367,7 +37367,7 @@
       <c r="O85" s="30"/>
     </row>
     <row r="86" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="72"/>
+      <c r="A86" s="66"/>
       <c r="B86" s="42">
         <v>16</v>
       </c>
@@ -37392,24 +37392,24 @@
       <c r="O86" s="30"/>
     </row>
     <row r="87" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="72"/>
+      <c r="A87" s="66"/>
       <c r="B87" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="C87" s="83" t="s">
+      <c r="C87" s="67" t="s">
         <v>106</v>
       </c>
-      <c r="D87" s="84"/>
-      <c r="E87" s="84"/>
-      <c r="F87" s="84"/>
-      <c r="G87" s="84"/>
-      <c r="H87" s="84"/>
-      <c r="I87" s="84"/>
-      <c r="J87" s="84"/>
-      <c r="K87" s="84"/>
-      <c r="L87" s="84"/>
-      <c r="M87" s="84"/>
-      <c r="N87" s="85"/>
+      <c r="D87" s="68"/>
+      <c r="E87" s="68"/>
+      <c r="F87" s="68"/>
+      <c r="G87" s="68"/>
+      <c r="H87" s="68"/>
+      <c r="I87" s="68"/>
+      <c r="J87" s="68"/>
+      <c r="K87" s="68"/>
+      <c r="L87" s="68"/>
+      <c r="M87" s="68"/>
+      <c r="N87" s="69"/>
     </row>
     <row r="88" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="49" t="s">
@@ -37428,25 +37428,25 @@
       <c r="L88" s="50"/>
       <c r="M88" s="50"/>
       <c r="N88" s="50"/>
-      <c r="O88" s="86" t="s">
+      <c r="O88" s="62" t="s">
         <v>113</v>
       </c>
-      <c r="P88" s="87"/>
-      <c r="Q88" s="87"/>
-      <c r="R88" s="87"/>
-      <c r="S88" s="87"/>
-      <c r="T88" s="88"/>
+      <c r="P88" s="63"/>
+      <c r="Q88" s="63"/>
+      <c r="R88" s="63"/>
+      <c r="S88" s="63"/>
+      <c r="T88" s="64"/>
     </row>
     <row r="89" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="76" t="s">
+      <c r="A89" s="79" t="s">
         <v>85</v>
       </c>
-      <c r="B89" s="65" t="s">
+      <c r="B89" s="74" t="s">
         <v>78</v>
       </c>
-      <c r="C89" s="66"/>
-      <c r="D89" s="66"/>
-      <c r="E89" s="67"/>
+      <c r="C89" s="75"/>
+      <c r="D89" s="75"/>
+      <c r="E89" s="76"/>
       <c r="F89" s="31"/>
       <c r="G89" s="31"/>
       <c r="H89" s="31"/>
@@ -37464,7 +37464,7 @@
       <c r="T89" s="31"/>
     </row>
     <row r="90" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="76"/>
+      <c r="A90" s="79"/>
       <c r="B90" s="42" t="s">
         <v>77</v>
       </c>
@@ -37494,7 +37494,7 @@
       <c r="T90" s="31"/>
     </row>
     <row r="91" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="76"/>
+      <c r="A91" s="79"/>
       <c r="B91" s="15">
         <v>1</v>
       </c>
@@ -37524,7 +37524,7 @@
       <c r="T91" s="31"/>
     </row>
     <row r="92" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="76"/>
+      <c r="A92" s="79"/>
       <c r="B92" s="15">
         <v>2</v>
       </c>
@@ -37554,7 +37554,7 @@
       <c r="T92" s="31"/>
     </row>
     <row r="93" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="76"/>
+      <c r="A93" s="79"/>
       <c r="B93" s="15">
         <v>4</v>
       </c>
@@ -37584,7 +37584,7 @@
       <c r="T93" s="31"/>
     </row>
     <row r="94" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="76"/>
+      <c r="A94" s="79"/>
       <c r="B94" s="15">
         <v>6</v>
       </c>
@@ -37614,7 +37614,7 @@
       <c r="T94" s="31"/>
     </row>
     <row r="95" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="76"/>
+      <c r="A95" s="79"/>
       <c r="B95" s="15">
         <v>8</v>
       </c>
@@ -37644,7 +37644,7 @@
       <c r="T95" s="31"/>
     </row>
     <row r="96" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="76"/>
+      <c r="A96" s="79"/>
       <c r="B96" s="15">
         <v>10</v>
       </c>
@@ -37674,7 +37674,7 @@
       <c r="T96" s="31"/>
     </row>
     <row r="97" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="76"/>
+      <c r="A97" s="79"/>
       <c r="B97" s="15">
         <v>12</v>
       </c>
@@ -37704,7 +37704,7 @@
       <c r="T97" s="31"/>
     </row>
     <row r="98" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="76"/>
+      <c r="A98" s="79"/>
       <c r="B98" s="15">
         <v>16</v>
       </c>
@@ -37734,13 +37734,13 @@
       <c r="T98" s="31"/>
     </row>
     <row r="99" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="76"/>
-      <c r="B99" s="65" t="s">
+      <c r="A99" s="79"/>
+      <c r="B99" s="74" t="s">
         <v>96</v>
       </c>
-      <c r="C99" s="66"/>
-      <c r="D99" s="66"/>
-      <c r="E99" s="67"/>
+      <c r="C99" s="75"/>
+      <c r="D99" s="75"/>
+      <c r="E99" s="76"/>
       <c r="F99" s="31"/>
       <c r="G99" s="31"/>
       <c r="H99" s="31"/>
@@ -37758,7 +37758,7 @@
       <c r="T99" s="31"/>
     </row>
     <row r="100" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="76"/>
+      <c r="A100" s="79"/>
       <c r="B100" s="42" t="s">
         <v>77</v>
       </c>
@@ -37788,7 +37788,7 @@
       <c r="T100" s="16"/>
     </row>
     <row r="101" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="76"/>
+      <c r="A101" s="79"/>
       <c r="B101" s="42">
         <v>1</v>
       </c>
@@ -37821,7 +37821,7 @@
       <c r="T101" s="16"/>
     </row>
     <row r="102" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="76"/>
+      <c r="A102" s="79"/>
       <c r="B102" s="42">
         <v>2</v>
       </c>
@@ -37854,7 +37854,7 @@
       <c r="T102" s="16"/>
     </row>
     <row r="103" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="76"/>
+      <c r="A103" s="79"/>
       <c r="B103" s="42">
         <v>4</v>
       </c>
@@ -37887,7 +37887,7 @@
       <c r="T103" s="16"/>
     </row>
     <row r="104" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="76"/>
+      <c r="A104" s="79"/>
       <c r="B104" s="42">
         <v>6</v>
       </c>
@@ -37920,7 +37920,7 @@
       <c r="T104" s="16"/>
     </row>
     <row r="105" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="76"/>
+      <c r="A105" s="79"/>
       <c r="B105" s="42">
         <v>8</v>
       </c>
@@ -37953,7 +37953,7 @@
       <c r="T105" s="16"/>
     </row>
     <row r="106" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="76"/>
+      <c r="A106" s="79"/>
       <c r="B106" s="42">
         <v>10</v>
       </c>
@@ -37986,7 +37986,7 @@
       <c r="T106" s="16"/>
     </row>
     <row r="107" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="76"/>
+      <c r="A107" s="79"/>
       <c r="B107" s="42">
         <v>12</v>
       </c>
@@ -38019,7 +38019,7 @@
       <c r="T107" s="16"/>
     </row>
     <row r="108" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="76"/>
+      <c r="A108" s="79"/>
       <c r="B108" s="42">
         <v>16</v>
       </c>
@@ -38052,13 +38052,13 @@
       <c r="T108" s="16"/>
     </row>
     <row r="109" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="76"/>
-      <c r="B109" s="65" t="s">
+      <c r="A109" s="79"/>
+      <c r="B109" s="74" t="s">
         <v>97</v>
       </c>
-      <c r="C109" s="66"/>
-      <c r="D109" s="66"/>
-      <c r="E109" s="67"/>
+      <c r="C109" s="75"/>
+      <c r="D109" s="75"/>
+      <c r="E109" s="76"/>
       <c r="F109" s="43"/>
       <c r="G109" s="16"/>
       <c r="H109" s="16"/>
@@ -38076,7 +38076,7 @@
       <c r="T109" s="16"/>
     </row>
     <row r="110" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="76"/>
+      <c r="A110" s="79"/>
       <c r="B110" s="42" t="s">
         <v>77</v>
       </c>
@@ -38106,20 +38106,20 @@
       <c r="T110" s="16"/>
     </row>
     <row r="111" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="76"/>
+      <c r="A111" s="79"/>
       <c r="B111" s="42">
         <v>1</v>
       </c>
       <c r="C111" s="40">
-        <f>ROUND(C101/$B101,5)</f>
+        <f t="shared" ref="C111:C118" si="4">ROUND(C101/$B101,5)</f>
         <v>1</v>
       </c>
       <c r="D111" s="40">
-        <f>ROUND(D101/B101,5)</f>
+        <f t="shared" ref="D111:D118" si="5">ROUND(D101/B101,5)</f>
         <v>1</v>
       </c>
       <c r="E111" s="40">
-        <f>ROUND(E101/$B101,5)</f>
+        <f t="shared" ref="E111:E118" si="6">ROUND(E101/$B101,5)</f>
         <v>1</v>
       </c>
       <c r="F111" s="43"/>
@@ -38139,20 +38139,20 @@
       <c r="T111" s="16"/>
     </row>
     <row r="112" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="76"/>
+      <c r="A112" s="79"/>
       <c r="B112" s="42">
         <v>2</v>
       </c>
       <c r="C112" s="40">
-        <f>ROUND(C102/$B102,5)</f>
+        <f t="shared" si="4"/>
         <v>0.84987999999999997</v>
       </c>
       <c r="D112" s="40">
-        <f>ROUND(D102/B102,5)</f>
+        <f t="shared" si="5"/>
         <v>0.92278000000000004</v>
       </c>
       <c r="E112" s="40">
-        <f>ROUND(E102/$B102,5)</f>
+        <f t="shared" si="6"/>
         <v>0.95840999999999998</v>
       </c>
       <c r="F112" s="43"/>
@@ -38172,20 +38172,20 @@
       <c r="T112" s="16"/>
     </row>
     <row r="113" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="76"/>
+      <c r="A113" s="79"/>
       <c r="B113" s="42">
         <v>4</v>
       </c>
       <c r="C113" s="40">
-        <f>ROUND(C103/$B103,5)</f>
+        <f t="shared" si="4"/>
         <v>0.61082000000000003</v>
       </c>
       <c r="D113" s="40">
-        <f>ROUND(D103/B103,5)</f>
+        <f t="shared" si="5"/>
         <v>0.90251000000000003</v>
       </c>
       <c r="E113" s="40">
-        <f>ROUND(E103/$B103,5)</f>
+        <f t="shared" si="6"/>
         <v>0.76773999999999998</v>
       </c>
       <c r="F113" s="43"/>
@@ -38205,20 +38205,20 @@
       <c r="T113" s="16"/>
     </row>
     <row r="114" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="76"/>
+      <c r="A114" s="79"/>
       <c r="B114" s="42">
         <v>6</v>
       </c>
       <c r="C114" s="40">
-        <f>ROUND(C104/$B104,5)</f>
+        <f t="shared" si="4"/>
         <v>0.53564000000000001</v>
       </c>
       <c r="D114" s="40">
-        <f>ROUND(D104/B104,5)</f>
+        <f t="shared" si="5"/>
         <v>0.67223999999999995</v>
       </c>
       <c r="E114" s="40">
-        <f>ROUND(E104/$B104,5)</f>
+        <f t="shared" si="6"/>
         <v>0.70923000000000003</v>
       </c>
       <c r="F114" s="43"/>
@@ -38238,20 +38238,20 @@
       <c r="T114" s="16"/>
     </row>
     <row r="115" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="76"/>
+      <c r="A115" s="79"/>
       <c r="B115" s="42">
         <v>8</v>
       </c>
       <c r="C115" s="40">
-        <f>ROUND(C105/$B105,5)</f>
+        <f t="shared" si="4"/>
         <v>0.41647000000000001</v>
       </c>
       <c r="D115" s="40">
-        <f>ROUND(D105/B105,5)</f>
+        <f t="shared" si="5"/>
         <v>0.55611999999999995</v>
       </c>
       <c r="E115" s="40">
-        <f>ROUND(E105/$B105,5)</f>
+        <f t="shared" si="6"/>
         <v>0.58760999999999997</v>
       </c>
       <c r="F115" s="43"/>
@@ -38271,20 +38271,20 @@
       <c r="T115" s="16"/>
     </row>
     <row r="116" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="76"/>
+      <c r="A116" s="79"/>
       <c r="B116" s="42">
         <v>10</v>
       </c>
       <c r="C116" s="40">
-        <f>ROUND(C106/$B106,5)</f>
+        <f t="shared" si="4"/>
         <v>0.33856999999999998</v>
       </c>
       <c r="D116" s="40">
-        <f>ROUND(D106/B106,5)</f>
+        <f t="shared" si="5"/>
         <v>0.46194000000000002</v>
       </c>
       <c r="E116" s="40">
-        <f>ROUND(E106/$B106,5)</f>
+        <f t="shared" si="6"/>
         <v>0.50873999999999997</v>
       </c>
       <c r="F116" s="43"/>
@@ -38304,20 +38304,20 @@
       <c r="T116" s="16"/>
     </row>
     <row r="117" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="76"/>
+      <c r="A117" s="79"/>
       <c r="B117" s="42">
         <v>12</v>
       </c>
       <c r="C117" s="40">
-        <f>ROUND(C107/$B107,5)</f>
+        <f t="shared" si="4"/>
         <v>0.29110999999999998</v>
       </c>
       <c r="D117" s="40">
-        <f>ROUND(D107/B107,5)</f>
+        <f t="shared" si="5"/>
         <v>0.39256999999999997</v>
       </c>
       <c r="E117" s="40">
-        <f>ROUND(E107/$B107,5)</f>
+        <f t="shared" si="6"/>
         <v>0.44751999999999997</v>
       </c>
       <c r="F117" s="31"/>
@@ -38337,20 +38337,20 @@
       <c r="T117" s="31"/>
     </row>
     <row r="118" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="76"/>
+      <c r="A118" s="79"/>
       <c r="B118" s="42">
         <v>16</v>
       </c>
       <c r="C118" s="40">
-        <f>ROUND(C108/$B108,5)</f>
+        <f t="shared" si="4"/>
         <v>0.21833</v>
       </c>
       <c r="D118" s="40">
-        <f>ROUND(D108/B108,5)</f>
+        <f t="shared" si="5"/>
         <v>0.30623</v>
       </c>
       <c r="E118" s="40">
-        <f>ROUND(E108/$B108,5)</f>
+        <f t="shared" si="6"/>
         <v>0.34717999999999999</v>
       </c>
       <c r="F118" s="31"/>
@@ -38370,41 +38370,41 @@
       <c r="T118" s="31"/>
     </row>
     <row r="119" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="76"/>
+      <c r="A119" s="79"/>
       <c r="B119" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="C119" s="75" t="s">
+      <c r="C119" s="78" t="s">
         <v>114</v>
       </c>
-      <c r="D119" s="80"/>
-      <c r="E119" s="80"/>
-      <c r="F119" s="80"/>
-      <c r="G119" s="80"/>
-      <c r="H119" s="80"/>
-      <c r="I119" s="80"/>
-      <c r="J119" s="80"/>
-      <c r="K119" s="80"/>
-      <c r="L119" s="80"/>
-      <c r="M119" s="80"/>
-      <c r="N119" s="80"/>
-      <c r="O119" s="80"/>
-      <c r="P119" s="80"/>
-      <c r="Q119" s="80"/>
-      <c r="R119" s="80"/>
-      <c r="S119" s="80"/>
-      <c r="T119" s="81"/>
+      <c r="D119" s="84"/>
+      <c r="E119" s="84"/>
+      <c r="F119" s="84"/>
+      <c r="G119" s="84"/>
+      <c r="H119" s="84"/>
+      <c r="I119" s="84"/>
+      <c r="J119" s="84"/>
+      <c r="K119" s="84"/>
+      <c r="L119" s="84"/>
+      <c r="M119" s="84"/>
+      <c r="N119" s="84"/>
+      <c r="O119" s="84"/>
+      <c r="P119" s="84"/>
+      <c r="Q119" s="84"/>
+      <c r="R119" s="84"/>
+      <c r="S119" s="84"/>
+      <c r="T119" s="85"/>
     </row>
     <row r="120" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="71" t="s">
+      <c r="A120" s="65" t="s">
         <v>108</v>
       </c>
-      <c r="B120" s="65" t="s">
+      <c r="B120" s="74" t="s">
         <v>78</v>
       </c>
-      <c r="C120" s="66"/>
-      <c r="D120" s="66"/>
-      <c r="E120" s="67"/>
+      <c r="C120" s="75"/>
+      <c r="D120" s="75"/>
+      <c r="E120" s="76"/>
       <c r="F120" s="31"/>
       <c r="G120" s="31"/>
       <c r="H120" s="31"/>
@@ -38422,7 +38422,7 @@
       <c r="T120" s="31"/>
     </row>
     <row r="121" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="72"/>
+      <c r="A121" s="66"/>
       <c r="B121" s="42" t="s">
         <v>77</v>
       </c>
@@ -38452,7 +38452,7 @@
       <c r="T121" s="31"/>
     </row>
     <row r="122" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="72"/>
+      <c r="A122" s="66"/>
       <c r="B122" s="15">
         <v>1</v>
       </c>
@@ -38476,7 +38476,7 @@
       <c r="T122" s="31"/>
     </row>
     <row r="123" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="72"/>
+      <c r="A123" s="66"/>
       <c r="B123" s="15">
         <v>2</v>
       </c>
@@ -38500,7 +38500,7 @@
       <c r="T123" s="31"/>
     </row>
     <row r="124" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="72"/>
+      <c r="A124" s="66"/>
       <c r="B124" s="15">
         <v>4</v>
       </c>
@@ -38524,7 +38524,7 @@
       <c r="T124" s="31"/>
     </row>
     <row r="125" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="72"/>
+      <c r="A125" s="66"/>
       <c r="B125" s="15">
         <v>6</v>
       </c>
@@ -38548,7 +38548,7 @@
       <c r="T125" s="31"/>
     </row>
     <row r="126" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="72"/>
+      <c r="A126" s="66"/>
       <c r="B126" s="15">
         <v>8</v>
       </c>
@@ -38572,7 +38572,7 @@
       <c r="T126" s="31"/>
     </row>
     <row r="127" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="72"/>
+      <c r="A127" s="66"/>
       <c r="B127" s="15">
         <v>10</v>
       </c>
@@ -38596,7 +38596,7 @@
       <c r="T127" s="31"/>
     </row>
     <row r="128" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="72"/>
+      <c r="A128" s="66"/>
       <c r="B128" s="15">
         <v>12</v>
       </c>
@@ -38620,7 +38620,7 @@
       <c r="T128" s="31"/>
     </row>
     <row r="129" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="72"/>
+      <c r="A129" s="66"/>
       <c r="B129" s="15">
         <v>16</v>
       </c>
@@ -38644,13 +38644,13 @@
       <c r="T129" s="31"/>
     </row>
     <row r="130" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="72"/>
-      <c r="B130" s="65" t="s">
+      <c r="A130" s="66"/>
+      <c r="B130" s="74" t="s">
         <v>96</v>
       </c>
-      <c r="C130" s="66"/>
-      <c r="D130" s="66"/>
-      <c r="E130" s="67"/>
+      <c r="C130" s="75"/>
+      <c r="D130" s="75"/>
+      <c r="E130" s="76"/>
       <c r="F130" s="31"/>
       <c r="G130" s="31"/>
       <c r="H130" s="31"/>
@@ -38668,7 +38668,7 @@
       <c r="T130" s="31"/>
     </row>
     <row r="131" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="72"/>
+      <c r="A131" s="66"/>
       <c r="B131" s="42" t="s">
         <v>77</v>
       </c>
@@ -38698,7 +38698,7 @@
       <c r="T131" s="16"/>
     </row>
     <row r="132" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="72"/>
+      <c r="A132" s="66"/>
       <c r="B132" s="42">
         <v>1</v>
       </c>
@@ -38731,7 +38731,7 @@
       <c r="T132" s="16"/>
     </row>
     <row r="133" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="72"/>
+      <c r="A133" s="66"/>
       <c r="B133" s="42">
         <v>2</v>
       </c>
@@ -38764,7 +38764,7 @@
       <c r="T133" s="16"/>
     </row>
     <row r="134" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="72"/>
+      <c r="A134" s="66"/>
       <c r="B134" s="42">
         <v>4</v>
       </c>
@@ -38797,7 +38797,7 @@
       <c r="T134" s="16"/>
     </row>
     <row r="135" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="72"/>
+      <c r="A135" s="66"/>
       <c r="B135" s="42">
         <v>6</v>
       </c>
@@ -38830,7 +38830,7 @@
       <c r="T135" s="16"/>
     </row>
     <row r="136" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="72"/>
+      <c r="A136" s="66"/>
       <c r="B136" s="42">
         <v>8</v>
       </c>
@@ -38863,7 +38863,7 @@
       <c r="T136" s="16"/>
     </row>
     <row r="137" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="72"/>
+      <c r="A137" s="66"/>
       <c r="B137" s="42">
         <v>10</v>
       </c>
@@ -38896,7 +38896,7 @@
       <c r="T137" s="16"/>
     </row>
     <row r="138" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="72"/>
+      <c r="A138" s="66"/>
       <c r="B138" s="42">
         <v>12</v>
       </c>
@@ -38929,7 +38929,7 @@
       <c r="T138" s="16"/>
     </row>
     <row r="139" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="72"/>
+      <c r="A139" s="66"/>
       <c r="B139" s="42">
         <v>16</v>
       </c>
@@ -38962,13 +38962,13 @@
       <c r="T139" s="16"/>
     </row>
     <row r="140" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="72"/>
-      <c r="B140" s="65" t="s">
+      <c r="A140" s="66"/>
+      <c r="B140" s="74" t="s">
         <v>97</v>
       </c>
-      <c r="C140" s="66"/>
-      <c r="D140" s="66"/>
-      <c r="E140" s="67"/>
+      <c r="C140" s="75"/>
+      <c r="D140" s="75"/>
+      <c r="E140" s="76"/>
       <c r="F140" s="43"/>
       <c r="G140" s="43"/>
       <c r="H140" s="16"/>
@@ -38986,7 +38986,7 @@
       <c r="T140" s="16"/>
     </row>
     <row r="141" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="72"/>
+      <c r="A141" s="66"/>
       <c r="B141" s="42" t="s">
         <v>77</v>
       </c>
@@ -39016,20 +39016,20 @@
       <c r="T141" s="16"/>
     </row>
     <row r="142" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="72"/>
+      <c r="A142" s="66"/>
       <c r="B142" s="42">
         <v>1</v>
       </c>
       <c r="C142" s="40" t="e">
-        <f>C132/B132</f>
+        <f t="shared" ref="C142:C149" si="7">C132/B132</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D142" s="40" t="e">
-        <f>D132/$B132</f>
+        <f t="shared" ref="D142:E149" si="8">D132/$B132</f>
         <v>#DIV/0!</v>
       </c>
       <c r="E142" s="40" t="e">
-        <f>E132/$B132</f>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F142" s="43"/>
@@ -39049,20 +39049,20 @@
       <c r="T142" s="16"/>
     </row>
     <row r="143" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="72"/>
+      <c r="A143" s="66"/>
       <c r="B143" s="42">
         <v>2</v>
       </c>
       <c r="C143" s="40" t="e">
-        <f>C133/B133</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="D143" s="40" t="e">
-        <f>D133/$B133</f>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E143" s="40" t="e">
-        <f>E133/$B133</f>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F143" s="43"/>
@@ -39082,20 +39082,20 @@
       <c r="T143" s="16"/>
     </row>
     <row r="144" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="72"/>
+      <c r="A144" s="66"/>
       <c r="B144" s="42">
         <v>4</v>
       </c>
       <c r="C144" s="40" t="e">
-        <f>C134/B134</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="D144" s="40" t="e">
-        <f>D134/$B134</f>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E144" s="40" t="e">
-        <f>E134/$B134</f>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F144" s="43"/>
@@ -39115,20 +39115,20 @@
       <c r="T144" s="16"/>
     </row>
     <row r="145" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="72"/>
+      <c r="A145" s="66"/>
       <c r="B145" s="42">
         <v>6</v>
       </c>
       <c r="C145" s="40" t="e">
-        <f>C135/B135</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="D145" s="40" t="e">
-        <f>D135/$B135</f>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E145" s="40" t="e">
-        <f>E135/$B135</f>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F145" s="43"/>
@@ -39148,20 +39148,20 @@
       <c r="T145" s="16"/>
     </row>
     <row r="146" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="72"/>
+      <c r="A146" s="66"/>
       <c r="B146" s="42">
         <v>8</v>
       </c>
       <c r="C146" s="40" t="e">
-        <f>C136/B136</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="D146" s="40" t="e">
-        <f>D136/$B136</f>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E146" s="40" t="e">
-        <f>E136/$B136</f>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F146" s="43"/>
@@ -39181,20 +39181,20 @@
       <c r="T146" s="16"/>
     </row>
     <row r="147" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="72"/>
+      <c r="A147" s="66"/>
       <c r="B147" s="42">
         <v>10</v>
       </c>
       <c r="C147" s="40" t="e">
-        <f>C137/B137</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="D147" s="40" t="e">
-        <f>D137/$B137</f>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E147" s="40" t="e">
-        <f>E137/$B137</f>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F147" s="43"/>
@@ -39214,20 +39214,20 @@
       <c r="T147" s="16"/>
     </row>
     <row r="148" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="72"/>
+      <c r="A148" s="66"/>
       <c r="B148" s="42">
         <v>12</v>
       </c>
       <c r="C148" s="40" t="e">
-        <f>C138/B138</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="D148" s="40" t="e">
-        <f>D138/$B138</f>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E148" s="40" t="e">
-        <f>E138/$B138</f>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F148" s="31"/>
@@ -39247,20 +39247,20 @@
       <c r="T148" s="31"/>
     </row>
     <row r="149" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="72"/>
+      <c r="A149" s="66"/>
       <c r="B149" s="42">
         <v>16</v>
       </c>
       <c r="C149" s="40" t="e">
-        <f>C139/B139</f>
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
       <c r="D149" s="40" t="e">
-        <f>D139/$B139</f>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E149" s="40" t="e">
-        <f>E139/$B139</f>
+        <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F149" s="31"/>
@@ -39280,31 +39280,52 @@
       <c r="T149" s="31"/>
     </row>
     <row r="150" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="73"/>
+      <c r="A150" s="83"/>
       <c r="B150" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="C150" s="62"/>
-      <c r="D150" s="63"/>
-      <c r="E150" s="63"/>
-      <c r="F150" s="63"/>
-      <c r="G150" s="63"/>
-      <c r="H150" s="63"/>
-      <c r="I150" s="63"/>
-      <c r="J150" s="63"/>
-      <c r="K150" s="63"/>
-      <c r="L150" s="63"/>
-      <c r="M150" s="63"/>
-      <c r="N150" s="63"/>
-      <c r="O150" s="63"/>
-      <c r="P150" s="63"/>
-      <c r="Q150" s="63"/>
-      <c r="R150" s="63"/>
-      <c r="S150" s="63"/>
-      <c r="T150" s="64"/>
+      <c r="C150" s="86"/>
+      <c r="D150" s="87"/>
+      <c r="E150" s="87"/>
+      <c r="F150" s="87"/>
+      <c r="G150" s="87"/>
+      <c r="H150" s="87"/>
+      <c r="I150" s="87"/>
+      <c r="J150" s="87"/>
+      <c r="K150" s="87"/>
+      <c r="L150" s="87"/>
+      <c r="M150" s="87"/>
+      <c r="N150" s="87"/>
+      <c r="O150" s="87"/>
+      <c r="P150" s="87"/>
+      <c r="Q150" s="87"/>
+      <c r="R150" s="87"/>
+      <c r="S150" s="87"/>
+      <c r="T150" s="88"/>
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="A120:A150"/>
+    <mergeCell ref="A89:A119"/>
+    <mergeCell ref="C119:T119"/>
+    <mergeCell ref="B89:E89"/>
+    <mergeCell ref="B99:E99"/>
+    <mergeCell ref="B109:E109"/>
+    <mergeCell ref="B140:E140"/>
+    <mergeCell ref="B130:E130"/>
+    <mergeCell ref="B120:E120"/>
+    <mergeCell ref="C150:T150"/>
+    <mergeCell ref="A24:L24"/>
+    <mergeCell ref="M24:N24"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="C12:N12"/>
+    <mergeCell ref="A2:A12"/>
+    <mergeCell ref="A13:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:N23"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B2:D2"/>
     <mergeCell ref="O88:T88"/>
     <mergeCell ref="A88:N88"/>
     <mergeCell ref="A57:A87"/>
@@ -39319,27 +39340,6 @@
     <mergeCell ref="B45:D45"/>
     <mergeCell ref="B35:D35"/>
     <mergeCell ref="B25:D25"/>
-    <mergeCell ref="A24:L24"/>
-    <mergeCell ref="M24:N24"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="C12:N12"/>
-    <mergeCell ref="A2:A12"/>
-    <mergeCell ref="A13:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:N23"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="A120:A150"/>
-    <mergeCell ref="A89:A119"/>
-    <mergeCell ref="C119:T119"/>
-    <mergeCell ref="B89:E89"/>
-    <mergeCell ref="B99:E99"/>
-    <mergeCell ref="B109:E109"/>
-    <mergeCell ref="B140:E140"/>
-    <mergeCell ref="B130:E130"/>
-    <mergeCell ref="B120:E120"/>
-    <mergeCell ref="C150:T150"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <hyperlinks>

--- a/DecompositionLU/docs/statistics.xlsx
+++ b/DecompositionLU/docs/statistics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maxim\source\repos\practice\SECOND_COURSE\FOR_ITLAB\ArchBenchs\DecompositionLU\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{889A587D-CBA0-45E5-847D-B55C9EF9927A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44D20E5D-BB34-45CD-A2A5-B3661625034B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-114" yWindow="-114" windowWidth="27602" windowHeight="15027" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="124">
   <si>
     <t>Я не уверен, будет ли это использоваться в готовой презентации и так ли это надо делать, если да, так что пока считаем, что файл для личного пользования.</t>
   </si>
@@ -473,6 +473,33 @@
   <si>
     <t>Мне нравятся результаты, но есть ощущение, что можно лучше. Графики точно не самые хорошие.</t>
   </si>
+  <si>
+    <t>окак</t>
+  </si>
+  <si>
+    <t>Про кластер:</t>
+  </si>
+  <si>
+    <t>[simonov_m@master build]$ lscpu | grep -E "^(CPU\(s\)|Core\(s\) per socket|Socket\(s\)|NUMA)"</t>
+  </si>
+  <si>
+    <t>CPU(s):                8</t>
+  </si>
+  <si>
+    <t>Core(s) per socket:    1</t>
+  </si>
+  <si>
+    <t>Socket(s):             8</t>
+  </si>
+  <si>
+    <t>NUMA node(s):          1</t>
+  </si>
+  <si>
+    <t>NUMA node0 CPU(s):     0-7</t>
+  </si>
+  <si>
+    <t>n = 15000</t>
+  </si>
 </sst>
 </file>
 
@@ -659,7 +686,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -827,12 +854,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -975,6 +1011,45 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -983,12 +1058,6 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1011,50 +1080,11 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -8805,7 +8835,7 @@
               <a:rPr lang="en-US" baseline="0">
                 <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
               </a:rPr>
-              <a:t> = 5000</a:t>
+              <a:t> = 3000</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -8846,108 +8876,8 @@
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="0"/>
+          <c:idx val="1"/>
           <c:order val="0"/>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:srgbClr val="FF0000"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Графики!$B$37:$B$44</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>16</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Графики!$D$132:$D$139</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-A20B-40B3-98AD-69AA8CF4691F}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
           <c:tx>
             <c:v>Целевое значение</c:v>
           </c:tx>
@@ -8985,10 +8915,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Графики!$B$37:$B$44</c:f>
+              <c:f>Графики!$B$136:$B$147</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -9011,17 +8941,29 @@
                   <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>40</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Графики!$B$37:$B$44</c:f>
+              <c:f>Графики!$B$136:$B$146</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -9044,7 +8986,16 @@
                   <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9052,7 +9003,125 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-A20B-40B3-98AD-69AA8CF4691F}"/>
+              <c16:uniqueId val="{00000001-A557-493F-A449-73115457C681}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Графики!$B$136:$B$146</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Графики!$C$136:$C$146</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.7688250272826482</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.1615734720416127</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.1524338172502135</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.1728723404255321</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A557-493F-A449-73115457C681}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -9128,6 +9197,7 @@
         <c:crossAx val="1826559071"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
+        <c:majorUnit val="2"/>
       </c:valAx>
       <c:valAx>
         <c:axId val="1826559071"/>
@@ -9190,6 +9260,7 @@
         <c:crossAx val="1871156463"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
+        <c:majorUnit val="2"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -9286,7 +9357,7 @@
               <a:rPr lang="en-US" baseline="0">
                 <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
               </a:rPr>
-              <a:t> = 5000</a:t>
+              <a:t> = 3000</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -9327,108 +9398,8 @@
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="0"/>
+          <c:idx val="1"/>
           <c:order val="0"/>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:srgbClr val="FF0000"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Графики!$B$37:$B$44</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>16</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Графики!$D$142:$D$149</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-A273-46FB-A63A-FB8B69BD5D41}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
           <c:tx>
             <c:v>Целевое значение</c:v>
           </c:tx>
@@ -9466,10 +9437,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Графики!$B$37:$B$44</c:f>
+              <c:f>Графики!$B$150:$B$160</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -9492,7 +9463,16 @@
                   <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9500,7 +9480,7 @@
           <c:yVal>
             <c:numLit>
               <c:formatCode>General</c:formatCode>
-              <c:ptCount val="8"/>
+              <c:ptCount val="11"/>
               <c:pt idx="0">
                 <c:v>1</c:v>
               </c:pt>
@@ -9525,12 +9505,139 @@
               <c:pt idx="7">
                 <c:v>1</c:v>
               </c:pt>
+              <c:pt idx="8">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="9">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="10">
+                <c:v>1</c:v>
+              </c:pt>
             </c:numLit>
           </c:yVal>
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-A273-46FB-A63A-FB8B69BD5D41}"/>
+              <c16:uniqueId val="{00000001-0B96-43F7-986F-ADA288A8DECA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Графики!$B$150:$B$160</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Графики!$C$150:$C$160</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.88441251364132412</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.79039336801040316</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.69207230287503563</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.64660904255319152</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0B96-43F7-986F-ADA288A8DECA}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -9606,6 +9713,7 @@
         <c:crossAx val="1826559071"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
+        <c:majorUnit val="2"/>
       </c:valAx>
       <c:valAx>
         <c:axId val="1826559071"/>
@@ -9764,7 +9872,7 @@
               <a:rPr lang="en-US" baseline="0">
                 <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
               </a:rPr>
-              <a:t> = 5000</a:t>
+              <a:t> = 3000</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -9810,7 +9918,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:srgbClr val="FF0000"/>
+                <a:schemeClr val="accent2"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -9821,11 +9929,11 @@
             <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="FF0000"/>
+                <a:schemeClr val="accent2"/>
               </a:solidFill>
               <a:ln w="9525">
                 <a:solidFill>
-                  <a:srgbClr val="FF0000"/>
+                  <a:schemeClr val="accent2"/>
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
@@ -9833,10 +9941,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Графики!$B$37:$B$44</c:f>
+              <c:f>Графики!$B$122:$B$132</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -9859,24 +9967,48 @@
                   <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Графики!$D$122:$D$129</c:f>
+              <c:f>Графики!$C$122:$C$132</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>9725</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5498</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3076</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2342</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1880</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-B24B-46CE-9C90-667175EBAFB1}"/>
+              <c16:uniqueId val="{00000000-637E-4817-9C47-33391629FBA9}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -9952,6 +10084,7 @@
         <c:crossAx val="1826559071"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
+        <c:majorUnit val="2"/>
       </c:valAx>
       <c:valAx>
         <c:axId val="1826559071"/>
@@ -10110,7 +10243,7 @@
               <a:rPr lang="en-US" baseline="0">
                 <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
               </a:rPr>
-              <a:t> = 3000</a:t>
+              <a:t> = 5000</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -10156,7 +10289,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:srgbClr val="FF0000"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -10167,11 +10300,11 @@
             <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:srgbClr val="FF0000"/>
               </a:solidFill>
               <a:ln w="9525">
                 <a:solidFill>
-                  <a:schemeClr val="accent2"/>
+                  <a:srgbClr val="FF0000"/>
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
@@ -10179,10 +10312,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Графики!$B$37:$B$44</c:f>
+              <c:f>Графики!$B$122:$B$132</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -10205,40 +10338,58 @@
                   <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Графики!$C$132:$C$139</c:f>
+              <c:f>Графики!$D$122:$D$132</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>76160</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>39071</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>20102</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>14063</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>11690</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>10161</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>7756</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>7789</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>7039</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>6201</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>6056</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10246,118 +10397,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-A557-493F-A449-73115457C681}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:v>Целевое значение</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="bg1">
-                  <a:lumMod val="65000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:prstDash val="sysDash"/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="bg1">
-                  <a:lumMod val="65000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="bg1">
-                    <a:lumMod val="65000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:prstDash val="sysDash"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Графики!$B$37:$B$44</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>16</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Графики!$B$37:$B$44</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>16</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-A557-493F-A449-73115457C681}"/>
+              <c16:uniqueId val="{00000000-3AEF-4894-805C-216D9CE5104E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -10433,6 +10473,7 @@
         <c:crossAx val="1826559071"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
+        <c:majorUnit val="2"/>
       </c:valAx>
       <c:valAx>
         <c:axId val="1826559071"/>
@@ -10791,7 +10832,19 @@
               <a:rPr lang="en-US" baseline="0">
                 <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
               </a:rPr>
-              <a:t> = 3000</a:t>
+              <a:t> = </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ru-RU" baseline="0">
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t>10</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0">
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t>000</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -10837,7 +10890,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:srgbClr val="C00000"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -10848,11 +10901,11 @@
             <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:srgbClr val="C00000"/>
               </a:solidFill>
               <a:ln w="9525">
                 <a:solidFill>
-                  <a:schemeClr val="accent2"/>
+                  <a:srgbClr val="C00000"/>
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
@@ -10860,10 +10913,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Графики!$B$37:$B$44</c:f>
+              <c:f>Графики!$B$122:$B$132</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -10886,156 +10939,33 @@
                   <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Графики!$C$142:$C$149</c:f>
+              <c:f>Графики!$E$122:$E$132</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0</c:v>
-                </c:pt>
+                <c:ptCount val="11"/>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-0B96-43F7-986F-ADA288A8DECA}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:v>Целевое значение</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="bg1">
-                  <a:lumMod val="65000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:prstDash val="sysDash"/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="bg1">
-                  <a:lumMod val="65000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="bg1">
-                    <a:lumMod val="65000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:prstDash val="sysDash"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Графики!$B$37:$B$44</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>16</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numLit>
-              <c:formatCode>General</c:formatCode>
-              <c:ptCount val="8"/>
-              <c:pt idx="0">
-                <c:v>1</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>1</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>1</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>1</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>1</c:v>
-              </c:pt>
-              <c:pt idx="5">
-                <c:v>1</c:v>
-              </c:pt>
-              <c:pt idx="6">
-                <c:v>1</c:v>
-              </c:pt>
-              <c:pt idx="7">
-                <c:v>1</c:v>
-              </c:pt>
-            </c:numLit>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-0B96-43F7-986F-ADA288A8DECA}"/>
+              <c16:uniqueId val="{00000000-29DE-46B5-99D0-81F81045F765}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -11111,6 +11041,7 @@
         <c:crossAx val="1826559071"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
+        <c:majorUnit val="2"/>
       </c:valAx>
       <c:valAx>
         <c:axId val="1826559071"/>
@@ -11269,7 +11200,19 @@
               <a:rPr lang="en-US" baseline="0">
                 <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
               </a:rPr>
-              <a:t> = 3000</a:t>
+              <a:t> = </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ru-RU" baseline="0">
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t>10</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0">
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t>000</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -11310,12 +11253,141 @@
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="0"/>
+          <c:idx val="1"/>
           <c:order val="0"/>
+          <c:tx>
+            <c:v>Целевое значение</c:v>
+          </c:tx>
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="65000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:prstDash val="sysDash"/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="65000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="bg1">
+                    <a:lumMod val="65000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:prstDash val="sysDash"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Графики!$B$136:$B$146</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Графики!$B$136:$B$146</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4B1F-4C7F-AC86-ECAA526DC8D6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -11326,11 +11398,11 @@
             <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:srgbClr val="C00000"/>
               </a:solidFill>
               <a:ln w="9525">
                 <a:solidFill>
-                  <a:schemeClr val="accent2"/>
+                  <a:srgbClr val="C00000"/>
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
@@ -11338,10 +11410,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Графики!$B$37:$B$44</c:f>
+              <c:f>Графики!$B$136:$B$146</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -11364,24 +11436,66 @@
                   <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Графики!$C$122:$C$129</c:f>
+              <c:f>Графики!$E$136:$E$146</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-637E-4817-9C47-33391629FBA9}"/>
+              <c16:uniqueId val="{00000001-4B1F-4C7F-AC86-ECAA526DC8D6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -11457,6 +11571,7 @@
         <c:crossAx val="1826559071"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
+        <c:majorUnit val="2"/>
       </c:valAx>
       <c:valAx>
         <c:axId val="1826559071"/>
@@ -11519,6 +11634,7 @@
         <c:crossAx val="1871156463"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
+        <c:majorUnit val="2"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -11615,19 +11731,7 @@
               <a:rPr lang="en-US" baseline="0">
                 <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
               </a:rPr>
-              <a:t> = </a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="ru-RU" baseline="0">
-                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              </a:rPr>
-              <a:t>10</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" baseline="0">
-                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              </a:rPr>
-              <a:t>000</a:t>
+              <a:t> = 5000</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -11668,108 +11772,8 @@
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="0"/>
+          <c:idx val="1"/>
           <c:order val="0"/>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:srgbClr val="C00000"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="C00000"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:srgbClr val="C00000"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Графики!$B$37:$B$44</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>16</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Графики!$E$132:$E$139</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-FBFA-4E74-82F6-609D55138937}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
           <c:tx>
             <c:v>Целевое значение</c:v>
           </c:tx>
@@ -11807,10 +11811,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Графики!$B$37:$B$44</c:f>
+              <c:f>Графики!$B$136:$B$146</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -11833,17 +11837,26 @@
                   <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Графики!$B$37:$B$44</c:f>
+              <c:f>Графики!$B$136:$B$146</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -11866,7 +11879,16 @@
                   <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11874,7 +11896,128 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-FBFA-4E74-82F6-609D55138937}"/>
+              <c16:uniqueId val="{00000000-8171-4E0C-9281-B9205E5691E5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Графики!$B$136:$B$146</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Графики!$D$136:$D$147</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.9492718384479537</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.7886777435081087</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.4156296665007471</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.5149700598802394</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7.4953252632614902</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9.8194945848375443</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9.777891898831685</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10.81971871004404</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>12.281890017739075</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>12.575957727873183</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11.124744376278118</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-8171-4E0C-9281-B9205E5691E5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -11950,6 +12093,7 @@
         <c:crossAx val="1826559071"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
+        <c:majorUnit val="2"/>
       </c:valAx>
       <c:valAx>
         <c:axId val="1826559071"/>
@@ -12012,6 +12156,7 @@
         <c:crossAx val="1871156463"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
+        <c:majorUnit val="2"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -12161,108 +12306,8 @@
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="0"/>
+          <c:idx val="1"/>
           <c:order val="0"/>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:srgbClr val="C00000"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="C00000"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:srgbClr val="C00000"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Графики!$B$37:$B$44</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>16</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Графики!$E$142:$E$149</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-F008-4072-9DA7-D43656FF6178}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
           <c:tx>
             <c:v>Целевое значение</c:v>
           </c:tx>
@@ -12300,10 +12345,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Графики!$B$37:$B$44</c:f>
+              <c:f>Графики!$B$150:$B$160</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -12326,7 +12371,16 @@
                   <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12334,7 +12388,7 @@
           <c:yVal>
             <c:numLit>
               <c:formatCode>General</c:formatCode>
-              <c:ptCount val="8"/>
+              <c:ptCount val="11"/>
               <c:pt idx="0">
                 <c:v>1</c:v>
               </c:pt>
@@ -12359,12 +12413,139 @@
               <c:pt idx="7">
                 <c:v>1</c:v>
               </c:pt>
+              <c:pt idx="8">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="9">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="10">
+                <c:v>1</c:v>
+              </c:pt>
             </c:numLit>
           </c:yVal>
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-F008-4072-9DA7-D43656FF6178}"/>
+              <c16:uniqueId val="{00000000-5E37-4B39-9139-AFEE8B2EE215}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="C00000"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Графики!$B$150:$B$160</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Графики!$E$150:$E$160</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-5E37-4B39-9139-AFEE8B2EE215}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -12440,6 +12621,7 @@
         <c:crossAx val="1826559071"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
+        <c:majorUnit val="2"/>
       </c:valAx>
       <c:valAx>
         <c:axId val="1826559071"/>
@@ -12598,19 +12780,7 @@
               <a:rPr lang="en-US" baseline="0">
                 <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
               </a:rPr>
-              <a:t> = </a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="ru-RU" baseline="0">
-                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              </a:rPr>
-              <a:t>10</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" baseline="0">
-                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-              </a:rPr>
-              <a:t>000</a:t>
+              <a:t> = 5000</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -12651,12 +12821,141 @@
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="0"/>
+          <c:idx val="1"/>
           <c:order val="0"/>
+          <c:tx>
+            <c:v>Целевое значение</c:v>
+          </c:tx>
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:srgbClr val="C00000"/>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="65000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:prstDash val="sysDash"/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="65000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="bg1">
+                    <a:lumMod val="65000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:prstDash val="sysDash"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Графики!$B$150:$B$161</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>40</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="11"/>
+              <c:pt idx="0">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="5">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="6">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="7">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="8">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="9">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="10">
+                <c:v>1</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-578B-4D7D-B648-11824E830792}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -12667,11 +12966,11 @@
             <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="C00000"/>
+                <a:srgbClr val="FF0000"/>
               </a:solidFill>
               <a:ln w="9525">
                 <a:solidFill>
-                  <a:srgbClr val="C00000"/>
+                  <a:srgbClr val="FF0000"/>
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
@@ -12679,10 +12978,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Графики!$B$37:$B$44</c:f>
+              <c:f>Графики!$B$150:$B$160</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -12705,24 +13004,66 @@
                   <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Графики!$E$122:$E$129</c:f>
+              <c:f>Графики!$D$150:$D$160</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.97463591922397685</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.94716943587702718</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.90260494441679118</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.81437125748502992</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.74953252632614897</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.81829121540312866</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.69842084991654896</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.67623241937775247</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.68232722320772643</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.62879788639365919</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-29DE-41B5-9D11-9A68295C2254}"/>
+              <c16:uniqueId val="{00000001-578B-4D7D-B648-11824E830792}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -12798,6 +13139,7 @@
         <c:crossAx val="1826559071"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
+        <c:majorUnit val="2"/>
       </c:valAx>
       <c:valAx>
         <c:axId val="1826559071"/>
@@ -33371,23 +33713,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>129</xdr:row>
+      <xdr:row>133</xdr:row>
       <xdr:rowOff>25868</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>875168</xdr:colOff>
-      <xdr:row>139</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>12934</xdr:colOff>
+      <xdr:row>147</xdr:row>
+      <xdr:rowOff>22665</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="55" name="Диаграмма 54">
+        <xdr:cNvPr id="58" name="Диаграмма 57">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C26A85B-1544-4476-BA3E-E163143F8F20}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8AEB44A-4667-4483-BC2D-CB23B4E2955C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -33409,23 +33751,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>139</xdr:row>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1358019</xdr:colOff>
+      <xdr:row>147</xdr:row>
       <xdr:rowOff>25866</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>875168</xdr:colOff>
-      <xdr:row>149</xdr:row>
-      <xdr:rowOff>4</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>879478</xdr:colOff>
+      <xdr:row>160</xdr:row>
+      <xdr:rowOff>271061</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="56" name="Диаграмма 55">
+        <xdr:cNvPr id="59" name="Диаграмма 58">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{538EF4CE-AF43-43C7-8035-A8735C42395E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{85889AAC-9BD8-4731-8A8C-7AC78E85257A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -33447,23 +33789,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1358019</xdr:colOff>
       <xdr:row>119</xdr:row>
       <xdr:rowOff>25866</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>875168</xdr:colOff>
-      <xdr:row>129</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>879478</xdr:colOff>
+      <xdr:row>132</xdr:row>
+      <xdr:rowOff>271059</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="57" name="Диаграмма 56">
+        <xdr:cNvPr id="60" name="Диаграмма 59">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E211DB4-80EC-4216-A845-F915B4157AE8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45899311-6625-49BE-9FD4-424B17CCB595}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -33485,23 +33827,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>129</xdr:row>
-      <xdr:rowOff>25868</xdr:rowOff>
+      <xdr:row>119</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>875169</xdr:colOff>
-      <xdr:row>139</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>880388</xdr:colOff>
+      <xdr:row>132</xdr:row>
+      <xdr:rowOff>245738</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="58" name="Диаграмма 57">
+        <xdr:cNvPr id="36" name="Диаграмма 35">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8AEB44A-4667-4483-BC2D-CB23B4E2955C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C32472AA-ADFA-4D1E-922D-02DF8A983CB2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -33523,23 +33865,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>139</xdr:row>
-      <xdr:rowOff>25866</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>119</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>875169</xdr:colOff>
-      <xdr:row>149</xdr:row>
-      <xdr:rowOff>4</xdr:rowOff>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>478541</xdr:colOff>
+      <xdr:row>132</xdr:row>
+      <xdr:rowOff>249817</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="59" name="Диаграмма 58">
+        <xdr:cNvPr id="64" name="Диаграмма 63">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{85889AAC-9BD8-4731-8A8C-7AC78E85257A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00FAE3B6-E51C-41A7-9789-ECDE2BA58830}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -33561,23 +33903,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
+      <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>119</xdr:row>
-      <xdr:rowOff>25866</xdr:rowOff>
+      <xdr:row>133</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>875169</xdr:colOff>
-      <xdr:row>129</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>465606</xdr:colOff>
+      <xdr:row>146</xdr:row>
+      <xdr:rowOff>260664</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="60" name="Диаграмма 59">
+        <xdr:cNvPr id="65" name="Диаграмма 64">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45899311-6625-49BE-9FD4-424B17CCB595}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C1664293-10B8-4A11-80A9-92103D22DD45}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -33599,23 +33941,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>129</xdr:row>
-      <xdr:rowOff>25868</xdr:rowOff>
+      <xdr:row>133</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>875169</xdr:colOff>
-      <xdr:row>139</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>892413</xdr:colOff>
+      <xdr:row>146</xdr:row>
+      <xdr:rowOff>252926</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="61" name="Диаграмма 60">
+        <xdr:cNvPr id="66" name="Диаграмма 65">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E39445A9-578D-44A4-B26A-5591270DB59B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BEB75FEF-420F-48A2-910F-203FF699D7B9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -33637,23 +33979,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
+      <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>139</xdr:row>
-      <xdr:rowOff>25866</xdr:rowOff>
+      <xdr:row>146</xdr:row>
+      <xdr:rowOff>271603</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>875169</xdr:colOff>
-      <xdr:row>149</xdr:row>
-      <xdr:rowOff>4</xdr:rowOff>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>452673</xdr:colOff>
+      <xdr:row>160</xdr:row>
+      <xdr:rowOff>252933</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="62" name="Диаграмма 61">
+        <xdr:cNvPr id="67" name="Диаграмма 66">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0DD1AF4D-C7D7-4261-8E89-DF3584759784}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E6D0036-B959-4770-A365-ADBF567038F4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -33675,23 +34017,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>119</xdr:row>
-      <xdr:rowOff>25866</xdr:rowOff>
+      <xdr:row>146</xdr:row>
+      <xdr:rowOff>271603</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>875169</xdr:colOff>
-      <xdr:row>129</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>160</xdr:row>
+      <xdr:rowOff>260671</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="63" name="Диаграмма 62">
+        <xdr:cNvPr id="68" name="Диаграмма 67">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{246C40BD-AF51-4D5F-AE81-0E6DE176CDBB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BEC6F7B1-5C2F-41E0-B6B6-0259E9BB524D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -35045,7 +35387,7 @@
       <c r="D64" s="54"/>
       <c r="E64" s="54"/>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
         <v>7</v>
       </c>
@@ -35062,7 +35404,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
         <v>8</v>
       </c>
@@ -35079,7 +35421,7 @@
         <v>58818</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
         <v>9</v>
       </c>
@@ -35096,12 +35438,12 @@
         <v>59837</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C68" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="49" t="s">
         <v>109</v>
       </c>
@@ -35114,7 +35456,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
         <v>4</v>
       </c>
@@ -35125,7 +35467,7 @@
       <c r="D71" s="53"/>
       <c r="E71" s="53"/>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="54" t="s">
         <v>110</v>
       </c>
@@ -35134,7 +35476,7 @@
       <c r="D72" s="54"/>
       <c r="E72" s="54"/>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
         <v>6</v>
       </c>
@@ -35151,7 +35493,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>7</v>
       </c>
@@ -35164,7 +35506,7 @@
         <v>1349</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
         <v>8</v>
       </c>
@@ -35177,7 +35519,7 @@
         <v>12676</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
         <v>9</v>
       </c>
@@ -35190,7 +35532,7 @@
         <v>14026</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="54" t="s">
         <v>111</v>
       </c>
@@ -35199,7 +35541,7 @@
       <c r="D77" s="54"/>
       <c r="E77" s="54"/>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
         <v>6</v>
       </c>
@@ -35216,40 +35558,74 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B79" s="9"/>
-      <c r="C79" s="10"/>
-      <c r="D79" s="10"/>
-      <c r="E79" s="10"/>
+      <c r="B79" s="9">
+        <v>792</v>
+      </c>
+      <c r="C79" s="10">
+        <v>2170</v>
+      </c>
+      <c r="D79" s="10">
+        <v>4256</v>
+      </c>
+      <c r="E79" s="10">
+        <v>8662</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>115</v>
+      </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B80" s="9"/>
-      <c r="C80" s="10"/>
-      <c r="D80" s="10"/>
-      <c r="E80" s="10"/>
+      <c r="B80" s="9">
+        <v>349</v>
+      </c>
+      <c r="C80" s="10">
+        <v>1505</v>
+      </c>
+      <c r="D80" s="10">
+        <v>3928</v>
+      </c>
+      <c r="E80" s="10">
+        <v>11608</v>
+      </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B81" s="9"/>
-      <c r="C81" s="10"/>
-      <c r="D81" s="10"/>
-      <c r="E81" s="10"/>
+      <c r="B81" s="9">
+        <v>1141</v>
+      </c>
+      <c r="C81" s="10">
+        <v>3677</v>
+      </c>
+      <c r="D81" s="10">
+        <v>8186</v>
+      </c>
+      <c r="E81" s="10">
+        <v>20279</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="A70:C70"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="B71:E71"/>
-    <mergeCell ref="A72:E72"/>
-    <mergeCell ref="A77:E77"/>
+    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="D57:E57"/>
+    <mergeCell ref="B58:E58"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A31:C31"/>
     <mergeCell ref="H24:I24"/>
     <mergeCell ref="G5:H8"/>
     <mergeCell ref="B42:E42"/>
@@ -35265,18 +35641,11 @@
     <mergeCell ref="B19:E19"/>
     <mergeCell ref="A21:E21"/>
     <mergeCell ref="A25:E25"/>
-    <mergeCell ref="B45:E45"/>
-    <mergeCell ref="A47:E47"/>
-    <mergeCell ref="A51:E51"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A57:C57"/>
-    <mergeCell ref="D57:E57"/>
-    <mergeCell ref="B58:E58"/>
-    <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="A70:C70"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="B71:E71"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A77:E77"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <hyperlinks>
@@ -35295,7 +35664,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Z150"/>
+  <dimension ref="A1:AC162"/>
   <sheetFormatPr defaultRowHeight="21.6" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.28515625" style="26" customWidth="1"/>
@@ -35303,7 +35672,8 @@
     <col min="3" max="3" width="23.5703125" style="26" customWidth="1"/>
     <col min="4" max="5" width="21.42578125" style="26" customWidth="1"/>
     <col min="6" max="20" width="14.28515625" style="26" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="26"/>
+    <col min="21" max="29" width="9.7109375" style="26" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="26"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -35339,14 +35709,14 @@
       <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="79" t="s">
+      <c r="A2" s="64" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="74" t="s">
+      <c r="B2" s="68" t="s">
         <v>78</v>
       </c>
-      <c r="C2" s="75"/>
-      <c r="D2" s="76"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="70"/>
       <c r="E2" s="31"/>
       <c r="F2" s="31"/>
       <c r="G2" s="31"/>
@@ -35371,7 +35741,7 @@
       <c r="Z2" s="30"/>
     </row>
     <row r="3" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="79"/>
+      <c r="A3" s="64"/>
       <c r="B3" s="29" t="s">
         <v>77</v>
       </c>
@@ -35405,7 +35775,7 @@
       <c r="Z3" s="30"/>
     </row>
     <row r="4" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="79"/>
+      <c r="A4" s="64"/>
       <c r="B4" s="15">
         <v>1</v>
       </c>
@@ -35439,7 +35809,7 @@
       <c r="Z4" s="30"/>
     </row>
     <row r="5" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="79"/>
+      <c r="A5" s="64"/>
       <c r="B5" s="15">
         <v>2</v>
       </c>
@@ -35473,7 +35843,7 @@
       <c r="Z5" s="30"/>
     </row>
     <row r="6" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="79"/>
+      <c r="A6" s="64"/>
       <c r="B6" s="15">
         <v>4</v>
       </c>
@@ -35496,7 +35866,7 @@
       <c r="O6" s="38"/>
     </row>
     <row r="7" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="79"/>
+      <c r="A7" s="64"/>
       <c r="B7" s="15">
         <v>6</v>
       </c>
@@ -35519,7 +35889,7 @@
       <c r="O7" s="38"/>
     </row>
     <row r="8" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="79"/>
+      <c r="A8" s="64"/>
       <c r="B8" s="15">
         <v>8</v>
       </c>
@@ -35542,7 +35912,7 @@
       <c r="O8" s="38"/>
     </row>
     <row r="9" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="79"/>
+      <c r="A9" s="64"/>
       <c r="B9" s="15">
         <v>10</v>
       </c>
@@ -35565,7 +35935,7 @@
       <c r="O9" s="38"/>
     </row>
     <row r="10" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="79"/>
+      <c r="A10" s="64"/>
       <c r="B10" s="15">
         <v>12</v>
       </c>
@@ -35588,7 +35958,7 @@
       <c r="O10" s="38"/>
     </row>
     <row r="11" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="79"/>
+      <c r="A11" s="64"/>
       <c r="B11" s="15">
         <v>16</v>
       </c>
@@ -35613,37 +35983,37 @@
       <c r="Q11" s="27"/>
     </row>
     <row r="12" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="79"/>
+      <c r="A12" s="64"/>
       <c r="B12" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="C12" s="77" t="s">
+      <c r="C12" s="71" t="s">
         <v>81</v>
       </c>
-      <c r="D12" s="77"/>
-      <c r="E12" s="77"/>
-      <c r="F12" s="77"/>
-      <c r="G12" s="77"/>
-      <c r="H12" s="77"/>
-      <c r="I12" s="77"/>
-      <c r="J12" s="77"/>
-      <c r="K12" s="77"/>
-      <c r="L12" s="77"/>
-      <c r="M12" s="77"/>
-      <c r="N12" s="78"/>
+      <c r="D12" s="71"/>
+      <c r="E12" s="71"/>
+      <c r="F12" s="71"/>
+      <c r="G12" s="71"/>
+      <c r="H12" s="71"/>
+      <c r="I12" s="71"/>
+      <c r="J12" s="71"/>
+      <c r="K12" s="71"/>
+      <c r="L12" s="71"/>
+      <c r="M12" s="71"/>
+      <c r="N12" s="65"/>
       <c r="O12" s="39"/>
       <c r="P12" s="23"/>
       <c r="Q12" s="23"/>
     </row>
     <row r="13" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="79" t="s">
+      <c r="A13" s="64" t="s">
         <v>87</v>
       </c>
-      <c r="B13" s="74" t="s">
+      <c r="B13" s="68" t="s">
         <v>78</v>
       </c>
-      <c r="C13" s="75"/>
-      <c r="D13" s="76"/>
+      <c r="C13" s="69"/>
+      <c r="D13" s="70"/>
       <c r="E13" s="32"/>
       <c r="F13" s="31"/>
       <c r="G13" s="31"/>
@@ -35659,7 +36029,7 @@
       <c r="Q13" s="23"/>
     </row>
     <row r="14" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="79"/>
+      <c r="A14" s="64"/>
       <c r="B14" s="13" t="s">
         <v>77</v>
       </c>
@@ -35684,7 +36054,7 @@
       <c r="Q14" s="23"/>
     </row>
     <row r="15" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="79"/>
+      <c r="A15" s="64"/>
       <c r="B15" s="15">
         <v>1</v>
       </c>
@@ -35709,7 +36079,7 @@
       <c r="Q15" s="27"/>
     </row>
     <row r="16" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="79"/>
+      <c r="A16" s="64"/>
       <c r="B16" s="15">
         <v>2</v>
       </c>
@@ -35734,7 +36104,7 @@
       <c r="Q16" s="23"/>
     </row>
     <row r="17" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="79"/>
+      <c r="A17" s="64"/>
       <c r="B17" s="15">
         <v>4</v>
       </c>
@@ -35759,7 +36129,7 @@
       <c r="Q17" s="23"/>
     </row>
     <row r="18" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="79"/>
+      <c r="A18" s="64"/>
       <c r="B18" s="15">
         <v>6</v>
       </c>
@@ -35784,7 +36154,7 @@
       <c r="Q18" s="23"/>
     </row>
     <row r="19" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="79"/>
+      <c r="A19" s="64"/>
       <c r="B19" s="15">
         <v>8</v>
       </c>
@@ -35807,7 +36177,7 @@
       <c r="O19" s="38"/>
     </row>
     <row r="20" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="79"/>
+      <c r="A20" s="64"/>
       <c r="B20" s="15">
         <v>10</v>
       </c>
@@ -35830,7 +36200,7 @@
       <c r="O20" s="38"/>
     </row>
     <row r="21" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="79"/>
+      <c r="A21" s="64"/>
       <c r="B21" s="15">
         <v>12</v>
       </c>
@@ -35853,41 +36223,41 @@
       <c r="O21" s="38"/>
     </row>
     <row r="22" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="79"/>
-      <c r="B22" s="80" t="s">
+      <c r="A22" s="64"/>
+      <c r="B22" s="72" t="s">
         <v>86</v>
       </c>
-      <c r="C22" s="81" t="s">
+      <c r="C22" s="73" t="s">
         <v>88</v>
       </c>
-      <c r="D22" s="81"/>
-      <c r="E22" s="81"/>
-      <c r="F22" s="81"/>
-      <c r="G22" s="81"/>
-      <c r="H22" s="81"/>
-      <c r="I22" s="81"/>
-      <c r="J22" s="81"/>
-      <c r="K22" s="81"/>
-      <c r="L22" s="81"/>
-      <c r="M22" s="81"/>
-      <c r="N22" s="82"/>
+      <c r="D22" s="73"/>
+      <c r="E22" s="73"/>
+      <c r="F22" s="73"/>
+      <c r="G22" s="73"/>
+      <c r="H22" s="73"/>
+      <c r="I22" s="73"/>
+      <c r="J22" s="73"/>
+      <c r="K22" s="73"/>
+      <c r="L22" s="73"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="74"/>
       <c r="O22" s="38"/>
     </row>
     <row r="23" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="79"/>
-      <c r="B23" s="80"/>
-      <c r="C23" s="81"/>
-      <c r="D23" s="81"/>
-      <c r="E23" s="81"/>
-      <c r="F23" s="81"/>
-      <c r="G23" s="81"/>
-      <c r="H23" s="81"/>
-      <c r="I23" s="81"/>
-      <c r="J23" s="81"/>
-      <c r="K23" s="81"/>
-      <c r="L23" s="81"/>
-      <c r="M23" s="81"/>
-      <c r="N23" s="82"/>
+      <c r="A23" s="64"/>
+      <c r="B23" s="72"/>
+      <c r="C23" s="73"/>
+      <c r="D23" s="73"/>
+      <c r="E23" s="73"/>
+      <c r="F23" s="73"/>
+      <c r="G23" s="73"/>
+      <c r="H23" s="73"/>
+      <c r="I23" s="73"/>
+      <c r="J23" s="73"/>
+      <c r="K23" s="73"/>
+      <c r="L23" s="73"/>
+      <c r="M23" s="73"/>
+      <c r="N23" s="74"/>
       <c r="O23" s="38"/>
     </row>
     <row r="24" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -35912,14 +36282,14 @@
       <c r="O24" s="38"/>
     </row>
     <row r="25" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="65" t="s">
+      <c r="A25" s="62" t="s">
         <v>85</v>
       </c>
-      <c r="B25" s="74" t="s">
+      <c r="B25" s="68" t="s">
         <v>78</v>
       </c>
-      <c r="C25" s="75"/>
-      <c r="D25" s="76"/>
+      <c r="C25" s="69"/>
+      <c r="D25" s="70"/>
       <c r="E25" s="31"/>
       <c r="F25" s="31"/>
       <c r="G25" s="31"/>
@@ -35933,7 +36303,7 @@
       <c r="O25" s="27"/>
     </row>
     <row r="26" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="66"/>
+      <c r="A26" s="63"/>
       <c r="B26" s="42" t="s">
         <v>77</v>
       </c>
@@ -35956,7 +36326,7 @@
       <c r="O26" s="27"/>
     </row>
     <row r="27" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="66"/>
+      <c r="A27" s="63"/>
       <c r="B27" s="15">
         <v>1</v>
       </c>
@@ -35979,7 +36349,7 @@
       <c r="O27" s="27"/>
     </row>
     <row r="28" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="66"/>
+      <c r="A28" s="63"/>
       <c r="B28" s="15">
         <v>2</v>
       </c>
@@ -36002,7 +36372,7 @@
       <c r="O28" s="27"/>
     </row>
     <row r="29" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="66"/>
+      <c r="A29" s="63"/>
       <c r="B29" s="15">
         <v>4</v>
       </c>
@@ -36025,7 +36395,7 @@
       <c r="O29" s="27"/>
     </row>
     <row r="30" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="66"/>
+      <c r="A30" s="63"/>
       <c r="B30" s="15">
         <v>6</v>
       </c>
@@ -36048,7 +36418,7 @@
       <c r="O30" s="27"/>
     </row>
     <row r="31" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="66"/>
+      <c r="A31" s="63"/>
       <c r="B31" s="15">
         <v>8</v>
       </c>
@@ -36071,7 +36441,7 @@
       <c r="O31" s="27"/>
     </row>
     <row r="32" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="66"/>
+      <c r="A32" s="63"/>
       <c r="B32" s="15">
         <v>10</v>
       </c>
@@ -36094,7 +36464,7 @@
       <c r="O32" s="27"/>
     </row>
     <row r="33" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="66"/>
+      <c r="A33" s="63"/>
       <c r="B33" s="15">
         <v>12</v>
       </c>
@@ -36117,7 +36487,7 @@
       <c r="O33" s="27"/>
     </row>
     <row r="34" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="66"/>
+      <c r="A34" s="63"/>
       <c r="B34" s="15">
         <v>16</v>
       </c>
@@ -36140,12 +36510,12 @@
       <c r="O34" s="27"/>
     </row>
     <row r="35" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="66"/>
-      <c r="B35" s="74" t="s">
+      <c r="A35" s="63"/>
+      <c r="B35" s="68" t="s">
         <v>96</v>
       </c>
-      <c r="C35" s="75"/>
-      <c r="D35" s="76"/>
+      <c r="C35" s="69"/>
+      <c r="D35" s="70"/>
       <c r="E35" s="31"/>
       <c r="F35" s="31"/>
       <c r="G35" s="31"/>
@@ -36159,7 +36529,7 @@
       <c r="O35" s="27"/>
     </row>
     <row r="36" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="66"/>
+      <c r="A36" s="63"/>
       <c r="B36" s="42" t="s">
         <v>77</v>
       </c>
@@ -36183,7 +36553,7 @@
       <c r="P36" s="1"/>
     </row>
     <row r="37" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="66"/>
+      <c r="A37" s="63"/>
       <c r="B37" s="42">
         <v>1</v>
       </c>
@@ -36209,7 +36579,7 @@
       <c r="P37" s="1"/>
     </row>
     <row r="38" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="66"/>
+      <c r="A38" s="63"/>
       <c r="B38" s="42">
         <v>2</v>
       </c>
@@ -36235,7 +36605,7 @@
       <c r="P38" s="1"/>
     </row>
     <row r="39" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="66"/>
+      <c r="A39" s="63"/>
       <c r="B39" s="42">
         <v>4</v>
       </c>
@@ -36261,7 +36631,7 @@
       <c r="P39" s="1"/>
     </row>
     <row r="40" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="66"/>
+      <c r="A40" s="63"/>
       <c r="B40" s="42">
         <v>6</v>
       </c>
@@ -36287,7 +36657,7 @@
       <c r="P40" s="1"/>
     </row>
     <row r="41" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="66"/>
+      <c r="A41" s="63"/>
       <c r="B41" s="42">
         <v>8</v>
       </c>
@@ -36313,7 +36683,7 @@
       <c r="P41" s="1"/>
     </row>
     <row r="42" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="66"/>
+      <c r="A42" s="63"/>
       <c r="B42" s="42">
         <v>10</v>
       </c>
@@ -36339,7 +36709,7 @@
       <c r="P42" s="1"/>
     </row>
     <row r="43" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="66"/>
+      <c r="A43" s="63"/>
       <c r="B43" s="42">
         <v>12</v>
       </c>
@@ -36365,7 +36735,7 @@
       <c r="P43" s="1"/>
     </row>
     <row r="44" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="66"/>
+      <c r="A44" s="63"/>
       <c r="B44" s="42">
         <v>16</v>
       </c>
@@ -36391,12 +36761,12 @@
       <c r="P44" s="1"/>
     </row>
     <row r="45" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="66"/>
-      <c r="B45" s="74" t="s">
+      <c r="A45" s="63"/>
+      <c r="B45" s="68" t="s">
         <v>97</v>
       </c>
-      <c r="C45" s="75"/>
-      <c r="D45" s="76"/>
+      <c r="C45" s="69"/>
+      <c r="D45" s="70"/>
       <c r="E45" s="43"/>
       <c r="F45" s="43"/>
       <c r="G45" s="43"/>
@@ -36411,7 +36781,7 @@
       <c r="P45" s="1"/>
     </row>
     <row r="46" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="66"/>
+      <c r="A46" s="63"/>
       <c r="B46" s="42" t="s">
         <v>77</v>
       </c>
@@ -36435,7 +36805,7 @@
       <c r="P46" s="1"/>
     </row>
     <row r="47" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="66"/>
+      <c r="A47" s="63"/>
       <c r="B47" s="42">
         <v>1</v>
       </c>
@@ -36461,7 +36831,7 @@
       <c r="P47" s="1"/>
     </row>
     <row r="48" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="66"/>
+      <c r="A48" s="63"/>
       <c r="B48" s="42">
         <v>2</v>
       </c>
@@ -36487,7 +36857,7 @@
       <c r="P48" s="1"/>
     </row>
     <row r="49" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="66"/>
+      <c r="A49" s="63"/>
       <c r="B49" s="42">
         <v>4</v>
       </c>
@@ -36513,7 +36883,7 @@
       <c r="P49" s="1"/>
     </row>
     <row r="50" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="66"/>
+      <c r="A50" s="63"/>
       <c r="B50" s="42">
         <v>6</v>
       </c>
@@ -36539,7 +36909,7 @@
       <c r="P50" s="1"/>
     </row>
     <row r="51" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="66"/>
+      <c r="A51" s="63"/>
       <c r="B51" s="42">
         <v>8</v>
       </c>
@@ -36564,7 +36934,7 @@
       <c r="O51" s="1"/>
     </row>
     <row r="52" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="66"/>
+      <c r="A52" s="63"/>
       <c r="B52" s="42">
         <v>10</v>
       </c>
@@ -36589,7 +36959,7 @@
       <c r="O52" s="1"/>
     </row>
     <row r="53" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="66"/>
+      <c r="A53" s="63"/>
       <c r="B53" s="42">
         <v>12</v>
       </c>
@@ -36614,7 +36984,7 @@
       <c r="O53" s="1"/>
     </row>
     <row r="54" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="66"/>
+      <c r="A54" s="63"/>
       <c r="B54" s="42">
         <v>16</v>
       </c>
@@ -36639,40 +37009,40 @@
       <c r="O54" s="1"/>
     </row>
     <row r="55" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="66"/>
+      <c r="A55" s="63"/>
       <c r="B55" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="C55" s="70" t="s">
+      <c r="C55" s="81" t="s">
         <v>102</v>
       </c>
-      <c r="D55" s="70"/>
-      <c r="E55" s="70"/>
-      <c r="F55" s="70"/>
-      <c r="G55" s="70"/>
-      <c r="H55" s="70"/>
-      <c r="I55" s="70"/>
-      <c r="J55" s="70"/>
-      <c r="K55" s="70"/>
-      <c r="L55" s="70"/>
-      <c r="M55" s="70"/>
-      <c r="N55" s="70"/>
+      <c r="D55" s="81"/>
+      <c r="E55" s="81"/>
+      <c r="F55" s="81"/>
+      <c r="G55" s="81"/>
+      <c r="H55" s="81"/>
+      <c r="I55" s="81"/>
+      <c r="J55" s="81"/>
+      <c r="K55" s="81"/>
+      <c r="L55" s="81"/>
+      <c r="M55" s="81"/>
+      <c r="N55" s="81"/>
     </row>
     <row r="56" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="71" t="s">
+      <c r="A56" s="82" t="s">
         <v>103</v>
       </c>
-      <c r="B56" s="72"/>
-      <c r="C56" s="72"/>
-      <c r="D56" s="72"/>
-      <c r="E56" s="72"/>
-      <c r="F56" s="72"/>
-      <c r="G56" s="72"/>
-      <c r="H56" s="72"/>
-      <c r="I56" s="72"/>
-      <c r="J56" s="72"/>
-      <c r="K56" s="72"/>
-      <c r="L56" s="73"/>
+      <c r="B56" s="83"/>
+      <c r="C56" s="83"/>
+      <c r="D56" s="83"/>
+      <c r="E56" s="83"/>
+      <c r="F56" s="83"/>
+      <c r="G56" s="83"/>
+      <c r="H56" s="83"/>
+      <c r="I56" s="83"/>
+      <c r="J56" s="83"/>
+      <c r="K56" s="83"/>
+      <c r="L56" s="84"/>
       <c r="M56" s="52" t="s">
         <v>90</v>
       </c>
@@ -36680,14 +37050,14 @@
       <c r="O56" s="30"/>
     </row>
     <row r="57" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="65" t="s">
+      <c r="A57" s="62" t="s">
         <v>85</v>
       </c>
-      <c r="B57" s="74" t="s">
+      <c r="B57" s="68" t="s">
         <v>78</v>
       </c>
-      <c r="C57" s="75"/>
-      <c r="D57" s="76"/>
+      <c r="C57" s="69"/>
+      <c r="D57" s="70"/>
       <c r="E57" s="31"/>
       <c r="F57" s="31"/>
       <c r="G57" s="31"/>
@@ -36701,7 +37071,7 @@
       <c r="O57" s="30"/>
     </row>
     <row r="58" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="66"/>
+      <c r="A58" s="63"/>
       <c r="B58" s="42" t="s">
         <v>77</v>
       </c>
@@ -36724,7 +37094,7 @@
       <c r="O58" s="30"/>
     </row>
     <row r="59" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="66"/>
+      <c r="A59" s="63"/>
       <c r="B59" s="15">
         <v>1</v>
       </c>
@@ -36747,7 +37117,7 @@
       <c r="O59" s="30"/>
     </row>
     <row r="60" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="66"/>
+      <c r="A60" s="63"/>
       <c r="B60" s="15">
         <v>2</v>
       </c>
@@ -36770,7 +37140,7 @@
       <c r="O60" s="30"/>
     </row>
     <row r="61" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="66"/>
+      <c r="A61" s="63"/>
       <c r="B61" s="15">
         <v>4</v>
       </c>
@@ -36793,7 +37163,7 @@
       <c r="O61" s="30"/>
     </row>
     <row r="62" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="66"/>
+      <c r="A62" s="63"/>
       <c r="B62" s="15">
         <v>6</v>
       </c>
@@ -36816,7 +37186,7 @@
       <c r="O62" s="30"/>
     </row>
     <row r="63" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="66"/>
+      <c r="A63" s="63"/>
       <c r="B63" s="15">
         <v>8</v>
       </c>
@@ -36839,7 +37209,7 @@
       <c r="O63" s="30"/>
     </row>
     <row r="64" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="66"/>
+      <c r="A64" s="63"/>
       <c r="B64" s="15">
         <v>10</v>
       </c>
@@ -36862,7 +37232,7 @@
       <c r="O64" s="30"/>
     </row>
     <row r="65" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="66"/>
+      <c r="A65" s="63"/>
       <c r="B65" s="15">
         <v>12</v>
       </c>
@@ -36885,7 +37255,7 @@
       <c r="O65" s="30"/>
     </row>
     <row r="66" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="66"/>
+      <c r="A66" s="63"/>
       <c r="B66" s="15">
         <v>16</v>
       </c>
@@ -36908,12 +37278,12 @@
       <c r="O66" s="30"/>
     </row>
     <row r="67" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="66"/>
-      <c r="B67" s="74" t="s">
+      <c r="A67" s="63"/>
+      <c r="B67" s="68" t="s">
         <v>96</v>
       </c>
-      <c r="C67" s="75"/>
-      <c r="D67" s="76"/>
+      <c r="C67" s="69"/>
+      <c r="D67" s="70"/>
       <c r="E67" s="31"/>
       <c r="F67" s="31"/>
       <c r="G67" s="31"/>
@@ -36927,7 +37297,7 @@
       <c r="O67" s="30"/>
     </row>
     <row r="68" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="66"/>
+      <c r="A68" s="63"/>
       <c r="B68" s="42" t="s">
         <v>77</v>
       </c>
@@ -36950,7 +37320,7 @@
       <c r="O68" s="30"/>
     </row>
     <row r="69" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="66"/>
+      <c r="A69" s="63"/>
       <c r="B69" s="42">
         <v>1</v>
       </c>
@@ -36975,7 +37345,7 @@
       <c r="O69" s="30"/>
     </row>
     <row r="70" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="66"/>
+      <c r="A70" s="63"/>
       <c r="B70" s="42">
         <v>2</v>
       </c>
@@ -37000,7 +37370,7 @@
       <c r="O70" s="30"/>
     </row>
     <row r="71" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="66"/>
+      <c r="A71" s="63"/>
       <c r="B71" s="42">
         <v>4</v>
       </c>
@@ -37025,7 +37395,7 @@
       <c r="O71" s="30"/>
     </row>
     <row r="72" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="66"/>
+      <c r="A72" s="63"/>
       <c r="B72" s="42">
         <v>6</v>
       </c>
@@ -37050,7 +37420,7 @@
       <c r="O72" s="30"/>
     </row>
     <row r="73" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="66"/>
+      <c r="A73" s="63"/>
       <c r="B73" s="42">
         <v>8</v>
       </c>
@@ -37075,7 +37445,7 @@
       <c r="O73" s="30"/>
     </row>
     <row r="74" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="66"/>
+      <c r="A74" s="63"/>
       <c r="B74" s="42">
         <v>10</v>
       </c>
@@ -37100,7 +37470,7 @@
       <c r="O74" s="30"/>
     </row>
     <row r="75" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="66"/>
+      <c r="A75" s="63"/>
       <c r="B75" s="42">
         <v>12</v>
       </c>
@@ -37125,7 +37495,7 @@
       <c r="O75" s="30"/>
     </row>
     <row r="76" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="66"/>
+      <c r="A76" s="63"/>
       <c r="B76" s="42">
         <v>16</v>
       </c>
@@ -37150,12 +37520,12 @@
       <c r="O76" s="30"/>
     </row>
     <row r="77" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="66"/>
-      <c r="B77" s="74" t="s">
+      <c r="A77" s="63"/>
+      <c r="B77" s="68" t="s">
         <v>97</v>
       </c>
-      <c r="C77" s="75"/>
-      <c r="D77" s="76"/>
+      <c r="C77" s="69"/>
+      <c r="D77" s="70"/>
       <c r="E77" s="43"/>
       <c r="F77" s="43"/>
       <c r="G77" s="43"/>
@@ -37169,7 +37539,7 @@
       <c r="O77" s="30"/>
     </row>
     <row r="78" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="66"/>
+      <c r="A78" s="63"/>
       <c r="B78" s="42" t="s">
         <v>77</v>
       </c>
@@ -37192,7 +37562,7 @@
       <c r="O78" s="30"/>
     </row>
     <row r="79" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="66"/>
+      <c r="A79" s="63"/>
       <c r="B79" s="42">
         <v>1</v>
       </c>
@@ -37217,7 +37587,7 @@
       <c r="O79" s="30"/>
     </row>
     <row r="80" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="66"/>
+      <c r="A80" s="63"/>
       <c r="B80" s="42">
         <v>2</v>
       </c>
@@ -37242,7 +37612,7 @@
       <c r="O80" s="30"/>
     </row>
     <row r="81" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="66"/>
+      <c r="A81" s="63"/>
       <c r="B81" s="42">
         <v>4</v>
       </c>
@@ -37267,7 +37637,7 @@
       <c r="O81" s="30"/>
     </row>
     <row r="82" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="66"/>
+      <c r="A82" s="63"/>
       <c r="B82" s="42">
         <v>6</v>
       </c>
@@ -37292,7 +37662,7 @@
       <c r="O82" s="30"/>
     </row>
     <row r="83" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="66"/>
+      <c r="A83" s="63"/>
       <c r="B83" s="42">
         <v>8</v>
       </c>
@@ -37317,7 +37687,7 @@
       <c r="O83" s="30"/>
     </row>
     <row r="84" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="66"/>
+      <c r="A84" s="63"/>
       <c r="B84" s="42">
         <v>10</v>
       </c>
@@ -37342,7 +37712,7 @@
       <c r="O84" s="30"/>
     </row>
     <row r="85" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="66"/>
+      <c r="A85" s="63"/>
       <c r="B85" s="42">
         <v>12</v>
       </c>
@@ -37367,7 +37737,7 @@
       <c r="O85" s="30"/>
     </row>
     <row r="86" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="66"/>
+      <c r="A86" s="63"/>
       <c r="B86" s="42">
         <v>16</v>
       </c>
@@ -37392,24 +37762,24 @@
       <c r="O86" s="30"/>
     </row>
     <row r="87" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="66"/>
+      <c r="A87" s="63"/>
       <c r="B87" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="C87" s="67" t="s">
+      <c r="C87" s="78" t="s">
         <v>106</v>
       </c>
-      <c r="D87" s="68"/>
-      <c r="E87" s="68"/>
-      <c r="F87" s="68"/>
-      <c r="G87" s="68"/>
-      <c r="H87" s="68"/>
-      <c r="I87" s="68"/>
-      <c r="J87" s="68"/>
-      <c r="K87" s="68"/>
-      <c r="L87" s="68"/>
-      <c r="M87" s="68"/>
-      <c r="N87" s="69"/>
+      <c r="D87" s="79"/>
+      <c r="E87" s="79"/>
+      <c r="F87" s="79"/>
+      <c r="G87" s="79"/>
+      <c r="H87" s="79"/>
+      <c r="I87" s="79"/>
+      <c r="J87" s="79"/>
+      <c r="K87" s="79"/>
+      <c r="L87" s="79"/>
+      <c r="M87" s="79"/>
+      <c r="N87" s="80"/>
     </row>
     <row r="88" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="49" t="s">
@@ -37428,25 +37798,25 @@
       <c r="L88" s="50"/>
       <c r="M88" s="50"/>
       <c r="N88" s="50"/>
-      <c r="O88" s="62" t="s">
+      <c r="O88" s="75" t="s">
         <v>113</v>
       </c>
-      <c r="P88" s="63"/>
-      <c r="Q88" s="63"/>
-      <c r="R88" s="63"/>
-      <c r="S88" s="63"/>
-      <c r="T88" s="64"/>
+      <c r="P88" s="76"/>
+      <c r="Q88" s="76"/>
+      <c r="R88" s="76"/>
+      <c r="S88" s="76"/>
+      <c r="T88" s="77"/>
     </row>
     <row r="89" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="79" t="s">
+      <c r="A89" s="64" t="s">
         <v>85</v>
       </c>
-      <c r="B89" s="74" t="s">
+      <c r="B89" s="68" t="s">
         <v>78</v>
       </c>
-      <c r="C89" s="75"/>
-      <c r="D89" s="75"/>
-      <c r="E89" s="76"/>
+      <c r="C89" s="69"/>
+      <c r="D89" s="69"/>
+      <c r="E89" s="70"/>
       <c r="F89" s="31"/>
       <c r="G89" s="31"/>
       <c r="H89" s="31"/>
@@ -37464,7 +37834,7 @@
       <c r="T89" s="31"/>
     </row>
     <row r="90" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="79"/>
+      <c r="A90" s="64"/>
       <c r="B90" s="42" t="s">
         <v>77</v>
       </c>
@@ -37494,7 +37864,7 @@
       <c r="T90" s="31"/>
     </row>
     <row r="91" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="79"/>
+      <c r="A91" s="64"/>
       <c r="B91" s="15">
         <v>1</v>
       </c>
@@ -37524,7 +37894,7 @@
       <c r="T91" s="31"/>
     </row>
     <row r="92" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="79"/>
+      <c r="A92" s="64"/>
       <c r="B92" s="15">
         <v>2</v>
       </c>
@@ -37554,7 +37924,7 @@
       <c r="T92" s="31"/>
     </row>
     <row r="93" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="79"/>
+      <c r="A93" s="64"/>
       <c r="B93" s="15">
         <v>4</v>
       </c>
@@ -37584,7 +37954,7 @@
       <c r="T93" s="31"/>
     </row>
     <row r="94" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="79"/>
+      <c r="A94" s="64"/>
       <c r="B94" s="15">
         <v>6</v>
       </c>
@@ -37614,7 +37984,7 @@
       <c r="T94" s="31"/>
     </row>
     <row r="95" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="79"/>
+      <c r="A95" s="64"/>
       <c r="B95" s="15">
         <v>8</v>
       </c>
@@ -37644,7 +38014,7 @@
       <c r="T95" s="31"/>
     </row>
     <row r="96" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="79"/>
+      <c r="A96" s="64"/>
       <c r="B96" s="15">
         <v>10</v>
       </c>
@@ -37674,7 +38044,7 @@
       <c r="T96" s="31"/>
     </row>
     <row r="97" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="79"/>
+      <c r="A97" s="64"/>
       <c r="B97" s="15">
         <v>12</v>
       </c>
@@ -37704,7 +38074,7 @@
       <c r="T97" s="31"/>
     </row>
     <row r="98" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="79"/>
+      <c r="A98" s="64"/>
       <c r="B98" s="15">
         <v>16</v>
       </c>
@@ -37734,13 +38104,13 @@
       <c r="T98" s="31"/>
     </row>
     <row r="99" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="79"/>
-      <c r="B99" s="74" t="s">
+      <c r="A99" s="64"/>
+      <c r="B99" s="68" t="s">
         <v>96</v>
       </c>
-      <c r="C99" s="75"/>
-      <c r="D99" s="75"/>
-      <c r="E99" s="76"/>
+      <c r="C99" s="69"/>
+      <c r="D99" s="69"/>
+      <c r="E99" s="70"/>
       <c r="F99" s="31"/>
       <c r="G99" s="31"/>
       <c r="H99" s="31"/>
@@ -37758,7 +38128,7 @@
       <c r="T99" s="31"/>
     </row>
     <row r="100" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="79"/>
+      <c r="A100" s="64"/>
       <c r="B100" s="42" t="s">
         <v>77</v>
       </c>
@@ -37788,7 +38158,7 @@
       <c r="T100" s="16"/>
     </row>
     <row r="101" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="79"/>
+      <c r="A101" s="64"/>
       <c r="B101" s="42">
         <v>1</v>
       </c>
@@ -37821,7 +38191,7 @@
       <c r="T101" s="16"/>
     </row>
     <row r="102" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="79"/>
+      <c r="A102" s="64"/>
       <c r="B102" s="42">
         <v>2</v>
       </c>
@@ -37854,7 +38224,7 @@
       <c r="T102" s="16"/>
     </row>
     <row r="103" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="79"/>
+      <c r="A103" s="64"/>
       <c r="B103" s="42">
         <v>4</v>
       </c>
@@ -37887,7 +38257,7 @@
       <c r="T103" s="16"/>
     </row>
     <row r="104" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="79"/>
+      <c r="A104" s="64"/>
       <c r="B104" s="42">
         <v>6</v>
       </c>
@@ -37920,7 +38290,7 @@
       <c r="T104" s="16"/>
     </row>
     <row r="105" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="79"/>
+      <c r="A105" s="64"/>
       <c r="B105" s="42">
         <v>8</v>
       </c>
@@ -37953,7 +38323,7 @@
       <c r="T105" s="16"/>
     </row>
     <row r="106" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="79"/>
+      <c r="A106" s="64"/>
       <c r="B106" s="42">
         <v>10</v>
       </c>
@@ -37986,7 +38356,7 @@
       <c r="T106" s="16"/>
     </row>
     <row r="107" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="79"/>
+      <c r="A107" s="64"/>
       <c r="B107" s="42">
         <v>12</v>
       </c>
@@ -38019,7 +38389,7 @@
       <c r="T107" s="16"/>
     </row>
     <row r="108" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="79"/>
+      <c r="A108" s="64"/>
       <c r="B108" s="42">
         <v>16</v>
       </c>
@@ -38052,13 +38422,13 @@
       <c r="T108" s="16"/>
     </row>
     <row r="109" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="79"/>
-      <c r="B109" s="74" t="s">
+      <c r="A109" s="64"/>
+      <c r="B109" s="68" t="s">
         <v>97</v>
       </c>
-      <c r="C109" s="75"/>
-      <c r="D109" s="75"/>
-      <c r="E109" s="76"/>
+      <c r="C109" s="69"/>
+      <c r="D109" s="69"/>
+      <c r="E109" s="70"/>
       <c r="F109" s="43"/>
       <c r="G109" s="16"/>
       <c r="H109" s="16"/>
@@ -38076,7 +38446,7 @@
       <c r="T109" s="16"/>
     </row>
     <row r="110" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="79"/>
+      <c r="A110" s="64"/>
       <c r="B110" s="42" t="s">
         <v>77</v>
       </c>
@@ -38106,7 +38476,7 @@
       <c r="T110" s="16"/>
     </row>
     <row r="111" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="79"/>
+      <c r="A111" s="64"/>
       <c r="B111" s="42">
         <v>1</v>
       </c>
@@ -38139,7 +38509,7 @@
       <c r="T111" s="16"/>
     </row>
     <row r="112" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="79"/>
+      <c r="A112" s="64"/>
       <c r="B112" s="42">
         <v>2</v>
       </c>
@@ -38171,8 +38541,8 @@
       <c r="S112" s="16"/>
       <c r="T112" s="16"/>
     </row>
-    <row r="113" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="79"/>
+    <row r="113" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="64"/>
       <c r="B113" s="42">
         <v>4</v>
       </c>
@@ -38204,8 +38574,8 @@
       <c r="S113" s="16"/>
       <c r="T113" s="16"/>
     </row>
-    <row r="114" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="79"/>
+    <row r="114" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="64"/>
       <c r="B114" s="42">
         <v>6</v>
       </c>
@@ -38237,8 +38607,8 @@
       <c r="S114" s="16"/>
       <c r="T114" s="16"/>
     </row>
-    <row r="115" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="79"/>
+    <row r="115" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="64"/>
       <c r="B115" s="42">
         <v>8</v>
       </c>
@@ -38270,8 +38640,8 @@
       <c r="S115" s="16"/>
       <c r="T115" s="16"/>
     </row>
-    <row r="116" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="79"/>
+    <row r="116" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="64"/>
       <c r="B116" s="42">
         <v>10</v>
       </c>
@@ -38303,8 +38673,8 @@
       <c r="S116" s="16"/>
       <c r="T116" s="16"/>
     </row>
-    <row r="117" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="79"/>
+    <row r="117" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="64"/>
       <c r="B117" s="42">
         <v>12</v>
       </c>
@@ -38336,8 +38706,8 @@
       <c r="S117" s="31"/>
       <c r="T117" s="31"/>
     </row>
-    <row r="118" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="79"/>
+    <row r="118" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="64"/>
       <c r="B118" s="42">
         <v>16</v>
       </c>
@@ -38369,42 +38739,42 @@
       <c r="S118" s="31"/>
       <c r="T118" s="31"/>
     </row>
-    <row r="119" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="79"/>
+    <row r="119" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="64"/>
       <c r="B119" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="C119" s="78" t="s">
+      <c r="C119" s="65" t="s">
         <v>114</v>
       </c>
-      <c r="D119" s="84"/>
-      <c r="E119" s="84"/>
-      <c r="F119" s="84"/>
-      <c r="G119" s="84"/>
-      <c r="H119" s="84"/>
-      <c r="I119" s="84"/>
-      <c r="J119" s="84"/>
-      <c r="K119" s="84"/>
-      <c r="L119" s="84"/>
-      <c r="M119" s="84"/>
-      <c r="N119" s="84"/>
-      <c r="O119" s="84"/>
-      <c r="P119" s="84"/>
-      <c r="Q119" s="84"/>
-      <c r="R119" s="84"/>
-      <c r="S119" s="84"/>
-      <c r="T119" s="85"/>
+      <c r="D119" s="66"/>
+      <c r="E119" s="66"/>
+      <c r="F119" s="66"/>
+      <c r="G119" s="66"/>
+      <c r="H119" s="66"/>
+      <c r="I119" s="66"/>
+      <c r="J119" s="66"/>
+      <c r="K119" s="66"/>
+      <c r="L119" s="66"/>
+      <c r="M119" s="66"/>
+      <c r="N119" s="66"/>
+      <c r="O119" s="66"/>
+      <c r="P119" s="66"/>
+      <c r="Q119" s="66"/>
+      <c r="R119" s="66"/>
+      <c r="S119" s="66"/>
+      <c r="T119" s="67"/>
     </row>
-    <row r="120" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="65" t="s">
+    <row r="120" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="85" t="s">
         <v>108</v>
       </c>
-      <c r="B120" s="74" t="s">
+      <c r="B120" s="68" t="s">
         <v>78</v>
       </c>
-      <c r="C120" s="75"/>
-      <c r="D120" s="75"/>
-      <c r="E120" s="76"/>
+      <c r="C120" s="69"/>
+      <c r="D120" s="69"/>
+      <c r="E120" s="70"/>
       <c r="F120" s="31"/>
       <c r="G120" s="31"/>
       <c r="H120" s="31"/>
@@ -38420,20 +38790,29 @@
       <c r="R120" s="31"/>
       <c r="S120" s="31"/>
       <c r="T120" s="31"/>
+      <c r="U120" s="31"/>
+      <c r="V120" s="31"/>
+      <c r="W120" s="31"/>
+      <c r="X120" s="31"/>
+      <c r="Y120" s="31"/>
+      <c r="Z120" s="31"/>
+      <c r="AA120" s="31"/>
+      <c r="AB120" s="31"/>
+      <c r="AC120" s="31"/>
     </row>
-    <row r="121" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="66"/>
+    <row r="121" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="86"/>
       <c r="B121" s="42" t="s">
         <v>77</v>
       </c>
       <c r="C121" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D121" s="25" t="s">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="E121" s="25" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="F121" s="31"/>
       <c r="G121" s="31"/>
@@ -38450,14 +38829,27 @@
       <c r="R121" s="31"/>
       <c r="S121" s="31"/>
       <c r="T121" s="31"/>
+      <c r="U121" s="31"/>
+      <c r="V121" s="31"/>
+      <c r="W121" s="31"/>
+      <c r="X121" s="31"/>
+      <c r="Y121" s="31"/>
+      <c r="Z121" s="31"/>
+      <c r="AA121" s="31"/>
+      <c r="AB121" s="31"/>
+      <c r="AC121" s="31"/>
     </row>
-    <row r="122" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="66"/>
+    <row r="122" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="86"/>
       <c r="B122" s="15">
         <v>1</v>
       </c>
-      <c r="C122" s="40"/>
-      <c r="D122" s="24"/>
+      <c r="C122" s="24">
+        <v>9725</v>
+      </c>
+      <c r="D122" s="24">
+        <v>76160</v>
+      </c>
       <c r="E122" s="24"/>
       <c r="F122" s="31"/>
       <c r="G122" s="31"/>
@@ -38474,14 +38866,27 @@
       <c r="R122" s="31"/>
       <c r="S122" s="31"/>
       <c r="T122" s="31"/>
+      <c r="U122" s="31"/>
+      <c r="V122" s="31"/>
+      <c r="W122" s="31"/>
+      <c r="X122" s="31"/>
+      <c r="Y122" s="31"/>
+      <c r="Z122" s="31"/>
+      <c r="AA122" s="31"/>
+      <c r="AB122" s="31"/>
+      <c r="AC122" s="31"/>
     </row>
-    <row r="123" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="66"/>
+    <row r="123" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="86"/>
       <c r="B123" s="15">
         <v>2</v>
       </c>
-      <c r="C123" s="40"/>
-      <c r="D123" s="24"/>
+      <c r="C123" s="24">
+        <v>5498</v>
+      </c>
+      <c r="D123" s="24">
+        <v>39071</v>
+      </c>
       <c r="E123" s="24"/>
       <c r="F123" s="31"/>
       <c r="G123" s="31"/>
@@ -38498,14 +38903,27 @@
       <c r="R123" s="31"/>
       <c r="S123" s="31"/>
       <c r="T123" s="31"/>
+      <c r="U123" s="31"/>
+      <c r="V123" s="31"/>
+      <c r="W123" s="31"/>
+      <c r="X123" s="31"/>
+      <c r="Y123" s="31"/>
+      <c r="Z123" s="31"/>
+      <c r="AA123" s="31"/>
+      <c r="AB123" s="31"/>
+      <c r="AC123" s="31"/>
     </row>
-    <row r="124" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="66"/>
+    <row r="124" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="86"/>
       <c r="B124" s="15">
         <v>4</v>
       </c>
-      <c r="C124" s="40"/>
-      <c r="D124" s="24"/>
+      <c r="C124" s="24">
+        <v>3076</v>
+      </c>
+      <c r="D124" s="24">
+        <v>20102</v>
+      </c>
       <c r="E124" s="24"/>
       <c r="F124" s="31"/>
       <c r="G124" s="31"/>
@@ -38522,14 +38940,27 @@
       <c r="R124" s="31"/>
       <c r="S124" s="31"/>
       <c r="T124" s="31"/>
+      <c r="U124" s="31"/>
+      <c r="V124" s="31"/>
+      <c r="W124" s="31"/>
+      <c r="X124" s="31"/>
+      <c r="Y124" s="31"/>
+      <c r="Z124" s="31"/>
+      <c r="AA124" s="31"/>
+      <c r="AB124" s="31"/>
+      <c r="AC124" s="31"/>
     </row>
-    <row r="125" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="66"/>
+    <row r="125" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="86"/>
       <c r="B125" s="15">
         <v>6</v>
       </c>
-      <c r="C125" s="40"/>
-      <c r="D125" s="24"/>
+      <c r="C125" s="24">
+        <v>2342</v>
+      </c>
+      <c r="D125" s="24">
+        <v>14063</v>
+      </c>
       <c r="E125" s="24"/>
       <c r="F125" s="31"/>
       <c r="G125" s="31"/>
@@ -38546,14 +38977,27 @@
       <c r="R125" s="31"/>
       <c r="S125" s="31"/>
       <c r="T125" s="31"/>
+      <c r="U125" s="31"/>
+      <c r="V125" s="31"/>
+      <c r="W125" s="31"/>
+      <c r="X125" s="31"/>
+      <c r="Y125" s="31"/>
+      <c r="Z125" s="31"/>
+      <c r="AA125" s="31"/>
+      <c r="AB125" s="31"/>
+      <c r="AC125" s="31"/>
     </row>
-    <row r="126" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="66"/>
+    <row r="126" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="86"/>
       <c r="B126" s="15">
         <v>8</v>
       </c>
-      <c r="C126" s="40"/>
-      <c r="D126" s="24"/>
+      <c r="C126" s="40">
+        <v>1880</v>
+      </c>
+      <c r="D126" s="24">
+        <v>11690</v>
+      </c>
       <c r="E126" s="24"/>
       <c r="F126" s="31"/>
       <c r="G126" s="31"/>
@@ -38570,14 +39014,25 @@
       <c r="R126" s="31"/>
       <c r="S126" s="31"/>
       <c r="T126" s="31"/>
+      <c r="U126" s="31"/>
+      <c r="V126" s="31"/>
+      <c r="W126" s="31"/>
+      <c r="X126" s="31"/>
+      <c r="Y126" s="31"/>
+      <c r="Z126" s="31"/>
+      <c r="AA126" s="31"/>
+      <c r="AB126" s="31"/>
+      <c r="AC126" s="31"/>
     </row>
-    <row r="127" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="66"/>
+    <row r="127" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="86"/>
       <c r="B127" s="15">
         <v>10</v>
       </c>
       <c r="C127" s="40"/>
-      <c r="D127" s="24"/>
+      <c r="D127" s="24">
+        <v>10161</v>
+      </c>
       <c r="E127" s="24"/>
       <c r="F127" s="31"/>
       <c r="G127" s="31"/>
@@ -38594,14 +39049,25 @@
       <c r="R127" s="31"/>
       <c r="S127" s="31"/>
       <c r="T127" s="31"/>
+      <c r="U127" s="31"/>
+      <c r="V127" s="31"/>
+      <c r="W127" s="31"/>
+      <c r="X127" s="31"/>
+      <c r="Y127" s="31"/>
+      <c r="Z127" s="31"/>
+      <c r="AA127" s="31"/>
+      <c r="AB127" s="31"/>
+      <c r="AC127" s="31"/>
     </row>
-    <row r="128" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="66"/>
+    <row r="128" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="86"/>
       <c r="B128" s="15">
         <v>12</v>
       </c>
       <c r="C128" s="40"/>
-      <c r="D128" s="24"/>
+      <c r="D128" s="24">
+        <v>7756</v>
+      </c>
       <c r="E128" s="24"/>
       <c r="F128" s="31"/>
       <c r="G128" s="31"/>
@@ -38618,14 +39084,25 @@
       <c r="R128" s="31"/>
       <c r="S128" s="31"/>
       <c r="T128" s="31"/>
+      <c r="U128" s="31"/>
+      <c r="V128" s="31"/>
+      <c r="W128" s="31"/>
+      <c r="X128" s="31"/>
+      <c r="Y128" s="31"/>
+      <c r="Z128" s="31"/>
+      <c r="AA128" s="31"/>
+      <c r="AB128" s="31"/>
+      <c r="AC128" s="31"/>
     </row>
-    <row r="129" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="66"/>
+    <row r="129" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="86"/>
       <c r="B129" s="15">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C129" s="40"/>
-      <c r="D129" s="24"/>
+      <c r="D129" s="24">
+        <v>7789</v>
+      </c>
       <c r="E129" s="24"/>
       <c r="F129" s="31"/>
       <c r="G129" s="31"/>
@@ -38642,15 +39119,26 @@
       <c r="R129" s="31"/>
       <c r="S129" s="31"/>
       <c r="T129" s="31"/>
+      <c r="U129" s="31"/>
+      <c r="V129" s="31"/>
+      <c r="W129" s="31"/>
+      <c r="X129" s="31"/>
+      <c r="Y129" s="31"/>
+      <c r="Z129" s="31"/>
+      <c r="AA129" s="31"/>
+      <c r="AB129" s="31"/>
+      <c r="AC129" s="31"/>
     </row>
-    <row r="130" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="66"/>
-      <c r="B130" s="74" t="s">
-        <v>96</v>
-      </c>
-      <c r="C130" s="75"/>
-      <c r="D130" s="75"/>
-      <c r="E130" s="76"/>
+    <row r="130" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="86"/>
+      <c r="B130" s="15">
+        <v>16</v>
+      </c>
+      <c r="C130" s="40"/>
+      <c r="D130" s="24">
+        <v>7039</v>
+      </c>
+      <c r="E130" s="24"/>
       <c r="F130" s="31"/>
       <c r="G130" s="31"/>
       <c r="H130" s="31"/>
@@ -38666,155 +39154,170 @@
       <c r="R130" s="31"/>
       <c r="S130" s="31"/>
       <c r="T130" s="31"/>
+      <c r="U130" s="31"/>
+      <c r="V130" s="31"/>
+      <c r="W130" s="31"/>
+      <c r="X130" s="31"/>
+      <c r="Y130" s="31"/>
+      <c r="Z130" s="31"/>
+      <c r="AA130" s="31"/>
+      <c r="AB130" s="31"/>
+      <c r="AC130" s="31"/>
     </row>
-    <row r="131" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="66"/>
-      <c r="B131" s="42" t="s">
+    <row r="131" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="86"/>
+      <c r="B131" s="15">
+        <v>18</v>
+      </c>
+      <c r="C131" s="40"/>
+      <c r="D131" s="24">
+        <v>6201</v>
+      </c>
+      <c r="E131" s="24"/>
+      <c r="F131" s="31"/>
+      <c r="G131" s="31"/>
+      <c r="H131" s="31"/>
+      <c r="I131" s="31"/>
+      <c r="J131" s="31"/>
+      <c r="K131" s="31"/>
+      <c r="L131" s="31"/>
+      <c r="M131" s="31"/>
+      <c r="N131" s="31"/>
+      <c r="O131" s="31"/>
+      <c r="P131" s="31"/>
+      <c r="Q131" s="31"/>
+      <c r="R131" s="31"/>
+      <c r="S131" s="31"/>
+      <c r="T131" s="31"/>
+      <c r="U131" s="31"/>
+      <c r="V131" s="31"/>
+      <c r="W131" s="31"/>
+      <c r="X131" s="31"/>
+      <c r="Y131" s="31"/>
+      <c r="Z131" s="31"/>
+      <c r="AA131" s="31"/>
+      <c r="AB131" s="31"/>
+      <c r="AC131" s="31"/>
+    </row>
+    <row r="132" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="86"/>
+      <c r="B132" s="15">
+        <v>20</v>
+      </c>
+      <c r="C132" s="40"/>
+      <c r="D132" s="24">
+        <v>6056</v>
+      </c>
+      <c r="E132" s="24"/>
+      <c r="F132" s="31"/>
+      <c r="G132" s="31"/>
+      <c r="H132" s="31"/>
+      <c r="I132" s="31"/>
+      <c r="J132" s="31"/>
+      <c r="K132" s="31"/>
+      <c r="L132" s="31"/>
+      <c r="M132" s="31"/>
+      <c r="N132" s="31"/>
+      <c r="O132" s="31"/>
+      <c r="P132" s="31"/>
+      <c r="Q132" s="31"/>
+      <c r="R132" s="31"/>
+      <c r="S132" s="31"/>
+      <c r="T132" s="31"/>
+      <c r="U132" s="31"/>
+      <c r="V132" s="31"/>
+      <c r="W132" s="31"/>
+      <c r="X132" s="31"/>
+      <c r="Y132" s="31"/>
+      <c r="Z132" s="31"/>
+      <c r="AA132" s="31"/>
+      <c r="AB132" s="31"/>
+      <c r="AC132" s="31"/>
+    </row>
+    <row r="133" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="86"/>
+      <c r="B133" s="15">
+        <v>40</v>
+      </c>
+      <c r="C133" s="40"/>
+      <c r="D133" s="24">
+        <v>6846</v>
+      </c>
+      <c r="E133" s="24"/>
+      <c r="F133" s="31"/>
+      <c r="G133" s="31"/>
+      <c r="H133" s="31"/>
+      <c r="I133" s="31"/>
+      <c r="J133" s="31"/>
+      <c r="K133" s="31"/>
+      <c r="L133" s="31"/>
+      <c r="M133" s="31"/>
+      <c r="N133" s="31"/>
+      <c r="O133" s="31"/>
+      <c r="P133" s="31"/>
+      <c r="Q133" s="31"/>
+      <c r="R133" s="31"/>
+      <c r="S133" s="31"/>
+      <c r="T133" s="31"/>
+      <c r="U133" s="31"/>
+      <c r="V133" s="31"/>
+      <c r="W133" s="31"/>
+      <c r="X133" s="31"/>
+      <c r="Y133" s="31"/>
+      <c r="Z133" s="31"/>
+      <c r="AA133" s="31"/>
+      <c r="AB133" s="31"/>
+      <c r="AC133" s="31"/>
+    </row>
+    <row r="134" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A134" s="86"/>
+      <c r="B134" s="68" t="s">
+        <v>96</v>
+      </c>
+      <c r="C134" s="69"/>
+      <c r="D134" s="69"/>
+      <c r="E134" s="70"/>
+      <c r="F134" s="31"/>
+      <c r="G134" s="31"/>
+      <c r="H134" s="31"/>
+      <c r="I134" s="31"/>
+      <c r="J134" s="31"/>
+      <c r="K134" s="31"/>
+      <c r="L134" s="31"/>
+      <c r="M134" s="31"/>
+      <c r="N134" s="31"/>
+      <c r="O134" s="31"/>
+      <c r="P134" s="31"/>
+      <c r="Q134" s="31"/>
+      <c r="R134" s="31"/>
+      <c r="S134" s="31"/>
+      <c r="T134" s="31"/>
+      <c r="U134" s="31"/>
+      <c r="V134" s="31"/>
+      <c r="W134" s="31"/>
+      <c r="X134" s="31"/>
+      <c r="Y134" s="31"/>
+      <c r="Z134" s="31"/>
+      <c r="AA134" s="31"/>
+      <c r="AB134" s="31"/>
+      <c r="AC134" s="31"/>
+    </row>
+    <row r="135" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A135" s="86"/>
+      <c r="B135" s="42" t="s">
         <v>77</v>
       </c>
-      <c r="C131" s="25" t="s">
-        <v>80</v>
-      </c>
-      <c r="D131" s="25" t="s">
+      <c r="C135" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="E131" s="25" t="s">
+      <c r="D135" s="25" t="s">
         <v>112</v>
       </c>
-      <c r="F131" s="43"/>
-      <c r="G131" s="43"/>
-      <c r="H131" s="16"/>
-      <c r="I131" s="16"/>
-      <c r="J131" s="16"/>
-      <c r="K131" s="16"/>
-      <c r="L131" s="16"/>
-      <c r="M131" s="16"/>
-      <c r="N131" s="16"/>
-      <c r="O131" s="43"/>
-      <c r="P131" s="43"/>
-      <c r="Q131" s="43"/>
-      <c r="R131" s="16"/>
-      <c r="S131" s="16"/>
-      <c r="T131" s="16"/>
-    </row>
-    <row r="132" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="66"/>
-      <c r="B132" s="42">
-        <v>1</v>
-      </c>
-      <c r="C132" s="40" t="e">
-        <f>C122/C122</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D132" s="40" t="e">
-        <f>D122/D122</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E132" s="40" t="e">
-        <f>E122/E122</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F132" s="43"/>
-      <c r="G132" s="43"/>
-      <c r="H132" s="16"/>
-      <c r="I132" s="16"/>
-      <c r="J132" s="16"/>
-      <c r="K132" s="16"/>
-      <c r="L132" s="16"/>
-      <c r="M132" s="16"/>
-      <c r="N132" s="16"/>
-      <c r="O132" s="43"/>
-      <c r="P132" s="43"/>
-      <c r="Q132" s="43"/>
-      <c r="R132" s="16"/>
-      <c r="S132" s="16"/>
-      <c r="T132" s="16"/>
-    </row>
-    <row r="133" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="66"/>
-      <c r="B133" s="42">
-        <v>2</v>
-      </c>
-      <c r="C133" s="40" t="e">
-        <f>C122/C123</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D133" s="40" t="e">
-        <f>D122/D123</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E133" s="40" t="e">
-        <f>E122/E123</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F133" s="43"/>
-      <c r="G133" s="43"/>
-      <c r="H133" s="16"/>
-      <c r="I133" s="16"/>
-      <c r="J133" s="16"/>
-      <c r="K133" s="16"/>
-      <c r="L133" s="16"/>
-      <c r="M133" s="16"/>
-      <c r="N133" s="16"/>
-      <c r="O133" s="43"/>
-      <c r="P133" s="43"/>
-      <c r="Q133" s="43"/>
-      <c r="R133" s="16"/>
-      <c r="S133" s="16"/>
-      <c r="T133" s="16"/>
-    </row>
-    <row r="134" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="66"/>
-      <c r="B134" s="42">
-        <v>4</v>
-      </c>
-      <c r="C134" s="40" t="e">
-        <f>C122/C124</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D134" s="40" t="e">
-        <f>D122/D124</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E134" s="40" t="e">
-        <f>E122/E124</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F134" s="43"/>
-      <c r="G134" s="43"/>
-      <c r="H134" s="16"/>
-      <c r="I134" s="16"/>
-      <c r="J134" s="16"/>
-      <c r="K134" s="16"/>
-      <c r="L134" s="16"/>
-      <c r="M134" s="16"/>
-      <c r="N134" s="16"/>
-      <c r="O134" s="43"/>
-      <c r="P134" s="43"/>
-      <c r="Q134" s="43"/>
-      <c r="R134" s="16"/>
-      <c r="S134" s="16"/>
-      <c r="T134" s="16"/>
-    </row>
-    <row r="135" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="66"/>
-      <c r="B135" s="42">
-        <v>6</v>
-      </c>
-      <c r="C135" s="40" t="e">
-        <f>C122/C125</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D135" s="40" t="e">
-        <f>D122/D125</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E135" s="40" t="e">
-        <f>E122/E125</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F135" s="43"/>
-      <c r="G135" s="43"/>
+      <c r="E135" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="F135" s="16"/>
+      <c r="G135" s="16"/>
       <c r="H135" s="16"/>
       <c r="I135" s="16"/>
       <c r="J135" s="16"/>
@@ -38822,32 +39325,41 @@
       <c r="L135" s="16"/>
       <c r="M135" s="16"/>
       <c r="N135" s="16"/>
-      <c r="O135" s="43"/>
-      <c r="P135" s="43"/>
-      <c r="Q135" s="43"/>
+      <c r="O135" s="16"/>
+      <c r="P135" s="16"/>
+      <c r="Q135" s="16"/>
       <c r="R135" s="16"/>
       <c r="S135" s="16"/>
       <c r="T135" s="16"/>
+      <c r="U135" s="16"/>
+      <c r="V135" s="16"/>
+      <c r="W135" s="16"/>
+      <c r="X135" s="16"/>
+      <c r="Y135" s="16"/>
+      <c r="Z135" s="16"/>
+      <c r="AA135" s="16"/>
+      <c r="AB135" s="16"/>
+      <c r="AC135" s="16"/>
     </row>
-    <row r="136" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="66"/>
-      <c r="B136" s="42">
-        <v>8</v>
-      </c>
-      <c r="C136" s="40" t="e">
-        <f>C122/C126</f>
+    <row r="136" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="86"/>
+      <c r="B136" s="15">
+        <v>1</v>
+      </c>
+      <c r="C136" s="40">
+        <f>C122/C122</f>
+        <v>1</v>
+      </c>
+      <c r="D136" s="40">
+        <f>D122/D122</f>
+        <v>1</v>
+      </c>
+      <c r="E136" s="40" t="e">
+        <f>E122/E122</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D136" s="40" t="e">
-        <f>D122/D126</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E136" s="40" t="e">
-        <f>E122/E126</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F136" s="43"/>
-      <c r="G136" s="43"/>
+      <c r="F136" s="16"/>
+      <c r="G136" s="16"/>
       <c r="H136" s="16"/>
       <c r="I136" s="16"/>
       <c r="J136" s="16"/>
@@ -38855,32 +39367,41 @@
       <c r="L136" s="16"/>
       <c r="M136" s="16"/>
       <c r="N136" s="16"/>
-      <c r="O136" s="43"/>
-      <c r="P136" s="43"/>
-      <c r="Q136" s="43"/>
+      <c r="O136" s="16"/>
+      <c r="P136" s="16"/>
+      <c r="Q136" s="16"/>
       <c r="R136" s="16"/>
       <c r="S136" s="16"/>
       <c r="T136" s="16"/>
+      <c r="U136" s="16"/>
+      <c r="V136" s="16"/>
+      <c r="W136" s="16"/>
+      <c r="X136" s="16"/>
+      <c r="Y136" s="16"/>
+      <c r="Z136" s="16"/>
+      <c r="AA136" s="16"/>
+      <c r="AB136" s="16"/>
+      <c r="AC136" s="16"/>
     </row>
-    <row r="137" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="66"/>
-      <c r="B137" s="42">
-        <v>10</v>
-      </c>
-      <c r="C137" s="40" t="e">
-        <f>C122/C127</f>
+    <row r="137" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A137" s="86"/>
+      <c r="B137" s="15">
+        <v>2</v>
+      </c>
+      <c r="C137" s="40">
+        <f>C122/C123</f>
+        <v>1.7688250272826482</v>
+      </c>
+      <c r="D137" s="40">
+        <f>D122/D123</f>
+        <v>1.9492718384479537</v>
+      </c>
+      <c r="E137" s="40" t="e">
+        <f>E122/E123</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D137" s="40" t="e">
-        <f>D122/D127</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E137" s="40" t="e">
-        <f>E122/E127</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F137" s="43"/>
-      <c r="G137" s="43"/>
+      <c r="F137" s="16"/>
+      <c r="G137" s="16"/>
       <c r="H137" s="16"/>
       <c r="I137" s="16"/>
       <c r="J137" s="16"/>
@@ -38888,32 +39409,41 @@
       <c r="L137" s="16"/>
       <c r="M137" s="16"/>
       <c r="N137" s="16"/>
-      <c r="O137" s="43"/>
-      <c r="P137" s="43"/>
-      <c r="Q137" s="43"/>
+      <c r="O137" s="16"/>
+      <c r="P137" s="16"/>
+      <c r="Q137" s="16"/>
       <c r="R137" s="16"/>
       <c r="S137" s="16"/>
       <c r="T137" s="16"/>
+      <c r="U137" s="16"/>
+      <c r="V137" s="16"/>
+      <c r="W137" s="16"/>
+      <c r="X137" s="16"/>
+      <c r="Y137" s="16"/>
+      <c r="Z137" s="16"/>
+      <c r="AA137" s="16"/>
+      <c r="AB137" s="16"/>
+      <c r="AC137" s="16"/>
     </row>
-    <row r="138" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="66"/>
-      <c r="B138" s="42">
-        <v>12</v>
-      </c>
-      <c r="C138" s="40" t="e">
-        <f>C122/C128</f>
+    <row r="138" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="86"/>
+      <c r="B138" s="15">
+        <v>4</v>
+      </c>
+      <c r="C138" s="40">
+        <f>C122/C124</f>
+        <v>3.1615734720416127</v>
+      </c>
+      <c r="D138" s="40">
+        <f>D122/D124</f>
+        <v>3.7886777435081087</v>
+      </c>
+      <c r="E138" s="40" t="e">
+        <f>E122/E124</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D138" s="40" t="e">
-        <f>D122/D128</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E138" s="40" t="e">
-        <f>E122/E128</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F138" s="43"/>
-      <c r="G138" s="43"/>
+      <c r="F138" s="16"/>
+      <c r="G138" s="16"/>
       <c r="H138" s="16"/>
       <c r="I138" s="16"/>
       <c r="J138" s="16"/>
@@ -38921,32 +39451,41 @@
       <c r="L138" s="16"/>
       <c r="M138" s="16"/>
       <c r="N138" s="16"/>
-      <c r="O138" s="43"/>
-      <c r="P138" s="43"/>
-      <c r="Q138" s="43"/>
+      <c r="O138" s="16"/>
+      <c r="P138" s="16"/>
+      <c r="Q138" s="16"/>
       <c r="R138" s="16"/>
       <c r="S138" s="16"/>
       <c r="T138" s="16"/>
+      <c r="U138" s="16"/>
+      <c r="V138" s="16"/>
+      <c r="W138" s="16"/>
+      <c r="X138" s="16"/>
+      <c r="Y138" s="16"/>
+      <c r="Z138" s="16"/>
+      <c r="AA138" s="16"/>
+      <c r="AB138" s="16"/>
+      <c r="AC138" s="16"/>
     </row>
-    <row r="139" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="66"/>
-      <c r="B139" s="42">
-        <v>16</v>
-      </c>
-      <c r="C139" s="40" t="e">
-        <f>C122/C129</f>
+    <row r="139" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="86"/>
+      <c r="B139" s="15">
+        <v>6</v>
+      </c>
+      <c r="C139" s="40">
+        <f>C122/C125</f>
+        <v>4.1524338172502135</v>
+      </c>
+      <c r="D139" s="40">
+        <f>D122/D125</f>
+        <v>5.4156296665007471</v>
+      </c>
+      <c r="E139" s="40" t="e">
+        <f>E122/E125</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D139" s="40" t="e">
-        <f>D122/D129</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E139" s="40" t="e">
-        <f>E122/E129</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F139" s="43"/>
-      <c r="G139" s="43"/>
+      <c r="F139" s="16"/>
+      <c r="G139" s="16"/>
       <c r="H139" s="16"/>
       <c r="I139" s="16"/>
       <c r="J139" s="16"/>
@@ -38954,23 +39493,41 @@
       <c r="L139" s="16"/>
       <c r="M139" s="16"/>
       <c r="N139" s="16"/>
-      <c r="O139" s="43"/>
-      <c r="P139" s="43"/>
-      <c r="Q139" s="43"/>
+      <c r="O139" s="16"/>
+      <c r="P139" s="16"/>
+      <c r="Q139" s="16"/>
       <c r="R139" s="16"/>
       <c r="S139" s="16"/>
       <c r="T139" s="16"/>
+      <c r="U139" s="16"/>
+      <c r="V139" s="16"/>
+      <c r="W139" s="16"/>
+      <c r="X139" s="16"/>
+      <c r="Y139" s="16"/>
+      <c r="Z139" s="16"/>
+      <c r="AA139" s="16"/>
+      <c r="AB139" s="16"/>
+      <c r="AC139" s="16"/>
     </row>
-    <row r="140" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="66"/>
-      <c r="B140" s="74" t="s">
-        <v>97</v>
-      </c>
-      <c r="C140" s="75"/>
-      <c r="D140" s="75"/>
-      <c r="E140" s="76"/>
-      <c r="F140" s="43"/>
-      <c r="G140" s="43"/>
+    <row r="140" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="86"/>
+      <c r="B140" s="15">
+        <v>8</v>
+      </c>
+      <c r="C140" s="40">
+        <f>C122/C126</f>
+        <v>5.1728723404255321</v>
+      </c>
+      <c r="D140" s="40">
+        <f>D122/D126</f>
+        <v>6.5149700598802394</v>
+      </c>
+      <c r="E140" s="40" t="e">
+        <f>E122/E126</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F140" s="16"/>
+      <c r="G140" s="16"/>
       <c r="H140" s="16"/>
       <c r="I140" s="16"/>
       <c r="J140" s="16"/>
@@ -38978,29 +39535,41 @@
       <c r="L140" s="16"/>
       <c r="M140" s="16"/>
       <c r="N140" s="16"/>
-      <c r="O140" s="43"/>
-      <c r="P140" s="43"/>
-      <c r="Q140" s="43"/>
+      <c r="O140" s="16"/>
+      <c r="P140" s="16"/>
+      <c r="Q140" s="16"/>
       <c r="R140" s="16"/>
       <c r="S140" s="16"/>
       <c r="T140" s="16"/>
+      <c r="U140" s="16"/>
+      <c r="V140" s="16"/>
+      <c r="W140" s="16"/>
+      <c r="X140" s="16"/>
+      <c r="Y140" s="16"/>
+      <c r="Z140" s="16"/>
+      <c r="AA140" s="16"/>
+      <c r="AB140" s="16"/>
+      <c r="AC140" s="16"/>
     </row>
-    <row r="141" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="66"/>
-      <c r="B141" s="42" t="s">
-        <v>77</v>
-      </c>
-      <c r="C141" s="25" t="s">
-        <v>80</v>
-      </c>
-      <c r="D141" s="25" t="s">
-        <v>79</v>
-      </c>
-      <c r="E141" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="F141" s="43"/>
-      <c r="G141" s="43"/>
+    <row r="141" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="86"/>
+      <c r="B141" s="15">
+        <v>10</v>
+      </c>
+      <c r="C141" s="40" t="e">
+        <f>C122/C127</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D141" s="40">
+        <f>D122/D127</f>
+        <v>7.4953252632614902</v>
+      </c>
+      <c r="E141" s="40" t="e">
+        <f>E122/E127</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F141" s="16"/>
+      <c r="G141" s="16"/>
       <c r="H141" s="16"/>
       <c r="I141" s="16"/>
       <c r="J141" s="16"/>
@@ -39008,32 +39577,41 @@
       <c r="L141" s="16"/>
       <c r="M141" s="16"/>
       <c r="N141" s="16"/>
-      <c r="O141" s="43"/>
-      <c r="P141" s="43"/>
-      <c r="Q141" s="43"/>
+      <c r="O141" s="16"/>
+      <c r="P141" s="16"/>
+      <c r="Q141" s="16"/>
       <c r="R141" s="16"/>
       <c r="S141" s="16"/>
       <c r="T141" s="16"/>
+      <c r="U141" s="16"/>
+      <c r="V141" s="16"/>
+      <c r="W141" s="16"/>
+      <c r="X141" s="16"/>
+      <c r="Y141" s="16"/>
+      <c r="Z141" s="16"/>
+      <c r="AA141" s="16"/>
+      <c r="AB141" s="16"/>
+      <c r="AC141" s="16"/>
     </row>
-    <row r="142" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="66"/>
-      <c r="B142" s="42">
-        <v>1</v>
+    <row r="142" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A142" s="86"/>
+      <c r="B142" s="15">
+        <v>12</v>
       </c>
       <c r="C142" s="40" t="e">
-        <f t="shared" ref="C142:C149" si="7">C132/B132</f>
+        <f>C122/C128</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D142" s="40" t="e">
-        <f t="shared" ref="D142:E149" si="8">D132/$B132</f>
+      <c r="D142" s="40">
+        <f>D122/D128</f>
+        <v>9.8194945848375443</v>
+      </c>
+      <c r="E142" s="40" t="e">
+        <f>E122/E128</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E142" s="40" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F142" s="43"/>
-      <c r="G142" s="43"/>
+      <c r="F142" s="16"/>
+      <c r="G142" s="16"/>
       <c r="H142" s="16"/>
       <c r="I142" s="16"/>
       <c r="J142" s="16"/>
@@ -39041,32 +39619,41 @@
       <c r="L142" s="16"/>
       <c r="M142" s="16"/>
       <c r="N142" s="16"/>
-      <c r="O142" s="43"/>
-      <c r="P142" s="43"/>
-      <c r="Q142" s="43"/>
+      <c r="O142" s="16"/>
+      <c r="P142" s="16"/>
+      <c r="Q142" s="16"/>
       <c r="R142" s="16"/>
       <c r="S142" s="16"/>
       <c r="T142" s="16"/>
+      <c r="U142" s="16"/>
+      <c r="V142" s="16"/>
+      <c r="W142" s="16"/>
+      <c r="X142" s="16"/>
+      <c r="Y142" s="16"/>
+      <c r="Z142" s="16"/>
+      <c r="AA142" s="16"/>
+      <c r="AB142" s="16"/>
+      <c r="AC142" s="16"/>
     </row>
-    <row r="143" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="66"/>
-      <c r="B143" s="42">
-        <v>2</v>
+    <row r="143" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A143" s="86"/>
+      <c r="B143" s="15">
+        <v>14</v>
       </c>
       <c r="C143" s="40" t="e">
-        <f t="shared" si="7"/>
+        <f>C$122/C129</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D143" s="40" t="e">
-        <f t="shared" si="8"/>
+      <c r="D143" s="40">
+        <f>D$122/D129</f>
+        <v>9.777891898831685</v>
+      </c>
+      <c r="E143" s="40" t="e">
+        <f>E$122/E129</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E143" s="40" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F143" s="43"/>
-      <c r="G143" s="43"/>
+      <c r="F143" s="16"/>
+      <c r="G143" s="16"/>
       <c r="H143" s="16"/>
       <c r="I143" s="16"/>
       <c r="J143" s="16"/>
@@ -39074,65 +39661,83 @@
       <c r="L143" s="16"/>
       <c r="M143" s="16"/>
       <c r="N143" s="16"/>
-      <c r="O143" s="43"/>
-      <c r="P143" s="43"/>
-      <c r="Q143" s="43"/>
+      <c r="O143" s="16"/>
+      <c r="P143" s="16"/>
+      <c r="Q143" s="16"/>
       <c r="R143" s="16"/>
       <c r="S143" s="16"/>
       <c r="T143" s="16"/>
+      <c r="U143" s="16"/>
+      <c r="V143" s="16"/>
+      <c r="W143" s="16"/>
+      <c r="X143" s="16"/>
+      <c r="Y143" s="16"/>
+      <c r="Z143" s="16"/>
+      <c r="AA143" s="16"/>
+      <c r="AB143" s="16"/>
+      <c r="AC143" s="16"/>
     </row>
-    <row r="144" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="66"/>
-      <c r="B144" s="42">
-        <v>4</v>
+    <row r="144" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="86"/>
+      <c r="B144" s="15">
+        <v>16</v>
       </c>
       <c r="C144" s="40" t="e">
-        <f t="shared" si="7"/>
+        <f>C$122/C130</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D144" s="40" t="e">
-        <f t="shared" si="8"/>
+      <c r="D144" s="40">
+        <f>D$122/D130</f>
+        <v>10.81971871004404</v>
+      </c>
+      <c r="E144" s="40" t="e">
+        <f t="shared" ref="E144" si="7">E$122/E130</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E144" s="40" t="e">
-        <f t="shared" si="8"/>
+      <c r="F144" s="31"/>
+      <c r="G144" s="31"/>
+      <c r="H144" s="31"/>
+      <c r="I144" s="31"/>
+      <c r="J144" s="31"/>
+      <c r="K144" s="31"/>
+      <c r="L144" s="31"/>
+      <c r="M144" s="31"/>
+      <c r="N144" s="31"/>
+      <c r="O144" s="31"/>
+      <c r="P144" s="31"/>
+      <c r="Q144" s="31"/>
+      <c r="R144" s="31"/>
+      <c r="S144" s="31"/>
+      <c r="T144" s="31"/>
+      <c r="U144" s="31"/>
+      <c r="V144" s="31"/>
+      <c r="W144" s="31"/>
+      <c r="X144" s="31"/>
+      <c r="Y144" s="31"/>
+      <c r="Z144" s="31"/>
+      <c r="AA144" s="31"/>
+      <c r="AB144" s="31"/>
+      <c r="AC144" s="31"/>
+    </row>
+    <row r="145" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="86"/>
+      <c r="B145" s="15">
+        <v>18</v>
+      </c>
+      <c r="C145" s="40" t="e">
+        <f>C$122/C131</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F144" s="43"/>
-      <c r="G144" s="43"/>
-      <c r="H144" s="16"/>
-      <c r="I144" s="16"/>
-      <c r="J144" s="16"/>
-      <c r="K144" s="16"/>
-      <c r="L144" s="16"/>
-      <c r="M144" s="16"/>
-      <c r="N144" s="16"/>
-      <c r="O144" s="43"/>
-      <c r="P144" s="43"/>
-      <c r="Q144" s="43"/>
-      <c r="R144" s="16"/>
-      <c r="S144" s="16"/>
-      <c r="T144" s="16"/>
-    </row>
-    <row r="145" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="66"/>
-      <c r="B145" s="42">
-        <v>6</v>
-      </c>
-      <c r="C145" s="40" t="e">
-        <f t="shared" si="7"/>
+      <c r="D145" s="40">
+        <f>D$122/D131</f>
+        <v>12.281890017739075</v>
+      </c>
+      <c r="E145" s="40" t="e">
+        <f t="shared" ref="E145" si="8">E$122/E131</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D145" s="40" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E145" s="40" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F145" s="43"/>
-      <c r="G145" s="43"/>
+      <c r="F145" s="16"/>
+      <c r="G145" s="16"/>
       <c r="H145" s="16"/>
       <c r="I145" s="16"/>
       <c r="J145" s="16"/>
@@ -39140,32 +39745,41 @@
       <c r="L145" s="16"/>
       <c r="M145" s="16"/>
       <c r="N145" s="16"/>
-      <c r="O145" s="43"/>
-      <c r="P145" s="43"/>
-      <c r="Q145" s="43"/>
+      <c r="O145" s="16"/>
+      <c r="P145" s="16"/>
+      <c r="Q145" s="16"/>
       <c r="R145" s="16"/>
       <c r="S145" s="16"/>
       <c r="T145" s="16"/>
+      <c r="U145" s="16"/>
+      <c r="V145" s="16"/>
+      <c r="W145" s="16"/>
+      <c r="X145" s="16"/>
+      <c r="Y145" s="16"/>
+      <c r="Z145" s="16"/>
+      <c r="AA145" s="16"/>
+      <c r="AB145" s="16"/>
+      <c r="AC145" s="16"/>
     </row>
-    <row r="146" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="66"/>
-      <c r="B146" s="42">
-        <v>8</v>
+    <row r="146" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="86"/>
+      <c r="B146" s="15">
+        <v>20</v>
       </c>
       <c r="C146" s="40" t="e">
-        <f t="shared" si="7"/>
+        <f>C$122/C132</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D146" s="40" t="e">
-        <f t="shared" si="8"/>
+      <c r="D146" s="40">
+        <f>D$122/D132</f>
+        <v>12.575957727873183</v>
+      </c>
+      <c r="E146" s="40" t="e">
+        <f t="shared" ref="E146" si="9">E$122/E132</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E146" s="40" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F146" s="43"/>
-      <c r="G146" s="43"/>
+      <c r="F146" s="16"/>
+      <c r="G146" s="16"/>
       <c r="H146" s="16"/>
       <c r="I146" s="16"/>
       <c r="J146" s="16"/>
@@ -39173,32 +39787,41 @@
       <c r="L146" s="16"/>
       <c r="M146" s="16"/>
       <c r="N146" s="16"/>
-      <c r="O146" s="43"/>
-      <c r="P146" s="43"/>
-      <c r="Q146" s="43"/>
+      <c r="O146" s="16"/>
+      <c r="P146" s="16"/>
+      <c r="Q146" s="16"/>
       <c r="R146" s="16"/>
       <c r="S146" s="16"/>
       <c r="T146" s="16"/>
+      <c r="U146" s="16"/>
+      <c r="V146" s="16"/>
+      <c r="W146" s="16"/>
+      <c r="X146" s="16"/>
+      <c r="Y146" s="16"/>
+      <c r="Z146" s="16"/>
+      <c r="AA146" s="16"/>
+      <c r="AB146" s="16"/>
+      <c r="AC146" s="16"/>
     </row>
-    <row r="147" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="66"/>
-      <c r="B147" s="42">
-        <v>10</v>
+    <row r="147" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A147" s="86"/>
+      <c r="B147" s="15">
+        <v>40</v>
       </c>
       <c r="C147" s="40" t="e">
-        <f t="shared" si="7"/>
+        <f>C$122/C133</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D147" s="40" t="e">
-        <f t="shared" si="8"/>
+      <c r="D147" s="40">
+        <f>D$122/D133</f>
+        <v>11.124744376278118</v>
+      </c>
+      <c r="E147" s="40" t="e">
+        <f>E$122/E133</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E147" s="40" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F147" s="43"/>
-      <c r="G147" s="43"/>
+      <c r="F147" s="16"/>
+      <c r="G147" s="16"/>
       <c r="H147" s="16"/>
       <c r="I147" s="16"/>
       <c r="J147" s="16"/>
@@ -39206,126 +39829,633 @@
       <c r="L147" s="16"/>
       <c r="M147" s="16"/>
       <c r="N147" s="16"/>
-      <c r="O147" s="43"/>
-      <c r="P147" s="43"/>
-      <c r="Q147" s="43"/>
+      <c r="O147" s="16"/>
+      <c r="P147" s="16"/>
+      <c r="Q147" s="16"/>
       <c r="R147" s="16"/>
       <c r="S147" s="16"/>
       <c r="T147" s="16"/>
+      <c r="U147" s="16"/>
+      <c r="V147" s="16"/>
+      <c r="W147" s="16"/>
+      <c r="X147" s="16"/>
+      <c r="Y147" s="16"/>
+      <c r="Z147" s="16"/>
+      <c r="AA147" s="16"/>
+      <c r="AB147" s="16"/>
+      <c r="AC147" s="16"/>
     </row>
-    <row r="148" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="66"/>
-      <c r="B148" s="42">
+    <row r="148" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="86"/>
+      <c r="B148" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="C148" s="69"/>
+      <c r="D148" s="69"/>
+      <c r="E148" s="70"/>
+      <c r="F148" s="16"/>
+      <c r="G148" s="16"/>
+      <c r="H148" s="16"/>
+      <c r="I148" s="16"/>
+      <c r="J148" s="16"/>
+      <c r="K148" s="16"/>
+      <c r="L148" s="16"/>
+      <c r="M148" s="16"/>
+      <c r="N148" s="16"/>
+      <c r="O148" s="16"/>
+      <c r="P148" s="16"/>
+      <c r="Q148" s="16"/>
+      <c r="R148" s="16"/>
+      <c r="S148" s="16"/>
+      <c r="T148" s="16"/>
+      <c r="U148" s="16"/>
+      <c r="V148" s="16"/>
+      <c r="W148" s="16"/>
+      <c r="X148" s="16"/>
+      <c r="Y148" s="16"/>
+      <c r="Z148" s="16"/>
+      <c r="AA148" s="16"/>
+      <c r="AB148" s="16"/>
+      <c r="AC148" s="16"/>
+    </row>
+    <row r="149" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="86"/>
+      <c r="B149" s="42" t="s">
+        <v>77</v>
+      </c>
+      <c r="C149" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="D149" s="25" t="s">
+        <v>112</v>
+      </c>
+      <c r="E149" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="F149" s="16"/>
+      <c r="G149" s="16"/>
+      <c r="H149" s="16"/>
+      <c r="I149" s="16"/>
+      <c r="J149" s="16"/>
+      <c r="K149" s="16"/>
+      <c r="L149" s="16"/>
+      <c r="M149" s="16"/>
+      <c r="N149" s="16"/>
+      <c r="O149" s="16"/>
+      <c r="P149" s="16"/>
+      <c r="Q149" s="16"/>
+      <c r="R149" s="16"/>
+      <c r="S149" s="16"/>
+      <c r="T149" s="16"/>
+      <c r="U149" s="16"/>
+      <c r="V149" s="16"/>
+      <c r="W149" s="16"/>
+      <c r="X149" s="16"/>
+      <c r="Y149" s="16"/>
+      <c r="Z149" s="16"/>
+      <c r="AA149" s="16"/>
+      <c r="AB149" s="16"/>
+      <c r="AC149" s="16"/>
+    </row>
+    <row r="150" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A150" s="86"/>
+      <c r="B150" s="15">
+        <v>1</v>
+      </c>
+      <c r="C150" s="40">
+        <f>C136/$B136</f>
+        <v>1</v>
+      </c>
+      <c r="D150" s="40">
+        <f>D136/$B136</f>
+        <v>1</v>
+      </c>
+      <c r="E150" s="40" t="e">
+        <f>E136/$B136</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F150" s="16"/>
+      <c r="G150" s="16"/>
+      <c r="H150" s="16"/>
+      <c r="I150" s="16"/>
+      <c r="J150" s="16"/>
+      <c r="K150" s="16"/>
+      <c r="L150" s="16"/>
+      <c r="M150" s="16"/>
+      <c r="N150" s="16"/>
+      <c r="O150" s="16"/>
+      <c r="P150" s="16"/>
+      <c r="Q150" s="16"/>
+      <c r="R150" s="16"/>
+      <c r="S150" s="16"/>
+      <c r="T150" s="16"/>
+      <c r="U150" s="16"/>
+      <c r="V150" s="16"/>
+      <c r="W150" s="16"/>
+      <c r="X150" s="16"/>
+      <c r="Y150" s="16"/>
+      <c r="Z150" s="16"/>
+      <c r="AA150" s="16"/>
+      <c r="AB150" s="16"/>
+      <c r="AC150" s="16"/>
+    </row>
+    <row r="151" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A151" s="86"/>
+      <c r="B151" s="15">
+        <v>2</v>
+      </c>
+      <c r="C151" s="40">
+        <f>C137/$B137</f>
+        <v>0.88441251364132412</v>
+      </c>
+      <c r="D151" s="40">
+        <f>D137/$B137</f>
+        <v>0.97463591922397685</v>
+      </c>
+      <c r="E151" s="40" t="e">
+        <f>E137/$B137</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F151" s="16"/>
+      <c r="G151" s="16"/>
+      <c r="H151" s="16"/>
+      <c r="I151" s="16"/>
+      <c r="J151" s="16"/>
+      <c r="K151" s="16"/>
+      <c r="L151" s="16"/>
+      <c r="M151" s="16"/>
+      <c r="N151" s="16"/>
+      <c r="O151" s="16"/>
+      <c r="P151" s="16"/>
+      <c r="Q151" s="16"/>
+      <c r="R151" s="16"/>
+      <c r="S151" s="16"/>
+      <c r="T151" s="16"/>
+      <c r="U151" s="16"/>
+      <c r="V151" s="16"/>
+      <c r="W151" s="16"/>
+      <c r="X151" s="16"/>
+      <c r="Y151" s="16"/>
+      <c r="Z151" s="16"/>
+      <c r="AA151" s="16"/>
+      <c r="AB151" s="16"/>
+      <c r="AC151" s="16"/>
+    </row>
+    <row r="152" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="86"/>
+      <c r="B152" s="15">
+        <v>4</v>
+      </c>
+      <c r="C152" s="40">
+        <f>C138/$B138</f>
+        <v>0.79039336801040316</v>
+      </c>
+      <c r="D152" s="40">
+        <f>D138/$B138</f>
+        <v>0.94716943587702718</v>
+      </c>
+      <c r="E152" s="40" t="e">
+        <f>E138/$B138</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F152" s="16"/>
+      <c r="G152" s="16"/>
+      <c r="H152" s="16"/>
+      <c r="I152" s="16"/>
+      <c r="J152" s="16"/>
+      <c r="K152" s="16"/>
+      <c r="L152" s="16"/>
+      <c r="M152" s="16"/>
+      <c r="N152" s="16"/>
+      <c r="O152" s="16"/>
+      <c r="P152" s="16"/>
+      <c r="Q152" s="16"/>
+      <c r="R152" s="16"/>
+      <c r="S152" s="16"/>
+      <c r="T152" s="16"/>
+      <c r="U152" s="16"/>
+      <c r="V152" s="16"/>
+      <c r="W152" s="16"/>
+      <c r="X152" s="16"/>
+      <c r="Y152" s="16"/>
+      <c r="Z152" s="16"/>
+      <c r="AA152" s="16"/>
+      <c r="AB152" s="16"/>
+      <c r="AC152" s="16"/>
+    </row>
+    <row r="153" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="86"/>
+      <c r="B153" s="15">
+        <v>6</v>
+      </c>
+      <c r="C153" s="40">
+        <f>C139/$B139</f>
+        <v>0.69207230287503563</v>
+      </c>
+      <c r="D153" s="40">
+        <f>D139/$B139</f>
+        <v>0.90260494441679118</v>
+      </c>
+      <c r="E153" s="40" t="e">
+        <f>E139/$B139</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F153" s="16"/>
+      <c r="G153" s="16"/>
+      <c r="H153" s="16"/>
+      <c r="I153" s="16"/>
+      <c r="J153" s="16"/>
+      <c r="K153" s="16"/>
+      <c r="L153" s="16"/>
+      <c r="M153" s="16"/>
+      <c r="N153" s="16"/>
+      <c r="O153" s="16"/>
+      <c r="P153" s="16"/>
+      <c r="Q153" s="16"/>
+      <c r="R153" s="16"/>
+      <c r="S153" s="16"/>
+      <c r="T153" s="16"/>
+      <c r="U153" s="16"/>
+      <c r="V153" s="16"/>
+      <c r="W153" s="16"/>
+      <c r="X153" s="16"/>
+      <c r="Y153" s="16"/>
+      <c r="Z153" s="16"/>
+      <c r="AA153" s="16"/>
+      <c r="AB153" s="16"/>
+      <c r="AC153" s="16"/>
+    </row>
+    <row r="154" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A154" s="86"/>
+      <c r="B154" s="15">
+        <v>8</v>
+      </c>
+      <c r="C154" s="40">
+        <f>C140/$B140</f>
+        <v>0.64660904255319152</v>
+      </c>
+      <c r="D154" s="40">
+        <f>D140/$B140</f>
+        <v>0.81437125748502992</v>
+      </c>
+      <c r="E154" s="40" t="e">
+        <f>E140/$B140</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F154" s="16"/>
+      <c r="G154" s="16"/>
+      <c r="H154" s="16"/>
+      <c r="I154" s="16"/>
+      <c r="J154" s="16"/>
+      <c r="K154" s="16"/>
+      <c r="L154" s="16"/>
+      <c r="M154" s="16"/>
+      <c r="N154" s="16"/>
+      <c r="O154" s="16"/>
+      <c r="P154" s="16"/>
+      <c r="Q154" s="16"/>
+      <c r="R154" s="16"/>
+      <c r="S154" s="16"/>
+      <c r="T154" s="16"/>
+      <c r="U154" s="16"/>
+      <c r="V154" s="16"/>
+      <c r="W154" s="16"/>
+      <c r="X154" s="16"/>
+      <c r="Y154" s="16"/>
+      <c r="Z154" s="16"/>
+      <c r="AA154" s="16"/>
+      <c r="AB154" s="16"/>
+      <c r="AC154" s="16"/>
+    </row>
+    <row r="155" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A155" s="86"/>
+      <c r="B155" s="15">
+        <v>10</v>
+      </c>
+      <c r="C155" s="40" t="e">
+        <f>C141/B141</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D155" s="40">
+        <f>D141/$B141</f>
+        <v>0.74953252632614897</v>
+      </c>
+      <c r="E155" s="40" t="e">
+        <f>E141/$B141</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F155" s="16"/>
+      <c r="G155" s="16"/>
+      <c r="H155" s="16"/>
+      <c r="I155" s="16"/>
+      <c r="J155" s="16"/>
+      <c r="K155" s="16"/>
+      <c r="L155" s="16"/>
+      <c r="M155" s="16"/>
+      <c r="N155" s="16"/>
+      <c r="O155" s="16"/>
+      <c r="P155" s="16"/>
+      <c r="Q155" s="16"/>
+      <c r="R155" s="16"/>
+      <c r="S155" s="16"/>
+      <c r="T155" s="16"/>
+      <c r="U155" s="16"/>
+      <c r="V155" s="16"/>
+      <c r="W155" s="16"/>
+      <c r="X155" s="16"/>
+      <c r="Y155" s="16"/>
+      <c r="Z155" s="16"/>
+      <c r="AA155" s="16"/>
+      <c r="AB155" s="16"/>
+      <c r="AC155" s="16"/>
+    </row>
+    <row r="156" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A156" s="86"/>
+      <c r="B156" s="15">
         <v>12</v>
       </c>
-      <c r="C148" s="40" t="e">
-        <f t="shared" si="7"/>
+      <c r="C156" s="40" t="e">
+        <f>C142/$B142</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D148" s="40" t="e">
-        <f t="shared" si="8"/>
+      <c r="D156" s="40">
+        <f>D142/$B142</f>
+        <v>0.81829121540312866</v>
+      </c>
+      <c r="E156" s="40" t="e">
+        <f>E142/$B142</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E148" s="40" t="e">
-        <f t="shared" si="8"/>
+      <c r="F156" s="31"/>
+      <c r="G156" s="31"/>
+      <c r="H156" s="31"/>
+      <c r="I156" s="31"/>
+      <c r="J156" s="31"/>
+      <c r="K156" s="31"/>
+      <c r="L156" s="31"/>
+      <c r="M156" s="31"/>
+      <c r="N156" s="31"/>
+      <c r="O156" s="31"/>
+      <c r="P156" s="31"/>
+      <c r="Q156" s="31"/>
+      <c r="R156" s="31"/>
+      <c r="S156" s="31"/>
+      <c r="T156" s="31"/>
+      <c r="U156" s="31"/>
+      <c r="V156" s="31"/>
+      <c r="W156" s="31"/>
+      <c r="X156" s="31"/>
+      <c r="Y156" s="31"/>
+      <c r="Z156" s="31"/>
+      <c r="AA156" s="31"/>
+      <c r="AB156" s="31"/>
+      <c r="AC156" s="31"/>
+    </row>
+    <row r="157" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A157" s="86"/>
+      <c r="B157" s="15">
+        <v>14</v>
+      </c>
+      <c r="C157" s="40" t="e">
+        <f>C143/$B143</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F148" s="31"/>
-      <c r="G148" s="31"/>
-      <c r="H148" s="31"/>
-      <c r="I148" s="31"/>
-      <c r="J148" s="31"/>
-      <c r="K148" s="31"/>
-      <c r="L148" s="31"/>
-      <c r="M148" s="31"/>
-      <c r="N148" s="31"/>
-      <c r="O148" s="31"/>
-      <c r="P148" s="31"/>
-      <c r="Q148" s="31"/>
-      <c r="R148" s="31"/>
-      <c r="S148" s="31"/>
-      <c r="T148" s="31"/>
+      <c r="D157" s="40">
+        <f>D143/$B143</f>
+        <v>0.69842084991654896</v>
+      </c>
+      <c r="E157" s="40" t="e">
+        <f>E143/$B143</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F157" s="31"/>
+      <c r="G157" s="31"/>
+      <c r="H157" s="31"/>
+      <c r="I157" s="31"/>
+      <c r="J157" s="31"/>
+      <c r="K157" s="31"/>
+      <c r="L157" s="31"/>
+      <c r="M157" s="31"/>
+      <c r="N157" s="31"/>
+      <c r="O157" s="31"/>
+      <c r="P157" s="31"/>
+      <c r="Q157" s="31"/>
+      <c r="R157" s="31"/>
+      <c r="S157" s="31"/>
+      <c r="T157" s="31"/>
+      <c r="U157" s="31"/>
+      <c r="V157" s="31"/>
+      <c r="W157" s="31"/>
+      <c r="X157" s="31"/>
+      <c r="Y157" s="31"/>
+      <c r="Z157" s="31"/>
+      <c r="AA157" s="31"/>
+      <c r="AB157" s="31"/>
+      <c r="AC157" s="31"/>
     </row>
-    <row r="149" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="66"/>
-      <c r="B149" s="42">
+    <row r="158" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A158" s="86"/>
+      <c r="B158" s="15">
         <v>16</v>
       </c>
-      <c r="C149" s="40" t="e">
-        <f t="shared" si="7"/>
+      <c r="C158" s="40" t="e">
+        <f>C144/$B144</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D149" s="40" t="e">
-        <f t="shared" si="8"/>
+      <c r="D158" s="40">
+        <f>D144/$B144</f>
+        <v>0.67623241937775247</v>
+      </c>
+      <c r="E158" s="40" t="e">
+        <f>E144/$B144</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E149" s="40" t="e">
-        <f t="shared" si="8"/>
+      <c r="F158" s="16"/>
+      <c r="G158" s="16"/>
+      <c r="H158" s="16"/>
+      <c r="I158" s="16"/>
+      <c r="J158" s="16"/>
+      <c r="K158" s="16"/>
+      <c r="L158" s="16"/>
+      <c r="M158" s="16"/>
+      <c r="N158" s="16"/>
+      <c r="O158" s="16"/>
+      <c r="P158" s="16"/>
+      <c r="Q158" s="16"/>
+      <c r="R158" s="16"/>
+      <c r="S158" s="16"/>
+      <c r="T158" s="16"/>
+      <c r="U158" s="16"/>
+      <c r="V158" s="16"/>
+      <c r="W158" s="16"/>
+      <c r="X158" s="16"/>
+      <c r="Y158" s="16"/>
+      <c r="Z158" s="16"/>
+      <c r="AA158" s="16"/>
+      <c r="AB158" s="16"/>
+      <c r="AC158" s="16"/>
+    </row>
+    <row r="159" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A159" s="86"/>
+      <c r="B159" s="15">
+        <v>18</v>
+      </c>
+      <c r="C159" s="40" t="e">
+        <f>C145/$B145</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F149" s="31"/>
-      <c r="G149" s="31"/>
-      <c r="H149" s="31"/>
-      <c r="I149" s="31"/>
-      <c r="J149" s="31"/>
-      <c r="K149" s="31"/>
-      <c r="L149" s="31"/>
-      <c r="M149" s="31"/>
-      <c r="N149" s="31"/>
-      <c r="O149" s="31"/>
-      <c r="P149" s="31"/>
-      <c r="Q149" s="31"/>
-      <c r="R149" s="31"/>
-      <c r="S149" s="31"/>
-      <c r="T149" s="31"/>
+      <c r="D159" s="40">
+        <f>D145/$B145</f>
+        <v>0.68232722320772643</v>
+      </c>
+      <c r="E159" s="40" t="e">
+        <f>E145/$B145</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F159" s="16"/>
+      <c r="G159" s="16"/>
+      <c r="H159" s="16"/>
+      <c r="I159" s="16"/>
+      <c r="J159" s="16"/>
+      <c r="K159" s="16"/>
+      <c r="L159" s="16"/>
+      <c r="M159" s="16"/>
+      <c r="N159" s="16"/>
+      <c r="O159" s="16"/>
+      <c r="P159" s="16"/>
+      <c r="Q159" s="16"/>
+      <c r="R159" s="16"/>
+      <c r="S159" s="16"/>
+      <c r="T159" s="16"/>
+      <c r="U159" s="16"/>
+      <c r="V159" s="16"/>
+      <c r="W159" s="16"/>
+      <c r="X159" s="16"/>
+      <c r="Y159" s="16"/>
+      <c r="Z159" s="16"/>
+      <c r="AA159" s="16"/>
+      <c r="AB159" s="16"/>
+      <c r="AC159" s="16"/>
     </row>
-    <row r="150" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="83"/>
-      <c r="B150" s="33" t="s">
+    <row r="160" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A160" s="86"/>
+      <c r="B160" s="15">
+        <v>20</v>
+      </c>
+      <c r="C160" s="40" t="e">
+        <f>C146/$B146</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D160" s="40">
+        <f>D146/$B146</f>
+        <v>0.62879788639365919</v>
+      </c>
+      <c r="E160" s="40" t="e">
+        <f>E146/$B146</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F160" s="16"/>
+      <c r="G160" s="16"/>
+      <c r="H160" s="16"/>
+      <c r="I160" s="16"/>
+      <c r="J160" s="16"/>
+      <c r="K160" s="16"/>
+      <c r="L160" s="16"/>
+      <c r="M160" s="16"/>
+      <c r="N160" s="16"/>
+      <c r="O160" s="16"/>
+      <c r="P160" s="16"/>
+      <c r="Q160" s="16"/>
+      <c r="R160" s="16"/>
+      <c r="S160" s="16"/>
+      <c r="T160" s="16"/>
+      <c r="U160" s="16"/>
+      <c r="V160" s="16"/>
+      <c r="W160" s="16"/>
+      <c r="X160" s="16"/>
+      <c r="Y160" s="16"/>
+      <c r="Z160" s="16"/>
+      <c r="AA160" s="16"/>
+      <c r="AB160" s="16"/>
+      <c r="AC160" s="16"/>
+    </row>
+    <row r="161" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="86"/>
+      <c r="B161" s="15">
+        <v>40</v>
+      </c>
+      <c r="C161" s="40" t="e">
+        <f>C147/$B147</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D161" s="40">
+        <f>D147/$B147</f>
+        <v>0.27811860940695293</v>
+      </c>
+      <c r="E161" s="40" t="e">
+        <f>E147/$B147</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F161" s="16"/>
+      <c r="G161" s="16"/>
+      <c r="H161" s="16"/>
+      <c r="I161" s="16"/>
+      <c r="J161" s="16"/>
+      <c r="K161" s="16"/>
+      <c r="L161" s="16"/>
+      <c r="M161" s="16"/>
+      <c r="N161" s="16"/>
+      <c r="O161" s="16"/>
+      <c r="P161" s="16"/>
+      <c r="Q161" s="16"/>
+      <c r="R161" s="16"/>
+      <c r="S161" s="16"/>
+      <c r="T161" s="16"/>
+      <c r="U161" s="16"/>
+      <c r="V161" s="16"/>
+      <c r="W161" s="16"/>
+      <c r="X161" s="16"/>
+      <c r="Y161" s="16"/>
+      <c r="Z161" s="16"/>
+      <c r="AA161" s="16"/>
+      <c r="AB161" s="16"/>
+      <c r="AC161" s="16"/>
+    </row>
+    <row r="162" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A162" s="86"/>
+      <c r="B162" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="C150" s="86"/>
-      <c r="D150" s="87"/>
-      <c r="E150" s="87"/>
-      <c r="F150" s="87"/>
-      <c r="G150" s="87"/>
-      <c r="H150" s="87"/>
-      <c r="I150" s="87"/>
-      <c r="J150" s="87"/>
-      <c r="K150" s="87"/>
-      <c r="L150" s="87"/>
-      <c r="M150" s="87"/>
-      <c r="N150" s="87"/>
-      <c r="O150" s="87"/>
-      <c r="P150" s="87"/>
-      <c r="Q150" s="87"/>
-      <c r="R150" s="87"/>
-      <c r="S150" s="87"/>
-      <c r="T150" s="88"/>
+      <c r="C162" s="65"/>
+      <c r="D162" s="66"/>
+      <c r="E162" s="66"/>
+      <c r="F162" s="66"/>
+      <c r="G162" s="66"/>
+      <c r="H162" s="66"/>
+      <c r="I162" s="66"/>
+      <c r="J162" s="66"/>
+      <c r="K162" s="66"/>
+      <c r="L162" s="66"/>
+      <c r="M162" s="66"/>
+      <c r="N162" s="66"/>
+      <c r="O162" s="66"/>
+      <c r="P162" s="66"/>
+      <c r="Q162" s="66"/>
+      <c r="R162" s="66"/>
+      <c r="S162" s="66"/>
+      <c r="T162" s="66"/>
+      <c r="U162" s="66"/>
+      <c r="V162" s="66"/>
+      <c r="W162" s="66"/>
+      <c r="X162" s="66"/>
+      <c r="Y162" s="66"/>
+      <c r="Z162" s="66"/>
+      <c r="AA162" s="66"/>
+      <c r="AB162" s="66"/>
+      <c r="AC162" s="67"/>
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="A120:A150"/>
-    <mergeCell ref="A89:A119"/>
-    <mergeCell ref="C119:T119"/>
-    <mergeCell ref="B89:E89"/>
-    <mergeCell ref="B99:E99"/>
-    <mergeCell ref="B109:E109"/>
-    <mergeCell ref="B140:E140"/>
-    <mergeCell ref="B130:E130"/>
-    <mergeCell ref="B120:E120"/>
-    <mergeCell ref="C150:T150"/>
-    <mergeCell ref="A24:L24"/>
-    <mergeCell ref="M24:N24"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="C12:N12"/>
-    <mergeCell ref="A2:A12"/>
-    <mergeCell ref="A13:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:N23"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B2:D2"/>
     <mergeCell ref="O88:T88"/>
     <mergeCell ref="A88:N88"/>
     <mergeCell ref="A57:A87"/>
@@ -39340,6 +40470,27 @@
     <mergeCell ref="B45:D45"/>
     <mergeCell ref="B35:D35"/>
     <mergeCell ref="B25:D25"/>
+    <mergeCell ref="A24:L24"/>
+    <mergeCell ref="M24:N24"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="C12:N12"/>
+    <mergeCell ref="A2:A12"/>
+    <mergeCell ref="A13:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:N23"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="A89:A119"/>
+    <mergeCell ref="C119:T119"/>
+    <mergeCell ref="B89:E89"/>
+    <mergeCell ref="B99:E99"/>
+    <mergeCell ref="B109:E109"/>
+    <mergeCell ref="B148:E148"/>
+    <mergeCell ref="B134:E134"/>
+    <mergeCell ref="B120:E120"/>
+    <mergeCell ref="A120:A162"/>
+    <mergeCell ref="C162:AC162"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <hyperlinks>
@@ -39359,7 +40510,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4269BDC4-CFAE-4A4A-95F0-395DE59C8746}">
-  <dimension ref="M10:M14"/>
+  <dimension ref="M10:M23"/>
   <sheetFormatPr defaultRowHeight="22.1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="16384" width="9.140625" style="41"/>
@@ -39390,6 +40541,41 @@
         <v>101</v>
       </c>
     </row>
+    <row r="17" spans="13:13" x14ac:dyDescent="0.3">
+      <c r="M17" s="44" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="18" spans="13:13" x14ac:dyDescent="0.3">
+      <c r="M18" s="41" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="19" spans="13:13" x14ac:dyDescent="0.3">
+      <c r="M19" s="41" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="20" spans="13:13" x14ac:dyDescent="0.3">
+      <c r="M20" s="41" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="21" spans="13:13" x14ac:dyDescent="0.3">
+      <c r="M21" s="41" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="22" spans="13:13" x14ac:dyDescent="0.3">
+      <c r="M22" s="41" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="23" spans="13:13" x14ac:dyDescent="0.3">
+      <c r="M23" s="41" t="s">
+        <v>122</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/DecompositionLU/docs/statistics.xlsx
+++ b/DecompositionLU/docs/statistics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maxim\source\repos\practice\SECOND_COURSE\FOR_ITLAB\ArchBenchs\DecompositionLU\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{889A587D-CBA0-45E5-847D-B55C9EF9927A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10EC723C-D471-490B-9B42-2551FCE50A64}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-114" yWindow="-114" windowWidth="27602" windowHeight="15027" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="125">
   <si>
     <t>Я не уверен, будет ли это использоваться в готовой презентации и так ли это надо делать, если да, так что пока считаем, что файл для личного пользования.</t>
   </si>
@@ -473,6 +473,36 @@
   <si>
     <t>Мне нравятся результаты, но есть ощущение, что можно лучше. Графики точно не самые хорошие.</t>
   </si>
+  <si>
+    <t>окак</t>
+  </si>
+  <si>
+    <t>Про кластер:</t>
+  </si>
+  <si>
+    <t>[simonov_m@master build]$ lscpu | grep -E "^(CPU\(s\)|Core\(s\) per socket|Socket\(s\)|NUMA)"</t>
+  </si>
+  <si>
+    <t>CPU(s):                8</t>
+  </si>
+  <si>
+    <t>Core(s) per socket:    1</t>
+  </si>
+  <si>
+    <t>Socket(s):             8</t>
+  </si>
+  <si>
+    <t>NUMA node(s):          1</t>
+  </si>
+  <si>
+    <t>NUMA node0 CPU(s):     0-7</t>
+  </si>
+  <si>
+    <t>n = 15000</t>
+  </si>
+  <si>
+    <t>В ходе работы выяснил следующее - на миникластере 2 процессора по 10 физ ядер, балансировать их надо так: число потоков &lt;= 10 - все на одном, &gt;10 - поровну, но на каждом четное количество.</t>
+  </si>
 </sst>
 </file>
 
@@ -621,7 +651,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -658,8 +688,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="15">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -827,12 +863,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -1038,22 +1083,25 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -8805,7 +8853,19 @@
               <a:rPr lang="en-US" baseline="0">
                 <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
               </a:rPr>
-              <a:t> = 5000</a:t>
+              <a:t> = </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ru-RU" baseline="0">
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t>5</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0">
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t>000</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -8846,108 +8906,8 @@
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="0"/>
+          <c:idx val="1"/>
           <c:order val="0"/>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:srgbClr val="FF0000"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Графики!$B$37:$B$44</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>16</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Графики!$D$132:$D$139</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-A20B-40B3-98AD-69AA8CF4691F}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
           <c:tx>
             <c:v>Целевое значение</c:v>
           </c:tx>
@@ -8985,10 +8945,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Графики!$B$37:$B$44</c:f>
+              <c:f>Графики!$B$136:$B$147</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -9011,17 +8971,29 @@
                   <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>40</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Графики!$B$37:$B$44</c:f>
+              <c:f>Графики!$B$136:$B$146</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -9044,7 +9016,16 @@
                   <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9052,7 +9033,125 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-A20B-40B3-98AD-69AA8CF4691F}"/>
+              <c16:uniqueId val="{00000001-A557-493F-A449-73115457C681}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Графики!$B$136:$B$146</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Графики!$C$136:$C$146</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.7688250272826482</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.1615734720416127</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.1524338172502135</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.1728723404255321</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.8939393939393936</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>6.7770034843205575</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7.3786039453717756</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>7.9517579721995091</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>8.2695578231292526</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>9.1143392689784442</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A557-493F-A449-73115457C681}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -9128,6 +9227,7 @@
         <c:crossAx val="1826559071"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
+        <c:majorUnit val="2"/>
       </c:valAx>
       <c:valAx>
         <c:axId val="1826559071"/>
@@ -9190,6 +9290,7 @@
         <c:crossAx val="1871156463"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
+        <c:majorUnit val="2"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -9286,7 +9387,19 @@
               <a:rPr lang="en-US" baseline="0">
                 <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
               </a:rPr>
-              <a:t> = 5000</a:t>
+              <a:t> = </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ru-RU" baseline="0">
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t>5</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0">
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t>000</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -9327,108 +9440,8 @@
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="0"/>
+          <c:idx val="1"/>
           <c:order val="0"/>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:srgbClr val="FF0000"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Графики!$B$37:$B$44</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>16</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Графики!$D$142:$D$149</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-A273-46FB-A63A-FB8B69BD5D41}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
           <c:tx>
             <c:v>Целевое значение</c:v>
           </c:tx>
@@ -9466,10 +9479,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Графики!$B$37:$B$44</c:f>
+              <c:f>Графики!$B$150:$B$160</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -9492,7 +9505,16 @@
                   <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9500,7 +9522,7 @@
           <c:yVal>
             <c:numLit>
               <c:formatCode>General</c:formatCode>
-              <c:ptCount val="8"/>
+              <c:ptCount val="11"/>
               <c:pt idx="0">
                 <c:v>1</c:v>
               </c:pt>
@@ -9525,12 +9547,139 @@
               <c:pt idx="7">
                 <c:v>1</c:v>
               </c:pt>
+              <c:pt idx="8">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="9">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="10">
+                <c:v>1</c:v>
+              </c:pt>
             </c:numLit>
           </c:yVal>
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-A273-46FB-A63A-FB8B69BD5D41}"/>
+              <c16:uniqueId val="{00000001-0B96-43F7-986F-ADA288A8DECA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Графики!$B$150:$B$160</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Графики!$C$150:$C$160</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.88441251364132412</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.79039336801040316</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.69207230287503563</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.64660904255319152</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.58939393939393936</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.56475029036004643</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.52704313895512678</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.49698487326246932</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.45941987906273624</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.45571696344892221</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0B96-43F7-986F-ADA288A8DECA}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -9606,6 +9755,7 @@
         <c:crossAx val="1826559071"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
+        <c:majorUnit val="2"/>
       </c:valAx>
       <c:valAx>
         <c:axId val="1826559071"/>
@@ -9764,7 +9914,19 @@
               <a:rPr lang="en-US" baseline="0">
                 <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
               </a:rPr>
-              <a:t> = 5000</a:t>
+              <a:t> = </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ru-RU" baseline="0">
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t>5</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0">
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t>000</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -9810,7 +9972,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:srgbClr val="FF0000"/>
+                <a:schemeClr val="accent2"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -9821,11 +9983,11 @@
             <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="FF0000"/>
+                <a:schemeClr val="accent2"/>
               </a:solidFill>
               <a:ln w="9525">
                 <a:solidFill>
-                  <a:srgbClr val="FF0000"/>
+                  <a:schemeClr val="accent2"/>
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
@@ -9833,10 +9995,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Графики!$B$37:$B$44</c:f>
+              <c:f>Графики!$B$122:$B$132</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -9859,24 +10021,66 @@
                   <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Графики!$D$122:$D$129</c:f>
+              <c:f>Графики!$C$122:$C$132</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>9725</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5498</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3076</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2342</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1880</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1650</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1435</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1318</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1223</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1176</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1067</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-B24B-46CE-9C90-667175EBAFB1}"/>
+              <c16:uniqueId val="{00000000-637E-4817-9C47-33391629FBA9}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -9952,6 +10156,7 @@
         <c:crossAx val="1826559071"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
+        <c:majorUnit val="2"/>
       </c:valAx>
       <c:valAx>
         <c:axId val="1826559071"/>
@@ -10110,7 +10315,19 @@
               <a:rPr lang="en-US" baseline="0">
                 <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
               </a:rPr>
-              <a:t> = 3000</a:t>
+              <a:t> = </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ru-RU" baseline="0">
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t>10</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0">
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t>000</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -10156,7 +10373,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:srgbClr val="FF0000"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -10167,11 +10384,11 @@
             <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:srgbClr val="FF0000"/>
               </a:solidFill>
               <a:ln w="9525">
                 <a:solidFill>
-                  <a:schemeClr val="accent2"/>
+                  <a:srgbClr val="FF0000"/>
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
@@ -10179,10 +10396,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Графики!$B$37:$B$44</c:f>
+              <c:f>Графики!$B$122:$B$132</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -10205,40 +10422,58 @@
                   <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Графики!$C$132:$C$139</c:f>
+              <c:f>Графики!$D$122:$D$132</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>76160</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>39071</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>20102</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>14063</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>11690</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>10161</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>8034</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>7301</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6821</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>6201</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>6056</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10246,118 +10481,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-A557-493F-A449-73115457C681}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:v>Целевое значение</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="bg1">
-                  <a:lumMod val="65000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:prstDash val="sysDash"/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="bg1">
-                  <a:lumMod val="65000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="bg1">
-                    <a:lumMod val="65000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:prstDash val="sysDash"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Графики!$B$37:$B$44</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>16</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Графики!$B$37:$B$44</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>16</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-A557-493F-A449-73115457C681}"/>
+              <c16:uniqueId val="{00000000-3AEF-4894-805C-216D9CE5104E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -10433,6 +10557,7 @@
         <c:crossAx val="1826559071"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
+        <c:majorUnit val="2"/>
       </c:valAx>
       <c:valAx>
         <c:axId val="1826559071"/>
@@ -10791,7 +10916,19 @@
               <a:rPr lang="en-US" baseline="0">
                 <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
               </a:rPr>
-              <a:t> = 3000</a:t>
+              <a:t> = </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ru-RU" baseline="0">
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t>15</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0">
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t>000</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -10837,7 +10974,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:srgbClr val="C00000"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -10848,11 +10985,11 @@
             <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:srgbClr val="C00000"/>
               </a:solidFill>
               <a:ln w="9525">
                 <a:solidFill>
-                  <a:schemeClr val="accent2"/>
+                  <a:srgbClr val="C00000"/>
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
@@ -10860,10 +10997,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Графики!$B$37:$B$44</c:f>
+              <c:f>Графики!$B$122:$B$132</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -10886,40 +11023,37 @@
                   <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Графики!$C$142:$C$149</c:f>
+              <c:f>Графики!$E$122:$E$132</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0</c:v>
-                </c:pt>
+                <c:ptCount val="11"/>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>23660</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>21062</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>20637</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>18311</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10927,115 +11061,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-0B96-43F7-986F-ADA288A8DECA}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:v>Целевое значение</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="bg1">
-                  <a:lumMod val="65000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:prstDash val="sysDash"/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="bg1">
-                  <a:lumMod val="65000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="bg1">
-                    <a:lumMod val="65000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:prstDash val="sysDash"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Графики!$B$37:$B$44</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>16</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numLit>
-              <c:formatCode>General</c:formatCode>
-              <c:ptCount val="8"/>
-              <c:pt idx="0">
-                <c:v>1</c:v>
-              </c:pt>
-              <c:pt idx="1">
-                <c:v>1</c:v>
-              </c:pt>
-              <c:pt idx="2">
-                <c:v>1</c:v>
-              </c:pt>
-              <c:pt idx="3">
-                <c:v>1</c:v>
-              </c:pt>
-              <c:pt idx="4">
-                <c:v>1</c:v>
-              </c:pt>
-              <c:pt idx="5">
-                <c:v>1</c:v>
-              </c:pt>
-              <c:pt idx="6">
-                <c:v>1</c:v>
-              </c:pt>
-              <c:pt idx="7">
-                <c:v>1</c:v>
-              </c:pt>
-            </c:numLit>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-0B96-43F7-986F-ADA288A8DECA}"/>
+              <c16:uniqueId val="{00000000-29DE-46B5-99D0-81F81045F765}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -11111,6 +11137,7 @@
         <c:crossAx val="1826559071"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
+        <c:majorUnit val="2"/>
       </c:valAx>
       <c:valAx>
         <c:axId val="1826559071"/>
@@ -11269,7 +11296,19 @@
               <a:rPr lang="en-US" baseline="0">
                 <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
               </a:rPr>
-              <a:t> = 3000</a:t>
+              <a:t> = </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="ru-RU" baseline="0">
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t>15</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0">
+                <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t>000</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -11310,12 +11349,141 @@
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="0"/>
+          <c:idx val="1"/>
           <c:order val="0"/>
+          <c:tx>
+            <c:v>Целевое значение</c:v>
+          </c:tx>
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="65000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:prstDash val="sysDash"/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="65000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="bg1">
+                    <a:lumMod val="65000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:prstDash val="sysDash"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Графики!$B$136:$B$146</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Графики!$B$136:$B$146</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4B1F-4C7F-AC86-ECAA526DC8D6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -11326,11 +11494,11 @@
             <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:srgbClr val="C00000"/>
               </a:solidFill>
               <a:ln w="9525">
                 <a:solidFill>
-                  <a:schemeClr val="accent2"/>
+                  <a:srgbClr val="C00000"/>
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
@@ -11338,10 +11506,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Графики!$B$37:$B$44</c:f>
+              <c:f>Графики!$B$136:$B$146</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -11364,24 +11532,66 @@
                   <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Графики!$C$122:$C$129</c:f>
+              <c:f>Графики!$E$136:$E$146</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-637E-4817-9C47-33391629FBA9}"/>
+              <c16:uniqueId val="{00000001-4B1F-4C7F-AC86-ECAA526DC8D6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -11457,6 +11667,7 @@
         <c:crossAx val="1826559071"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
+        <c:majorUnit val="2"/>
       </c:valAx>
       <c:valAx>
         <c:axId val="1826559071"/>
@@ -11519,6 +11730,7 @@
         <c:crossAx val="1871156463"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
+        <c:majorUnit val="2"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -11668,108 +11880,8 @@
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="0"/>
+          <c:idx val="1"/>
           <c:order val="0"/>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:srgbClr val="C00000"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="C00000"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:srgbClr val="C00000"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Графики!$B$37:$B$44</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>16</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Графики!$E$132:$E$139</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-FBFA-4E74-82F6-609D55138937}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
           <c:tx>
             <c:v>Целевое значение</c:v>
           </c:tx>
@@ -11807,10 +11919,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Графики!$B$37:$B$44</c:f>
+              <c:f>Графики!$B$136:$B$146</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -11833,17 +11945,26 @@
                   <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Графики!$B$37:$B$44</c:f>
+              <c:f>Графики!$B$136:$B$146</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -11866,7 +11987,16 @@
                   <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11874,7 +12004,128 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-FBFA-4E74-82F6-609D55138937}"/>
+              <c16:uniqueId val="{00000000-8171-4E0C-9281-B9205E5691E5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Графики!$B$136:$B$146</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Графики!$D$136:$D$147</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.9492718384479537</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.7886777435081087</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5.4156296665007471</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.5149700598802394</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7.4953252632614902</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9.4797112272840423</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>10.431447746883988</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>11.165518252455652</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>12.281890017739075</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>12.575957727873183</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11.124744376278118</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-8171-4E0C-9281-B9205E5691E5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -11950,6 +12201,7 @@
         <c:crossAx val="1826559071"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
+        <c:majorUnit val="2"/>
       </c:valAx>
       <c:valAx>
         <c:axId val="1826559071"/>
@@ -12012,6 +12264,7 @@
         <c:crossAx val="1871156463"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
+        <c:majorUnit val="2"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -12114,7 +12367,7 @@
               <a:rPr lang="ru-RU" baseline="0">
                 <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
               </a:rPr>
-              <a:t>10</a:t>
+              <a:t>15</a:t>
             </a:r>
             <a:r>
               <a:rPr lang="en-US" baseline="0">
@@ -12161,108 +12414,8 @@
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="0"/>
+          <c:idx val="1"/>
           <c:order val="0"/>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:srgbClr val="C00000"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="C00000"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:srgbClr val="C00000"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>Графики!$B$37:$B$44</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>16</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>Графики!$E$142:$E$149</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-F008-4072-9DA7-D43656FF6178}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
           <c:tx>
             <c:v>Целевое значение</c:v>
           </c:tx>
@@ -12300,10 +12453,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Графики!$B$37:$B$44</c:f>
+              <c:f>Графики!$B$150:$B$160</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -12326,7 +12479,16 @@
                   <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12334,7 +12496,7 @@
           <c:yVal>
             <c:numLit>
               <c:formatCode>General</c:formatCode>
-              <c:ptCount val="8"/>
+              <c:ptCount val="11"/>
               <c:pt idx="0">
                 <c:v>1</c:v>
               </c:pt>
@@ -12359,12 +12521,139 @@
               <c:pt idx="7">
                 <c:v>1</c:v>
               </c:pt>
+              <c:pt idx="8">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="9">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="10">
+                <c:v>1</c:v>
+              </c:pt>
             </c:numLit>
           </c:yVal>
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-F008-4072-9DA7-D43656FF6178}"/>
+              <c16:uniqueId val="{00000000-5E37-4B39-9139-AFEE8B2EE215}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="C00000"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="C00000"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Графики!$B$150:$B$160</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Графики!$E$150:$E$160</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-5E37-4B39-9139-AFEE8B2EE215}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -12440,6 +12729,7 @@
         <c:crossAx val="1826559071"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
+        <c:majorUnit val="2"/>
       </c:valAx>
       <c:valAx>
         <c:axId val="1826559071"/>
@@ -12651,12 +12941,141 @@
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="0"/>
+          <c:idx val="1"/>
           <c:order val="0"/>
+          <c:tx>
+            <c:v>Целевое значение</c:v>
+          </c:tx>
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:srgbClr val="C00000"/>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="65000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:prstDash val="sysDash"/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="65000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="bg1">
+                    <a:lumMod val="65000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:prstDash val="sysDash"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Графики!$B$150:$B$161</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>40</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="11"/>
+              <c:pt idx="0">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="5">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="6">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="7">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="8">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="9">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="10">
+                <c:v>1</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-578B-4D7D-B648-11824E830792}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -12667,11 +13086,11 @@
             <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="C00000"/>
+                <a:srgbClr val="FF0000"/>
               </a:solidFill>
               <a:ln w="9525">
                 <a:solidFill>
-                  <a:srgbClr val="C00000"/>
+                  <a:srgbClr val="FF0000"/>
                 </a:solidFill>
               </a:ln>
               <a:effectLst/>
@@ -12679,10 +13098,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Графики!$B$37:$B$44</c:f>
+              <c:f>Графики!$B$150:$B$160</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="11"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -12705,24 +13124,66 @@
                   <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>20</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Графики!$E$122:$E$129</c:f>
+              <c:f>Графики!$D$150:$D$160</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.97463591922397685</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.94716943587702718</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.90260494441679118</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.81437125748502992</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.74953252632614897</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.78997593560700352</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.74510341049171347</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.69784489077847822</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.68232722320772643</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.62879788639365919</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-29DE-41B5-9D11-9A68295C2254}"/>
+              <c16:uniqueId val="{00000001-578B-4D7D-B648-11824E830792}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -12798,6 +13259,7 @@
         <c:crossAx val="1826559071"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
+        <c:majorUnit val="2"/>
       </c:valAx>
       <c:valAx>
         <c:axId val="1826559071"/>
@@ -33371,23 +33833,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
+      <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>129</xdr:row>
+      <xdr:row>133</xdr:row>
       <xdr:rowOff>25868</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>875168</xdr:colOff>
-      <xdr:row>139</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>12934</xdr:colOff>
+      <xdr:row>147</xdr:row>
+      <xdr:rowOff>22665</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="55" name="Диаграмма 54">
+        <xdr:cNvPr id="58" name="Диаграмма 57">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C26A85B-1544-4476-BA3E-E163143F8F20}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8AEB44A-4667-4483-BC2D-CB23B4E2955C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -33409,23 +33871,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>139</xdr:row>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1358019</xdr:colOff>
+      <xdr:row>147</xdr:row>
       <xdr:rowOff>25866</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>875168</xdr:colOff>
-      <xdr:row>149</xdr:row>
-      <xdr:rowOff>4</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>879478</xdr:colOff>
+      <xdr:row>160</xdr:row>
+      <xdr:rowOff>271061</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="56" name="Диаграмма 55">
+        <xdr:cNvPr id="59" name="Диаграмма 58">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{538EF4CE-AF43-43C7-8035-A8735C42395E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{85889AAC-9BD8-4731-8A8C-7AC78E85257A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -33447,23 +33909,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1358019</xdr:colOff>
       <xdr:row>119</xdr:row>
       <xdr:rowOff>25866</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>875168</xdr:colOff>
-      <xdr:row>129</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>879478</xdr:colOff>
+      <xdr:row>132</xdr:row>
+      <xdr:rowOff>271059</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="57" name="Диаграмма 56">
+        <xdr:cNvPr id="60" name="Диаграмма 59">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E211DB4-80EC-4216-A845-F915B4157AE8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45899311-6625-49BE-9FD4-424B17CCB595}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -33485,23 +33947,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>129</xdr:row>
-      <xdr:rowOff>25868</xdr:rowOff>
+      <xdr:row>119</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>875169</xdr:colOff>
-      <xdr:row>139</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>880388</xdr:colOff>
+      <xdr:row>132</xdr:row>
+      <xdr:rowOff>245738</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="58" name="Диаграмма 57">
+        <xdr:cNvPr id="36" name="Диаграмма 35">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8AEB44A-4667-4483-BC2D-CB23B4E2955C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C32472AA-ADFA-4D1E-922D-02DF8A983CB2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -33523,23 +33985,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>139</xdr:row>
-      <xdr:rowOff>25866</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>119</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>875169</xdr:colOff>
-      <xdr:row>149</xdr:row>
-      <xdr:rowOff>4</xdr:rowOff>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>478541</xdr:colOff>
+      <xdr:row>132</xdr:row>
+      <xdr:rowOff>249817</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="59" name="Диаграмма 58">
+        <xdr:cNvPr id="64" name="Диаграмма 63">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{85889AAC-9BD8-4731-8A8C-7AC78E85257A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00FAE3B6-E51C-41A7-9789-ECDE2BA58830}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -33561,23 +34023,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
+      <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>119</xdr:row>
-      <xdr:rowOff>25866</xdr:rowOff>
+      <xdr:row>133</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>875169</xdr:colOff>
-      <xdr:row>129</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>465606</xdr:colOff>
+      <xdr:row>146</xdr:row>
+      <xdr:rowOff>260664</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="60" name="Диаграмма 59">
+        <xdr:cNvPr id="65" name="Диаграмма 64">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45899311-6625-49BE-9FD4-424B17CCB595}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C1664293-10B8-4A11-80A9-92103D22DD45}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -33599,23 +34061,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>129</xdr:row>
-      <xdr:rowOff>25868</xdr:rowOff>
+      <xdr:row>133</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>875169</xdr:colOff>
-      <xdr:row>139</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>892413</xdr:colOff>
+      <xdr:row>146</xdr:row>
+      <xdr:rowOff>252926</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="61" name="Диаграмма 60">
+        <xdr:cNvPr id="66" name="Диаграмма 65">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E39445A9-578D-44A4-B26A-5591270DB59B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BEB75FEF-420F-48A2-910F-203FF699D7B9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -33637,23 +34099,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
+      <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>139</xdr:row>
-      <xdr:rowOff>25866</xdr:rowOff>
+      <xdr:row>146</xdr:row>
+      <xdr:rowOff>271603</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>875169</xdr:colOff>
-      <xdr:row>149</xdr:row>
-      <xdr:rowOff>4</xdr:rowOff>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>452673</xdr:colOff>
+      <xdr:row>160</xdr:row>
+      <xdr:rowOff>252933</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="62" name="Диаграмма 61">
+        <xdr:cNvPr id="67" name="Диаграмма 66">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0DD1AF4D-C7D7-4261-8E89-DF3584759784}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E6D0036-B959-4770-A365-ADBF567038F4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -33675,23 +34137,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>119</xdr:row>
-      <xdr:rowOff>25866</xdr:rowOff>
+      <xdr:row>146</xdr:row>
+      <xdr:rowOff>271603</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>875169</xdr:colOff>
-      <xdr:row>129</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>160</xdr:row>
+      <xdr:rowOff>260671</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="63" name="Диаграмма 62">
+        <xdr:cNvPr id="68" name="Диаграмма 67">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{246C40BD-AF51-4D5F-AE81-0E6DE176CDBB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BEC6F7B1-5C2F-41E0-B6B6-0259E9BB524D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -35045,7 +35507,7 @@
       <c r="D64" s="54"/>
       <c r="E64" s="54"/>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
         <v>7</v>
       </c>
@@ -35062,7 +35524,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
         <v>8</v>
       </c>
@@ -35079,7 +35541,7 @@
         <v>58818</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
         <v>9</v>
       </c>
@@ -35096,12 +35558,12 @@
         <v>59837</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C68" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="49" t="s">
         <v>109</v>
       </c>
@@ -35114,7 +35576,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
         <v>4</v>
       </c>
@@ -35125,7 +35587,7 @@
       <c r="D71" s="53"/>
       <c r="E71" s="53"/>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="54" t="s">
         <v>110</v>
       </c>
@@ -35134,7 +35596,7 @@
       <c r="D72" s="54"/>
       <c r="E72" s="54"/>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
         <v>6</v>
       </c>
@@ -35151,7 +35613,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>7</v>
       </c>
@@ -35164,7 +35626,7 @@
         <v>1349</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
         <v>8</v>
       </c>
@@ -35177,7 +35639,7 @@
         <v>12676</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
         <v>9</v>
       </c>
@@ -35190,7 +35652,7 @@
         <v>14026</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="54" t="s">
         <v>111</v>
       </c>
@@ -35199,7 +35661,7 @@
       <c r="D77" s="54"/>
       <c r="E77" s="54"/>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
         <v>6</v>
       </c>
@@ -35216,32 +35678,59 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B79" s="9"/>
-      <c r="C79" s="10"/>
-      <c r="D79" s="10"/>
-      <c r="E79" s="10"/>
+      <c r="B79" s="9">
+        <v>792</v>
+      </c>
+      <c r="C79" s="10">
+        <v>2170</v>
+      </c>
+      <c r="D79" s="10">
+        <v>4256</v>
+      </c>
+      <c r="E79" s="10">
+        <v>8662</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>115</v>
+      </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B80" s="9"/>
-      <c r="C80" s="10"/>
-      <c r="D80" s="10"/>
-      <c r="E80" s="10"/>
+      <c r="B80" s="9">
+        <v>349</v>
+      </c>
+      <c r="C80" s="10">
+        <v>1505</v>
+      </c>
+      <c r="D80" s="10">
+        <v>3928</v>
+      </c>
+      <c r="E80" s="10">
+        <v>11608</v>
+      </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B81" s="9"/>
-      <c r="C81" s="10"/>
-      <c r="D81" s="10"/>
-      <c r="E81" s="10"/>
+      <c r="B81" s="9">
+        <v>1141</v>
+      </c>
+      <c r="C81" s="10">
+        <v>3677</v>
+      </c>
+      <c r="D81" s="10">
+        <v>8186</v>
+      </c>
+      <c r="E81" s="10">
+        <v>20279</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="32">
@@ -35295,7 +35784,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Z150"/>
+  <dimension ref="A1:AC162"/>
   <sheetFormatPr defaultRowHeight="21.6" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.28515625" style="26" customWidth="1"/>
@@ -35303,7 +35792,8 @@
     <col min="3" max="3" width="23.5703125" style="26" customWidth="1"/>
     <col min="4" max="5" width="21.42578125" style="26" customWidth="1"/>
     <col min="6" max="20" width="14.28515625" style="26" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="26"/>
+    <col min="21" max="29" width="9.7109375" style="26" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="26"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -38171,7 +38661,7 @@
       <c r="S112" s="16"/>
       <c r="T112" s="16"/>
     </row>
-    <row r="113" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="79"/>
       <c r="B113" s="42">
         <v>4</v>
@@ -38204,7 +38694,7 @@
       <c r="S113" s="16"/>
       <c r="T113" s="16"/>
     </row>
-    <row r="114" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="79"/>
       <c r="B114" s="42">
         <v>6</v>
@@ -38237,7 +38727,7 @@
       <c r="S114" s="16"/>
       <c r="T114" s="16"/>
     </row>
-    <row r="115" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="79"/>
       <c r="B115" s="42">
         <v>8</v>
@@ -38270,7 +38760,7 @@
       <c r="S115" s="16"/>
       <c r="T115" s="16"/>
     </row>
-    <row r="116" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="79"/>
       <c r="B116" s="42">
         <v>10</v>
@@ -38303,7 +38793,7 @@
       <c r="S116" s="16"/>
       <c r="T116" s="16"/>
     </row>
-    <row r="117" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="79"/>
       <c r="B117" s="42">
         <v>12</v>
@@ -38336,7 +38826,7 @@
       <c r="S117" s="31"/>
       <c r="T117" s="31"/>
     </row>
-    <row r="118" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="79"/>
       <c r="B118" s="42">
         <v>16</v>
@@ -38369,7 +38859,7 @@
       <c r="S118" s="31"/>
       <c r="T118" s="31"/>
     </row>
-    <row r="119" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="79"/>
       <c r="B119" s="33" t="s">
         <v>86</v>
@@ -38377,26 +38867,26 @@
       <c r="C119" s="78" t="s">
         <v>114</v>
       </c>
-      <c r="D119" s="84"/>
-      <c r="E119" s="84"/>
-      <c r="F119" s="84"/>
-      <c r="G119" s="84"/>
-      <c r="H119" s="84"/>
-      <c r="I119" s="84"/>
-      <c r="J119" s="84"/>
-      <c r="K119" s="84"/>
-      <c r="L119" s="84"/>
-      <c r="M119" s="84"/>
-      <c r="N119" s="84"/>
-      <c r="O119" s="84"/>
-      <c r="P119" s="84"/>
-      <c r="Q119" s="84"/>
-      <c r="R119" s="84"/>
-      <c r="S119" s="84"/>
-      <c r="T119" s="85"/>
+      <c r="D119" s="83"/>
+      <c r="E119" s="83"/>
+      <c r="F119" s="83"/>
+      <c r="G119" s="83"/>
+      <c r="H119" s="83"/>
+      <c r="I119" s="83"/>
+      <c r="J119" s="83"/>
+      <c r="K119" s="83"/>
+      <c r="L119" s="83"/>
+      <c r="M119" s="83"/>
+      <c r="N119" s="83"/>
+      <c r="O119" s="83"/>
+      <c r="P119" s="83"/>
+      <c r="Q119" s="83"/>
+      <c r="R119" s="83"/>
+      <c r="S119" s="83"/>
+      <c r="T119" s="84"/>
     </row>
-    <row r="120" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="65" t="s">
+    <row r="120" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="85" t="s">
         <v>108</v>
       </c>
       <c r="B120" s="74" t="s">
@@ -38420,20 +38910,29 @@
       <c r="R120" s="31"/>
       <c r="S120" s="31"/>
       <c r="T120" s="31"/>
+      <c r="U120" s="31"/>
+      <c r="V120" s="31"/>
+      <c r="W120" s="31"/>
+      <c r="X120" s="31"/>
+      <c r="Y120" s="31"/>
+      <c r="Z120" s="31"/>
+      <c r="AA120" s="31"/>
+      <c r="AB120" s="31"/>
+      <c r="AC120" s="31"/>
     </row>
-    <row r="121" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="66"/>
+    <row r="121" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="86"/>
       <c r="B121" s="42" t="s">
         <v>77</v>
       </c>
       <c r="C121" s="25" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D121" s="25" t="s">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="E121" s="25" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="F121" s="31"/>
       <c r="G121" s="31"/>
@@ -38450,14 +38949,27 @@
       <c r="R121" s="31"/>
       <c r="S121" s="31"/>
       <c r="T121" s="31"/>
+      <c r="U121" s="31"/>
+      <c r="V121" s="31"/>
+      <c r="W121" s="31"/>
+      <c r="X121" s="31"/>
+      <c r="Y121" s="31"/>
+      <c r="Z121" s="31"/>
+      <c r="AA121" s="31"/>
+      <c r="AB121" s="31"/>
+      <c r="AC121" s="31"/>
     </row>
-    <row r="122" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="66"/>
+    <row r="122" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="86"/>
       <c r="B122" s="15">
         <v>1</v>
       </c>
-      <c r="C122" s="40"/>
-      <c r="D122" s="24"/>
+      <c r="C122" s="24">
+        <v>9725</v>
+      </c>
+      <c r="D122" s="24">
+        <v>76160</v>
+      </c>
       <c r="E122" s="24"/>
       <c r="F122" s="31"/>
       <c r="G122" s="31"/>
@@ -38474,14 +38986,27 @@
       <c r="R122" s="31"/>
       <c r="S122" s="31"/>
       <c r="T122" s="31"/>
+      <c r="U122" s="31"/>
+      <c r="V122" s="31"/>
+      <c r="W122" s="31"/>
+      <c r="X122" s="31"/>
+      <c r="Y122" s="31"/>
+      <c r="Z122" s="31"/>
+      <c r="AA122" s="31"/>
+      <c r="AB122" s="31"/>
+      <c r="AC122" s="31"/>
     </row>
-    <row r="123" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="66"/>
+    <row r="123" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="86"/>
       <c r="B123" s="15">
         <v>2</v>
       </c>
-      <c r="C123" s="40"/>
-      <c r="D123" s="24"/>
+      <c r="C123" s="24">
+        <v>5498</v>
+      </c>
+      <c r="D123" s="24">
+        <v>39071</v>
+      </c>
       <c r="E123" s="24"/>
       <c r="F123" s="31"/>
       <c r="G123" s="31"/>
@@ -38498,14 +39023,27 @@
       <c r="R123" s="31"/>
       <c r="S123" s="31"/>
       <c r="T123" s="31"/>
+      <c r="U123" s="31"/>
+      <c r="V123" s="31"/>
+      <c r="W123" s="31"/>
+      <c r="X123" s="31"/>
+      <c r="Y123" s="31"/>
+      <c r="Z123" s="31"/>
+      <c r="AA123" s="31"/>
+      <c r="AB123" s="31"/>
+      <c r="AC123" s="31"/>
     </row>
-    <row r="124" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="66"/>
+    <row r="124" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="86"/>
       <c r="B124" s="15">
         <v>4</v>
       </c>
-      <c r="C124" s="40"/>
-      <c r="D124" s="24"/>
+      <c r="C124" s="24">
+        <v>3076</v>
+      </c>
+      <c r="D124" s="24">
+        <v>20102</v>
+      </c>
       <c r="E124" s="24"/>
       <c r="F124" s="31"/>
       <c r="G124" s="31"/>
@@ -38522,14 +39060,27 @@
       <c r="R124" s="31"/>
       <c r="S124" s="31"/>
       <c r="T124" s="31"/>
+      <c r="U124" s="31"/>
+      <c r="V124" s="31"/>
+      <c r="W124" s="31"/>
+      <c r="X124" s="31"/>
+      <c r="Y124" s="31"/>
+      <c r="Z124" s="31"/>
+      <c r="AA124" s="31"/>
+      <c r="AB124" s="31"/>
+      <c r="AC124" s="31"/>
     </row>
-    <row r="125" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="66"/>
+    <row r="125" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="86"/>
       <c r="B125" s="15">
         <v>6</v>
       </c>
-      <c r="C125" s="40"/>
-      <c r="D125" s="24"/>
+      <c r="C125" s="24">
+        <v>2342</v>
+      </c>
+      <c r="D125" s="24">
+        <v>14063</v>
+      </c>
       <c r="E125" s="24"/>
       <c r="F125" s="31"/>
       <c r="G125" s="31"/>
@@ -38546,14 +39097,27 @@
       <c r="R125" s="31"/>
       <c r="S125" s="31"/>
       <c r="T125" s="31"/>
+      <c r="U125" s="31"/>
+      <c r="V125" s="31"/>
+      <c r="W125" s="31"/>
+      <c r="X125" s="31"/>
+      <c r="Y125" s="31"/>
+      <c r="Z125" s="31"/>
+      <c r="AA125" s="31"/>
+      <c r="AB125" s="31"/>
+      <c r="AC125" s="31"/>
     </row>
-    <row r="126" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="66"/>
+    <row r="126" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="86"/>
       <c r="B126" s="15">
         <v>8</v>
       </c>
-      <c r="C126" s="40"/>
-      <c r="D126" s="24"/>
+      <c r="C126" s="40">
+        <v>1880</v>
+      </c>
+      <c r="D126" s="24">
+        <v>11690</v>
+      </c>
       <c r="E126" s="24"/>
       <c r="F126" s="31"/>
       <c r="G126" s="31"/>
@@ -38570,14 +39134,27 @@
       <c r="R126" s="31"/>
       <c r="S126" s="31"/>
       <c r="T126" s="31"/>
+      <c r="U126" s="31"/>
+      <c r="V126" s="31"/>
+      <c r="W126" s="31"/>
+      <c r="X126" s="31"/>
+      <c r="Y126" s="31"/>
+      <c r="Z126" s="31"/>
+      <c r="AA126" s="31"/>
+      <c r="AB126" s="31"/>
+      <c r="AC126" s="31"/>
     </row>
-    <row r="127" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="66"/>
+    <row r="127" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="86"/>
       <c r="B127" s="15">
         <v>10</v>
       </c>
-      <c r="C127" s="40"/>
-      <c r="D127" s="24"/>
+      <c r="C127" s="40">
+        <v>1650</v>
+      </c>
+      <c r="D127" s="24">
+        <v>10161</v>
+      </c>
       <c r="E127" s="24"/>
       <c r="F127" s="31"/>
       <c r="G127" s="31"/>
@@ -38594,14 +39171,27 @@
       <c r="R127" s="31"/>
       <c r="S127" s="31"/>
       <c r="T127" s="31"/>
+      <c r="U127" s="31"/>
+      <c r="V127" s="31"/>
+      <c r="W127" s="31"/>
+      <c r="X127" s="31"/>
+      <c r="Y127" s="31"/>
+      <c r="Z127" s="31"/>
+      <c r="AA127" s="31"/>
+      <c r="AB127" s="31"/>
+      <c r="AC127" s="31"/>
     </row>
-    <row r="128" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="66"/>
+    <row r="128" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="86"/>
       <c r="B128" s="15">
         <v>12</v>
       </c>
-      <c r="C128" s="40"/>
-      <c r="D128" s="24"/>
+      <c r="C128" s="40">
+        <v>1435</v>
+      </c>
+      <c r="D128" s="24">
+        <v>8034</v>
+      </c>
       <c r="E128" s="24"/>
       <c r="F128" s="31"/>
       <c r="G128" s="31"/>
@@ -38618,15 +39208,30 @@
       <c r="R128" s="31"/>
       <c r="S128" s="31"/>
       <c r="T128" s="31"/>
+      <c r="U128" s="31"/>
+      <c r="V128" s="31"/>
+      <c r="W128" s="31"/>
+      <c r="X128" s="31"/>
+      <c r="Y128" s="31"/>
+      <c r="Z128" s="31"/>
+      <c r="AA128" s="31"/>
+      <c r="AB128" s="31"/>
+      <c r="AC128" s="31"/>
     </row>
-    <row r="129" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="66"/>
+    <row r="129" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="86"/>
       <c r="B129" s="15">
-        <v>16</v>
-      </c>
-      <c r="C129" s="40"/>
-      <c r="D129" s="24"/>
-      <c r="E129" s="24"/>
+        <v>14</v>
+      </c>
+      <c r="C129" s="40">
+        <v>1318</v>
+      </c>
+      <c r="D129" s="24">
+        <v>7301</v>
+      </c>
+      <c r="E129" s="24">
+        <v>23660</v>
+      </c>
       <c r="F129" s="31"/>
       <c r="G129" s="31"/>
       <c r="H129" s="31"/>
@@ -38642,15 +39247,30 @@
       <c r="R129" s="31"/>
       <c r="S129" s="31"/>
       <c r="T129" s="31"/>
+      <c r="U129" s="31"/>
+      <c r="V129" s="31"/>
+      <c r="W129" s="31"/>
+      <c r="X129" s="31"/>
+      <c r="Y129" s="31"/>
+      <c r="Z129" s="31"/>
+      <c r="AA129" s="31"/>
+      <c r="AB129" s="31"/>
+      <c r="AC129" s="31"/>
     </row>
-    <row r="130" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="66"/>
-      <c r="B130" s="74" t="s">
-        <v>96</v>
-      </c>
-      <c r="C130" s="75"/>
-      <c r="D130" s="75"/>
-      <c r="E130" s="76"/>
+    <row r="130" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="86"/>
+      <c r="B130" s="15">
+        <v>16</v>
+      </c>
+      <c r="C130" s="40">
+        <v>1223</v>
+      </c>
+      <c r="D130" s="24">
+        <v>6821</v>
+      </c>
+      <c r="E130" s="24">
+        <v>21062</v>
+      </c>
       <c r="F130" s="31"/>
       <c r="G130" s="31"/>
       <c r="H130" s="31"/>
@@ -38666,155 +39286,182 @@
       <c r="R130" s="31"/>
       <c r="S130" s="31"/>
       <c r="T130" s="31"/>
+      <c r="U130" s="31"/>
+      <c r="V130" s="31"/>
+      <c r="W130" s="31"/>
+      <c r="X130" s="31"/>
+      <c r="Y130" s="31"/>
+      <c r="Z130" s="31"/>
+      <c r="AA130" s="31"/>
+      <c r="AB130" s="31"/>
+      <c r="AC130" s="31"/>
     </row>
-    <row r="131" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="66"/>
-      <c r="B131" s="42" t="s">
+    <row r="131" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="86"/>
+      <c r="B131" s="15">
+        <v>18</v>
+      </c>
+      <c r="C131" s="40">
+        <v>1176</v>
+      </c>
+      <c r="D131" s="24">
+        <v>6201</v>
+      </c>
+      <c r="E131" s="24">
+        <v>20637</v>
+      </c>
+      <c r="F131" s="31"/>
+      <c r="G131" s="31"/>
+      <c r="H131" s="31"/>
+      <c r="I131" s="31"/>
+      <c r="J131" s="31"/>
+      <c r="K131" s="31"/>
+      <c r="L131" s="31"/>
+      <c r="M131" s="31"/>
+      <c r="N131" s="31"/>
+      <c r="O131" s="31"/>
+      <c r="P131" s="31"/>
+      <c r="Q131" s="31"/>
+      <c r="R131" s="31"/>
+      <c r="S131" s="31"/>
+      <c r="T131" s="31"/>
+      <c r="U131" s="31"/>
+      <c r="V131" s="31"/>
+      <c r="W131" s="31"/>
+      <c r="X131" s="31"/>
+      <c r="Y131" s="31"/>
+      <c r="Z131" s="31"/>
+      <c r="AA131" s="31"/>
+      <c r="AB131" s="31"/>
+      <c r="AC131" s="31"/>
+    </row>
+    <row r="132" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="86"/>
+      <c r="B132" s="15">
+        <v>20</v>
+      </c>
+      <c r="C132" s="40">
+        <v>1067</v>
+      </c>
+      <c r="D132" s="24">
+        <v>6056</v>
+      </c>
+      <c r="E132" s="24">
+        <v>18311</v>
+      </c>
+      <c r="F132" s="31"/>
+      <c r="G132" s="31"/>
+      <c r="H132" s="31"/>
+      <c r="I132" s="31"/>
+      <c r="J132" s="31"/>
+      <c r="K132" s="31"/>
+      <c r="L132" s="31"/>
+      <c r="M132" s="31"/>
+      <c r="N132" s="31"/>
+      <c r="O132" s="31"/>
+      <c r="P132" s="31"/>
+      <c r="Q132" s="31"/>
+      <c r="R132" s="31"/>
+      <c r="S132" s="31"/>
+      <c r="T132" s="31"/>
+      <c r="U132" s="31"/>
+      <c r="V132" s="31"/>
+      <c r="W132" s="31"/>
+      <c r="X132" s="31"/>
+      <c r="Y132" s="31"/>
+      <c r="Z132" s="31"/>
+      <c r="AA132" s="31"/>
+      <c r="AB132" s="31"/>
+      <c r="AC132" s="31"/>
+    </row>
+    <row r="133" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="86"/>
+      <c r="B133" s="87">
+        <v>40</v>
+      </c>
+      <c r="C133" s="88">
+        <v>1201</v>
+      </c>
+      <c r="D133" s="89">
+        <v>6846</v>
+      </c>
+      <c r="E133" s="89">
+        <v>20629</v>
+      </c>
+      <c r="F133" s="31"/>
+      <c r="G133" s="31"/>
+      <c r="H133" s="31"/>
+      <c r="I133" s="31"/>
+      <c r="J133" s="31"/>
+      <c r="K133" s="31"/>
+      <c r="L133" s="31"/>
+      <c r="M133" s="31"/>
+      <c r="N133" s="31"/>
+      <c r="O133" s="31"/>
+      <c r="P133" s="31"/>
+      <c r="Q133" s="31"/>
+      <c r="R133" s="31"/>
+      <c r="S133" s="31"/>
+      <c r="T133" s="31"/>
+      <c r="U133" s="31"/>
+      <c r="V133" s="31"/>
+      <c r="W133" s="31"/>
+      <c r="X133" s="31"/>
+      <c r="Y133" s="31"/>
+      <c r="Z133" s="31"/>
+      <c r="AA133" s="31"/>
+      <c r="AB133" s="31"/>
+      <c r="AC133" s="31"/>
+    </row>
+    <row r="134" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A134" s="86"/>
+      <c r="B134" s="74" t="s">
+        <v>96</v>
+      </c>
+      <c r="C134" s="75"/>
+      <c r="D134" s="75"/>
+      <c r="E134" s="76"/>
+      <c r="F134" s="31"/>
+      <c r="G134" s="31"/>
+      <c r="H134" s="31"/>
+      <c r="I134" s="31"/>
+      <c r="J134" s="31"/>
+      <c r="K134" s="31"/>
+      <c r="L134" s="31"/>
+      <c r="M134" s="31"/>
+      <c r="N134" s="31"/>
+      <c r="O134" s="31"/>
+      <c r="P134" s="31"/>
+      <c r="Q134" s="31"/>
+      <c r="R134" s="31"/>
+      <c r="S134" s="31"/>
+      <c r="T134" s="31"/>
+      <c r="U134" s="31"/>
+      <c r="V134" s="31"/>
+      <c r="W134" s="31"/>
+      <c r="X134" s="31"/>
+      <c r="Y134" s="31"/>
+      <c r="Z134" s="31"/>
+      <c r="AA134" s="31"/>
+      <c r="AB134" s="31"/>
+      <c r="AC134" s="31"/>
+    </row>
+    <row r="135" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A135" s="86"/>
+      <c r="B135" s="42" t="s">
         <v>77</v>
       </c>
-      <c r="C131" s="25" t="s">
-        <v>80</v>
-      </c>
-      <c r="D131" s="25" t="s">
+      <c r="C135" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="E131" s="25" t="s">
+      <c r="D135" s="25" t="s">
         <v>112</v>
       </c>
-      <c r="F131" s="43"/>
-      <c r="G131" s="43"/>
-      <c r="H131" s="16"/>
-      <c r="I131" s="16"/>
-      <c r="J131" s="16"/>
-      <c r="K131" s="16"/>
-      <c r="L131" s="16"/>
-      <c r="M131" s="16"/>
-      <c r="N131" s="16"/>
-      <c r="O131" s="43"/>
-      <c r="P131" s="43"/>
-      <c r="Q131" s="43"/>
-      <c r="R131" s="16"/>
-      <c r="S131" s="16"/>
-      <c r="T131" s="16"/>
-    </row>
-    <row r="132" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="66"/>
-      <c r="B132" s="42">
-        <v>1</v>
-      </c>
-      <c r="C132" s="40" t="e">
-        <f>C122/C122</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D132" s="40" t="e">
-        <f>D122/D122</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E132" s="40" t="e">
-        <f>E122/E122</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F132" s="43"/>
-      <c r="G132" s="43"/>
-      <c r="H132" s="16"/>
-      <c r="I132" s="16"/>
-      <c r="J132" s="16"/>
-      <c r="K132" s="16"/>
-      <c r="L132" s="16"/>
-      <c r="M132" s="16"/>
-      <c r="N132" s="16"/>
-      <c r="O132" s="43"/>
-      <c r="P132" s="43"/>
-      <c r="Q132" s="43"/>
-      <c r="R132" s="16"/>
-      <c r="S132" s="16"/>
-      <c r="T132" s="16"/>
-    </row>
-    <row r="133" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="66"/>
-      <c r="B133" s="42">
-        <v>2</v>
-      </c>
-      <c r="C133" s="40" t="e">
-        <f>C122/C123</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D133" s="40" t="e">
-        <f>D122/D123</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E133" s="40" t="e">
-        <f>E122/E123</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F133" s="43"/>
-      <c r="G133" s="43"/>
-      <c r="H133" s="16"/>
-      <c r="I133" s="16"/>
-      <c r="J133" s="16"/>
-      <c r="K133" s="16"/>
-      <c r="L133" s="16"/>
-      <c r="M133" s="16"/>
-      <c r="N133" s="16"/>
-      <c r="O133" s="43"/>
-      <c r="P133" s="43"/>
-      <c r="Q133" s="43"/>
-      <c r="R133" s="16"/>
-      <c r="S133" s="16"/>
-      <c r="T133" s="16"/>
-    </row>
-    <row r="134" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="66"/>
-      <c r="B134" s="42">
-        <v>4</v>
-      </c>
-      <c r="C134" s="40" t="e">
-        <f>C122/C124</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D134" s="40" t="e">
-        <f>D122/D124</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E134" s="40" t="e">
-        <f>E122/E124</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F134" s="43"/>
-      <c r="G134" s="43"/>
-      <c r="H134" s="16"/>
-      <c r="I134" s="16"/>
-      <c r="J134" s="16"/>
-      <c r="K134" s="16"/>
-      <c r="L134" s="16"/>
-      <c r="M134" s="16"/>
-      <c r="N134" s="16"/>
-      <c r="O134" s="43"/>
-      <c r="P134" s="43"/>
-      <c r="Q134" s="43"/>
-      <c r="R134" s="16"/>
-      <c r="S134" s="16"/>
-      <c r="T134" s="16"/>
-    </row>
-    <row r="135" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="66"/>
-      <c r="B135" s="42">
-        <v>6</v>
-      </c>
-      <c r="C135" s="40" t="e">
-        <f>C122/C125</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D135" s="40" t="e">
-        <f>D122/D125</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E135" s="40" t="e">
-        <f>E122/E125</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F135" s="43"/>
-      <c r="G135" s="43"/>
+      <c r="E135" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="F135" s="16"/>
+      <c r="G135" s="16"/>
       <c r="H135" s="16"/>
       <c r="I135" s="16"/>
       <c r="J135" s="16"/>
@@ -38822,32 +39469,41 @@
       <c r="L135" s="16"/>
       <c r="M135" s="16"/>
       <c r="N135" s="16"/>
-      <c r="O135" s="43"/>
-      <c r="P135" s="43"/>
-      <c r="Q135" s="43"/>
+      <c r="O135" s="16"/>
+      <c r="P135" s="16"/>
+      <c r="Q135" s="16"/>
       <c r="R135" s="16"/>
       <c r="S135" s="16"/>
       <c r="T135" s="16"/>
+      <c r="U135" s="16"/>
+      <c r="V135" s="16"/>
+      <c r="W135" s="16"/>
+      <c r="X135" s="16"/>
+      <c r="Y135" s="16"/>
+      <c r="Z135" s="16"/>
+      <c r="AA135" s="16"/>
+      <c r="AB135" s="16"/>
+      <c r="AC135" s="16"/>
     </row>
-    <row r="136" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="66"/>
-      <c r="B136" s="42">
-        <v>8</v>
-      </c>
-      <c r="C136" s="40" t="e">
-        <f>C122/C126</f>
+    <row r="136" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="86"/>
+      <c r="B136" s="15">
+        <v>1</v>
+      </c>
+      <c r="C136" s="40">
+        <f>C122/C122</f>
+        <v>1</v>
+      </c>
+      <c r="D136" s="40">
+        <f>D122/D122</f>
+        <v>1</v>
+      </c>
+      <c r="E136" s="40" t="e">
+        <f>E122/E122</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D136" s="40" t="e">
-        <f>D122/D126</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E136" s="40" t="e">
-        <f>E122/E126</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F136" s="43"/>
-      <c r="G136" s="43"/>
+      <c r="F136" s="16"/>
+      <c r="G136" s="16"/>
       <c r="H136" s="16"/>
       <c r="I136" s="16"/>
       <c r="J136" s="16"/>
@@ -38855,32 +39511,41 @@
       <c r="L136" s="16"/>
       <c r="M136" s="16"/>
       <c r="N136" s="16"/>
-      <c r="O136" s="43"/>
-      <c r="P136" s="43"/>
-      <c r="Q136" s="43"/>
+      <c r="O136" s="16"/>
+      <c r="P136" s="16"/>
+      <c r="Q136" s="16"/>
       <c r="R136" s="16"/>
       <c r="S136" s="16"/>
       <c r="T136" s="16"/>
+      <c r="U136" s="16"/>
+      <c r="V136" s="16"/>
+      <c r="W136" s="16"/>
+      <c r="X136" s="16"/>
+      <c r="Y136" s="16"/>
+      <c r="Z136" s="16"/>
+      <c r="AA136" s="16"/>
+      <c r="AB136" s="16"/>
+      <c r="AC136" s="16"/>
     </row>
-    <row r="137" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="66"/>
-      <c r="B137" s="42">
-        <v>10</v>
-      </c>
-      <c r="C137" s="40" t="e">
-        <f>C122/C127</f>
+    <row r="137" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A137" s="86"/>
+      <c r="B137" s="15">
+        <v>2</v>
+      </c>
+      <c r="C137" s="40">
+        <f>C122/C123</f>
+        <v>1.7688250272826482</v>
+      </c>
+      <c r="D137" s="40">
+        <f>D122/D123</f>
+        <v>1.9492718384479537</v>
+      </c>
+      <c r="E137" s="40" t="e">
+        <f>E122/E123</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D137" s="40" t="e">
-        <f>D122/D127</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E137" s="40" t="e">
-        <f>E122/E127</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F137" s="43"/>
-      <c r="G137" s="43"/>
+      <c r="F137" s="16"/>
+      <c r="G137" s="16"/>
       <c r="H137" s="16"/>
       <c r="I137" s="16"/>
       <c r="J137" s="16"/>
@@ -38888,32 +39553,41 @@
       <c r="L137" s="16"/>
       <c r="M137" s="16"/>
       <c r="N137" s="16"/>
-      <c r="O137" s="43"/>
-      <c r="P137" s="43"/>
-      <c r="Q137" s="43"/>
+      <c r="O137" s="16"/>
+      <c r="P137" s="16"/>
+      <c r="Q137" s="16"/>
       <c r="R137" s="16"/>
       <c r="S137" s="16"/>
       <c r="T137" s="16"/>
+      <c r="U137" s="16"/>
+      <c r="V137" s="16"/>
+      <c r="W137" s="16"/>
+      <c r="X137" s="16"/>
+      <c r="Y137" s="16"/>
+      <c r="Z137" s="16"/>
+      <c r="AA137" s="16"/>
+      <c r="AB137" s="16"/>
+      <c r="AC137" s="16"/>
     </row>
-    <row r="138" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="66"/>
-      <c r="B138" s="42">
-        <v>12</v>
-      </c>
-      <c r="C138" s="40" t="e">
-        <f>C122/C128</f>
+    <row r="138" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="86"/>
+      <c r="B138" s="15">
+        <v>4</v>
+      </c>
+      <c r="C138" s="40">
+        <f>C122/C124</f>
+        <v>3.1615734720416127</v>
+      </c>
+      <c r="D138" s="40">
+        <f>D122/D124</f>
+        <v>3.7886777435081087</v>
+      </c>
+      <c r="E138" s="40" t="e">
+        <f>E122/E124</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D138" s="40" t="e">
-        <f>D122/D128</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E138" s="40" t="e">
-        <f>E122/E128</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F138" s="43"/>
-      <c r="G138" s="43"/>
+      <c r="F138" s="16"/>
+      <c r="G138" s="16"/>
       <c r="H138" s="16"/>
       <c r="I138" s="16"/>
       <c r="J138" s="16"/>
@@ -38921,32 +39595,41 @@
       <c r="L138" s="16"/>
       <c r="M138" s="16"/>
       <c r="N138" s="16"/>
-      <c r="O138" s="43"/>
-      <c r="P138" s="43"/>
-      <c r="Q138" s="43"/>
+      <c r="O138" s="16"/>
+      <c r="P138" s="16"/>
+      <c r="Q138" s="16"/>
       <c r="R138" s="16"/>
       <c r="S138" s="16"/>
       <c r="T138" s="16"/>
+      <c r="U138" s="16"/>
+      <c r="V138" s="16"/>
+      <c r="W138" s="16"/>
+      <c r="X138" s="16"/>
+      <c r="Y138" s="16"/>
+      <c r="Z138" s="16"/>
+      <c r="AA138" s="16"/>
+      <c r="AB138" s="16"/>
+      <c r="AC138" s="16"/>
     </row>
-    <row r="139" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="66"/>
-      <c r="B139" s="42">
-        <v>16</v>
-      </c>
-      <c r="C139" s="40" t="e">
-        <f>C122/C129</f>
+    <row r="139" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="86"/>
+      <c r="B139" s="15">
+        <v>6</v>
+      </c>
+      <c r="C139" s="40">
+        <f>C122/C125</f>
+        <v>4.1524338172502135</v>
+      </c>
+      <c r="D139" s="40">
+        <f>D122/D125</f>
+        <v>5.4156296665007471</v>
+      </c>
+      <c r="E139" s="40" t="e">
+        <f>E122/E125</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D139" s="40" t="e">
-        <f>D122/D129</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E139" s="40" t="e">
-        <f>E122/E129</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F139" s="43"/>
-      <c r="G139" s="43"/>
+      <c r="F139" s="16"/>
+      <c r="G139" s="16"/>
       <c r="H139" s="16"/>
       <c r="I139" s="16"/>
       <c r="J139" s="16"/>
@@ -38954,23 +39637,41 @@
       <c r="L139" s="16"/>
       <c r="M139" s="16"/>
       <c r="N139" s="16"/>
-      <c r="O139" s="43"/>
-      <c r="P139" s="43"/>
-      <c r="Q139" s="43"/>
+      <c r="O139" s="16"/>
+      <c r="P139" s="16"/>
+      <c r="Q139" s="16"/>
       <c r="R139" s="16"/>
       <c r="S139" s="16"/>
       <c r="T139" s="16"/>
+      <c r="U139" s="16"/>
+      <c r="V139" s="16"/>
+      <c r="W139" s="16"/>
+      <c r="X139" s="16"/>
+      <c r="Y139" s="16"/>
+      <c r="Z139" s="16"/>
+      <c r="AA139" s="16"/>
+      <c r="AB139" s="16"/>
+      <c r="AC139" s="16"/>
     </row>
-    <row r="140" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="66"/>
-      <c r="B140" s="74" t="s">
-        <v>97</v>
-      </c>
-      <c r="C140" s="75"/>
-      <c r="D140" s="75"/>
-      <c r="E140" s="76"/>
-      <c r="F140" s="43"/>
-      <c r="G140" s="43"/>
+    <row r="140" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="86"/>
+      <c r="B140" s="15">
+        <v>8</v>
+      </c>
+      <c r="C140" s="40">
+        <f>C122/C126</f>
+        <v>5.1728723404255321</v>
+      </c>
+      <c r="D140" s="40">
+        <f>D122/D126</f>
+        <v>6.5149700598802394</v>
+      </c>
+      <c r="E140" s="40" t="e">
+        <f>E122/E126</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F140" s="16"/>
+      <c r="G140" s="16"/>
       <c r="H140" s="16"/>
       <c r="I140" s="16"/>
       <c r="J140" s="16"/>
@@ -38978,29 +39679,41 @@
       <c r="L140" s="16"/>
       <c r="M140" s="16"/>
       <c r="N140" s="16"/>
-      <c r="O140" s="43"/>
-      <c r="P140" s="43"/>
-      <c r="Q140" s="43"/>
+      <c r="O140" s="16"/>
+      <c r="P140" s="16"/>
+      <c r="Q140" s="16"/>
       <c r="R140" s="16"/>
       <c r="S140" s="16"/>
       <c r="T140" s="16"/>
+      <c r="U140" s="16"/>
+      <c r="V140" s="16"/>
+      <c r="W140" s="16"/>
+      <c r="X140" s="16"/>
+      <c r="Y140" s="16"/>
+      <c r="Z140" s="16"/>
+      <c r="AA140" s="16"/>
+      <c r="AB140" s="16"/>
+      <c r="AC140" s="16"/>
     </row>
-    <row r="141" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="66"/>
-      <c r="B141" s="42" t="s">
-        <v>77</v>
-      </c>
-      <c r="C141" s="25" t="s">
-        <v>80</v>
-      </c>
-      <c r="D141" s="25" t="s">
-        <v>79</v>
-      </c>
-      <c r="E141" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="F141" s="43"/>
-      <c r="G141" s="43"/>
+    <row r="141" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="86"/>
+      <c r="B141" s="15">
+        <v>10</v>
+      </c>
+      <c r="C141" s="40">
+        <f>C122/C127</f>
+        <v>5.8939393939393936</v>
+      </c>
+      <c r="D141" s="40">
+        <f>D122/D127</f>
+        <v>7.4953252632614902</v>
+      </c>
+      <c r="E141" s="40" t="e">
+        <f>E122/E127</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F141" s="16"/>
+      <c r="G141" s="16"/>
       <c r="H141" s="16"/>
       <c r="I141" s="16"/>
       <c r="J141" s="16"/>
@@ -39008,32 +39721,41 @@
       <c r="L141" s="16"/>
       <c r="M141" s="16"/>
       <c r="N141" s="16"/>
-      <c r="O141" s="43"/>
-      <c r="P141" s="43"/>
-      <c r="Q141" s="43"/>
+      <c r="O141" s="16"/>
+      <c r="P141" s="16"/>
+      <c r="Q141" s="16"/>
       <c r="R141" s="16"/>
       <c r="S141" s="16"/>
       <c r="T141" s="16"/>
+      <c r="U141" s="16"/>
+      <c r="V141" s="16"/>
+      <c r="W141" s="16"/>
+      <c r="X141" s="16"/>
+      <c r="Y141" s="16"/>
+      <c r="Z141" s="16"/>
+      <c r="AA141" s="16"/>
+      <c r="AB141" s="16"/>
+      <c r="AC141" s="16"/>
     </row>
-    <row r="142" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="66"/>
-      <c r="B142" s="42">
-        <v>1</v>
-      </c>
-      <c r="C142" s="40" t="e">
-        <f t="shared" ref="C142:C149" si="7">C132/B132</f>
+    <row r="142" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A142" s="86"/>
+      <c r="B142" s="15">
+        <v>12</v>
+      </c>
+      <c r="C142" s="40">
+        <f>C122/C128</f>
+        <v>6.7770034843205575</v>
+      </c>
+      <c r="D142" s="40">
+        <f>D122/D128</f>
+        <v>9.4797112272840423</v>
+      </c>
+      <c r="E142" s="40" t="e">
+        <f>E122/E128</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="D142" s="40" t="e">
-        <f t="shared" ref="D142:E149" si="8">D132/$B132</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E142" s="40" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F142" s="43"/>
-      <c r="G142" s="43"/>
+      <c r="F142" s="16"/>
+      <c r="G142" s="16"/>
       <c r="H142" s="16"/>
       <c r="I142" s="16"/>
       <c r="J142" s="16"/>
@@ -39041,32 +39763,41 @@
       <c r="L142" s="16"/>
       <c r="M142" s="16"/>
       <c r="N142" s="16"/>
-      <c r="O142" s="43"/>
-      <c r="P142" s="43"/>
-      <c r="Q142" s="43"/>
+      <c r="O142" s="16"/>
+      <c r="P142" s="16"/>
+      <c r="Q142" s="16"/>
       <c r="R142" s="16"/>
       <c r="S142" s="16"/>
       <c r="T142" s="16"/>
+      <c r="U142" s="16"/>
+      <c r="V142" s="16"/>
+      <c r="W142" s="16"/>
+      <c r="X142" s="16"/>
+      <c r="Y142" s="16"/>
+      <c r="Z142" s="16"/>
+      <c r="AA142" s="16"/>
+      <c r="AB142" s="16"/>
+      <c r="AC142" s="16"/>
     </row>
-    <row r="143" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="66"/>
-      <c r="B143" s="42">
-        <v>2</v>
-      </c>
-      <c r="C143" s="40" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D143" s="40" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E143" s="40" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F143" s="43"/>
-      <c r="G143" s="43"/>
+    <row r="143" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A143" s="86"/>
+      <c r="B143" s="15">
+        <v>14</v>
+      </c>
+      <c r="C143" s="40">
+        <f>C$122/C129</f>
+        <v>7.3786039453717756</v>
+      </c>
+      <c r="D143" s="40">
+        <f>D$122/D129</f>
+        <v>10.431447746883988</v>
+      </c>
+      <c r="E143" s="40">
+        <f>E$122/E129</f>
+        <v>0</v>
+      </c>
+      <c r="F143" s="16"/>
+      <c r="G143" s="16"/>
       <c r="H143" s="16"/>
       <c r="I143" s="16"/>
       <c r="J143" s="16"/>
@@ -39074,65 +39805,83 @@
       <c r="L143" s="16"/>
       <c r="M143" s="16"/>
       <c r="N143" s="16"/>
-      <c r="O143" s="43"/>
-      <c r="P143" s="43"/>
-      <c r="Q143" s="43"/>
+      <c r="O143" s="16"/>
+      <c r="P143" s="16"/>
+      <c r="Q143" s="16"/>
       <c r="R143" s="16"/>
       <c r="S143" s="16"/>
       <c r="T143" s="16"/>
+      <c r="U143" s="16"/>
+      <c r="V143" s="16"/>
+      <c r="W143" s="16"/>
+      <c r="X143" s="16"/>
+      <c r="Y143" s="16"/>
+      <c r="Z143" s="16"/>
+      <c r="AA143" s="16"/>
+      <c r="AB143" s="16"/>
+      <c r="AC143" s="16"/>
     </row>
-    <row r="144" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="66"/>
-      <c r="B144" s="42">
-        <v>4</v>
-      </c>
-      <c r="C144" s="40" t="e">
+    <row r="144" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="86"/>
+      <c r="B144" s="15">
+        <v>16</v>
+      </c>
+      <c r="C144" s="40">
+        <f t="shared" ref="C144:D147" si="7">C$122/C130</f>
+        <v>7.9517579721995091</v>
+      </c>
+      <c r="D144" s="40">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D144" s="40" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E144" s="40" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F144" s="43"/>
-      <c r="G144" s="43"/>
-      <c r="H144" s="16"/>
-      <c r="I144" s="16"/>
-      <c r="J144" s="16"/>
-      <c r="K144" s="16"/>
-      <c r="L144" s="16"/>
-      <c r="M144" s="16"/>
-      <c r="N144" s="16"/>
-      <c r="O144" s="43"/>
-      <c r="P144" s="43"/>
-      <c r="Q144" s="43"/>
-      <c r="R144" s="16"/>
-      <c r="S144" s="16"/>
-      <c r="T144" s="16"/>
+        <v>11.165518252455652</v>
+      </c>
+      <c r="E144" s="40">
+        <f t="shared" ref="E144" si="8">E$122/E130</f>
+        <v>0</v>
+      </c>
+      <c r="F144" s="31"/>
+      <c r="G144" s="31"/>
+      <c r="H144" s="31"/>
+      <c r="I144" s="31"/>
+      <c r="J144" s="31"/>
+      <c r="K144" s="31"/>
+      <c r="L144" s="31"/>
+      <c r="M144" s="31"/>
+      <c r="N144" s="31"/>
+      <c r="O144" s="31"/>
+      <c r="P144" s="31"/>
+      <c r="Q144" s="31"/>
+      <c r="R144" s="31"/>
+      <c r="S144" s="31"/>
+      <c r="T144" s="31"/>
+      <c r="U144" s="31"/>
+      <c r="V144" s="31"/>
+      <c r="W144" s="31"/>
+      <c r="X144" s="31"/>
+      <c r="Y144" s="31"/>
+      <c r="Z144" s="31"/>
+      <c r="AA144" s="31"/>
+      <c r="AB144" s="31"/>
+      <c r="AC144" s="31"/>
     </row>
-    <row r="145" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="66"/>
-      <c r="B145" s="42">
-        <v>6</v>
-      </c>
-      <c r="C145" s="40" t="e">
+    <row r="145" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="86"/>
+      <c r="B145" s="15">
+        <v>18</v>
+      </c>
+      <c r="C145" s="40">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D145" s="40" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E145" s="40" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F145" s="43"/>
-      <c r="G145" s="43"/>
+        <v>8.2695578231292526</v>
+      </c>
+      <c r="D145" s="40">
+        <f t="shared" si="7"/>
+        <v>12.281890017739075</v>
+      </c>
+      <c r="E145" s="40">
+        <f t="shared" ref="E145" si="9">E$122/E131</f>
+        <v>0</v>
+      </c>
+      <c r="F145" s="16"/>
+      <c r="G145" s="16"/>
       <c r="H145" s="16"/>
       <c r="I145" s="16"/>
       <c r="J145" s="16"/>
@@ -39140,32 +39889,41 @@
       <c r="L145" s="16"/>
       <c r="M145" s="16"/>
       <c r="N145" s="16"/>
-      <c r="O145" s="43"/>
-      <c r="P145" s="43"/>
-      <c r="Q145" s="43"/>
+      <c r="O145" s="16"/>
+      <c r="P145" s="16"/>
+      <c r="Q145" s="16"/>
       <c r="R145" s="16"/>
       <c r="S145" s="16"/>
       <c r="T145" s="16"/>
+      <c r="U145" s="16"/>
+      <c r="V145" s="16"/>
+      <c r="W145" s="16"/>
+      <c r="X145" s="16"/>
+      <c r="Y145" s="16"/>
+      <c r="Z145" s="16"/>
+      <c r="AA145" s="16"/>
+      <c r="AB145" s="16"/>
+      <c r="AC145" s="16"/>
     </row>
-    <row r="146" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="66"/>
-      <c r="B146" s="42">
-        <v>8</v>
-      </c>
-      <c r="C146" s="40" t="e">
+    <row r="146" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="86"/>
+      <c r="B146" s="15">
+        <v>20</v>
+      </c>
+      <c r="C146" s="40">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D146" s="40" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E146" s="40" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F146" s="43"/>
-      <c r="G146" s="43"/>
+        <v>9.1143392689784442</v>
+      </c>
+      <c r="D146" s="40">
+        <f t="shared" si="7"/>
+        <v>12.575957727873183</v>
+      </c>
+      <c r="E146" s="40">
+        <f t="shared" ref="E146" si="10">E$122/E132</f>
+        <v>0</v>
+      </c>
+      <c r="F146" s="16"/>
+      <c r="G146" s="16"/>
       <c r="H146" s="16"/>
       <c r="I146" s="16"/>
       <c r="J146" s="16"/>
@@ -39173,32 +39931,41 @@
       <c r="L146" s="16"/>
       <c r="M146" s="16"/>
       <c r="N146" s="16"/>
-      <c r="O146" s="43"/>
-      <c r="P146" s="43"/>
-      <c r="Q146" s="43"/>
+      <c r="O146" s="16"/>
+      <c r="P146" s="16"/>
+      <c r="Q146" s="16"/>
       <c r="R146" s="16"/>
       <c r="S146" s="16"/>
       <c r="T146" s="16"/>
+      <c r="U146" s="16"/>
+      <c r="V146" s="16"/>
+      <c r="W146" s="16"/>
+      <c r="X146" s="16"/>
+      <c r="Y146" s="16"/>
+      <c r="Z146" s="16"/>
+      <c r="AA146" s="16"/>
+      <c r="AB146" s="16"/>
+      <c r="AC146" s="16"/>
     </row>
-    <row r="147" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="66"/>
-      <c r="B147" s="42">
-        <v>10</v>
-      </c>
-      <c r="C147" s="40" t="e">
+    <row r="147" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A147" s="86"/>
+      <c r="B147" s="87">
+        <v>40</v>
+      </c>
+      <c r="C147" s="88">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D147" s="40" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E147" s="40" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F147" s="43"/>
-      <c r="G147" s="43"/>
+        <v>8.0974188176519561</v>
+      </c>
+      <c r="D147" s="88">
+        <f t="shared" si="7"/>
+        <v>11.124744376278118</v>
+      </c>
+      <c r="E147" s="88">
+        <f>E$122/E133</f>
+        <v>0</v>
+      </c>
+      <c r="F147" s="16"/>
+      <c r="G147" s="16"/>
       <c r="H147" s="16"/>
       <c r="I147" s="16"/>
       <c r="J147" s="16"/>
@@ -39206,115 +39973,645 @@
       <c r="L147" s="16"/>
       <c r="M147" s="16"/>
       <c r="N147" s="16"/>
-      <c r="O147" s="43"/>
-      <c r="P147" s="43"/>
-      <c r="Q147" s="43"/>
+      <c r="O147" s="16"/>
+      <c r="P147" s="16"/>
+      <c r="Q147" s="16"/>
       <c r="R147" s="16"/>
       <c r="S147" s="16"/>
       <c r="T147" s="16"/>
+      <c r="U147" s="16"/>
+      <c r="V147" s="16"/>
+      <c r="W147" s="16"/>
+      <c r="X147" s="16"/>
+      <c r="Y147" s="16"/>
+      <c r="Z147" s="16"/>
+      <c r="AA147" s="16"/>
+      <c r="AB147" s="16"/>
+      <c r="AC147" s="16"/>
     </row>
-    <row r="148" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="66"/>
-      <c r="B148" s="42">
+    <row r="148" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="86"/>
+      <c r="B148" s="74" t="s">
+        <v>97</v>
+      </c>
+      <c r="C148" s="75"/>
+      <c r="D148" s="75"/>
+      <c r="E148" s="76"/>
+      <c r="F148" s="16"/>
+      <c r="G148" s="16"/>
+      <c r="H148" s="16"/>
+      <c r="I148" s="16"/>
+      <c r="J148" s="16"/>
+      <c r="K148" s="16"/>
+      <c r="L148" s="16"/>
+      <c r="M148" s="16"/>
+      <c r="N148" s="16"/>
+      <c r="O148" s="16"/>
+      <c r="P148" s="16"/>
+      <c r="Q148" s="16"/>
+      <c r="R148" s="16"/>
+      <c r="S148" s="16"/>
+      <c r="T148" s="16"/>
+      <c r="U148" s="16"/>
+      <c r="V148" s="16"/>
+      <c r="W148" s="16"/>
+      <c r="X148" s="16"/>
+      <c r="Y148" s="16"/>
+      <c r="Z148" s="16"/>
+      <c r="AA148" s="16"/>
+      <c r="AB148" s="16"/>
+      <c r="AC148" s="16"/>
+    </row>
+    <row r="149" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="86"/>
+      <c r="B149" s="42" t="s">
+        <v>77</v>
+      </c>
+      <c r="C149" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="D149" s="25" t="s">
+        <v>112</v>
+      </c>
+      <c r="E149" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="F149" s="16"/>
+      <c r="G149" s="16"/>
+      <c r="H149" s="16"/>
+      <c r="I149" s="16"/>
+      <c r="J149" s="16"/>
+      <c r="K149" s="16"/>
+      <c r="L149" s="16"/>
+      <c r="M149" s="16"/>
+      <c r="N149" s="16"/>
+      <c r="O149" s="16"/>
+      <c r="P149" s="16"/>
+      <c r="Q149" s="16"/>
+      <c r="R149" s="16"/>
+      <c r="S149" s="16"/>
+      <c r="T149" s="16"/>
+      <c r="U149" s="16"/>
+      <c r="V149" s="16"/>
+      <c r="W149" s="16"/>
+      <c r="X149" s="16"/>
+      <c r="Y149" s="16"/>
+      <c r="Z149" s="16"/>
+      <c r="AA149" s="16"/>
+      <c r="AB149" s="16"/>
+      <c r="AC149" s="16"/>
+    </row>
+    <row r="150" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A150" s="86"/>
+      <c r="B150" s="15">
+        <v>1</v>
+      </c>
+      <c r="C150" s="40">
+        <f t="shared" ref="C150:E154" si="11">C136/$B136</f>
+        <v>1</v>
+      </c>
+      <c r="D150" s="40">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="E150" s="40" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F150" s="16"/>
+      <c r="G150" s="16"/>
+      <c r="H150" s="16"/>
+      <c r="I150" s="16"/>
+      <c r="J150" s="16"/>
+      <c r="K150" s="16"/>
+      <c r="L150" s="16"/>
+      <c r="M150" s="16"/>
+      <c r="N150" s="16"/>
+      <c r="O150" s="16"/>
+      <c r="P150" s="16"/>
+      <c r="Q150" s="16"/>
+      <c r="R150" s="16"/>
+      <c r="S150" s="16"/>
+      <c r="T150" s="16"/>
+      <c r="U150" s="16"/>
+      <c r="V150" s="16"/>
+      <c r="W150" s="16"/>
+      <c r="X150" s="16"/>
+      <c r="Y150" s="16"/>
+      <c r="Z150" s="16"/>
+      <c r="AA150" s="16"/>
+      <c r="AB150" s="16"/>
+      <c r="AC150" s="16"/>
+    </row>
+    <row r="151" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A151" s="86"/>
+      <c r="B151" s="15">
+        <v>2</v>
+      </c>
+      <c r="C151" s="40">
+        <f t="shared" si="11"/>
+        <v>0.88441251364132412</v>
+      </c>
+      <c r="D151" s="40">
+        <f t="shared" si="11"/>
+        <v>0.97463591922397685</v>
+      </c>
+      <c r="E151" s="40" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F151" s="16"/>
+      <c r="G151" s="16"/>
+      <c r="H151" s="16"/>
+      <c r="I151" s="16"/>
+      <c r="J151" s="16"/>
+      <c r="K151" s="16"/>
+      <c r="L151" s="16"/>
+      <c r="M151" s="16"/>
+      <c r="N151" s="16"/>
+      <c r="O151" s="16"/>
+      <c r="P151" s="16"/>
+      <c r="Q151" s="16"/>
+      <c r="R151" s="16"/>
+      <c r="S151" s="16"/>
+      <c r="T151" s="16"/>
+      <c r="U151" s="16"/>
+      <c r="V151" s="16"/>
+      <c r="W151" s="16"/>
+      <c r="X151" s="16"/>
+      <c r="Y151" s="16"/>
+      <c r="Z151" s="16"/>
+      <c r="AA151" s="16"/>
+      <c r="AB151" s="16"/>
+      <c r="AC151" s="16"/>
+    </row>
+    <row r="152" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="86"/>
+      <c r="B152" s="15">
+        <v>4</v>
+      </c>
+      <c r="C152" s="40">
+        <f t="shared" si="11"/>
+        <v>0.79039336801040316</v>
+      </c>
+      <c r="D152" s="40">
+        <f t="shared" si="11"/>
+        <v>0.94716943587702718</v>
+      </c>
+      <c r="E152" s="40" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F152" s="16"/>
+      <c r="G152" s="16"/>
+      <c r="H152" s="16"/>
+      <c r="I152" s="16"/>
+      <c r="J152" s="16"/>
+      <c r="K152" s="16"/>
+      <c r="L152" s="16"/>
+      <c r="M152" s="16"/>
+      <c r="N152" s="16"/>
+      <c r="O152" s="16"/>
+      <c r="P152" s="16"/>
+      <c r="Q152" s="16"/>
+      <c r="R152" s="16"/>
+      <c r="S152" s="16"/>
+      <c r="T152" s="16"/>
+      <c r="U152" s="16"/>
+      <c r="V152" s="16"/>
+      <c r="W152" s="16"/>
+      <c r="X152" s="16"/>
+      <c r="Y152" s="16"/>
+      <c r="Z152" s="16"/>
+      <c r="AA152" s="16"/>
+      <c r="AB152" s="16"/>
+      <c r="AC152" s="16"/>
+    </row>
+    <row r="153" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="86"/>
+      <c r="B153" s="15">
+        <v>6</v>
+      </c>
+      <c r="C153" s="40">
+        <f t="shared" si="11"/>
+        <v>0.69207230287503563</v>
+      </c>
+      <c r="D153" s="40">
+        <f t="shared" si="11"/>
+        <v>0.90260494441679118</v>
+      </c>
+      <c r="E153" s="40" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F153" s="16"/>
+      <c r="G153" s="16"/>
+      <c r="H153" s="16"/>
+      <c r="I153" s="16"/>
+      <c r="J153" s="16"/>
+      <c r="K153" s="16"/>
+      <c r="L153" s="16"/>
+      <c r="M153" s="16"/>
+      <c r="N153" s="16"/>
+      <c r="O153" s="16"/>
+      <c r="P153" s="16"/>
+      <c r="Q153" s="16"/>
+      <c r="R153" s="16"/>
+      <c r="S153" s="16"/>
+      <c r="T153" s="16"/>
+      <c r="U153" s="16"/>
+      <c r="V153" s="16"/>
+      <c r="W153" s="16"/>
+      <c r="X153" s="16"/>
+      <c r="Y153" s="16"/>
+      <c r="Z153" s="16"/>
+      <c r="AA153" s="16"/>
+      <c r="AB153" s="16"/>
+      <c r="AC153" s="16"/>
+    </row>
+    <row r="154" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A154" s="86"/>
+      <c r="B154" s="15">
+        <v>8</v>
+      </c>
+      <c r="C154" s="40">
+        <f t="shared" si="11"/>
+        <v>0.64660904255319152</v>
+      </c>
+      <c r="D154" s="40">
+        <f t="shared" si="11"/>
+        <v>0.81437125748502992</v>
+      </c>
+      <c r="E154" s="40" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F154" s="16"/>
+      <c r="G154" s="16"/>
+      <c r="H154" s="16"/>
+      <c r="I154" s="16"/>
+      <c r="J154" s="16"/>
+      <c r="K154" s="16"/>
+      <c r="L154" s="16"/>
+      <c r="M154" s="16"/>
+      <c r="N154" s="16"/>
+      <c r="O154" s="16"/>
+      <c r="P154" s="16"/>
+      <c r="Q154" s="16"/>
+      <c r="R154" s="16"/>
+      <c r="S154" s="16"/>
+      <c r="T154" s="16"/>
+      <c r="U154" s="16"/>
+      <c r="V154" s="16"/>
+      <c r="W154" s="16"/>
+      <c r="X154" s="16"/>
+      <c r="Y154" s="16"/>
+      <c r="Z154" s="16"/>
+      <c r="AA154" s="16"/>
+      <c r="AB154" s="16"/>
+      <c r="AC154" s="16"/>
+    </row>
+    <row r="155" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A155" s="86"/>
+      <c r="B155" s="15">
+        <v>10</v>
+      </c>
+      <c r="C155" s="40">
+        <f>C141/B141</f>
+        <v>0.58939393939393936</v>
+      </c>
+      <c r="D155" s="40">
+        <f t="shared" ref="D155:E161" si="12">D141/$B141</f>
+        <v>0.74953252632614897</v>
+      </c>
+      <c r="E155" s="40" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F155" s="16"/>
+      <c r="G155" s="16"/>
+      <c r="H155" s="16"/>
+      <c r="I155" s="16"/>
+      <c r="J155" s="16"/>
+      <c r="K155" s="16"/>
+      <c r="L155" s="16"/>
+      <c r="M155" s="16"/>
+      <c r="N155" s="16"/>
+      <c r="O155" s="16"/>
+      <c r="P155" s="16"/>
+      <c r="Q155" s="16"/>
+      <c r="R155" s="16"/>
+      <c r="S155" s="16"/>
+      <c r="T155" s="16"/>
+      <c r="U155" s="16"/>
+      <c r="V155" s="16"/>
+      <c r="W155" s="16"/>
+      <c r="X155" s="16"/>
+      <c r="Y155" s="16"/>
+      <c r="Z155" s="16"/>
+      <c r="AA155" s="16"/>
+      <c r="AB155" s="16"/>
+      <c r="AC155" s="16"/>
+    </row>
+    <row r="156" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A156" s="86"/>
+      <c r="B156" s="15">
         <v>12</v>
       </c>
-      <c r="C148" s="40" t="e">
-        <f t="shared" si="7"/>
+      <c r="C156" s="40">
+        <f t="shared" ref="C156:C161" si="13">C142/$B142</f>
+        <v>0.56475029036004643</v>
+      </c>
+      <c r="D156" s="40">
+        <f t="shared" si="12"/>
+        <v>0.78997593560700352</v>
+      </c>
+      <c r="E156" s="40" t="e">
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="D148" s="40" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E148" s="40" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F148" s="31"/>
-      <c r="G148" s="31"/>
-      <c r="H148" s="31"/>
-      <c r="I148" s="31"/>
-      <c r="J148" s="31"/>
-      <c r="K148" s="31"/>
-      <c r="L148" s="31"/>
-      <c r="M148" s="31"/>
-      <c r="N148" s="31"/>
-      <c r="O148" s="31"/>
-      <c r="P148" s="31"/>
-      <c r="Q148" s="31"/>
-      <c r="R148" s="31"/>
-      <c r="S148" s="31"/>
-      <c r="T148" s="31"/>
+      <c r="F156" s="31"/>
+      <c r="G156" s="31"/>
+      <c r="H156" s="31"/>
+      <c r="I156" s="31"/>
+      <c r="J156" s="31"/>
+      <c r="K156" s="31"/>
+      <c r="L156" s="31"/>
+      <c r="M156" s="31"/>
+      <c r="N156" s="31"/>
+      <c r="O156" s="31"/>
+      <c r="P156" s="31"/>
+      <c r="Q156" s="31"/>
+      <c r="R156" s="31"/>
+      <c r="S156" s="31"/>
+      <c r="T156" s="31"/>
+      <c r="U156" s="31"/>
+      <c r="V156" s="31"/>
+      <c r="W156" s="31"/>
+      <c r="X156" s="31"/>
+      <c r="Y156" s="31"/>
+      <c r="Z156" s="31"/>
+      <c r="AA156" s="31"/>
+      <c r="AB156" s="31"/>
+      <c r="AC156" s="31"/>
     </row>
-    <row r="149" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="66"/>
-      <c r="B149" s="42">
+    <row r="157" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A157" s="86"/>
+      <c r="B157" s="15">
+        <v>14</v>
+      </c>
+      <c r="C157" s="40">
+        <f t="shared" si="13"/>
+        <v>0.52704313895512678</v>
+      </c>
+      <c r="D157" s="40">
+        <f t="shared" si="12"/>
+        <v>0.74510341049171347</v>
+      </c>
+      <c r="E157" s="40">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="F157" s="31"/>
+      <c r="G157" s="31"/>
+      <c r="H157" s="31"/>
+      <c r="I157" s="31"/>
+      <c r="J157" s="31"/>
+      <c r="K157" s="31"/>
+      <c r="L157" s="31"/>
+      <c r="M157" s="31"/>
+      <c r="N157" s="31"/>
+      <c r="O157" s="31"/>
+      <c r="P157" s="31"/>
+      <c r="Q157" s="31"/>
+      <c r="R157" s="31"/>
+      <c r="S157" s="31"/>
+      <c r="T157" s="31"/>
+      <c r="U157" s="31"/>
+      <c r="V157" s="31"/>
+      <c r="W157" s="31"/>
+      <c r="X157" s="31"/>
+      <c r="Y157" s="31"/>
+      <c r="Z157" s="31"/>
+      <c r="AA157" s="31"/>
+      <c r="AB157" s="31"/>
+      <c r="AC157" s="31"/>
+    </row>
+    <row r="158" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A158" s="86"/>
+      <c r="B158" s="15">
         <v>16</v>
       </c>
-      <c r="C149" s="40" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D149" s="40" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E149" s="40" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F149" s="31"/>
-      <c r="G149" s="31"/>
-      <c r="H149" s="31"/>
-      <c r="I149" s="31"/>
-      <c r="J149" s="31"/>
-      <c r="K149" s="31"/>
-      <c r="L149" s="31"/>
-      <c r="M149" s="31"/>
-      <c r="N149" s="31"/>
-      <c r="O149" s="31"/>
-      <c r="P149" s="31"/>
-      <c r="Q149" s="31"/>
-      <c r="R149" s="31"/>
-      <c r="S149" s="31"/>
-      <c r="T149" s="31"/>
+      <c r="C158" s="40">
+        <f t="shared" si="13"/>
+        <v>0.49698487326246932</v>
+      </c>
+      <c r="D158" s="40">
+        <f t="shared" si="12"/>
+        <v>0.69784489077847822</v>
+      </c>
+      <c r="E158" s="40">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="F158" s="16"/>
+      <c r="G158" s="16"/>
+      <c r="H158" s="16"/>
+      <c r="I158" s="16"/>
+      <c r="J158" s="16"/>
+      <c r="K158" s="16"/>
+      <c r="L158" s="16"/>
+      <c r="M158" s="16"/>
+      <c r="N158" s="16"/>
+      <c r="O158" s="16"/>
+      <c r="P158" s="16"/>
+      <c r="Q158" s="16"/>
+      <c r="R158" s="16"/>
+      <c r="S158" s="16"/>
+      <c r="T158" s="16"/>
+      <c r="U158" s="16"/>
+      <c r="V158" s="16"/>
+      <c r="W158" s="16"/>
+      <c r="X158" s="16"/>
+      <c r="Y158" s="16"/>
+      <c r="Z158" s="16"/>
+      <c r="AA158" s="16"/>
+      <c r="AB158" s="16"/>
+      <c r="AC158" s="16"/>
     </row>
-    <row r="150" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="83"/>
-      <c r="B150" s="33" t="s">
+    <row r="159" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A159" s="86"/>
+      <c r="B159" s="15">
+        <v>18</v>
+      </c>
+      <c r="C159" s="40">
+        <f t="shared" si="13"/>
+        <v>0.45941987906273624</v>
+      </c>
+      <c r="D159" s="40">
+        <f t="shared" si="12"/>
+        <v>0.68232722320772643</v>
+      </c>
+      <c r="E159" s="40">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="F159" s="16"/>
+      <c r="G159" s="16"/>
+      <c r="H159" s="16"/>
+      <c r="I159" s="16"/>
+      <c r="J159" s="16"/>
+      <c r="K159" s="16"/>
+      <c r="L159" s="16"/>
+      <c r="M159" s="16"/>
+      <c r="N159" s="16"/>
+      <c r="O159" s="16"/>
+      <c r="P159" s="16"/>
+      <c r="Q159" s="16"/>
+      <c r="R159" s="16"/>
+      <c r="S159" s="16"/>
+      <c r="T159" s="16"/>
+      <c r="U159" s="16"/>
+      <c r="V159" s="16"/>
+      <c r="W159" s="16"/>
+      <c r="X159" s="16"/>
+      <c r="Y159" s="16"/>
+      <c r="Z159" s="16"/>
+      <c r="AA159" s="16"/>
+      <c r="AB159" s="16"/>
+      <c r="AC159" s="16"/>
+    </row>
+    <row r="160" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A160" s="86"/>
+      <c r="B160" s="15">
+        <v>20</v>
+      </c>
+      <c r="C160" s="40">
+        <f t="shared" si="13"/>
+        <v>0.45571696344892221</v>
+      </c>
+      <c r="D160" s="40">
+        <f t="shared" si="12"/>
+        <v>0.62879788639365919</v>
+      </c>
+      <c r="E160" s="40">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="F160" s="16"/>
+      <c r="G160" s="16"/>
+      <c r="H160" s="16"/>
+      <c r="I160" s="16"/>
+      <c r="J160" s="16"/>
+      <c r="K160" s="16"/>
+      <c r="L160" s="16"/>
+      <c r="M160" s="16"/>
+      <c r="N160" s="16"/>
+      <c r="O160" s="16"/>
+      <c r="P160" s="16"/>
+      <c r="Q160" s="16"/>
+      <c r="R160" s="16"/>
+      <c r="S160" s="16"/>
+      <c r="T160" s="16"/>
+      <c r="U160" s="16"/>
+      <c r="V160" s="16"/>
+      <c r="W160" s="16"/>
+      <c r="X160" s="16"/>
+      <c r="Y160" s="16"/>
+      <c r="Z160" s="16"/>
+      <c r="AA160" s="16"/>
+      <c r="AB160" s="16"/>
+      <c r="AC160" s="16"/>
+    </row>
+    <row r="161" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="86"/>
+      <c r="B161" s="87">
+        <v>40</v>
+      </c>
+      <c r="C161" s="88">
+        <f t="shared" si="13"/>
+        <v>0.20243547044129889</v>
+      </c>
+      <c r="D161" s="88">
+        <f t="shared" si="12"/>
+        <v>0.27811860940695293</v>
+      </c>
+      <c r="E161" s="88">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="F161" s="16"/>
+      <c r="G161" s="16"/>
+      <c r="H161" s="16"/>
+      <c r="I161" s="16"/>
+      <c r="J161" s="16"/>
+      <c r="K161" s="16"/>
+      <c r="L161" s="16"/>
+      <c r="M161" s="16"/>
+      <c r="N161" s="16"/>
+      <c r="O161" s="16"/>
+      <c r="P161" s="16"/>
+      <c r="Q161" s="16"/>
+      <c r="R161" s="16"/>
+      <c r="S161" s="16"/>
+      <c r="T161" s="16"/>
+      <c r="U161" s="16"/>
+      <c r="V161" s="16"/>
+      <c r="W161" s="16"/>
+      <c r="X161" s="16"/>
+      <c r="Y161" s="16"/>
+      <c r="Z161" s="16"/>
+      <c r="AA161" s="16"/>
+      <c r="AB161" s="16"/>
+      <c r="AC161" s="16"/>
+    </row>
+    <row r="162" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A162" s="86"/>
+      <c r="B162" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="C150" s="86"/>
-      <c r="D150" s="87"/>
-      <c r="E150" s="87"/>
-      <c r="F150" s="87"/>
-      <c r="G150" s="87"/>
-      <c r="H150" s="87"/>
-      <c r="I150" s="87"/>
-      <c r="J150" s="87"/>
-      <c r="K150" s="87"/>
-      <c r="L150" s="87"/>
-      <c r="M150" s="87"/>
-      <c r="N150" s="87"/>
-      <c r="O150" s="87"/>
-      <c r="P150" s="87"/>
-      <c r="Q150" s="87"/>
-      <c r="R150" s="87"/>
-      <c r="S150" s="87"/>
-      <c r="T150" s="88"/>
+      <c r="C162" s="78" t="s">
+        <v>124</v>
+      </c>
+      <c r="D162" s="83"/>
+      <c r="E162" s="83"/>
+      <c r="F162" s="83"/>
+      <c r="G162" s="83"/>
+      <c r="H162" s="83"/>
+      <c r="I162" s="83"/>
+      <c r="J162" s="83"/>
+      <c r="K162" s="83"/>
+      <c r="L162" s="83"/>
+      <c r="M162" s="83"/>
+      <c r="N162" s="83"/>
+      <c r="O162" s="83"/>
+      <c r="P162" s="83"/>
+      <c r="Q162" s="83"/>
+      <c r="R162" s="83"/>
+      <c r="S162" s="83"/>
+      <c r="T162" s="83"/>
+      <c r="U162" s="83"/>
+      <c r="V162" s="83"/>
+      <c r="W162" s="83"/>
+      <c r="X162" s="83"/>
+      <c r="Y162" s="83"/>
+      <c r="Z162" s="83"/>
+      <c r="AA162" s="83"/>
+      <c r="AB162" s="83"/>
+      <c r="AC162" s="84"/>
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="A120:A150"/>
+    <mergeCell ref="B148:E148"/>
+    <mergeCell ref="B134:E134"/>
+    <mergeCell ref="B120:E120"/>
+    <mergeCell ref="A120:A162"/>
+    <mergeCell ref="C162:AC162"/>
     <mergeCell ref="A89:A119"/>
     <mergeCell ref="C119:T119"/>
     <mergeCell ref="B89:E89"/>
     <mergeCell ref="B99:E99"/>
     <mergeCell ref="B109:E109"/>
-    <mergeCell ref="B140:E140"/>
-    <mergeCell ref="B130:E130"/>
-    <mergeCell ref="B120:E120"/>
-    <mergeCell ref="C150:T150"/>
     <mergeCell ref="A24:L24"/>
     <mergeCell ref="M24:N24"/>
     <mergeCell ref="M1:N1"/>
@@ -39359,7 +40656,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4269BDC4-CFAE-4A4A-95F0-395DE59C8746}">
-  <dimension ref="M10:M14"/>
+  <dimension ref="M10:M23"/>
   <sheetFormatPr defaultRowHeight="22.1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="16384" width="9.140625" style="41"/>
@@ -39390,6 +40687,41 @@
         <v>101</v>
       </c>
     </row>
+    <row r="17" spans="13:13" x14ac:dyDescent="0.3">
+      <c r="M17" s="44" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="18" spans="13:13" x14ac:dyDescent="0.3">
+      <c r="M18" s="41" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="19" spans="13:13" x14ac:dyDescent="0.3">
+      <c r="M19" s="41" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="20" spans="13:13" x14ac:dyDescent="0.3">
+      <c r="M20" s="41" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="21" spans="13:13" x14ac:dyDescent="0.3">
+      <c r="M21" s="41" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="22" spans="13:13" x14ac:dyDescent="0.3">
+      <c r="M22" s="41" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="23" spans="13:13" x14ac:dyDescent="0.3">
+      <c r="M23" s="41" t="s">
+        <v>122</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/DecompositionLU/docs/statistics.xlsx
+++ b/DecompositionLU/docs/statistics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maxim\source\repos\practice\SECOND_COURSE\FOR_ITLAB\ArchBenchs\DecompositionLU\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10EC723C-D471-490B-9B42-2551FCE50A64}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC2A0560-C327-424F-8F5A-116FD11421DC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-114" yWindow="-114" windowWidth="27602" windowHeight="15027" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="117">
   <si>
     <t>Я не уверен, будет ли это использоваться в готовой презентации и так ли это надо делать, если да, так что пока считаем, что файл для личного пользования.</t>
   </si>
@@ -427,9 +427,6 @@
     <t>Замеры версии 3.2</t>
   </si>
   <si>
-    <t>Замеры на кластере</t>
-  </si>
-  <si>
     <t>Версия 3.2</t>
   </si>
   <si>
@@ -474,34 +471,13 @@
     <t>Мне нравятся результаты, но есть ощущение, что можно лучше. Графики точно не самые хорошие.</t>
   </si>
   <si>
-    <t>окак</t>
-  </si>
-  <si>
-    <t>Про кластер:</t>
-  </si>
-  <si>
-    <t>[simonov_m@master build]$ lscpu | grep -E "^(CPU\(s\)|Core\(s\) per socket|Socket\(s\)|NUMA)"</t>
-  </si>
-  <si>
-    <t>CPU(s):                8</t>
-  </si>
-  <si>
-    <t>Core(s) per socket:    1</t>
-  </si>
-  <si>
-    <t>Socket(s):             8</t>
-  </si>
-  <si>
-    <t>NUMA node(s):          1</t>
-  </si>
-  <si>
-    <t>NUMA node0 CPU(s):     0-7</t>
-  </si>
-  <si>
     <t>n = 15000</t>
   </si>
   <si>
-    <t>В ходе работы выяснил следующее - на миникластере 2 процессора по 10 физ ядер, балансировать их надо так: число потоков &lt;= 10 - все на одном, &gt;10 - поровну, но на каждом четное количество.</t>
+    <t>В ходе работы выяснил следующее - на миникластере 2 процессора по 10 физ ядер, балансировать их надо поровну, но на каждом четное количество (чем больше размер матрицы, тем более заметно, например, при n=10000 и числе потоков &lt;= 10, это незаметно)</t>
+  </si>
+  <si>
+    <t>Замеры на кластере, данные, аналогично, вкладке "Про процессор"</t>
   </si>
 </sst>
 </file>
@@ -981,6 +957,15 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1020,6 +1005,45 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1054,54 +1078,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -11043,6 +11019,27 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>257265</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>130577</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>66384</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46005</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>35587</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>29914</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>25229</c:v>
+                </c:pt>
                 <c:pt idx="7">
                   <c:v>23660</c:v>
                 </c:pt>
@@ -11553,37 +11550,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>1.970216806941498</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>3.8754067245119308</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>5.5921095533094229</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>7.2291848146795177</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>8.6001537741525702</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>10.19719370565619</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>10.873415046491969</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>12.214651979868957</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>12.466201482773659</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>14.049751515482496</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12615,37 +12612,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>0.98510840347074902</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>0.9688516811279827</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>0.93201825888490386</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>0.90364810183493971</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>0.86001537741525702</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>0.84976614213801582</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>0.77667250332085491</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>0.76341574874180984</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>0.6925667490429811</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>0.7024875757741248</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -34610,17 +34607,17 @@
       <c r="N3" s="6"/>
     </row>
     <row r="5" spans="1:23" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="49" t="s">
+      <c r="A5" s="52" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="50"/>
-      <c r="C5" s="50"/>
-      <c r="D5" s="50"/>
-      <c r="E5" s="51"/>
-      <c r="G5" s="56" t="s">
+      <c r="B5" s="53"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="54"/>
+      <c r="G5" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="H5" s="56"/>
+      <c r="H5" s="59"/>
       <c r="S5" s="5"/>
       <c r="T5" s="14"/>
       <c r="U5" s="14"/>
@@ -34631,14 +34628,14 @@
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="53" t="s">
+      <c r="B6" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="53"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="G6" s="56"/>
-      <c r="H6" s="56"/>
+      <c r="C6" s="56"/>
+      <c r="D6" s="56"/>
+      <c r="E6" s="56"/>
+      <c r="G6" s="59"/>
+      <c r="H6" s="59"/>
       <c r="S6" s="14"/>
       <c r="T6" s="14"/>
       <c r="U6" s="14"/>
@@ -34661,8 +34658,8 @@
       <c r="E7" s="8">
         <v>10000</v>
       </c>
-      <c r="G7" s="56"/>
-      <c r="H7" s="56"/>
+      <c r="G7" s="59"/>
+      <c r="H7" s="59"/>
       <c r="S7" s="14"/>
       <c r="T7" s="14"/>
       <c r="U7" s="14"/>
@@ -34670,15 +34667,15 @@
       <c r="W7" s="14"/>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A8" s="54" t="s">
+      <c r="A8" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="54"/>
-      <c r="C8" s="54"/>
-      <c r="D8" s="54"/>
-      <c r="E8" s="54"/>
-      <c r="G8" s="56"/>
-      <c r="H8" s="56"/>
+      <c r="B8" s="57"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
       <c r="S8" s="14"/>
       <c r="T8" s="14"/>
       <c r="U8" s="14"/>
@@ -34754,13 +34751,13 @@
       <c r="W11" s="5"/>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A12" s="54" t="s">
+      <c r="A12" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="54"/>
-      <c r="C12" s="54"/>
-      <c r="D12" s="54"/>
-      <c r="E12" s="54"/>
+      <c r="B12" s="57"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="57"/>
       <c r="F12" s="5"/>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.25">
@@ -34773,7 +34770,7 @@
       <c r="C13" s="10">
         <v>232</v>
       </c>
-      <c r="D13" s="58" t="s">
+      <c r="D13" s="61" t="s">
         <v>21</v>
       </c>
       <c r="E13" s="10">
@@ -34791,7 +34788,7 @@
       <c r="C14" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="59"/>
+      <c r="D14" s="62"/>
       <c r="E14" s="10" t="s">
         <v>10</v>
       </c>
@@ -34809,30 +34806,30 @@
       <c r="C15" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="60"/>
+      <c r="D15" s="63"/>
       <c r="E15" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="61" t="s">
+      <c r="A18" s="64" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="61"/>
-      <c r="C18" s="61"/>
-      <c r="D18" s="61"/>
-      <c r="E18" s="61"/>
+      <c r="B18" s="64"/>
+      <c r="C18" s="64"/>
+      <c r="D18" s="64"/>
+      <c r="E18" s="64"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B19" s="53" t="s">
+      <c r="B19" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="C19" s="53"/>
-      <c r="D19" s="53"/>
-      <c r="E19" s="53"/>
+      <c r="C19" s="56"/>
+      <c r="D19" s="56"/>
+      <c r="E19" s="56"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
@@ -34852,13 +34849,13 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="54" t="s">
+      <c r="A21" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="B21" s="54"/>
-      <c r="C21" s="54"/>
-      <c r="D21" s="54"/>
-      <c r="E21" s="54"/>
+      <c r="B21" s="57"/>
+      <c r="C21" s="57"/>
+      <c r="D21" s="57"/>
+      <c r="E21" s="57"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
@@ -34911,17 +34908,17 @@
         <v>35</v>
       </c>
       <c r="G24" s="18"/>
-      <c r="H24" s="55"/>
-      <c r="I24" s="55"/>
+      <c r="H24" s="58"/>
+      <c r="I24" s="58"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="54" t="s">
+      <c r="A25" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="B25" s="54"/>
-      <c r="C25" s="54"/>
-      <c r="D25" s="54"/>
-      <c r="E25" s="54"/>
+      <c r="B25" s="57"/>
+      <c r="C25" s="57"/>
+      <c r="D25" s="57"/>
+      <c r="E25" s="57"/>
       <c r="G25" s="19"/>
       <c r="H25" s="17"/>
       <c r="I25" s="17"/>
@@ -35006,15 +35003,15 @@
       <c r="I30" s="18"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="49" t="s">
+      <c r="A31" s="52" t="s">
         <v>70</v>
       </c>
-      <c r="B31" s="50"/>
-      <c r="C31" s="51"/>
-      <c r="D31" s="52" t="s">
+      <c r="B31" s="53"/>
+      <c r="C31" s="54"/>
+      <c r="D31" s="55" t="s">
         <v>91</v>
       </c>
-      <c r="E31" s="52" t="s">
+      <c r="E31" s="55" t="s">
         <v>91</v>
       </c>
       <c r="G31" s="20"/>
@@ -35025,12 +35022,12 @@
       <c r="A32" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B32" s="53" t="s">
+      <c r="B32" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="53"/>
-      <c r="D32" s="53"/>
-      <c r="E32" s="53"/>
+      <c r="C32" s="56"/>
+      <c r="D32" s="56"/>
+      <c r="E32" s="56"/>
       <c r="G32" s="23"/>
       <c r="H32" s="18"/>
       <c r="I32" s="18"/>
@@ -35056,13 +35053,13 @@
       <c r="I33" s="18"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="54" t="s">
+      <c r="A34" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="B34" s="54"/>
-      <c r="C34" s="54"/>
-      <c r="D34" s="54"/>
-      <c r="E34" s="54"/>
+      <c r="B34" s="57"/>
+      <c r="C34" s="57"/>
+      <c r="D34" s="57"/>
+      <c r="E34" s="57"/>
       <c r="G34" s="23"/>
       <c r="H34" s="18"/>
       <c r="I34" s="18"/>
@@ -35128,13 +35125,13 @@
       <c r="I37" s="18"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="54" t="s">
+      <c r="A38" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="B38" s="54"/>
-      <c r="C38" s="54"/>
-      <c r="D38" s="54"/>
-      <c r="E38" s="54"/>
+      <c r="B38" s="57"/>
+      <c r="C38" s="57"/>
+      <c r="D38" s="57"/>
+      <c r="E38" s="57"/>
       <c r="G38" s="23"/>
       <c r="H38" s="18"/>
       <c r="I38" s="18"/>
@@ -35200,23 +35197,23 @@
       <c r="I41" s="18"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B42" s="57" t="s">
+      <c r="B42" s="60" t="s">
         <v>66</v>
       </c>
-      <c r="C42" s="57"/>
-      <c r="D42" s="57"/>
-      <c r="E42" s="57"/>
+      <c r="C42" s="60"/>
+      <c r="D42" s="60"/>
+      <c r="E42" s="60"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="49" t="s">
+      <c r="A44" s="52" t="s">
         <v>82</v>
       </c>
-      <c r="B44" s="50"/>
-      <c r="C44" s="51"/>
-      <c r="D44" s="52" t="s">
+      <c r="B44" s="53"/>
+      <c r="C44" s="54"/>
+      <c r="D44" s="55" t="s">
         <v>92</v>
       </c>
-      <c r="E44" s="52" t="s">
+      <c r="E44" s="55" t="s">
         <v>91</v>
       </c>
     </row>
@@ -35224,12 +35221,12 @@
       <c r="A45" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B45" s="53" t="s">
+      <c r="B45" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="C45" s="53"/>
-      <c r="D45" s="53"/>
-      <c r="E45" s="53"/>
+      <c r="C45" s="56"/>
+      <c r="D45" s="56"/>
+      <c r="E45" s="56"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
@@ -35249,13 +35246,13 @@
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="54" t="s">
+      <c r="A47" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="B47" s="54"/>
-      <c r="C47" s="54"/>
-      <c r="D47" s="54"/>
-      <c r="E47" s="54"/>
+      <c r="B47" s="57"/>
+      <c r="C47" s="57"/>
+      <c r="D47" s="57"/>
+      <c r="E47" s="57"/>
       <c r="G47" s="1" t="s">
         <v>95</v>
       </c>
@@ -35333,13 +35330,13 @@
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="54" t="s">
+      <c r="A51" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="B51" s="54"/>
-      <c r="C51" s="54"/>
-      <c r="D51" s="54"/>
-      <c r="E51" s="54"/>
+      <c r="B51" s="57"/>
+      <c r="C51" s="57"/>
+      <c r="D51" s="57"/>
+      <c r="E51" s="57"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
@@ -35398,15 +35395,15 @@
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="49" t="s">
+      <c r="A57" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="B57" s="50"/>
-      <c r="C57" s="51"/>
-      <c r="D57" s="52" t="s">
+      <c r="B57" s="53"/>
+      <c r="C57" s="54"/>
+      <c r="D57" s="55" t="s">
         <v>92</v>
       </c>
-      <c r="E57" s="52" t="s">
+      <c r="E57" s="55" t="s">
         <v>91</v>
       </c>
     </row>
@@ -35414,12 +35411,12 @@
       <c r="A58" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B58" s="53" t="s">
+      <c r="B58" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="C58" s="53"/>
-      <c r="D58" s="53"/>
-      <c r="E58" s="53"/>
+      <c r="C58" s="56"/>
+      <c r="D58" s="56"/>
+      <c r="E58" s="56"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
@@ -35439,13 +35436,13 @@
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="54" t="s">
+      <c r="A60" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="B60" s="54"/>
-      <c r="C60" s="54"/>
-      <c r="D60" s="54"/>
-      <c r="E60" s="54"/>
+      <c r="B60" s="57"/>
+      <c r="C60" s="57"/>
+      <c r="D60" s="57"/>
+      <c r="E60" s="57"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
@@ -35499,15 +35496,15 @@
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="54" t="s">
+      <c r="A64" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="B64" s="54"/>
-      <c r="C64" s="54"/>
-      <c r="D64" s="54"/>
-      <c r="E64" s="54"/>
+      <c r="B64" s="57"/>
+      <c r="C64" s="57"/>
+      <c r="D64" s="57"/>
+      <c r="E64" s="57"/>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
         <v>7</v>
       </c>
@@ -35524,7 +35521,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
         <v>8</v>
       </c>
@@ -35541,7 +35538,7 @@
         <v>58818</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
         <v>9</v>
       </c>
@@ -35558,45 +35555,45 @@
         <v>59837</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C68" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="49" t="s">
-        <v>109</v>
-      </c>
-      <c r="B70" s="50"/>
-      <c r="C70" s="51"/>
-      <c r="D70" s="52" t="s">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="52" t="s">
+        <v>108</v>
+      </c>
+      <c r="B70" s="53"/>
+      <c r="C70" s="54"/>
+      <c r="D70" s="55" t="s">
         <v>92</v>
       </c>
-      <c r="E70" s="52" t="s">
+      <c r="E70" s="55" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B71" s="53" t="s">
+      <c r="B71" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="C71" s="53"/>
-      <c r="D71" s="53"/>
-      <c r="E71" s="53"/>
+      <c r="C71" s="56"/>
+      <c r="D71" s="56"/>
+      <c r="E71" s="56"/>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="54" t="s">
-        <v>110</v>
-      </c>
-      <c r="B72" s="54"/>
-      <c r="C72" s="54"/>
-      <c r="D72" s="54"/>
-      <c r="E72" s="54"/>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="57" t="s">
+        <v>109</v>
+      </c>
+      <c r="B72" s="57"/>
+      <c r="C72" s="57"/>
+      <c r="D72" s="57"/>
+      <c r="E72" s="57"/>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
         <v>6</v>
       </c>
@@ -35613,55 +35610,67 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B74" s="9"/>
+      <c r="B74" s="9">
+        <v>13</v>
+      </c>
       <c r="C74" s="10">
         <v>107</v>
       </c>
-      <c r="D74" s="10"/>
+      <c r="D74" s="10">
+        <v>450</v>
+      </c>
       <c r="E74" s="10">
         <v>1349</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B75" s="9"/>
+      <c r="B75" s="9">
+        <v>50</v>
+      </c>
       <c r="C75" s="10">
         <v>598</v>
       </c>
-      <c r="D75" s="10"/>
+      <c r="D75" s="10">
+        <v>5232</v>
+      </c>
       <c r="E75" s="10">
         <v>12676</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B76" s="9"/>
+      <c r="B76" s="9">
+        <v>64</v>
+      </c>
       <c r="C76" s="10">
         <v>720</v>
       </c>
-      <c r="D76" s="10"/>
+      <c r="D76" s="10">
+        <v>5682</v>
+      </c>
       <c r="E76" s="10">
         <v>14026</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="54" t="s">
-        <v>111</v>
-      </c>
-      <c r="B77" s="54"/>
-      <c r="C77" s="54"/>
-      <c r="D77" s="54"/>
-      <c r="E77" s="54"/>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="57" t="s">
+        <v>110</v>
+      </c>
+      <c r="B77" s="57"/>
+      <c r="C77" s="57"/>
+      <c r="D77" s="57"/>
+      <c r="E77" s="57"/>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
         <v>6</v>
       </c>
@@ -35678,67 +35687,47 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B79" s="9">
-        <v>792</v>
-      </c>
-      <c r="C79" s="10">
-        <v>2170</v>
-      </c>
-      <c r="D79" s="10">
-        <v>4256</v>
-      </c>
-      <c r="E79" s="10">
-        <v>8662</v>
-      </c>
-      <c r="F79" s="1" t="s">
-        <v>115</v>
-      </c>
+      <c r="B79" s="9"/>
+      <c r="C79" s="10"/>
+      <c r="D79" s="10"/>
+      <c r="E79" s="10"/>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B80" s="9">
-        <v>349</v>
-      </c>
-      <c r="C80" s="10">
-        <v>1505</v>
-      </c>
-      <c r="D80" s="10">
-        <v>3928</v>
-      </c>
-      <c r="E80" s="10">
-        <v>11608</v>
-      </c>
+      <c r="B80" s="9"/>
+      <c r="C80" s="10"/>
+      <c r="D80" s="10"/>
+      <c r="E80" s="10"/>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B81" s="9">
-        <v>1141</v>
-      </c>
-      <c r="C81" s="10">
-        <v>3677</v>
-      </c>
-      <c r="D81" s="10">
-        <v>8186</v>
-      </c>
-      <c r="E81" s="10">
-        <v>20279</v>
-      </c>
+      <c r="B81" s="9"/>
+      <c r="C81" s="10"/>
+      <c r="D81" s="10"/>
+      <c r="E81" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="A70:C70"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="B71:E71"/>
-    <mergeCell ref="A72:E72"/>
-    <mergeCell ref="A77:E77"/>
+    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="D57:E57"/>
+    <mergeCell ref="B58:E58"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A31:C31"/>
     <mergeCell ref="H24:I24"/>
     <mergeCell ref="G5:H8"/>
     <mergeCell ref="B42:E42"/>
@@ -35754,18 +35743,11 @@
     <mergeCell ref="B19:E19"/>
     <mergeCell ref="A21:E21"/>
     <mergeCell ref="A25:E25"/>
-    <mergeCell ref="B45:E45"/>
-    <mergeCell ref="A47:E47"/>
-    <mergeCell ref="A51:E51"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A57:C57"/>
-    <mergeCell ref="D57:E57"/>
-    <mergeCell ref="B58:E58"/>
-    <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="A70:C70"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="B71:E71"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A77:E77"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <hyperlinks>
@@ -35797,24 +35779,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="64" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-      <c r="J1" s="61"/>
-      <c r="K1" s="61"/>
-      <c r="L1" s="61"/>
-      <c r="M1" s="52" t="s">
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="64"/>
+      <c r="M1" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="N1" s="52"/>
+      <c r="N1" s="55"/>
       <c r="O1" s="36"/>
       <c r="P1" s="35"/>
       <c r="Q1" s="35"/>
@@ -35829,14 +35811,14 @@
       <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="79" t="s">
+      <c r="A2" s="73" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="74" t="s">
+      <c r="B2" s="65" t="s">
         <v>78</v>
       </c>
-      <c r="C2" s="75"/>
-      <c r="D2" s="76"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="67"/>
       <c r="E2" s="31"/>
       <c r="F2" s="31"/>
       <c r="G2" s="31"/>
@@ -35861,7 +35843,7 @@
       <c r="Z2" s="30"/>
     </row>
     <row r="3" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="79"/>
+      <c r="A3" s="73"/>
       <c r="B3" s="29" t="s">
         <v>77</v>
       </c>
@@ -35895,7 +35877,7 @@
       <c r="Z3" s="30"/>
     </row>
     <row r="4" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="79"/>
+      <c r="A4" s="73"/>
       <c r="B4" s="15">
         <v>1</v>
       </c>
@@ -35929,7 +35911,7 @@
       <c r="Z4" s="30"/>
     </row>
     <row r="5" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="79"/>
+      <c r="A5" s="73"/>
       <c r="B5" s="15">
         <v>2</v>
       </c>
@@ -35963,7 +35945,7 @@
       <c r="Z5" s="30"/>
     </row>
     <row r="6" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="79"/>
+      <c r="A6" s="73"/>
       <c r="B6" s="15">
         <v>4</v>
       </c>
@@ -35986,7 +35968,7 @@
       <c r="O6" s="38"/>
     </row>
     <row r="7" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="79"/>
+      <c r="A7" s="73"/>
       <c r="B7" s="15">
         <v>6</v>
       </c>
@@ -36009,7 +35991,7 @@
       <c r="O7" s="38"/>
     </row>
     <row r="8" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="79"/>
+      <c r="A8" s="73"/>
       <c r="B8" s="15">
         <v>8</v>
       </c>
@@ -36032,7 +36014,7 @@
       <c r="O8" s="38"/>
     </row>
     <row r="9" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="79"/>
+      <c r="A9" s="73"/>
       <c r="B9" s="15">
         <v>10</v>
       </c>
@@ -36055,7 +36037,7 @@
       <c r="O9" s="38"/>
     </row>
     <row r="10" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="79"/>
+      <c r="A10" s="73"/>
       <c r="B10" s="15">
         <v>12</v>
       </c>
@@ -36078,7 +36060,7 @@
       <c r="O10" s="38"/>
     </row>
     <row r="11" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="79"/>
+      <c r="A11" s="73"/>
       <c r="B11" s="15">
         <v>16</v>
       </c>
@@ -36103,37 +36085,37 @@
       <c r="Q11" s="27"/>
     </row>
     <row r="12" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="79"/>
+      <c r="A12" s="73"/>
       <c r="B12" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="C12" s="77" t="s">
+      <c r="C12" s="74" t="s">
         <v>81</v>
       </c>
-      <c r="D12" s="77"/>
-      <c r="E12" s="77"/>
-      <c r="F12" s="77"/>
-      <c r="G12" s="77"/>
-      <c r="H12" s="77"/>
-      <c r="I12" s="77"/>
-      <c r="J12" s="77"/>
-      <c r="K12" s="77"/>
-      <c r="L12" s="77"/>
-      <c r="M12" s="77"/>
-      <c r="N12" s="78"/>
+      <c r="D12" s="74"/>
+      <c r="E12" s="74"/>
+      <c r="F12" s="74"/>
+      <c r="G12" s="74"/>
+      <c r="H12" s="74"/>
+      <c r="I12" s="74"/>
+      <c r="J12" s="74"/>
+      <c r="K12" s="74"/>
+      <c r="L12" s="74"/>
+      <c r="M12" s="74"/>
+      <c r="N12" s="70"/>
       <c r="O12" s="39"/>
       <c r="P12" s="23"/>
       <c r="Q12" s="23"/>
     </row>
     <row r="13" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="79" t="s">
+      <c r="A13" s="73" t="s">
         <v>87</v>
       </c>
-      <c r="B13" s="74" t="s">
+      <c r="B13" s="65" t="s">
         <v>78</v>
       </c>
-      <c r="C13" s="75"/>
-      <c r="D13" s="76"/>
+      <c r="C13" s="66"/>
+      <c r="D13" s="67"/>
       <c r="E13" s="32"/>
       <c r="F13" s="31"/>
       <c r="G13" s="31"/>
@@ -36149,7 +36131,7 @@
       <c r="Q13" s="23"/>
     </row>
     <row r="14" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="79"/>
+      <c r="A14" s="73"/>
       <c r="B14" s="13" t="s">
         <v>77</v>
       </c>
@@ -36174,7 +36156,7 @@
       <c r="Q14" s="23"/>
     </row>
     <row r="15" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="79"/>
+      <c r="A15" s="73"/>
       <c r="B15" s="15">
         <v>1</v>
       </c>
@@ -36199,7 +36181,7 @@
       <c r="Q15" s="27"/>
     </row>
     <row r="16" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="79"/>
+      <c r="A16" s="73"/>
       <c r="B16" s="15">
         <v>2</v>
       </c>
@@ -36224,7 +36206,7 @@
       <c r="Q16" s="23"/>
     </row>
     <row r="17" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="79"/>
+      <c r="A17" s="73"/>
       <c r="B17" s="15">
         <v>4</v>
       </c>
@@ -36249,7 +36231,7 @@
       <c r="Q17" s="23"/>
     </row>
     <row r="18" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="79"/>
+      <c r="A18" s="73"/>
       <c r="B18" s="15">
         <v>6</v>
       </c>
@@ -36274,7 +36256,7 @@
       <c r="Q18" s="23"/>
     </row>
     <row r="19" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="79"/>
+      <c r="A19" s="73"/>
       <c r="B19" s="15">
         <v>8</v>
       </c>
@@ -36297,7 +36279,7 @@
       <c r="O19" s="38"/>
     </row>
     <row r="20" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="79"/>
+      <c r="A20" s="73"/>
       <c r="B20" s="15">
         <v>10</v>
       </c>
@@ -36320,7 +36302,7 @@
       <c r="O20" s="38"/>
     </row>
     <row r="21" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="79"/>
+      <c r="A21" s="73"/>
       <c r="B21" s="15">
         <v>12</v>
       </c>
@@ -36343,73 +36325,73 @@
       <c r="O21" s="38"/>
     </row>
     <row r="22" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="79"/>
-      <c r="B22" s="80" t="s">
+      <c r="A22" s="73"/>
+      <c r="B22" s="75" t="s">
         <v>86</v>
       </c>
-      <c r="C22" s="81" t="s">
+      <c r="C22" s="76" t="s">
         <v>88</v>
       </c>
-      <c r="D22" s="81"/>
-      <c r="E22" s="81"/>
-      <c r="F22" s="81"/>
-      <c r="G22" s="81"/>
-      <c r="H22" s="81"/>
-      <c r="I22" s="81"/>
-      <c r="J22" s="81"/>
-      <c r="K22" s="81"/>
-      <c r="L22" s="81"/>
-      <c r="M22" s="81"/>
-      <c r="N22" s="82"/>
+      <c r="D22" s="76"/>
+      <c r="E22" s="76"/>
+      <c r="F22" s="76"/>
+      <c r="G22" s="76"/>
+      <c r="H22" s="76"/>
+      <c r="I22" s="76"/>
+      <c r="J22" s="76"/>
+      <c r="K22" s="76"/>
+      <c r="L22" s="76"/>
+      <c r="M22" s="76"/>
+      <c r="N22" s="77"/>
       <c r="O22" s="38"/>
     </row>
     <row r="23" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="79"/>
-      <c r="B23" s="80"/>
-      <c r="C23" s="81"/>
-      <c r="D23" s="81"/>
-      <c r="E23" s="81"/>
-      <c r="F23" s="81"/>
-      <c r="G23" s="81"/>
-      <c r="H23" s="81"/>
-      <c r="I23" s="81"/>
-      <c r="J23" s="81"/>
-      <c r="K23" s="81"/>
-      <c r="L23" s="81"/>
-      <c r="M23" s="81"/>
-      <c r="N23" s="82"/>
+      <c r="A23" s="73"/>
+      <c r="B23" s="75"/>
+      <c r="C23" s="76"/>
+      <c r="D23" s="76"/>
+      <c r="E23" s="76"/>
+      <c r="F23" s="76"/>
+      <c r="G23" s="76"/>
+      <c r="H23" s="76"/>
+      <c r="I23" s="76"/>
+      <c r="J23" s="76"/>
+      <c r="K23" s="76"/>
+      <c r="L23" s="76"/>
+      <c r="M23" s="76"/>
+      <c r="N23" s="77"/>
       <c r="O23" s="38"/>
     </row>
     <row r="24" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="61" t="s">
+      <c r="A24" s="64" t="s">
         <v>89</v>
       </c>
-      <c r="B24" s="61"/>
-      <c r="C24" s="61"/>
-      <c r="D24" s="61"/>
-      <c r="E24" s="61"/>
-      <c r="F24" s="61"/>
-      <c r="G24" s="61"/>
-      <c r="H24" s="61"/>
-      <c r="I24" s="61"/>
-      <c r="J24" s="61"/>
-      <c r="K24" s="61"/>
-      <c r="L24" s="61"/>
-      <c r="M24" s="52" t="s">
+      <c r="B24" s="64"/>
+      <c r="C24" s="64"/>
+      <c r="D24" s="64"/>
+      <c r="E24" s="64"/>
+      <c r="F24" s="64"/>
+      <c r="G24" s="64"/>
+      <c r="H24" s="64"/>
+      <c r="I24" s="64"/>
+      <c r="J24" s="64"/>
+      <c r="K24" s="64"/>
+      <c r="L24" s="64"/>
+      <c r="M24" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="N24" s="52"/>
+      <c r="N24" s="55"/>
       <c r="O24" s="38"/>
     </row>
     <row r="25" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="65" t="s">
+      <c r="A25" s="81" t="s">
         <v>85</v>
       </c>
-      <c r="B25" s="74" t="s">
+      <c r="B25" s="65" t="s">
         <v>78</v>
       </c>
-      <c r="C25" s="75"/>
-      <c r="D25" s="76"/>
+      <c r="C25" s="66"/>
+      <c r="D25" s="67"/>
       <c r="E25" s="31"/>
       <c r="F25" s="31"/>
       <c r="G25" s="31"/>
@@ -36423,7 +36405,7 @@
       <c r="O25" s="27"/>
     </row>
     <row r="26" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="66"/>
+      <c r="A26" s="82"/>
       <c r="B26" s="42" t="s">
         <v>77</v>
       </c>
@@ -36446,7 +36428,7 @@
       <c r="O26" s="27"/>
     </row>
     <row r="27" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="66"/>
+      <c r="A27" s="82"/>
       <c r="B27" s="15">
         <v>1</v>
       </c>
@@ -36469,7 +36451,7 @@
       <c r="O27" s="27"/>
     </row>
     <row r="28" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="66"/>
+      <c r="A28" s="82"/>
       <c r="B28" s="15">
         <v>2</v>
       </c>
@@ -36492,7 +36474,7 @@
       <c r="O28" s="27"/>
     </row>
     <row r="29" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="66"/>
+      <c r="A29" s="82"/>
       <c r="B29" s="15">
         <v>4</v>
       </c>
@@ -36515,7 +36497,7 @@
       <c r="O29" s="27"/>
     </row>
     <row r="30" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="66"/>
+      <c r="A30" s="82"/>
       <c r="B30" s="15">
         <v>6</v>
       </c>
@@ -36538,7 +36520,7 @@
       <c r="O30" s="27"/>
     </row>
     <row r="31" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="66"/>
+      <c r="A31" s="82"/>
       <c r="B31" s="15">
         <v>8</v>
       </c>
@@ -36561,7 +36543,7 @@
       <c r="O31" s="27"/>
     </row>
     <row r="32" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="66"/>
+      <c r="A32" s="82"/>
       <c r="B32" s="15">
         <v>10</v>
       </c>
@@ -36584,7 +36566,7 @@
       <c r="O32" s="27"/>
     </row>
     <row r="33" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="66"/>
+      <c r="A33" s="82"/>
       <c r="B33" s="15">
         <v>12</v>
       </c>
@@ -36607,7 +36589,7 @@
       <c r="O33" s="27"/>
     </row>
     <row r="34" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="66"/>
+      <c r="A34" s="82"/>
       <c r="B34" s="15">
         <v>16</v>
       </c>
@@ -36630,12 +36612,12 @@
       <c r="O34" s="27"/>
     </row>
     <row r="35" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="66"/>
-      <c r="B35" s="74" t="s">
+      <c r="A35" s="82"/>
+      <c r="B35" s="65" t="s">
         <v>96</v>
       </c>
-      <c r="C35" s="75"/>
-      <c r="D35" s="76"/>
+      <c r="C35" s="66"/>
+      <c r="D35" s="67"/>
       <c r="E35" s="31"/>
       <c r="F35" s="31"/>
       <c r="G35" s="31"/>
@@ -36649,7 +36631,7 @@
       <c r="O35" s="27"/>
     </row>
     <row r="36" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="66"/>
+      <c r="A36" s="82"/>
       <c r="B36" s="42" t="s">
         <v>77</v>
       </c>
@@ -36673,7 +36655,7 @@
       <c r="P36" s="1"/>
     </row>
     <row r="37" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="66"/>
+      <c r="A37" s="82"/>
       <c r="B37" s="42">
         <v>1</v>
       </c>
@@ -36699,7 +36681,7 @@
       <c r="P37" s="1"/>
     </row>
     <row r="38" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="66"/>
+      <c r="A38" s="82"/>
       <c r="B38" s="42">
         <v>2</v>
       </c>
@@ -36725,7 +36707,7 @@
       <c r="P38" s="1"/>
     </row>
     <row r="39" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="66"/>
+      <c r="A39" s="82"/>
       <c r="B39" s="42">
         <v>4</v>
       </c>
@@ -36751,7 +36733,7 @@
       <c r="P39" s="1"/>
     </row>
     <row r="40" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="66"/>
+      <c r="A40" s="82"/>
       <c r="B40" s="42">
         <v>6</v>
       </c>
@@ -36777,7 +36759,7 @@
       <c r="P40" s="1"/>
     </row>
     <row r="41" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="66"/>
+      <c r="A41" s="82"/>
       <c r="B41" s="42">
         <v>8</v>
       </c>
@@ -36803,7 +36785,7 @@
       <c r="P41" s="1"/>
     </row>
     <row r="42" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="66"/>
+      <c r="A42" s="82"/>
       <c r="B42" s="42">
         <v>10</v>
       </c>
@@ -36829,7 +36811,7 @@
       <c r="P42" s="1"/>
     </row>
     <row r="43" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="66"/>
+      <c r="A43" s="82"/>
       <c r="B43" s="42">
         <v>12</v>
       </c>
@@ -36855,7 +36837,7 @@
       <c r="P43" s="1"/>
     </row>
     <row r="44" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="66"/>
+      <c r="A44" s="82"/>
       <c r="B44" s="42">
         <v>16</v>
       </c>
@@ -36881,12 +36863,12 @@
       <c r="P44" s="1"/>
     </row>
     <row r="45" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="66"/>
-      <c r="B45" s="74" t="s">
+      <c r="A45" s="82"/>
+      <c r="B45" s="65" t="s">
         <v>97</v>
       </c>
-      <c r="C45" s="75"/>
-      <c r="D45" s="76"/>
+      <c r="C45" s="66"/>
+      <c r="D45" s="67"/>
       <c r="E45" s="43"/>
       <c r="F45" s="43"/>
       <c r="G45" s="43"/>
@@ -36901,7 +36883,7 @@
       <c r="P45" s="1"/>
     </row>
     <row r="46" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="66"/>
+      <c r="A46" s="82"/>
       <c r="B46" s="42" t="s">
         <v>77</v>
       </c>
@@ -36925,7 +36907,7 @@
       <c r="P46" s="1"/>
     </row>
     <row r="47" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="66"/>
+      <c r="A47" s="82"/>
       <c r="B47" s="42">
         <v>1</v>
       </c>
@@ -36951,7 +36933,7 @@
       <c r="P47" s="1"/>
     </row>
     <row r="48" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="66"/>
+      <c r="A48" s="82"/>
       <c r="B48" s="42">
         <v>2</v>
       </c>
@@ -36977,7 +36959,7 @@
       <c r="P48" s="1"/>
     </row>
     <row r="49" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="66"/>
+      <c r="A49" s="82"/>
       <c r="B49" s="42">
         <v>4</v>
       </c>
@@ -37003,7 +36985,7 @@
       <c r="P49" s="1"/>
     </row>
     <row r="50" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="66"/>
+      <c r="A50" s="82"/>
       <c r="B50" s="42">
         <v>6</v>
       </c>
@@ -37029,7 +37011,7 @@
       <c r="P50" s="1"/>
     </row>
     <row r="51" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="66"/>
+      <c r="A51" s="82"/>
       <c r="B51" s="42">
         <v>8</v>
       </c>
@@ -37054,7 +37036,7 @@
       <c r="O51" s="1"/>
     </row>
     <row r="52" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="66"/>
+      <c r="A52" s="82"/>
       <c r="B52" s="42">
         <v>10</v>
       </c>
@@ -37079,7 +37061,7 @@
       <c r="O52" s="1"/>
     </row>
     <row r="53" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="66"/>
+      <c r="A53" s="82"/>
       <c r="B53" s="42">
         <v>12</v>
       </c>
@@ -37104,7 +37086,7 @@
       <c r="O53" s="1"/>
     </row>
     <row r="54" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="66"/>
+      <c r="A54" s="82"/>
       <c r="B54" s="42">
         <v>16</v>
       </c>
@@ -37129,55 +37111,55 @@
       <c r="O54" s="1"/>
     </row>
     <row r="55" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="66"/>
+      <c r="A55" s="82"/>
       <c r="B55" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="C55" s="70" t="s">
+      <c r="C55" s="86" t="s">
         <v>102</v>
       </c>
-      <c r="D55" s="70"/>
-      <c r="E55" s="70"/>
-      <c r="F55" s="70"/>
-      <c r="G55" s="70"/>
-      <c r="H55" s="70"/>
-      <c r="I55" s="70"/>
-      <c r="J55" s="70"/>
-      <c r="K55" s="70"/>
-      <c r="L55" s="70"/>
-      <c r="M55" s="70"/>
-      <c r="N55" s="70"/>
+      <c r="D55" s="86"/>
+      <c r="E55" s="86"/>
+      <c r="F55" s="86"/>
+      <c r="G55" s="86"/>
+      <c r="H55" s="86"/>
+      <c r="I55" s="86"/>
+      <c r="J55" s="86"/>
+      <c r="K55" s="86"/>
+      <c r="L55" s="86"/>
+      <c r="M55" s="86"/>
+      <c r="N55" s="86"/>
     </row>
     <row r="56" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="71" t="s">
+      <c r="A56" s="87" t="s">
         <v>103</v>
       </c>
-      <c r="B56" s="72"/>
-      <c r="C56" s="72"/>
-      <c r="D56" s="72"/>
-      <c r="E56" s="72"/>
-      <c r="F56" s="72"/>
-      <c r="G56" s="72"/>
-      <c r="H56" s="72"/>
-      <c r="I56" s="72"/>
-      <c r="J56" s="72"/>
-      <c r="K56" s="72"/>
-      <c r="L56" s="73"/>
-      <c r="M56" s="52" t="s">
+      <c r="B56" s="88"/>
+      <c r="C56" s="88"/>
+      <c r="D56" s="88"/>
+      <c r="E56" s="88"/>
+      <c r="F56" s="88"/>
+      <c r="G56" s="88"/>
+      <c r="H56" s="88"/>
+      <c r="I56" s="88"/>
+      <c r="J56" s="88"/>
+      <c r="K56" s="88"/>
+      <c r="L56" s="89"/>
+      <c r="M56" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="N56" s="52"/>
+      <c r="N56" s="55"/>
       <c r="O56" s="30"/>
     </row>
     <row r="57" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="65" t="s">
+      <c r="A57" s="81" t="s">
         <v>85</v>
       </c>
-      <c r="B57" s="74" t="s">
+      <c r="B57" s="65" t="s">
         <v>78</v>
       </c>
-      <c r="C57" s="75"/>
-      <c r="D57" s="76"/>
+      <c r="C57" s="66"/>
+      <c r="D57" s="67"/>
       <c r="E57" s="31"/>
       <c r="F57" s="31"/>
       <c r="G57" s="31"/>
@@ -37191,7 +37173,7 @@
       <c r="O57" s="30"/>
     </row>
     <row r="58" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="66"/>
+      <c r="A58" s="82"/>
       <c r="B58" s="42" t="s">
         <v>77</v>
       </c>
@@ -37214,7 +37196,7 @@
       <c r="O58" s="30"/>
     </row>
     <row r="59" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="66"/>
+      <c r="A59" s="82"/>
       <c r="B59" s="15">
         <v>1</v>
       </c>
@@ -37237,7 +37219,7 @@
       <c r="O59" s="30"/>
     </row>
     <row r="60" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="66"/>
+      <c r="A60" s="82"/>
       <c r="B60" s="15">
         <v>2</v>
       </c>
@@ -37260,7 +37242,7 @@
       <c r="O60" s="30"/>
     </row>
     <row r="61" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="66"/>
+      <c r="A61" s="82"/>
       <c r="B61" s="15">
         <v>4</v>
       </c>
@@ -37283,7 +37265,7 @@
       <c r="O61" s="30"/>
     </row>
     <row r="62" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="66"/>
+      <c r="A62" s="82"/>
       <c r="B62" s="15">
         <v>6</v>
       </c>
@@ -37306,7 +37288,7 @@
       <c r="O62" s="30"/>
     </row>
     <row r="63" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="66"/>
+      <c r="A63" s="82"/>
       <c r="B63" s="15">
         <v>8</v>
       </c>
@@ -37329,7 +37311,7 @@
       <c r="O63" s="30"/>
     </row>
     <row r="64" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="66"/>
+      <c r="A64" s="82"/>
       <c r="B64" s="15">
         <v>10</v>
       </c>
@@ -37352,7 +37334,7 @@
       <c r="O64" s="30"/>
     </row>
     <row r="65" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="66"/>
+      <c r="A65" s="82"/>
       <c r="B65" s="15">
         <v>12</v>
       </c>
@@ -37375,7 +37357,7 @@
       <c r="O65" s="30"/>
     </row>
     <row r="66" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="66"/>
+      <c r="A66" s="82"/>
       <c r="B66" s="15">
         <v>16</v>
       </c>
@@ -37398,12 +37380,12 @@
       <c r="O66" s="30"/>
     </row>
     <row r="67" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="66"/>
-      <c r="B67" s="74" t="s">
+      <c r="A67" s="82"/>
+      <c r="B67" s="65" t="s">
         <v>96</v>
       </c>
-      <c r="C67" s="75"/>
-      <c r="D67" s="76"/>
+      <c r="C67" s="66"/>
+      <c r="D67" s="67"/>
       <c r="E67" s="31"/>
       <c r="F67" s="31"/>
       <c r="G67" s="31"/>
@@ -37417,7 +37399,7 @@
       <c r="O67" s="30"/>
     </row>
     <row r="68" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="66"/>
+      <c r="A68" s="82"/>
       <c r="B68" s="42" t="s">
         <v>77</v>
       </c>
@@ -37440,7 +37422,7 @@
       <c r="O68" s="30"/>
     </row>
     <row r="69" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="66"/>
+      <c r="A69" s="82"/>
       <c r="B69" s="42">
         <v>1</v>
       </c>
@@ -37465,7 +37447,7 @@
       <c r="O69" s="30"/>
     </row>
     <row r="70" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="66"/>
+      <c r="A70" s="82"/>
       <c r="B70" s="42">
         <v>2</v>
       </c>
@@ -37490,7 +37472,7 @@
       <c r="O70" s="30"/>
     </row>
     <row r="71" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="66"/>
+      <c r="A71" s="82"/>
       <c r="B71" s="42">
         <v>4</v>
       </c>
@@ -37515,7 +37497,7 @@
       <c r="O71" s="30"/>
     </row>
     <row r="72" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="66"/>
+      <c r="A72" s="82"/>
       <c r="B72" s="42">
         <v>6</v>
       </c>
@@ -37540,7 +37522,7 @@
       <c r="O72" s="30"/>
     </row>
     <row r="73" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="66"/>
+      <c r="A73" s="82"/>
       <c r="B73" s="42">
         <v>8</v>
       </c>
@@ -37565,7 +37547,7 @@
       <c r="O73" s="30"/>
     </row>
     <row r="74" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="66"/>
+      <c r="A74" s="82"/>
       <c r="B74" s="42">
         <v>10</v>
       </c>
@@ -37590,7 +37572,7 @@
       <c r="O74" s="30"/>
     </row>
     <row r="75" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="66"/>
+      <c r="A75" s="82"/>
       <c r="B75" s="42">
         <v>12</v>
       </c>
@@ -37615,7 +37597,7 @@
       <c r="O75" s="30"/>
     </row>
     <row r="76" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="66"/>
+      <c r="A76" s="82"/>
       <c r="B76" s="42">
         <v>16</v>
       </c>
@@ -37640,12 +37622,12 @@
       <c r="O76" s="30"/>
     </row>
     <row r="77" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="66"/>
-      <c r="B77" s="74" t="s">
+      <c r="A77" s="82"/>
+      <c r="B77" s="65" t="s">
         <v>97</v>
       </c>
-      <c r="C77" s="75"/>
-      <c r="D77" s="76"/>
+      <c r="C77" s="66"/>
+      <c r="D77" s="67"/>
       <c r="E77" s="43"/>
       <c r="F77" s="43"/>
       <c r="G77" s="43"/>
@@ -37659,7 +37641,7 @@
       <c r="O77" s="30"/>
     </row>
     <row r="78" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="66"/>
+      <c r="A78" s="82"/>
       <c r="B78" s="42" t="s">
         <v>77</v>
       </c>
@@ -37682,7 +37664,7 @@
       <c r="O78" s="30"/>
     </row>
     <row r="79" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="66"/>
+      <c r="A79" s="82"/>
       <c r="B79" s="42">
         <v>1</v>
       </c>
@@ -37707,7 +37689,7 @@
       <c r="O79" s="30"/>
     </row>
     <row r="80" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="66"/>
+      <c r="A80" s="82"/>
       <c r="B80" s="42">
         <v>2</v>
       </c>
@@ -37732,7 +37714,7 @@
       <c r="O80" s="30"/>
     </row>
     <row r="81" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="66"/>
+      <c r="A81" s="82"/>
       <c r="B81" s="42">
         <v>4</v>
       </c>
@@ -37757,7 +37739,7 @@
       <c r="O81" s="30"/>
     </row>
     <row r="82" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="66"/>
+      <c r="A82" s="82"/>
       <c r="B82" s="42">
         <v>6</v>
       </c>
@@ -37782,7 +37764,7 @@
       <c r="O82" s="30"/>
     </row>
     <row r="83" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="66"/>
+      <c r="A83" s="82"/>
       <c r="B83" s="42">
         <v>8</v>
       </c>
@@ -37807,7 +37789,7 @@
       <c r="O83" s="30"/>
     </row>
     <row r="84" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="66"/>
+      <c r="A84" s="82"/>
       <c r="B84" s="42">
         <v>10</v>
       </c>
@@ -37832,7 +37814,7 @@
       <c r="O84" s="30"/>
     </row>
     <row r="85" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="66"/>
+      <c r="A85" s="82"/>
       <c r="B85" s="42">
         <v>12</v>
       </c>
@@ -37857,7 +37839,7 @@
       <c r="O85" s="30"/>
     </row>
     <row r="86" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="66"/>
+      <c r="A86" s="82"/>
       <c r="B86" s="42">
         <v>16</v>
       </c>
@@ -37882,61 +37864,61 @@
       <c r="O86" s="30"/>
     </row>
     <row r="87" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="66"/>
+      <c r="A87" s="82"/>
       <c r="B87" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="C87" s="67" t="s">
+      <c r="C87" s="83" t="s">
         <v>106</v>
       </c>
-      <c r="D87" s="68"/>
-      <c r="E87" s="68"/>
-      <c r="F87" s="68"/>
-      <c r="G87" s="68"/>
-      <c r="H87" s="68"/>
-      <c r="I87" s="68"/>
-      <c r="J87" s="68"/>
-      <c r="K87" s="68"/>
-      <c r="L87" s="68"/>
-      <c r="M87" s="68"/>
-      <c r="N87" s="69"/>
+      <c r="D87" s="84"/>
+      <c r="E87" s="84"/>
+      <c r="F87" s="84"/>
+      <c r="G87" s="84"/>
+      <c r="H87" s="84"/>
+      <c r="I87" s="84"/>
+      <c r="J87" s="84"/>
+      <c r="K87" s="84"/>
+      <c r="L87" s="84"/>
+      <c r="M87" s="84"/>
+      <c r="N87" s="85"/>
     </row>
     <row r="88" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="49" t="s">
+      <c r="A88" s="52" t="s">
         <v>107</v>
       </c>
-      <c r="B88" s="50"/>
-      <c r="C88" s="50"/>
-      <c r="D88" s="50"/>
-      <c r="E88" s="50"/>
-      <c r="F88" s="50"/>
-      <c r="G88" s="50"/>
-      <c r="H88" s="50"/>
-      <c r="I88" s="50"/>
-      <c r="J88" s="50"/>
-      <c r="K88" s="50"/>
-      <c r="L88" s="50"/>
-      <c r="M88" s="50"/>
-      <c r="N88" s="50"/>
-      <c r="O88" s="62" t="s">
-        <v>113</v>
-      </c>
-      <c r="P88" s="63"/>
-      <c r="Q88" s="63"/>
-      <c r="R88" s="63"/>
-      <c r="S88" s="63"/>
-      <c r="T88" s="64"/>
+      <c r="B88" s="53"/>
+      <c r="C88" s="53"/>
+      <c r="D88" s="53"/>
+      <c r="E88" s="53"/>
+      <c r="F88" s="53"/>
+      <c r="G88" s="53"/>
+      <c r="H88" s="53"/>
+      <c r="I88" s="53"/>
+      <c r="J88" s="53"/>
+      <c r="K88" s="53"/>
+      <c r="L88" s="53"/>
+      <c r="M88" s="53"/>
+      <c r="N88" s="53"/>
+      <c r="O88" s="78" t="s">
+        <v>112</v>
+      </c>
+      <c r="P88" s="79"/>
+      <c r="Q88" s="79"/>
+      <c r="R88" s="79"/>
+      <c r="S88" s="79"/>
+      <c r="T88" s="80"/>
     </row>
     <row r="89" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="79" t="s">
+      <c r="A89" s="73" t="s">
         <v>85</v>
       </c>
-      <c r="B89" s="74" t="s">
+      <c r="B89" s="65" t="s">
         <v>78</v>
       </c>
-      <c r="C89" s="75"/>
-      <c r="D89" s="75"/>
-      <c r="E89" s="76"/>
+      <c r="C89" s="66"/>
+      <c r="D89" s="66"/>
+      <c r="E89" s="67"/>
       <c r="F89" s="31"/>
       <c r="G89" s="31"/>
       <c r="H89" s="31"/>
@@ -37954,7 +37936,7 @@
       <c r="T89" s="31"/>
     </row>
     <row r="90" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="79"/>
+      <c r="A90" s="73"/>
       <c r="B90" s="42" t="s">
         <v>77</v>
       </c>
@@ -37965,7 +37947,7 @@
         <v>79</v>
       </c>
       <c r="E90" s="25" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F90" s="31"/>
       <c r="G90" s="31"/>
@@ -37984,7 +37966,7 @@
       <c r="T90" s="31"/>
     </row>
     <row r="91" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="79"/>
+      <c r="A91" s="73"/>
       <c r="B91" s="15">
         <v>1</v>
       </c>
@@ -38014,7 +37996,7 @@
       <c r="T91" s="31"/>
     </row>
     <row r="92" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="79"/>
+      <c r="A92" s="73"/>
       <c r="B92" s="15">
         <v>2</v>
       </c>
@@ -38044,7 +38026,7 @@
       <c r="T92" s="31"/>
     </row>
     <row r="93" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="79"/>
+      <c r="A93" s="73"/>
       <c r="B93" s="15">
         <v>4</v>
       </c>
@@ -38074,7 +38056,7 @@
       <c r="T93" s="31"/>
     </row>
     <row r="94" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="79"/>
+      <c r="A94" s="73"/>
       <c r="B94" s="15">
         <v>6</v>
       </c>
@@ -38104,7 +38086,7 @@
       <c r="T94" s="31"/>
     </row>
     <row r="95" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="79"/>
+      <c r="A95" s="73"/>
       <c r="B95" s="15">
         <v>8</v>
       </c>
@@ -38134,7 +38116,7 @@
       <c r="T95" s="31"/>
     </row>
     <row r="96" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="79"/>
+      <c r="A96" s="73"/>
       <c r="B96" s="15">
         <v>10</v>
       </c>
@@ -38164,7 +38146,7 @@
       <c r="T96" s="31"/>
     </row>
     <row r="97" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="79"/>
+      <c r="A97" s="73"/>
       <c r="B97" s="15">
         <v>12</v>
       </c>
@@ -38194,7 +38176,7 @@
       <c r="T97" s="31"/>
     </row>
     <row r="98" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="79"/>
+      <c r="A98" s="73"/>
       <c r="B98" s="15">
         <v>16</v>
       </c>
@@ -38224,13 +38206,13 @@
       <c r="T98" s="31"/>
     </row>
     <row r="99" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="79"/>
-      <c r="B99" s="74" t="s">
+      <c r="A99" s="73"/>
+      <c r="B99" s="65" t="s">
         <v>96</v>
       </c>
-      <c r="C99" s="75"/>
-      <c r="D99" s="75"/>
-      <c r="E99" s="76"/>
+      <c r="C99" s="66"/>
+      <c r="D99" s="66"/>
+      <c r="E99" s="67"/>
       <c r="F99" s="31"/>
       <c r="G99" s="31"/>
       <c r="H99" s="31"/>
@@ -38248,7 +38230,7 @@
       <c r="T99" s="31"/>
     </row>
     <row r="100" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="79"/>
+      <c r="A100" s="73"/>
       <c r="B100" s="42" t="s">
         <v>77</v>
       </c>
@@ -38259,7 +38241,7 @@
         <v>79</v>
       </c>
       <c r="E100" s="25" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F100" s="43"/>
       <c r="G100" s="16"/>
@@ -38278,7 +38260,7 @@
       <c r="T100" s="16"/>
     </row>
     <row r="101" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="79"/>
+      <c r="A101" s="73"/>
       <c r="B101" s="42">
         <v>1</v>
       </c>
@@ -38311,7 +38293,7 @@
       <c r="T101" s="16"/>
     </row>
     <row r="102" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="79"/>
+      <c r="A102" s="73"/>
       <c r="B102" s="42">
         <v>2</v>
       </c>
@@ -38344,7 +38326,7 @@
       <c r="T102" s="16"/>
     </row>
     <row r="103" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="79"/>
+      <c r="A103" s="73"/>
       <c r="B103" s="42">
         <v>4</v>
       </c>
@@ -38377,7 +38359,7 @@
       <c r="T103" s="16"/>
     </row>
     <row r="104" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="79"/>
+      <c r="A104" s="73"/>
       <c r="B104" s="42">
         <v>6</v>
       </c>
@@ -38410,7 +38392,7 @@
       <c r="T104" s="16"/>
     </row>
     <row r="105" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="79"/>
+      <c r="A105" s="73"/>
       <c r="B105" s="42">
         <v>8</v>
       </c>
@@ -38443,7 +38425,7 @@
       <c r="T105" s="16"/>
     </row>
     <row r="106" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="79"/>
+      <c r="A106" s="73"/>
       <c r="B106" s="42">
         <v>10</v>
       </c>
@@ -38476,7 +38458,7 @@
       <c r="T106" s="16"/>
     </row>
     <row r="107" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="79"/>
+      <c r="A107" s="73"/>
       <c r="B107" s="42">
         <v>12</v>
       </c>
@@ -38509,7 +38491,7 @@
       <c r="T107" s="16"/>
     </row>
     <row r="108" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="79"/>
+      <c r="A108" s="73"/>
       <c r="B108" s="42">
         <v>16</v>
       </c>
@@ -38542,13 +38524,13 @@
       <c r="T108" s="16"/>
     </row>
     <row r="109" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="79"/>
-      <c r="B109" s="74" t="s">
+      <c r="A109" s="73"/>
+      <c r="B109" s="65" t="s">
         <v>97</v>
       </c>
-      <c r="C109" s="75"/>
-      <c r="D109" s="75"/>
-      <c r="E109" s="76"/>
+      <c r="C109" s="66"/>
+      <c r="D109" s="66"/>
+      <c r="E109" s="67"/>
       <c r="F109" s="43"/>
       <c r="G109" s="16"/>
       <c r="H109" s="16"/>
@@ -38566,7 +38548,7 @@
       <c r="T109" s="16"/>
     </row>
     <row r="110" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="79"/>
+      <c r="A110" s="73"/>
       <c r="B110" s="42" t="s">
         <v>77</v>
       </c>
@@ -38577,7 +38559,7 @@
         <v>79</v>
       </c>
       <c r="E110" s="25" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F110" s="43"/>
       <c r="G110" s="16"/>
@@ -38596,7 +38578,7 @@
       <c r="T110" s="16"/>
     </row>
     <row r="111" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="79"/>
+      <c r="A111" s="73"/>
       <c r="B111" s="42">
         <v>1</v>
       </c>
@@ -38629,7 +38611,7 @@
       <c r="T111" s="16"/>
     </row>
     <row r="112" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="79"/>
+      <c r="A112" s="73"/>
       <c r="B112" s="42">
         <v>2</v>
       </c>
@@ -38662,7 +38644,7 @@
       <c r="T112" s="16"/>
     </row>
     <row r="113" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="79"/>
+      <c r="A113" s="73"/>
       <c r="B113" s="42">
         <v>4</v>
       </c>
@@ -38695,7 +38677,7 @@
       <c r="T113" s="16"/>
     </row>
     <row r="114" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="79"/>
+      <c r="A114" s="73"/>
       <c r="B114" s="42">
         <v>6</v>
       </c>
@@ -38728,7 +38710,7 @@
       <c r="T114" s="16"/>
     </row>
     <row r="115" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="79"/>
+      <c r="A115" s="73"/>
       <c r="B115" s="42">
         <v>8</v>
       </c>
@@ -38761,7 +38743,7 @@
       <c r="T115" s="16"/>
     </row>
     <row r="116" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="79"/>
+      <c r="A116" s="73"/>
       <c r="B116" s="42">
         <v>10</v>
       </c>
@@ -38794,7 +38776,7 @@
       <c r="T116" s="16"/>
     </row>
     <row r="117" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="79"/>
+      <c r="A117" s="73"/>
       <c r="B117" s="42">
         <v>12</v>
       </c>
@@ -38827,7 +38809,7 @@
       <c r="T117" s="31"/>
     </row>
     <row r="118" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="79"/>
+      <c r="A118" s="73"/>
       <c r="B118" s="42">
         <v>16</v>
       </c>
@@ -38860,41 +38842,41 @@
       <c r="T118" s="31"/>
     </row>
     <row r="119" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="79"/>
+      <c r="A119" s="73"/>
       <c r="B119" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="C119" s="78" t="s">
-        <v>114</v>
-      </c>
-      <c r="D119" s="83"/>
-      <c r="E119" s="83"/>
-      <c r="F119" s="83"/>
-      <c r="G119" s="83"/>
-      <c r="H119" s="83"/>
-      <c r="I119" s="83"/>
-      <c r="J119" s="83"/>
-      <c r="K119" s="83"/>
-      <c r="L119" s="83"/>
-      <c r="M119" s="83"/>
-      <c r="N119" s="83"/>
-      <c r="O119" s="83"/>
-      <c r="P119" s="83"/>
-      <c r="Q119" s="83"/>
-      <c r="R119" s="83"/>
-      <c r="S119" s="83"/>
-      <c r="T119" s="84"/>
+      <c r="C119" s="70" t="s">
+        <v>113</v>
+      </c>
+      <c r="D119" s="71"/>
+      <c r="E119" s="71"/>
+      <c r="F119" s="71"/>
+      <c r="G119" s="71"/>
+      <c r="H119" s="71"/>
+      <c r="I119" s="71"/>
+      <c r="J119" s="71"/>
+      <c r="K119" s="71"/>
+      <c r="L119" s="71"/>
+      <c r="M119" s="71"/>
+      <c r="N119" s="71"/>
+      <c r="O119" s="71"/>
+      <c r="P119" s="71"/>
+      <c r="Q119" s="71"/>
+      <c r="R119" s="71"/>
+      <c r="S119" s="71"/>
+      <c r="T119" s="72"/>
     </row>
     <row r="120" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="85" t="s">
-        <v>108</v>
-      </c>
-      <c r="B120" s="74" t="s">
+      <c r="A120" s="68" t="s">
+        <v>116</v>
+      </c>
+      <c r="B120" s="65" t="s">
         <v>78</v>
       </c>
-      <c r="C120" s="75"/>
-      <c r="D120" s="75"/>
-      <c r="E120" s="76"/>
+      <c r="C120" s="66"/>
+      <c r="D120" s="66"/>
+      <c r="E120" s="67"/>
       <c r="F120" s="31"/>
       <c r="G120" s="31"/>
       <c r="H120" s="31"/>
@@ -38921,7 +38903,7 @@
       <c r="AC120" s="31"/>
     </row>
     <row r="121" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="86"/>
+      <c r="A121" s="69"/>
       <c r="B121" s="42" t="s">
         <v>77</v>
       </c>
@@ -38929,10 +38911,10 @@
         <v>79</v>
       </c>
       <c r="D121" s="25" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E121" s="25" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="F121" s="31"/>
       <c r="G121" s="31"/>
@@ -38960,7 +38942,7 @@
       <c r="AC121" s="31"/>
     </row>
     <row r="122" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="86"/>
+      <c r="A122" s="69"/>
       <c r="B122" s="15">
         <v>1</v>
       </c>
@@ -38970,7 +38952,9 @@
       <c r="D122" s="24">
         <v>76160</v>
       </c>
-      <c r="E122" s="24"/>
+      <c r="E122" s="24">
+        <v>257265</v>
+      </c>
       <c r="F122" s="31"/>
       <c r="G122" s="31"/>
       <c r="H122" s="31"/>
@@ -38997,7 +38981,7 @@
       <c r="AC122" s="31"/>
     </row>
     <row r="123" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="86"/>
+      <c r="A123" s="69"/>
       <c r="B123" s="15">
         <v>2</v>
       </c>
@@ -39007,7 +38991,9 @@
       <c r="D123" s="24">
         <v>39071</v>
       </c>
-      <c r="E123" s="24"/>
+      <c r="E123" s="24">
+        <v>130577</v>
+      </c>
       <c r="F123" s="31"/>
       <c r="G123" s="31"/>
       <c r="H123" s="31"/>
@@ -39034,7 +39020,7 @@
       <c r="AC123" s="31"/>
     </row>
     <row r="124" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="86"/>
+      <c r="A124" s="69"/>
       <c r="B124" s="15">
         <v>4</v>
       </c>
@@ -39044,7 +39030,9 @@
       <c r="D124" s="24">
         <v>20102</v>
       </c>
-      <c r="E124" s="24"/>
+      <c r="E124" s="24">
+        <v>66384</v>
+      </c>
       <c r="F124" s="31"/>
       <c r="G124" s="31"/>
       <c r="H124" s="31"/>
@@ -39071,7 +39059,7 @@
       <c r="AC124" s="31"/>
     </row>
     <row r="125" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="86"/>
+      <c r="A125" s="69"/>
       <c r="B125" s="15">
         <v>6</v>
       </c>
@@ -39081,7 +39069,9 @@
       <c r="D125" s="24">
         <v>14063</v>
       </c>
-      <c r="E125" s="24"/>
+      <c r="E125" s="24">
+        <v>46005</v>
+      </c>
       <c r="F125" s="31"/>
       <c r="G125" s="31"/>
       <c r="H125" s="31"/>
@@ -39108,7 +39098,7 @@
       <c r="AC125" s="31"/>
     </row>
     <row r="126" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="86"/>
+      <c r="A126" s="69"/>
       <c r="B126" s="15">
         <v>8</v>
       </c>
@@ -39118,7 +39108,9 @@
       <c r="D126" s="24">
         <v>11690</v>
       </c>
-      <c r="E126" s="24"/>
+      <c r="E126" s="24">
+        <v>35587</v>
+      </c>
       <c r="F126" s="31"/>
       <c r="G126" s="31"/>
       <c r="H126" s="31"/>
@@ -39145,7 +39137,7 @@
       <c r="AC126" s="31"/>
     </row>
     <row r="127" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="86"/>
+      <c r="A127" s="69"/>
       <c r="B127" s="15">
         <v>10</v>
       </c>
@@ -39155,7 +39147,9 @@
       <c r="D127" s="24">
         <v>10161</v>
       </c>
-      <c r="E127" s="24"/>
+      <c r="E127" s="24">
+        <v>29914</v>
+      </c>
       <c r="F127" s="31"/>
       <c r="G127" s="31"/>
       <c r="H127" s="31"/>
@@ -39182,7 +39176,7 @@
       <c r="AC127" s="31"/>
     </row>
     <row r="128" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="86"/>
+      <c r="A128" s="69"/>
       <c r="B128" s="15">
         <v>12</v>
       </c>
@@ -39192,7 +39186,9 @@
       <c r="D128" s="24">
         <v>8034</v>
       </c>
-      <c r="E128" s="24"/>
+      <c r="E128" s="24">
+        <v>25229</v>
+      </c>
       <c r="F128" s="31"/>
       <c r="G128" s="31"/>
       <c r="H128" s="31"/>
@@ -39219,7 +39215,7 @@
       <c r="AC128" s="31"/>
     </row>
     <row r="129" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="86"/>
+      <c r="A129" s="69"/>
       <c r="B129" s="15">
         <v>14</v>
       </c>
@@ -39258,7 +39254,7 @@
       <c r="AC129" s="31"/>
     </row>
     <row r="130" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="86"/>
+      <c r="A130" s="69"/>
       <c r="B130" s="15">
         <v>16</v>
       </c>
@@ -39297,7 +39293,7 @@
       <c r="AC130" s="31"/>
     </row>
     <row r="131" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="86"/>
+      <c r="A131" s="69"/>
       <c r="B131" s="15">
         <v>18</v>
       </c>
@@ -39336,7 +39332,7 @@
       <c r="AC131" s="31"/>
     </row>
     <row r="132" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="86"/>
+      <c r="A132" s="69"/>
       <c r="B132" s="15">
         <v>20</v>
       </c>
@@ -39375,17 +39371,17 @@
       <c r="AC132" s="31"/>
     </row>
     <row r="133" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="86"/>
-      <c r="B133" s="87">
+      <c r="A133" s="69"/>
+      <c r="B133" s="49">
         <v>40</v>
       </c>
-      <c r="C133" s="88">
+      <c r="C133" s="50">
         <v>1201</v>
       </c>
-      <c r="D133" s="89">
+      <c r="D133" s="51">
         <v>6846</v>
       </c>
-      <c r="E133" s="89">
+      <c r="E133" s="51">
         <v>20629</v>
       </c>
       <c r="F133" s="31"/>
@@ -39414,13 +39410,13 @@
       <c r="AC133" s="31"/>
     </row>
     <row r="134" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="86"/>
-      <c r="B134" s="74" t="s">
+      <c r="A134" s="69"/>
+      <c r="B134" s="65" t="s">
         <v>96</v>
       </c>
-      <c r="C134" s="75"/>
-      <c r="D134" s="75"/>
-      <c r="E134" s="76"/>
+      <c r="C134" s="66"/>
+      <c r="D134" s="66"/>
+      <c r="E134" s="67"/>
       <c r="F134" s="31"/>
       <c r="G134" s="31"/>
       <c r="H134" s="31"/>
@@ -39447,7 +39443,7 @@
       <c r="AC134" s="31"/>
     </row>
     <row r="135" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="86"/>
+      <c r="A135" s="69"/>
       <c r="B135" s="42" t="s">
         <v>77</v>
       </c>
@@ -39455,10 +39451,10 @@
         <v>79</v>
       </c>
       <c r="D135" s="25" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E135" s="25" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="F135" s="16"/>
       <c r="G135" s="16"/>
@@ -39486,7 +39482,7 @@
       <c r="AC135" s="16"/>
     </row>
     <row r="136" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="86"/>
+      <c r="A136" s="69"/>
       <c r="B136" s="15">
         <v>1</v>
       </c>
@@ -39498,9 +39494,9 @@
         <f>D122/D122</f>
         <v>1</v>
       </c>
-      <c r="E136" s="40" t="e">
+      <c r="E136" s="40">
         <f>E122/E122</f>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
       <c r="F136" s="16"/>
       <c r="G136" s="16"/>
@@ -39528,7 +39524,7 @@
       <c r="AC136" s="16"/>
     </row>
     <row r="137" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="86"/>
+      <c r="A137" s="69"/>
       <c r="B137" s="15">
         <v>2</v>
       </c>
@@ -39540,9 +39536,9 @@
         <f>D122/D123</f>
         <v>1.9492718384479537</v>
       </c>
-      <c r="E137" s="40" t="e">
+      <c r="E137" s="40">
         <f>E122/E123</f>
-        <v>#DIV/0!</v>
+        <v>1.970216806941498</v>
       </c>
       <c r="F137" s="16"/>
       <c r="G137" s="16"/>
@@ -39570,7 +39566,7 @@
       <c r="AC137" s="16"/>
     </row>
     <row r="138" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="86"/>
+      <c r="A138" s="69"/>
       <c r="B138" s="15">
         <v>4</v>
       </c>
@@ -39582,9 +39578,9 @@
         <f>D122/D124</f>
         <v>3.7886777435081087</v>
       </c>
-      <c r="E138" s="40" t="e">
+      <c r="E138" s="40">
         <f>E122/E124</f>
-        <v>#DIV/0!</v>
+        <v>3.8754067245119308</v>
       </c>
       <c r="F138" s="16"/>
       <c r="G138" s="16"/>
@@ -39612,7 +39608,7 @@
       <c r="AC138" s="16"/>
     </row>
     <row r="139" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="86"/>
+      <c r="A139" s="69"/>
       <c r="B139" s="15">
         <v>6</v>
       </c>
@@ -39624,9 +39620,9 @@
         <f>D122/D125</f>
         <v>5.4156296665007471</v>
       </c>
-      <c r="E139" s="40" t="e">
+      <c r="E139" s="40">
         <f>E122/E125</f>
-        <v>#DIV/0!</v>
+        <v>5.5921095533094229</v>
       </c>
       <c r="F139" s="16"/>
       <c r="G139" s="16"/>
@@ -39654,7 +39650,7 @@
       <c r="AC139" s="16"/>
     </row>
     <row r="140" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="86"/>
+      <c r="A140" s="69"/>
       <c r="B140" s="15">
         <v>8</v>
       </c>
@@ -39666,9 +39662,9 @@
         <f>D122/D126</f>
         <v>6.5149700598802394</v>
       </c>
-      <c r="E140" s="40" t="e">
+      <c r="E140" s="40">
         <f>E122/E126</f>
-        <v>#DIV/0!</v>
+        <v>7.2291848146795177</v>
       </c>
       <c r="F140" s="16"/>
       <c r="G140" s="16"/>
@@ -39696,7 +39692,7 @@
       <c r="AC140" s="16"/>
     </row>
     <row r="141" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="86"/>
+      <c r="A141" s="69"/>
       <c r="B141" s="15">
         <v>10</v>
       </c>
@@ -39708,9 +39704,9 @@
         <f>D122/D127</f>
         <v>7.4953252632614902</v>
       </c>
-      <c r="E141" s="40" t="e">
+      <c r="E141" s="40">
         <f>E122/E127</f>
-        <v>#DIV/0!</v>
+        <v>8.6001537741525702</v>
       </c>
       <c r="F141" s="16"/>
       <c r="G141" s="16"/>
@@ -39738,7 +39734,7 @@
       <c r="AC141" s="16"/>
     </row>
     <row r="142" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="86"/>
+      <c r="A142" s="69"/>
       <c r="B142" s="15">
         <v>12</v>
       </c>
@@ -39750,9 +39746,9 @@
         <f>D122/D128</f>
         <v>9.4797112272840423</v>
       </c>
-      <c r="E142" s="40" t="e">
+      <c r="E142" s="40">
         <f>E122/E128</f>
-        <v>#DIV/0!</v>
+        <v>10.19719370565619</v>
       </c>
       <c r="F142" s="16"/>
       <c r="G142" s="16"/>
@@ -39780,7 +39776,7 @@
       <c r="AC142" s="16"/>
     </row>
     <row r="143" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="86"/>
+      <c r="A143" s="69"/>
       <c r="B143" s="15">
         <v>14</v>
       </c>
@@ -39794,7 +39790,7 @@
       </c>
       <c r="E143" s="40">
         <f>E$122/E129</f>
-        <v>0</v>
+        <v>10.873415046491969</v>
       </c>
       <c r="F143" s="16"/>
       <c r="G143" s="16"/>
@@ -39822,7 +39818,7 @@
       <c r="AC143" s="16"/>
     </row>
     <row r="144" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="86"/>
+      <c r="A144" s="69"/>
       <c r="B144" s="15">
         <v>16</v>
       </c>
@@ -39836,7 +39832,7 @@
       </c>
       <c r="E144" s="40">
         <f t="shared" ref="E144" si="8">E$122/E130</f>
-        <v>0</v>
+        <v>12.214651979868957</v>
       </c>
       <c r="F144" s="31"/>
       <c r="G144" s="31"/>
@@ -39864,7 +39860,7 @@
       <c r="AC144" s="31"/>
     </row>
     <row r="145" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="86"/>
+      <c r="A145" s="69"/>
       <c r="B145" s="15">
         <v>18</v>
       </c>
@@ -39878,7 +39874,7 @@
       </c>
       <c r="E145" s="40">
         <f t="shared" ref="E145" si="9">E$122/E131</f>
-        <v>0</v>
+        <v>12.466201482773659</v>
       </c>
       <c r="F145" s="16"/>
       <c r="G145" s="16"/>
@@ -39906,7 +39902,7 @@
       <c r="AC145" s="16"/>
     </row>
     <row r="146" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="86"/>
+      <c r="A146" s="69"/>
       <c r="B146" s="15">
         <v>20</v>
       </c>
@@ -39920,7 +39916,7 @@
       </c>
       <c r="E146" s="40">
         <f t="shared" ref="E146" si="10">E$122/E132</f>
-        <v>0</v>
+        <v>14.049751515482496</v>
       </c>
       <c r="F146" s="16"/>
       <c r="G146" s="16"/>
@@ -39948,21 +39944,21 @@
       <c r="AC146" s="16"/>
     </row>
     <row r="147" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="86"/>
-      <c r="B147" s="87">
+      <c r="A147" s="69"/>
+      <c r="B147" s="49">
         <v>40</v>
       </c>
-      <c r="C147" s="88">
+      <c r="C147" s="50">
         <f t="shared" si="7"/>
         <v>8.0974188176519561</v>
       </c>
-      <c r="D147" s="88">
+      <c r="D147" s="50">
         <f t="shared" si="7"/>
         <v>11.124744376278118</v>
       </c>
-      <c r="E147" s="88">
+      <c r="E147" s="50">
         <f>E$122/E133</f>
-        <v>0</v>
+        <v>12.471035920306365</v>
       </c>
       <c r="F147" s="16"/>
       <c r="G147" s="16"/>
@@ -39990,13 +39986,13 @@
       <c r="AC147" s="16"/>
     </row>
     <row r="148" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="86"/>
-      <c r="B148" s="74" t="s">
+      <c r="A148" s="69"/>
+      <c r="B148" s="65" t="s">
         <v>97</v>
       </c>
-      <c r="C148" s="75"/>
-      <c r="D148" s="75"/>
-      <c r="E148" s="76"/>
+      <c r="C148" s="66"/>
+      <c r="D148" s="66"/>
+      <c r="E148" s="67"/>
       <c r="F148" s="16"/>
       <c r="G148" s="16"/>
       <c r="H148" s="16"/>
@@ -40023,7 +40019,7 @@
       <c r="AC148" s="16"/>
     </row>
     <row r="149" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="86"/>
+      <c r="A149" s="69"/>
       <c r="B149" s="42" t="s">
         <v>77</v>
       </c>
@@ -40031,10 +40027,10 @@
         <v>79</v>
       </c>
       <c r="D149" s="25" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E149" s="25" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="F149" s="16"/>
       <c r="G149" s="16"/>
@@ -40062,7 +40058,7 @@
       <c r="AC149" s="16"/>
     </row>
     <row r="150" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="86"/>
+      <c r="A150" s="69"/>
       <c r="B150" s="15">
         <v>1</v>
       </c>
@@ -40074,9 +40070,9 @@
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="E150" s="40" t="e">
+      <c r="E150" s="40">
         <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
       <c r="F150" s="16"/>
       <c r="G150" s="16"/>
@@ -40104,7 +40100,7 @@
       <c r="AC150" s="16"/>
     </row>
     <row r="151" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="86"/>
+      <c r="A151" s="69"/>
       <c r="B151" s="15">
         <v>2</v>
       </c>
@@ -40116,9 +40112,9 @@
         <f t="shared" si="11"/>
         <v>0.97463591922397685</v>
       </c>
-      <c r="E151" s="40" t="e">
+      <c r="E151" s="40">
         <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
+        <v>0.98510840347074902</v>
       </c>
       <c r="F151" s="16"/>
       <c r="G151" s="16"/>
@@ -40146,7 +40142,7 @@
       <c r="AC151" s="16"/>
     </row>
     <row r="152" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="86"/>
+      <c r="A152" s="69"/>
       <c r="B152" s="15">
         <v>4</v>
       </c>
@@ -40158,9 +40154,9 @@
         <f t="shared" si="11"/>
         <v>0.94716943587702718</v>
       </c>
-      <c r="E152" s="40" t="e">
+      <c r="E152" s="40">
         <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
+        <v>0.9688516811279827</v>
       </c>
       <c r="F152" s="16"/>
       <c r="G152" s="16"/>
@@ -40188,7 +40184,7 @@
       <c r="AC152" s="16"/>
     </row>
     <row r="153" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="86"/>
+      <c r="A153" s="69"/>
       <c r="B153" s="15">
         <v>6</v>
       </c>
@@ -40200,9 +40196,9 @@
         <f t="shared" si="11"/>
         <v>0.90260494441679118</v>
       </c>
-      <c r="E153" s="40" t="e">
+      <c r="E153" s="40">
         <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
+        <v>0.93201825888490386</v>
       </c>
       <c r="F153" s="16"/>
       <c r="G153" s="16"/>
@@ -40230,7 +40226,7 @@
       <c r="AC153" s="16"/>
     </row>
     <row r="154" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="86"/>
+      <c r="A154" s="69"/>
       <c r="B154" s="15">
         <v>8</v>
       </c>
@@ -40242,9 +40238,9 @@
         <f t="shared" si="11"/>
         <v>0.81437125748502992</v>
       </c>
-      <c r="E154" s="40" t="e">
+      <c r="E154" s="40">
         <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
+        <v>0.90364810183493971</v>
       </c>
       <c r="F154" s="16"/>
       <c r="G154" s="16"/>
@@ -40272,7 +40268,7 @@
       <c r="AC154" s="16"/>
     </row>
     <row r="155" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="86"/>
+      <c r="A155" s="69"/>
       <c r="B155" s="15">
         <v>10</v>
       </c>
@@ -40284,9 +40280,9 @@
         <f t="shared" ref="D155:E161" si="12">D141/$B141</f>
         <v>0.74953252632614897</v>
       </c>
-      <c r="E155" s="40" t="e">
+      <c r="E155" s="40">
         <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
+        <v>0.86001537741525702</v>
       </c>
       <c r="F155" s="16"/>
       <c r="G155" s="16"/>
@@ -40314,7 +40310,7 @@
       <c r="AC155" s="16"/>
     </row>
     <row r="156" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="86"/>
+      <c r="A156" s="69"/>
       <c r="B156" s="15">
         <v>12</v>
       </c>
@@ -40326,9 +40322,9 @@
         <f t="shared" si="12"/>
         <v>0.78997593560700352</v>
       </c>
-      <c r="E156" s="40" t="e">
+      <c r="E156" s="40">
         <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
+        <v>0.84976614213801582</v>
       </c>
       <c r="F156" s="31"/>
       <c r="G156" s="31"/>
@@ -40356,7 +40352,7 @@
       <c r="AC156" s="31"/>
     </row>
     <row r="157" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="86"/>
+      <c r="A157" s="69"/>
       <c r="B157" s="15">
         <v>14</v>
       </c>
@@ -40370,7 +40366,7 @@
       </c>
       <c r="E157" s="40">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>0.77667250332085491</v>
       </c>
       <c r="F157" s="31"/>
       <c r="G157" s="31"/>
@@ -40398,7 +40394,7 @@
       <c r="AC157" s="31"/>
     </row>
     <row r="158" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="86"/>
+      <c r="A158" s="69"/>
       <c r="B158" s="15">
         <v>16</v>
       </c>
@@ -40412,7 +40408,7 @@
       </c>
       <c r="E158" s="40">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>0.76341574874180984</v>
       </c>
       <c r="F158" s="16"/>
       <c r="G158" s="16"/>
@@ -40440,7 +40436,7 @@
       <c r="AC158" s="16"/>
     </row>
     <row r="159" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="86"/>
+      <c r="A159" s="69"/>
       <c r="B159" s="15">
         <v>18</v>
       </c>
@@ -40454,7 +40450,7 @@
       </c>
       <c r="E159" s="40">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>0.6925667490429811</v>
       </c>
       <c r="F159" s="16"/>
       <c r="G159" s="16"/>
@@ -40482,7 +40478,7 @@
       <c r="AC159" s="16"/>
     </row>
     <row r="160" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A160" s="86"/>
+      <c r="A160" s="69"/>
       <c r="B160" s="15">
         <v>20</v>
       </c>
@@ -40496,7 +40492,7 @@
       </c>
       <c r="E160" s="40">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>0.7024875757741248</v>
       </c>
       <c r="F160" s="16"/>
       <c r="G160" s="16"/>
@@ -40524,21 +40520,21 @@
       <c r="AC160" s="16"/>
     </row>
     <row r="161" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="86"/>
-      <c r="B161" s="87">
+      <c r="A161" s="69"/>
+      <c r="B161" s="49">
         <v>40</v>
       </c>
-      <c r="C161" s="88">
+      <c r="C161" s="50">
         <f t="shared" si="13"/>
         <v>0.20243547044129889</v>
       </c>
-      <c r="D161" s="88">
+      <c r="D161" s="50">
         <f t="shared" si="12"/>
         <v>0.27811860940695293</v>
       </c>
-      <c r="E161" s="88">
+      <c r="E161" s="50">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>0.31177589800765915</v>
       </c>
       <c r="F161" s="16"/>
       <c r="G161" s="16"/>
@@ -40566,63 +40562,42 @@
       <c r="AC161" s="16"/>
     </row>
     <row r="162" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A162" s="86"/>
+      <c r="A162" s="69"/>
       <c r="B162" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="C162" s="78" t="s">
-        <v>124</v>
-      </c>
-      <c r="D162" s="83"/>
-      <c r="E162" s="83"/>
-      <c r="F162" s="83"/>
-      <c r="G162" s="83"/>
-      <c r="H162" s="83"/>
-      <c r="I162" s="83"/>
-      <c r="J162" s="83"/>
-      <c r="K162" s="83"/>
-      <c r="L162" s="83"/>
-      <c r="M162" s="83"/>
-      <c r="N162" s="83"/>
-      <c r="O162" s="83"/>
-      <c r="P162" s="83"/>
-      <c r="Q162" s="83"/>
-      <c r="R162" s="83"/>
-      <c r="S162" s="83"/>
-      <c r="T162" s="83"/>
-      <c r="U162" s="83"/>
-      <c r="V162" s="83"/>
-      <c r="W162" s="83"/>
-      <c r="X162" s="83"/>
-      <c r="Y162" s="83"/>
-      <c r="Z162" s="83"/>
-      <c r="AA162" s="83"/>
-      <c r="AB162" s="83"/>
-      <c r="AC162" s="84"/>
+      <c r="C162" s="70" t="s">
+        <v>115</v>
+      </c>
+      <c r="D162" s="71"/>
+      <c r="E162" s="71"/>
+      <c r="F162" s="71"/>
+      <c r="G162" s="71"/>
+      <c r="H162" s="71"/>
+      <c r="I162" s="71"/>
+      <c r="J162" s="71"/>
+      <c r="K162" s="71"/>
+      <c r="L162" s="71"/>
+      <c r="M162" s="71"/>
+      <c r="N162" s="71"/>
+      <c r="O162" s="71"/>
+      <c r="P162" s="71"/>
+      <c r="Q162" s="71"/>
+      <c r="R162" s="71"/>
+      <c r="S162" s="71"/>
+      <c r="T162" s="71"/>
+      <c r="U162" s="71"/>
+      <c r="V162" s="71"/>
+      <c r="W162" s="71"/>
+      <c r="X162" s="71"/>
+      <c r="Y162" s="71"/>
+      <c r="Z162" s="71"/>
+      <c r="AA162" s="71"/>
+      <c r="AB162" s="71"/>
+      <c r="AC162" s="72"/>
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="B148:E148"/>
-    <mergeCell ref="B134:E134"/>
-    <mergeCell ref="B120:E120"/>
-    <mergeCell ref="A120:A162"/>
-    <mergeCell ref="C162:AC162"/>
-    <mergeCell ref="A89:A119"/>
-    <mergeCell ref="C119:T119"/>
-    <mergeCell ref="B89:E89"/>
-    <mergeCell ref="B99:E99"/>
-    <mergeCell ref="B109:E109"/>
-    <mergeCell ref="A24:L24"/>
-    <mergeCell ref="M24:N24"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="C12:N12"/>
-    <mergeCell ref="A2:A12"/>
-    <mergeCell ref="A13:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:N23"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B2:D2"/>
     <mergeCell ref="O88:T88"/>
     <mergeCell ref="A88:N88"/>
     <mergeCell ref="A57:A87"/>
@@ -40637,6 +40612,27 @@
     <mergeCell ref="B45:D45"/>
     <mergeCell ref="B35:D35"/>
     <mergeCell ref="B25:D25"/>
+    <mergeCell ref="A24:L24"/>
+    <mergeCell ref="M24:N24"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="C12:N12"/>
+    <mergeCell ref="A2:A12"/>
+    <mergeCell ref="A13:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:N23"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="A89:A119"/>
+    <mergeCell ref="C119:T119"/>
+    <mergeCell ref="B89:E89"/>
+    <mergeCell ref="B99:E99"/>
+    <mergeCell ref="B109:E109"/>
+    <mergeCell ref="B148:E148"/>
+    <mergeCell ref="B134:E134"/>
+    <mergeCell ref="B120:E120"/>
+    <mergeCell ref="A120:A162"/>
+    <mergeCell ref="C162:AC162"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <hyperlinks>
@@ -40656,7 +40652,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4269BDC4-CFAE-4A4A-95F0-395DE59C8746}">
-  <dimension ref="M10:M23"/>
+  <dimension ref="M10:M17"/>
   <sheetFormatPr defaultRowHeight="22.1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="16384" width="9.140625" style="41"/>
@@ -40688,39 +40684,7 @@
       </c>
     </row>
     <row r="17" spans="13:13" x14ac:dyDescent="0.3">
-      <c r="M17" s="44" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="18" spans="13:13" x14ac:dyDescent="0.3">
-      <c r="M18" s="41" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="19" spans="13:13" x14ac:dyDescent="0.3">
-      <c r="M19" s="41" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="20" spans="13:13" x14ac:dyDescent="0.3">
-      <c r="M20" s="41" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="21" spans="13:13" x14ac:dyDescent="0.3">
-      <c r="M21" s="41" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="22" spans="13:13" x14ac:dyDescent="0.3">
-      <c r="M22" s="41" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="23" spans="13:13" x14ac:dyDescent="0.3">
-      <c r="M23" s="41" t="s">
-        <v>122</v>
-      </c>
+      <c r="M17" s="44"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/DecompositionLU/docs/statistics.xlsx
+++ b/DecompositionLU/docs/statistics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maxim\source\repos\practice\SECOND_COURSE\FOR_ITLAB\ArchBenchs\DecompositionLU\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC2A0560-C327-424F-8F5A-116FD11421DC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19261714-9429-42C2-965A-10FB4931A57B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-114" yWindow="-114" windowWidth="27602" windowHeight="15027" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4627,7 +4627,7 @@
                   <c:v>4.7108100000000004</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4.8997400000000004</c:v>
+                  <c:v>5.4617599999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5108,7 +5108,7 @@
                   <c:v>0.39256999999999997</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.30623</c:v>
+                  <c:v>0.34136</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5586,7 +5586,7 @@
                   <c:v>1971</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1895</c:v>
+                  <c:v>1700</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6287,7 +6287,7 @@
                   <c:v>3.4933100000000001</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.4933100000000001</c:v>
+                  <c:v>4.5314500000000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6768,7 +6768,7 @@
                   <c:v>0.29110999999999998</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.21833</c:v>
+                  <c:v>0.28322000000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7246,7 +7246,7 @@
                   <c:v>598</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>598</c:v>
+                  <c:v>461</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7616,7 +7616,7 @@
                   <c:v>5.3701999999999996</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>5.5549099999999996</c:v>
+                  <c:v>6.0136599999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8109,7 +8109,7 @@
                   <c:v>0.44751999999999997</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.34717999999999999</c:v>
+                  <c:v>0.37585000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8587,7 +8587,7 @@
                   <c:v>13112</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>12676</c:v>
+                  <c:v>11709</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -35618,13 +35618,13 @@
         <v>13</v>
       </c>
       <c r="C74" s="10">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="D74" s="10">
-        <v>450</v>
+        <v>633</v>
       </c>
       <c r="E74" s="10">
-        <v>1349</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -35635,13 +35635,13 @@
         <v>50</v>
       </c>
       <c r="C75" s="10">
-        <v>598</v>
+        <v>461</v>
       </c>
       <c r="D75" s="10">
-        <v>5232</v>
+        <v>4644</v>
       </c>
       <c r="E75" s="10">
-        <v>12676</v>
+        <v>11709</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -35652,13 +35652,13 @@
         <v>64</v>
       </c>
       <c r="C76" s="10">
-        <v>720</v>
+        <v>582</v>
       </c>
       <c r="D76" s="10">
-        <v>5682</v>
+        <v>5284</v>
       </c>
       <c r="E76" s="10">
-        <v>14026</v>
+        <v>12810</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -38181,13 +38181,13 @@
         <v>16</v>
       </c>
       <c r="C98" s="40">
-        <v>598</v>
+        <v>461</v>
       </c>
       <c r="D98" s="24">
-        <v>1895</v>
+        <v>1700</v>
       </c>
       <c r="E98" s="24">
-        <v>12676</v>
+        <v>11709</v>
       </c>
       <c r="F98" s="31"/>
       <c r="G98" s="31"/>
@@ -38497,15 +38497,15 @@
       </c>
       <c r="C108" s="40">
         <f>ROUND(C91/C98,5)</f>
-        <v>3.4933100000000001</v>
+        <v>4.5314500000000004</v>
       </c>
       <c r="D108" s="40">
         <f>ROUND(D91/D98,5)</f>
-        <v>4.8997400000000004</v>
+        <v>5.4617599999999999</v>
       </c>
       <c r="E108" s="40">
         <f>ROUND(E91/E98,5)</f>
-        <v>5.5549099999999996</v>
+        <v>6.0136599999999998</v>
       </c>
       <c r="F108" s="43"/>
       <c r="G108" s="16"/>
@@ -38815,15 +38815,15 @@
       </c>
       <c r="C118" s="40">
         <f t="shared" si="4"/>
-        <v>0.21833</v>
+        <v>0.28322000000000003</v>
       </c>
       <c r="D118" s="40">
         <f t="shared" si="5"/>
-        <v>0.30623</v>
+        <v>0.34136</v>
       </c>
       <c r="E118" s="40">
         <f t="shared" si="6"/>
-        <v>0.34717999999999999</v>
+        <v>0.37585000000000002</v>
       </c>
       <c r="F118" s="31"/>
       <c r="G118" s="31"/>

--- a/DecompositionLU/docs/statistics.xlsx
+++ b/DecompositionLU/docs/statistics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maxim\source\repos\practice\SECOND_COURSE\FOR_ITLAB\ArchBenchs\DecompositionLU\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC2A0560-C327-424F-8F5A-116FD11421DC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8730C858-ED17-4A5F-A6F0-5B7E2934BBAA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-114" yWindow="-114" windowWidth="27602" windowHeight="15027" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1005,45 +1005,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1079,6 +1040,45 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4627,7 +4627,7 @@
                   <c:v>4.7108100000000004</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4.8997400000000004</c:v>
+                  <c:v>5.4617599999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5108,7 +5108,7 @@
                   <c:v>0.39256999999999997</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.30623</c:v>
+                  <c:v>0.34136</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5586,7 +5586,7 @@
                   <c:v>1971</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1895</c:v>
+                  <c:v>1700</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6287,7 +6287,7 @@
                   <c:v>3.4933100000000001</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.4933100000000001</c:v>
+                  <c:v>4.5314500000000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6768,7 +6768,7 @@
                   <c:v>0.29110999999999998</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.21833</c:v>
+                  <c:v>0.28322000000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7246,7 +7246,7 @@
                   <c:v>598</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>598</c:v>
+                  <c:v>461</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7616,7 +7616,7 @@
                   <c:v>5.3701999999999996</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>5.5549099999999996</c:v>
+                  <c:v>5.4314999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8109,7 +8109,7 @@
                   <c:v>0.44751999999999997</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.34717999999999999</c:v>
+                  <c:v>0.33946999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8587,7 +8587,7 @@
                   <c:v>13112</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>12676</c:v>
+                  <c:v>12964</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9092,34 +9092,34 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.7688250272826482</c:v>
+                  <c:v>1.7688299999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.1615734720416127</c:v>
+                  <c:v>3.1615700000000002</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.1524338172502135</c:v>
+                  <c:v>4.1524299999999998</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.1728723404255321</c:v>
+                  <c:v>5.1728699999999996</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.8939393939393936</c:v>
+                  <c:v>5.8939399999999997</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>6.7770034843205575</c:v>
+                  <c:v>6.7770000000000001</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>7.3786039453717756</c:v>
+                  <c:v>7.3785999999999996</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>7.9517579721995091</c:v>
+                  <c:v>7.9517600000000002</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>8.2695578231292526</c:v>
+                  <c:v>8.2695600000000002</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>9.1143392689784442</c:v>
+                  <c:v>9.1143400000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9620,34 +9620,34 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.88441251364132412</c:v>
+                  <c:v>0.88441999999999998</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.79039336801040316</c:v>
+                  <c:v>0.79039000000000004</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.69207230287503563</c:v>
+                  <c:v>0.69206999999999996</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.64660904255319152</c:v>
+                  <c:v>0.64661000000000002</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.58939393939393936</c:v>
+                  <c:v>0.58938999999999997</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.56475029036004643</c:v>
+                  <c:v>0.56474999999999997</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.52704313895512678</c:v>
+                  <c:v>0.52703999999999995</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.49698487326246932</c:v>
+                  <c:v>0.49698999999999999</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.45941987906273624</c:v>
+                  <c:v>0.45942</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.45571696344892221</c:v>
+                  <c:v>0.45572000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11553,34 +11553,34 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.970216806941498</c:v>
+                  <c:v>1.9702200000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.8754067245119308</c:v>
+                  <c:v>3.87541</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.5921095533094229</c:v>
+                  <c:v>5.5921099999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7.2291848146795177</c:v>
+                  <c:v>7.2291800000000004</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>8.6001537741525702</c:v>
+                  <c:v>8.6001499999999993</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>10.19719370565619</c:v>
+                  <c:v>10.197190000000001</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>10.873415046491969</c:v>
+                  <c:v>10.873419999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>12.214651979868957</c:v>
+                  <c:v>12.214650000000001</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>12.466201482773659</c:v>
+                  <c:v>12.466200000000001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>14.049751515482496</c:v>
+                  <c:v>14.04975</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12084,37 +12084,37 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.9492718384479537</c:v>
+                  <c:v>1.9492700000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.7886777435081087</c:v>
+                  <c:v>3.7886799999999998</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.4156296665007471</c:v>
+                  <c:v>5.4156300000000002</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6.5149700598802394</c:v>
+                  <c:v>6.5149699999999999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>7.4953252632614902</c:v>
+                  <c:v>7.49533</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>9.4797112272840423</c:v>
+                  <c:v>9.4797100000000007</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>10.431447746883988</c:v>
+                  <c:v>10.43145</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>11.165518252455652</c:v>
+                  <c:v>11.165520000000001</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>12.281890017739075</c:v>
+                  <c:v>12.281890000000001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>12.575957727873183</c:v>
+                  <c:v>12.57596</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>11.124744376278118</c:v>
+                  <c:v>11.124739999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12615,34 +12615,34 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.98510840347074902</c:v>
+                  <c:v>0.98511000000000004</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.9688516811279827</c:v>
+                  <c:v>0.96885250000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.93201825888490386</c:v>
+                  <c:v>0.93201833333333328</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.90364810183493971</c:v>
+                  <c:v>0.90364750000000005</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.86001537741525702</c:v>
+                  <c:v>0.86001499999999997</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.84976614213801582</c:v>
+                  <c:v>0.84976583333333344</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.77667250332085491</c:v>
+                  <c:v>0.77667285714285705</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.76341574874180984</c:v>
+                  <c:v>0.76341562500000004</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.6925667490429811</c:v>
+                  <c:v>0.69256666666666666</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.7024875757741248</c:v>
+                  <c:v>0.70248749999999993</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13145,34 +13145,34 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.97463591922397685</c:v>
+                  <c:v>0.97463500000000003</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.94716943587702718</c:v>
+                  <c:v>0.94716999999999996</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.90260494441679118</c:v>
+                  <c:v>0.90260499999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.81437125748502992</c:v>
+                  <c:v>0.81437124999999999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.74953252632614897</c:v>
+                  <c:v>0.749533</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.78997593560700352</c:v>
+                  <c:v>0.78997583333333343</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.74510341049171347</c:v>
+                  <c:v>0.74510357142857142</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.69784489077847822</c:v>
+                  <c:v>0.69784500000000005</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.68232722320772643</c:v>
+                  <c:v>0.68232722222222231</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.62879788639365919</c:v>
+                  <c:v>0.62879799999999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -35618,13 +35618,13 @@
         <v>13</v>
       </c>
       <c r="C74" s="10">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="D74" s="10">
-        <v>450</v>
+        <v>633</v>
       </c>
       <c r="E74" s="10">
-        <v>1349</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -35635,13 +35635,13 @@
         <v>50</v>
       </c>
       <c r="C75" s="10">
-        <v>598</v>
+        <v>461</v>
       </c>
       <c r="D75" s="10">
-        <v>5232</v>
+        <v>4644</v>
       </c>
       <c r="E75" s="10">
-        <v>12676</v>
+        <v>11709</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -35652,13 +35652,13 @@
         <v>64</v>
       </c>
       <c r="C76" s="10">
-        <v>720</v>
+        <v>582</v>
       </c>
       <c r="D76" s="10">
-        <v>5682</v>
+        <v>5284</v>
       </c>
       <c r="E76" s="10">
-        <v>14026</v>
+        <v>12810</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -35716,18 +35716,11 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="A57:C57"/>
-    <mergeCell ref="D57:E57"/>
-    <mergeCell ref="B58:E58"/>
-    <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A64:E64"/>
-    <mergeCell ref="B45:E45"/>
-    <mergeCell ref="A47:E47"/>
-    <mergeCell ref="A51:E51"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A70:C70"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="B71:E71"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A77:E77"/>
     <mergeCell ref="H24:I24"/>
     <mergeCell ref="G5:H8"/>
     <mergeCell ref="B42:E42"/>
@@ -35743,11 +35736,18 @@
     <mergeCell ref="B19:E19"/>
     <mergeCell ref="A21:E21"/>
     <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A70:C70"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="B71:E71"/>
-    <mergeCell ref="A72:E72"/>
-    <mergeCell ref="A77:E77"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="D57:E57"/>
+    <mergeCell ref="B58:E58"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A64:E64"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <hyperlinks>
@@ -35811,14 +35811,14 @@
       <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="73" t="s">
+      <c r="A2" s="82" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="65" t="s">
+      <c r="B2" s="77" t="s">
         <v>78</v>
       </c>
-      <c r="C2" s="66"/>
-      <c r="D2" s="67"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="79"/>
       <c r="E2" s="31"/>
       <c r="F2" s="31"/>
       <c r="G2" s="31"/>
@@ -35843,7 +35843,7 @@
       <c r="Z2" s="30"/>
     </row>
     <row r="3" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="73"/>
+      <c r="A3" s="82"/>
       <c r="B3" s="29" t="s">
         <v>77</v>
       </c>
@@ -35877,7 +35877,7 @@
       <c r="Z3" s="30"/>
     </row>
     <row r="4" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="73"/>
+      <c r="A4" s="82"/>
       <c r="B4" s="15">
         <v>1</v>
       </c>
@@ -35911,7 +35911,7 @@
       <c r="Z4" s="30"/>
     </row>
     <row r="5" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="73"/>
+      <c r="A5" s="82"/>
       <c r="B5" s="15">
         <v>2</v>
       </c>
@@ -35945,7 +35945,7 @@
       <c r="Z5" s="30"/>
     </row>
     <row r="6" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="73"/>
+      <c r="A6" s="82"/>
       <c r="B6" s="15">
         <v>4</v>
       </c>
@@ -35968,7 +35968,7 @@
       <c r="O6" s="38"/>
     </row>
     <row r="7" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="73"/>
+      <c r="A7" s="82"/>
       <c r="B7" s="15">
         <v>6</v>
       </c>
@@ -35991,7 +35991,7 @@
       <c r="O7" s="38"/>
     </row>
     <row r="8" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="73"/>
+      <c r="A8" s="82"/>
       <c r="B8" s="15">
         <v>8</v>
       </c>
@@ -36014,7 +36014,7 @@
       <c r="O8" s="38"/>
     </row>
     <row r="9" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="73"/>
+      <c r="A9" s="82"/>
       <c r="B9" s="15">
         <v>10</v>
       </c>
@@ -36037,7 +36037,7 @@
       <c r="O9" s="38"/>
     </row>
     <row r="10" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="73"/>
+      <c r="A10" s="82"/>
       <c r="B10" s="15">
         <v>12</v>
       </c>
@@ -36060,7 +36060,7 @@
       <c r="O10" s="38"/>
     </row>
     <row r="11" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="73"/>
+      <c r="A11" s="82"/>
       <c r="B11" s="15">
         <v>16</v>
       </c>
@@ -36085,37 +36085,37 @@
       <c r="Q11" s="27"/>
     </row>
     <row r="12" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="73"/>
+      <c r="A12" s="82"/>
       <c r="B12" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="C12" s="74" t="s">
+      <c r="C12" s="80" t="s">
         <v>81</v>
       </c>
-      <c r="D12" s="74"/>
-      <c r="E12" s="74"/>
-      <c r="F12" s="74"/>
-      <c r="G12" s="74"/>
-      <c r="H12" s="74"/>
-      <c r="I12" s="74"/>
-      <c r="J12" s="74"/>
-      <c r="K12" s="74"/>
-      <c r="L12" s="74"/>
-      <c r="M12" s="74"/>
-      <c r="N12" s="70"/>
+      <c r="D12" s="80"/>
+      <c r="E12" s="80"/>
+      <c r="F12" s="80"/>
+      <c r="G12" s="80"/>
+      <c r="H12" s="80"/>
+      <c r="I12" s="80"/>
+      <c r="J12" s="80"/>
+      <c r="K12" s="80"/>
+      <c r="L12" s="80"/>
+      <c r="M12" s="80"/>
+      <c r="N12" s="81"/>
       <c r="O12" s="39"/>
       <c r="P12" s="23"/>
       <c r="Q12" s="23"/>
     </row>
     <row r="13" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="73" t="s">
+      <c r="A13" s="82" t="s">
         <v>87</v>
       </c>
-      <c r="B13" s="65" t="s">
+      <c r="B13" s="77" t="s">
         <v>78</v>
       </c>
-      <c r="C13" s="66"/>
-      <c r="D13" s="67"/>
+      <c r="C13" s="78"/>
+      <c r="D13" s="79"/>
       <c r="E13" s="32"/>
       <c r="F13" s="31"/>
       <c r="G13" s="31"/>
@@ -36131,7 +36131,7 @@
       <c r="Q13" s="23"/>
     </row>
     <row r="14" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="73"/>
+      <c r="A14" s="82"/>
       <c r="B14" s="13" t="s">
         <v>77</v>
       </c>
@@ -36156,7 +36156,7 @@
       <c r="Q14" s="23"/>
     </row>
     <row r="15" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="73"/>
+      <c r="A15" s="82"/>
       <c r="B15" s="15">
         <v>1</v>
       </c>
@@ -36181,7 +36181,7 @@
       <c r="Q15" s="27"/>
     </row>
     <row r="16" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="73"/>
+      <c r="A16" s="82"/>
       <c r="B16" s="15">
         <v>2</v>
       </c>
@@ -36206,7 +36206,7 @@
       <c r="Q16" s="23"/>
     </row>
     <row r="17" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="73"/>
+      <c r="A17" s="82"/>
       <c r="B17" s="15">
         <v>4</v>
       </c>
@@ -36231,7 +36231,7 @@
       <c r="Q17" s="23"/>
     </row>
     <row r="18" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="73"/>
+      <c r="A18" s="82"/>
       <c r="B18" s="15">
         <v>6</v>
       </c>
@@ -36256,7 +36256,7 @@
       <c r="Q18" s="23"/>
     </row>
     <row r="19" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="73"/>
+      <c r="A19" s="82"/>
       <c r="B19" s="15">
         <v>8</v>
       </c>
@@ -36279,7 +36279,7 @@
       <c r="O19" s="38"/>
     </row>
     <row r="20" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="73"/>
+      <c r="A20" s="82"/>
       <c r="B20" s="15">
         <v>10</v>
       </c>
@@ -36302,7 +36302,7 @@
       <c r="O20" s="38"/>
     </row>
     <row r="21" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="73"/>
+      <c r="A21" s="82"/>
       <c r="B21" s="15">
         <v>12</v>
       </c>
@@ -36325,41 +36325,41 @@
       <c r="O21" s="38"/>
     </row>
     <row r="22" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="73"/>
-      <c r="B22" s="75" t="s">
+      <c r="A22" s="82"/>
+      <c r="B22" s="83" t="s">
         <v>86</v>
       </c>
-      <c r="C22" s="76" t="s">
+      <c r="C22" s="84" t="s">
         <v>88</v>
       </c>
-      <c r="D22" s="76"/>
-      <c r="E22" s="76"/>
-      <c r="F22" s="76"/>
-      <c r="G22" s="76"/>
-      <c r="H22" s="76"/>
-      <c r="I22" s="76"/>
-      <c r="J22" s="76"/>
-      <c r="K22" s="76"/>
-      <c r="L22" s="76"/>
-      <c r="M22" s="76"/>
-      <c r="N22" s="77"/>
+      <c r="D22" s="84"/>
+      <c r="E22" s="84"/>
+      <c r="F22" s="84"/>
+      <c r="G22" s="84"/>
+      <c r="H22" s="84"/>
+      <c r="I22" s="84"/>
+      <c r="J22" s="84"/>
+      <c r="K22" s="84"/>
+      <c r="L22" s="84"/>
+      <c r="M22" s="84"/>
+      <c r="N22" s="85"/>
       <c r="O22" s="38"/>
     </row>
     <row r="23" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="73"/>
-      <c r="B23" s="75"/>
-      <c r="C23" s="76"/>
-      <c r="D23" s="76"/>
-      <c r="E23" s="76"/>
-      <c r="F23" s="76"/>
-      <c r="G23" s="76"/>
-      <c r="H23" s="76"/>
-      <c r="I23" s="76"/>
-      <c r="J23" s="76"/>
-      <c r="K23" s="76"/>
-      <c r="L23" s="76"/>
-      <c r="M23" s="76"/>
-      <c r="N23" s="77"/>
+      <c r="A23" s="82"/>
+      <c r="B23" s="83"/>
+      <c r="C23" s="84"/>
+      <c r="D23" s="84"/>
+      <c r="E23" s="84"/>
+      <c r="F23" s="84"/>
+      <c r="G23" s="84"/>
+      <c r="H23" s="84"/>
+      <c r="I23" s="84"/>
+      <c r="J23" s="84"/>
+      <c r="K23" s="84"/>
+      <c r="L23" s="84"/>
+      <c r="M23" s="84"/>
+      <c r="N23" s="85"/>
       <c r="O23" s="38"/>
     </row>
     <row r="24" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -36384,14 +36384,14 @@
       <c r="O24" s="38"/>
     </row>
     <row r="25" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="81" t="s">
+      <c r="A25" s="68" t="s">
         <v>85</v>
       </c>
-      <c r="B25" s="65" t="s">
+      <c r="B25" s="77" t="s">
         <v>78</v>
       </c>
-      <c r="C25" s="66"/>
-      <c r="D25" s="67"/>
+      <c r="C25" s="78"/>
+      <c r="D25" s="79"/>
       <c r="E25" s="31"/>
       <c r="F25" s="31"/>
       <c r="G25" s="31"/>
@@ -36405,7 +36405,7 @@
       <c r="O25" s="27"/>
     </row>
     <row r="26" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="82"/>
+      <c r="A26" s="69"/>
       <c r="B26" s="42" t="s">
         <v>77</v>
       </c>
@@ -36428,7 +36428,7 @@
       <c r="O26" s="27"/>
     </row>
     <row r="27" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="82"/>
+      <c r="A27" s="69"/>
       <c r="B27" s="15">
         <v>1</v>
       </c>
@@ -36451,7 +36451,7 @@
       <c r="O27" s="27"/>
     </row>
     <row r="28" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="82"/>
+      <c r="A28" s="69"/>
       <c r="B28" s="15">
         <v>2</v>
       </c>
@@ -36474,7 +36474,7 @@
       <c r="O28" s="27"/>
     </row>
     <row r="29" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="82"/>
+      <c r="A29" s="69"/>
       <c r="B29" s="15">
         <v>4</v>
       </c>
@@ -36497,7 +36497,7 @@
       <c r="O29" s="27"/>
     </row>
     <row r="30" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="82"/>
+      <c r="A30" s="69"/>
       <c r="B30" s="15">
         <v>6</v>
       </c>
@@ -36520,7 +36520,7 @@
       <c r="O30" s="27"/>
     </row>
     <row r="31" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="82"/>
+      <c r="A31" s="69"/>
       <c r="B31" s="15">
         <v>8</v>
       </c>
@@ -36543,7 +36543,7 @@
       <c r="O31" s="27"/>
     </row>
     <row r="32" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="82"/>
+      <c r="A32" s="69"/>
       <c r="B32" s="15">
         <v>10</v>
       </c>
@@ -36566,7 +36566,7 @@
       <c r="O32" s="27"/>
     </row>
     <row r="33" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="82"/>
+      <c r="A33" s="69"/>
       <c r="B33" s="15">
         <v>12</v>
       </c>
@@ -36589,7 +36589,7 @@
       <c r="O33" s="27"/>
     </row>
     <row r="34" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="82"/>
+      <c r="A34" s="69"/>
       <c r="B34" s="15">
         <v>16</v>
       </c>
@@ -36612,12 +36612,12 @@
       <c r="O34" s="27"/>
     </row>
     <row r="35" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="82"/>
-      <c r="B35" s="65" t="s">
+      <c r="A35" s="69"/>
+      <c r="B35" s="77" t="s">
         <v>96</v>
       </c>
-      <c r="C35" s="66"/>
-      <c r="D35" s="67"/>
+      <c r="C35" s="78"/>
+      <c r="D35" s="79"/>
       <c r="E35" s="31"/>
       <c r="F35" s="31"/>
       <c r="G35" s="31"/>
@@ -36631,7 +36631,7 @@
       <c r="O35" s="27"/>
     </row>
     <row r="36" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="82"/>
+      <c r="A36" s="69"/>
       <c r="B36" s="42" t="s">
         <v>77</v>
       </c>
@@ -36655,7 +36655,7 @@
       <c r="P36" s="1"/>
     </row>
     <row r="37" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="82"/>
+      <c r="A37" s="69"/>
       <c r="B37" s="42">
         <v>1</v>
       </c>
@@ -36681,7 +36681,7 @@
       <c r="P37" s="1"/>
     </row>
     <row r="38" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="82"/>
+      <c r="A38" s="69"/>
       <c r="B38" s="42">
         <v>2</v>
       </c>
@@ -36707,7 +36707,7 @@
       <c r="P38" s="1"/>
     </row>
     <row r="39" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="82"/>
+      <c r="A39" s="69"/>
       <c r="B39" s="42">
         <v>4</v>
       </c>
@@ -36733,7 +36733,7 @@
       <c r="P39" s="1"/>
     </row>
     <row r="40" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="82"/>
+      <c r="A40" s="69"/>
       <c r="B40" s="42">
         <v>6</v>
       </c>
@@ -36759,7 +36759,7 @@
       <c r="P40" s="1"/>
     </row>
     <row r="41" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="82"/>
+      <c r="A41" s="69"/>
       <c r="B41" s="42">
         <v>8</v>
       </c>
@@ -36785,7 +36785,7 @@
       <c r="P41" s="1"/>
     </row>
     <row r="42" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="82"/>
+      <c r="A42" s="69"/>
       <c r="B42" s="42">
         <v>10</v>
       </c>
@@ -36811,7 +36811,7 @@
       <c r="P42" s="1"/>
     </row>
     <row r="43" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="82"/>
+      <c r="A43" s="69"/>
       <c r="B43" s="42">
         <v>12</v>
       </c>
@@ -36837,7 +36837,7 @@
       <c r="P43" s="1"/>
     </row>
     <row r="44" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="82"/>
+      <c r="A44" s="69"/>
       <c r="B44" s="42">
         <v>16</v>
       </c>
@@ -36863,12 +36863,12 @@
       <c r="P44" s="1"/>
     </row>
     <row r="45" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="82"/>
-      <c r="B45" s="65" t="s">
+      <c r="A45" s="69"/>
+      <c r="B45" s="77" t="s">
         <v>97</v>
       </c>
-      <c r="C45" s="66"/>
-      <c r="D45" s="67"/>
+      <c r="C45" s="78"/>
+      <c r="D45" s="79"/>
       <c r="E45" s="43"/>
       <c r="F45" s="43"/>
       <c r="G45" s="43"/>
@@ -36883,7 +36883,7 @@
       <c r="P45" s="1"/>
     </row>
     <row r="46" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="82"/>
+      <c r="A46" s="69"/>
       <c r="B46" s="42" t="s">
         <v>77</v>
       </c>
@@ -36907,7 +36907,7 @@
       <c r="P46" s="1"/>
     </row>
     <row r="47" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="82"/>
+      <c r="A47" s="69"/>
       <c r="B47" s="42">
         <v>1</v>
       </c>
@@ -36933,7 +36933,7 @@
       <c r="P47" s="1"/>
     </row>
     <row r="48" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="82"/>
+      <c r="A48" s="69"/>
       <c r="B48" s="42">
         <v>2</v>
       </c>
@@ -36959,7 +36959,7 @@
       <c r="P48" s="1"/>
     </row>
     <row r="49" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="82"/>
+      <c r="A49" s="69"/>
       <c r="B49" s="42">
         <v>4</v>
       </c>
@@ -36985,7 +36985,7 @@
       <c r="P49" s="1"/>
     </row>
     <row r="50" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="82"/>
+      <c r="A50" s="69"/>
       <c r="B50" s="42">
         <v>6</v>
       </c>
@@ -37011,7 +37011,7 @@
       <c r="P50" s="1"/>
     </row>
     <row r="51" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="82"/>
+      <c r="A51" s="69"/>
       <c r="B51" s="42">
         <v>8</v>
       </c>
@@ -37036,7 +37036,7 @@
       <c r="O51" s="1"/>
     </row>
     <row r="52" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="82"/>
+      <c r="A52" s="69"/>
       <c r="B52" s="42">
         <v>10</v>
       </c>
@@ -37061,7 +37061,7 @@
       <c r="O52" s="1"/>
     </row>
     <row r="53" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="82"/>
+      <c r="A53" s="69"/>
       <c r="B53" s="42">
         <v>12</v>
       </c>
@@ -37086,7 +37086,7 @@
       <c r="O53" s="1"/>
     </row>
     <row r="54" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="82"/>
+      <c r="A54" s="69"/>
       <c r="B54" s="42">
         <v>16</v>
       </c>
@@ -37111,40 +37111,40 @@
       <c r="O54" s="1"/>
     </row>
     <row r="55" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="82"/>
+      <c r="A55" s="69"/>
       <c r="B55" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="C55" s="86" t="s">
+      <c r="C55" s="73" t="s">
         <v>102</v>
       </c>
-      <c r="D55" s="86"/>
-      <c r="E55" s="86"/>
-      <c r="F55" s="86"/>
-      <c r="G55" s="86"/>
-      <c r="H55" s="86"/>
-      <c r="I55" s="86"/>
-      <c r="J55" s="86"/>
-      <c r="K55" s="86"/>
-      <c r="L55" s="86"/>
-      <c r="M55" s="86"/>
-      <c r="N55" s="86"/>
+      <c r="D55" s="73"/>
+      <c r="E55" s="73"/>
+      <c r="F55" s="73"/>
+      <c r="G55" s="73"/>
+      <c r="H55" s="73"/>
+      <c r="I55" s="73"/>
+      <c r="J55" s="73"/>
+      <c r="K55" s="73"/>
+      <c r="L55" s="73"/>
+      <c r="M55" s="73"/>
+      <c r="N55" s="73"/>
     </row>
     <row r="56" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="87" t="s">
+      <c r="A56" s="74" t="s">
         <v>103</v>
       </c>
-      <c r="B56" s="88"/>
-      <c r="C56" s="88"/>
-      <c r="D56" s="88"/>
-      <c r="E56" s="88"/>
-      <c r="F56" s="88"/>
-      <c r="G56" s="88"/>
-      <c r="H56" s="88"/>
-      <c r="I56" s="88"/>
-      <c r="J56" s="88"/>
-      <c r="K56" s="88"/>
-      <c r="L56" s="89"/>
+      <c r="B56" s="75"/>
+      <c r="C56" s="75"/>
+      <c r="D56" s="75"/>
+      <c r="E56" s="75"/>
+      <c r="F56" s="75"/>
+      <c r="G56" s="75"/>
+      <c r="H56" s="75"/>
+      <c r="I56" s="75"/>
+      <c r="J56" s="75"/>
+      <c r="K56" s="75"/>
+      <c r="L56" s="76"/>
       <c r="M56" s="55" t="s">
         <v>90</v>
       </c>
@@ -37152,14 +37152,14 @@
       <c r="O56" s="30"/>
     </row>
     <row r="57" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="81" t="s">
+      <c r="A57" s="68" t="s">
         <v>85</v>
       </c>
-      <c r="B57" s="65" t="s">
+      <c r="B57" s="77" t="s">
         <v>78</v>
       </c>
-      <c r="C57" s="66"/>
-      <c r="D57" s="67"/>
+      <c r="C57" s="78"/>
+      <c r="D57" s="79"/>
       <c r="E57" s="31"/>
       <c r="F57" s="31"/>
       <c r="G57" s="31"/>
@@ -37173,7 +37173,7 @@
       <c r="O57" s="30"/>
     </row>
     <row r="58" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="82"/>
+      <c r="A58" s="69"/>
       <c r="B58" s="42" t="s">
         <v>77</v>
       </c>
@@ -37196,7 +37196,7 @@
       <c r="O58" s="30"/>
     </row>
     <row r="59" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="82"/>
+      <c r="A59" s="69"/>
       <c r="B59" s="15">
         <v>1</v>
       </c>
@@ -37219,7 +37219,7 @@
       <c r="O59" s="30"/>
     </row>
     <row r="60" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="82"/>
+      <c r="A60" s="69"/>
       <c r="B60" s="15">
         <v>2</v>
       </c>
@@ -37242,7 +37242,7 @@
       <c r="O60" s="30"/>
     </row>
     <row r="61" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="82"/>
+      <c r="A61" s="69"/>
       <c r="B61" s="15">
         <v>4</v>
       </c>
@@ -37265,7 +37265,7 @@
       <c r="O61" s="30"/>
     </row>
     <row r="62" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="82"/>
+      <c r="A62" s="69"/>
       <c r="B62" s="15">
         <v>6</v>
       </c>
@@ -37288,7 +37288,7 @@
       <c r="O62" s="30"/>
     </row>
     <row r="63" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="82"/>
+      <c r="A63" s="69"/>
       <c r="B63" s="15">
         <v>8</v>
       </c>
@@ -37311,7 +37311,7 @@
       <c r="O63" s="30"/>
     </row>
     <row r="64" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="82"/>
+      <c r="A64" s="69"/>
       <c r="B64" s="15">
         <v>10</v>
       </c>
@@ -37334,7 +37334,7 @@
       <c r="O64" s="30"/>
     </row>
     <row r="65" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="82"/>
+      <c r="A65" s="69"/>
       <c r="B65" s="15">
         <v>12</v>
       </c>
@@ -37357,7 +37357,7 @@
       <c r="O65" s="30"/>
     </row>
     <row r="66" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="82"/>
+      <c r="A66" s="69"/>
       <c r="B66" s="15">
         <v>16</v>
       </c>
@@ -37380,12 +37380,12 @@
       <c r="O66" s="30"/>
     </row>
     <row r="67" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="82"/>
-      <c r="B67" s="65" t="s">
+      <c r="A67" s="69"/>
+      <c r="B67" s="77" t="s">
         <v>96</v>
       </c>
-      <c r="C67" s="66"/>
-      <c r="D67" s="67"/>
+      <c r="C67" s="78"/>
+      <c r="D67" s="79"/>
       <c r="E67" s="31"/>
       <c r="F67" s="31"/>
       <c r="G67" s="31"/>
@@ -37399,7 +37399,7 @@
       <c r="O67" s="30"/>
     </row>
     <row r="68" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="82"/>
+      <c r="A68" s="69"/>
       <c r="B68" s="42" t="s">
         <v>77</v>
       </c>
@@ -37422,7 +37422,7 @@
       <c r="O68" s="30"/>
     </row>
     <row r="69" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="82"/>
+      <c r="A69" s="69"/>
       <c r="B69" s="42">
         <v>1</v>
       </c>
@@ -37447,7 +37447,7 @@
       <c r="O69" s="30"/>
     </row>
     <row r="70" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="82"/>
+      <c r="A70" s="69"/>
       <c r="B70" s="42">
         <v>2</v>
       </c>
@@ -37472,7 +37472,7 @@
       <c r="O70" s="30"/>
     </row>
     <row r="71" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="82"/>
+      <c r="A71" s="69"/>
       <c r="B71" s="42">
         <v>4</v>
       </c>
@@ -37497,7 +37497,7 @@
       <c r="O71" s="30"/>
     </row>
     <row r="72" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="82"/>
+      <c r="A72" s="69"/>
       <c r="B72" s="42">
         <v>6</v>
       </c>
@@ -37522,7 +37522,7 @@
       <c r="O72" s="30"/>
     </row>
     <row r="73" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="82"/>
+      <c r="A73" s="69"/>
       <c r="B73" s="42">
         <v>8</v>
       </c>
@@ -37547,7 +37547,7 @@
       <c r="O73" s="30"/>
     </row>
     <row r="74" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="82"/>
+      <c r="A74" s="69"/>
       <c r="B74" s="42">
         <v>10</v>
       </c>
@@ -37572,7 +37572,7 @@
       <c r="O74" s="30"/>
     </row>
     <row r="75" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="82"/>
+      <c r="A75" s="69"/>
       <c r="B75" s="42">
         <v>12</v>
       </c>
@@ -37597,7 +37597,7 @@
       <c r="O75" s="30"/>
     </row>
     <row r="76" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="82"/>
+      <c r="A76" s="69"/>
       <c r="B76" s="42">
         <v>16</v>
       </c>
@@ -37622,12 +37622,12 @@
       <c r="O76" s="30"/>
     </row>
     <row r="77" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="82"/>
-      <c r="B77" s="65" t="s">
+      <c r="A77" s="69"/>
+      <c r="B77" s="77" t="s">
         <v>97</v>
       </c>
-      <c r="C77" s="66"/>
-      <c r="D77" s="67"/>
+      <c r="C77" s="78"/>
+      <c r="D77" s="79"/>
       <c r="E77" s="43"/>
       <c r="F77" s="43"/>
       <c r="G77" s="43"/>
@@ -37641,7 +37641,7 @@
       <c r="O77" s="30"/>
     </row>
     <row r="78" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="82"/>
+      <c r="A78" s="69"/>
       <c r="B78" s="42" t="s">
         <v>77</v>
       </c>
@@ -37664,7 +37664,7 @@
       <c r="O78" s="30"/>
     </row>
     <row r="79" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="82"/>
+      <c r="A79" s="69"/>
       <c r="B79" s="42">
         <v>1</v>
       </c>
@@ -37689,7 +37689,7 @@
       <c r="O79" s="30"/>
     </row>
     <row r="80" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="82"/>
+      <c r="A80" s="69"/>
       <c r="B80" s="42">
         <v>2</v>
       </c>
@@ -37714,7 +37714,7 @@
       <c r="O80" s="30"/>
     </row>
     <row r="81" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="82"/>
+      <c r="A81" s="69"/>
       <c r="B81" s="42">
         <v>4</v>
       </c>
@@ -37739,7 +37739,7 @@
       <c r="O81" s="30"/>
     </row>
     <row r="82" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="82"/>
+      <c r="A82" s="69"/>
       <c r="B82" s="42">
         <v>6</v>
       </c>
@@ -37764,7 +37764,7 @@
       <c r="O82" s="30"/>
     </row>
     <row r="83" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="82"/>
+      <c r="A83" s="69"/>
       <c r="B83" s="42">
         <v>8</v>
       </c>
@@ -37789,7 +37789,7 @@
       <c r="O83" s="30"/>
     </row>
     <row r="84" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="82"/>
+      <c r="A84" s="69"/>
       <c r="B84" s="42">
         <v>10</v>
       </c>
@@ -37814,7 +37814,7 @@
       <c r="O84" s="30"/>
     </row>
     <row r="85" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="82"/>
+      <c r="A85" s="69"/>
       <c r="B85" s="42">
         <v>12</v>
       </c>
@@ -37839,7 +37839,7 @@
       <c r="O85" s="30"/>
     </row>
     <row r="86" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="82"/>
+      <c r="A86" s="69"/>
       <c r="B86" s="42">
         <v>16</v>
       </c>
@@ -37864,24 +37864,24 @@
       <c r="O86" s="30"/>
     </row>
     <row r="87" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="82"/>
+      <c r="A87" s="69"/>
       <c r="B87" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="C87" s="83" t="s">
+      <c r="C87" s="70" t="s">
         <v>106</v>
       </c>
-      <c r="D87" s="84"/>
-      <c r="E87" s="84"/>
-      <c r="F87" s="84"/>
-      <c r="G87" s="84"/>
-      <c r="H87" s="84"/>
-      <c r="I87" s="84"/>
-      <c r="J87" s="84"/>
-      <c r="K87" s="84"/>
-      <c r="L87" s="84"/>
-      <c r="M87" s="84"/>
-      <c r="N87" s="85"/>
+      <c r="D87" s="71"/>
+      <c r="E87" s="71"/>
+      <c r="F87" s="71"/>
+      <c r="G87" s="71"/>
+      <c r="H87" s="71"/>
+      <c r="I87" s="71"/>
+      <c r="J87" s="71"/>
+      <c r="K87" s="71"/>
+      <c r="L87" s="71"/>
+      <c r="M87" s="71"/>
+      <c r="N87" s="72"/>
     </row>
     <row r="88" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="52" t="s">
@@ -37900,25 +37900,25 @@
       <c r="L88" s="53"/>
       <c r="M88" s="53"/>
       <c r="N88" s="53"/>
-      <c r="O88" s="78" t="s">
+      <c r="O88" s="65" t="s">
         <v>112</v>
       </c>
-      <c r="P88" s="79"/>
-      <c r="Q88" s="79"/>
-      <c r="R88" s="79"/>
-      <c r="S88" s="79"/>
-      <c r="T88" s="80"/>
+      <c r="P88" s="66"/>
+      <c r="Q88" s="66"/>
+      <c r="R88" s="66"/>
+      <c r="S88" s="66"/>
+      <c r="T88" s="67"/>
     </row>
     <row r="89" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="73" t="s">
+      <c r="A89" s="82" t="s">
         <v>85</v>
       </c>
-      <c r="B89" s="65" t="s">
+      <c r="B89" s="77" t="s">
         <v>78</v>
       </c>
-      <c r="C89" s="66"/>
-      <c r="D89" s="66"/>
-      <c r="E89" s="67"/>
+      <c r="C89" s="78"/>
+      <c r="D89" s="78"/>
+      <c r="E89" s="79"/>
       <c r="F89" s="31"/>
       <c r="G89" s="31"/>
       <c r="H89" s="31"/>
@@ -37936,7 +37936,7 @@
       <c r="T89" s="31"/>
     </row>
     <row r="90" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="73"/>
+      <c r="A90" s="82"/>
       <c r="B90" s="42" t="s">
         <v>77</v>
       </c>
@@ -37966,7 +37966,7 @@
       <c r="T90" s="31"/>
     </row>
     <row r="91" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="73"/>
+      <c r="A91" s="82"/>
       <c r="B91" s="15">
         <v>1</v>
       </c>
@@ -37996,7 +37996,7 @@
       <c r="T91" s="31"/>
     </row>
     <row r="92" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="73"/>
+      <c r="A92" s="82"/>
       <c r="B92" s="15">
         <v>2</v>
       </c>
@@ -38026,7 +38026,7 @@
       <c r="T92" s="31"/>
     </row>
     <row r="93" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="73"/>
+      <c r="A93" s="82"/>
       <c r="B93" s="15">
         <v>4</v>
       </c>
@@ -38056,7 +38056,7 @@
       <c r="T93" s="31"/>
     </row>
     <row r="94" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="73"/>
+      <c r="A94" s="82"/>
       <c r="B94" s="15">
         <v>6</v>
       </c>
@@ -38086,7 +38086,7 @@
       <c r="T94" s="31"/>
     </row>
     <row r="95" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="73"/>
+      <c r="A95" s="82"/>
       <c r="B95" s="15">
         <v>8</v>
       </c>
@@ -38116,7 +38116,7 @@
       <c r="T95" s="31"/>
     </row>
     <row r="96" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="73"/>
+      <c r="A96" s="82"/>
       <c r="B96" s="15">
         <v>10</v>
       </c>
@@ -38146,7 +38146,7 @@
       <c r="T96" s="31"/>
     </row>
     <row r="97" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="73"/>
+      <c r="A97" s="82"/>
       <c r="B97" s="15">
         <v>12</v>
       </c>
@@ -38176,18 +38176,18 @@
       <c r="T97" s="31"/>
     </row>
     <row r="98" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="73"/>
+      <c r="A98" s="82"/>
       <c r="B98" s="15">
         <v>16</v>
       </c>
       <c r="C98" s="40">
-        <v>598</v>
+        <v>461</v>
       </c>
       <c r="D98" s="24">
-        <v>1895</v>
+        <v>1700</v>
       </c>
       <c r="E98" s="24">
-        <v>12676</v>
+        <v>12964</v>
       </c>
       <c r="F98" s="31"/>
       <c r="G98" s="31"/>
@@ -38206,13 +38206,13 @@
       <c r="T98" s="31"/>
     </row>
     <row r="99" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="73"/>
-      <c r="B99" s="65" t="s">
+      <c r="A99" s="82"/>
+      <c r="B99" s="77" t="s">
         <v>96</v>
       </c>
-      <c r="C99" s="66"/>
-      <c r="D99" s="66"/>
-      <c r="E99" s="67"/>
+      <c r="C99" s="78"/>
+      <c r="D99" s="78"/>
+      <c r="E99" s="79"/>
       <c r="F99" s="31"/>
       <c r="G99" s="31"/>
       <c r="H99" s="31"/>
@@ -38230,7 +38230,7 @@
       <c r="T99" s="31"/>
     </row>
     <row r="100" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="73"/>
+      <c r="A100" s="82"/>
       <c r="B100" s="42" t="s">
         <v>77</v>
       </c>
@@ -38260,7 +38260,7 @@
       <c r="T100" s="16"/>
     </row>
     <row r="101" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="73"/>
+      <c r="A101" s="82"/>
       <c r="B101" s="42">
         <v>1</v>
       </c>
@@ -38293,7 +38293,7 @@
       <c r="T101" s="16"/>
     </row>
     <row r="102" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="73"/>
+      <c r="A102" s="82"/>
       <c r="B102" s="42">
         <v>2</v>
       </c>
@@ -38326,7 +38326,7 @@
       <c r="T102" s="16"/>
     </row>
     <row r="103" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="73"/>
+      <c r="A103" s="82"/>
       <c r="B103" s="42">
         <v>4</v>
       </c>
@@ -38359,7 +38359,7 @@
       <c r="T103" s="16"/>
     </row>
     <row r="104" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="73"/>
+      <c r="A104" s="82"/>
       <c r="B104" s="42">
         <v>6</v>
       </c>
@@ -38392,7 +38392,7 @@
       <c r="T104" s="16"/>
     </row>
     <row r="105" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="73"/>
+      <c r="A105" s="82"/>
       <c r="B105" s="42">
         <v>8</v>
       </c>
@@ -38425,7 +38425,7 @@
       <c r="T105" s="16"/>
     </row>
     <row r="106" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="73"/>
+      <c r="A106" s="82"/>
       <c r="B106" s="42">
         <v>10</v>
       </c>
@@ -38458,7 +38458,7 @@
       <c r="T106" s="16"/>
     </row>
     <row r="107" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="73"/>
+      <c r="A107" s="82"/>
       <c r="B107" s="42">
         <v>12</v>
       </c>
@@ -38491,21 +38491,21 @@
       <c r="T107" s="16"/>
     </row>
     <row r="108" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="73"/>
+      <c r="A108" s="82"/>
       <c r="B108" s="42">
         <v>16</v>
       </c>
       <c r="C108" s="40">
         <f>ROUND(C91/C98,5)</f>
-        <v>3.4933100000000001</v>
+        <v>4.5314500000000004</v>
       </c>
       <c r="D108" s="40">
         <f>ROUND(D91/D98,5)</f>
-        <v>4.8997400000000004</v>
+        <v>5.4617599999999999</v>
       </c>
       <c r="E108" s="40">
         <f>ROUND(E91/E98,5)</f>
-        <v>5.5549099999999996</v>
+        <v>5.4314999999999998</v>
       </c>
       <c r="F108" s="43"/>
       <c r="G108" s="16"/>
@@ -38524,13 +38524,13 @@
       <c r="T108" s="16"/>
     </row>
     <row r="109" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="73"/>
-      <c r="B109" s="65" t="s">
+      <c r="A109" s="82"/>
+      <c r="B109" s="77" t="s">
         <v>97</v>
       </c>
-      <c r="C109" s="66"/>
-      <c r="D109" s="66"/>
-      <c r="E109" s="67"/>
+      <c r="C109" s="78"/>
+      <c r="D109" s="78"/>
+      <c r="E109" s="79"/>
       <c r="F109" s="43"/>
       <c r="G109" s="16"/>
       <c r="H109" s="16"/>
@@ -38548,7 +38548,7 @@
       <c r="T109" s="16"/>
     </row>
     <row r="110" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="73"/>
+      <c r="A110" s="82"/>
       <c r="B110" s="42" t="s">
         <v>77</v>
       </c>
@@ -38578,7 +38578,7 @@
       <c r="T110" s="16"/>
     </row>
     <row r="111" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="73"/>
+      <c r="A111" s="82"/>
       <c r="B111" s="42">
         <v>1</v>
       </c>
@@ -38611,7 +38611,7 @@
       <c r="T111" s="16"/>
     </row>
     <row r="112" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="73"/>
+      <c r="A112" s="82"/>
       <c r="B112" s="42">
         <v>2</v>
       </c>
@@ -38644,7 +38644,7 @@
       <c r="T112" s="16"/>
     </row>
     <row r="113" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="73"/>
+      <c r="A113" s="82"/>
       <c r="B113" s="42">
         <v>4</v>
       </c>
@@ -38677,7 +38677,7 @@
       <c r="T113" s="16"/>
     </row>
     <row r="114" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="73"/>
+      <c r="A114" s="82"/>
       <c r="B114" s="42">
         <v>6</v>
       </c>
@@ -38710,7 +38710,7 @@
       <c r="T114" s="16"/>
     </row>
     <row r="115" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="73"/>
+      <c r="A115" s="82"/>
       <c r="B115" s="42">
         <v>8</v>
       </c>
@@ -38743,7 +38743,7 @@
       <c r="T115" s="16"/>
     </row>
     <row r="116" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="73"/>
+      <c r="A116" s="82"/>
       <c r="B116" s="42">
         <v>10</v>
       </c>
@@ -38776,7 +38776,7 @@
       <c r="T116" s="16"/>
     </row>
     <row r="117" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="73"/>
+      <c r="A117" s="82"/>
       <c r="B117" s="42">
         <v>12</v>
       </c>
@@ -38809,21 +38809,21 @@
       <c r="T117" s="31"/>
     </row>
     <row r="118" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="73"/>
+      <c r="A118" s="82"/>
       <c r="B118" s="42">
         <v>16</v>
       </c>
       <c r="C118" s="40">
         <f t="shared" si="4"/>
-        <v>0.21833</v>
+        <v>0.28322000000000003</v>
       </c>
       <c r="D118" s="40">
         <f t="shared" si="5"/>
-        <v>0.30623</v>
+        <v>0.34136</v>
       </c>
       <c r="E118" s="40">
         <f t="shared" si="6"/>
-        <v>0.34717999999999999</v>
+        <v>0.33946999999999999</v>
       </c>
       <c r="F118" s="31"/>
       <c r="G118" s="31"/>
@@ -38842,41 +38842,41 @@
       <c r="T118" s="31"/>
     </row>
     <row r="119" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="73"/>
+      <c r="A119" s="82"/>
       <c r="B119" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="C119" s="70" t="s">
+      <c r="C119" s="81" t="s">
         <v>113</v>
       </c>
-      <c r="D119" s="71"/>
-      <c r="E119" s="71"/>
-      <c r="F119" s="71"/>
-      <c r="G119" s="71"/>
-      <c r="H119" s="71"/>
-      <c r="I119" s="71"/>
-      <c r="J119" s="71"/>
-      <c r="K119" s="71"/>
-      <c r="L119" s="71"/>
-      <c r="M119" s="71"/>
-      <c r="N119" s="71"/>
-      <c r="O119" s="71"/>
-      <c r="P119" s="71"/>
-      <c r="Q119" s="71"/>
-      <c r="R119" s="71"/>
-      <c r="S119" s="71"/>
-      <c r="T119" s="72"/>
+      <c r="D119" s="86"/>
+      <c r="E119" s="86"/>
+      <c r="F119" s="86"/>
+      <c r="G119" s="86"/>
+      <c r="H119" s="86"/>
+      <c r="I119" s="86"/>
+      <c r="J119" s="86"/>
+      <c r="K119" s="86"/>
+      <c r="L119" s="86"/>
+      <c r="M119" s="86"/>
+      <c r="N119" s="86"/>
+      <c r="O119" s="86"/>
+      <c r="P119" s="86"/>
+      <c r="Q119" s="86"/>
+      <c r="R119" s="86"/>
+      <c r="S119" s="86"/>
+      <c r="T119" s="87"/>
     </row>
     <row r="120" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="68" t="s">
+      <c r="A120" s="88" t="s">
         <v>116</v>
       </c>
-      <c r="B120" s="65" t="s">
+      <c r="B120" s="77" t="s">
         <v>78</v>
       </c>
-      <c r="C120" s="66"/>
-      <c r="D120" s="66"/>
-      <c r="E120" s="67"/>
+      <c r="C120" s="78"/>
+      <c r="D120" s="78"/>
+      <c r="E120" s="79"/>
       <c r="F120" s="31"/>
       <c r="G120" s="31"/>
       <c r="H120" s="31"/>
@@ -38903,7 +38903,7 @@
       <c r="AC120" s="31"/>
     </row>
     <row r="121" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="69"/>
+      <c r="A121" s="89"/>
       <c r="B121" s="42" t="s">
         <v>77</v>
       </c>
@@ -38942,7 +38942,7 @@
       <c r="AC121" s="31"/>
     </row>
     <row r="122" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="69"/>
+      <c r="A122" s="89"/>
       <c r="B122" s="15">
         <v>1</v>
       </c>
@@ -38981,7 +38981,7 @@
       <c r="AC122" s="31"/>
     </row>
     <row r="123" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="69"/>
+      <c r="A123" s="89"/>
       <c r="B123" s="15">
         <v>2</v>
       </c>
@@ -39020,7 +39020,7 @@
       <c r="AC123" s="31"/>
     </row>
     <row r="124" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="69"/>
+      <c r="A124" s="89"/>
       <c r="B124" s="15">
         <v>4</v>
       </c>
@@ -39059,7 +39059,7 @@
       <c r="AC124" s="31"/>
     </row>
     <row r="125" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="69"/>
+      <c r="A125" s="89"/>
       <c r="B125" s="15">
         <v>6</v>
       </c>
@@ -39098,7 +39098,7 @@
       <c r="AC125" s="31"/>
     </row>
     <row r="126" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="69"/>
+      <c r="A126" s="89"/>
       <c r="B126" s="15">
         <v>8</v>
       </c>
@@ -39137,7 +39137,7 @@
       <c r="AC126" s="31"/>
     </row>
     <row r="127" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="69"/>
+      <c r="A127" s="89"/>
       <c r="B127" s="15">
         <v>10</v>
       </c>
@@ -39176,7 +39176,7 @@
       <c r="AC127" s="31"/>
     </row>
     <row r="128" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="69"/>
+      <c r="A128" s="89"/>
       <c r="B128" s="15">
         <v>12</v>
       </c>
@@ -39215,7 +39215,7 @@
       <c r="AC128" s="31"/>
     </row>
     <row r="129" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="69"/>
+      <c r="A129" s="89"/>
       <c r="B129" s="15">
         <v>14</v>
       </c>
@@ -39254,7 +39254,7 @@
       <c r="AC129" s="31"/>
     </row>
     <row r="130" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="69"/>
+      <c r="A130" s="89"/>
       <c r="B130" s="15">
         <v>16</v>
       </c>
@@ -39293,7 +39293,7 @@
       <c r="AC130" s="31"/>
     </row>
     <row r="131" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="69"/>
+      <c r="A131" s="89"/>
       <c r="B131" s="15">
         <v>18</v>
       </c>
@@ -39332,7 +39332,7 @@
       <c r="AC131" s="31"/>
     </row>
     <row r="132" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="69"/>
+      <c r="A132" s="89"/>
       <c r="B132" s="15">
         <v>20</v>
       </c>
@@ -39371,7 +39371,7 @@
       <c r="AC132" s="31"/>
     </row>
     <row r="133" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="69"/>
+      <c r="A133" s="89"/>
       <c r="B133" s="49">
         <v>40</v>
       </c>
@@ -39410,13 +39410,13 @@
       <c r="AC133" s="31"/>
     </row>
     <row r="134" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="69"/>
-      <c r="B134" s="65" t="s">
+      <c r="A134" s="89"/>
+      <c r="B134" s="77" t="s">
         <v>96</v>
       </c>
-      <c r="C134" s="66"/>
-      <c r="D134" s="66"/>
-      <c r="E134" s="67"/>
+      <c r="C134" s="78"/>
+      <c r="D134" s="78"/>
+      <c r="E134" s="79"/>
       <c r="F134" s="31"/>
       <c r="G134" s="31"/>
       <c r="H134" s="31"/>
@@ -39443,7 +39443,7 @@
       <c r="AC134" s="31"/>
     </row>
     <row r="135" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="69"/>
+      <c r="A135" s="89"/>
       <c r="B135" s="42" t="s">
         <v>77</v>
       </c>
@@ -39482,7 +39482,7 @@
       <c r="AC135" s="16"/>
     </row>
     <row r="136" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="69"/>
+      <c r="A136" s="89"/>
       <c r="B136" s="15">
         <v>1</v>
       </c>
@@ -39495,7 +39495,7 @@
         <v>1</v>
       </c>
       <c r="E136" s="40">
-        <f>E122/E122</f>
+        <f>ROUND(E122/E122,5)</f>
         <v>1</v>
       </c>
       <c r="F136" s="16"/>
@@ -39524,21 +39524,21 @@
       <c r="AC136" s="16"/>
     </row>
     <row r="137" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="69"/>
+      <c r="A137" s="89"/>
       <c r="B137" s="15">
         <v>2</v>
       </c>
       <c r="C137" s="40">
-        <f>C122/C123</f>
-        <v>1.7688250272826482</v>
+        <f>ROUND(C122/C123,5)</f>
+        <v>1.7688299999999999</v>
       </c>
       <c r="D137" s="40">
-        <f>D122/D123</f>
-        <v>1.9492718384479537</v>
+        <f>ROUND(D122/D123,5)</f>
+        <v>1.9492700000000001</v>
       </c>
       <c r="E137" s="40">
-        <f>E122/E123</f>
-        <v>1.970216806941498</v>
+        <f>ROUND(E122/E123,5)</f>
+        <v>1.9702200000000001</v>
       </c>
       <c r="F137" s="16"/>
       <c r="G137" s="16"/>
@@ -39566,21 +39566,21 @@
       <c r="AC137" s="16"/>
     </row>
     <row r="138" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="69"/>
+      <c r="A138" s="89"/>
       <c r="B138" s="15">
         <v>4</v>
       </c>
       <c r="C138" s="40">
-        <f>C122/C124</f>
-        <v>3.1615734720416127</v>
+        <f>ROUND(C122/C124,5)</f>
+        <v>3.1615700000000002</v>
       </c>
       <c r="D138" s="40">
-        <f>D122/D124</f>
-        <v>3.7886777435081087</v>
+        <f>ROUND(D122/D124,5)</f>
+        <v>3.7886799999999998</v>
       </c>
       <c r="E138" s="40">
-        <f>E122/E124</f>
-        <v>3.8754067245119308</v>
+        <f>ROUND(E122/E124,5)</f>
+        <v>3.87541</v>
       </c>
       <c r="F138" s="16"/>
       <c r="G138" s="16"/>
@@ -39608,21 +39608,21 @@
       <c r="AC138" s="16"/>
     </row>
     <row r="139" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="69"/>
+      <c r="A139" s="89"/>
       <c r="B139" s="15">
         <v>6</v>
       </c>
       <c r="C139" s="40">
-        <f>C122/C125</f>
-        <v>4.1524338172502135</v>
+        <f>ROUND(C122/C125,5)</f>
+        <v>4.1524299999999998</v>
       </c>
       <c r="D139" s="40">
-        <f>D122/D125</f>
-        <v>5.4156296665007471</v>
+        <f>ROUND(D122/D125,5)</f>
+        <v>5.4156300000000002</v>
       </c>
       <c r="E139" s="40">
-        <f>E122/E125</f>
-        <v>5.5921095533094229</v>
+        <f>ROUND(E122/E125,5)</f>
+        <v>5.5921099999999999</v>
       </c>
       <c r="F139" s="16"/>
       <c r="G139" s="16"/>
@@ -39650,21 +39650,21 @@
       <c r="AC139" s="16"/>
     </row>
     <row r="140" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="69"/>
+      <c r="A140" s="89"/>
       <c r="B140" s="15">
         <v>8</v>
       </c>
       <c r="C140" s="40">
-        <f>C122/C126</f>
-        <v>5.1728723404255321</v>
+        <f>ROUND(C122/C126,5)</f>
+        <v>5.1728699999999996</v>
       </c>
       <c r="D140" s="40">
-        <f>D122/D126</f>
-        <v>6.5149700598802394</v>
+        <f>ROUND(D122/D126,5)</f>
+        <v>6.5149699999999999</v>
       </c>
       <c r="E140" s="40">
-        <f>E122/E126</f>
-        <v>7.2291848146795177</v>
+        <f>ROUND(E122/E126,5)</f>
+        <v>7.2291800000000004</v>
       </c>
       <c r="F140" s="16"/>
       <c r="G140" s="16"/>
@@ -39692,21 +39692,21 @@
       <c r="AC140" s="16"/>
     </row>
     <row r="141" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="69"/>
+      <c r="A141" s="89"/>
       <c r="B141" s="15">
         <v>10</v>
       </c>
       <c r="C141" s="40">
-        <f>C122/C127</f>
-        <v>5.8939393939393936</v>
+        <f>ROUND(C122/C127,5)</f>
+        <v>5.8939399999999997</v>
       </c>
       <c r="D141" s="40">
-        <f>D122/D127</f>
-        <v>7.4953252632614902</v>
+        <f>ROUND(D122/D127,5)</f>
+        <v>7.49533</v>
       </c>
       <c r="E141" s="40">
-        <f>E122/E127</f>
-        <v>8.6001537741525702</v>
+        <f>ROUND(E122/E127,5)</f>
+        <v>8.6001499999999993</v>
       </c>
       <c r="F141" s="16"/>
       <c r="G141" s="16"/>
@@ -39734,21 +39734,21 @@
       <c r="AC141" s="16"/>
     </row>
     <row r="142" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="69"/>
+      <c r="A142" s="89"/>
       <c r="B142" s="15">
         <v>12</v>
       </c>
       <c r="C142" s="40">
-        <f>C122/C128</f>
-        <v>6.7770034843205575</v>
+        <f>ROUND(C122/C128,5)</f>
+        <v>6.7770000000000001</v>
       </c>
       <c r="D142" s="40">
-        <f>D122/D128</f>
-        <v>9.4797112272840423</v>
+        <f>ROUND(D122/D128,5)</f>
+        <v>9.4797100000000007</v>
       </c>
       <c r="E142" s="40">
-        <f>E122/E128</f>
-        <v>10.19719370565619</v>
+        <f>ROUND(E122/E128,5)</f>
+        <v>10.197190000000001</v>
       </c>
       <c r="F142" s="16"/>
       <c r="G142" s="16"/>
@@ -39776,21 +39776,21 @@
       <c r="AC142" s="16"/>
     </row>
     <row r="143" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="69"/>
+      <c r="A143" s="89"/>
       <c r="B143" s="15">
         <v>14</v>
       </c>
       <c r="C143" s="40">
-        <f>C$122/C129</f>
-        <v>7.3786039453717756</v>
+        <f t="shared" ref="C143:E147" si="7">ROUND(C$122/C129,5)</f>
+        <v>7.3785999999999996</v>
       </c>
       <c r="D143" s="40">
-        <f>D$122/D129</f>
-        <v>10.431447746883988</v>
+        <f t="shared" si="7"/>
+        <v>10.43145</v>
       </c>
       <c r="E143" s="40">
-        <f>E$122/E129</f>
-        <v>10.873415046491969</v>
+        <f t="shared" si="7"/>
+        <v>10.873419999999999</v>
       </c>
       <c r="F143" s="16"/>
       <c r="G143" s="16"/>
@@ -39818,21 +39818,21 @@
       <c r="AC143" s="16"/>
     </row>
     <row r="144" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="69"/>
+      <c r="A144" s="89"/>
       <c r="B144" s="15">
         <v>16</v>
       </c>
       <c r="C144" s="40">
-        <f t="shared" ref="C144:D147" si="7">C$122/C130</f>
-        <v>7.9517579721995091</v>
+        <f t="shared" si="7"/>
+        <v>7.9517600000000002</v>
       </c>
       <c r="D144" s="40">
         <f t="shared" si="7"/>
-        <v>11.165518252455652</v>
+        <v>11.165520000000001</v>
       </c>
       <c r="E144" s="40">
-        <f t="shared" ref="E144" si="8">E$122/E130</f>
-        <v>12.214651979868957</v>
+        <f t="shared" si="7"/>
+        <v>12.214650000000001</v>
       </c>
       <c r="F144" s="31"/>
       <c r="G144" s="31"/>
@@ -39860,21 +39860,21 @@
       <c r="AC144" s="31"/>
     </row>
     <row r="145" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="69"/>
+      <c r="A145" s="89"/>
       <c r="B145" s="15">
         <v>18</v>
       </c>
       <c r="C145" s="40">
         <f t="shared" si="7"/>
-        <v>8.2695578231292526</v>
+        <v>8.2695600000000002</v>
       </c>
       <c r="D145" s="40">
         <f t="shared" si="7"/>
-        <v>12.281890017739075</v>
+        <v>12.281890000000001</v>
       </c>
       <c r="E145" s="40">
-        <f t="shared" ref="E145" si="9">E$122/E131</f>
-        <v>12.466201482773659</v>
+        <f t="shared" si="7"/>
+        <v>12.466200000000001</v>
       </c>
       <c r="F145" s="16"/>
       <c r="G145" s="16"/>
@@ -39902,21 +39902,21 @@
       <c r="AC145" s="16"/>
     </row>
     <row r="146" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="69"/>
+      <c r="A146" s="89"/>
       <c r="B146" s="15">
         <v>20</v>
       </c>
       <c r="C146" s="40">
         <f t="shared" si="7"/>
-        <v>9.1143392689784442</v>
+        <v>9.1143400000000003</v>
       </c>
       <c r="D146" s="40">
         <f t="shared" si="7"/>
-        <v>12.575957727873183</v>
+        <v>12.57596</v>
       </c>
       <c r="E146" s="40">
-        <f t="shared" ref="E146" si="10">E$122/E132</f>
-        <v>14.049751515482496</v>
+        <f t="shared" si="7"/>
+        <v>14.04975</v>
       </c>
       <c r="F146" s="16"/>
       <c r="G146" s="16"/>
@@ -39944,21 +39944,21 @@
       <c r="AC146" s="16"/>
     </row>
     <row r="147" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="69"/>
+      <c r="A147" s="89"/>
       <c r="B147" s="49">
         <v>40</v>
       </c>
       <c r="C147" s="50">
         <f t="shared" si="7"/>
-        <v>8.0974188176519561</v>
+        <v>8.0974199999999996</v>
       </c>
       <c r="D147" s="50">
         <f t="shared" si="7"/>
-        <v>11.124744376278118</v>
+        <v>11.124739999999999</v>
       </c>
       <c r="E147" s="50">
-        <f>E$122/E133</f>
-        <v>12.471035920306365</v>
+        <f t="shared" si="7"/>
+        <v>12.47104</v>
       </c>
       <c r="F147" s="16"/>
       <c r="G147" s="16"/>
@@ -39986,13 +39986,13 @@
       <c r="AC147" s="16"/>
     </row>
     <row r="148" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="69"/>
-      <c r="B148" s="65" t="s">
+      <c r="A148" s="89"/>
+      <c r="B148" s="77" t="s">
         <v>97</v>
       </c>
-      <c r="C148" s="66"/>
-      <c r="D148" s="66"/>
-      <c r="E148" s="67"/>
+      <c r="C148" s="78"/>
+      <c r="D148" s="78"/>
+      <c r="E148" s="79"/>
       <c r="F148" s="16"/>
       <c r="G148" s="16"/>
       <c r="H148" s="16"/>
@@ -40019,7 +40019,7 @@
       <c r="AC148" s="16"/>
     </row>
     <row r="149" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="69"/>
+      <c r="A149" s="89"/>
       <c r="B149" s="42" t="s">
         <v>77</v>
       </c>
@@ -40058,20 +40058,20 @@
       <c r="AC149" s="16"/>
     </row>
     <row r="150" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="69"/>
+      <c r="A150" s="89"/>
       <c r="B150" s="15">
         <v>1</v>
       </c>
       <c r="C150" s="40">
-        <f t="shared" ref="C150:E154" si="11">C136/$B136</f>
+        <f t="shared" ref="C150:C161" si="8">ROUND(C136/$B136,5)</f>
         <v>1</v>
       </c>
       <c r="D150" s="40">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="D150:E154" si="9">D136/$B136</f>
         <v>1</v>
       </c>
       <c r="E150" s="40">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="F150" s="16"/>
@@ -40100,21 +40100,21 @@
       <c r="AC150" s="16"/>
     </row>
     <row r="151" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="69"/>
+      <c r="A151" s="89"/>
       <c r="B151" s="15">
         <v>2</v>
       </c>
       <c r="C151" s="40">
-        <f t="shared" si="11"/>
-        <v>0.88441251364132412</v>
+        <f t="shared" si="8"/>
+        <v>0.88441999999999998</v>
       </c>
       <c r="D151" s="40">
-        <f t="shared" si="11"/>
-        <v>0.97463591922397685</v>
+        <f t="shared" si="9"/>
+        <v>0.97463500000000003</v>
       </c>
       <c r="E151" s="40">
-        <f t="shared" si="11"/>
-        <v>0.98510840347074902</v>
+        <f t="shared" si="9"/>
+        <v>0.98511000000000004</v>
       </c>
       <c r="F151" s="16"/>
       <c r="G151" s="16"/>
@@ -40142,21 +40142,21 @@
       <c r="AC151" s="16"/>
     </row>
     <row r="152" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="69"/>
+      <c r="A152" s="89"/>
       <c r="B152" s="15">
         <v>4</v>
       </c>
       <c r="C152" s="40">
-        <f t="shared" si="11"/>
-        <v>0.79039336801040316</v>
+        <f t="shared" si="8"/>
+        <v>0.79039000000000004</v>
       </c>
       <c r="D152" s="40">
-        <f t="shared" si="11"/>
-        <v>0.94716943587702718</v>
+        <f t="shared" si="9"/>
+        <v>0.94716999999999996</v>
       </c>
       <c r="E152" s="40">
-        <f t="shared" si="11"/>
-        <v>0.9688516811279827</v>
+        <f t="shared" si="9"/>
+        <v>0.96885250000000001</v>
       </c>
       <c r="F152" s="16"/>
       <c r="G152" s="16"/>
@@ -40184,21 +40184,21 @@
       <c r="AC152" s="16"/>
     </row>
     <row r="153" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="69"/>
+      <c r="A153" s="89"/>
       <c r="B153" s="15">
         <v>6</v>
       </c>
       <c r="C153" s="40">
-        <f t="shared" si="11"/>
-        <v>0.69207230287503563</v>
+        <f t="shared" si="8"/>
+        <v>0.69206999999999996</v>
       </c>
       <c r="D153" s="40">
-        <f t="shared" si="11"/>
-        <v>0.90260494441679118</v>
+        <f t="shared" si="9"/>
+        <v>0.90260499999999999</v>
       </c>
       <c r="E153" s="40">
-        <f t="shared" si="11"/>
-        <v>0.93201825888490386</v>
+        <f t="shared" si="9"/>
+        <v>0.93201833333333328</v>
       </c>
       <c r="F153" s="16"/>
       <c r="G153" s="16"/>
@@ -40226,21 +40226,21 @@
       <c r="AC153" s="16"/>
     </row>
     <row r="154" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="69"/>
+      <c r="A154" s="89"/>
       <c r="B154" s="15">
         <v>8</v>
       </c>
       <c r="C154" s="40">
-        <f t="shared" si="11"/>
-        <v>0.64660904255319152</v>
+        <f t="shared" si="8"/>
+        <v>0.64661000000000002</v>
       </c>
       <c r="D154" s="40">
-        <f t="shared" si="11"/>
-        <v>0.81437125748502992</v>
+        <f t="shared" si="9"/>
+        <v>0.81437124999999999</v>
       </c>
       <c r="E154" s="40">
-        <f t="shared" si="11"/>
-        <v>0.90364810183493971</v>
+        <f t="shared" si="9"/>
+        <v>0.90364750000000005</v>
       </c>
       <c r="F154" s="16"/>
       <c r="G154" s="16"/>
@@ -40268,21 +40268,21 @@
       <c r="AC154" s="16"/>
     </row>
     <row r="155" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="69"/>
+      <c r="A155" s="89"/>
       <c r="B155" s="15">
         <v>10</v>
       </c>
       <c r="C155" s="40">
-        <f>C141/B141</f>
-        <v>0.58939393939393936</v>
+        <f t="shared" si="8"/>
+        <v>0.58938999999999997</v>
       </c>
       <c r="D155" s="40">
-        <f t="shared" ref="D155:E161" si="12">D141/$B141</f>
-        <v>0.74953252632614897</v>
+        <f t="shared" ref="D155:E161" si="10">D141/$B141</f>
+        <v>0.749533</v>
       </c>
       <c r="E155" s="40">
-        <f t="shared" si="12"/>
-        <v>0.86001537741525702</v>
+        <f t="shared" si="10"/>
+        <v>0.86001499999999997</v>
       </c>
       <c r="F155" s="16"/>
       <c r="G155" s="16"/>
@@ -40310,21 +40310,21 @@
       <c r="AC155" s="16"/>
     </row>
     <row r="156" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="69"/>
+      <c r="A156" s="89"/>
       <c r="B156" s="15">
         <v>12</v>
       </c>
       <c r="C156" s="40">
-        <f t="shared" ref="C156:C161" si="13">C142/$B142</f>
-        <v>0.56475029036004643</v>
+        <f t="shared" si="8"/>
+        <v>0.56474999999999997</v>
       </c>
       <c r="D156" s="40">
-        <f t="shared" si="12"/>
-        <v>0.78997593560700352</v>
+        <f t="shared" si="10"/>
+        <v>0.78997583333333343</v>
       </c>
       <c r="E156" s="40">
-        <f t="shared" si="12"/>
-        <v>0.84976614213801582</v>
+        <f t="shared" si="10"/>
+        <v>0.84976583333333344</v>
       </c>
       <c r="F156" s="31"/>
       <c r="G156" s="31"/>
@@ -40352,21 +40352,21 @@
       <c r="AC156" s="31"/>
     </row>
     <row r="157" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="69"/>
+      <c r="A157" s="89"/>
       <c r="B157" s="15">
         <v>14</v>
       </c>
       <c r="C157" s="40">
-        <f t="shared" si="13"/>
-        <v>0.52704313895512678</v>
+        <f t="shared" si="8"/>
+        <v>0.52703999999999995</v>
       </c>
       <c r="D157" s="40">
-        <f t="shared" si="12"/>
-        <v>0.74510341049171347</v>
+        <f t="shared" si="10"/>
+        <v>0.74510357142857142</v>
       </c>
       <c r="E157" s="40">
-        <f t="shared" si="12"/>
-        <v>0.77667250332085491</v>
+        <f t="shared" si="10"/>
+        <v>0.77667285714285705</v>
       </c>
       <c r="F157" s="31"/>
       <c r="G157" s="31"/>
@@ -40394,21 +40394,21 @@
       <c r="AC157" s="31"/>
     </row>
     <row r="158" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="69"/>
+      <c r="A158" s="89"/>
       <c r="B158" s="15">
         <v>16</v>
       </c>
       <c r="C158" s="40">
-        <f t="shared" si="13"/>
-        <v>0.49698487326246932</v>
+        <f t="shared" si="8"/>
+        <v>0.49698999999999999</v>
       </c>
       <c r="D158" s="40">
-        <f t="shared" si="12"/>
-        <v>0.69784489077847822</v>
+        <f t="shared" si="10"/>
+        <v>0.69784500000000005</v>
       </c>
       <c r="E158" s="40">
-        <f t="shared" si="12"/>
-        <v>0.76341574874180984</v>
+        <f t="shared" si="10"/>
+        <v>0.76341562500000004</v>
       </c>
       <c r="F158" s="16"/>
       <c r="G158" s="16"/>
@@ -40436,21 +40436,21 @@
       <c r="AC158" s="16"/>
     </row>
     <row r="159" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="69"/>
+      <c r="A159" s="89"/>
       <c r="B159" s="15">
         <v>18</v>
       </c>
       <c r="C159" s="40">
-        <f t="shared" si="13"/>
-        <v>0.45941987906273624</v>
+        <f t="shared" si="8"/>
+        <v>0.45942</v>
       </c>
       <c r="D159" s="40">
-        <f t="shared" si="12"/>
-        <v>0.68232722320772643</v>
+        <f t="shared" si="10"/>
+        <v>0.68232722222222231</v>
       </c>
       <c r="E159" s="40">
-        <f t="shared" si="12"/>
-        <v>0.6925667490429811</v>
+        <f t="shared" si="10"/>
+        <v>0.69256666666666666</v>
       </c>
       <c r="F159" s="16"/>
       <c r="G159" s="16"/>
@@ -40478,21 +40478,21 @@
       <c r="AC159" s="16"/>
     </row>
     <row r="160" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A160" s="69"/>
+      <c r="A160" s="89"/>
       <c r="B160" s="15">
         <v>20</v>
       </c>
       <c r="C160" s="40">
-        <f t="shared" si="13"/>
-        <v>0.45571696344892221</v>
+        <f t="shared" si="8"/>
+        <v>0.45572000000000001</v>
       </c>
       <c r="D160" s="40">
-        <f t="shared" si="12"/>
-        <v>0.62879788639365919</v>
+        <f t="shared" si="10"/>
+        <v>0.62879799999999997</v>
       </c>
       <c r="E160" s="40">
-        <f t="shared" si="12"/>
-        <v>0.7024875757741248</v>
+        <f t="shared" si="10"/>
+        <v>0.70248749999999993</v>
       </c>
       <c r="F160" s="16"/>
       <c r="G160" s="16"/>
@@ -40520,21 +40520,21 @@
       <c r="AC160" s="16"/>
     </row>
     <row r="161" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="69"/>
+      <c r="A161" s="89"/>
       <c r="B161" s="49">
         <v>40</v>
       </c>
       <c r="C161" s="50">
-        <f t="shared" si="13"/>
-        <v>0.20243547044129889</v>
+        <f t="shared" si="8"/>
+        <v>0.20244000000000001</v>
       </c>
       <c r="D161" s="50">
-        <f t="shared" si="12"/>
-        <v>0.27811860940695293</v>
+        <f t="shared" si="10"/>
+        <v>0.27811849999999999</v>
       </c>
       <c r="E161" s="50">
-        <f t="shared" si="12"/>
-        <v>0.31177589800765915</v>
+        <f t="shared" si="10"/>
+        <v>0.311776</v>
       </c>
       <c r="F161" s="16"/>
       <c r="G161" s="16"/>
@@ -40562,42 +40562,63 @@
       <c r="AC161" s="16"/>
     </row>
     <row r="162" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A162" s="69"/>
+      <c r="A162" s="89"/>
       <c r="B162" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="C162" s="70" t="s">
+      <c r="C162" s="81" t="s">
         <v>115</v>
       </c>
-      <c r="D162" s="71"/>
-      <c r="E162" s="71"/>
-      <c r="F162" s="71"/>
-      <c r="G162" s="71"/>
-      <c r="H162" s="71"/>
-      <c r="I162" s="71"/>
-      <c r="J162" s="71"/>
-      <c r="K162" s="71"/>
-      <c r="L162" s="71"/>
-      <c r="M162" s="71"/>
-      <c r="N162" s="71"/>
-      <c r="O162" s="71"/>
-      <c r="P162" s="71"/>
-      <c r="Q162" s="71"/>
-      <c r="R162" s="71"/>
-      <c r="S162" s="71"/>
-      <c r="T162" s="71"/>
-      <c r="U162" s="71"/>
-      <c r="V162" s="71"/>
-      <c r="W162" s="71"/>
-      <c r="X162" s="71"/>
-      <c r="Y162" s="71"/>
-      <c r="Z162" s="71"/>
-      <c r="AA162" s="71"/>
-      <c r="AB162" s="71"/>
-      <c r="AC162" s="72"/>
+      <c r="D162" s="86"/>
+      <c r="E162" s="86"/>
+      <c r="F162" s="86"/>
+      <c r="G162" s="86"/>
+      <c r="H162" s="86"/>
+      <c r="I162" s="86"/>
+      <c r="J162" s="86"/>
+      <c r="K162" s="86"/>
+      <c r="L162" s="86"/>
+      <c r="M162" s="86"/>
+      <c r="N162" s="86"/>
+      <c r="O162" s="86"/>
+      <c r="P162" s="86"/>
+      <c r="Q162" s="86"/>
+      <c r="R162" s="86"/>
+      <c r="S162" s="86"/>
+      <c r="T162" s="86"/>
+      <c r="U162" s="86"/>
+      <c r="V162" s="86"/>
+      <c r="W162" s="86"/>
+      <c r="X162" s="86"/>
+      <c r="Y162" s="86"/>
+      <c r="Z162" s="86"/>
+      <c r="AA162" s="86"/>
+      <c r="AB162" s="86"/>
+      <c r="AC162" s="87"/>
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="B148:E148"/>
+    <mergeCell ref="B134:E134"/>
+    <mergeCell ref="B120:E120"/>
+    <mergeCell ref="A120:A162"/>
+    <mergeCell ref="C162:AC162"/>
+    <mergeCell ref="A89:A119"/>
+    <mergeCell ref="C119:T119"/>
+    <mergeCell ref="B89:E89"/>
+    <mergeCell ref="B99:E99"/>
+    <mergeCell ref="B109:E109"/>
+    <mergeCell ref="A24:L24"/>
+    <mergeCell ref="M24:N24"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="C12:N12"/>
+    <mergeCell ref="A2:A12"/>
+    <mergeCell ref="A13:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:N23"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B2:D2"/>
     <mergeCell ref="O88:T88"/>
     <mergeCell ref="A88:N88"/>
     <mergeCell ref="A57:A87"/>
@@ -40612,27 +40633,6 @@
     <mergeCell ref="B45:D45"/>
     <mergeCell ref="B35:D35"/>
     <mergeCell ref="B25:D25"/>
-    <mergeCell ref="A24:L24"/>
-    <mergeCell ref="M24:N24"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="C12:N12"/>
-    <mergeCell ref="A2:A12"/>
-    <mergeCell ref="A13:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:N23"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="A89:A119"/>
-    <mergeCell ref="C119:T119"/>
-    <mergeCell ref="B89:E89"/>
-    <mergeCell ref="B99:E99"/>
-    <mergeCell ref="B109:E109"/>
-    <mergeCell ref="B148:E148"/>
-    <mergeCell ref="B134:E134"/>
-    <mergeCell ref="B120:E120"/>
-    <mergeCell ref="A120:A162"/>
-    <mergeCell ref="C162:AC162"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <hyperlinks>

--- a/DecompositionLU/docs/statistics.xlsx
+++ b/DecompositionLU/docs/statistics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maxim\source\repos\practice\SECOND_COURSE\FOR_ITLAB\ArchBenchs\DecompositionLU\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8730C858-ED17-4A5F-A6F0-5B7E2934BBAA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EF867C6-078C-45FB-8D57-EF0D3112A1F6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-114" yWindow="-114" windowWidth="27602" windowHeight="15027" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="119">
   <si>
     <t>Я не уверен, будет ли это использоваться в готовой презентации и так ли это надо делать, если да, так что пока считаем, что файл для личного пользования.</t>
   </si>
@@ -478,6 +478,12 @@
   </si>
   <si>
     <t>Замеры на кластере, данные, аналогично, вкладке "Про процессор"</t>
+  </si>
+  <si>
+    <t>icpx -g -O2 -fopenmp -march=icelake-server ./test.cpp -o test</t>
+  </si>
+  <si>
+    <t>srun -N 1 advisor --collect=roofline …</t>
   </si>
 </sst>
 </file>
@@ -35691,28 +35697,52 @@
       <c r="A79" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B79" s="9"/>
-      <c r="C79" s="10"/>
-      <c r="D79" s="10"/>
-      <c r="E79" s="10"/>
+      <c r="B79" s="9">
+        <v>1179</v>
+      </c>
+      <c r="C79" s="10">
+        <v>2737</v>
+      </c>
+      <c r="D79" s="10">
+        <v>4927</v>
+      </c>
+      <c r="E79" s="10">
+        <v>9248</v>
+      </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B80" s="9"/>
-      <c r="C80" s="10"/>
-      <c r="D80" s="10"/>
-      <c r="E80" s="10"/>
+      <c r="B80" s="9">
+        <v>459</v>
+      </c>
+      <c r="C80" s="10">
+        <v>1310</v>
+      </c>
+      <c r="D80" s="10">
+        <v>2689</v>
+      </c>
+      <c r="E80" s="10">
+        <v>6665</v>
+      </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B81" s="9"/>
-      <c r="C81" s="10"/>
-      <c r="D81" s="10"/>
-      <c r="E81" s="10"/>
+      <c r="B81" s="9">
+        <v>1638</v>
+      </c>
+      <c r="C81" s="10">
+        <v>4048</v>
+      </c>
+      <c r="D81" s="10">
+        <v>7636</v>
+      </c>
+      <c r="E81" s="10">
+        <v>15914</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="32">
@@ -35766,7 +35796,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AC162"/>
+  <dimension ref="A1:AC167"/>
   <sheetFormatPr defaultRowHeight="21.6" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.28515625" style="26" customWidth="1"/>
@@ -40595,6 +40625,16 @@
       <c r="AA162" s="86"/>
       <c r="AB162" s="86"/>
       <c r="AC162" s="87"/>
+    </row>
+    <row r="165" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B165" s="26" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="167" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B167" s="26" t="s">
+        <v>118</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="35">

--- a/DecompositionLU/docs/statistics.xlsx
+++ b/DecompositionLU/docs/statistics.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maxim\source\repos\practice\SECOND_COURSE\FOR_ITLAB\ArchBenchs\DecompositionLU\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EF867C6-078C-45FB-8D57-EF0D3112A1F6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7569BE9-6E9F-4482-B87C-E87E23EA383E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-114" yWindow="-114" windowWidth="27602" windowHeight="15027" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-114" yWindow="-114" windowWidth="27602" windowHeight="15027" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Таблица" sheetId="1" r:id="rId1"/>
     <sheet name="Графики" sheetId="2" r:id="rId2"/>
-    <sheet name="Про процессор" sheetId="3" r:id="rId3"/>
+    <sheet name="Про ноутбук" sheetId="3" r:id="rId3"/>
+    <sheet name="Про кластер" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="125">
   <si>
     <t>Я не уверен, будет ли это использоваться в готовой презентации и так ли это надо делать, если да, так что пока считаем, что файл для личного пользования.</t>
   </si>
@@ -474,9 +475,6 @@
     <t>n = 15000</t>
   </si>
   <si>
-    <t>В ходе работы выяснил следующее - на миникластере 2 процессора по 10 физ ядер, балансировать их надо поровну, но на каждом четное количество (чем больше размер матрицы, тем более заметно, например, при n=10000 и числе потоков &lt;= 10, это незаметно)</t>
-  </si>
-  <si>
     <t>Замеры на кластере, данные, аналогично, вкладке "Про процессор"</t>
   </si>
   <si>
@@ -485,12 +483,33 @@
   <si>
     <t>srun -N 1 advisor --collect=roofline …</t>
   </si>
+  <si>
+    <t>на 20000:</t>
+  </si>
+  <si>
+    <t>1 поток</t>
+  </si>
+  <si>
+    <t>20 потоков</t>
+  </si>
+  <si>
+    <t>время</t>
+  </si>
+  <si>
+    <t>ускорение</t>
+  </si>
+  <si>
+    <t>эффективность</t>
+  </si>
+  <si>
+    <t>с ключом -march=icelake-server программа ускорилась вдвое, но потеряла в ускорении.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -631,6 +650,13 @@
       <family val="2"/>
       <charset val="204"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="GOST Common"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="8">
@@ -859,7 +885,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -972,6 +998,27 @@
     <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1011,6 +1058,48 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1046,45 +1135,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -9098,34 +9148,34 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.7688299999999999</c:v>
+                  <c:v>1.9660200000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.1615700000000002</c:v>
+                  <c:v>3.7708499999999998</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.1524299999999998</c:v>
+                  <c:v>5.16411</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.1728699999999996</c:v>
+                  <c:v>6.5782400000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.8939399999999997</c:v>
+                  <c:v>7.8900300000000003</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>6.7770000000000001</c:v>
+                  <c:v>9.0895299999999999</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>7.3785999999999996</c:v>
+                  <c:v>9.7836400000000001</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>7.9517600000000002</c:v>
+                  <c:v>10.21063</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>8.2695600000000002</c:v>
+                  <c:v>10.82696</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>9.1143400000000003</c:v>
+                  <c:v>11.23382</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9626,34 +9676,34 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.88441999999999998</c:v>
+                  <c:v>0.98301000000000005</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.79039000000000004</c:v>
+                  <c:v>0.94271000000000005</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.69206999999999996</c:v>
+                  <c:v>0.86068999999999996</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.64661000000000002</c:v>
+                  <c:v>0.82228000000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.58938999999999997</c:v>
+                  <c:v>0.78900000000000003</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.56474999999999997</c:v>
+                  <c:v>0.75746000000000002</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.52703999999999995</c:v>
+                  <c:v>0.69882999999999995</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.49698999999999999</c:v>
+                  <c:v>0.63815999999999995</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.45942</c:v>
+                  <c:v>0.60150000000000003</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.45572000000000001</c:v>
+                  <c:v>0.56169000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10024,37 +10074,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>9725</c:v>
+                  <c:v>5381</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5498</c:v>
+                  <c:v>2737</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3076</c:v>
+                  <c:v>1427</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2342</c:v>
+                  <c:v>1042</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1880</c:v>
+                  <c:v>818</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1650</c:v>
+                  <c:v>682</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1435</c:v>
+                  <c:v>592</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1318</c:v>
+                  <c:v>550</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1223</c:v>
+                  <c:v>527</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1176</c:v>
+                  <c:v>497</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1067</c:v>
+                  <c:v>479</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10425,37 +10475,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>76160</c:v>
+                  <c:v>41829</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>39071</c:v>
+                  <c:v>21202</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>20102</c:v>
+                  <c:v>11078</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>14063</c:v>
+                  <c:v>7787</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>11690</c:v>
+                  <c:v>6260</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>10161</c:v>
+                  <c:v>5372</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>8034</c:v>
+                  <c:v>4574</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>7301</c:v>
+                  <c:v>4295</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>6821</c:v>
+                  <c:v>3969</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>6201</c:v>
+                  <c:v>3709</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>6056</c:v>
+                  <c:v>3554</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11026,37 +11076,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>257265</c:v>
+                  <c:v>142216</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>130577</c:v>
+                  <c:v>70771</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>66384</c:v>
+                  <c:v>36194</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46005</c:v>
+                  <c:v>25435</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>35587</c:v>
+                  <c:v>19632</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>29914</c:v>
+                  <c:v>16476</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>25229</c:v>
+                  <c:v>14220</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>23660</c:v>
+                  <c:v>13252</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>21062</c:v>
+                  <c:v>12007</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>20637</c:v>
+                  <c:v>11351</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>18311</c:v>
+                  <c:v>10884</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11559,34 +11609,34 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.9702200000000001</c:v>
+                  <c:v>2.0095200000000002</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.87541</c:v>
+                  <c:v>3.9292699999999998</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.5921099999999999</c:v>
+                  <c:v>5.5913500000000003</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7.2291800000000004</c:v>
+                  <c:v>7.2440899999999999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>8.6001499999999993</c:v>
+                  <c:v>8.63171</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>10.197190000000001</c:v>
+                  <c:v>10.00113</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>10.873419999999999</c:v>
+                  <c:v>10.73166</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>12.214650000000001</c:v>
+                  <c:v>11.84442</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>12.466200000000001</c:v>
+                  <c:v>12.52894</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>14.04975</c:v>
+                  <c:v>13.066520000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12090,37 +12140,37 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.9492700000000001</c:v>
+                  <c:v>1.97288</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.7886799999999998</c:v>
+                  <c:v>3.7758600000000002</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.4156300000000002</c:v>
+                  <c:v>5.3716499999999998</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6.5149699999999999</c:v>
+                  <c:v>6.6819499999999996</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>7.49533</c:v>
+                  <c:v>7.7864899999999997</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>9.4797100000000007</c:v>
+                  <c:v>9.1449499999999997</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>10.43145</c:v>
+                  <c:v>9.7390000000000008</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>11.165520000000001</c:v>
+                  <c:v>10.538930000000001</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>12.281890000000001</c:v>
+                  <c:v>11.277699999999999</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>12.57596</c:v>
+                  <c:v>11.76956</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>11.124739999999999</c:v>
+                  <c:v>11.314310000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12621,34 +12671,34 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.98511000000000004</c:v>
+                  <c:v>1.0047600000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.96885250000000001</c:v>
+                  <c:v>0.98231999999999997</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.93201833333333328</c:v>
+                  <c:v>0.93189</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.90364750000000005</c:v>
+                  <c:v>0.90551000000000004</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.86001499999999997</c:v>
+                  <c:v>0.86316999999999999</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.84976583333333344</c:v>
+                  <c:v>0.83343</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.77667285714285705</c:v>
+                  <c:v>0.76654999999999995</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.76341562500000004</c:v>
+                  <c:v>0.74028000000000005</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.69256666666666666</c:v>
+                  <c:v>0.69604999999999995</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.70248749999999993</c:v>
+                  <c:v>0.65332999999999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13151,34 +13201,34 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.97463500000000003</c:v>
+                  <c:v>0.98643999999999998</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.94716999999999996</c:v>
+                  <c:v>0.94396999999999998</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.90260499999999999</c:v>
+                  <c:v>0.89527999999999996</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.81437124999999999</c:v>
+                  <c:v>0.83523999999999998</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.749533</c:v>
+                  <c:v>0.77864999999999995</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.78997583333333343</c:v>
+                  <c:v>0.76207999999999998</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.74510357142857142</c:v>
+                  <c:v>0.69564000000000004</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.69784500000000005</c:v>
+                  <c:v>0.65868000000000004</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.68232722222222231</c:v>
+                  <c:v>0.62653999999999999</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.62879799999999997</c:v>
+                  <c:v>0.58848</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -34272,6 +34322,55 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>314076</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>93477</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Рисунок 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{737DEF32-62D1-4C14-BC14-417238EFD225}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="579422" y="280657"/>
+          <a:ext cx="7267137" cy="1496765"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -34613,17 +34712,17 @@
       <c r="N3" s="6"/>
     </row>
     <row r="5" spans="1:23" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="59" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="53"/>
-      <c r="C5" s="53"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="54"/>
-      <c r="G5" s="59" t="s">
+      <c r="B5" s="60"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="61"/>
+      <c r="G5" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="H5" s="59"/>
+      <c r="H5" s="66"/>
       <c r="S5" s="5"/>
       <c r="T5" s="14"/>
       <c r="U5" s="14"/>
@@ -34634,14 +34733,14 @@
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="56" t="s">
+      <c r="B6" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="56"/>
-      <c r="D6" s="56"/>
-      <c r="E6" s="56"/>
-      <c r="G6" s="59"/>
-      <c r="H6" s="59"/>
+      <c r="C6" s="63"/>
+      <c r="D6" s="63"/>
+      <c r="E6" s="63"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="66"/>
       <c r="S6" s="14"/>
       <c r="T6" s="14"/>
       <c r="U6" s="14"/>
@@ -34664,8 +34763,8 @@
       <c r="E7" s="8">
         <v>10000</v>
       </c>
-      <c r="G7" s="59"/>
-      <c r="H7" s="59"/>
+      <c r="G7" s="66"/>
+      <c r="H7" s="66"/>
       <c r="S7" s="14"/>
       <c r="T7" s="14"/>
       <c r="U7" s="14"/>
@@ -34673,15 +34772,15 @@
       <c r="W7" s="14"/>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A8" s="57" t="s">
+      <c r="A8" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="57"/>
-      <c r="C8" s="57"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
-      <c r="G8" s="59"/>
-      <c r="H8" s="59"/>
+      <c r="B8" s="64"/>
+      <c r="C8" s="64"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="64"/>
+      <c r="G8" s="66"/>
+      <c r="H8" s="66"/>
       <c r="S8" s="14"/>
       <c r="T8" s="14"/>
       <c r="U8" s="14"/>
@@ -34757,13 +34856,13 @@
       <c r="W11" s="5"/>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A12" s="57" t="s">
+      <c r="A12" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="57"/>
-      <c r="C12" s="57"/>
-      <c r="D12" s="57"/>
-      <c r="E12" s="57"/>
+      <c r="B12" s="64"/>
+      <c r="C12" s="64"/>
+      <c r="D12" s="64"/>
+      <c r="E12" s="64"/>
       <c r="F12" s="5"/>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.25">
@@ -34776,7 +34875,7 @@
       <c r="C13" s="10">
         <v>232</v>
       </c>
-      <c r="D13" s="61" t="s">
+      <c r="D13" s="68" t="s">
         <v>21</v>
       </c>
       <c r="E13" s="10">
@@ -34794,7 +34893,7 @@
       <c r="C14" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="62"/>
+      <c r="D14" s="69"/>
       <c r="E14" s="10" t="s">
         <v>10</v>
       </c>
@@ -34812,30 +34911,30 @@
       <c r="C15" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="63"/>
+      <c r="D15" s="70"/>
       <c r="E15" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="64" t="s">
+      <c r="A18" s="71" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="64"/>
-      <c r="C18" s="64"/>
-      <c r="D18" s="64"/>
-      <c r="E18" s="64"/>
+      <c r="B18" s="71"/>
+      <c r="C18" s="71"/>
+      <c r="D18" s="71"/>
+      <c r="E18" s="71"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B19" s="56" t="s">
+      <c r="B19" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="C19" s="56"/>
-      <c r="D19" s="56"/>
-      <c r="E19" s="56"/>
+      <c r="C19" s="63"/>
+      <c r="D19" s="63"/>
+      <c r="E19" s="63"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
@@ -34855,13 +34954,13 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="57" t="s">
+      <c r="A21" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="B21" s="57"/>
-      <c r="C21" s="57"/>
-      <c r="D21" s="57"/>
-      <c r="E21" s="57"/>
+      <c r="B21" s="64"/>
+      <c r="C21" s="64"/>
+      <c r="D21" s="64"/>
+      <c r="E21" s="64"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
@@ -34914,17 +35013,17 @@
         <v>35</v>
       </c>
       <c r="G24" s="18"/>
-      <c r="H24" s="58"/>
-      <c r="I24" s="58"/>
+      <c r="H24" s="65"/>
+      <c r="I24" s="65"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="57" t="s">
+      <c r="A25" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="B25" s="57"/>
-      <c r="C25" s="57"/>
-      <c r="D25" s="57"/>
-      <c r="E25" s="57"/>
+      <c r="B25" s="64"/>
+      <c r="C25" s="64"/>
+      <c r="D25" s="64"/>
+      <c r="E25" s="64"/>
       <c r="G25" s="19"/>
       <c r="H25" s="17"/>
       <c r="I25" s="17"/>
@@ -35009,15 +35108,15 @@
       <c r="I30" s="18"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="52" t="s">
+      <c r="A31" s="59" t="s">
         <v>70</v>
       </c>
-      <c r="B31" s="53"/>
-      <c r="C31" s="54"/>
-      <c r="D31" s="55" t="s">
+      <c r="B31" s="60"/>
+      <c r="C31" s="61"/>
+      <c r="D31" s="62" t="s">
         <v>91</v>
       </c>
-      <c r="E31" s="55" t="s">
+      <c r="E31" s="62" t="s">
         <v>91</v>
       </c>
       <c r="G31" s="20"/>
@@ -35028,12 +35127,12 @@
       <c r="A32" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B32" s="56" t="s">
+      <c r="B32" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="56"/>
-      <c r="D32" s="56"/>
-      <c r="E32" s="56"/>
+      <c r="C32" s="63"/>
+      <c r="D32" s="63"/>
+      <c r="E32" s="63"/>
       <c r="G32" s="23"/>
       <c r="H32" s="18"/>
       <c r="I32" s="18"/>
@@ -35059,13 +35158,13 @@
       <c r="I33" s="18"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="57" t="s">
+      <c r="A34" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="B34" s="57"/>
-      <c r="C34" s="57"/>
-      <c r="D34" s="57"/>
-      <c r="E34" s="57"/>
+      <c r="B34" s="64"/>
+      <c r="C34" s="64"/>
+      <c r="D34" s="64"/>
+      <c r="E34" s="64"/>
       <c r="G34" s="23"/>
       <c r="H34" s="18"/>
       <c r="I34" s="18"/>
@@ -35131,13 +35230,13 @@
       <c r="I37" s="18"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="57" t="s">
+      <c r="A38" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="B38" s="57"/>
-      <c r="C38" s="57"/>
-      <c r="D38" s="57"/>
-      <c r="E38" s="57"/>
+      <c r="B38" s="64"/>
+      <c r="C38" s="64"/>
+      <c r="D38" s="64"/>
+      <c r="E38" s="64"/>
       <c r="G38" s="23"/>
       <c r="H38" s="18"/>
       <c r="I38" s="18"/>
@@ -35203,23 +35302,23 @@
       <c r="I41" s="18"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B42" s="60" t="s">
+      <c r="B42" s="67" t="s">
         <v>66</v>
       </c>
-      <c r="C42" s="60"/>
-      <c r="D42" s="60"/>
-      <c r="E42" s="60"/>
+      <c r="C42" s="67"/>
+      <c r="D42" s="67"/>
+      <c r="E42" s="67"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="52" t="s">
+      <c r="A44" s="59" t="s">
         <v>82</v>
       </c>
-      <c r="B44" s="53"/>
-      <c r="C44" s="54"/>
-      <c r="D44" s="55" t="s">
+      <c r="B44" s="60"/>
+      <c r="C44" s="61"/>
+      <c r="D44" s="62" t="s">
         <v>92</v>
       </c>
-      <c r="E44" s="55" t="s">
+      <c r="E44" s="62" t="s">
         <v>91</v>
       </c>
     </row>
@@ -35227,12 +35326,12 @@
       <c r="A45" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B45" s="56" t="s">
+      <c r="B45" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="C45" s="56"/>
-      <c r="D45" s="56"/>
-      <c r="E45" s="56"/>
+      <c r="C45" s="63"/>
+      <c r="D45" s="63"/>
+      <c r="E45" s="63"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
@@ -35252,13 +35351,13 @@
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="57" t="s">
+      <c r="A47" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="B47" s="57"/>
-      <c r="C47" s="57"/>
-      <c r="D47" s="57"/>
-      <c r="E47" s="57"/>
+      <c r="B47" s="64"/>
+      <c r="C47" s="64"/>
+      <c r="D47" s="64"/>
+      <c r="E47" s="64"/>
       <c r="G47" s="1" t="s">
         <v>95</v>
       </c>
@@ -35336,13 +35435,13 @@
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="57" t="s">
+      <c r="A51" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="B51" s="57"/>
-      <c r="C51" s="57"/>
-      <c r="D51" s="57"/>
-      <c r="E51" s="57"/>
+      <c r="B51" s="64"/>
+      <c r="C51" s="64"/>
+      <c r="D51" s="64"/>
+      <c r="E51" s="64"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
@@ -35401,15 +35500,15 @@
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="52" t="s">
+      <c r="A57" s="59" t="s">
         <v>104</v>
       </c>
-      <c r="B57" s="53"/>
-      <c r="C57" s="54"/>
-      <c r="D57" s="55" t="s">
+      <c r="B57" s="60"/>
+      <c r="C57" s="61"/>
+      <c r="D57" s="62" t="s">
         <v>92</v>
       </c>
-      <c r="E57" s="55" t="s">
+      <c r="E57" s="62" t="s">
         <v>91</v>
       </c>
     </row>
@@ -35417,12 +35516,12 @@
       <c r="A58" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B58" s="56" t="s">
+      <c r="B58" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="C58" s="56"/>
-      <c r="D58" s="56"/>
-      <c r="E58" s="56"/>
+      <c r="C58" s="63"/>
+      <c r="D58" s="63"/>
+      <c r="E58" s="63"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
@@ -35442,13 +35541,13 @@
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="57" t="s">
+      <c r="A60" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="B60" s="57"/>
-      <c r="C60" s="57"/>
-      <c r="D60" s="57"/>
-      <c r="E60" s="57"/>
+      <c r="B60" s="64"/>
+      <c r="C60" s="64"/>
+      <c r="D60" s="64"/>
+      <c r="E60" s="64"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
@@ -35502,13 +35601,13 @@
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="57" t="s">
+      <c r="A64" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="B64" s="57"/>
-      <c r="C64" s="57"/>
-      <c r="D64" s="57"/>
-      <c r="E64" s="57"/>
+      <c r="B64" s="64"/>
+      <c r="C64" s="64"/>
+      <c r="D64" s="64"/>
+      <c r="E64" s="64"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
@@ -35567,15 +35666,15 @@
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="52" t="s">
+      <c r="A70" s="59" t="s">
         <v>108</v>
       </c>
-      <c r="B70" s="53"/>
-      <c r="C70" s="54"/>
-      <c r="D70" s="55" t="s">
+      <c r="B70" s="60"/>
+      <c r="C70" s="61"/>
+      <c r="D70" s="62" t="s">
         <v>92</v>
       </c>
-      <c r="E70" s="55" t="s">
+      <c r="E70" s="62" t="s">
         <v>91</v>
       </c>
     </row>
@@ -35583,21 +35682,21 @@
       <c r="A71" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B71" s="56" t="s">
+      <c r="B71" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="C71" s="56"/>
-      <c r="D71" s="56"/>
-      <c r="E71" s="56"/>
+      <c r="C71" s="63"/>
+      <c r="D71" s="63"/>
+      <c r="E71" s="63"/>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="57" t="s">
+      <c r="A72" s="64" t="s">
         <v>109</v>
       </c>
-      <c r="B72" s="57"/>
-      <c r="C72" s="57"/>
-      <c r="D72" s="57"/>
-      <c r="E72" s="57"/>
+      <c r="B72" s="64"/>
+      <c r="C72" s="64"/>
+      <c r="D72" s="64"/>
+      <c r="E72" s="64"/>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
@@ -35668,13 +35767,13 @@
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="57" t="s">
+      <c r="A77" s="64" t="s">
         <v>110</v>
       </c>
-      <c r="B77" s="57"/>
-      <c r="C77" s="57"/>
-      <c r="D77" s="57"/>
-      <c r="E77" s="57"/>
+      <c r="B77" s="64"/>
+      <c r="C77" s="64"/>
+      <c r="D77" s="64"/>
+      <c r="E77" s="64"/>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
@@ -35746,11 +35845,18 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="A70:C70"/>
-    <mergeCell ref="D70:E70"/>
-    <mergeCell ref="B71:E71"/>
-    <mergeCell ref="A72:E72"/>
-    <mergeCell ref="A77:E77"/>
+    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="D57:E57"/>
+    <mergeCell ref="B58:E58"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A31:C31"/>
     <mergeCell ref="H24:I24"/>
     <mergeCell ref="G5:H8"/>
     <mergeCell ref="B42:E42"/>
@@ -35766,18 +35872,11 @@
     <mergeCell ref="B19:E19"/>
     <mergeCell ref="A21:E21"/>
     <mergeCell ref="A25:E25"/>
-    <mergeCell ref="B45:E45"/>
-    <mergeCell ref="A47:E47"/>
-    <mergeCell ref="A51:E51"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A57:C57"/>
-    <mergeCell ref="D57:E57"/>
-    <mergeCell ref="B58:E58"/>
-    <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="A70:C70"/>
+    <mergeCell ref="D70:E70"/>
+    <mergeCell ref="B71:E71"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A77:E77"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <hyperlinks>
@@ -35796,7 +35895,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AC167"/>
+  <dimension ref="A1:AC175"/>
   <sheetFormatPr defaultRowHeight="21.6" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.28515625" style="26" customWidth="1"/>
@@ -35809,24 +35908,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="71" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
-      <c r="J1" s="64"/>
-      <c r="K1" s="64"/>
-      <c r="L1" s="64"/>
-      <c r="M1" s="55" t="s">
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="71"/>
+      <c r="J1" s="71"/>
+      <c r="K1" s="71"/>
+      <c r="L1" s="71"/>
+      <c r="M1" s="62" t="s">
         <v>90</v>
       </c>
-      <c r="N1" s="55"/>
+      <c r="N1" s="62"/>
       <c r="O1" s="36"/>
       <c r="P1" s="35"/>
       <c r="Q1" s="35"/>
@@ -35841,14 +35940,14 @@
       <c r="Z1" s="35"/>
     </row>
     <row r="2" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="82" t="s">
+      <c r="A2" s="81" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="77" t="s">
+      <c r="B2" s="73" t="s">
         <v>78</v>
       </c>
-      <c r="C2" s="78"/>
-      <c r="D2" s="79"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="75"/>
       <c r="E2" s="31"/>
       <c r="F2" s="31"/>
       <c r="G2" s="31"/>
@@ -35873,7 +35972,7 @@
       <c r="Z2" s="30"/>
     </row>
     <row r="3" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="82"/>
+      <c r="A3" s="81"/>
       <c r="B3" s="29" t="s">
         <v>77</v>
       </c>
@@ -35907,7 +36006,7 @@
       <c r="Z3" s="30"/>
     </row>
     <row r="4" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="82"/>
+      <c r="A4" s="81"/>
       <c r="B4" s="15">
         <v>1</v>
       </c>
@@ -35941,7 +36040,7 @@
       <c r="Z4" s="30"/>
     </row>
     <row r="5" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="82"/>
+      <c r="A5" s="81"/>
       <c r="B5" s="15">
         <v>2</v>
       </c>
@@ -35975,7 +36074,7 @@
       <c r="Z5" s="30"/>
     </row>
     <row r="6" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="82"/>
+      <c r="A6" s="81"/>
       <c r="B6" s="15">
         <v>4</v>
       </c>
@@ -35998,7 +36097,7 @@
       <c r="O6" s="38"/>
     </row>
     <row r="7" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="82"/>
+      <c r="A7" s="81"/>
       <c r="B7" s="15">
         <v>6</v>
       </c>
@@ -36021,7 +36120,7 @@
       <c r="O7" s="38"/>
     </row>
     <row r="8" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="82"/>
+      <c r="A8" s="81"/>
       <c r="B8" s="15">
         <v>8</v>
       </c>
@@ -36044,7 +36143,7 @@
       <c r="O8" s="38"/>
     </row>
     <row r="9" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="82"/>
+      <c r="A9" s="81"/>
       <c r="B9" s="15">
         <v>10</v>
       </c>
@@ -36067,7 +36166,7 @@
       <c r="O9" s="38"/>
     </row>
     <row r="10" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="82"/>
+      <c r="A10" s="81"/>
       <c r="B10" s="15">
         <v>12</v>
       </c>
@@ -36090,7 +36189,7 @@
       <c r="O10" s="38"/>
     </row>
     <row r="11" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="82"/>
+      <c r="A11" s="81"/>
       <c r="B11" s="15">
         <v>16</v>
       </c>
@@ -36115,37 +36214,37 @@
       <c r="Q11" s="27"/>
     </row>
     <row r="12" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="82"/>
+      <c r="A12" s="81"/>
       <c r="B12" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="C12" s="80" t="s">
+      <c r="C12" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="D12" s="80"/>
-      <c r="E12" s="80"/>
-      <c r="F12" s="80"/>
-      <c r="G12" s="80"/>
-      <c r="H12" s="80"/>
-      <c r="I12" s="80"/>
-      <c r="J12" s="80"/>
-      <c r="K12" s="80"/>
-      <c r="L12" s="80"/>
-      <c r="M12" s="80"/>
-      <c r="N12" s="81"/>
+      <c r="D12" s="82"/>
+      <c r="E12" s="82"/>
+      <c r="F12" s="82"/>
+      <c r="G12" s="82"/>
+      <c r="H12" s="82"/>
+      <c r="I12" s="82"/>
+      <c r="J12" s="82"/>
+      <c r="K12" s="82"/>
+      <c r="L12" s="82"/>
+      <c r="M12" s="82"/>
+      <c r="N12" s="78"/>
       <c r="O12" s="39"/>
       <c r="P12" s="23"/>
       <c r="Q12" s="23"/>
     </row>
     <row r="13" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="82" t="s">
+      <c r="A13" s="81" t="s">
         <v>87</v>
       </c>
-      <c r="B13" s="77" t="s">
+      <c r="B13" s="73" t="s">
         <v>78</v>
       </c>
-      <c r="C13" s="78"/>
-      <c r="D13" s="79"/>
+      <c r="C13" s="74"/>
+      <c r="D13" s="75"/>
       <c r="E13" s="32"/>
       <c r="F13" s="31"/>
       <c r="G13" s="31"/>
@@ -36161,7 +36260,7 @@
       <c r="Q13" s="23"/>
     </row>
     <row r="14" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="82"/>
+      <c r="A14" s="81"/>
       <c r="B14" s="13" t="s">
         <v>77</v>
       </c>
@@ -36186,7 +36285,7 @@
       <c r="Q14" s="23"/>
     </row>
     <row r="15" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="82"/>
+      <c r="A15" s="81"/>
       <c r="B15" s="15">
         <v>1</v>
       </c>
@@ -36211,7 +36310,7 @@
       <c r="Q15" s="27"/>
     </row>
     <row r="16" spans="1:26" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="82"/>
+      <c r="A16" s="81"/>
       <c r="B16" s="15">
         <v>2</v>
       </c>
@@ -36236,7 +36335,7 @@
       <c r="Q16" s="23"/>
     </row>
     <row r="17" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="82"/>
+      <c r="A17" s="81"/>
       <c r="B17" s="15">
         <v>4</v>
       </c>
@@ -36261,7 +36360,7 @@
       <c r="Q17" s="23"/>
     </row>
     <row r="18" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="82"/>
+      <c r="A18" s="81"/>
       <c r="B18" s="15">
         <v>6</v>
       </c>
@@ -36286,7 +36385,7 @@
       <c r="Q18" s="23"/>
     </row>
     <row r="19" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="82"/>
+      <c r="A19" s="81"/>
       <c r="B19" s="15">
         <v>8</v>
       </c>
@@ -36309,7 +36408,7 @@
       <c r="O19" s="38"/>
     </row>
     <row r="20" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="82"/>
+      <c r="A20" s="81"/>
       <c r="B20" s="15">
         <v>10</v>
       </c>
@@ -36332,7 +36431,7 @@
       <c r="O20" s="38"/>
     </row>
     <row r="21" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="82"/>
+      <c r="A21" s="81"/>
       <c r="B21" s="15">
         <v>12</v>
       </c>
@@ -36355,7 +36454,7 @@
       <c r="O21" s="38"/>
     </row>
     <row r="22" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="82"/>
+      <c r="A22" s="81"/>
       <c r="B22" s="83" t="s">
         <v>86</v>
       </c>
@@ -36376,7 +36475,7 @@
       <c r="O22" s="38"/>
     </row>
     <row r="23" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="82"/>
+      <c r="A23" s="81"/>
       <c r="B23" s="83"/>
       <c r="C23" s="84"/>
       <c r="D23" s="84"/>
@@ -36393,35 +36492,35 @@
       <c r="O23" s="38"/>
     </row>
     <row r="24" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="64" t="s">
+      <c r="A24" s="71" t="s">
         <v>89</v>
       </c>
-      <c r="B24" s="64"/>
-      <c r="C24" s="64"/>
-      <c r="D24" s="64"/>
-      <c r="E24" s="64"/>
-      <c r="F24" s="64"/>
-      <c r="G24" s="64"/>
-      <c r="H24" s="64"/>
-      <c r="I24" s="64"/>
-      <c r="J24" s="64"/>
-      <c r="K24" s="64"/>
-      <c r="L24" s="64"/>
-      <c r="M24" s="55" t="s">
+      <c r="B24" s="71"/>
+      <c r="C24" s="71"/>
+      <c r="D24" s="71"/>
+      <c r="E24" s="71"/>
+      <c r="F24" s="71"/>
+      <c r="G24" s="71"/>
+      <c r="H24" s="71"/>
+      <c r="I24" s="71"/>
+      <c r="J24" s="71"/>
+      <c r="K24" s="71"/>
+      <c r="L24" s="71"/>
+      <c r="M24" s="62" t="s">
         <v>90</v>
       </c>
-      <c r="N24" s="55"/>
+      <c r="N24" s="62"/>
       <c r="O24" s="38"/>
     </row>
     <row r="25" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="68" t="s">
+      <c r="A25" s="89" t="s">
         <v>85</v>
       </c>
-      <c r="B25" s="77" t="s">
+      <c r="B25" s="73" t="s">
         <v>78</v>
       </c>
-      <c r="C25" s="78"/>
-      <c r="D25" s="79"/>
+      <c r="C25" s="74"/>
+      <c r="D25" s="75"/>
       <c r="E25" s="31"/>
       <c r="F25" s="31"/>
       <c r="G25" s="31"/>
@@ -36435,7 +36534,7 @@
       <c r="O25" s="27"/>
     </row>
     <row r="26" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="69"/>
+      <c r="A26" s="90"/>
       <c r="B26" s="42" t="s">
         <v>77</v>
       </c>
@@ -36458,7 +36557,7 @@
       <c r="O26" s="27"/>
     </row>
     <row r="27" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="69"/>
+      <c r="A27" s="90"/>
       <c r="B27" s="15">
         <v>1</v>
       </c>
@@ -36481,7 +36580,7 @@
       <c r="O27" s="27"/>
     </row>
     <row r="28" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="69"/>
+      <c r="A28" s="90"/>
       <c r="B28" s="15">
         <v>2</v>
       </c>
@@ -36504,7 +36603,7 @@
       <c r="O28" s="27"/>
     </row>
     <row r="29" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="69"/>
+      <c r="A29" s="90"/>
       <c r="B29" s="15">
         <v>4</v>
       </c>
@@ -36527,7 +36626,7 @@
       <c r="O29" s="27"/>
     </row>
     <row r="30" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="69"/>
+      <c r="A30" s="90"/>
       <c r="B30" s="15">
         <v>6</v>
       </c>
@@ -36550,7 +36649,7 @@
       <c r="O30" s="27"/>
     </row>
     <row r="31" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="69"/>
+      <c r="A31" s="90"/>
       <c r="B31" s="15">
         <v>8</v>
       </c>
@@ -36573,7 +36672,7 @@
       <c r="O31" s="27"/>
     </row>
     <row r="32" spans="1:17" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="69"/>
+      <c r="A32" s="90"/>
       <c r="B32" s="15">
         <v>10</v>
       </c>
@@ -36596,7 +36695,7 @@
       <c r="O32" s="27"/>
     </row>
     <row r="33" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="69"/>
+      <c r="A33" s="90"/>
       <c r="B33" s="15">
         <v>12</v>
       </c>
@@ -36619,7 +36718,7 @@
       <c r="O33" s="27"/>
     </row>
     <row r="34" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="69"/>
+      <c r="A34" s="90"/>
       <c r="B34" s="15">
         <v>16</v>
       </c>
@@ -36642,12 +36741,12 @@
       <c r="O34" s="27"/>
     </row>
     <row r="35" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="69"/>
-      <c r="B35" s="77" t="s">
+      <c r="A35" s="90"/>
+      <c r="B35" s="73" t="s">
         <v>96</v>
       </c>
-      <c r="C35" s="78"/>
-      <c r="D35" s="79"/>
+      <c r="C35" s="74"/>
+      <c r="D35" s="75"/>
       <c r="E35" s="31"/>
       <c r="F35" s="31"/>
       <c r="G35" s="31"/>
@@ -36661,7 +36760,7 @@
       <c r="O35" s="27"/>
     </row>
     <row r="36" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="69"/>
+      <c r="A36" s="90"/>
       <c r="B36" s="42" t="s">
         <v>77</v>
       </c>
@@ -36685,7 +36784,7 @@
       <c r="P36" s="1"/>
     </row>
     <row r="37" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="69"/>
+      <c r="A37" s="90"/>
       <c r="B37" s="42">
         <v>1</v>
       </c>
@@ -36711,7 +36810,7 @@
       <c r="P37" s="1"/>
     </row>
     <row r="38" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="69"/>
+      <c r="A38" s="90"/>
       <c r="B38" s="42">
         <v>2</v>
       </c>
@@ -36737,7 +36836,7 @@
       <c r="P38" s="1"/>
     </row>
     <row r="39" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="69"/>
+      <c r="A39" s="90"/>
       <c r="B39" s="42">
         <v>4</v>
       </c>
@@ -36763,7 +36862,7 @@
       <c r="P39" s="1"/>
     </row>
     <row r="40" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="69"/>
+      <c r="A40" s="90"/>
       <c r="B40" s="42">
         <v>6</v>
       </c>
@@ -36789,7 +36888,7 @@
       <c r="P40" s="1"/>
     </row>
     <row r="41" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="69"/>
+      <c r="A41" s="90"/>
       <c r="B41" s="42">
         <v>8</v>
       </c>
@@ -36815,7 +36914,7 @@
       <c r="P41" s="1"/>
     </row>
     <row r="42" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="69"/>
+      <c r="A42" s="90"/>
       <c r="B42" s="42">
         <v>10</v>
       </c>
@@ -36841,7 +36940,7 @@
       <c r="P42" s="1"/>
     </row>
     <row r="43" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="69"/>
+      <c r="A43" s="90"/>
       <c r="B43" s="42">
         <v>12</v>
       </c>
@@ -36867,7 +36966,7 @@
       <c r="P43" s="1"/>
     </row>
     <row r="44" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="69"/>
+      <c r="A44" s="90"/>
       <c r="B44" s="42">
         <v>16</v>
       </c>
@@ -36893,12 +36992,12 @@
       <c r="P44" s="1"/>
     </row>
     <row r="45" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="69"/>
-      <c r="B45" s="77" t="s">
+      <c r="A45" s="90"/>
+      <c r="B45" s="73" t="s">
         <v>97</v>
       </c>
-      <c r="C45" s="78"/>
-      <c r="D45" s="79"/>
+      <c r="C45" s="74"/>
+      <c r="D45" s="75"/>
       <c r="E45" s="43"/>
       <c r="F45" s="43"/>
       <c r="G45" s="43"/>
@@ -36913,7 +37012,7 @@
       <c r="P45" s="1"/>
     </row>
     <row r="46" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="69"/>
+      <c r="A46" s="90"/>
       <c r="B46" s="42" t="s">
         <v>77</v>
       </c>
@@ -36937,7 +37036,7 @@
       <c r="P46" s="1"/>
     </row>
     <row r="47" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="69"/>
+      <c r="A47" s="90"/>
       <c r="B47" s="42">
         <v>1</v>
       </c>
@@ -36963,7 +37062,7 @@
       <c r="P47" s="1"/>
     </row>
     <row r="48" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="69"/>
+      <c r="A48" s="90"/>
       <c r="B48" s="42">
         <v>2</v>
       </c>
@@ -36989,7 +37088,7 @@
       <c r="P48" s="1"/>
     </row>
     <row r="49" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="69"/>
+      <c r="A49" s="90"/>
       <c r="B49" s="42">
         <v>4</v>
       </c>
@@ -37015,7 +37114,7 @@
       <c r="P49" s="1"/>
     </row>
     <row r="50" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="69"/>
+      <c r="A50" s="90"/>
       <c r="B50" s="42">
         <v>6</v>
       </c>
@@ -37041,7 +37140,7 @@
       <c r="P50" s="1"/>
     </row>
     <row r="51" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="69"/>
+      <c r="A51" s="90"/>
       <c r="B51" s="42">
         <v>8</v>
       </c>
@@ -37066,7 +37165,7 @@
       <c r="O51" s="1"/>
     </row>
     <row r="52" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="69"/>
+      <c r="A52" s="90"/>
       <c r="B52" s="42">
         <v>10</v>
       </c>
@@ -37091,7 +37190,7 @@
       <c r="O52" s="1"/>
     </row>
     <row r="53" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="69"/>
+      <c r="A53" s="90"/>
       <c r="B53" s="42">
         <v>12</v>
       </c>
@@ -37116,7 +37215,7 @@
       <c r="O53" s="1"/>
     </row>
     <row r="54" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="69"/>
+      <c r="A54" s="90"/>
       <c r="B54" s="42">
         <v>16</v>
       </c>
@@ -37141,55 +37240,55 @@
       <c r="O54" s="1"/>
     </row>
     <row r="55" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="69"/>
+      <c r="A55" s="90"/>
       <c r="B55" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="C55" s="73" t="s">
+      <c r="C55" s="94" t="s">
         <v>102</v>
       </c>
-      <c r="D55" s="73"/>
-      <c r="E55" s="73"/>
-      <c r="F55" s="73"/>
-      <c r="G55" s="73"/>
-      <c r="H55" s="73"/>
-      <c r="I55" s="73"/>
-      <c r="J55" s="73"/>
-      <c r="K55" s="73"/>
-      <c r="L55" s="73"/>
-      <c r="M55" s="73"/>
-      <c r="N55" s="73"/>
+      <c r="D55" s="94"/>
+      <c r="E55" s="94"/>
+      <c r="F55" s="94"/>
+      <c r="G55" s="94"/>
+      <c r="H55" s="94"/>
+      <c r="I55" s="94"/>
+      <c r="J55" s="94"/>
+      <c r="K55" s="94"/>
+      <c r="L55" s="94"/>
+      <c r="M55" s="94"/>
+      <c r="N55" s="94"/>
     </row>
     <row r="56" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="74" t="s">
+      <c r="A56" s="95" t="s">
         <v>103</v>
       </c>
-      <c r="B56" s="75"/>
-      <c r="C56" s="75"/>
-      <c r="D56" s="75"/>
-      <c r="E56" s="75"/>
-      <c r="F56" s="75"/>
-      <c r="G56" s="75"/>
-      <c r="H56" s="75"/>
-      <c r="I56" s="75"/>
-      <c r="J56" s="75"/>
-      <c r="K56" s="75"/>
-      <c r="L56" s="76"/>
-      <c r="M56" s="55" t="s">
+      <c r="B56" s="96"/>
+      <c r="C56" s="96"/>
+      <c r="D56" s="96"/>
+      <c r="E56" s="96"/>
+      <c r="F56" s="96"/>
+      <c r="G56" s="96"/>
+      <c r="H56" s="96"/>
+      <c r="I56" s="96"/>
+      <c r="J56" s="96"/>
+      <c r="K56" s="96"/>
+      <c r="L56" s="97"/>
+      <c r="M56" s="62" t="s">
         <v>90</v>
       </c>
-      <c r="N56" s="55"/>
+      <c r="N56" s="62"/>
       <c r="O56" s="30"/>
     </row>
     <row r="57" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="68" t="s">
+      <c r="A57" s="89" t="s">
         <v>85</v>
       </c>
-      <c r="B57" s="77" t="s">
+      <c r="B57" s="73" t="s">
         <v>78</v>
       </c>
-      <c r="C57" s="78"/>
-      <c r="D57" s="79"/>
+      <c r="C57" s="74"/>
+      <c r="D57" s="75"/>
       <c r="E57" s="31"/>
       <c r="F57" s="31"/>
       <c r="G57" s="31"/>
@@ -37203,7 +37302,7 @@
       <c r="O57" s="30"/>
     </row>
     <row r="58" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="69"/>
+      <c r="A58" s="90"/>
       <c r="B58" s="42" t="s">
         <v>77</v>
       </c>
@@ -37226,7 +37325,7 @@
       <c r="O58" s="30"/>
     </row>
     <row r="59" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="69"/>
+      <c r="A59" s="90"/>
       <c r="B59" s="15">
         <v>1</v>
       </c>
@@ -37249,7 +37348,7 @@
       <c r="O59" s="30"/>
     </row>
     <row r="60" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="69"/>
+      <c r="A60" s="90"/>
       <c r="B60" s="15">
         <v>2</v>
       </c>
@@ -37272,7 +37371,7 @@
       <c r="O60" s="30"/>
     </row>
     <row r="61" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="69"/>
+      <c r="A61" s="90"/>
       <c r="B61" s="15">
         <v>4</v>
       </c>
@@ -37295,7 +37394,7 @@
       <c r="O61" s="30"/>
     </row>
     <row r="62" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="69"/>
+      <c r="A62" s="90"/>
       <c r="B62" s="15">
         <v>6</v>
       </c>
@@ -37318,7 +37417,7 @@
       <c r="O62" s="30"/>
     </row>
     <row r="63" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="69"/>
+      <c r="A63" s="90"/>
       <c r="B63" s="15">
         <v>8</v>
       </c>
@@ -37341,7 +37440,7 @@
       <c r="O63" s="30"/>
     </row>
     <row r="64" spans="1:16" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="69"/>
+      <c r="A64" s="90"/>
       <c r="B64" s="15">
         <v>10</v>
       </c>
@@ -37364,7 +37463,7 @@
       <c r="O64" s="30"/>
     </row>
     <row r="65" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="69"/>
+      <c r="A65" s="90"/>
       <c r="B65" s="15">
         <v>12</v>
       </c>
@@ -37387,7 +37486,7 @@
       <c r="O65" s="30"/>
     </row>
     <row r="66" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="69"/>
+      <c r="A66" s="90"/>
       <c r="B66" s="15">
         <v>16</v>
       </c>
@@ -37410,12 +37509,12 @@
       <c r="O66" s="30"/>
     </row>
     <row r="67" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="69"/>
-      <c r="B67" s="77" t="s">
+      <c r="A67" s="90"/>
+      <c r="B67" s="73" t="s">
         <v>96</v>
       </c>
-      <c r="C67" s="78"/>
-      <c r="D67" s="79"/>
+      <c r="C67" s="74"/>
+      <c r="D67" s="75"/>
       <c r="E67" s="31"/>
       <c r="F67" s="31"/>
       <c r="G67" s="31"/>
@@ -37429,7 +37528,7 @@
       <c r="O67" s="30"/>
     </row>
     <row r="68" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="69"/>
+      <c r="A68" s="90"/>
       <c r="B68" s="42" t="s">
         <v>77</v>
       </c>
@@ -37452,7 +37551,7 @@
       <c r="O68" s="30"/>
     </row>
     <row r="69" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="69"/>
+      <c r="A69" s="90"/>
       <c r="B69" s="42">
         <v>1</v>
       </c>
@@ -37477,7 +37576,7 @@
       <c r="O69" s="30"/>
     </row>
     <row r="70" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="69"/>
+      <c r="A70" s="90"/>
       <c r="B70" s="42">
         <v>2</v>
       </c>
@@ -37502,7 +37601,7 @@
       <c r="O70" s="30"/>
     </row>
     <row r="71" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="69"/>
+      <c r="A71" s="90"/>
       <c r="B71" s="42">
         <v>4</v>
       </c>
@@ -37527,7 +37626,7 @@
       <c r="O71" s="30"/>
     </row>
     <row r="72" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="69"/>
+      <c r="A72" s="90"/>
       <c r="B72" s="42">
         <v>6</v>
       </c>
@@ -37552,7 +37651,7 @@
       <c r="O72" s="30"/>
     </row>
     <row r="73" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="69"/>
+      <c r="A73" s="90"/>
       <c r="B73" s="42">
         <v>8</v>
       </c>
@@ -37577,7 +37676,7 @@
       <c r="O73" s="30"/>
     </row>
     <row r="74" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="69"/>
+      <c r="A74" s="90"/>
       <c r="B74" s="42">
         <v>10</v>
       </c>
@@ -37602,7 +37701,7 @@
       <c r="O74" s="30"/>
     </row>
     <row r="75" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="69"/>
+      <c r="A75" s="90"/>
       <c r="B75" s="42">
         <v>12</v>
       </c>
@@ -37627,7 +37726,7 @@
       <c r="O75" s="30"/>
     </row>
     <row r="76" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="69"/>
+      <c r="A76" s="90"/>
       <c r="B76" s="42">
         <v>16</v>
       </c>
@@ -37652,12 +37751,12 @@
       <c r="O76" s="30"/>
     </row>
     <row r="77" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="69"/>
-      <c r="B77" s="77" t="s">
+      <c r="A77" s="90"/>
+      <c r="B77" s="73" t="s">
         <v>97</v>
       </c>
-      <c r="C77" s="78"/>
-      <c r="D77" s="79"/>
+      <c r="C77" s="74"/>
+      <c r="D77" s="75"/>
       <c r="E77" s="43"/>
       <c r="F77" s="43"/>
       <c r="G77" s="43"/>
@@ -37671,7 +37770,7 @@
       <c r="O77" s="30"/>
     </row>
     <row r="78" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="69"/>
+      <c r="A78" s="90"/>
       <c r="B78" s="42" t="s">
         <v>77</v>
       </c>
@@ -37694,7 +37793,7 @@
       <c r="O78" s="30"/>
     </row>
     <row r="79" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="69"/>
+      <c r="A79" s="90"/>
       <c r="B79" s="42">
         <v>1</v>
       </c>
@@ -37719,7 +37818,7 @@
       <c r="O79" s="30"/>
     </row>
     <row r="80" spans="1:15" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="69"/>
+      <c r="A80" s="90"/>
       <c r="B80" s="42">
         <v>2</v>
       </c>
@@ -37744,7 +37843,7 @@
       <c r="O80" s="30"/>
     </row>
     <row r="81" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="69"/>
+      <c r="A81" s="90"/>
       <c r="B81" s="42">
         <v>4</v>
       </c>
@@ -37769,7 +37868,7 @@
       <c r="O81" s="30"/>
     </row>
     <row r="82" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="69"/>
+      <c r="A82" s="90"/>
       <c r="B82" s="42">
         <v>6</v>
       </c>
@@ -37794,7 +37893,7 @@
       <c r="O82" s="30"/>
     </row>
     <row r="83" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="69"/>
+      <c r="A83" s="90"/>
       <c r="B83" s="42">
         <v>8</v>
       </c>
@@ -37819,7 +37918,7 @@
       <c r="O83" s="30"/>
     </row>
     <row r="84" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="69"/>
+      <c r="A84" s="90"/>
       <c r="B84" s="42">
         <v>10</v>
       </c>
@@ -37844,7 +37943,7 @@
       <c r="O84" s="30"/>
     </row>
     <row r="85" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="69"/>
+      <c r="A85" s="90"/>
       <c r="B85" s="42">
         <v>12</v>
       </c>
@@ -37869,7 +37968,7 @@
       <c r="O85" s="30"/>
     </row>
     <row r="86" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="69"/>
+      <c r="A86" s="90"/>
       <c r="B86" s="42">
         <v>16</v>
       </c>
@@ -37894,61 +37993,61 @@
       <c r="O86" s="30"/>
     </row>
     <row r="87" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="69"/>
+      <c r="A87" s="90"/>
       <c r="B87" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="C87" s="70" t="s">
+      <c r="C87" s="91" t="s">
         <v>106</v>
       </c>
-      <c r="D87" s="71"/>
-      <c r="E87" s="71"/>
-      <c r="F87" s="71"/>
-      <c r="G87" s="71"/>
-      <c r="H87" s="71"/>
-      <c r="I87" s="71"/>
-      <c r="J87" s="71"/>
-      <c r="K87" s="71"/>
-      <c r="L87" s="71"/>
-      <c r="M87" s="71"/>
-      <c r="N87" s="72"/>
+      <c r="D87" s="92"/>
+      <c r="E87" s="92"/>
+      <c r="F87" s="92"/>
+      <c r="G87" s="92"/>
+      <c r="H87" s="92"/>
+      <c r="I87" s="92"/>
+      <c r="J87" s="92"/>
+      <c r="K87" s="92"/>
+      <c r="L87" s="92"/>
+      <c r="M87" s="92"/>
+      <c r="N87" s="93"/>
     </row>
     <row r="88" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="52" t="s">
+      <c r="A88" s="59" t="s">
         <v>107</v>
       </c>
-      <c r="B88" s="53"/>
-      <c r="C88" s="53"/>
-      <c r="D88" s="53"/>
-      <c r="E88" s="53"/>
-      <c r="F88" s="53"/>
-      <c r="G88" s="53"/>
-      <c r="H88" s="53"/>
-      <c r="I88" s="53"/>
-      <c r="J88" s="53"/>
-      <c r="K88" s="53"/>
-      <c r="L88" s="53"/>
-      <c r="M88" s="53"/>
-      <c r="N88" s="53"/>
-      <c r="O88" s="65" t="s">
+      <c r="B88" s="60"/>
+      <c r="C88" s="60"/>
+      <c r="D88" s="60"/>
+      <c r="E88" s="60"/>
+      <c r="F88" s="60"/>
+      <c r="G88" s="60"/>
+      <c r="H88" s="60"/>
+      <c r="I88" s="60"/>
+      <c r="J88" s="60"/>
+      <c r="K88" s="60"/>
+      <c r="L88" s="60"/>
+      <c r="M88" s="60"/>
+      <c r="N88" s="60"/>
+      <c r="O88" s="86" t="s">
         <v>112</v>
       </c>
-      <c r="P88" s="66"/>
-      <c r="Q88" s="66"/>
-      <c r="R88" s="66"/>
-      <c r="S88" s="66"/>
-      <c r="T88" s="67"/>
+      <c r="P88" s="87"/>
+      <c r="Q88" s="87"/>
+      <c r="R88" s="87"/>
+      <c r="S88" s="87"/>
+      <c r="T88" s="88"/>
     </row>
     <row r="89" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="82" t="s">
+      <c r="A89" s="81" t="s">
         <v>85</v>
       </c>
-      <c r="B89" s="77" t="s">
+      <c r="B89" s="73" t="s">
         <v>78</v>
       </c>
-      <c r="C89" s="78"/>
-      <c r="D89" s="78"/>
-      <c r="E89" s="79"/>
+      <c r="C89" s="74"/>
+      <c r="D89" s="74"/>
+      <c r="E89" s="75"/>
       <c r="F89" s="31"/>
       <c r="G89" s="31"/>
       <c r="H89" s="31"/>
@@ -37966,7 +38065,7 @@
       <c r="T89" s="31"/>
     </row>
     <row r="90" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="82"/>
+      <c r="A90" s="81"/>
       <c r="B90" s="42" t="s">
         <v>77</v>
       </c>
@@ -37996,7 +38095,7 @@
       <c r="T90" s="31"/>
     </row>
     <row r="91" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="82"/>
+      <c r="A91" s="81"/>
       <c r="B91" s="15">
         <v>1</v>
       </c>
@@ -38026,7 +38125,7 @@
       <c r="T91" s="31"/>
     </row>
     <row r="92" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="82"/>
+      <c r="A92" s="81"/>
       <c r="B92" s="15">
         <v>2</v>
       </c>
@@ -38056,7 +38155,7 @@
       <c r="T92" s="31"/>
     </row>
     <row r="93" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="82"/>
+      <c r="A93" s="81"/>
       <c r="B93" s="15">
         <v>4</v>
       </c>
@@ -38086,7 +38185,7 @@
       <c r="T93" s="31"/>
     </row>
     <row r="94" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="82"/>
+      <c r="A94" s="81"/>
       <c r="B94" s="15">
         <v>6</v>
       </c>
@@ -38116,7 +38215,7 @@
       <c r="T94" s="31"/>
     </row>
     <row r="95" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="82"/>
+      <c r="A95" s="81"/>
       <c r="B95" s="15">
         <v>8</v>
       </c>
@@ -38146,7 +38245,7 @@
       <c r="T95" s="31"/>
     </row>
     <row r="96" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="82"/>
+      <c r="A96" s="81"/>
       <c r="B96" s="15">
         <v>10</v>
       </c>
@@ -38176,7 +38275,7 @@
       <c r="T96" s="31"/>
     </row>
     <row r="97" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="82"/>
+      <c r="A97" s="81"/>
       <c r="B97" s="15">
         <v>12</v>
       </c>
@@ -38206,7 +38305,7 @@
       <c r="T97" s="31"/>
     </row>
     <row r="98" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="82"/>
+      <c r="A98" s="81"/>
       <c r="B98" s="15">
         <v>16</v>
       </c>
@@ -38236,13 +38335,13 @@
       <c r="T98" s="31"/>
     </row>
     <row r="99" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="82"/>
-      <c r="B99" s="77" t="s">
+      <c r="A99" s="81"/>
+      <c r="B99" s="73" t="s">
         <v>96</v>
       </c>
-      <c r="C99" s="78"/>
-      <c r="D99" s="78"/>
-      <c r="E99" s="79"/>
+      <c r="C99" s="74"/>
+      <c r="D99" s="74"/>
+      <c r="E99" s="75"/>
       <c r="F99" s="31"/>
       <c r="G99" s="31"/>
       <c r="H99" s="31"/>
@@ -38260,7 +38359,7 @@
       <c r="T99" s="31"/>
     </row>
     <row r="100" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="82"/>
+      <c r="A100" s="81"/>
       <c r="B100" s="42" t="s">
         <v>77</v>
       </c>
@@ -38290,7 +38389,7 @@
       <c r="T100" s="16"/>
     </row>
     <row r="101" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="82"/>
+      <c r="A101" s="81"/>
       <c r="B101" s="42">
         <v>1</v>
       </c>
@@ -38323,7 +38422,7 @@
       <c r="T101" s="16"/>
     </row>
     <row r="102" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="82"/>
+      <c r="A102" s="81"/>
       <c r="B102" s="42">
         <v>2</v>
       </c>
@@ -38356,7 +38455,7 @@
       <c r="T102" s="16"/>
     </row>
     <row r="103" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="82"/>
+      <c r="A103" s="81"/>
       <c r="B103" s="42">
         <v>4</v>
       </c>
@@ -38389,7 +38488,7 @@
       <c r="T103" s="16"/>
     </row>
     <row r="104" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="82"/>
+      <c r="A104" s="81"/>
       <c r="B104" s="42">
         <v>6</v>
       </c>
@@ -38422,7 +38521,7 @@
       <c r="T104" s="16"/>
     </row>
     <row r="105" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="82"/>
+      <c r="A105" s="81"/>
       <c r="B105" s="42">
         <v>8</v>
       </c>
@@ -38455,7 +38554,7 @@
       <c r="T105" s="16"/>
     </row>
     <row r="106" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="82"/>
+      <c r="A106" s="81"/>
       <c r="B106" s="42">
         <v>10</v>
       </c>
@@ -38488,7 +38587,7 @@
       <c r="T106" s="16"/>
     </row>
     <row r="107" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="82"/>
+      <c r="A107" s="81"/>
       <c r="B107" s="42">
         <v>12</v>
       </c>
@@ -38521,7 +38620,7 @@
       <c r="T107" s="16"/>
     </row>
     <row r="108" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="82"/>
+      <c r="A108" s="81"/>
       <c r="B108" s="42">
         <v>16</v>
       </c>
@@ -38554,13 +38653,13 @@
       <c r="T108" s="16"/>
     </row>
     <row r="109" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="82"/>
-      <c r="B109" s="77" t="s">
+      <c r="A109" s="81"/>
+      <c r="B109" s="73" t="s">
         <v>97</v>
       </c>
-      <c r="C109" s="78"/>
-      <c r="D109" s="78"/>
-      <c r="E109" s="79"/>
+      <c r="C109" s="74"/>
+      <c r="D109" s="74"/>
+      <c r="E109" s="75"/>
       <c r="F109" s="43"/>
       <c r="G109" s="16"/>
       <c r="H109" s="16"/>
@@ -38578,7 +38677,7 @@
       <c r="T109" s="16"/>
     </row>
     <row r="110" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="82"/>
+      <c r="A110" s="81"/>
       <c r="B110" s="42" t="s">
         <v>77</v>
       </c>
@@ -38608,7 +38707,7 @@
       <c r="T110" s="16"/>
     </row>
     <row r="111" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="82"/>
+      <c r="A111" s="81"/>
       <c r="B111" s="42">
         <v>1</v>
       </c>
@@ -38641,7 +38740,7 @@
       <c r="T111" s="16"/>
     </row>
     <row r="112" spans="1:20" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="82"/>
+      <c r="A112" s="81"/>
       <c r="B112" s="42">
         <v>2</v>
       </c>
@@ -38674,7 +38773,7 @@
       <c r="T112" s="16"/>
     </row>
     <row r="113" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="82"/>
+      <c r="A113" s="81"/>
       <c r="B113" s="42">
         <v>4</v>
       </c>
@@ -38707,7 +38806,7 @@
       <c r="T113" s="16"/>
     </row>
     <row r="114" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="82"/>
+      <c r="A114" s="81"/>
       <c r="B114" s="42">
         <v>6</v>
       </c>
@@ -38740,7 +38839,7 @@
       <c r="T114" s="16"/>
     </row>
     <row r="115" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="82"/>
+      <c r="A115" s="81"/>
       <c r="B115" s="42">
         <v>8</v>
       </c>
@@ -38773,7 +38872,7 @@
       <c r="T115" s="16"/>
     </row>
     <row r="116" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="82"/>
+      <c r="A116" s="81"/>
       <c r="B116" s="42">
         <v>10</v>
       </c>
@@ -38806,7 +38905,7 @@
       <c r="T116" s="16"/>
     </row>
     <row r="117" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="82"/>
+      <c r="A117" s="81"/>
       <c r="B117" s="42">
         <v>12</v>
       </c>
@@ -38839,7 +38938,7 @@
       <c r="T117" s="31"/>
     </row>
     <row r="118" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="82"/>
+      <c r="A118" s="81"/>
       <c r="B118" s="42">
         <v>16</v>
       </c>
@@ -38872,41 +38971,41 @@
       <c r="T118" s="31"/>
     </row>
     <row r="119" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="82"/>
+      <c r="A119" s="81"/>
       <c r="B119" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="C119" s="81" t="s">
+      <c r="C119" s="78" t="s">
         <v>113</v>
       </c>
-      <c r="D119" s="86"/>
-      <c r="E119" s="86"/>
-      <c r="F119" s="86"/>
-      <c r="G119" s="86"/>
-      <c r="H119" s="86"/>
-      <c r="I119" s="86"/>
-      <c r="J119" s="86"/>
-      <c r="K119" s="86"/>
-      <c r="L119" s="86"/>
-      <c r="M119" s="86"/>
-      <c r="N119" s="86"/>
-      <c r="O119" s="86"/>
-      <c r="P119" s="86"/>
-      <c r="Q119" s="86"/>
-      <c r="R119" s="86"/>
-      <c r="S119" s="86"/>
-      <c r="T119" s="87"/>
+      <c r="D119" s="79"/>
+      <c r="E119" s="79"/>
+      <c r="F119" s="79"/>
+      <c r="G119" s="79"/>
+      <c r="H119" s="79"/>
+      <c r="I119" s="79"/>
+      <c r="J119" s="79"/>
+      <c r="K119" s="79"/>
+      <c r="L119" s="79"/>
+      <c r="M119" s="79"/>
+      <c r="N119" s="79"/>
+      <c r="O119" s="79"/>
+      <c r="P119" s="79"/>
+      <c r="Q119" s="79"/>
+      <c r="R119" s="79"/>
+      <c r="S119" s="79"/>
+      <c r="T119" s="80"/>
     </row>
     <row r="120" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="88" t="s">
-        <v>116</v>
-      </c>
-      <c r="B120" s="77" t="s">
+      <c r="A120" s="76" t="s">
+        <v>115</v>
+      </c>
+      <c r="B120" s="73" t="s">
         <v>78</v>
       </c>
-      <c r="C120" s="78"/>
-      <c r="D120" s="78"/>
-      <c r="E120" s="79"/>
+      <c r="C120" s="74"/>
+      <c r="D120" s="74"/>
+      <c r="E120" s="75"/>
       <c r="F120" s="31"/>
       <c r="G120" s="31"/>
       <c r="H120" s="31"/>
@@ -38933,7 +39032,7 @@
       <c r="AC120" s="31"/>
     </row>
     <row r="121" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="89"/>
+      <c r="A121" s="77"/>
       <c r="B121" s="42" t="s">
         <v>77</v>
       </c>
@@ -38972,18 +39071,18 @@
       <c r="AC121" s="31"/>
     </row>
     <row r="122" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="89"/>
+      <c r="A122" s="77"/>
       <c r="B122" s="15">
         <v>1</v>
       </c>
       <c r="C122" s="24">
-        <v>9725</v>
+        <v>5381</v>
       </c>
       <c r="D122" s="24">
-        <v>76160</v>
+        <v>41829</v>
       </c>
       <c r="E122" s="24">
-        <v>257265</v>
+        <v>142216</v>
       </c>
       <c r="F122" s="31"/>
       <c r="G122" s="31"/>
@@ -39011,18 +39110,18 @@
       <c r="AC122" s="31"/>
     </row>
     <row r="123" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="89"/>
+      <c r="A123" s="77"/>
       <c r="B123" s="15">
         <v>2</v>
       </c>
       <c r="C123" s="24">
-        <v>5498</v>
+        <v>2737</v>
       </c>
       <c r="D123" s="24">
-        <v>39071</v>
+        <v>21202</v>
       </c>
       <c r="E123" s="24">
-        <v>130577</v>
+        <v>70771</v>
       </c>
       <c r="F123" s="31"/>
       <c r="G123" s="31"/>
@@ -39050,18 +39149,18 @@
       <c r="AC123" s="31"/>
     </row>
     <row r="124" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="89"/>
+      <c r="A124" s="77"/>
       <c r="B124" s="15">
         <v>4</v>
       </c>
       <c r="C124" s="24">
-        <v>3076</v>
+        <v>1427</v>
       </c>
       <c r="D124" s="24">
-        <v>20102</v>
+        <v>11078</v>
       </c>
       <c r="E124" s="24">
-        <v>66384</v>
+        <v>36194</v>
       </c>
       <c r="F124" s="31"/>
       <c r="G124" s="31"/>
@@ -39089,18 +39188,18 @@
       <c r="AC124" s="31"/>
     </row>
     <row r="125" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="89"/>
+      <c r="A125" s="77"/>
       <c r="B125" s="15">
         <v>6</v>
       </c>
       <c r="C125" s="24">
-        <v>2342</v>
+        <v>1042</v>
       </c>
       <c r="D125" s="24">
-        <v>14063</v>
+        <v>7787</v>
       </c>
       <c r="E125" s="24">
-        <v>46005</v>
+        <v>25435</v>
       </c>
       <c r="F125" s="31"/>
       <c r="G125" s="31"/>
@@ -39128,18 +39227,18 @@
       <c r="AC125" s="31"/>
     </row>
     <row r="126" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="89"/>
+      <c r="A126" s="77"/>
       <c r="B126" s="15">
         <v>8</v>
       </c>
       <c r="C126" s="40">
-        <v>1880</v>
+        <v>818</v>
       </c>
       <c r="D126" s="24">
-        <v>11690</v>
+        <v>6260</v>
       </c>
       <c r="E126" s="24">
-        <v>35587</v>
+        <v>19632</v>
       </c>
       <c r="F126" s="31"/>
       <c r="G126" s="31"/>
@@ -39167,18 +39266,18 @@
       <c r="AC126" s="31"/>
     </row>
     <row r="127" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="89"/>
+      <c r="A127" s="77"/>
       <c r="B127" s="15">
         <v>10</v>
       </c>
       <c r="C127" s="40">
-        <v>1650</v>
+        <v>682</v>
       </c>
       <c r="D127" s="24">
-        <v>10161</v>
+        <v>5372</v>
       </c>
       <c r="E127" s="24">
-        <v>29914</v>
+        <v>16476</v>
       </c>
       <c r="F127" s="31"/>
       <c r="G127" s="31"/>
@@ -39206,18 +39305,18 @@
       <c r="AC127" s="31"/>
     </row>
     <row r="128" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="89"/>
+      <c r="A128" s="77"/>
       <c r="B128" s="15">
         <v>12</v>
       </c>
       <c r="C128" s="40">
-        <v>1435</v>
+        <v>592</v>
       </c>
       <c r="D128" s="24">
-        <v>8034</v>
+        <v>4574</v>
       </c>
       <c r="E128" s="24">
-        <v>25229</v>
+        <v>14220</v>
       </c>
       <c r="F128" s="31"/>
       <c r="G128" s="31"/>
@@ -39245,18 +39344,18 @@
       <c r="AC128" s="31"/>
     </row>
     <row r="129" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="89"/>
+      <c r="A129" s="77"/>
       <c r="B129" s="15">
         <v>14</v>
       </c>
       <c r="C129" s="40">
-        <v>1318</v>
+        <v>550</v>
       </c>
       <c r="D129" s="24">
-        <v>7301</v>
+        <v>4295</v>
       </c>
       <c r="E129" s="24">
-        <v>23660</v>
+        <v>13252</v>
       </c>
       <c r="F129" s="31"/>
       <c r="G129" s="31"/>
@@ -39284,18 +39383,18 @@
       <c r="AC129" s="31"/>
     </row>
     <row r="130" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="89"/>
+      <c r="A130" s="77"/>
       <c r="B130" s="15">
         <v>16</v>
       </c>
       <c r="C130" s="40">
-        <v>1223</v>
+        <v>527</v>
       </c>
       <c r="D130" s="24">
-        <v>6821</v>
+        <v>3969</v>
       </c>
       <c r="E130" s="24">
-        <v>21062</v>
+        <v>12007</v>
       </c>
       <c r="F130" s="31"/>
       <c r="G130" s="31"/>
@@ -39323,18 +39422,18 @@
       <c r="AC130" s="31"/>
     </row>
     <row r="131" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="89"/>
+      <c r="A131" s="77"/>
       <c r="B131" s="15">
         <v>18</v>
       </c>
       <c r="C131" s="40">
-        <v>1176</v>
+        <v>497</v>
       </c>
       <c r="D131" s="24">
-        <v>6201</v>
+        <v>3709</v>
       </c>
       <c r="E131" s="24">
-        <v>20637</v>
+        <v>11351</v>
       </c>
       <c r="F131" s="31"/>
       <c r="G131" s="31"/>
@@ -39362,18 +39461,18 @@
       <c r="AC131" s="31"/>
     </row>
     <row r="132" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="89"/>
+      <c r="A132" s="77"/>
       <c r="B132" s="15">
         <v>20</v>
       </c>
       <c r="C132" s="40">
-        <v>1067</v>
+        <v>479</v>
       </c>
       <c r="D132" s="24">
-        <v>6056</v>
+        <v>3554</v>
       </c>
       <c r="E132" s="24">
-        <v>18311</v>
+        <v>10884</v>
       </c>
       <c r="F132" s="31"/>
       <c r="G132" s="31"/>
@@ -39401,18 +39500,18 @@
       <c r="AC132" s="31"/>
     </row>
     <row r="133" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="89"/>
+      <c r="A133" s="77"/>
       <c r="B133" s="49">
         <v>40</v>
       </c>
       <c r="C133" s="50">
-        <v>1201</v>
+        <v>518</v>
       </c>
       <c r="D133" s="51">
-        <v>6846</v>
+        <v>3697</v>
       </c>
       <c r="E133" s="51">
-        <v>20629</v>
+        <v>11163</v>
       </c>
       <c r="F133" s="31"/>
       <c r="G133" s="31"/>
@@ -39440,13 +39539,13 @@
       <c r="AC133" s="31"/>
     </row>
     <row r="134" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="89"/>
-      <c r="B134" s="77" t="s">
+      <c r="A134" s="77"/>
+      <c r="B134" s="73" t="s">
         <v>96</v>
       </c>
-      <c r="C134" s="78"/>
-      <c r="D134" s="78"/>
-      <c r="E134" s="79"/>
+      <c r="C134" s="74"/>
+      <c r="D134" s="74"/>
+      <c r="E134" s="75"/>
       <c r="F134" s="31"/>
       <c r="G134" s="31"/>
       <c r="H134" s="31"/>
@@ -39473,7 +39572,7 @@
       <c r="AC134" s="31"/>
     </row>
     <row r="135" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="89"/>
+      <c r="A135" s="77"/>
       <c r="B135" s="42" t="s">
         <v>77</v>
       </c>
@@ -39512,7 +39611,7 @@
       <c r="AC135" s="16"/>
     </row>
     <row r="136" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="89"/>
+      <c r="A136" s="77"/>
       <c r="B136" s="15">
         <v>1</v>
       </c>
@@ -39554,21 +39653,21 @@
       <c r="AC136" s="16"/>
     </row>
     <row r="137" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="89"/>
+      <c r="A137" s="77"/>
       <c r="B137" s="15">
         <v>2</v>
       </c>
       <c r="C137" s="40">
         <f>ROUND(C122/C123,5)</f>
-        <v>1.7688299999999999</v>
+        <v>1.9660200000000001</v>
       </c>
       <c r="D137" s="40">
         <f>ROUND(D122/D123,5)</f>
-        <v>1.9492700000000001</v>
+        <v>1.97288</v>
       </c>
       <c r="E137" s="40">
         <f>ROUND(E122/E123,5)</f>
-        <v>1.9702200000000001</v>
+        <v>2.0095200000000002</v>
       </c>
       <c r="F137" s="16"/>
       <c r="G137" s="16"/>
@@ -39596,21 +39695,21 @@
       <c r="AC137" s="16"/>
     </row>
     <row r="138" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="89"/>
+      <c r="A138" s="77"/>
       <c r="B138" s="15">
         <v>4</v>
       </c>
       <c r="C138" s="40">
         <f>ROUND(C122/C124,5)</f>
-        <v>3.1615700000000002</v>
+        <v>3.7708499999999998</v>
       </c>
       <c r="D138" s="40">
         <f>ROUND(D122/D124,5)</f>
-        <v>3.7886799999999998</v>
+        <v>3.7758600000000002</v>
       </c>
       <c r="E138" s="40">
         <f>ROUND(E122/E124,5)</f>
-        <v>3.87541</v>
+        <v>3.9292699999999998</v>
       </c>
       <c r="F138" s="16"/>
       <c r="G138" s="16"/>
@@ -39638,21 +39737,21 @@
       <c r="AC138" s="16"/>
     </row>
     <row r="139" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="89"/>
+      <c r="A139" s="77"/>
       <c r="B139" s="15">
         <v>6</v>
       </c>
       <c r="C139" s="40">
         <f>ROUND(C122/C125,5)</f>
-        <v>4.1524299999999998</v>
+        <v>5.16411</v>
       </c>
       <c r="D139" s="40">
         <f>ROUND(D122/D125,5)</f>
-        <v>5.4156300000000002</v>
+        <v>5.3716499999999998</v>
       </c>
       <c r="E139" s="40">
         <f>ROUND(E122/E125,5)</f>
-        <v>5.5921099999999999</v>
+        <v>5.5913500000000003</v>
       </c>
       <c r="F139" s="16"/>
       <c r="G139" s="16"/>
@@ -39680,21 +39779,21 @@
       <c r="AC139" s="16"/>
     </row>
     <row r="140" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="89"/>
+      <c r="A140" s="77"/>
       <c r="B140" s="15">
         <v>8</v>
       </c>
       <c r="C140" s="40">
         <f>ROUND(C122/C126,5)</f>
-        <v>5.1728699999999996</v>
+        <v>6.5782400000000001</v>
       </c>
       <c r="D140" s="40">
         <f>ROUND(D122/D126,5)</f>
-        <v>6.5149699999999999</v>
+        <v>6.6819499999999996</v>
       </c>
       <c r="E140" s="40">
         <f>ROUND(E122/E126,5)</f>
-        <v>7.2291800000000004</v>
+        <v>7.2440899999999999</v>
       </c>
       <c r="F140" s="16"/>
       <c r="G140" s="16"/>
@@ -39722,21 +39821,21 @@
       <c r="AC140" s="16"/>
     </row>
     <row r="141" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="89"/>
+      <c r="A141" s="77"/>
       <c r="B141" s="15">
         <v>10</v>
       </c>
       <c r="C141" s="40">
         <f>ROUND(C122/C127,5)</f>
-        <v>5.8939399999999997</v>
+        <v>7.8900300000000003</v>
       </c>
       <c r="D141" s="40">
         <f>ROUND(D122/D127,5)</f>
-        <v>7.49533</v>
+        <v>7.7864899999999997</v>
       </c>
       <c r="E141" s="40">
         <f>ROUND(E122/E127,5)</f>
-        <v>8.6001499999999993</v>
+        <v>8.63171</v>
       </c>
       <c r="F141" s="16"/>
       <c r="G141" s="16"/>
@@ -39764,21 +39863,21 @@
       <c r="AC141" s="16"/>
     </row>
     <row r="142" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="89"/>
+      <c r="A142" s="77"/>
       <c r="B142" s="15">
         <v>12</v>
       </c>
       <c r="C142" s="40">
         <f>ROUND(C122/C128,5)</f>
-        <v>6.7770000000000001</v>
+        <v>9.0895299999999999</v>
       </c>
       <c r="D142" s="40">
         <f>ROUND(D122/D128,5)</f>
-        <v>9.4797100000000007</v>
+        <v>9.1449499999999997</v>
       </c>
       <c r="E142" s="40">
         <f>ROUND(E122/E128,5)</f>
-        <v>10.197190000000001</v>
+        <v>10.00113</v>
       </c>
       <c r="F142" s="16"/>
       <c r="G142" s="16"/>
@@ -39806,21 +39905,21 @@
       <c r="AC142" s="16"/>
     </row>
     <row r="143" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="89"/>
+      <c r="A143" s="77"/>
       <c r="B143" s="15">
         <v>14</v>
       </c>
       <c r="C143" s="40">
-        <f t="shared" ref="C143:E147" si="7">ROUND(C$122/C129,5)</f>
-        <v>7.3785999999999996</v>
+        <f>ROUND(C$122/C129,5)</f>
+        <v>9.7836400000000001</v>
       </c>
       <c r="D143" s="40">
-        <f t="shared" si="7"/>
-        <v>10.43145</v>
+        <f t="shared" ref="C143:E147" si="7">ROUND(D$122/D129,5)</f>
+        <v>9.7390000000000008</v>
       </c>
       <c r="E143" s="40">
         <f t="shared" si="7"/>
-        <v>10.873419999999999</v>
+        <v>10.73166</v>
       </c>
       <c r="F143" s="16"/>
       <c r="G143" s="16"/>
@@ -39848,21 +39947,21 @@
       <c r="AC143" s="16"/>
     </row>
     <row r="144" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="89"/>
+      <c r="A144" s="77"/>
       <c r="B144" s="15">
         <v>16</v>
       </c>
       <c r="C144" s="40">
         <f t="shared" si="7"/>
-        <v>7.9517600000000002</v>
+        <v>10.21063</v>
       </c>
       <c r="D144" s="40">
         <f t="shared" si="7"/>
-        <v>11.165520000000001</v>
+        <v>10.538930000000001</v>
       </c>
       <c r="E144" s="40">
         <f t="shared" si="7"/>
-        <v>12.214650000000001</v>
+        <v>11.84442</v>
       </c>
       <c r="F144" s="31"/>
       <c r="G144" s="31"/>
@@ -39890,21 +39989,21 @@
       <c r="AC144" s="31"/>
     </row>
     <row r="145" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="89"/>
+      <c r="A145" s="77"/>
       <c r="B145" s="15">
         <v>18</v>
       </c>
       <c r="C145" s="40">
         <f t="shared" si="7"/>
-        <v>8.2695600000000002</v>
+        <v>10.82696</v>
       </c>
       <c r="D145" s="40">
         <f t="shared" si="7"/>
-        <v>12.281890000000001</v>
+        <v>11.277699999999999</v>
       </c>
       <c r="E145" s="40">
         <f t="shared" si="7"/>
-        <v>12.466200000000001</v>
+        <v>12.52894</v>
       </c>
       <c r="F145" s="16"/>
       <c r="G145" s="16"/>
@@ -39932,21 +40031,21 @@
       <c r="AC145" s="16"/>
     </row>
     <row r="146" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="89"/>
+      <c r="A146" s="77"/>
       <c r="B146" s="15">
         <v>20</v>
       </c>
       <c r="C146" s="40">
         <f t="shared" si="7"/>
-        <v>9.1143400000000003</v>
+        <v>11.23382</v>
       </c>
       <c r="D146" s="40">
         <f t="shared" si="7"/>
-        <v>12.57596</v>
+        <v>11.76956</v>
       </c>
       <c r="E146" s="40">
         <f t="shared" si="7"/>
-        <v>14.04975</v>
+        <v>13.066520000000001</v>
       </c>
       <c r="F146" s="16"/>
       <c r="G146" s="16"/>
@@ -39974,21 +40073,21 @@
       <c r="AC146" s="16"/>
     </row>
     <row r="147" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="89"/>
+      <c r="A147" s="77"/>
       <c r="B147" s="49">
         <v>40</v>
       </c>
       <c r="C147" s="50">
         <f t="shared" si="7"/>
-        <v>8.0974199999999996</v>
+        <v>10.388030000000001</v>
       </c>
       <c r="D147" s="50">
         <f t="shared" si="7"/>
-        <v>11.124739999999999</v>
+        <v>11.314310000000001</v>
       </c>
       <c r="E147" s="50">
         <f t="shared" si="7"/>
-        <v>12.47104</v>
+        <v>12.739940000000001</v>
       </c>
       <c r="F147" s="16"/>
       <c r="G147" s="16"/>
@@ -40016,13 +40115,13 @@
       <c r="AC147" s="16"/>
     </row>
     <row r="148" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="89"/>
-      <c r="B148" s="77" t="s">
+      <c r="A148" s="77"/>
+      <c r="B148" s="73" t="s">
         <v>97</v>
       </c>
-      <c r="C148" s="78"/>
-      <c r="D148" s="78"/>
-      <c r="E148" s="79"/>
+      <c r="C148" s="74"/>
+      <c r="D148" s="74"/>
+      <c r="E148" s="75"/>
       <c r="F148" s="16"/>
       <c r="G148" s="16"/>
       <c r="H148" s="16"/>
@@ -40049,7 +40148,7 @@
       <c r="AC148" s="16"/>
     </row>
     <row r="149" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="89"/>
+      <c r="A149" s="77"/>
       <c r="B149" s="42" t="s">
         <v>77</v>
       </c>
@@ -40088,16 +40187,16 @@
       <c r="AC149" s="16"/>
     </row>
     <row r="150" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="89"/>
+      <c r="A150" s="77"/>
       <c r="B150" s="15">
         <v>1</v>
       </c>
       <c r="C150" s="40">
-        <f t="shared" ref="C150:C161" si="8">ROUND(C136/$B136,5)</f>
+        <f t="shared" ref="C150:E161" si="8">ROUND(C136/$B136,5)</f>
         <v>1</v>
       </c>
       <c r="D150" s="40">
-        <f t="shared" ref="D150:E154" si="9">D136/$B136</f>
+        <f t="shared" ref="D150:E150" si="9">D136/$B136</f>
         <v>1</v>
       </c>
       <c r="E150" s="40">
@@ -40130,21 +40229,21 @@
       <c r="AC150" s="16"/>
     </row>
     <row r="151" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="89"/>
+      <c r="A151" s="77"/>
       <c r="B151" s="15">
         <v>2</v>
       </c>
       <c r="C151" s="40">
         <f t="shared" si="8"/>
-        <v>0.88441999999999998</v>
+        <v>0.98301000000000005</v>
       </c>
       <c r="D151" s="40">
-        <f t="shared" si="9"/>
-        <v>0.97463500000000003</v>
+        <f t="shared" si="8"/>
+        <v>0.98643999999999998</v>
       </c>
       <c r="E151" s="40">
-        <f t="shared" si="9"/>
-        <v>0.98511000000000004</v>
+        <f t="shared" si="8"/>
+        <v>1.0047600000000001</v>
       </c>
       <c r="F151" s="16"/>
       <c r="G151" s="16"/>
@@ -40172,21 +40271,21 @@
       <c r="AC151" s="16"/>
     </row>
     <row r="152" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="89"/>
+      <c r="A152" s="77"/>
       <c r="B152" s="15">
         <v>4</v>
       </c>
       <c r="C152" s="40">
         <f t="shared" si="8"/>
-        <v>0.79039000000000004</v>
+        <v>0.94271000000000005</v>
       </c>
       <c r="D152" s="40">
-        <f t="shared" si="9"/>
-        <v>0.94716999999999996</v>
+        <f>ROUND(D138/$B138,5)</f>
+        <v>0.94396999999999998</v>
       </c>
       <c r="E152" s="40">
-        <f t="shared" si="9"/>
-        <v>0.96885250000000001</v>
+        <f t="shared" si="8"/>
+        <v>0.98231999999999997</v>
       </c>
       <c r="F152" s="16"/>
       <c r="G152" s="16"/>
@@ -40214,21 +40313,21 @@
       <c r="AC152" s="16"/>
     </row>
     <row r="153" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="89"/>
+      <c r="A153" s="77"/>
       <c r="B153" s="15">
         <v>6</v>
       </c>
       <c r="C153" s="40">
         <f t="shared" si="8"/>
-        <v>0.69206999999999996</v>
+        <v>0.86068999999999996</v>
       </c>
       <c r="D153" s="40">
-        <f t="shared" si="9"/>
-        <v>0.90260499999999999</v>
+        <f t="shared" si="8"/>
+        <v>0.89527999999999996</v>
       </c>
       <c r="E153" s="40">
-        <f t="shared" si="9"/>
-        <v>0.93201833333333328</v>
+        <f t="shared" si="8"/>
+        <v>0.93189</v>
       </c>
       <c r="F153" s="16"/>
       <c r="G153" s="16"/>
@@ -40256,21 +40355,21 @@
       <c r="AC153" s="16"/>
     </row>
     <row r="154" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="89"/>
+      <c r="A154" s="77"/>
       <c r="B154" s="15">
         <v>8</v>
       </c>
       <c r="C154" s="40">
         <f t="shared" si="8"/>
-        <v>0.64661000000000002</v>
+        <v>0.82228000000000001</v>
       </c>
       <c r="D154" s="40">
-        <f t="shared" si="9"/>
-        <v>0.81437124999999999</v>
+        <f t="shared" si="8"/>
+        <v>0.83523999999999998</v>
       </c>
       <c r="E154" s="40">
-        <f t="shared" si="9"/>
-        <v>0.90364750000000005</v>
+        <f t="shared" si="8"/>
+        <v>0.90551000000000004</v>
       </c>
       <c r="F154" s="16"/>
       <c r="G154" s="16"/>
@@ -40298,21 +40397,21 @@
       <c r="AC154" s="16"/>
     </row>
     <row r="155" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="89"/>
+      <c r="A155" s="77"/>
       <c r="B155" s="15">
         <v>10</v>
       </c>
       <c r="C155" s="40">
         <f t="shared" si="8"/>
-        <v>0.58938999999999997</v>
+        <v>0.78900000000000003</v>
       </c>
       <c r="D155" s="40">
-        <f t="shared" ref="D155:E161" si="10">D141/$B141</f>
-        <v>0.749533</v>
+        <f t="shared" si="8"/>
+        <v>0.77864999999999995</v>
       </c>
       <c r="E155" s="40">
-        <f t="shared" si="10"/>
-        <v>0.86001499999999997</v>
+        <f t="shared" si="8"/>
+        <v>0.86316999999999999</v>
       </c>
       <c r="F155" s="16"/>
       <c r="G155" s="16"/>
@@ -40340,21 +40439,21 @@
       <c r="AC155" s="16"/>
     </row>
     <row r="156" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="89"/>
+      <c r="A156" s="77"/>
       <c r="B156" s="15">
         <v>12</v>
       </c>
       <c r="C156" s="40">
         <f t="shared" si="8"/>
-        <v>0.56474999999999997</v>
+        <v>0.75746000000000002</v>
       </c>
       <c r="D156" s="40">
-        <f t="shared" si="10"/>
-        <v>0.78997583333333343</v>
+        <f t="shared" si="8"/>
+        <v>0.76207999999999998</v>
       </c>
       <c r="E156" s="40">
-        <f t="shared" si="10"/>
-        <v>0.84976583333333344</v>
+        <f t="shared" si="8"/>
+        <v>0.83343</v>
       </c>
       <c r="F156" s="31"/>
       <c r="G156" s="31"/>
@@ -40382,21 +40481,21 @@
       <c r="AC156" s="31"/>
     </row>
     <row r="157" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="89"/>
+      <c r="A157" s="77"/>
       <c r="B157" s="15">
         <v>14</v>
       </c>
       <c r="C157" s="40">
         <f t="shared" si="8"/>
-        <v>0.52703999999999995</v>
+        <v>0.69882999999999995</v>
       </c>
       <c r="D157" s="40">
-        <f t="shared" si="10"/>
-        <v>0.74510357142857142</v>
+        <f t="shared" si="8"/>
+        <v>0.69564000000000004</v>
       </c>
       <c r="E157" s="40">
-        <f t="shared" si="10"/>
-        <v>0.77667285714285705</v>
+        <f t="shared" si="8"/>
+        <v>0.76654999999999995</v>
       </c>
       <c r="F157" s="31"/>
       <c r="G157" s="31"/>
@@ -40424,21 +40523,21 @@
       <c r="AC157" s="31"/>
     </row>
     <row r="158" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="89"/>
+      <c r="A158" s="77"/>
       <c r="B158" s="15">
         <v>16</v>
       </c>
       <c r="C158" s="40">
         <f t="shared" si="8"/>
-        <v>0.49698999999999999</v>
+        <v>0.63815999999999995</v>
       </c>
       <c r="D158" s="40">
-        <f t="shared" si="10"/>
-        <v>0.69784500000000005</v>
+        <f t="shared" si="8"/>
+        <v>0.65868000000000004</v>
       </c>
       <c r="E158" s="40">
-        <f t="shared" si="10"/>
-        <v>0.76341562500000004</v>
+        <f t="shared" si="8"/>
+        <v>0.74028000000000005</v>
       </c>
       <c r="F158" s="16"/>
       <c r="G158" s="16"/>
@@ -40466,21 +40565,21 @@
       <c r="AC158" s="16"/>
     </row>
     <row r="159" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="89"/>
+      <c r="A159" s="77"/>
       <c r="B159" s="15">
         <v>18</v>
       </c>
       <c r="C159" s="40">
         <f t="shared" si="8"/>
-        <v>0.45942</v>
+        <v>0.60150000000000003</v>
       </c>
       <c r="D159" s="40">
-        <f t="shared" si="10"/>
-        <v>0.68232722222222231</v>
+        <f t="shared" si="8"/>
+        <v>0.62653999999999999</v>
       </c>
       <c r="E159" s="40">
-        <f t="shared" si="10"/>
-        <v>0.69256666666666666</v>
+        <f t="shared" si="8"/>
+        <v>0.69604999999999995</v>
       </c>
       <c r="F159" s="16"/>
       <c r="G159" s="16"/>
@@ -40508,21 +40607,21 @@
       <c r="AC159" s="16"/>
     </row>
     <row r="160" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A160" s="89"/>
+      <c r="A160" s="77"/>
       <c r="B160" s="15">
         <v>20</v>
       </c>
       <c r="C160" s="40">
         <f t="shared" si="8"/>
-        <v>0.45572000000000001</v>
+        <v>0.56169000000000002</v>
       </c>
       <c r="D160" s="40">
-        <f t="shared" si="10"/>
-        <v>0.62879799999999997</v>
+        <f t="shared" si="8"/>
+        <v>0.58848</v>
       </c>
       <c r="E160" s="40">
-        <f t="shared" si="10"/>
-        <v>0.70248749999999993</v>
+        <f t="shared" si="8"/>
+        <v>0.65332999999999997</v>
       </c>
       <c r="F160" s="16"/>
       <c r="G160" s="16"/>
@@ -40550,21 +40649,21 @@
       <c r="AC160" s="16"/>
     </row>
     <row r="161" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="89"/>
+      <c r="A161" s="77"/>
       <c r="B161" s="49">
         <v>40</v>
       </c>
       <c r="C161" s="50">
         <f t="shared" si="8"/>
-        <v>0.20244000000000001</v>
+        <v>0.25969999999999999</v>
       </c>
       <c r="D161" s="50">
-        <f t="shared" si="10"/>
-        <v>0.27811849999999999</v>
+        <f t="shared" si="8"/>
+        <v>0.28286</v>
       </c>
       <c r="E161" s="50">
-        <f t="shared" si="10"/>
-        <v>0.311776</v>
+        <f t="shared" si="8"/>
+        <v>0.31850000000000001</v>
       </c>
       <c r="F161" s="16"/>
       <c r="G161" s="16"/>
@@ -40592,73 +40691,153 @@
       <c r="AC161" s="16"/>
     </row>
     <row r="162" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A162" s="89"/>
+      <c r="A162" s="77"/>
       <c r="B162" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="C162" s="81" t="s">
-        <v>115</v>
-      </c>
-      <c r="D162" s="86"/>
-      <c r="E162" s="86"/>
-      <c r="F162" s="86"/>
-      <c r="G162" s="86"/>
-      <c r="H162" s="86"/>
-      <c r="I162" s="86"/>
-      <c r="J162" s="86"/>
-      <c r="K162" s="86"/>
-      <c r="L162" s="86"/>
-      <c r="M162" s="86"/>
-      <c r="N162" s="86"/>
-      <c r="O162" s="86"/>
-      <c r="P162" s="86"/>
-      <c r="Q162" s="86"/>
-      <c r="R162" s="86"/>
-      <c r="S162" s="86"/>
-      <c r="T162" s="86"/>
-      <c r="U162" s="86"/>
-      <c r="V162" s="86"/>
-      <c r="W162" s="86"/>
-      <c r="X162" s="86"/>
-      <c r="Y162" s="86"/>
-      <c r="Z162" s="86"/>
-      <c r="AA162" s="86"/>
-      <c r="AB162" s="86"/>
-      <c r="AC162" s="87"/>
+      <c r="C162" s="78" t="s">
+        <v>124</v>
+      </c>
+      <c r="D162" s="79"/>
+      <c r="E162" s="79"/>
+      <c r="F162" s="79"/>
+      <c r="G162" s="79"/>
+      <c r="H162" s="79"/>
+      <c r="I162" s="79"/>
+      <c r="J162" s="79"/>
+      <c r="K162" s="79"/>
+      <c r="L162" s="79"/>
+      <c r="M162" s="79"/>
+      <c r="N162" s="79"/>
+      <c r="O162" s="79"/>
+      <c r="P162" s="79"/>
+      <c r="Q162" s="79"/>
+      <c r="R162" s="79"/>
+      <c r="S162" s="79"/>
+      <c r="T162" s="79"/>
+      <c r="U162" s="79"/>
+      <c r="V162" s="79"/>
+      <c r="W162" s="79"/>
+      <c r="X162" s="79"/>
+      <c r="Y162" s="79"/>
+      <c r="Z162" s="79"/>
+      <c r="AA162" s="79"/>
+      <c r="AB162" s="79"/>
+      <c r="AC162" s="80"/>
+    </row>
+    <row r="164" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E164" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="F164" s="54" t="s">
+        <v>121</v>
+      </c>
+      <c r="G164" s="54" t="s">
+        <v>122</v>
+      </c>
+      <c r="H164" s="55" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="165" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B165" s="26" t="s">
-        <v>117</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="E165" s="54" t="s">
+        <v>119</v>
+      </c>
+      <c r="F165" s="54">
+        <v>331549</v>
+      </c>
+      <c r="G165" s="72">
+        <f>ROUND(F165/F166,5)</f>
+        <v>13.740690000000001</v>
+      </c>
+      <c r="H165" s="72">
+        <f>ROUND(G165/20,5)</f>
+        <v>0.68703000000000003</v>
+      </c>
+    </row>
+    <row r="166" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E166" s="52" t="s">
+        <v>120</v>
+      </c>
+      <c r="F166" s="54">
+        <v>24129</v>
+      </c>
+      <c r="G166" s="72"/>
+      <c r="H166" s="72"/>
     </row>
     <row r="167" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B167" s="26" t="s">
-        <v>118</v>
-      </c>
+        <v>117</v>
+      </c>
+    </row>
+    <row r="169" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B169" s="56"/>
+      <c r="C169" s="56"/>
+      <c r="D169" s="56"/>
+      <c r="E169" s="56"/>
+      <c r="F169" s="57"/>
+      <c r="G169" s="57"/>
+      <c r="H169" s="57"/>
+    </row>
+    <row r="170" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B170" s="56"/>
+      <c r="C170" s="56"/>
+      <c r="D170" s="56"/>
+      <c r="E170" s="56"/>
+      <c r="F170" s="57"/>
+      <c r="G170" s="57"/>
+      <c r="H170" s="57"/>
+    </row>
+    <row r="171" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B171" s="53"/>
+      <c r="C171" s="53"/>
+      <c r="D171" s="53"/>
+      <c r="E171" s="53"/>
+      <c r="F171" s="58"/>
+      <c r="G171" s="58"/>
+      <c r="H171" s="58"/>
+    </row>
+    <row r="172" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B172" s="53"/>
+      <c r="C172" s="53"/>
+      <c r="D172" s="53"/>
+      <c r="E172" s="53"/>
+      <c r="F172" s="53"/>
+      <c r="G172" s="53"/>
+      <c r="H172" s="53"/>
+    </row>
+    <row r="173" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B173" s="53"/>
+      <c r="C173" s="53"/>
+      <c r="D173" s="53"/>
+      <c r="E173" s="53"/>
+      <c r="F173" s="53"/>
+      <c r="G173" s="53"/>
+      <c r="H173" s="53"/>
+    </row>
+    <row r="174" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B174" s="53"/>
+      <c r="C174" s="53"/>
+      <c r="D174" s="53"/>
+      <c r="E174" s="53"/>
+      <c r="F174" s="53"/>
+      <c r="G174" s="53"/>
+      <c r="H174" s="53"/>
+    </row>
+    <row r="175" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B175" s="53"/>
+      <c r="C175" s="53"/>
+      <c r="D175" s="53"/>
+      <c r="E175" s="53"/>
+      <c r="F175" s="53"/>
+      <c r="G175" s="53"/>
+      <c r="H175" s="53"/>
     </row>
   </sheetData>
-  <mergeCells count="35">
-    <mergeCell ref="B148:E148"/>
-    <mergeCell ref="B134:E134"/>
-    <mergeCell ref="B120:E120"/>
-    <mergeCell ref="A120:A162"/>
-    <mergeCell ref="C162:AC162"/>
-    <mergeCell ref="A89:A119"/>
-    <mergeCell ref="C119:T119"/>
-    <mergeCell ref="B89:E89"/>
-    <mergeCell ref="B99:E99"/>
-    <mergeCell ref="B109:E109"/>
-    <mergeCell ref="A24:L24"/>
-    <mergeCell ref="M24:N24"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="C12:N12"/>
-    <mergeCell ref="A2:A12"/>
-    <mergeCell ref="A13:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:N23"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B2:D2"/>
+  <mergeCells count="37">
     <mergeCell ref="O88:T88"/>
     <mergeCell ref="A88:N88"/>
     <mergeCell ref="A57:A87"/>
@@ -40673,6 +40852,29 @@
     <mergeCell ref="B45:D45"/>
     <mergeCell ref="B35:D35"/>
     <mergeCell ref="B25:D25"/>
+    <mergeCell ref="A24:L24"/>
+    <mergeCell ref="M24:N24"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="C12:N12"/>
+    <mergeCell ref="A2:A12"/>
+    <mergeCell ref="A13:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:N23"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="A120:A162"/>
+    <mergeCell ref="C162:AC162"/>
+    <mergeCell ref="A89:A119"/>
+    <mergeCell ref="C119:T119"/>
+    <mergeCell ref="B89:E89"/>
+    <mergeCell ref="B99:E99"/>
+    <mergeCell ref="B109:E109"/>
+    <mergeCell ref="G165:G166"/>
+    <mergeCell ref="H165:H166"/>
+    <mergeCell ref="B148:E148"/>
+    <mergeCell ref="B134:E134"/>
+    <mergeCell ref="B120:E120"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <hyperlinks>
@@ -40731,4 +40933,24 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{971D527A-984B-4A9B-8624-22FA2B3C082C}">
+  <dimension ref="M10:M17"/>
+  <sheetFormatPr defaultRowHeight="22.1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="16384" width="9.140625" style="41"/>
+  </cols>
+  <sheetData>
+    <row r="10" spans="13:13" x14ac:dyDescent="0.3">
+      <c r="M10" s="44"/>
+    </row>
+    <row r="17" spans="13:13" x14ac:dyDescent="0.3">
+      <c r="M17" s="44"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>